--- a/leadrun_jewelry/jewelry_qualified.xlsx
+++ b/leadrun_jewelry/jewelry_qualified.xlsx
@@ -642,8 +642,16 @@
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Corey Friedman</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Featured On About Page</t>
+        </is>
+      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>https://coreyfriedman.com</t>
@@ -2978,8 +2986,16 @@
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Bob Cohen</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Featured On About Page</t>
+        </is>
+      </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
           <t>https://cohensjewelers.com</t>
@@ -4830,8 +4846,16 @@
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Ricardo Basta</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Featured On About Page</t>
+        </is>
+      </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
           <t>https://ricardobasta.com</t>
@@ -4942,8 +4966,16 @@
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Phyllis Incidis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
           <t>https://siorojewelry.com</t>
@@ -5146,8 +5178,16 @@
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Stephen Forward</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Featured On About Page</t>
+        </is>
+      </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
           <t>https://beverleyr.com</t>
@@ -5906,8 +5946,16 @@
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Stan Razny</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
           <t>https://www.razny.com</t>
@@ -6678,8 +6726,16 @@
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Lance Deutsch</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Featured On About Page</t>
+        </is>
+      </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
           <t>https://www.deutschhouston.com</t>
@@ -7338,8 +7394,16 @@
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Matthew Cooper</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Featured On About Page</t>
+        </is>
+      </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
           <t>https://www.kanonn.net</t>
@@ -11782,8 +11846,16 @@
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Andrea Hill</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
           <t>https://www.atlantajewelryshow.com</t>
@@ -12846,8 +12918,16 @@
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Ron DeSumma</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
           <t>https://desummaandwexler.com</t>
@@ -13170,8 +13250,16 @@
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Kenyatta Black</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
           <t>https://www.philadelphiadiamondco.com</t>
@@ -14562,8 +14650,16 @@
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Lia Davis Lombara</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
           <t>https://colbydavisofboston.com</t>
@@ -15699,7 +15795,7 @@
         <v>20</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -15726,7 +15822,7 @@
         <v>22</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -15753,7 +15849,7 @@
         <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -15780,7 +15876,7 @@
         <v>20</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -15861,7 +15957,7 @@
         <v>11</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -15888,7 +15984,7 @@
         <v>7</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -15942,7 +16038,7 @@
         <v>9</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -15969,7 +16065,7 @@
         <v>136</v>
       </c>
       <c r="F12" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -16113,7 +16209,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T19:16:28+05:30</t>
+          <t>2026-10-13T21:22:07+05:30</t>
         </is>
       </c>
     </row>

--- a/leadrun_jewelry/jewelry_qualified.xlsx
+++ b/leadrun_jewelry/jewelry_qualified.xlsx
@@ -15889,14 +15889,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>464</v>
+        <v>484</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -16051,7 +16051,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6511</v>
+        <v>6531</v>
       </c>
       <c r="C12" t="n">
         <v>136</v>
@@ -16209,7 +16209,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T21:22:07+05:30</t>
+          <t>2026-10-13T21:40:10+05:30</t>
         </is>
       </c>
     </row>
@@ -16230,7 +16230,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>6511</v>
+        <v>6531</v>
       </c>
     </row>
     <row r="4">

--- a/leadrun_jewelry/jewelry_qualified.xlsx
+++ b/leadrun_jewelry/jewelry_qualified.xlsx
@@ -8830,8 +8830,16 @@
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Luis Alvarez</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
           <t>https://palazzojewelers.com</t>
@@ -8871,7 +8879,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design</t>
+          <t>2 of 3, direct-line, custom-design, since-1995</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8893,7 +8901,7 @@
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr">
@@ -15889,7 +15897,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>484</v>
+        <v>500</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
@@ -15903,7 +15911,7 @@
         <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -15916,14 +15924,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="C7" t="n">
         <v>24</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -16051,7 +16059,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6531</v>
+        <v>6552</v>
       </c>
       <c r="C12" t="n">
         <v>136</v>
@@ -16065,7 +16073,7 @@
         <v>136</v>
       </c>
       <c r="F12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -16209,7 +16217,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T21:40:10+05:30</t>
+          <t>2026-10-13T22:00:18+05:30</t>
         </is>
       </c>
     </row>
@@ -16230,7 +16238,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>6531</v>
+        <v>6552</v>
       </c>
     </row>
     <row r="4">

--- a/leadrun_jewelry/jewelry_qualified.xlsx
+++ b/leadrun_jewelry/jewelry_qualified.xlsx
@@ -10318,8 +10318,16 @@
           <t>4805 SW 8th St, Miami, FL 33134, United States</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Coral Gables</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
       <c r="M91" t="inlineStr">
         <is>
           <t>Miami, FL</t>
@@ -10343,7 +10351,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-2021</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -10364,14 +10372,18 @@
       </c>
       <c r="W91" t="inlineStr">
         <is>
-          <t>Miami The Jeweler</t>
+          <t>Miami The Jeweler, Franky Joyeria Inc</t>
         </is>
       </c>
       <c r="X91" t="inlineStr"/>
       <c r="Y91" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z91" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>(305) 735-1256</t>
@@ -15924,14 +15936,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>661</v>
+        <v>737</v>
       </c>
       <c r="C7" t="n">
         <v>24</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -16059,7 +16071,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6552</v>
+        <v>6628</v>
       </c>
       <c r="C12" t="n">
         <v>136</v>
@@ -16217,7 +16229,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T22:00:18+05:30</t>
+          <t>2026-10-13T22:20:26+05:30</t>
         </is>
       </c>
     </row>
@@ -16238,7 +16250,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>6552</v>
+        <v>6628</v>
       </c>
     </row>
     <row r="4">

--- a/leadrun_jewelry/jewelry_qualified.xlsx
+++ b/leadrun_jewelry/jewelry_qualified.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qualified Leads'!$A$1:$AB$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qualified Leads'!$A$1:$AB$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB166"/>
+  <dimension ref="A1:AB169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -15670,7 +15670,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Regal Studio</t>
+          <t>Loring &amp; Co. Fine Jewelers</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -15680,48 +15680,48 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>(404) 846-2525</t>
+          <t>(256) 880-1909</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>info@regal.studio</t>
+          <t>jason@loringjewelers.com</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ben Tobian</t>
+          <t>Jason N. Jason</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Featured On About Page</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>https://regal.studio</t>
+          <t>https://www.loringjewelers.com</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>3384 Peachtree Rd NE #120, Atlanta, GA 30326, United States</t>
+          <t>800 Airport Road, HUNTSVILLE, AL 35802</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>HUNTSVILLE</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -15731,23 +15731,19 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O140" t="n">
-        <v>5</v>
-      </c>
-      <c r="P140" t="n">
-        <v>417</v>
-      </c>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
       <c r="Q140" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Regal+Studio/data=!4m7!3m6!1s0x88f5058e7ed1e263:0xd40fb192ce48ba78!8m2!3d33.8495051!4d-84.3656907!16s%2Fg%2F1tppst8z!19sChIJY-LRfo4F9YgReLpIzpKxD9Q</t>
+          <t>https://www.bbb.org/us/al/huntsville/profile/jewelry-stores/loring-co-fine-jewelers-0513-900026245</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, gia, bench, custom-design, since-1986</t>
+          <t>2 of 3, direct-line, gia, custom-design, since-1996</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
@@ -15757,81 +15753,89 @@
       </c>
       <c r="T140" s="2" t="inlineStr">
         <is>
-          <t>https://regal.studio/</t>
+          <t>https://www.loringjewelers.com/company/our-team/jason-n/</t>
         </is>
       </c>
       <c r="U140" t="inlineStr"/>
       <c r="V140" t="inlineStr">
         <is>
-          <t>2026-10-13T17:52:42+05:30</t>
-        </is>
-      </c>
-      <c r="W140" t="inlineStr">
-        <is>
-          <t>Essex Fine Jewelry &amp; Watches, Essex Fine Jewelry, Essex Fine Jewelry + Watches, Regal Fine Jewelry, Elan Diamond Group</t>
-        </is>
-      </c>
+          <t>2026-10-13T22:44:26+05:30</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr"/>
       <c r="Y140" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z140" t="inlineStr"/>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>(404) 481-5555, (404) 643-8855</t>
+          <t>(256) 425-5834</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>https://instagram.com/regalstudiojewelry, https://facebook.com/profile.php?id=61573410419630, https://twitter.com/rccdiamond, https://x.com/i/grok, https://facebook.com/pages/EssexFineJewelry/2110724562359992, https://instagram.com/essexfinejewelry</t>
+          <t>https://instagram.com/loringandco, https://facebook.com/loringandco, https://instagram.com/loringandco/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Royal Jewelry &amp; Watches</t>
+          <t>Markman's Diamonds</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Wholesale jeweler</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>(404) 661-0410</t>
+          <t>(423) 894-7581</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>online@royaljewelrywholesale.com</t>
+          <t>info@markmansdiamonds.com</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Scott Burnett</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>https://www.royaljewelrywholesale.com</t>
+          <t>https://www.markmansdiamonds.com</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Atlanta, GA 30303, United States</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
+          <t>2104 Hamilton Place Blvd, Chattanooga, TN 37421-6001</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Chattanooga</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
       <c r="M141" t="inlineStr">
         <is>
           <t>Atlanta, GA</t>
@@ -15839,23 +15843,19 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O141" t="n">
-        <v>3</v>
-      </c>
-      <c r="P141" t="n">
-        <v>4</v>
-      </c>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr"/>
       <c r="Q141" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Royal+Jewelry+%26+Watches/data=!4m7!3m6!1s0x88f5056fe87f5de3:0x338ab8feb6338180!8m2!3d33.7602601!4d-84.389627!16s%2Fg%2F11f7r13z_k!19sChIJ411_6G8F9YgRgIEztv64ijM</t>
+          <t>https://www.bbb.org/us/tn/chattanooga/profile/jewelry-stores/markmans-diamonds-0483-4741</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design</t>
+          <t>2 of 3, role-email, direct-line, gia, since-1976</t>
         </is>
       </c>
       <c r="S141" t="inlineStr">
@@ -15865,13 +15865,13 @@
       </c>
       <c r="T141" s="2" t="inlineStr">
         <is>
-          <t>https://www.royaljewelrywholesale.com/pages/contact</t>
+          <t>https://www.markmansdiamonds.com/</t>
         </is>
       </c>
       <c r="U141" t="inlineStr"/>
       <c r="V141" t="inlineStr">
         <is>
-          <t>2026-10-13T17:56:45+05:30</t>
+          <t>2026-10-13T22:39:14+05:30</t>
         </is>
       </c>
       <c r="W141" t="inlineStr"/>
@@ -15882,57 +15882,65 @@
       <c r="Z141" t="inlineStr"/>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>(404) 840-7535</t>
+          <t>(865) 584-0247</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>https://instagram.com/royalwholesale.atl</t>
+          <t>https://instagram.com/markmansdiamonds, https://facebook.com/MarkmansDiamonds, https://instagram.com/markmansdiamonds/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S.B. Company Jewelers</t>
+          <t>Regal Studio</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Buyers</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>(770) 960-0001</t>
+          <t>(404) 846-2525</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>ahouston@southlakemall.com</t>
+          <t>info@regal.studio</t>
         </is>
       </c>
       <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Ben Tobian</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>https://www.southlakemall.com</t>
+          <t>https://regal.studio</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>1000 Southlake Mall, Morrow, GA 30260</t>
+          <t>3384 Peachtree Rd NE #120, Atlanta, GA 30326, United States</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Morrow</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -15947,19 +15955,23 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O142" t="inlineStr"/>
-      <c r="P142" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O142" t="n">
+        <v>5</v>
+      </c>
+      <c r="P142" t="n">
+        <v>417</v>
+      </c>
       <c r="Q142" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/morrow-ga/mip/s-b-company-jewelers-529548766</t>
+          <t>https://www.google.com/maps/place/Regal+Studio/data=!4m7!3m6!1s0x88f5058e7ed1e263:0xd40fb192ce48ba78!8m2!3d33.8495051!4d-84.3656907!16s%2Fg%2F1tppst8z!19sChIJY-LRfo4F9YgReLpIzpKxD9Q</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, role-email, direct-line, gia, bench, custom-design, since-1986</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
@@ -15969,56 +15981,64 @@
       </c>
       <c r="T142" s="2" t="inlineStr">
         <is>
-          <t>https://www.southlakemall.com/contact-us</t>
+          <t>https://regal.studio/</t>
         </is>
       </c>
       <c r="U142" t="inlineStr"/>
       <c r="V142" t="inlineStr">
         <is>
-          <t>2026-10-13T16:49:48+05:30</t>
-        </is>
-      </c>
-      <c r="W142" t="inlineStr"/>
+          <t>2026-10-13T17:52:42+05:30</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Essex Fine Jewelry &amp; Watches, Essex Fine Jewelry, Essex Fine Jewelry + Watches, Regal Fine Jewelry, Elan Diamond Group</t>
+        </is>
+      </c>
       <c r="X142" t="inlineStr"/>
       <c r="Y142" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z142" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>(770) 961-1050</t>
+          <t>(404) 481-5555, (404) 643-8855</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>https://facebook.com/ShopSouthlakeMall, https://instagram.com/shopsouthlakemall</t>
+          <t>https://instagram.com/regalstudiojewelry, https://facebook.com/profile.php?id=61573410419630, https://twitter.com/rccdiamond, https://x.com/i/grok, https://facebook.com/pages/EssexFineJewelry/2110724562359992, https://instagram.com/essexfinejewelry</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SB Jewelers</t>
+          <t>Royal Jewelry &amp; Watches</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Repairing</t>
+          <t>Wholesale jeweler</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>(470) 926-1684</t>
+          <t>(404) 661-0410</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> info@sbjewelersga.com</t>
+          <t>online@royaljewelrywholesale.com</t>
         </is>
       </c>
       <c r="F143" t="inlineStr"/>
@@ -16026,24 +16046,16 @@
       <c r="H143" t="inlineStr"/>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>https://sbjewelersga.com</t>
+          <t>https://www.royaljewelrywholesale.com</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>256 Pharr Rd NE, Atlanta, GA 30305</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>Atlanta</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>GA</t>
-        </is>
-      </c>
+          <t>Atlanta, GA 30303, United States</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr">
         <is>
           <t>Atlanta, GA</t>
@@ -16051,19 +16063,23 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O143" t="inlineStr"/>
-      <c r="P143" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O143" t="n">
+        <v>3</v>
+      </c>
+      <c r="P143" t="n">
+        <v>4</v>
+      </c>
       <c r="Q143" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/atlanta-ga/mip/sb-jewelers-576536946</t>
+          <t>https://www.google.com/maps/place/Royal+Jewelry+%26+Watches/data=!4m7!3m6!1s0x88f5056fe87f5de3:0x338ab8feb6338180!8m2!3d33.7602601!4d-84.389627!16s%2Fg%2F11f7r13z_k!19sChIJ411_6G8F9YgRgIEztv64ijM</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, gia, custom-design</t>
+          <t>2 of 3, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S143" t="inlineStr">
@@ -16073,13 +16089,13 @@
       </c>
       <c r="T143" s="2" t="inlineStr">
         <is>
-          <t>https://sbjewelersga.com/</t>
+          <t>https://www.royaljewelrywholesale.com/pages/contact</t>
         </is>
       </c>
       <c r="U143" t="inlineStr"/>
       <c r="V143" t="inlineStr">
         <is>
-          <t>2026-10-13T16:48:20+05:30</t>
+          <t>2026-10-13T17:56:45+05:30</t>
         </is>
       </c>
       <c r="W143" t="inlineStr"/>
@@ -16090,19 +16106,19 @@
       <c r="Z143" t="inlineStr"/>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>(470) 461-9239, (678) 709-5911</t>
+          <t>(404) 840-7535</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>https://facebook.com/people/SB-Jewelers/61561749161475, https://instagram.com/sbcustomjewelers, https://instagram.com/thesbjewelers</t>
+          <t>https://instagram.com/royalwholesale.atl</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Celtic Knot Jewelry &amp; Co</t>
+          <t>S.B. Company Jewelers</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -16112,17 +16128,17 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Jewelry Buyers</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>(201) 613-2309</t>
+          <t>(770) 960-0001</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>orders@celtic-knot.com</t>
+          <t>ahouston@southlakemall.com</t>
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
@@ -16130,27 +16146,27 @@
       <c r="H144" t="inlineStr"/>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>https://celtic-knot.com</t>
+          <t>https://www.southlakemall.com</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>25 Lane Ave, Gloucester City, NJ 08030</t>
+          <t>1000 Southlake Mall, Morrow, GA 30260</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Gloucester City</t>
+          <t>Morrow</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -16162,12 +16178,12 @@
       <c r="P144" t="inlineStr"/>
       <c r="Q144" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/gloucester-city-nj/mip/celtic-knot-jewelry-co-561012234</t>
+          <t>https://www.yellowpages.com/morrow-ga/mip/s-b-company-jewelers-529548766</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S144" t="inlineStr">
@@ -16177,13 +16193,13 @@
       </c>
       <c r="T144" s="2" t="inlineStr">
         <is>
-          <t>https://celtic-knot.com/pages/contact</t>
+          <t>https://www.southlakemall.com/contact-us</t>
         </is>
       </c>
       <c r="U144" t="inlineStr"/>
       <c r="V144" t="inlineStr">
         <is>
-          <t>2026-10-13T16:51:38+05:30</t>
+          <t>2026-10-13T16:49:48+05:30</t>
         </is>
       </c>
       <c r="W144" t="inlineStr"/>
@@ -16194,75 +16210,67 @@
       <c r="Z144" t="inlineStr"/>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>(314) 455-6688, (317) 455-6688</t>
+          <t>(770) 961-1050</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>https://instagram.com/mycelticknotjewellery</t>
+          <t>https://facebook.com/ShopSouthlakeMall, https://instagram.com/shopsouthlakemall</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>DeSumma &amp; Wexler Fine Jewelry, INC</t>
+          <t>SB Jewelers</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Appraisers</t>
+          <t>Jewelers, Jewelry Repairing</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>(215) 627-5379</t>
+          <t>(470) 926-1684</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>dandw@desummaandwexler.com</t>
+          <t xml:space="preserve"> info@sbjewelersga.com</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>Ron DeSumma</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>https://desummaandwexler.com</t>
+          <t>https://sbjewelersga.com</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>734 Sansom St, Philadelphia, PA 19106</t>
+          <t>256 Pharr Rd NE, Atlanta, GA 30305</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -16270,20 +16278,16 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O145" t="n">
-        <v>5</v>
-      </c>
-      <c r="P145" t="n">
-        <v>221</v>
-      </c>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
       <c r="Q145" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/philadelphia-pa/mip/desumma-wexler-fine-jewelry-inc-12226752</t>
+          <t>https://www.yellowpages.com/atlanta-ga/mip/sb-jewelers-576536946</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design, since-1993</t>
+          <t>2 of 3, role-email, direct-line, gia, custom-design</t>
         </is>
       </c>
       <c r="S145" t="inlineStr">
@@ -16293,105 +16297,109 @@
       </c>
       <c r="T145" s="2" t="inlineStr">
         <is>
-          <t>https://desummaandwexler.com/</t>
+          <t>https://sbjewelersga.com/</t>
         </is>
       </c>
       <c r="U145" t="inlineStr"/>
       <c r="V145" t="inlineStr">
         <is>
-          <t>2026-10-13T16:50:14+05:30</t>
+          <t>2026-10-13T16:48:20+05:30</t>
         </is>
       </c>
       <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr"/>
       <c r="Y145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z145" t="inlineStr"/>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>(445) 248-6111</t>
+          <t>(470) 461-9239, (678) 709-5911</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>https://facebook.com/DeSummaWexler</t>
+          <t>https://facebook.com/people/SB-Jewelers/61561749161475, https://instagram.com/sbcustomjewelers, https://instagram.com/thesbjewelers</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Ellis Antiques</t>
+          <t>Ware Jewelers, Inc.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Jewelers, Antiques</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>(856) 854-6346</t>
+          <t>(334) 821-7375</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>ellisantiq@aol.com</t>
+          <t>ronnie@warejewelers.com</t>
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Steven Lagos</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>https://www.ellisantique.com</t>
+          <t>https://www.warejewelers.com</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>812 Haddon Ave, Collingswood, NJ 08108</t>
+          <t>111 S College St, Auburn, AL 36830-5418</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Collingswood</t>
+          <t>Auburn</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O146" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P146" t="n">
-        <v>2</v>
-      </c>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
       <c r="Q146" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/collingswood-nj/mip/ellis-antiques-2155204</t>
+          <t>https://www.bbb.org/us/al/opelika/profile/jewelry-stores/ware-jewelers-inc-0743-107725</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, direct-line, bench, custom-design, since-1946</t>
         </is>
       </c>
       <c r="S146" t="inlineStr">
@@ -16401,36 +16409,36 @@
       </c>
       <c r="T146" s="2" t="inlineStr">
         <is>
-          <t>https://ellisantique.com/contact-us/</t>
+          <t>https://www.warejewelers.com/</t>
         </is>
       </c>
       <c r="U146" t="inlineStr"/>
       <c r="V146" t="inlineStr">
         <is>
-          <t>2026-10-13T16:51:53+05:30</t>
+          <t>2026-10-13T22:39:59+05:30</t>
         </is>
       </c>
       <c r="W146" t="inlineStr"/>
       <c r="X146" t="inlineStr"/>
       <c r="Y146" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z146" t="inlineStr"/>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>(856) 905-3339</t>
+          <t>(334) 826-9000</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>https://facebook.com/EllisAntiques, https://instagram.com/ellisantiquescollingswood, https://twitter.com/EllisAntiques</t>
+          <t>https://facebook.com/WareJewelers1946, https://twitter.com/WareJewelers, https://instagram.com/warejewelers</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Paul Morelli</t>
+          <t>Celtic Knot Jewelry &amp; Co</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -16440,17 +16448,17 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>(215) 922-7392</t>
+          <t>(201) 613-2309</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>concierge@paulmorelli.com</t>
+          <t>orders@celtic-knot.com</t>
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
@@ -16458,22 +16466,22 @@
       <c r="H147" t="inlineStr"/>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>https://www.paulmorelli.com</t>
+          <t>https://celtic-knot.com</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>1118 Walnut St, Philadelphia, PA 19107</t>
+          <t>25 Lane Ave, Gloucester City, NJ 08030</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Gloucester City</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -16490,7 +16498,7 @@
       <c r="P147" t="inlineStr"/>
       <c r="Q147" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/philadelphia-pa/mip/paul-morelli-460503475</t>
+          <t>https://www.yellowpages.com/gloucester-city-nj/mip/celtic-knot-jewelry-co-561012234</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -16505,40 +16513,36 @@
       </c>
       <c r="T147" s="2" t="inlineStr">
         <is>
-          <t>https://paulmorelli.com/</t>
+          <t>https://celtic-knot.com/pages/contact</t>
         </is>
       </c>
       <c r="U147" t="inlineStr"/>
       <c r="V147" t="inlineStr">
         <is>
-          <t>2026-10-13T16:50:55+05:30</t>
-        </is>
-      </c>
-      <c r="W147" t="inlineStr">
-        <is>
-          <t>Paul Morelli Design Inc</t>
-        </is>
-      </c>
+          <t>2026-10-13T16:51:38+05:30</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr"/>
       <c r="X147" t="inlineStr"/>
       <c r="Y147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z147" t="inlineStr"/>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>(212) 585-4200</t>
+          <t>(314) 455-6688, (317) 455-6688</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>https://facebook.com/PaulMorelli.Designs, https://instagram.com/paulmorellistudio</t>
+          <t>https://instagram.com/mycelticknotjewellery</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Philadelphia Diamond Company</t>
+          <t>DeSumma &amp; Wexler Fine Jewelry, INC</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -16548,23 +16552,23 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Jeweler</t>
+          <t>Jewelers, Jewelry Appraisers</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>(215) 607-6700</t>
+          <t>(215) 627-5379</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>info@philadelphiadiamondco.com</t>
+          <t>dandw@desummaandwexler.com</t>
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Kenyatta Black</t>
+          <t>Ron DeSumma</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -16574,12 +16578,12 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>https://www.philadelphiadiamondco.com</t>
+          <t>https://desummaandwexler.com</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>421 Chestnut St, Philadelphia, PA 19106, United States</t>
+          <t>734 Sansom St, Philadelphia, PA 19106</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -16599,23 +16603,23 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O148" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P148" t="n">
-        <v>116</v>
+        <v>221</v>
       </c>
       <c r="Q148" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Philadelphia+Diamond+Company/data=!4m7!3m6!1s0x89c6c88116a871dd:0xc12679b6bb8c882e!8m2!3d39.9490554!4d-75.1483217!16s%2Fg%2F12q4s_d1z!19sChIJ3XGoFoHIxokRLoiMu7Z5JsE</t>
+          <t>https://www.yellowpages.com/philadelphia-pa/mip/desumma-wexler-fine-jewelry-inc-12226752</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, gia, custom-design</t>
+          <t>2 of 3, direct-line, gia, custom-design, since-1993</t>
         </is>
       </c>
       <c r="S148" t="inlineStr">
@@ -16625,64 +16629,56 @@
       </c>
       <c r="T148" s="2" t="inlineStr">
         <is>
-          <t>https://www.philadelphiadiamondco.com/pages/contact</t>
+          <t>https://desummaandwexler.com/</t>
         </is>
       </c>
       <c r="U148" t="inlineStr"/>
       <c r="V148" t="inlineStr">
         <is>
-          <t>2026-10-13T18:00:42+05:30</t>
-        </is>
-      </c>
-      <c r="W148" t="inlineStr">
-        <is>
-          <t>Phialdelphia Diamond Co, Philadelphia Diamond Co</t>
-        </is>
-      </c>
+          <t>2026-10-13T16:50:14+05:30</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr"/>
       <c r="X148" t="inlineStr"/>
       <c r="Y148" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Z148" t="inlineStr"/>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>(215) 607-6707, (215) 607-6710</t>
+          <t>(445) 248-6111</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>https://instagram.com/DiamondCompanyGroup, https://facebook.com/PhiladelphiaDiamondCompany</t>
+          <t>https://facebook.com/DeSummaWexler</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>S &amp; I Creations</t>
+          <t>Ellis Antiques</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Antiques</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>(215) 629-0260</t>
+          <t>(856) 854-6346</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>sales@sophiabydesign.com</t>
+          <t>ellisantiq@aol.com</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
@@ -16690,22 +16686,22 @@
       <c r="H149" t="inlineStr"/>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>https://www.sophiabydesign.com</t>
+          <t>https://www.ellisantique.com</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>125 S 9th St, Philadelphia, PA 19107</t>
+          <t>812 Haddon Ave, Collingswood, NJ 08108</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Collingswood</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -16718,16 +16714,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O149" t="inlineStr"/>
-      <c r="P149" t="inlineStr"/>
+      <c r="O149" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P149" t="n">
+        <v>2</v>
+      </c>
       <c r="Q149" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/philadelphia-pa/mip/s-i-creations-454700315</t>
+          <t>https://www.yellowpages.com/collingswood-nj/mip/ellis-antiques-2155204</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
@@ -16737,13 +16737,13 @@
       </c>
       <c r="T149" s="2" t="inlineStr">
         <is>
-          <t>https://www.sophiabydesign.com/</t>
+          <t>https://ellisantique.com/contact-us/</t>
         </is>
       </c>
       <c r="U149" t="inlineStr"/>
       <c r="V149" t="inlineStr">
         <is>
-          <t>2026-10-13T16:50:55+05:30</t>
+          <t>2026-10-13T16:51:53+05:30</t>
         </is>
       </c>
       <c r="W149" t="inlineStr"/>
@@ -16754,19 +16754,19 @@
       <c r="Z149" t="inlineStr"/>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>(215) 629-0513</t>
+          <t>(856) 905-3339</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>https://facebook.com/SophiaByDesign, https://instagram.com/sophia_by_design</t>
+          <t>https://facebook.com/EllisAntiques, https://instagram.com/ellisantiquescollingswood, https://twitter.com/EllisAntiques</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Sunny Rx</t>
+          <t>Paul Morelli</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -16776,17 +16776,17 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Jewelers, Criminal Law Attorneys, Home Health Services</t>
+          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>(610) 259-0660</t>
+          <t>(215) 922-7392</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>sunnypharmacypa@gmail.com</t>
+          <t>concierge@paulmorelli.com</t>
         </is>
       </c>
       <c r="F150" t="inlineStr"/>
@@ -16794,17 +16794,17 @@
       <c r="H150" t="inlineStr"/>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>https://www.sunnypharmacypa.com</t>
+          <t>https://www.paulmorelli.com</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>918 E Baltimore Ave, Lansdowne, PA 19050</t>
+          <t>1118 Walnut St, Philadelphia, PA 19107</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Lansdowne</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -16826,12 +16826,12 @@
       <c r="P150" t="inlineStr"/>
       <c r="Q150" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/lansdowne-pa/mip/sunny-rx-524592945</t>
+          <t>https://www.yellowpages.com/philadelphia-pa/mip/paul-morelli-460503475</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, since-2016</t>
+          <t>2 of 3, role-email, direct-line</t>
         </is>
       </c>
       <c r="S150" t="inlineStr">
@@ -16841,101 +16841,117 @@
       </c>
       <c r="T150" s="2" t="inlineStr">
         <is>
-          <t>https://sunnypharmacypa.com/</t>
+          <t>https://paulmorelli.com/</t>
         </is>
       </c>
       <c r="U150" t="inlineStr"/>
       <c r="V150" t="inlineStr">
         <is>
-          <t>2026-10-13T16:51:53+05:30</t>
-        </is>
-      </c>
-      <c r="W150" t="inlineStr"/>
+          <t>2026-10-13T16:50:55+05:30</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Paul Morelli Design Inc</t>
+        </is>
+      </c>
       <c r="X150" t="inlineStr"/>
       <c r="Y150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z150" t="inlineStr"/>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>(215) 839-9732</t>
-        </is>
-      </c>
-      <c r="AB150" t="inlineStr"/>
+          <t>(212) 585-4200</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>https://facebook.com/PaulMorelli.Designs, https://instagram.com/paulmorellistudio</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Amir H. Mozaffarian Fine Jewels</t>
+          <t>Philadelphia Diamond Company</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Jewelers, Watches, Watch Repair</t>
+          <t>Jeweler</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>(415) 391-9995</t>
+          <t>(215) 607-6700</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>info@amirhmozaffarian.com</t>
+          <t>info@philadelphiadiamondco.com</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Kenyatta Black</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>https://www.amirhmozaffarian.com</t>
+          <t>https://www.philadelphiadiamondco.com</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>155 Post St, San Francisco, CA 94108</t>
+          <t>421 Chestnut St, Philadelphia, PA 19106, United States</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O151" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P151" t="n">
-        <v>1</v>
+        <v>116</v>
       </c>
       <c r="Q151" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/san-francisco-ca/mip/amir-h-mozaffarian-fine-jewels-1428504</t>
+          <t>https://www.google.com/maps/place/Philadelphia+Diamond+Company/data=!4m7!3m6!1s0x89c6c88116a871dd:0xc12679b6bb8c882e!8m2!3d39.9490554!4d-75.1483217!16s%2Fg%2F12q4s_d1z!19sChIJ3XGoFoHIxokRLoiMu7Z5JsE</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line</t>
+          <t>2 of 3, role-email, direct-line, gia, custom-design</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
@@ -16945,36 +16961,44 @@
       </c>
       <c r="T151" s="2" t="inlineStr">
         <is>
-          <t>https://www.amirhmozaffarian.com/</t>
+          <t>https://www.philadelphiadiamondco.com/pages/contact</t>
         </is>
       </c>
       <c r="U151" t="inlineStr"/>
       <c r="V151" t="inlineStr">
         <is>
-          <t>2026-10-13T16:52:02+05:30</t>
-        </is>
-      </c>
-      <c r="W151" t="inlineStr"/>
+          <t>2026-10-13T18:00:42+05:30</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Phialdelphia Diamond Co, Philadelphia Diamond Co</t>
+        </is>
+      </c>
       <c r="X151" t="inlineStr"/>
       <c r="Y151" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z151" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>(415) 728-1401</t>
+          <t>(215) 607-6707, (215) 607-6710</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>https://facebook.com/AmirHMozaffarianFineJewels</t>
+          <t>https://instagram.com/DiamondCompanyGroup, https://facebook.com/PhiladelphiaDiamondCompany</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Baumell Pearl Co Inc</t>
+          <t>S &amp; I Creations</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -16984,17 +17008,17 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Jewelers, Pearls</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>(415) 421-2113</t>
+          <t>(215) 629-0260</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>info@baumellpearl.com</t>
+          <t>sales@sophiabydesign.com</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
@@ -17002,27 +17026,27 @@
       <c r="H152" t="inlineStr"/>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>https://www.baumellpearl.com</t>
+          <t>https://www.sophiabydesign.com</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>210 Post St, San Francisco, CA 94108</t>
+          <t>125 S 9th St, Philadelphia, PA 19107</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -17034,12 +17058,12 @@
       <c r="P152" t="inlineStr"/>
       <c r="Q152" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/san-francisco-ca/mip/baumell-pearl-co-inc-459129940</t>
+          <t>https://www.yellowpages.com/philadelphia-pa/mip/s-i-creations-454700315</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, since-1962</t>
+          <t>2 of 3, role-email, direct-line</t>
         </is>
       </c>
       <c r="S152" t="inlineStr">
@@ -17049,13 +17073,13 @@
       </c>
       <c r="T152" s="2" t="inlineStr">
         <is>
-          <t>https://www.baumellpearl.com/</t>
+          <t>https://www.sophiabydesign.com/</t>
         </is>
       </c>
       <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr">
         <is>
-          <t>2026-10-13T16:53:25+05:30</t>
+          <t>2026-10-13T16:50:55+05:30</t>
         </is>
       </c>
       <c r="W152" t="inlineStr"/>
@@ -17066,19 +17090,19 @@
       <c r="Z152" t="inlineStr"/>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>(201) 438-7400</t>
+          <t>(215) 629-0513</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>https://facebook.com/BaumellPearl</t>
+          <t>https://facebook.com/SophiaByDesign, https://instagram.com/sophia_by_design</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Bay Area Gold and Silver Buyers</t>
+          <t>Sunny Rx</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -17088,17 +17112,17 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Gold dealer</t>
+          <t>Jewelers, Criminal Law Attorneys, Home Health Services</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>(415) 233-9999</t>
+          <t>(610) 259-0660</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>bayareagsb@gmail.com</t>
+          <t>sunnypharmacypa@gmail.com</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -17106,40 +17130,44 @@
       <c r="H153" t="inlineStr"/>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>https://bayareagoldandsilverbuyers.com</t>
+          <t>https://www.sunnypharmacypa.com</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>780 Sutter St, San Francisco, CA 94109, United States</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
+          <t>918 E Baltimore Ave, Lansdowne, PA 19050</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Lansdowne</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O153" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P153" t="n">
-        <v>130</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
       <c r="Q153" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Bay+Area+Gold+and+Silver+Buyers/data=!4m7!3m6!1s0x808f7dc9530e4cf7:0x81d10cd4f7c2392a!8m2!3d37.7887655!4d-122.4133159!16s%2Fg%2F11b6pdgl9c!19sChIJ90wOU8l9j4ARKjnC99QM0YE</t>
+          <t>https://www.yellowpages.com/lansdowne-pa/mip/sunny-rx-524592945</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, direct-line, since-2016</t>
         </is>
       </c>
       <c r="S153" t="inlineStr">
@@ -17149,13 +17177,13 @@
       </c>
       <c r="T153" s="2" t="inlineStr">
         <is>
-          <t>https://bayareagoldandsilverbuyers.com/</t>
+          <t>https://sunnypharmacypa.com/</t>
         </is>
       </c>
       <c r="U153" t="inlineStr"/>
       <c r="V153" t="inlineStr">
         <is>
-          <t>2026-10-13T18:11:47+05:30</t>
+          <t>2026-10-13T16:51:53+05:30</t>
         </is>
       </c>
       <c r="W153" t="inlineStr"/>
@@ -17166,7 +17194,7 @@
       <c r="Z153" t="inlineStr"/>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>(832) 415-9999</t>
+          <t>(215) 839-9732</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr"/>
@@ -17174,7 +17202,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Dioro Jewelers</t>
+          <t>Amir H. Mozaffarian Fine Jewels</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -17184,17 +17212,17 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers, Watches</t>
+          <t>Jewelers, Watches, Watch Repair</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>(415) 864-8525</t>
+          <t>(415) 391-9995</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>diorousa@gmail.com</t>
+          <t>info@amirhmozaffarian.com</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
@@ -17202,12 +17230,12 @@
       <c r="H154" t="inlineStr"/>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>https://www.diorojewelers.com</t>
+          <t>https://www.amirhmozaffarian.com</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>888 Brannan St Ste 182, San Francisco, CA 94103</t>
+          <t>155 Post St, San Francisco, CA 94108</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -17231,19 +17259,19 @@
         </is>
       </c>
       <c r="O154" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P154" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q154" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/san-francisco-ca/mip/dioro-jewelers-451651517</t>
+          <t>https://www.yellowpages.com/san-francisco-ca/mip/amir-h-mozaffarian-fine-jewels-1428504</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design</t>
+          <t>2 of 3, role-email, direct-line</t>
         </is>
       </c>
       <c r="S154" t="inlineStr">
@@ -17253,36 +17281,36 @@
       </c>
       <c r="T154" s="2" t="inlineStr">
         <is>
-          <t>https://diorojewelers.com/</t>
+          <t>https://www.amirhmozaffarian.com/</t>
         </is>
       </c>
       <c r="U154" t="inlineStr"/>
       <c r="V154" t="inlineStr">
         <is>
-          <t>2026-10-13T16:53:06+05:30</t>
+          <t>2026-10-13T16:52:02+05:30</t>
         </is>
       </c>
       <c r="W154" t="inlineStr"/>
       <c r="X154" t="inlineStr"/>
       <c r="Y154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z154" t="inlineStr"/>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>(925) 837-2340</t>
+          <t>(415) 728-1401</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>https://instagram.com/diorojewelers, https://facebook.com/people/Dioro-Jewelers/61568258612586</t>
+          <t>https://facebook.com/AmirHMozaffarianFineJewels</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Edward's Jewelry &amp; Imports</t>
+          <t>Baumell Pearl Co Inc</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -17292,17 +17320,17 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Jeweler</t>
+          <t>Jewelers, Pearls</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>(628) 257-7990</t>
+          <t>(415) 421-2113</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>edwardsjewelryimports@gmail.com</t>
+          <t>info@baumellpearl.com</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
@@ -17310,12 +17338,12 @@
       <c r="H155" t="inlineStr"/>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>https://edwardsjewelryimports.com</t>
+          <t>https://www.baumellpearl.com</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>888 Brannan St #160, San Francisco, CA 94103, United States</t>
+          <t>210 Post St, San Francisco, CA 94108</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -17335,23 +17363,19 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O155" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P155" t="n">
-        <v>19</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr"/>
       <c r="Q155" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Edward%27s+Jewelry+%26+Imports/data=!4m7!3m6!1s0x808f7e2c76ed152d:0x5152324c7a03dba!8m2!3d37.7717311!4d-122.4051118!16s%2Fg%2F1tg2dqt5!19sChIJLRXtdix-j4ARuj2gxyQjFQU</t>
+          <t>https://www.yellowpages.com/san-francisco-ca/mip/baumell-pearl-co-inc-459129940</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design, since-1983</t>
+          <t>2 of 3, role-email, direct-line, since-1962</t>
         </is>
       </c>
       <c r="S155" t="inlineStr">
@@ -17361,60 +17385,56 @@
       </c>
       <c r="T155" s="2" t="inlineStr">
         <is>
-          <t>https://edwardsjewelryimports.com/pages/contact</t>
+          <t>https://www.baumellpearl.com/</t>
         </is>
       </c>
       <c r="U155" t="inlineStr"/>
       <c r="V155" t="inlineStr">
         <is>
-          <t>2026-10-13T18:12:11+05:30</t>
-        </is>
-      </c>
-      <c r="W155" t="inlineStr">
-        <is>
-          <t>Edwards Jewelry &amp; Imports</t>
-        </is>
-      </c>
+          <t>2026-10-13T16:53:25+05:30</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr"/>
       <c r="X155" t="inlineStr"/>
       <c r="Y155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z155" t="inlineStr"/>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>(415) 877-3730</t>
+          <t>(201) 438-7400</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>https://facebook.com/EdwardJewelry, https://instagram.com/edwardsjewelry160/, https://instagram.com/edwardsjewelry160</t>
+          <t>https://facebook.com/BaumellPearl</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Shreve &amp; Co.</t>
+          <t>Bay Area Gold and Silver Buyers</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>shop=jewelry</t>
+          <t>Gold dealer</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>(415) 421-2600</t>
+          <t>(415) 233-9999</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>sales@shreve.com</t>
+          <t>bayareagsb@gmail.com</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
@@ -17422,24 +17442,16 @@
       <c r="H156" t="inlineStr"/>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>https://shreve.com</t>
+          <t>https://bayareagoldandsilverbuyers.com</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>150 Post Street, San Francisco, CA 94108</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
+          <t>780 Sutter St, San Francisco, CA 94109, United States</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr">
         <is>
           <t>San Francisco, CA</t>
@@ -17447,19 +17459,23 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>OpenStreetMap</t>
-        </is>
-      </c>
-      <c r="O156" t="inlineStr"/>
-      <c r="P156" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O156" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P156" t="n">
+        <v>130</v>
+      </c>
       <c r="Q156" s="2" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/4625205007</t>
+          <t>https://www.google.com/maps/place/Bay+Area+Gold+and+Silver+Buyers/data=!4m7!3m6!1s0x808f7dc9530e4cf7:0x81d10cd4f7c2392a!8m2!3d37.7887655!4d-122.4133159!16s%2Fg%2F11b6pdgl9c!19sChIJ90wOU8l9j4ARKjnC99QM0YE</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S156" t="inlineStr">
@@ -17469,13 +17485,13 @@
       </c>
       <c r="T156" s="2" t="inlineStr">
         <is>
-          <t>https://shreve.com/</t>
+          <t>https://bayareagoldandsilverbuyers.com/</t>
         </is>
       </c>
       <c r="U156" t="inlineStr"/>
       <c r="V156" t="inlineStr">
         <is>
-          <t>2026-10-13T17:30:25+05:30</t>
+          <t>2026-10-13T18:11:47+05:30</t>
         </is>
       </c>
       <c r="W156" t="inlineStr"/>
@@ -17486,39 +17502,35 @@
       <c r="Z156" t="inlineStr"/>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>(650) 327-2211</t>
-        </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>https://facebook.com/shreveandco, https://instagram.com/shreveco</t>
-        </is>
-      </c>
+          <t>(832) 415-9999</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>The Pearl Factory</t>
+          <t>Dioro Jewelers</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Designers</t>
+          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers, Watches</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>(415) 928-0963</t>
+          <t>(415) 864-8525</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>customerservice@pearl-factory.com</t>
+          <t>diorousa@gmail.com</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -17526,12 +17538,12 @@
       <c r="H157" t="inlineStr"/>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>https://www.pearl-factory.com</t>
+          <t>https://www.diorojewelers.com</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>271 Jefferson St, San Francisco, CA 94133</t>
+          <t>888 Brannan St Ste 182, San Francisco, CA 94103</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -17554,16 +17566,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O157" t="inlineStr"/>
-      <c r="P157" t="inlineStr"/>
+      <c r="O157" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P157" t="n">
+        <v>6</v>
+      </c>
       <c r="Q157" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/san-francisco-ca/mip/the-pearl-factory-3059205</t>
+          <t>https://www.yellowpages.com/san-francisco-ca/mip/dioro-jewelers-451651517</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, since-1924</t>
+          <t>2 of 3, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S157" t="inlineStr">
@@ -17573,56 +17589,56 @@
       </c>
       <c r="T157" s="2" t="inlineStr">
         <is>
-          <t>https://www.pearl-factory.com/</t>
+          <t>https://diorojewelers.com/</t>
         </is>
       </c>
       <c r="U157" t="inlineStr"/>
       <c r="V157" t="inlineStr">
         <is>
-          <t>2026-10-13T16:53:29+05:30</t>
-        </is>
-      </c>
-      <c r="W157" t="inlineStr">
-        <is>
-          <t>Pearl Factory</t>
-        </is>
-      </c>
+          <t>2026-10-13T16:53:06+05:30</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr"/>
       <c r="X157" t="inlineStr"/>
       <c r="Y157" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z157" t="inlineStr"/>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>(407) 704-0564, (415) 421-0920, (619) 226-3677, (702) 207-0033, (702) 798-3342, (702) 836-1935, (702) 891-0525, (808) 293-2980, (808) 327-1749, (808) 661-8042, (808) 886-5019, (808) 942-2447, (831) 612-7320</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr"/>
+          <t>(925) 837-2340</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>https://instagram.com/diorojewelers, https://facebook.com/people/Dioro-Jewelers/61568258612586</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Art Carl Jewelers &amp; AC Loan</t>
+          <t>Edward's Jewelry &amp; Imports</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Jewelers, Gold, Silver &amp; Platinum Buyers &amp; Dealers, Antiques</t>
+          <t>Jeweler</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>(781) 322-4551</t>
+          <t>(628) 257-7990</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>artcarljewelers@gmail.com</t>
+          <t>edwardsjewelryimports@gmail.com</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
@@ -17630,44 +17646,48 @@
       <c r="H158" t="inlineStr"/>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>https://www.artcarljewelers.com</t>
+          <t>https://edwardsjewelryimports.com</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>56 Pleasant St, Malden, MA 02148</t>
+          <t>888 Brannan St #160, San Francisco, CA 94103, United States</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Malden</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O158" t="inlineStr"/>
-      <c r="P158" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O158" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P158" t="n">
+        <v>19</v>
+      </c>
       <c r="Q158" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/malden-ma/mip/art-carl-jewelers-ac-loan-1806518</t>
+          <t>https://www.google.com/maps/place/Edward%27s+Jewelry+%26+Imports/data=!4m7!3m6!1s0x808f7e2c76ed152d:0x5152324c7a03dba!8m2!3d37.7717311!4d-122.4051118!16s%2Fg%2F1tg2dqt5!19sChIJLRXtdix-j4ARuj2gxyQjFQU</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia</t>
+          <t>2 of 3, direct-line, gia, custom-design, since-1983</t>
         </is>
       </c>
       <c r="S158" t="inlineStr">
@@ -17677,52 +17697,60 @@
       </c>
       <c r="T158" s="2" t="inlineStr">
         <is>
-          <t>https://artcarljewelers.com/</t>
+          <t>https://edwardsjewelryimports.com/pages/contact</t>
         </is>
       </c>
       <c r="U158" t="inlineStr"/>
       <c r="V158" t="inlineStr">
         <is>
-          <t>2026-10-13T16:54:39+05:30</t>
-        </is>
-      </c>
-      <c r="W158" t="inlineStr"/>
+          <t>2026-10-13T18:12:11+05:30</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Edwards Jewelry &amp; Imports</t>
+        </is>
+      </c>
       <c r="X158" t="inlineStr"/>
       <c r="Y158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z158" t="inlineStr"/>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>(781) 321-2242</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr"/>
+          <t>(415) 877-3730</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>https://facebook.com/EdwardJewelry, https://instagram.com/edwardsjewelry160/, https://instagram.com/edwardsjewelry160</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Barmakian Brothers</t>
+          <t>Shreve &amp; Co.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers, Diamonds-Wholesale</t>
+          <t>shop=jewelry</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>(617) 227-3724</t>
+          <t>(415) 421-2600</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>diamonds@barmakian.com</t>
+          <t>sales@shreve.com</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -17730,48 +17758,44 @@
       <c r="H159" t="inlineStr"/>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>https://www.barmakian.com</t>
+          <t>https://shreve.com</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>333 Washington St, Boston, MA 02108</t>
+          <t>150 Post Street, San Francisco, CA 94108</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O159" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P159" t="n">
-        <v>249</v>
-      </c>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr"/>
       <c r="Q159" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/boston-ma/mip/barmakian-brothers-467708515</t>
+          <t>https://www.openstreetmap.org/node/4625205007</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design, since-1910</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
@@ -17781,100 +17805,84 @@
       </c>
       <c r="T159" s="2" t="inlineStr">
         <is>
-          <t>https://www.barmakian.com/pages/about</t>
+          <t>https://shreve.com/</t>
         </is>
       </c>
       <c r="U159" t="inlineStr"/>
       <c r="V159" t="inlineStr">
         <is>
-          <t>2026-10-13T16:53:38+05:30</t>
-        </is>
-      </c>
-      <c r="W159" t="inlineStr">
-        <is>
-          <t>Jewelers Building Boston, Barmakian Jewelers, G A Chapman Co, Gigian Jewelers</t>
-        </is>
-      </c>
+          <t>2026-10-13T17:30:25+05:30</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr"/>
       <c r="X159" t="inlineStr"/>
       <c r="Y159" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z159" t="inlineStr"/>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>(508) 872-5454, (603) 888-7800</t>
+          <t>(650) 327-2211</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>https://facebook.com/BarmakianJewelers, https://instagram.com/barmakian, https://facebook.com/JewelersBuildingofBoston, https://instagram.com/jewelersbuilding333</t>
+          <t>https://facebook.com/shreveandco, https://instagram.com/shreveco</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Bouvier Jewelers</t>
+          <t>The Pearl Factory</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Jewelry Designers</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>(781) 643-0084</t>
+          <t>(415) 928-0963</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>jeffbouvier@comcast.net</t>
+          <t>customerservice@pearl-factory.com</t>
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>Jeff Bouvier</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>https://www.bouvierjewelersfordiamonds.com</t>
+          <t>https://www.pearl-factory.com</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>1310 Massachusetts Ave, Arlington, MA 02476</t>
+          <t>271 Jefferson St, San Francisco, CA 94133</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Arlington</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -17882,20 +17890,16 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O160" t="n">
-        <v>5</v>
-      </c>
-      <c r="P160" t="n">
-        <v>7</v>
-      </c>
+      <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr"/>
       <c r="Q160" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/arlington-ma/mip/bouvier-jewelers-7985346</t>
+          <t>https://www.yellowpages.com/san-francisco-ca/mip/the-pearl-factory-3059205</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, since-1956</t>
+          <t>2 of 3, role-email, direct-line, since-1924</t>
         </is>
       </c>
       <c r="S160" t="inlineStr">
@@ -17905,85 +17909,81 @@
       </c>
       <c r="T160" s="2" t="inlineStr">
         <is>
-          <t>https://www.bouvierjewelersfordiamonds.com/</t>
+          <t>https://www.pearl-factory.com/</t>
         </is>
       </c>
       <c r="U160" t="inlineStr"/>
       <c r="V160" t="inlineStr">
         <is>
-          <t>2026-10-13T16:54:34+05:30</t>
-        </is>
-      </c>
-      <c r="W160" t="inlineStr"/>
+          <t>2026-10-13T16:53:29+05:30</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Pearl Factory</t>
+        </is>
+      </c>
       <c r="X160" t="inlineStr"/>
       <c r="Y160" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="Z160" t="inlineStr"/>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>(617) 877-1603</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>https://facebook.com/Bouvier-Jewelers-103598593066674</t>
-        </is>
-      </c>
+          <t>(407) 704-0564, (415) 421-0920, (619) 226-3677, (702) 207-0033, (702) 798-3342, (702) 836-1935, (702) 891-0525, (808) 293-2980, (808) 327-1749, (808) 661-8042, (808) 886-5019, (808) 942-2447, (831) 612-7320</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Colby Davis of Boston</t>
+          <t>Art Carl Jewelers &amp; AC Loan</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers, Gold, Silver &amp; Platinum Buyers &amp; Dealers, Antiques</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>(978) 836-8654</t>
+          <t>(781) 322-4551</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>customerservice@colbydavisofboston.com</t>
+          <t>artcarljewelers@gmail.com</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>Lia Davis Lombara</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>https://colbydavisofboston.com</t>
+          <t>https://www.artcarljewelers.com</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>33 Newbury St, Boston, MA 02116, United States</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
+          <t>56 Pleasant St, Malden, MA 02148</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Malden</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
       <c r="M161" t="inlineStr">
         <is>
           <t>Boston, MA</t>
@@ -17991,23 +17991,19 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O161" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P161" t="n">
-        <v>12</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr"/>
       <c r="Q161" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Colby+Davis+of+Boston/data=!4m7!3m6!1s0x89e37b8729691633:0x31e1a7207b36ff89!8m2!3d42.3524611!4d-71.0729092!16s%2Fg%2F11l1f7k01g!19sChIJMxZpKYd744kRif82eyCn4TE</t>
+          <t>https://www.yellowpages.com/malden-ma/mip/art-carl-jewelers-ac-loan-1806518</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line</t>
+          <t>2 of 3, direct-line, gia</t>
         </is>
       </c>
       <c r="S161" t="inlineStr">
@@ -18017,13 +18013,13 @@
       </c>
       <c r="T161" s="2" t="inlineStr">
         <is>
-          <t>https://colbydavisofboston.com/pages/about-us</t>
+          <t>https://artcarljewelers.com/</t>
         </is>
       </c>
       <c r="U161" t="inlineStr"/>
       <c r="V161" t="inlineStr">
         <is>
-          <t>2026-10-13T18:20:06+05:30</t>
+          <t>2026-10-13T16:54:39+05:30</t>
         </is>
       </c>
       <c r="W161" t="inlineStr"/>
@@ -18034,60 +18030,48 @@
       <c r="Z161" t="inlineStr"/>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>(978) 375-4456</t>
-        </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>https://facebook.com/colbydavisofboston, https://instagram.com/colbydavisofboston</t>
-        </is>
-      </c>
+          <t>(781) 321-2242</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Cynthia Britt Custom Jewelry</t>
+          <t>Barmakian Brothers</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Designers</t>
+          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers, Diamonds-Wholesale</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>(857) 239-9885</t>
+          <t>(617) 227-3724</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>cynthia@cynthiabritt.com</t>
+          <t>diamonds@barmakian.com</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>Cynthia Pischdotchian</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Featured On About Page</t>
-        </is>
-      </c>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>https://www.cynthiabritt.com</t>
+          <t>https://www.barmakian.com</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>45 Newbury St, Boston, MA 02116</t>
+          <t>333 Washington St, Boston, MA 02108</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -18111,19 +18095,19 @@
         </is>
       </c>
       <c r="O162" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="P162" t="n">
-        <v>102</v>
+        <v>249</v>
       </c>
       <c r="Q162" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/boston-ma/mip/cynthia-britt-custom-jewelry-481536502</t>
+          <t>https://www.yellowpages.com/boston-ma/mip/barmakian-brothers-467708515</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design</t>
+          <t>2 of 3, direct-line, custom-design, since-1910</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
@@ -18133,40 +18117,44 @@
       </c>
       <c r="T162" s="2" t="inlineStr">
         <is>
-          <t>https://cynthiabritt.com/pages/contact</t>
+          <t>https://www.barmakian.com/pages/about</t>
         </is>
       </c>
       <c r="U162" t="inlineStr"/>
       <c r="V162" t="inlineStr">
         <is>
-          <t>2026-10-13T16:53:53+05:30</t>
+          <t>2026-10-13T16:53:38+05:30</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>Cynthia Britt Custom Jewelry (Boston)</t>
+          <t>Jewelers Building Boston, Barmakian Jewelers, G A Chapman Co, Gigian Jewelers</t>
         </is>
       </c>
       <c r="X162" t="inlineStr"/>
       <c r="Y162" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z162" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>(646) 351-9904</t>
+          <t>(508) 872-5454, (603) 888-7800</t>
         </is>
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>https://facebook.com/CynthiaBrittFineJewelry, https://twitter.com/cynthiabritt, https://instagram.com/cynthiabrittcustomjewelry</t>
+          <t>https://facebook.com/BarmakianJewelers, https://instagram.com/barmakian, https://facebook.com/JewelersBuildingofBoston, https://instagram.com/jewelersbuilding333</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>December Thieves</t>
+          <t>Bouvier Jewelers</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -18181,38 +18169,38 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>(617) 982-6802</t>
+          <t>(781) 643-0084</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>hello@decemberthieves.com</t>
+          <t>jeffbouvier@comcast.net</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Kristin Jenkins</t>
+          <t>Jeff Bouvier</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>President</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>https://decemberthieves.com</t>
+          <t>https://www.bouvierjewelersfordiamonds.com</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>51 Charles St, Boston, MA 02114</t>
+          <t>1310 Massachusetts Ave, Arlington, MA 02476</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Arlington</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -18230,16 +18218,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O163" t="inlineStr"/>
-      <c r="P163" t="inlineStr"/>
+      <c r="O163" t="n">
+        <v>5</v>
+      </c>
+      <c r="P163" t="n">
+        <v>7</v>
+      </c>
       <c r="Q163" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/boston-ma/mip/december-thieves-504011303</t>
+          <t>https://www.yellowpages.com/arlington-ma/mip/bouvier-jewelers-7985346</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, since-2013</t>
+          <t>2 of 3, direct-line, gia, since-1956</t>
         </is>
       </c>
       <c r="S163" t="inlineStr">
@@ -18249,36 +18241,40 @@
       </c>
       <c r="T163" s="2" t="inlineStr">
         <is>
-          <t>https://decemberthieves.com/</t>
+          <t>https://www.bouvierjewelersfordiamonds.com/</t>
         </is>
       </c>
       <c r="U163" t="inlineStr"/>
       <c r="V163" t="inlineStr">
         <is>
-          <t>2026-10-13T16:53:49+05:30</t>
+          <t>2026-10-13T16:54:34+05:30</t>
         </is>
       </c>
       <c r="W163" t="inlineStr"/>
       <c r="X163" t="inlineStr"/>
       <c r="Y163" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z163" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>(857) 239-9149</t>
+          <t>(617) 877-1603</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>https://instagram.com/decemberthieves, https://facebook.com/decemberthieves</t>
+          <t>https://facebook.com/Bouvier-Jewelers-103598593066674</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>DeScenza Diamonds | Boston</t>
+          <t>Colby Davis of Boston</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -18293,37 +18289,37 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>(617) 542-7974</t>
+          <t>(978) 836-8654</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>info@descenza.com</t>
+          <t>customerservice@colbydavisofboston.com</t>
         </is>
       </c>
       <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Lia Davis Lombara</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>https://www.descenza.com</t>
+          <t>https://colbydavisofboston.com</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>387 Washington St, Boston, MA 02108, United States</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>Peabody</t>
-        </is>
-      </c>
-      <c r="L164" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
+          <t>33 Newbury St, Boston, MA 02116, United States</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr">
         <is>
           <t>Boston, MA</t>
@@ -18335,19 +18331,19 @@
         </is>
       </c>
       <c r="O164" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="P164" t="n">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="Q164" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/DeScenza+Diamonds+%7C+Boston/data=!4m7!3m6!1s0x89e370836ce814e9:0xa7c7db2d89f6740b!8m2!3d42.3562247!4d-71.0598883!16s%2Fg%2F1tscq091!19sChIJ6RTobINw44kRC3T2iS3bx6c</t>
+          <t>https://www.google.com/maps/place/Colby+Davis+of+Boston/data=!4m7!3m6!1s0x89e37b8729691633:0x31e1a7207b36ff89!8m2!3d42.3524611!4d-71.0729092!16s%2Fg%2F11l1f7k01g!19sChIJMxZpKYd744kRif82eyCn4TE</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-1915</t>
+          <t>2 of 3, role-email, direct-line</t>
         </is>
       </c>
       <c r="S164" t="inlineStr">
@@ -18357,66 +18353,62 @@
       </c>
       <c r="T164" s="2" t="inlineStr">
         <is>
-          <t>https://www.descenza.com/contact</t>
+          <t>https://colbydavisofboston.com/pages/about-us</t>
         </is>
       </c>
       <c r="U164" t="inlineStr"/>
       <c r="V164" t="inlineStr">
         <is>
-          <t>2026-10-13T18:18:46+05:30</t>
-        </is>
-      </c>
-      <c r="W164" t="inlineStr">
-        <is>
-          <t>D-M Diamonds Framingham</t>
-        </is>
-      </c>
+          <t>2026-10-13T18:20:06+05:30</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr"/>
       <c r="X164" t="inlineStr"/>
       <c r="Y164" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z164" t="inlineStr"/>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>(508) 620-0090, (781) 740-2070, (978) 977-0090</t>
+          <t>(978) 375-4456</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>https://facebook.com/descenza, https://instagram.com/descenzadiamonds, https://facebook.com/descenzadiamonds</t>
+          <t>https://facebook.com/colbydavisofboston, https://instagram.com/colbydavisofboston</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Long's Jewelers</t>
+          <t>Cynthia Britt Custom Jewelry</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Jewelry Designers</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>(617) 426-8500</t>
+          <t>(857) 239-9885</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>requests@longsjewelers.com</t>
+          <t>cynthia@cynthiabritt.com</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dana Rebecca</t>
+          <t>Cynthia Pischdotchian</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -18426,12 +18418,12 @@
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>https://www.longsjewelers.com</t>
+          <t>https://www.cynthiabritt.com</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>100 Summer St, Boston, MA 02110</t>
+          <t>45 Newbury St, Boston, MA 02116</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -18455,14 +18447,14 @@
         </is>
       </c>
       <c r="O165" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="P165" t="n">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="Q165" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/boston-ma/mip/longs-jewelers-1717605</t>
+          <t>https://www.yellowpages.com/boston-ma/mip/cynthia-britt-custom-jewelry-481536502</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -18477,18 +18469,18 @@
       </c>
       <c r="T165" s="2" t="inlineStr">
         <is>
-          <t>https://www.longsjewelers.com/pages/contact</t>
+          <t>https://cynthiabritt.com/pages/contact</t>
         </is>
       </c>
       <c r="U165" t="inlineStr"/>
       <c r="V165" t="inlineStr">
         <is>
-          <t>2026-10-13T16:53:57+05:30</t>
+          <t>2026-10-13T16:53:53+05:30</t>
         </is>
       </c>
       <c r="W165" t="inlineStr">
         <is>
-          <t>Long's Jewelers with Patek Philippe</t>
+          <t>Cynthia Britt Custom Jewelry (Boston)</t>
         </is>
       </c>
       <c r="X165" t="inlineStr"/>
@@ -18498,19 +18490,19 @@
       <c r="Z165" t="inlineStr"/>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>(617) 426-7000, (781) 272-5400, (781) 356-5300, (978) 531-6900</t>
+          <t>(646) 351-9904</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>https://facebook.com/longsjewelersboston, https://instagram.com/longsjewelers</t>
+          <t>https://facebook.com/CynthiaBrittFineJewelry, https://twitter.com/cynthiabritt, https://instagram.com/cynthiabrittcustomjewelry</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Pageo Fine Jewelers</t>
+          <t>December Thieves</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -18520,30 +18512,38 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>shop=jewelry</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>(617) 266-0066</t>
+          <t>(617) 982-6802</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>info@pageo.com</t>
+          <t>hello@decemberthieves.com</t>
         </is>
       </c>
       <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Kristin Jenkins</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>https://www.pageo.com</t>
+          <t>https://decemberthieves.com</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>33 Newbury Street, Boston, MA 02116</t>
+          <t>51 Charles St, Boston, MA 02114</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -18563,19 +18563,19 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>OpenStreetMap</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr"/>
       <c r="Q166" s="2" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/7762364097</t>
+          <t>https://www.yellowpages.com/boston-ma/mip/december-thieves-504011303</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1978</t>
+          <t>2 of 3, role-email, direct-line, since-2013</t>
         </is>
       </c>
       <c r="S166" t="inlineStr">
@@ -18585,38 +18585,374 @@
       </c>
       <c r="T166" s="2" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/7762364097</t>
+          <t>https://decemberthieves.com/</t>
         </is>
       </c>
       <c r="U166" t="inlineStr"/>
       <c r="V166" t="inlineStr">
         <is>
-          <t>2026-10-13T17:32:04+05:30</t>
-        </is>
-      </c>
-      <c r="W166" t="inlineStr">
-        <is>
-          <t>Pageo (Boston)</t>
-        </is>
-      </c>
+          <t>2026-10-13T16:53:49+05:30</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr"/>
       <c r="X166" t="inlineStr"/>
       <c r="Y166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z166" t="inlineStr"/>
       <c r="AA166" t="inlineStr">
         <is>
+          <t>(857) 239-9149</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>https://instagram.com/decemberthieves, https://facebook.com/decemberthieves</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>DeScenza Diamonds | Boston</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Jewelry store</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>(617) 542-7974</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>info@descenza.com</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.descenza.com</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>387 Washington St, Boston, MA 02108, United States</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Peabody</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>Boston, MA</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O167" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P167" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/DeScenza+Diamonds+%7C+Boston/data=!4m7!3m6!1s0x89e370836ce814e9:0xa7c7db2d89f6740b!8m2!3d42.3562247!4d-71.0598883!16s%2Fg%2F1tscq091!19sChIJ6RTobINw44kRC3T2iS3bx6c</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, custom-design, since-1915</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.descenza.com/contact</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr"/>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>2026-10-13T18:18:46+05:30</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>D-M Diamonds Framingham</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr"/>
+      <c r="Y167" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z167" t="inlineStr"/>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>(508) 620-0090, (781) 740-2070, (978) 977-0090</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>https://facebook.com/descenza, https://instagram.com/descenzadiamonds, https://facebook.com/descenzadiamonds</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Long's Jewelers</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Jewelers</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>(617) 426-8500</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>requests@longsjewelers.com</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Dana Rebecca</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Featured On About Page</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.longsjewelers.com</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>100 Summer St, Boston, MA 02110</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>Boston, MA</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O168" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P168" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/boston-ma/mip/longs-jewelers-1717605</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>2 of 3, direct-line, gia, custom-design</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.longsjewelers.com/pages/contact</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr"/>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>2026-10-13T16:53:57+05:30</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>Long's Jewelers with Patek Philippe</t>
+        </is>
+      </c>
+      <c r="X168" t="inlineStr"/>
+      <c r="Y168" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z168" t="inlineStr"/>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>(617) 426-7000, (781) 272-5400, (781) 356-5300, (978) 531-6900</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>https://facebook.com/longsjewelersboston, https://instagram.com/longsjewelers</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Pageo Fine Jewelers</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>shop=jewelry</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>(617) 266-0066</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>info@pageo.com</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pageo.com</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>33 Newbury Street, Boston, MA 02116</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>Boston, MA</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr"/>
+      <c r="P169" t="inlineStr"/>
+      <c r="Q169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.openstreetmap.org/node/7762364097</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1978</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.openstreetmap.org/node/7762364097</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr"/>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>2026-10-13T17:32:04+05:30</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>Pageo (Boston)</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr"/>
+      <c r="Y169" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z169" t="inlineStr"/>
+      <c r="AA169" t="inlineStr">
+        <is>
           <t>(617) 964-4940</t>
         </is>
       </c>
-      <c r="AB166" t="inlineStr">
+      <c r="AB169" t="inlineStr">
         <is>
           <t>https://facebook.com/PageoJewelers, https://instagram.com/pageo_jewelers</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB166"/>
+  <autoFilter ref="A1:AB169"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId2"/>
@@ -19128,6 +19464,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I166" r:id="rId508"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q166" r:id="rId509"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T166" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q167" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T167" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I168" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q168" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T168" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I169" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q169" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T169" r:id="rId519"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19357,21 +19702,21 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>500</v>
+        <v>528</v>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -19384,7 +19729,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
@@ -19465,10 +19810,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6607</v>
+        <v>6646</v>
       </c>
       <c r="C12" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -19476,10 +19821,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G12" t="n">
         <v>8</v>
@@ -19522,7 +19867,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3">
@@ -19532,7 +19877,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4">
@@ -19594,7 +19939,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11">
@@ -19633,7 +19978,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T22:40:33+05:30</t>
+          <t>2026-10-13T23:00:41+05:30</t>
         </is>
       </c>
     </row>
@@ -19644,7 +19989,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3">
@@ -19654,7 +19999,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>6607</v>
+        <v>6646</v>
       </c>
     </row>
     <row r="4">

--- a/leadrun_jewelry/jewelry_qualified.xlsx
+++ b/leadrun_jewelry/jewelry_qualified.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qualified Leads'!$A$1:$AB$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qualified Leads'!$A$1:$AB$174</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB169"/>
+  <dimension ref="A1:AB174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -15670,12 +15670,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Loring &amp; Co. Fine Jewelers</t>
+          <t>John Smeal &amp; Co. Jewelers</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -15685,43 +15685,47 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>(256) 880-1909</t>
+          <t>(478) 219-7414</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>jason@loringjewelers.com</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr"/>
+          <t>info@johnsmeal.com</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andy-mukherjee-b137048b</t>
+        </is>
+      </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Jason N. Jason</t>
+          <t>Andy Mukherjee</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Featured On About Page</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>https://www.loringjewelers.com</t>
+          <t>https://johnsmeal.com</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>800 Airport Road, HUNTSVILLE, AL 35802</t>
+          <t>3661 Eisenhower Pkwy Ste 68, Macon, GA 31206-6111</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>HUNTSVILLE</t>
+          <t>Macon</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -15738,56 +15742,56 @@
       <c r="P140" t="inlineStr"/>
       <c r="Q140" s="2" t="inlineStr">
         <is>
-          <t>https://www.bbb.org/us/al/huntsville/profile/jewelry-stores/loring-co-fine-jewelers-0513-900026245</t>
+          <t>https://www.bbb.org/us/ga/centerville/profile/jewelry-stores/john-smeal-co-jewelers-0743-22721</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design, since-1996</t>
+          <t>2 of 3, role-email, custom-design, since-1999</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T140" s="2" t="inlineStr">
         <is>
-          <t>https://www.loringjewelers.com/company/our-team/jason-n/</t>
-        </is>
-      </c>
-      <c r="U140" t="inlineStr"/>
+          <t>https://johnsmeal.com/</t>
+        </is>
+      </c>
+      <c r="U140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Andy+Mukherjee%22+Macon+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V140" t="inlineStr">
         <is>
-          <t>2026-10-13T22:44:26+05:30</t>
+          <t>2026-10-13T22:38:25+05:30</t>
         </is>
       </c>
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr"/>
       <c r="Y140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z140" t="inlineStr"/>
-      <c r="AA140" t="inlineStr">
-        <is>
-          <t>(256) 425-5834</t>
-        </is>
-      </c>
+      <c r="AA140" t="inlineStr"/>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>https://instagram.com/loringandco, https://facebook.com/loringandco, https://instagram.com/loringandco/</t>
+          <t>https://facebook.com/johnsmealjewelers, https://instagram.com/johnsmealjewelers</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Markman's Diamonds</t>
+          <t>Loring &amp; Co. Fine Jewelers</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -15797,43 +15801,43 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>(423) 894-7581</t>
+          <t>(256) 880-1909</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>info@markmansdiamonds.com</t>
+          <t>jason@loringjewelers.com</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Scott Burnett</t>
+          <t>Jason N. Jason</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Featured On About Page</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>https://www.markmansdiamonds.com</t>
+          <t>https://www.loringjewelers.com</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>2104 Hamilton Place Blvd, Chattanooga, TN 37421-6001</t>
+          <t>800 Airport Road, HUNTSVILLE, AL 35802</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Chattanooga</t>
+          <t>HUNTSVILLE</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -15850,12 +15854,12 @@
       <c r="P141" t="inlineStr"/>
       <c r="Q141" s="2" t="inlineStr">
         <is>
-          <t>https://www.bbb.org/us/tn/chattanooga/profile/jewelry-stores/markmans-diamonds-0483-4741</t>
+          <t>https://www.bbb.org/us/al/huntsville/profile/jewelry-stores/loring-co-fine-jewelers-0513-900026245</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, gia, since-1976</t>
+          <t>2 of 3, direct-line, gia, custom-design, since-1996</t>
         </is>
       </c>
       <c r="S141" t="inlineStr">
@@ -15865,13 +15869,13 @@
       </c>
       <c r="T141" s="2" t="inlineStr">
         <is>
-          <t>https://www.markmansdiamonds.com/</t>
+          <t>https://www.loringjewelers.com/company/our-team/jason-n/</t>
         </is>
       </c>
       <c r="U141" t="inlineStr"/>
       <c r="V141" t="inlineStr">
         <is>
-          <t>2026-10-13T22:39:14+05:30</t>
+          <t>2026-10-13T22:44:26+05:30</t>
         </is>
       </c>
       <c r="W141" t="inlineStr"/>
@@ -15882,70 +15886,74 @@
       <c r="Z141" t="inlineStr"/>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>(865) 584-0247</t>
+          <t>(256) 425-5834</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>https://instagram.com/markmansdiamonds, https://facebook.com/MarkmansDiamonds, https://instagram.com/markmansdiamonds/</t>
+          <t>https://instagram.com/loringandco, https://facebook.com/loringandco, https://instagram.com/loringandco/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Regal Studio</t>
+          <t>Markman's Diamonds</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>(404) 846-2525</t>
+          <t>(423) 894-7581</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>info@regal.studio</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr"/>
+          <t>info@markmansdiamonds.com</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/burnettscott</t>
+        </is>
+      </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Ben Tobian</t>
+          <t>Scott Burnett</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>https://regal.studio</t>
+          <t>https://www.markmansdiamonds.com</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>3384 Peachtree Rd NE #120, Atlanta, GA 30326, United States</t>
+          <t>2104 Hamilton Place Blvd, Chattanooga, TN 37421-6001</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Chattanooga</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -15955,70 +15963,62 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O142" t="n">
-        <v>5</v>
-      </c>
-      <c r="P142" t="n">
-        <v>417</v>
-      </c>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr"/>
       <c r="Q142" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Regal+Studio/data=!4m7!3m6!1s0x88f5058e7ed1e263:0xd40fb192ce48ba78!8m2!3d33.8495051!4d-84.3656907!16s%2Fg%2F1tppst8z!19sChIJY-LRfo4F9YgReLpIzpKxD9Q</t>
+          <t>https://www.bbb.org/us/tn/chattanooga/profile/jewelry-stores/markmans-diamonds-0483-4741</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, gia, bench, custom-design, since-1986</t>
+          <t>3 of 3, role-email, direct-line, gia, since-1976</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T142" s="2" t="inlineStr">
         <is>
-          <t>https://regal.studio/</t>
-        </is>
-      </c>
-      <c r="U142" t="inlineStr"/>
+          <t>https://www.markmansdiamonds.com/</t>
+        </is>
+      </c>
+      <c r="U142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Scott+Burnett%22+Chattanooga+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>2026-10-13T17:52:42+05:30</t>
-        </is>
-      </c>
-      <c r="W142" t="inlineStr">
-        <is>
-          <t>Essex Fine Jewelry &amp; Watches, Essex Fine Jewelry, Essex Fine Jewelry + Watches, Regal Fine Jewelry, Elan Diamond Group</t>
-        </is>
-      </c>
+          <t>2026-10-13T22:39:14+05:30</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr"/>
       <c r="Y142" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z142" t="inlineStr"/>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>(404) 481-5555, (404) 643-8855</t>
+          <t>(865) 584-0247</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>https://instagram.com/regalstudiojewelry, https://facebook.com/profile.php?id=61573410419630, https://twitter.com/rccdiamond, https://x.com/i/grok, https://facebook.com/pages/EssexFineJewelry/2110724562359992, https://instagram.com/essexfinejewelry</t>
+          <t>https://instagram.com/markmansdiamonds, https://facebook.com/MarkmansDiamonds, https://instagram.com/markmansdiamonds/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Royal Jewelry &amp; Watches</t>
+          <t>Regal Studio</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -16028,34 +16028,50 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Wholesale jeweler</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>(404) 661-0410</t>
+          <t>(404) 846-2525</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>online@royaljewelrywholesale.com</t>
+          <t>info@regal.studio</t>
         </is>
       </c>
       <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Ben Tobian</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>https://www.royaljewelrywholesale.com</t>
+          <t>https://regal.studio</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Atlanta, GA 30303, United States</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
+          <t>3384 Peachtree Rd NE #120, Atlanta, GA 30326, United States</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
       <c r="M143" t="inlineStr">
         <is>
           <t>Atlanta, GA</t>
@@ -16067,19 +16083,19 @@
         </is>
       </c>
       <c r="O143" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P143" t="n">
-        <v>4</v>
+        <v>417</v>
       </c>
       <c r="Q143" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Royal+Jewelry+%26+Watches/data=!4m7!3m6!1s0x88f5056fe87f5de3:0x338ab8feb6338180!8m2!3d33.7602601!4d-84.389627!16s%2Fg%2F11f7r13z_k!19sChIJ411_6G8F9YgRgIEztv64ijM</t>
+          <t>https://www.google.com/maps/place/Regal+Studio/data=!4m7!3m6!1s0x88f5058e7ed1e263:0xd40fb192ce48ba78!8m2!3d33.8495051!4d-84.3656907!16s%2Fg%2F1tppst8z!19sChIJY-LRfo4F9YgReLpIzpKxD9Q</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design</t>
+          <t>2 of 3, role-email, direct-line, gia, bench, custom-design, since-1986</t>
         </is>
       </c>
       <c r="S143" t="inlineStr">
@@ -16089,56 +16105,64 @@
       </c>
       <c r="T143" s="2" t="inlineStr">
         <is>
-          <t>https://www.royaljewelrywholesale.com/pages/contact</t>
+          <t>https://regal.studio/</t>
         </is>
       </c>
       <c r="U143" t="inlineStr"/>
       <c r="V143" t="inlineStr">
         <is>
-          <t>2026-10-13T17:56:45+05:30</t>
-        </is>
-      </c>
-      <c r="W143" t="inlineStr"/>
+          <t>2026-10-13T17:52:42+05:30</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Essex Fine Jewelry &amp; Watches, Essex Fine Jewelry, Essex Fine Jewelry + Watches, Regal Fine Jewelry, Elan Diamond Group</t>
+        </is>
+      </c>
       <c r="X143" t="inlineStr"/>
       <c r="Y143" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z143" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>(404) 840-7535</t>
+          <t>(404) 481-5555, (404) 643-8855</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>https://instagram.com/royalwholesale.atl</t>
+          <t>https://instagram.com/regalstudiojewelry, https://facebook.com/profile.php?id=61573410419630, https://twitter.com/rccdiamond, https://x.com/i/grok, https://facebook.com/pages/EssexFineJewelry/2110724562359992, https://instagram.com/essexfinejewelry</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S.B. Company Jewelers</t>
+          <t>Royal Jewelry &amp; Watches</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Buyers</t>
+          <t>Wholesale jeweler</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>(770) 960-0001</t>
+          <t>(404) 661-0410</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>ahouston@southlakemall.com</t>
+          <t>online@royaljewelrywholesale.com</t>
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
@@ -16146,24 +16170,16 @@
       <c r="H144" t="inlineStr"/>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>https://www.southlakemall.com</t>
+          <t>https://www.royaljewelrywholesale.com</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>1000 Southlake Mall, Morrow, GA 30260</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>Morrow</t>
-        </is>
-      </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>GA</t>
-        </is>
-      </c>
+          <t>Atlanta, GA 30303, United States</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
         <is>
           <t>Atlanta, GA</t>
@@ -16171,19 +16187,23 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O144" t="inlineStr"/>
-      <c r="P144" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O144" t="n">
+        <v>3</v>
+      </c>
+      <c r="P144" t="n">
+        <v>4</v>
+      </c>
       <c r="Q144" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/morrow-ga/mip/s-b-company-jewelers-529548766</t>
+          <t>https://www.google.com/maps/place/Royal+Jewelry+%26+Watches/data=!4m7!3m6!1s0x88f5056fe87f5de3:0x338ab8feb6338180!8m2!3d33.7602601!4d-84.389627!16s%2Fg%2F11f7r13z_k!19sChIJ411_6G8F9YgRgIEztv64ijM</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S144" t="inlineStr">
@@ -16193,13 +16213,13 @@
       </c>
       <c r="T144" s="2" t="inlineStr">
         <is>
-          <t>https://www.southlakemall.com/contact-us</t>
+          <t>https://www.royaljewelrywholesale.com/pages/contact</t>
         </is>
       </c>
       <c r="U144" t="inlineStr"/>
       <c r="V144" t="inlineStr">
         <is>
-          <t>2026-10-13T16:49:48+05:30</t>
+          <t>2026-10-13T17:56:45+05:30</t>
         </is>
       </c>
       <c r="W144" t="inlineStr"/>
@@ -16210,19 +16230,19 @@
       <c r="Z144" t="inlineStr"/>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>(770) 961-1050</t>
+          <t>(404) 840-7535</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>https://facebook.com/ShopSouthlakeMall, https://instagram.com/shopsouthlakemall</t>
+          <t>https://instagram.com/royalwholesale.atl</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SB Jewelers</t>
+          <t>S.B. Company Jewelers</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -16232,17 +16252,17 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Repairing</t>
+          <t>Jewelers, Jewelry Buyers</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>(470) 926-1684</t>
+          <t>(770) 960-0001</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> info@sbjewelersga.com</t>
+          <t>ahouston@southlakemall.com</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
@@ -16250,17 +16270,17 @@
       <c r="H145" t="inlineStr"/>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>https://sbjewelersga.com</t>
+          <t>https://www.southlakemall.com</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>256 Pharr Rd NE, Atlanta, GA 30305</t>
+          <t>1000 Southlake Mall, Morrow, GA 30260</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Morrow</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -16282,12 +16302,12 @@
       <c r="P145" t="inlineStr"/>
       <c r="Q145" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/atlanta-ga/mip/sb-jewelers-576536946</t>
+          <t>https://www.yellowpages.com/morrow-ga/mip/s-b-company-jewelers-529548766</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, gia, custom-design</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S145" t="inlineStr">
@@ -16297,13 +16317,13 @@
       </c>
       <c r="T145" s="2" t="inlineStr">
         <is>
-          <t>https://sbjewelersga.com/</t>
+          <t>https://www.southlakemall.com/contact-us</t>
         </is>
       </c>
       <c r="U145" t="inlineStr"/>
       <c r="V145" t="inlineStr">
         <is>
-          <t>2026-10-13T16:48:20+05:30</t>
+          <t>2026-10-13T16:49:48+05:30</t>
         </is>
       </c>
       <c r="W145" t="inlineStr"/>
@@ -16314,70 +16334,62 @@
       <c r="Z145" t="inlineStr"/>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>(470) 461-9239, (678) 709-5911</t>
+          <t>(770) 961-1050</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>https://facebook.com/people/SB-Jewelers/61561749161475, https://instagram.com/sbcustomjewelers, https://instagram.com/thesbjewelers</t>
+          <t>https://facebook.com/ShopSouthlakeMall, https://instagram.com/shopsouthlakemall</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Ware Jewelers, Inc.</t>
+          <t>SB Jewelers</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Jewelry Stores</t>
+          <t>Jewelers, Jewelry Repairing</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>(334) 821-7375</t>
+          <t>(470) 926-1684</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>ronnie@warejewelers.com</t>
+          <t xml:space="preserve"> info@sbjewelersga.com</t>
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>Steven Lagos</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>https://www.warejewelers.com</t>
+          <t>https://sbjewelersga.com</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>111 S College St, Auburn, AL 36830-5418</t>
+          <t>256 Pharr Rd NE, Atlanta, GA 30305</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Auburn</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -16387,19 +16399,19 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>BBB</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr"/>
       <c r="Q146" s="2" t="inlineStr">
         <is>
-          <t>https://www.bbb.org/us/al/opelika/profile/jewelry-stores/ware-jewelers-inc-0743-107725</t>
+          <t>https://www.yellowpages.com/atlanta-ga/mip/sb-jewelers-576536946</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, bench, custom-design, since-1946</t>
+          <t>2 of 3, role-email, direct-line, gia, custom-design</t>
         </is>
       </c>
       <c r="S146" t="inlineStr">
@@ -16409,101 +16421,109 @@
       </c>
       <c r="T146" s="2" t="inlineStr">
         <is>
-          <t>https://www.warejewelers.com/</t>
+          <t>https://sbjewelersga.com/</t>
         </is>
       </c>
       <c r="U146" t="inlineStr"/>
       <c r="V146" t="inlineStr">
         <is>
-          <t>2026-10-13T22:39:59+05:30</t>
+          <t>2026-10-13T16:48:20+05:30</t>
         </is>
       </c>
       <c r="W146" t="inlineStr"/>
       <c r="X146" t="inlineStr"/>
       <c r="Y146" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z146" t="inlineStr"/>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>(334) 826-9000</t>
+          <t>(470) 461-9239, (678) 709-5911</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>https://facebook.com/WareJewelers1946, https://twitter.com/WareJewelers, https://instagram.com/warejewelers</t>
+          <t>https://facebook.com/people/SB-Jewelers/61561749161475, https://instagram.com/sbcustomjewelers, https://instagram.com/thesbjewelers</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Celtic Knot Jewelry &amp; Co</t>
+          <t>Ware Jewelers, Inc.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>(201) 613-2309</t>
+          <t>(334) 821-7375</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>orders@celtic-knot.com</t>
+          <t>ronnie@warejewelers.com</t>
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Steven Lagos</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>https://celtic-knot.com</t>
+          <t>https://www.warejewelers.com</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>25 Lane Ave, Gloucester City, NJ 08030</t>
+          <t>111 S College St, Auburn, AL 36830-5418</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Gloucester City</t>
+          <t>Auburn</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr"/>
       <c r="Q147" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/gloucester-city-nj/mip/celtic-knot-jewelry-co-561012234</t>
+          <t>https://www.bbb.org/us/al/opelika/profile/jewelry-stores/ware-jewelers-inc-0743-107725</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line</t>
+          <t>2 of 3, direct-line, bench, custom-design, since-1946</t>
         </is>
       </c>
       <c r="S147" t="inlineStr">
@@ -16513,87 +16533,79 @@
       </c>
       <c r="T147" s="2" t="inlineStr">
         <is>
-          <t>https://celtic-knot.com/pages/contact</t>
+          <t>https://www.warejewelers.com/</t>
         </is>
       </c>
       <c r="U147" t="inlineStr"/>
       <c r="V147" t="inlineStr">
         <is>
-          <t>2026-10-13T16:51:38+05:30</t>
+          <t>2026-10-13T22:39:59+05:30</t>
         </is>
       </c>
       <c r="W147" t="inlineStr"/>
       <c r="X147" t="inlineStr"/>
       <c r="Y147" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z147" t="inlineStr"/>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>(314) 455-6688, (317) 455-6688</t>
+          <t>(334) 826-9000</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>https://instagram.com/mycelticknotjewellery</t>
+          <t>https://facebook.com/WareJewelers1946, https://twitter.com/WareJewelers, https://instagram.com/warejewelers</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>DeSumma &amp; Wexler Fine Jewelry, INC</t>
+          <t>A. R. Morris Jewelers</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Appraisers</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>(215) 627-5379</t>
+          <t>(302) 888-2436</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>dandw@desummaandwexler.com</t>
+          <t>armorris@armorrisjewelers.com</t>
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>Ron DeSumma</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>https://desummaandwexler.com</t>
+          <t>https://www.armorrisjewelers.com</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>734 Sansom St, Philadelphia, PA 19106</t>
+          <t>3848 Kennett Pike, Greenville, DE 19807</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Greenville</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -16603,23 +16615,19 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O148" t="n">
-        <v>5</v>
-      </c>
-      <c r="P148" t="n">
-        <v>221</v>
-      </c>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
       <c r="Q148" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/philadelphia-pa/mip/desumma-wexler-fine-jewelry-inc-12226752</t>
+          <t>https://www.bbb.org/us/de/greenville/profile/jewelry-stores/a-r-morris-jewelers-0251-1945010</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design, since-1993</t>
+          <t>2 of 3, direct-line, gia, custom-design, since-1962</t>
         </is>
       </c>
       <c r="S148" t="inlineStr">
@@ -16629,79 +16637,87 @@
       </c>
       <c r="T148" s="2" t="inlineStr">
         <is>
-          <t>https://desummaandwexler.com/</t>
+          <t>https://www.armorrisjewelers.com/</t>
         </is>
       </c>
       <c r="U148" t="inlineStr"/>
       <c r="V148" t="inlineStr">
         <is>
-          <t>2026-10-13T16:50:14+05:30</t>
+          <t>2026-10-13T22:59:34+05:30</t>
         </is>
       </c>
       <c r="W148" t="inlineStr"/>
       <c r="X148" t="inlineStr"/>
       <c r="Y148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z148" t="inlineStr"/>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>(445) 248-6111</t>
+          <t>(302) 777-4367</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>https://facebook.com/DeSummaWexler</t>
+          <t>https://facebook.com/armorrisjewelers, https://instagram.com/a.r.morrisjewelers/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Ellis Antiques</t>
+          <t>Benari Jewelers</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Jewelers, Antiques</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>(856) 854-6346</t>
+          <t>(610) 363-8450</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>ellisantiq@aol.com</t>
+          <t>sales@benarijewelers.com</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Jacob BenAri</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>https://www.ellisantique.com</t>
+          <t>https://www.benarijewelers.com</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>812 Haddon Ave, Collingswood, NJ 08108</t>
+          <t>299 Main St, Exton, PA 19341-3701</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Collingswood</t>
+          <t>Exton</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -16711,23 +16727,19 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O149" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P149" t="n">
-        <v>2</v>
-      </c>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr"/>
       <c r="Q149" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/collingswood-nj/mip/ellis-antiques-2155204</t>
+          <t>https://www.bbb.org/us/pa/newtown-square/profile/jewelry-stores/benari-jewelers-0241-80002365</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-1987</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
@@ -16737,74 +16749,82 @@
       </c>
       <c r="T149" s="2" t="inlineStr">
         <is>
-          <t>https://ellisantique.com/contact-us/</t>
+          <t>https://www.benarijewelers.com/</t>
         </is>
       </c>
       <c r="U149" t="inlineStr"/>
       <c r="V149" t="inlineStr">
         <is>
-          <t>2026-10-13T16:51:53+05:30</t>
+          <t>2026-10-13T22:57:53+05:30</t>
         </is>
       </c>
       <c r="W149" t="inlineStr"/>
       <c r="X149" t="inlineStr"/>
       <c r="Y149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z149" t="inlineStr"/>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>(856) 905-3339</t>
+          <t>(610) 355-1800</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>https://facebook.com/EllisAntiques, https://instagram.com/ellisantiquescollingswood, https://twitter.com/EllisAntiques</t>
+          <t>https://facebook.com/BenariJewelers, https://instagram.com/benarijewelersofficial, https://instagram.com/benarijewelers, https://facebook.com/benarijewelersofficial, https://x.com/benarijewelers</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Paul Morelli</t>
+          <t>Calhoun Jewelers</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>(215) 922-7392</t>
+          <t>(610) 948-8515</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>concierge@paulmorelli.com</t>
+          <t>customerservice@calhounjewelers.com</t>
         </is>
       </c>
       <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Cathy Calhoun</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>https://www.paulmorelli.com</t>
+          <t>https://www.calhounjewelers.com</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>1118 Walnut St, Philadelphia, PA 19107</t>
+          <t>500 Main Street, Royersford, PA 19468-2306</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Royersford</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -16819,19 +16839,19 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr"/>
       <c r="Q150" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/philadelphia-pa/mip/paul-morelli-460503475</t>
+          <t>https://www.bbb.org/us/pa/royersford/profile/jewelry-stores/calhoun-jewelers-0241-80005738</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line</t>
+          <t>2 of 3, role-email, direct-line, ags, ja, custom-design, since-1951</t>
         </is>
       </c>
       <c r="S150" t="inlineStr">
@@ -16841,91 +16861,79 @@
       </c>
       <c r="T150" s="2" t="inlineStr">
         <is>
-          <t>https://paulmorelli.com/</t>
+          <t>https://www.calhounjewelers.com/</t>
         </is>
       </c>
       <c r="U150" t="inlineStr"/>
       <c r="V150" t="inlineStr">
         <is>
-          <t>2026-10-13T16:50:55+05:30</t>
-        </is>
-      </c>
-      <c r="W150" t="inlineStr">
-        <is>
-          <t>Paul Morelli Design Inc</t>
-        </is>
-      </c>
+          <t>2026-10-13T22:59:14+05:30</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr"/>
       <c r="X150" t="inlineStr"/>
       <c r="Y150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z150" t="inlineStr"/>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>(212) 585-4200</t>
+          <t>(831) 574-8044</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>https://facebook.com/PaulMorelli.Designs, https://instagram.com/paulmorellistudio</t>
+          <t>https://facebook.com/pages/Calhoun_Jewelers/134599369900143, https://instagram.com/calhoun_jewelers</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Philadelphia Diamond Company</t>
+          <t>Celtic Knot Jewelry &amp; Co</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Jeweler</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>(215) 607-6700</t>
+          <t>(201) 613-2309</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>info@philadelphiadiamondco.com</t>
+          <t>orders@celtic-knot.com</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>Kenyatta Black</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>https://www.philadelphiadiamondco.com</t>
+          <t>https://celtic-knot.com</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>421 Chestnut St, Philadelphia, PA 19106, United States</t>
+          <t>25 Lane Ave, Gloucester City, NJ 08030</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Gloucester City</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -16935,23 +16943,19 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O151" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P151" t="n">
-        <v>116</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr"/>
       <c r="Q151" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Philadelphia+Diamond+Company/data=!4m7!3m6!1s0x89c6c88116a871dd:0xc12679b6bb8c882e!8m2!3d39.9490554!4d-75.1483217!16s%2Fg%2F12q4s_d1z!19sChIJ3XGoFoHIxokRLoiMu7Z5JsE</t>
+          <t>https://www.yellowpages.com/gloucester-city-nj/mip/celtic-knot-jewelry-co-561012234</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, gia, custom-design</t>
+          <t>2 of 3, role-email, direct-line</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
@@ -16961,77 +16965,77 @@
       </c>
       <c r="T151" s="2" t="inlineStr">
         <is>
-          <t>https://www.philadelphiadiamondco.com/pages/contact</t>
+          <t>https://celtic-knot.com/pages/contact</t>
         </is>
       </c>
       <c r="U151" t="inlineStr"/>
       <c r="V151" t="inlineStr">
         <is>
-          <t>2026-10-13T18:00:42+05:30</t>
-        </is>
-      </c>
-      <c r="W151" t="inlineStr">
-        <is>
-          <t>Phialdelphia Diamond Co, Philadelphia Diamond Co</t>
-        </is>
-      </c>
+          <t>2026-10-13T16:51:38+05:30</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr"/>
       <c r="X151" t="inlineStr"/>
       <c r="Y151" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z151" t="inlineStr"/>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>(215) 607-6707, (215) 607-6710</t>
+          <t>(314) 455-6688, (317) 455-6688</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>https://instagram.com/DiamondCompanyGroup, https://facebook.com/PhiladelphiaDiamondCompany</t>
+          <t>https://instagram.com/mycelticknotjewellery</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S &amp; I Creations</t>
+          <t>DeSumma &amp; Wexler Fine Jewelry, INC</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Jewelry Appraisers</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>(215) 629-0260</t>
+          <t>(215) 627-5379</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>sales@sophiabydesign.com</t>
+          <t>dandw@desummaandwexler.com</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Ron DeSumma</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>https://www.sophiabydesign.com</t>
+          <t>https://desummaandwexler.com</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>125 S 9th St, Philadelphia, PA 19107</t>
+          <t>734 Sansom St, Philadelphia, PA 19106</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -17054,16 +17058,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O152" t="inlineStr"/>
-      <c r="P152" t="inlineStr"/>
+      <c r="O152" t="n">
+        <v>5</v>
+      </c>
+      <c r="P152" t="n">
+        <v>221</v>
+      </c>
       <c r="Q152" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/philadelphia-pa/mip/s-i-creations-454700315</t>
+          <t>https://www.yellowpages.com/philadelphia-pa/mip/desumma-wexler-fine-jewelry-inc-12226752</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line</t>
+          <t>2 of 3, direct-line, gia, custom-design, since-1993</t>
         </is>
       </c>
       <c r="S152" t="inlineStr">
@@ -17073,56 +17081,56 @@
       </c>
       <c r="T152" s="2" t="inlineStr">
         <is>
-          <t>https://www.sophiabydesign.com/</t>
+          <t>https://desummaandwexler.com/</t>
         </is>
       </c>
       <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr">
         <is>
-          <t>2026-10-13T16:50:55+05:30</t>
+          <t>2026-10-13T16:50:14+05:30</t>
         </is>
       </c>
       <c r="W152" t="inlineStr"/>
       <c r="X152" t="inlineStr"/>
       <c r="Y152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z152" t="inlineStr"/>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>(215) 629-0513</t>
+          <t>(445) 248-6111</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>https://facebook.com/SophiaByDesign, https://instagram.com/sophia_by_design</t>
+          <t>https://facebook.com/DeSummaWexler</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Sunny Rx</t>
+          <t>Ellis Antiques</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Jewelers, Criminal Law Attorneys, Home Health Services</t>
+          <t>Jewelers, Antiques</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>(610) 259-0660</t>
+          <t>(856) 854-6346</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>sunnypharmacypa@gmail.com</t>
+          <t>ellisantiq@aol.com</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -17130,22 +17138,22 @@
       <c r="H153" t="inlineStr"/>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>https://www.sunnypharmacypa.com</t>
+          <t>https://www.ellisantique.com</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>918 E Baltimore Ave, Lansdowne, PA 19050</t>
+          <t>812 Haddon Ave, Collingswood, NJ 08108</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Lansdowne</t>
+          <t>Collingswood</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -17158,16 +17166,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O153" t="inlineStr"/>
-      <c r="P153" t="inlineStr"/>
+      <c r="O153" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P153" t="n">
+        <v>2</v>
+      </c>
       <c r="Q153" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/lansdowne-pa/mip/sunny-rx-524592945</t>
+          <t>https://www.yellowpages.com/collingswood-nj/mip/ellis-antiques-2155204</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, since-2016</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S153" t="inlineStr">
@@ -17177,7 +17189,7 @@
       </c>
       <c r="T153" s="2" t="inlineStr">
         <is>
-          <t>https://sunnypharmacypa.com/</t>
+          <t>https://ellisantique.com/contact-us/</t>
         </is>
       </c>
       <c r="U153" t="inlineStr"/>
@@ -17194,15 +17206,19 @@
       <c r="Z153" t="inlineStr"/>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>(215) 839-9732</t>
-        </is>
-      </c>
-      <c r="AB153" t="inlineStr"/>
+          <t>(856) 905-3339</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>https://facebook.com/EllisAntiques, https://instagram.com/ellisantiquescollingswood, https://twitter.com/EllisAntiques</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Amir H. Mozaffarian Fine Jewels</t>
+          <t>Janvier Jewelers</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -17212,66 +17228,70 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Jewelers, Watches, Watch Repair</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>(415) 391-9995</t>
+          <t>(302) 366-7448</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>info@amirhmozaffarian.com</t>
+          <t>janvierjewelers@verizon.net</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Ed Janiver</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>https://www.amirhmozaffarian.com</t>
+          <t>https://www.janvierjewelers.com</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>155 Post St, San Francisco, CA 94108</t>
+          <t>543 Christiana Mall, Newark, DE 19702</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Newark</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O154" t="n">
-        <v>5</v>
-      </c>
-      <c r="P154" t="n">
-        <v>1</v>
-      </c>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
       <c r="Q154" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/san-francisco-ca/mip/amir-h-mozaffarian-fine-jewels-1428504</t>
+          <t>https://www.bbb.org/us/de/newark/profile/jewelry-stores/janvier-jewelers-0251-2541010</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line</t>
+          <t>2 of 3, direct-line, gia, since-1975</t>
         </is>
       </c>
       <c r="S154" t="inlineStr">
@@ -17281,13 +17301,13 @@
       </c>
       <c r="T154" s="2" t="inlineStr">
         <is>
-          <t>https://www.amirhmozaffarian.com/</t>
+          <t>https://www.janvierjewelers.com/</t>
         </is>
       </c>
       <c r="U154" t="inlineStr"/>
       <c r="V154" t="inlineStr">
         <is>
-          <t>2026-10-13T16:52:02+05:30</t>
+          <t>2026-10-13T22:59:48+05:30</t>
         </is>
       </c>
       <c r="W154" t="inlineStr"/>
@@ -17298,19 +17318,19 @@
       <c r="Z154" t="inlineStr"/>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>(415) 728-1401</t>
+          <t>(302) 440-2800</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>https://facebook.com/AmirHMozaffarianFineJewels</t>
+          <t>https://facebook.com/janvier.jeweler, https://twitter.com/janvierJewelers, https://instagram.com/janvierjewelers, https://twitter.com/JanvierJewelers</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Baumell Pearl Co Inc</t>
+          <t>Paul Morelli</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -17320,17 +17340,17 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Jewelers, Pearls</t>
+          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>(415) 421-2113</t>
+          <t>(215) 922-7392</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>info@baumellpearl.com</t>
+          <t>concierge@paulmorelli.com</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
@@ -17338,27 +17358,27 @@
       <c r="H155" t="inlineStr"/>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>https://www.baumellpearl.com</t>
+          <t>https://www.paulmorelli.com</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>210 Post St, San Francisco, CA 94108</t>
+          <t>1118 Walnut St, Philadelphia, PA 19107</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -17370,12 +17390,12 @@
       <c r="P155" t="inlineStr"/>
       <c r="Q155" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/san-francisco-ca/mip/baumell-pearl-co-inc-459129940</t>
+          <t>https://www.yellowpages.com/philadelphia-pa/mip/paul-morelli-460503475</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, since-1962</t>
+          <t>2 of 3, role-email, direct-line</t>
         </is>
       </c>
       <c r="S155" t="inlineStr">
@@ -17385,76 +17405,96 @@
       </c>
       <c r="T155" s="2" t="inlineStr">
         <is>
-          <t>https://www.baumellpearl.com/</t>
+          <t>https://paulmorelli.com/</t>
         </is>
       </c>
       <c r="U155" t="inlineStr"/>
       <c r="V155" t="inlineStr">
         <is>
-          <t>2026-10-13T16:53:25+05:30</t>
-        </is>
-      </c>
-      <c r="W155" t="inlineStr"/>
+          <t>2026-10-13T16:50:55+05:30</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Paul Morelli Design Inc</t>
+        </is>
+      </c>
       <c r="X155" t="inlineStr"/>
       <c r="Y155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z155" t="inlineStr"/>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>(201) 438-7400</t>
+          <t>(212) 585-4200</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>https://facebook.com/BaumellPearl</t>
+          <t>https://facebook.com/PaulMorelli.Designs, https://instagram.com/paulmorellistudio</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Bay Area Gold and Silver Buyers</t>
+          <t>Philadelphia Diamond Company</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Gold dealer</t>
+          <t>Jeweler</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>(415) 233-9999</t>
+          <t>(215) 607-6700</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>bayareagsb@gmail.com</t>
+          <t>info@philadelphiadiamondco.com</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Kenyatta Black</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>https://bayareagoldandsilverbuyers.com</t>
+          <t>https://www.philadelphiadiamondco.com</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>780 Sutter St, San Francisco, CA 94109, United States</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
+          <t>421 Chestnut St, Philadelphia, PA 19106, United States</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -17466,16 +17506,16 @@
         <v>4.9</v>
       </c>
       <c r="P156" t="n">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="Q156" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Bay+Area+Gold+and+Silver+Buyers/data=!4m7!3m6!1s0x808f7dc9530e4cf7:0x81d10cd4f7c2392a!8m2!3d37.7887655!4d-122.4133159!16s%2Fg%2F11b6pdgl9c!19sChIJ90wOU8l9j4ARKjnC99QM0YE</t>
+          <t>https://www.google.com/maps/place/Philadelphia+Diamond+Company/data=!4m7!3m6!1s0x89c6c88116a871dd:0xc12679b6bb8c882e!8m2!3d39.9490554!4d-75.1483217!16s%2Fg%2F12q4s_d1z!19sChIJ3XGoFoHIxokRLoiMu7Z5JsE</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, role-email, direct-line, gia, custom-design</t>
         </is>
       </c>
       <c r="S156" t="inlineStr">
@@ -17485,32 +17525,44 @@
       </c>
       <c r="T156" s="2" t="inlineStr">
         <is>
-          <t>https://bayareagoldandsilverbuyers.com/</t>
+          <t>https://www.philadelphiadiamondco.com/pages/contact</t>
         </is>
       </c>
       <c r="U156" t="inlineStr"/>
       <c r="V156" t="inlineStr">
         <is>
-          <t>2026-10-13T18:11:47+05:30</t>
-        </is>
-      </c>
-      <c r="W156" t="inlineStr"/>
+          <t>2026-10-13T18:00:42+05:30</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Phialdelphia Diamond Co, Philadelphia Diamond Co</t>
+        </is>
+      </c>
       <c r="X156" t="inlineStr"/>
       <c r="Y156" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z156" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>(832) 415-9999</t>
-        </is>
-      </c>
-      <c r="AB156" t="inlineStr"/>
+          <t>(215) 607-6707, (215) 607-6710</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>https://instagram.com/DiamondCompanyGroup, https://facebook.com/PhiladelphiaDiamondCompany</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Dioro Jewelers</t>
+          <t>S &amp; I Creations</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -17520,17 +17572,17 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers, Watches</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>(415) 864-8525</t>
+          <t>(215) 629-0260</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>diorousa@gmail.com</t>
+          <t>sales@sophiabydesign.com</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -17538,27 +17590,27 @@
       <c r="H157" t="inlineStr"/>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>https://www.diorojewelers.com</t>
+          <t>https://www.sophiabydesign.com</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>888 Brannan St Ste 182, San Francisco, CA 94103</t>
+          <t>125 S 9th St, Philadelphia, PA 19107</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -17566,20 +17618,16 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O157" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P157" t="n">
-        <v>6</v>
-      </c>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr"/>
       <c r="Q157" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/san-francisco-ca/mip/dioro-jewelers-451651517</t>
+          <t>https://www.yellowpages.com/philadelphia-pa/mip/s-i-creations-454700315</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design</t>
+          <t>2 of 3, role-email, direct-line</t>
         </is>
       </c>
       <c r="S157" t="inlineStr">
@@ -17589,36 +17637,36 @@
       </c>
       <c r="T157" s="2" t="inlineStr">
         <is>
-          <t>https://diorojewelers.com/</t>
+          <t>https://www.sophiabydesign.com/</t>
         </is>
       </c>
       <c r="U157" t="inlineStr"/>
       <c r="V157" t="inlineStr">
         <is>
-          <t>2026-10-13T16:53:06+05:30</t>
+          <t>2026-10-13T16:50:55+05:30</t>
         </is>
       </c>
       <c r="W157" t="inlineStr"/>
       <c r="X157" t="inlineStr"/>
       <c r="Y157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z157" t="inlineStr"/>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>(925) 837-2340</t>
+          <t>(215) 629-0513</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>https://instagram.com/diorojewelers, https://facebook.com/people/Dioro-Jewelers/61568258612586</t>
+          <t>https://facebook.com/SophiaByDesign, https://instagram.com/sophia_by_design</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Edward's Jewelry &amp; Imports</t>
+          <t>Sunny Rx</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -17628,17 +17676,17 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Jeweler</t>
+          <t>Jewelers, Criminal Law Attorneys, Home Health Services</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>(628) 257-7990</t>
+          <t>(610) 259-0660</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>edwardsjewelryimports@gmail.com</t>
+          <t>sunnypharmacypa@gmail.com</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
@@ -17646,48 +17694,44 @@
       <c r="H158" t="inlineStr"/>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>https://edwardsjewelryimports.com</t>
+          <t>https://www.sunnypharmacypa.com</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>888 Brannan St #160, San Francisco, CA 94103, United States</t>
+          <t>918 E Baltimore Ave, Lansdowne, PA 19050</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Lansdowne</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O158" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P158" t="n">
-        <v>19</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr"/>
       <c r="Q158" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Edward%27s+Jewelry+%26+Imports/data=!4m7!3m6!1s0x808f7e2c76ed152d:0x5152324c7a03dba!8m2!3d37.7717311!4d-122.4051118!16s%2Fg%2F1tg2dqt5!19sChIJLRXtdix-j4ARuj2gxyQjFQU</t>
+          <t>https://www.yellowpages.com/lansdowne-pa/mip/sunny-rx-524592945</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design, since-1983</t>
+          <t>2 of 3, direct-line, since-2016</t>
         </is>
       </c>
       <c r="S158" t="inlineStr">
@@ -17697,60 +17741,52 @@
       </c>
       <c r="T158" s="2" t="inlineStr">
         <is>
-          <t>https://edwardsjewelryimports.com/pages/contact</t>
+          <t>https://sunnypharmacypa.com/</t>
         </is>
       </c>
       <c r="U158" t="inlineStr"/>
       <c r="V158" t="inlineStr">
         <is>
-          <t>2026-10-13T18:12:11+05:30</t>
-        </is>
-      </c>
-      <c r="W158" t="inlineStr">
-        <is>
-          <t>Edwards Jewelry &amp; Imports</t>
-        </is>
-      </c>
+          <t>2026-10-13T16:51:53+05:30</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr"/>
       <c r="X158" t="inlineStr"/>
       <c r="Y158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z158" t="inlineStr"/>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>(415) 877-3730</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>https://facebook.com/EdwardJewelry, https://instagram.com/edwardsjewelry160/, https://instagram.com/edwardsjewelry160</t>
-        </is>
-      </c>
+          <t>(215) 839-9732</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Shreve &amp; Co.</t>
+          <t>Amir H. Mozaffarian Fine Jewels</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>shop=jewelry</t>
+          <t>Jewelers, Watches, Watch Repair</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>(415) 421-2600</t>
+          <t>(415) 391-9995</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>sales@shreve.com</t>
+          <t>info@amirhmozaffarian.com</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -17758,12 +17794,12 @@
       <c r="H159" t="inlineStr"/>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>https://shreve.com</t>
+          <t>https://www.amirhmozaffarian.com</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>150 Post Street, San Francisco, CA 94108</t>
+          <t>155 Post St, San Francisco, CA 94108</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -17783,19 +17819,23 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>OpenStreetMap</t>
-        </is>
-      </c>
-      <c r="O159" t="inlineStr"/>
-      <c r="P159" t="inlineStr"/>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O159" t="n">
+        <v>5</v>
+      </c>
+      <c r="P159" t="n">
+        <v>1</v>
+      </c>
       <c r="Q159" s="2" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/4625205007</t>
+          <t>https://www.yellowpages.com/san-francisco-ca/mip/amir-h-mozaffarian-fine-jewels-1428504</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, role-email, direct-line</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
@@ -17805,13 +17845,13 @@
       </c>
       <c r="T159" s="2" t="inlineStr">
         <is>
-          <t>https://shreve.com/</t>
+          <t>https://www.amirhmozaffarian.com/</t>
         </is>
       </c>
       <c r="U159" t="inlineStr"/>
       <c r="V159" t="inlineStr">
         <is>
-          <t>2026-10-13T17:30:25+05:30</t>
+          <t>2026-10-13T16:52:02+05:30</t>
         </is>
       </c>
       <c r="W159" t="inlineStr"/>
@@ -17822,39 +17862,39 @@
       <c r="Z159" t="inlineStr"/>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>(650) 327-2211</t>
+          <t>(415) 728-1401</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>https://facebook.com/shreveandco, https://instagram.com/shreveco</t>
+          <t>https://facebook.com/AmirHMozaffarianFineJewels</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>The Pearl Factory</t>
+          <t>Baumell Pearl Co Inc</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Designers</t>
+          <t>Jewelers, Pearls</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>(415) 928-0963</t>
+          <t>(415) 421-2113</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>customerservice@pearl-factory.com</t>
+          <t>info@baumellpearl.com</t>
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
@@ -17862,12 +17902,12 @@
       <c r="H160" t="inlineStr"/>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>https://www.pearl-factory.com</t>
+          <t>https://www.baumellpearl.com</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>271 Jefferson St, San Francisco, CA 94133</t>
+          <t>210 Post St, San Francisco, CA 94108</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -17894,12 +17934,12 @@
       <c r="P160" t="inlineStr"/>
       <c r="Q160" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/san-francisco-ca/mip/the-pearl-factory-3059205</t>
+          <t>https://www.yellowpages.com/san-francisco-ca/mip/baumell-pearl-co-inc-459129940</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, since-1924</t>
+          <t>2 of 3, role-email, direct-line, since-1962</t>
         </is>
       </c>
       <c r="S160" t="inlineStr">
@@ -17909,56 +17949,56 @@
       </c>
       <c r="T160" s="2" t="inlineStr">
         <is>
-          <t>https://www.pearl-factory.com/</t>
+          <t>https://www.baumellpearl.com/</t>
         </is>
       </c>
       <c r="U160" t="inlineStr"/>
       <c r="V160" t="inlineStr">
         <is>
-          <t>2026-10-13T16:53:29+05:30</t>
-        </is>
-      </c>
-      <c r="W160" t="inlineStr">
-        <is>
-          <t>Pearl Factory</t>
-        </is>
-      </c>
+          <t>2026-10-13T16:53:25+05:30</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr"/>
       <c r="X160" t="inlineStr"/>
       <c r="Y160" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z160" t="inlineStr"/>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>(407) 704-0564, (415) 421-0920, (619) 226-3677, (702) 207-0033, (702) 798-3342, (702) 836-1935, (702) 891-0525, (808) 293-2980, (808) 327-1749, (808) 661-8042, (808) 886-5019, (808) 942-2447, (831) 612-7320</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr"/>
+          <t>(201) 438-7400</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>https://facebook.com/BaumellPearl</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Art Carl Jewelers &amp; AC Loan</t>
+          <t>Bay Area Gold and Silver Buyers</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Jewelers, Gold, Silver &amp; Platinum Buyers &amp; Dealers, Antiques</t>
+          <t>Gold dealer</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>(781) 322-4551</t>
+          <t>(415) 233-9999</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>artcarljewelers@gmail.com</t>
+          <t>bayareagsb@gmail.com</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
@@ -17966,44 +18006,40 @@
       <c r="H161" t="inlineStr"/>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>https://www.artcarljewelers.com</t>
+          <t>https://bayareagoldandsilverbuyers.com</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>56 Pleasant St, Malden, MA 02148</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>Malden</t>
-        </is>
-      </c>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
+          <t>780 Sutter St, San Francisco, CA 94109, United States</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O161" t="inlineStr"/>
-      <c r="P161" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O161" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P161" t="n">
+        <v>130</v>
+      </c>
       <c r="Q161" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/malden-ma/mip/art-carl-jewelers-ac-loan-1806518</t>
+          <t>https://www.google.com/maps/place/Bay+Area+Gold+and+Silver+Buyers/data=!4m7!3m6!1s0x808f7dc9530e4cf7:0x81d10cd4f7c2392a!8m2!3d37.7887655!4d-122.4133159!16s%2Fg%2F11b6pdgl9c!19sChIJ90wOU8l9j4ARKjnC99QM0YE</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S161" t="inlineStr">
@@ -18013,13 +18049,13 @@
       </c>
       <c r="T161" s="2" t="inlineStr">
         <is>
-          <t>https://artcarljewelers.com/</t>
+          <t>https://bayareagoldandsilverbuyers.com/</t>
         </is>
       </c>
       <c r="U161" t="inlineStr"/>
       <c r="V161" t="inlineStr">
         <is>
-          <t>2026-10-13T16:54:39+05:30</t>
+          <t>2026-10-13T18:11:47+05:30</t>
         </is>
       </c>
       <c r="W161" t="inlineStr"/>
@@ -18030,7 +18066,7 @@
       <c r="Z161" t="inlineStr"/>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>(781) 321-2242</t>
+          <t>(832) 415-9999</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr"/>
@@ -18038,7 +18074,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Barmakian Brothers</t>
+          <t>Edward's Jewelry &amp; Imports</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -18048,17 +18084,17 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers, Diamonds-Wholesale</t>
+          <t>Jeweler</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>(617) 227-3724</t>
+          <t>(628) 257-7990</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>diamonds@barmakian.com</t>
+          <t>edwardsjewelryimports@gmail.com</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
@@ -18066,48 +18102,48 @@
       <c r="H162" t="inlineStr"/>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>https://www.barmakian.com</t>
+          <t>https://edwardsjewelryimports.com</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>333 Washington St, Boston, MA 02108</t>
+          <t>888 Brannan St #160, San Francisco, CA 94103, United States</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O162" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="P162" t="n">
-        <v>249</v>
+        <v>19</v>
       </c>
       <c r="Q162" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/boston-ma/mip/barmakian-brothers-467708515</t>
+          <t>https://www.google.com/maps/place/Edward%27s+Jewelry+%26+Imports/data=!4m7!3m6!1s0x808f7e2c76ed152d:0x5152324c7a03dba!8m2!3d37.7717311!4d-122.4051118!16s%2Fg%2F1tg2dqt5!19sChIJLRXtdix-j4ARuj2gxyQjFQU</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design, since-1910</t>
+          <t>2 of 3, direct-line, gia, custom-design, since-1983</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
@@ -18117,121 +18153,105 @@
       </c>
       <c r="T162" s="2" t="inlineStr">
         <is>
-          <t>https://www.barmakian.com/pages/about</t>
+          <t>https://edwardsjewelryimports.com/pages/contact</t>
         </is>
       </c>
       <c r="U162" t="inlineStr"/>
       <c r="V162" t="inlineStr">
         <is>
-          <t>2026-10-13T16:53:38+05:30</t>
+          <t>2026-10-13T18:12:11+05:30</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>Jewelers Building Boston, Barmakian Jewelers, G A Chapman Co, Gigian Jewelers</t>
+          <t>Edwards Jewelry &amp; Imports</t>
         </is>
       </c>
       <c r="X162" t="inlineStr"/>
       <c r="Y162" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Z162" t="inlineStr"/>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>(508) 872-5454, (603) 888-7800</t>
+          <t>(415) 877-3730</t>
         </is>
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>https://facebook.com/BarmakianJewelers, https://instagram.com/barmakian, https://facebook.com/JewelersBuildingofBoston, https://instagram.com/jewelersbuilding333</t>
+          <t>https://facebook.com/EdwardJewelry, https://instagram.com/edwardsjewelry160/, https://instagram.com/edwardsjewelry160</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Bouvier Jewelers</t>
+          <t>Shreve &amp; Co.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>shop=jewelry</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>(781) 643-0084</t>
+          <t>(415) 421-2600</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>jeffbouvier@comcast.net</t>
+          <t>sales@shreve.com</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>Jeff Bouvier</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>https://www.bouvierjewelersfordiamonds.com</t>
+          <t>https://shreve.com</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>1310 Massachusetts Ave, Arlington, MA 02476</t>
+          <t>150 Post Street, San Francisco, CA 94108</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Arlington</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O163" t="n">
-        <v>5</v>
-      </c>
-      <c r="P163" t="n">
-        <v>7</v>
-      </c>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr"/>
+      <c r="P163" t="inlineStr"/>
       <c r="Q163" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/arlington-ma/mip/bouvier-jewelers-7985346</t>
+          <t>https://www.openstreetmap.org/node/4625205007</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, since-1956</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S163" t="inlineStr">
@@ -18241,109 +18261,109 @@
       </c>
       <c r="T163" s="2" t="inlineStr">
         <is>
-          <t>https://www.bouvierjewelersfordiamonds.com/</t>
+          <t>https://shreve.com/</t>
         </is>
       </c>
       <c r="U163" t="inlineStr"/>
       <c r="V163" t="inlineStr">
         <is>
-          <t>2026-10-13T16:54:34+05:30</t>
+          <t>2026-10-13T17:30:25+05:30</t>
         </is>
       </c>
       <c r="W163" t="inlineStr"/>
       <c r="X163" t="inlineStr"/>
       <c r="Y163" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z163" t="inlineStr"/>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>(617) 877-1603</t>
+          <t>(650) 327-2211</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>https://facebook.com/Bouvier-Jewelers-103598593066674</t>
+          <t>https://facebook.com/shreveandco, https://instagram.com/shreveco</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Colby Davis of Boston</t>
+          <t>The Master's Touch Jewelers</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelry Repair</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>(978) 836-8654</t>
+          <t>(209) 578-0172</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>customerservice@colbydavisofboston.com</t>
+          <t>info@masterstouchjewelers.com</t>
         </is>
       </c>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lia Davis Lombara</t>
+          <t>Mike Cruce</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>https://colbydavisofboston.com</t>
+          <t>https://masterstouchjewelers.com</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>33 Newbury St, Boston, MA 02116, United States</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
+          <t>1600 McHenry Ave Ste F, Modesto, CA 95350-4342</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Modesto</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O164" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P164" t="n">
-        <v>12</v>
-      </c>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr"/>
+      <c r="P164" t="inlineStr"/>
       <c r="Q164" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Colby+Davis+of+Boston/data=!4m7!3m6!1s0x89e37b8729691633:0x31e1a7207b36ff89!8m2!3d42.3524611!4d-71.0729092!16s%2Fg%2F11l1f7k01g!19sChIJMxZpKYd744kRif82eyCn4TE</t>
+          <t>https://www.bbb.org/us/ca/modesto/profile/jewelry-repair/the-masters-touch-jewelers-1156-90038516</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-1981</t>
         </is>
       </c>
       <c r="S164" t="inlineStr">
@@ -18353,13 +18373,13 @@
       </c>
       <c r="T164" s="2" t="inlineStr">
         <is>
-          <t>https://colbydavisofboston.com/pages/about-us</t>
+          <t>https://masterstouchjewelers.com/</t>
         </is>
       </c>
       <c r="U164" t="inlineStr"/>
       <c r="V164" t="inlineStr">
         <is>
-          <t>2026-10-13T18:20:06+05:30</t>
+          <t>2026-10-13T23:20:05+05:30</t>
         </is>
       </c>
       <c r="W164" t="inlineStr"/>
@@ -18370,19 +18390,19 @@
       <c r="Z164" t="inlineStr"/>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>(978) 375-4456</t>
+          <t>(209) 526-2189</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>https://facebook.com/colbydavisofboston, https://instagram.com/colbydavisofboston</t>
+          <t>https://facebook.com/TheMastersTouchJewelers, https://instagram.com/masterstouchjeweler</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Cynthia Britt Custom Jewelry</t>
+          <t>The Pearl Factory</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -18397,48 +18417,40 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>(857) 239-9885</t>
+          <t>(415) 928-0963</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>cynthia@cynthiabritt.com</t>
+          <t>customerservice@pearl-factory.com</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>Cynthia Pischdotchian</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Featured On About Page</t>
-        </is>
-      </c>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>https://www.cynthiabritt.com</t>
+          <t>https://www.pearl-factory.com</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>45 Newbury St, Boston, MA 02116</t>
+          <t>271 Jefferson St, San Francisco, CA 94133</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -18446,20 +18458,16 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O165" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P165" t="n">
-        <v>102</v>
-      </c>
+      <c r="O165" t="inlineStr"/>
+      <c r="P165" t="inlineStr"/>
       <c r="Q165" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/boston-ma/mip/cynthia-britt-custom-jewelry-481536502</t>
+          <t>https://www.yellowpages.com/san-francisco-ca/mip/the-pearl-factory-3059205</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design</t>
+          <t>2 of 3, role-email, direct-line, since-1924</t>
         </is>
       </c>
       <c r="S165" t="inlineStr">
@@ -18469,86 +18477,74 @@
       </c>
       <c r="T165" s="2" t="inlineStr">
         <is>
-          <t>https://cynthiabritt.com/pages/contact</t>
+          <t>https://www.pearl-factory.com/</t>
         </is>
       </c>
       <c r="U165" t="inlineStr"/>
       <c r="V165" t="inlineStr">
         <is>
-          <t>2026-10-13T16:53:53+05:30</t>
+          <t>2026-10-13T16:53:29+05:30</t>
         </is>
       </c>
       <c r="W165" t="inlineStr">
         <is>
-          <t>Cynthia Britt Custom Jewelry (Boston)</t>
+          <t>Pearl Factory</t>
         </is>
       </c>
       <c r="X165" t="inlineStr"/>
       <c r="Y165" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z165" t="inlineStr"/>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>(646) 351-9904</t>
-        </is>
-      </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>https://facebook.com/CynthiaBrittFineJewelry, https://twitter.com/cynthiabritt, https://instagram.com/cynthiabrittcustomjewelry</t>
-        </is>
-      </c>
+          <t>(407) 704-0564, (415) 421-0920, (619) 226-3677, (702) 207-0033, (702) 798-3342, (702) 836-1935, (702) 891-0525, (808) 293-2980, (808) 327-1749, (808) 661-8042, (808) 886-5019, (808) 942-2447, (831) 612-7320</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>December Thieves</t>
+          <t>Art Carl Jewelers &amp; AC Loan</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Gold, Silver &amp; Platinum Buyers &amp; Dealers, Antiques</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>(617) 982-6802</t>
+          <t>(781) 322-4551</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>hello@decemberthieves.com</t>
+          <t>artcarljewelers@gmail.com</t>
         </is>
       </c>
       <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>Kristin Jenkins</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>https://decemberthieves.com</t>
+          <t>https://www.artcarljewelers.com</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>51 Charles St, Boston, MA 02114</t>
+          <t>56 Pleasant St, Malden, MA 02148</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Malden</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -18570,12 +18566,12 @@
       <c r="P166" t="inlineStr"/>
       <c r="Q166" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/boston-ma/mip/december-thieves-504011303</t>
+          <t>https://www.yellowpages.com/malden-ma/mip/art-carl-jewelers-ac-loan-1806518</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, since-2013</t>
+          <t>2 of 3, direct-line, gia</t>
         </is>
       </c>
       <c r="S166" t="inlineStr">
@@ -18585,13 +18581,13 @@
       </c>
       <c r="T166" s="2" t="inlineStr">
         <is>
-          <t>https://decemberthieves.com/</t>
+          <t>https://artcarljewelers.com/</t>
         </is>
       </c>
       <c r="U166" t="inlineStr"/>
       <c r="V166" t="inlineStr">
         <is>
-          <t>2026-10-13T16:53:49+05:30</t>
+          <t>2026-10-13T16:54:39+05:30</t>
         </is>
       </c>
       <c r="W166" t="inlineStr"/>
@@ -18602,19 +18598,15 @@
       <c r="Z166" t="inlineStr"/>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>(857) 239-9149</t>
-        </is>
-      </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>https://instagram.com/decemberthieves, https://facebook.com/decemberthieves</t>
-        </is>
-      </c>
+          <t>(781) 321-2242</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>DeScenza Diamonds | Boston</t>
+          <t>Barmakian Brothers</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -18624,17 +18616,17 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers, Diamonds-Wholesale</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>(617) 542-7974</t>
+          <t>(617) 227-3724</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>info@descenza.com</t>
+          <t>diamonds@barmakian.com</t>
         </is>
       </c>
       <c r="F167" t="inlineStr"/>
@@ -18642,17 +18634,17 @@
       <c r="H167" t="inlineStr"/>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>https://www.descenza.com</t>
+          <t>https://www.barmakian.com</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>387 Washington St, Boston, MA 02108, United States</t>
+          <t>333 Washington St, Boston, MA 02108</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Peabody</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -18667,23 +18659,23 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O167" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="P167" t="n">
-        <v>41</v>
+        <v>249</v>
       </c>
       <c r="Q167" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/DeScenza+Diamonds+%7C+Boston/data=!4m7!3m6!1s0x89e370836ce814e9:0xa7c7db2d89f6740b!8m2!3d42.3562247!4d-71.0598883!16s%2Fg%2F1tscq091!19sChIJ6RTobINw44kRC3T2iS3bx6c</t>
+          <t>https://www.yellowpages.com/boston-ma/mip/barmakian-brothers-467708515</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-1915</t>
+          <t>2 of 3, direct-line, custom-design, since-1910</t>
         </is>
       </c>
       <c r="S167" t="inlineStr">
@@ -18693,40 +18685,44 @@
       </c>
       <c r="T167" s="2" t="inlineStr">
         <is>
-          <t>https://www.descenza.com/contact</t>
+          <t>https://www.barmakian.com/pages/about</t>
         </is>
       </c>
       <c r="U167" t="inlineStr"/>
       <c r="V167" t="inlineStr">
         <is>
-          <t>2026-10-13T18:18:46+05:30</t>
+          <t>2026-10-13T16:53:38+05:30</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>D-M Diamonds Framingham</t>
+          <t>Jewelers Building Boston, Barmakian Jewelers, G A Chapman Co, Gigian Jewelers</t>
         </is>
       </c>
       <c r="X167" t="inlineStr"/>
       <c r="Y167" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z167" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>(508) 620-0090, (781) 740-2070, (978) 977-0090</t>
+          <t>(508) 872-5454, (603) 888-7800</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>https://facebook.com/descenza, https://instagram.com/descenzadiamonds, https://facebook.com/descenzadiamonds</t>
+          <t>https://facebook.com/BarmakianJewelers, https://instagram.com/barmakian, https://facebook.com/JewelersBuildingofBoston, https://instagram.com/jewelersbuilding333</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Long's Jewelers</t>
+          <t>Bouvier Jewelers</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -18741,38 +18737,38 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>(617) 426-8500</t>
+          <t>(781) 643-0084</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>requests@longsjewelers.com</t>
+          <t>jeffbouvier@comcast.net</t>
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Dana Rebecca</t>
+          <t>Jeff Bouvier</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Featured On About Page</t>
+          <t>President</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>https://www.longsjewelers.com</t>
+          <t>https://www.bouvierjewelersfordiamonds.com</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>100 Summer St, Boston, MA 02110</t>
+          <t>1310 Massachusetts Ave, Arlington, MA 02476</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Arlington</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -18791,19 +18787,19 @@
         </is>
       </c>
       <c r="O168" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P168" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="Q168" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/boston-ma/mip/longs-jewelers-1717605</t>
+          <t>https://www.yellowpages.com/arlington-ma/mip/bouvier-jewelers-7985346</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design</t>
+          <t>2 of 3, direct-line, gia, since-1956</t>
         </is>
       </c>
       <c r="S168" t="inlineStr">
@@ -18813,40 +18809,40 @@
       </c>
       <c r="T168" s="2" t="inlineStr">
         <is>
-          <t>https://www.longsjewelers.com/pages/contact</t>
+          <t>https://www.bouvierjewelersfordiamonds.com/</t>
         </is>
       </c>
       <c r="U168" t="inlineStr"/>
       <c r="V168" t="inlineStr">
         <is>
-          <t>2026-10-13T16:53:57+05:30</t>
-        </is>
-      </c>
-      <c r="W168" t="inlineStr">
-        <is>
-          <t>Long's Jewelers with Patek Philippe</t>
-        </is>
-      </c>
+          <t>2026-10-13T16:54:34+05:30</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr"/>
       <c r="X168" t="inlineStr"/>
       <c r="Y168" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z168" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>(617) 426-7000, (781) 272-5400, (781) 356-5300, (978) 531-6900</t>
+          <t>(617) 877-1603</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>https://facebook.com/longsjewelersboston, https://instagram.com/longsjewelers</t>
+          <t>https://facebook.com/Bouvier-Jewelers-103598593066674</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Pageo Fine Jewelers</t>
+          <t>Colby Davis of Boston</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -18856,42 +18852,42 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>shop=jewelry</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>(617) 266-0066</t>
+          <t>(978) 836-8654</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>info@pageo.com</t>
+          <t>customerservice@colbydavisofboston.com</t>
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Lia Davis Lombara</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>https://www.pageo.com</t>
+          <t>https://colbydavisofboston.com</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>33 Newbury Street, Boston, MA 02116</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>Boston</t>
-        </is>
-      </c>
-      <c r="L169" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
+          <t>33 Newbury St, Boston, MA 02116, United States</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
       <c r="M169" t="inlineStr">
         <is>
           <t>Boston, MA</t>
@@ -18899,19 +18895,23 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>OpenStreetMap</t>
-        </is>
-      </c>
-      <c r="O169" t="inlineStr"/>
-      <c r="P169" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O169" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P169" t="n">
+        <v>12</v>
+      </c>
       <c r="Q169" s="2" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/7762364097</t>
+          <t>https://www.google.com/maps/place/Colby+Davis+of+Boston/data=!4m7!3m6!1s0x89e37b8729691633:0x31e1a7207b36ff89!8m2!3d42.3524611!4d-71.0729092!16s%2Fg%2F11l1f7k01g!19sChIJMxZpKYd744kRif82eyCn4TE</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1978</t>
+          <t>2 of 3, role-email, direct-line</t>
         </is>
       </c>
       <c r="S169" t="inlineStr">
@@ -18921,38 +18921,606 @@
       </c>
       <c r="T169" s="2" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/7762364097</t>
+          <t>https://colbydavisofboston.com/pages/about-us</t>
         </is>
       </c>
       <c r="U169" t="inlineStr"/>
       <c r="V169" t="inlineStr">
         <is>
-          <t>2026-10-13T17:32:04+05:30</t>
-        </is>
-      </c>
-      <c r="W169" t="inlineStr">
-        <is>
-          <t>Pageo (Boston)</t>
-        </is>
-      </c>
+          <t>2026-10-13T18:20:06+05:30</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr"/>
       <c r="X169" t="inlineStr"/>
       <c r="Y169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z169" t="inlineStr"/>
       <c r="AA169" t="inlineStr">
         <is>
+          <t>(978) 375-4456</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>https://facebook.com/colbydavisofboston, https://instagram.com/colbydavisofboston</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Cynthia Britt Custom Jewelry</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Custom / bespoke jeweler</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Jewelers, Jewelry Designers</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>(857) 239-9885</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>cynthia@cynthiabritt.com</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Cynthia Pischdotchian</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Featured On About Page</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cynthiabritt.com</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>45 Newbury St, Boston, MA 02116</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>Boston, MA</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O170" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P170" t="n">
+        <v>102</v>
+      </c>
+      <c r="Q170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/boston-ma/mip/cynthia-britt-custom-jewelry-481536502</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>2 of 3, direct-line, gia, custom-design</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T170" s="2" t="inlineStr">
+        <is>
+          <t>https://cynthiabritt.com/pages/contact</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr"/>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>2026-10-13T16:53:53+05:30</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>Cynthia Britt Custom Jewelry (Boston)</t>
+        </is>
+      </c>
+      <c r="X170" t="inlineStr"/>
+      <c r="Y170" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z170" t="inlineStr"/>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>(646) 351-9904</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>https://facebook.com/CynthiaBrittFineJewelry, https://twitter.com/cynthiabritt, https://instagram.com/cynthiabrittcustomjewelry</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>December Thieves</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Jewelers</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>(617) 982-6802</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>hello@decemberthieves.com</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Kristin Jenkins</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>https://decemberthieves.com</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>51 Charles St, Boston, MA 02114</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>Boston, MA</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr"/>
+      <c r="P171" t="inlineStr"/>
+      <c r="Q171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/boston-ma/mip/december-thieves-504011303</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, since-2013</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T171" s="2" t="inlineStr">
+        <is>
+          <t>https://decemberthieves.com/</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr"/>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>2026-10-13T16:53:49+05:30</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr"/>
+      <c r="X171" t="inlineStr"/>
+      <c r="Y171" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z171" t="inlineStr"/>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>(857) 239-9149</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>https://instagram.com/decemberthieves, https://facebook.com/decemberthieves</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>DeScenza Diamonds | Boston</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Jewelry store</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>(617) 542-7974</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>info@descenza.com</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.descenza.com</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>387 Washington St, Boston, MA 02108, United States</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Peabody</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>Boston, MA</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O172" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P172" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/DeScenza+Diamonds+%7C+Boston/data=!4m7!3m6!1s0x89e370836ce814e9:0xa7c7db2d89f6740b!8m2!3d42.3562247!4d-71.0598883!16s%2Fg%2F1tscq091!19sChIJ6RTobINw44kRC3T2iS3bx6c</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, custom-design, since-1915</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.descenza.com/contact</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr"/>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>2026-10-13T18:18:46+05:30</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>D-M Diamonds Framingham</t>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr"/>
+      <c r="Y172" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z172" t="inlineStr"/>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>(508) 620-0090, (781) 740-2070, (978) 977-0090</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>https://facebook.com/descenza, https://instagram.com/descenzadiamonds, https://facebook.com/descenzadiamonds</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Long's Jewelers</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Jewelers</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>(617) 426-8500</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>requests@longsjewelers.com</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Dana Rebecca</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Featured On About Page</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.longsjewelers.com</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>100 Summer St, Boston, MA 02110</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>Boston, MA</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O173" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P173" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/boston-ma/mip/longs-jewelers-1717605</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>2 of 3, direct-line, gia, custom-design</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.longsjewelers.com/pages/contact</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr"/>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>2026-10-13T16:53:57+05:30</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>Long's Jewelers with Patek Philippe</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr"/>
+      <c r="Y173" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z173" t="inlineStr"/>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>(617) 426-7000, (781) 272-5400, (781) 356-5300, (978) 531-6900</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>https://facebook.com/longsjewelersboston, https://instagram.com/longsjewelers</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Pageo Fine Jewelers</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>shop=jewelry</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>(617) 266-0066</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>info@pageo.com</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pageo.com</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>33 Newbury Street, Boston, MA 02116</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>Boston, MA</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr"/>
+      <c r="P174" t="inlineStr"/>
+      <c r="Q174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.openstreetmap.org/node/7762364097</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1978</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.openstreetmap.org/node/7762364097</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr"/>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>2026-10-13T17:32:04+05:30</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>Pageo (Boston)</t>
+        </is>
+      </c>
+      <c r="X174" t="inlineStr"/>
+      <c r="Y174" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z174" t="inlineStr"/>
+      <c r="AA174" t="inlineStr">
+        <is>
           <t>(617) 964-4940</t>
         </is>
       </c>
-      <c r="AB169" t="inlineStr">
+      <c r="AB174" t="inlineStr">
         <is>
           <t>https://facebook.com/PageoJewelers, https://instagram.com/pageo_jewelers</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB169"/>
+  <autoFilter ref="A1:AB174"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId2"/>
@@ -19383,96 +19951,115 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId427"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q139" r:id="rId428"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T139" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I140" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q140" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T140" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I141" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q141" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T141" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I142" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q142" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T142" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I143" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q143" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T143" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I144" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q144" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T144" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I145" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q145" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T145" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q146" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T146" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q147" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T147" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I148" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q148" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T148" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I149" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q149" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T149" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I150" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q150" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T150" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I151" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q151" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T151" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q152" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T152" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q153" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T153" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I154" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q154" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T154" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q155" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T155" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I156" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q156" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T156" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I157" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q157" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T157" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I158" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q158" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T158" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I159" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q159" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T159" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I160" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q160" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T160" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q161" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T161" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I162" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q162" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T162" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I163" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q163" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T163" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I164" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q164" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T164" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I165" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q165" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T165" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I166" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q166" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T166" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q167" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T167" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I168" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q168" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T168" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I169" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q169" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T169" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F140" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I140" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q140" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T140" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U140" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I141" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q141" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T141" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F142" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I142" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q142" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T142" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U142" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I143" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q143" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T143" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I144" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q144" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T144" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I145" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q145" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T145" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q146" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T146" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q147" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T147" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I148" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q148" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T148" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I149" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q149" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T149" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I150" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q150" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T150" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I151" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q151" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T151" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q152" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T152" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q153" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T153" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I154" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q154" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T154" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q155" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T155" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I156" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q156" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T156" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I157" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q157" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T157" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I158" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q158" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T158" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I159" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q159" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T159" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I160" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q160" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T160" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q161" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T161" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I162" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q162" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T162" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I163" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q163" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T163" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I164" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q164" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T164" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I165" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q165" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T165" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I166" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q166" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T166" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q167" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T167" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I168" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q168" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T168" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I169" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q169" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T169" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I170" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q170" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T170" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I171" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q171" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T171" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I172" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q172" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T172" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I173" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q173" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T173" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I174" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q174" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T174" r:id="rId538"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19484,7 +20071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -19702,24 +20289,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -19729,21 +20316,21 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -19756,21 +20343,21 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>390</v>
+        <v>430</v>
       </c>
       <c r="C10" t="n">
         <v>7</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>7</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -19806,28 +20393,55 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>46</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>6646</v>
-      </c>
-      <c r="C12" t="n">
-        <v>168</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>167</v>
-      </c>
-      <c r="F12" t="n">
-        <v>65</v>
-      </c>
-      <c r="G12" t="n">
-        <v>8</v>
+      <c r="B13" t="n">
+        <v>6737</v>
+      </c>
+      <c r="C13" t="n">
+        <v>173</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>172</v>
+      </c>
+      <c r="F13" t="n">
+        <v>70</v>
+      </c>
+      <c r="G13" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -19867,7 +20481,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -19877,7 +20491,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
@@ -19887,7 +20501,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -19919,7 +20533,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9">
@@ -19939,7 +20553,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
@@ -19978,7 +20592,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:00:41+05:30</t>
+          <t>2026-10-13T23:35:27+05:30</t>
         </is>
       </c>
     </row>
@@ -19989,7 +20603,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3">
@@ -19999,7 +20613,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>6646</v>
+        <v>6737</v>
       </c>
     </row>
     <row r="4">

--- a/leadrun_jewelry/jewelry_qualified.xlsx
+++ b/leadrun_jewelry/jewelry_qualified.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qualified Leads'!$A$1:$AB$182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qualified Leads'!$A$1:$AB$196</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB182"/>
+  <dimension ref="A1:AB196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -18562,8 +18562,16 @@
         </is>
       </c>
       <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Edward Misserlian</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
           <t>https://edwardsjewelryimports.com</t>
@@ -18633,7 +18641,7 @@
       </c>
       <c r="X166" t="inlineStr"/>
       <c r="Y166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z166" t="inlineStr"/>
       <c r="AA166" t="inlineStr">
@@ -18650,40 +18658,48 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Shreve &amp; Co.</t>
+          <t>Premium Pearl</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>shop=jewelry</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>(415) 421-2600</t>
+          <t>(800) 801-3280</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>sales@shreve.com</t>
+          <t>info@premiumpearl.com</t>
         </is>
       </c>
       <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Iris Lee</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>https://shreve.com</t>
+          <t>https://www.premiumpearl.com</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>150 Post Street, San Francisco, CA 94108</t>
+          <t>1728 Ocean Ave Ste 218, San Francisco, CA 94112-1737</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -18703,19 +18719,19 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>OpenStreetMap</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr"/>
       <c r="Q167" s="2" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/4625205007</t>
+          <t>https://www.bbb.org/us/ca/san-francisco/profile/jewelry-stores/premium-pearl-1116-73642</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, role-email, direct-line, gia, custom-design, since-2003</t>
         </is>
       </c>
       <c r="S167" t="inlineStr">
@@ -18725,13 +18741,13 @@
       </c>
       <c r="T167" s="2" t="inlineStr">
         <is>
-          <t>https://shreve.com/</t>
+          <t>https://www.premiumpearl.com/</t>
         </is>
       </c>
       <c r="U167" t="inlineStr"/>
       <c r="V167" t="inlineStr">
         <is>
-          <t>2026-10-13T17:30:25+05:30</t>
+          <t>2026-10-14T00:04:36+05:30</t>
         </is>
       </c>
       <c r="W167" t="inlineStr"/>
@@ -18739,68 +18755,68 @@
       <c r="Y167" t="n">
         <v>0</v>
       </c>
-      <c r="Z167" t="inlineStr"/>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>toll-free</t>
+        </is>
+      </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>(650) 327-2211</t>
-        </is>
-      </c>
-      <c r="AB167" t="inlineStr">
-        <is>
-          <t>https://facebook.com/shreveandco, https://instagram.com/shreveco</t>
-        </is>
-      </c>
+          <t>(415) 585-0588</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>The Master's Touch Jewelers</t>
+          <t>Shreve &amp; Co</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Jewelry Repair</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>(209) 578-0172</t>
+          <t>(415) 421-2600</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>info@masterstouchjewelers.com</t>
+          <t>sales@shreve.com</t>
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Mike Cruce</t>
+          <t>Glen Ross</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>https://masterstouchjewelers.com</t>
+          <t>https://shreve.com</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>1600 McHenry Ave Ste F, Modesto, CA 95350-4342</t>
+          <t>150 Post Street, SAN FRANCISCO, CA 94108</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Modesto</t>
+          <t>SAN FRANCISCO</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -18822,12 +18838,12 @@
       <c r="P168" t="inlineStr"/>
       <c r="Q168" s="2" t="inlineStr">
         <is>
-          <t>https://www.bbb.org/us/ca/modesto/profile/jewelry-repair/the-masters-touch-jewelers-1156-90038516</t>
+          <t>https://www.bbb.org/us/ca/san-francisco/profile/jewelry-stores/shreve-co-1116-30292</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-1981</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-1947</t>
         </is>
       </c>
       <c r="S168" t="inlineStr">
@@ -18837,36 +18853,40 @@
       </c>
       <c r="T168" s="2" t="inlineStr">
         <is>
-          <t>https://masterstouchjewelers.com/</t>
+          <t>https://shreve.com/</t>
         </is>
       </c>
       <c r="U168" t="inlineStr"/>
       <c r="V168" t="inlineStr">
         <is>
-          <t>2026-10-13T23:20:05+05:30</t>
-        </is>
-      </c>
-      <c r="W168" t="inlineStr"/>
+          <t>2026-10-14T00:07:09+05:30</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>Shreve &amp; Co.</t>
+        </is>
+      </c>
       <c r="X168" t="inlineStr"/>
       <c r="Y168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z168" t="inlineStr"/>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>(209) 526-2189</t>
+          <t>(650) 327-2211</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>https://facebook.com/TheMastersTouchJewelers, https://instagram.com/masterstouchjeweler</t>
+          <t>https://facebook.com/shreveandco, https://instagram.com/shreveco</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>The Pearl Factory</t>
+          <t>The Master's Touch Jewelers</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -18876,35 +18896,43 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Designers</t>
+          <t>Jewelry Repair</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>(415) 928-0963</t>
+          <t>(209) 578-0172</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>customerservice@pearl-factory.com</t>
+          <t>info@masterstouchjewelers.com</t>
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Mike Cruce</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>https://www.pearl-factory.com</t>
+          <t>https://masterstouchjewelers.com</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>271 Jefferson St, San Francisco, CA 94133</t>
+          <t>1600 McHenry Ave Ste F, Modesto, CA 95350-4342</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Modesto</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -18919,19 +18947,19 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr"/>
       <c r="Q169" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/san-francisco-ca/mip/the-pearl-factory-3059205</t>
+          <t>https://www.bbb.org/us/ca/modesto/profile/jewelry-repair/the-masters-touch-jewelers-1156-90038516</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, since-1924</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-1981</t>
         </is>
       </c>
       <c r="S169" t="inlineStr">
@@ -18941,56 +18969,56 @@
       </c>
       <c r="T169" s="2" t="inlineStr">
         <is>
-          <t>https://www.pearl-factory.com/</t>
+          <t>https://masterstouchjewelers.com/</t>
         </is>
       </c>
       <c r="U169" t="inlineStr"/>
       <c r="V169" t="inlineStr">
         <is>
-          <t>2026-10-13T16:53:29+05:30</t>
-        </is>
-      </c>
-      <c r="W169" t="inlineStr">
-        <is>
-          <t>Pearl Factory</t>
-        </is>
-      </c>
+          <t>2026-10-13T23:20:05+05:30</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr"/>
       <c r="X169" t="inlineStr"/>
       <c r="Y169" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z169" t="inlineStr"/>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>(407) 704-0564, (415) 421-0920, (619) 226-3677, (702) 207-0033, (702) 798-3342, (702) 836-1935, (702) 891-0525, (808) 293-2980, (808) 327-1749, (808) 661-8042, (808) 886-5019, (808) 942-2447, (831) 612-7320</t>
-        </is>
-      </c>
-      <c r="AB169" t="inlineStr"/>
+          <t>(209) 526-2189</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>https://facebook.com/TheMastersTouchJewelers, https://instagram.com/masterstouchjeweler</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Art Carl Jewelers &amp; AC Loan</t>
+          <t>The Pearl Factory</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Jewelers, Gold, Silver &amp; Platinum Buyers &amp; Dealers, Antiques</t>
+          <t>Jewelers, Jewelry Designers</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>(781) 322-4551</t>
+          <t>(415) 928-0963</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>artcarljewelers@gmail.com</t>
+          <t>customerservice@pearl-factory.com</t>
         </is>
       </c>
       <c r="F170" t="inlineStr"/>
@@ -18998,27 +19026,27 @@
       <c r="H170" t="inlineStr"/>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>https://www.artcarljewelers.com</t>
+          <t>https://www.pearl-factory.com</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>56 Pleasant St, Malden, MA 02148</t>
+          <t>271 Jefferson St, San Francisco, CA 94133</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Malden</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -19030,12 +19058,12 @@
       <c r="P170" t="inlineStr"/>
       <c r="Q170" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/malden-ma/mip/art-carl-jewelers-ac-loan-1806518</t>
+          <t>https://www.yellowpages.com/san-francisco-ca/mip/the-pearl-factory-3059205</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia</t>
+          <t>2 of 3, role-email, direct-line, since-1924</t>
         </is>
       </c>
       <c r="S170" t="inlineStr">
@@ -19045,24 +19073,28 @@
       </c>
       <c r="T170" s="2" t="inlineStr">
         <is>
-          <t>https://artcarljewelers.com/</t>
+          <t>https://www.pearl-factory.com/</t>
         </is>
       </c>
       <c r="U170" t="inlineStr"/>
       <c r="V170" t="inlineStr">
         <is>
-          <t>2026-10-13T16:54:39+05:30</t>
-        </is>
-      </c>
-      <c r="W170" t="inlineStr"/>
+          <t>2026-10-13T16:53:29+05:30</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>Pearl Factory</t>
+        </is>
+      </c>
       <c r="X170" t="inlineStr"/>
       <c r="Y170" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z170" t="inlineStr"/>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>(781) 321-2242</t>
+          <t>(407) 704-0564, (415) 421-0920, (619) 226-3677, (702) 207-0033, (702) 798-3342, (702) 836-1935, (702) 891-0525, (808) 293-2980, (808) 327-1749, (808) 661-8042, (808) 886-5019, (808) 942-2447, (831) 612-7320</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr"/>
@@ -19070,27 +19102,27 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Barmakian Brothers</t>
+          <t>Art Carl Jewelers &amp; AC Loan</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers, Diamonds-Wholesale</t>
+          <t>Jewelers, Gold, Silver &amp; Platinum Buyers &amp; Dealers, Antiques</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>(617) 227-3724</t>
+          <t>(781) 322-4551</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>diamonds@barmakian.com</t>
+          <t>artcarljewelers@gmail.com</t>
         </is>
       </c>
       <c r="F171" t="inlineStr"/>
@@ -19098,17 +19130,17 @@
       <c r="H171" t="inlineStr"/>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>https://www.barmakian.com</t>
+          <t>https://www.artcarljewelers.com</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>333 Washington St, Boston, MA 02108</t>
+          <t>56 Pleasant St, Malden, MA 02148</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Malden</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -19126,20 +19158,16 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O171" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P171" t="n">
-        <v>249</v>
-      </c>
+      <c r="O171" t="inlineStr"/>
+      <c r="P171" t="inlineStr"/>
       <c r="Q171" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/boston-ma/mip/barmakian-brothers-467708515</t>
+          <t>https://www.yellowpages.com/malden-ma/mip/art-carl-jewelers-ac-loan-1806518</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design, since-1910</t>
+          <t>2 of 3, direct-line, gia</t>
         </is>
       </c>
       <c r="S171" t="inlineStr">
@@ -19149,44 +19177,32 @@
       </c>
       <c r="T171" s="2" t="inlineStr">
         <is>
-          <t>https://www.barmakian.com/pages/about</t>
+          <t>https://artcarljewelers.com/</t>
         </is>
       </c>
       <c r="U171" t="inlineStr"/>
       <c r="V171" t="inlineStr">
         <is>
-          <t>2026-10-13T16:53:38+05:30</t>
-        </is>
-      </c>
-      <c r="W171" t="inlineStr">
-        <is>
-          <t>Jewelers Building Boston, Barmakian Jewelers, G A Chapman Co, Gigian Jewelers</t>
-        </is>
-      </c>
+          <t>2026-10-13T16:54:39+05:30</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr"/>
       <c r="X171" t="inlineStr"/>
       <c r="Y171" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z171" t="inlineStr"/>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>(508) 872-5454, (603) 888-7800</t>
-        </is>
-      </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>https://facebook.com/BarmakianJewelers, https://instagram.com/barmakian, https://facebook.com/JewelersBuildingofBoston, https://instagram.com/jewelersbuilding333</t>
-        </is>
-      </c>
+          <t>(781) 321-2242</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Bouvier Jewelers</t>
+          <t>Barmakian Brothers</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -19196,43 +19212,35 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers, Diamonds-Wholesale</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>(781) 643-0084</t>
+          <t>(617) 227-3724</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>jeffbouvier@comcast.net</t>
+          <t>diamonds@barmakian.com</t>
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>Jeff Bouvier</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>https://www.bouvierjewelersfordiamonds.com</t>
+          <t>https://www.barmakian.com</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>1310 Massachusetts Ave, Arlington, MA 02476</t>
+          <t>333 Washington St, Boston, MA 02108</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Arlington</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -19251,19 +19259,19 @@
         </is>
       </c>
       <c r="O172" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="P172" t="n">
-        <v>7</v>
+        <v>249</v>
       </c>
       <c r="Q172" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/arlington-ma/mip/bouvier-jewelers-7985346</t>
+          <t>https://www.yellowpages.com/boston-ma/mip/barmakian-brothers-467708515</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, since-1956</t>
+          <t>2 of 3, direct-line, custom-design, since-1910</t>
         </is>
       </c>
       <c r="S172" t="inlineStr">
@@ -19273,19 +19281,23 @@
       </c>
       <c r="T172" s="2" t="inlineStr">
         <is>
-          <t>https://www.bouvierjewelersfordiamonds.com/</t>
+          <t>https://www.barmakian.com/pages/about</t>
         </is>
       </c>
       <c r="U172" t="inlineStr"/>
       <c r="V172" t="inlineStr">
         <is>
-          <t>2026-10-13T16:54:34+05:30</t>
-        </is>
-      </c>
-      <c r="W172" t="inlineStr"/>
+          <t>2026-10-13T16:53:38+05:30</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>Jewelers Building Boston, Barmakian Jewelers, G A Chapman Co, Gigian Jewelers</t>
+        </is>
+      </c>
       <c r="X172" t="inlineStr"/>
       <c r="Y172" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Z172" t="inlineStr">
         <is>
@@ -19294,19 +19306,19 @@
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>(617) 877-1603</t>
+          <t>(508) 872-5454, (603) 888-7800</t>
         </is>
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>https://facebook.com/Bouvier-Jewelers-103598593066674</t>
+          <t>https://facebook.com/BarmakianJewelers, https://instagram.com/barmakian, https://facebook.com/JewelersBuildingofBoston, https://instagram.com/jewelersbuilding333</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Colby Davis of Boston</t>
+          <t>Bouvier Jewelers</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -19316,42 +19328,50 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>(978) 836-8654</t>
+          <t>(781) 643-0084</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>customerservice@colbydavisofboston.com</t>
+          <t>jeffbouvier@comcast.net</t>
         </is>
       </c>
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Lia Davis Lombara</t>
+          <t>Jeff Bouvier</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>President</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>https://colbydavisofboston.com</t>
+          <t>https://www.bouvierjewelersfordiamonds.com</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>33 Newbury St, Boston, MA 02116, United States</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
+          <t>1310 Massachusetts Ave, Arlington, MA 02476</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Arlington</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
       <c r="M173" t="inlineStr">
         <is>
           <t>Boston, MA</t>
@@ -19359,23 +19379,23 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O173" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="P173" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q173" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Colby+Davis+of+Boston/data=!4m7!3m6!1s0x89e37b8729691633:0x31e1a7207b36ff89!8m2!3d42.3524611!4d-71.0729092!16s%2Fg%2F11l1f7k01g!19sChIJMxZpKYd744kRif82eyCn4TE</t>
+          <t>https://www.yellowpages.com/arlington-ma/mip/bouvier-jewelers-7985346</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line</t>
+          <t>2 of 3, direct-line, gia, since-1956</t>
         </is>
       </c>
       <c r="S173" t="inlineStr">
@@ -19385,89 +19405,85 @@
       </c>
       <c r="T173" s="2" t="inlineStr">
         <is>
-          <t>https://colbydavisofboston.com/pages/about-us</t>
+          <t>https://www.bouvierjewelersfordiamonds.com/</t>
         </is>
       </c>
       <c r="U173" t="inlineStr"/>
       <c r="V173" t="inlineStr">
         <is>
-          <t>2026-10-13T18:20:06+05:30</t>
+          <t>2026-10-13T16:54:34+05:30</t>
         </is>
       </c>
       <c r="W173" t="inlineStr"/>
       <c r="X173" t="inlineStr"/>
       <c r="Y173" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z173" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>(978) 375-4456</t>
+          <t>(617) 877-1603</t>
         </is>
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>https://facebook.com/colbydavisofboston, https://instagram.com/colbydavisofboston</t>
+          <t>https://facebook.com/Bouvier-Jewelers-103598593066674</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Cynthia Britt Custom Jewelry</t>
+          <t>Colby Davis of Boston</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Designers</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>(857) 239-9885</t>
+          <t>(978) 836-8654</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>cynthia@cynthiabritt.com</t>
+          <t>customerservice@colbydavisofboston.com</t>
         </is>
       </c>
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Cynthia Pischdotchian</t>
+          <t>Lia Davis Lombara</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Featured On About Page</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>https://www.cynthiabritt.com</t>
+          <t>https://colbydavisofboston.com</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>45 Newbury St, Boston, MA 02116</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>Boston</t>
-        </is>
-      </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
+          <t>33 Newbury St, Boston, MA 02116, United States</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr">
         <is>
           <t>Boston, MA</t>
@@ -19475,23 +19491,23 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O174" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="P174" t="n">
-        <v>102</v>
+        <v>12</v>
       </c>
       <c r="Q174" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/boston-ma/mip/cynthia-britt-custom-jewelry-481536502</t>
+          <t>https://www.google.com/maps/place/Colby+Davis+of+Boston/data=!4m7!3m6!1s0x89e37b8729691633:0x31e1a7207b36ff89!8m2!3d42.3524611!4d-71.0729092!16s%2Fg%2F11l1f7k01g!19sChIJMxZpKYd744kRif82eyCn4TE</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design</t>
+          <t>2 of 3, role-email, direct-line</t>
         </is>
       </c>
       <c r="S174" t="inlineStr">
@@ -19501,81 +19517,77 @@
       </c>
       <c r="T174" s="2" t="inlineStr">
         <is>
-          <t>https://cynthiabritt.com/pages/contact</t>
+          <t>https://colbydavisofboston.com/pages/about-us</t>
         </is>
       </c>
       <c r="U174" t="inlineStr"/>
       <c r="V174" t="inlineStr">
         <is>
-          <t>2026-10-13T16:53:53+05:30</t>
-        </is>
-      </c>
-      <c r="W174" t="inlineStr">
-        <is>
-          <t>Cynthia Britt Custom Jewelry (Boston)</t>
-        </is>
-      </c>
+          <t>2026-10-13T18:20:06+05:30</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr"/>
       <c r="X174" t="inlineStr"/>
       <c r="Y174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z174" t="inlineStr"/>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>(646) 351-9904</t>
+          <t>(978) 375-4456</t>
         </is>
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>https://facebook.com/CynthiaBrittFineJewelry, https://twitter.com/cynthiabritt, https://instagram.com/cynthiabrittcustomjewelry</t>
+          <t>https://facebook.com/colbydavisofboston, https://instagram.com/colbydavisofboston</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>December Thieves</t>
+          <t>Cynthia Britt Custom Jewelry</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Jewelry Designers</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>(617) 982-6802</t>
+          <t>(857) 239-9885</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>hello@decemberthieves.com</t>
+          <t>cynthia@cynthiabritt.com</t>
         </is>
       </c>
       <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Kristin Jenkins</t>
+          <t>Cynthia Pischdotchian</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Featured On About Page</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>https://decemberthieves.com</t>
+          <t>https://www.cynthiabritt.com</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>51 Charles St, Boston, MA 02114</t>
+          <t>45 Newbury St, Boston, MA 02116</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -19598,16 +19610,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O175" t="inlineStr"/>
-      <c r="P175" t="inlineStr"/>
+      <c r="O175" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P175" t="n">
+        <v>102</v>
+      </c>
       <c r="Q175" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/boston-ma/mip/december-thieves-504011303</t>
+          <t>https://www.yellowpages.com/boston-ma/mip/cynthia-britt-custom-jewelry-481536502</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, since-2013</t>
+          <t>2 of 3, direct-line, gia, custom-design</t>
         </is>
       </c>
       <c r="S175" t="inlineStr">
@@ -19617,36 +19633,40 @@
       </c>
       <c r="T175" s="2" t="inlineStr">
         <is>
-          <t>https://decemberthieves.com/</t>
+          <t>https://cynthiabritt.com/pages/contact</t>
         </is>
       </c>
       <c r="U175" t="inlineStr"/>
       <c r="V175" t="inlineStr">
         <is>
-          <t>2026-10-13T16:53:49+05:30</t>
-        </is>
-      </c>
-      <c r="W175" t="inlineStr"/>
+          <t>2026-10-13T16:53:53+05:30</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>Cynthia Britt Custom Jewelry (Boston)</t>
+        </is>
+      </c>
       <c r="X175" t="inlineStr"/>
       <c r="Y175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z175" t="inlineStr"/>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>(857) 239-9149</t>
+          <t>(646) 351-9904</t>
         </is>
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>https://instagram.com/decemberthieves, https://facebook.com/decemberthieves</t>
+          <t>https://facebook.com/CynthiaBrittFineJewelry, https://twitter.com/cynthiabritt, https://instagram.com/cynthiabrittcustomjewelry</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>DeScenza Diamonds | Boston</t>
+          <t>December Thieves</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -19656,35 +19676,43 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>(617) 542-7974</t>
+          <t>(617) 982-6802</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>info@descenza.com</t>
+          <t>hello@decemberthieves.com</t>
         </is>
       </c>
       <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr"/>
-      <c r="H176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Kristin Jenkins</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>https://www.descenza.com</t>
+          <t>https://decemberthieves.com</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>387 Washington St, Boston, MA 02108, United States</t>
+          <t>51 Charles St, Boston, MA 02114</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>Peabody</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -19699,23 +19727,19 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O176" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="P176" t="n">
-        <v>41</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr"/>
+      <c r="P176" t="inlineStr"/>
       <c r="Q176" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/DeScenza+Diamonds+%7C+Boston/data=!4m7!3m6!1s0x89e370836ce814e9:0xa7c7db2d89f6740b!8m2!3d42.3562247!4d-71.0598883!16s%2Fg%2F1tscq091!19sChIJ6RTobINw44kRC3T2iS3bx6c</t>
+          <t>https://www.yellowpages.com/boston-ma/mip/december-thieves-504011303</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-1915</t>
+          <t>2 of 3, role-email, direct-line, since-2013</t>
         </is>
       </c>
       <c r="S176" t="inlineStr">
@@ -19725,40 +19749,36 @@
       </c>
       <c r="T176" s="2" t="inlineStr">
         <is>
-          <t>https://www.descenza.com/contact</t>
+          <t>https://decemberthieves.com/</t>
         </is>
       </c>
       <c r="U176" t="inlineStr"/>
       <c r="V176" t="inlineStr">
         <is>
-          <t>2026-10-13T18:18:46+05:30</t>
-        </is>
-      </c>
-      <c r="W176" t="inlineStr">
-        <is>
-          <t>D-M Diamonds Framingham</t>
-        </is>
-      </c>
+          <t>2026-10-13T16:53:49+05:30</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr"/>
       <c r="X176" t="inlineStr"/>
       <c r="Y176" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z176" t="inlineStr"/>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>(508) 620-0090, (781) 740-2070, (978) 977-0090</t>
+          <t>(857) 239-9149</t>
         </is>
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>https://facebook.com/descenza, https://instagram.com/descenzadiamonds, https://facebook.com/descenzadiamonds</t>
+          <t>https://instagram.com/decemberthieves, https://facebook.com/decemberthieves</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Long's Jewelers</t>
+          <t>DeScenza Diamonds | Boston</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -19768,43 +19788,35 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>(617) 426-8500</t>
+          <t>(617) 542-7974</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>requests@longsjewelers.com</t>
+          <t>info@descenza.com</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>Dana Rebecca</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Featured On About Page</t>
-        </is>
-      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>https://www.longsjewelers.com</t>
+          <t>https://www.descenza.com</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>100 Summer St, Boston, MA 02110</t>
+          <t>387 Washington St, Boston, MA 02108, United States</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Peabody</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -19819,23 +19831,23 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O177" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="P177" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q177" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/boston-ma/mip/longs-jewelers-1717605</t>
+          <t>https://www.google.com/maps/place/DeScenza+Diamonds+%7C+Boston/data=!4m7!3m6!1s0x89e370836ce814e9:0xa7c7db2d89f6740b!8m2!3d42.3562247!4d-71.0598883!16s%2Fg%2F1tscq091!19sChIJ6RTobINw44kRC3T2iS3bx6c</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-1915</t>
         </is>
       </c>
       <c r="S177" t="inlineStr">
@@ -19845,40 +19857,40 @@
       </c>
       <c r="T177" s="2" t="inlineStr">
         <is>
-          <t>https://www.longsjewelers.com/pages/contact</t>
+          <t>https://www.descenza.com/contact</t>
         </is>
       </c>
       <c r="U177" t="inlineStr"/>
       <c r="V177" t="inlineStr">
         <is>
-          <t>2026-10-13T16:53:57+05:30</t>
+          <t>2026-10-13T18:18:46+05:30</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>Long's Jewelers with Patek Philippe</t>
+          <t>D-M Diamonds Framingham</t>
         </is>
       </c>
       <c r="X177" t="inlineStr"/>
       <c r="Y177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z177" t="inlineStr"/>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>(617) 426-7000, (781) 272-5400, (781) 356-5300, (978) 531-6900</t>
+          <t>(508) 620-0090, (781) 740-2070, (978) 977-0090</t>
         </is>
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>https://facebook.com/longsjewelersboston, https://instagram.com/longsjewelers</t>
+          <t>https://facebook.com/descenza, https://instagram.com/descenzadiamonds, https://facebook.com/descenzadiamonds</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Pageo Fine Jewelers</t>
+          <t>Long's Jewelers</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -19888,30 +19900,38 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>shop=jewelry</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>(617) 266-0066</t>
+          <t>(617) 426-8500</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>info@pageo.com</t>
+          <t>requests@longsjewelers.com</t>
         </is>
       </c>
       <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Dana Rebecca</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Featured On About Page</t>
+        </is>
+      </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>https://www.pageo.com</t>
+          <t>https://www.longsjewelers.com</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>33 Newbury Street, Boston, MA 02116</t>
+          <t>100 Summer St, Boston, MA 02110</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -19931,19 +19951,23 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>OpenStreetMap</t>
-        </is>
-      </c>
-      <c r="O178" t="inlineStr"/>
-      <c r="P178" t="inlineStr"/>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O178" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P178" t="n">
+        <v>36</v>
+      </c>
       <c r="Q178" s="2" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/7762364097</t>
+          <t>https://www.yellowpages.com/boston-ma/mip/longs-jewelers-1717605</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1978</t>
+          <t>2 of 3, direct-line, gia, custom-design</t>
         </is>
       </c>
       <c r="S178" t="inlineStr">
@@ -19953,18 +19977,18 @@
       </c>
       <c r="T178" s="2" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/7762364097</t>
+          <t>https://www.longsjewelers.com/pages/contact</t>
         </is>
       </c>
       <c r="U178" t="inlineStr"/>
       <c r="V178" t="inlineStr">
         <is>
-          <t>2026-10-13T17:32:04+05:30</t>
+          <t>2026-10-13T16:53:57+05:30</t>
         </is>
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>Pageo (Boston)</t>
+          <t>Long's Jewelers with Patek Philippe</t>
         </is>
       </c>
       <c r="X178" t="inlineStr"/>
@@ -19974,96 +19998,84 @@
       <c r="Z178" t="inlineStr"/>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>(617) 964-4940</t>
+          <t>(617) 426-7000, (781) 272-5400, (781) 356-5300, (978) 531-6900</t>
         </is>
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>https://facebook.com/PageoJewelers, https://instagram.com/pageo_jewelers</t>
+          <t>https://facebook.com/longsjewelersboston, https://instagram.com/longsjewelers</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Baraka Gems</t>
+          <t>Pageo Fine Jewelers</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>shop=jewelry</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>(206) 783-1313</t>
+          <t>(617) 266-0066</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>taylor@barakagems.com</t>
+          <t>info@pageo.com</t>
         </is>
       </c>
       <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>Jamie Jockwig</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>https://barakagems.com</t>
+          <t>https://www.pageo.com</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>8218 Greenwood Ave N, Seattle, WA 98103, United States</t>
+          <t>33 Newbury Street, Boston, MA 02116</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O179" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P179" t="n">
-        <v>585</v>
-      </c>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr"/>
+      <c r="P179" t="inlineStr"/>
       <c r="Q179" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Baraka+Gems/data=!4m7!3m6!1s0x549015c85747f579:0x37cf4273370d1242!8m2!3d47.6890046!4d-122.3551065!16s%2Fg%2F11cfbydgl!19sChIJefVHV8gVkFQRQhINN3NCzzc</t>
+          <t>https://www.openstreetmap.org/node/7762364097</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design</t>
+          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1978</t>
         </is>
       </c>
       <c r="S179" t="inlineStr">
@@ -20073,49 +20085,45 @@
       </c>
       <c r="T179" s="2" t="inlineStr">
         <is>
-          <t>https://barakagems.com/</t>
+          <t>https://www.openstreetmap.org/node/7762364097</t>
         </is>
       </c>
       <c r="U179" t="inlineStr"/>
       <c r="V179" t="inlineStr">
         <is>
-          <t>2026-10-13T23:32:27+05:30</t>
+          <t>2026-10-13T17:32:04+05:30</t>
         </is>
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>Baraka Gemstones and Jewelry</t>
+          <t>Pageo (Boston)</t>
         </is>
       </c>
       <c r="X179" t="inlineStr"/>
       <c r="Y179" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Z179" t="inlineStr"/>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>(351) 200-4800</t>
+          <t>(617) 964-4940</t>
         </is>
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>https://facebook.com/barakagems, https://instagram.com/barakagems, https://www.facebook.com/barakagems</t>
+          <t>https://facebook.com/PageoJewelers, https://instagram.com/pageo_jewelers</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Joseph Jewelry</t>
+          <t>Baraka Gems</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -20125,25 +20133,33 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>(206) 736-7348</t>
+          <t>(206) 783-1313</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>design@josephjewelry.com</t>
+          <t>taylor@barakagems.com</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Jamie Jockwig</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>https://www.josephjewelry.com</t>
+          <t>https://barakagems.com</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>1413 4th Ave, Seattle, WA 98101, United States</t>
+          <t>8218 Greenwood Ave N, Seattle, WA 98103, United States</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -20167,19 +20183,19 @@
         </is>
       </c>
       <c r="O180" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P180" t="n">
-        <v>307</v>
+        <v>585</v>
       </c>
       <c r="Q180" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Joseph+Jewelry/data=!4m7!3m6!1s0x54906b955d4780b5:0x1e1128c2da3aa0b!8m2!3d47.6095043!4d-122.3365272!16s%2Fg%2F11f66hfqqv!19sChIJtYBHXZVrkFQRC6qjLYwS4QE</t>
+          <t>https://www.google.com/maps/place/Baraka+Gems/data=!4m7!3m6!1s0x549015c85747f579:0x37cf4273370d1242!8m2!3d47.6890046!4d-122.3551065!16s%2Fg%2F11cfbydgl!19sChIJefVHV8gVkFQRQhINN3NCzzc</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S180" t="inlineStr">
@@ -20189,41 +20205,49 @@
       </c>
       <c r="T180" s="2" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/2404244839</t>
+          <t>https://barakagems.com/</t>
         </is>
       </c>
       <c r="U180" t="inlineStr"/>
       <c r="V180" t="inlineStr">
         <is>
-          <t>2026-10-13T23:32:33+05:30</t>
-        </is>
-      </c>
-      <c r="W180" t="inlineStr"/>
+          <t>2026-10-13T23:32:27+05:30</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>Baraka Gemstones and Jewelry</t>
+        </is>
+      </c>
       <c r="X180" t="inlineStr"/>
       <c r="Y180" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z180" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>(425) 453-8258</t>
+          <t>(351) 200-4800</t>
         </is>
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>https://instagram.com/josephjewelry, https://facebook.com/JosephJewelry, https://facebook.com/josephjewelry, https://twitter.com/josephjewelry</t>
+          <t>https://facebook.com/barakagems, https://instagram.com/barakagems, https://www.facebook.com/barakagems</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Marlow's Fine Jewelry</t>
+          <t>Joseph Jewelry</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -20233,12 +20257,12 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>(425) 230-3138</t>
+          <t>(206) 736-7348</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>info@marlowsfinejewelry.com</t>
+          <t>design@josephjewelry.com</t>
         </is>
       </c>
       <c r="F181" t="inlineStr"/>
@@ -20246,17 +20270,17 @@
       <c r="H181" t="inlineStr"/>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>https://www.marlowsfinejewelry.com</t>
+          <t>https://www.josephjewelry.com</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>1440 NW Gilman Blvd M4, Issaquah, WA 98027, United States</t>
+          <t>1413 4th Ave, Seattle, WA 98101, United States</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Issaquah</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -20275,19 +20299,19 @@
         </is>
       </c>
       <c r="O181" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="P181" t="n">
-        <v>106</v>
+        <v>307</v>
       </c>
       <c r="Q181" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Marlow%27s+Fine+Jewelry/data=!4m7!3m6!1s0x54906f753647443d:0x326e9c7338f3c283!8m2!3d47.5460116!4d-122.0589953!16s%2Fg%2F11b87l4_5r!19sChIJPURHNnVvkFQRg8LzOHOcbjI</t>
+          <t>https://www.google.com/maps/place/Joseph+Jewelry/data=!4m7!3m6!1s0x54906b955d4780b5:0x1e1128c2da3aa0b!8m2!3d47.6095043!4d-122.3365272!16s%2Fg%2F11f66hfqqv!19sChIJtYBHXZVrkFQRC6qjLYwS4QE</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1989</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S181" t="inlineStr">
@@ -20297,81 +20321,81 @@
       </c>
       <c r="T181" s="2" t="inlineStr">
         <is>
-          <t>https://marlowsfinejewelry.com/</t>
+          <t>https://www.openstreetmap.org/node/2404244839</t>
         </is>
       </c>
       <c r="U181" t="inlineStr"/>
       <c r="V181" t="inlineStr">
         <is>
-          <t>2026-10-13T23:42:21+05:30</t>
+          <t>2026-10-13T23:32:33+05:30</t>
         </is>
       </c>
       <c r="W181" t="inlineStr"/>
       <c r="X181" t="inlineStr"/>
       <c r="Y181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z181" t="inlineStr"/>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>(425) 270-3411</t>
+          <t>(425) 453-8258</t>
         </is>
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>https://facebook.com/marlowsfinejewelry, https://instagram.com/marlowsfinejewelry, https://instagram.com/marlowsfinejewelry/, https://twitter.com/marlowsjewelry</t>
+          <t>https://instagram.com/josephjewelry, https://facebook.com/JosephJewelry, https://facebook.com/josephjewelry, https://twitter.com/josephjewelry</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Tacoma Custom Jewelers</t>
+          <t>Marlow's Fine Jewelry</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Jeweler</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>(253) 572-0508</t>
+          <t>(425) 230-3138</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>info@tacomacustomjewelers.com</t>
+          <t>info@marlowsfinejewelry.com</t>
         </is>
       </c>
       <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>Dan Smith</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>https://www.tacomacustomjewelers.com</t>
+          <t>https://www.marlowsfinejewelry.com</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>2805 Bridgeport Way W #24, University Place, WA 98466, United States</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
+          <t>1440 NW Gilman Blvd M4, Issaquah, WA 98027, United States</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Issaquah</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
       <c r="M182" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
@@ -20383,19 +20407,19 @@
         </is>
       </c>
       <c r="O182" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="P182" t="n">
-        <v>204</v>
+        <v>106</v>
       </c>
       <c r="Q182" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Tacoma+Custom+Jewelers/data=!4m7!3m6!1s0x5490551a281b508f:0x853c07e59da386fd!8m2!3d47.2345843!4d-122.5365232!16s%2Fg%2F1vcq7949!19sChIJj1AbKBpVkFQR_YajneUHPIU</t>
+          <t>https://www.google.com/maps/place/Marlow%27s+Fine+Jewelry/data=!4m7!3m6!1s0x54906f753647443d:0x326e9c7338f3c283!8m2!3d47.5460116!4d-122.0589953!16s%2Fg%2F11b87l4_5r!19sChIJPURHNnVvkFQRg8LzOHOcbjI</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, bench, custom-design</t>
+          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1989</t>
         </is>
       </c>
       <c r="S182" t="inlineStr">
@@ -20405,13 +20429,13 @@
       </c>
       <c r="T182" s="2" t="inlineStr">
         <is>
-          <t>https://www.tacomacustomjewelers.com/contact-us.html</t>
+          <t>https://marlowsfinejewelry.com/</t>
         </is>
       </c>
       <c r="U182" t="inlineStr"/>
       <c r="V182" t="inlineStr">
         <is>
-          <t>2026-10-13T23:42:17+05:30</t>
+          <t>2026-10-13T23:42:21+05:30</t>
         </is>
       </c>
       <c r="W182" t="inlineStr"/>
@@ -20422,17 +20446,1505 @@
       <c r="Z182" t="inlineStr"/>
       <c r="AA182" t="inlineStr">
         <is>
+          <t>(425) 270-3411</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>https://facebook.com/marlowsfinejewelry, https://instagram.com/marlowsfinejewelry, https://instagram.com/marlowsfinejewelry/, https://twitter.com/marlowsjewelry</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Tacoma Custom Jewelers</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Custom / bespoke jeweler</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Jeweler</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>(253) 572-0508</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>info@tacomacustomjewelers.com</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Dan Smith</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tacomacustomjewelers.com</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>2805 Bridgeport Way W #24, University Place, WA 98466, United States</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O183" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P183" t="n">
+        <v>204</v>
+      </c>
+      <c r="Q183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Tacoma+Custom+Jewelers/data=!4m7!3m6!1s0x5490551a281b508f:0x853c07e59da386fd!8m2!3d47.2345843!4d-122.5365232!16s%2Fg%2F1vcq7949!19sChIJj1AbKBpVkFQR_YajneUHPIU</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, bench, custom-design</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tacomacustomjewelers.com/contact-us.html</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr"/>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>2026-10-13T23:42:17+05:30</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr"/>
+      <c r="X183" t="inlineStr"/>
+      <c r="Y183" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z183" t="inlineStr"/>
+      <c r="AA183" t="inlineStr">
+        <is>
           <t>(253) 224-3419</t>
         </is>
       </c>
-      <c r="AB182" t="inlineStr">
+      <c r="AB183" t="inlineStr">
         <is>
           <t>https://facebook.com/tacomacustomjewelry, https://instagram.com/tacomacustomjewelers</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Morgan Jewelers - Galleria at Sunset</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Jewelry store</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>(702) 733-1742</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>internetsales@morganjewelers.com</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Maria Luna</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.morganjewelers.com</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>1300 W Sunset Rd #2303, Henderson, NV 89014, United States</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O184" t="n">
+        <v>5</v>
+      </c>
+      <c r="P184" t="n">
+        <v>1383</v>
+      </c>
+      <c r="Q184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Morgan+Jewelers+-+Galleria+at+Sunset/data=!4m7!3m6!1s0x80c8c4f69824d9a7:0x275010c8436473e!8m2!3d36.0673234!4d-115.0416159!16s%2Fg%2F1td1dpry!19sChIJp9kkmPbEyIARPkc2hAwBdQI</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>2 of 3, direct-line, gia, custom-design, since-1914</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.morganjewelers.com/</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr"/>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>2026-10-13T23:46:51+05:30</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>Morgan Jewelers - Meadows Mall</t>
+        </is>
+      </c>
+      <c r="X184" t="inlineStr"/>
+      <c r="Y184" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z184" t="inlineStr"/>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>(208) 329-5656, (208) 376-6181, (360) 260-9212, (406) 543-7134, (435) 627-8375, (435) 753-3458, (503) 653-6086, (509) 452-8858, (702) 870-0901, (801) 224-1871, (801) 266-0294, (801) 363-5300, (801) 394-0906, (801) 546-3458, (801) 571-7307, (801) 966-3352</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>https://facebook.com/morganjewelers, https://twitter.com/MorganJewelers1, https://instagram.com/officialmorganjewelers</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Oro &amp; Jewelers Las Vegas</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Custom / bespoke jeweler</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Jewelry repair service</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>(725) 204-5295</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>orojewelers@gmail.com</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>https://oroandjewelers.com</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>6885 N Aliante Pkwy #105, North Las Vegas, NV 89084, United States</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O185" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P185" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Oro+%26+Jewelers+Las+Vegas/data=!4m7!3m6!1s0x80c8e94fc84551cd:0x9490097c534aa576!8m2!3d36.2858633!4d-115.1790987!16s%2Fg%2F11t7_3shcy!19sChIJzVFFyE_pyIARdqVKU3wJkJQ</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>2 of 3, direct-line, custom-design, since-1990</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T185" s="2" t="inlineStr">
+        <is>
+          <t>https://oroandjewelers.com/</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr"/>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>2026-10-13T23:46:24+05:30</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr"/>
+      <c r="X185" t="inlineStr"/>
+      <c r="Y185" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z185" t="inlineStr"/>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>(702) 293-1933</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>https://facebook.com/OroAndJewelers, https://instagram.com/orojewelers, https://twitter.com/OroJewelers, https://twitter.com/OroAndJewelers, https://instagram.com/OroAndJewelers</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>The Gold &amp; Diamond Company</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Jewelry store</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>(702) 880-1011</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>thegolddiamondcompany@gmail.com</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>David Smith</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thegdco.com</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>4300 Meadows Ln Ste 2480, Las Vegas, NV 89107, United States</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O186" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P186" t="n">
+        <v>1717</v>
+      </c>
+      <c r="Q186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/The+Gold+%26+Diamond+Company/data=!4m7!3m6!1s0x80c8c17bc763cc93:0x91e188f255c7d08c!8m2!3d36.1724363!4d-115.1968253!16s%2Fg%2F11gkvs_h4m!19sChIJk8xjx3vByIARjNDHVfKI4ZE</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>2 of 3, direct-line, custom-design</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T186" s="2" t="inlineStr">
+        <is>
+          <t>https://thegdco.com/contact/</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr"/>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>2026-10-13T23:43:50+05:30</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr"/>
+      <c r="X186" t="inlineStr"/>
+      <c r="Y186" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z186" t="inlineStr"/>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>(702) 823-0050</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sonny.the.jeweler.las.vegas</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Twila True Fine Jewelry &amp; Watches | Las Vegas</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Jeweler</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>(702) 676-7791</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>info@twilatrue.com</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>https://twilatruefinejewelry.com</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>3000 S Las Vegas Blvd Ste S131, Las Vegas, NV 89109, United States</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O187" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P187" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Twila+True+Fine+Jewelry+%26+Watches+%7C+Las+Vegas/data=!4m7!3m6!1s0x80c8c5acbb24491f:0xa126831af92ad3a5!8m2!3d36.1341269!4d-115.167604!16s%2Fg%2F11p5ry1xhp!19sChIJH0kku6zFyIARpdMq-RqDJqE</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T187" s="2" t="inlineStr">
+        <is>
+          <t>https://twilatruefinejewelry.com/</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr"/>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>2026-10-13T23:53:10+05:30</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr"/>
+      <c r="X187" t="inlineStr"/>
+      <c r="Y187" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z187" t="inlineStr"/>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>(949) 258-9720</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>https://instagram.com/twilatruefinejewelry, https://facebook.com/twilatruefinejewelry, https://twitter.com/jewelrybymardo</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Andrew Z Diamonds &amp; Fine Jewelry</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Estate &amp; antique jewelry</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>shop=jewelry</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>(623) 551-6892</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>info@andrewzdiamonds.com</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>https://andrewzdiamonds.com</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>3655 W Anthem Way C131, Anthem, AZ 85086</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Anthem</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr"/>
+      <c r="P188" t="inlineStr"/>
+      <c r="Q188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.openstreetmap.org/node/12076482784</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, custom-design, since-1949</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T188" s="2" t="inlineStr">
+        <is>
+          <t>https://andrewzdiamonds.com/policies/contact-information</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr"/>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>2026-10-13T23:52:47+05:30</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr"/>
+      <c r="X188" t="inlineStr"/>
+      <c r="Y188" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z188" t="inlineStr"/>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>(480) 284-6022, (480) 590-5419</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>https://facebook.com/andrewzdiamonds, https://instagram.com/andrewzdiamonds</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Bazzill Engraving Co</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Jewelry repair / goldsmith</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Engraver</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>(602) 437-9019</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>sam@bazzillengraving.com</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Charlie Bazzill</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>https://bazzillengraving.com</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>2432 W Peoria Ave Bldg 10, #1181, Phoenix, AZ 85029, United States</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O189" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P189" t="n">
+        <v>148</v>
+      </c>
+      <c r="Q189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Bazzill+Engraving+Co/data=!4m7!3m6!1s0x872b6c4659ac0c1f:0x7edb70cbba02b71b!8m2!3d33.5840386!4d-112.1104886!16s%2Fg%2F1tdy0b_q!19sChIJHwysWUZsK4cRG7cCustw234</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>2 of 3, direct-line, since-1969</t>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T189" s="2" t="inlineStr">
+        <is>
+          <t>https://bazzillengraving.com/</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr"/>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>2026-10-13T23:59:35+05:30</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr"/>
+      <c r="X189" t="inlineStr"/>
+      <c r="Y189" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z189" t="inlineStr"/>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>(623) 565-8475</t>
+        </is>
+      </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>https://facebook.com/Bazzill-Engraving-Co-486332631426802</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Braidy Jewelers</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>shop=jewelry</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>(623) 581-3000</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>info@braidyjewelers.com</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>https://braidyjewelers.com</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>2450 W Happy Calley Rd #1153, Phoenix, AZ 85085</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="O190" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P190" t="n">
+        <v>149</v>
+      </c>
+      <c r="Q190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.openstreetmap.org/node/12077950762</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, bench, custom-design, since-1993</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.braidyjewelers.com/contact-ohio-store/</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr"/>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>2026-10-13T23:52:47+05:30</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr"/>
+      <c r="X190" t="inlineStr"/>
+      <c r="Y190" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z190" t="inlineStr"/>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>(330) 686-9144</t>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Coffin and Trout Fine Jewelers</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Jewelry store</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>(480) 763-1300</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>info@coffinandtrout.com</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.coffinandtrout.com</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>7131 W Ray Rd, Chandler, AZ 85226, United States</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Chandler</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O191" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P191" t="n">
+        <v>513</v>
+      </c>
+      <c r="Q191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coffin+and+Trout+Fine+Jewelers/data=!4m7!3m6!1s0x872b04232cb1cd51:0x7eec3525c3b16a87!8m2!3d33.3181447!4d-111.9657591!16s%2Fg%2F1w665whc!19sChIJUc2xLCMEK4cRh2qxwyU17H4</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, ags, bench, custom-design</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T191" s="2" t="inlineStr">
+        <is>
+          <t>https://coffinandtrout.com/</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr"/>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>2026-10-13T23:58:24+05:30</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr"/>
+      <c r="X191" t="inlineStr"/>
+      <c r="Y191" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z191" t="inlineStr"/>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>(480) 405-1761, (480) 568-3352</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>https://facebook.com/coffinandtrout, https://instagram.com/coffinandtrout, https://facebook.com/CoffinandTrout, https://instagram.com/coffin_trout</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Hamra Jewelers</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Jewelry store</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>(480) 946-5110</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>info@hamra.com</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>https://hamra.com</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>15620 N Scottsdale Rd, Scottsdale, AZ 85254, United States</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Scottsdale</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O192" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P192" t="n">
+        <v>409</v>
+      </c>
+      <c r="Q192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Hamra+Jewelers/data=!4m7!3m6!1s0x872b743c31c59d77:0x6565115c41e927f!8m2!3d33.6285206!4d-111.9259963!16s%2Fg%2F1vxdyrdb!19sChIJd53FMTx0K4cRf5IexBVRVgY</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T192" s="2" t="inlineStr">
+        <is>
+          <t>https://hamra.com/</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr"/>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>2026-10-13T23:55:39+05:30</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr"/>
+      <c r="X192" t="inlineStr"/>
+      <c r="Y192" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z192" t="inlineStr"/>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>(480) 404-3792</t>
+        </is>
+      </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>https://instagram.com/hamrajewelers, https://facebook.com/HamraJewelers, https://instagram.com/hamrajewelers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Jewels of the West/Old Town Jewels</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Jeweler</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>(480) 970-8065</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>info@oldtownjewels.com</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.oldtownjewels.com</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>4009 N Brown Ave, Scottsdale, AZ 85251, United States</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O193" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P193" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Jewels+of+the+West%2FOld+Town+Jewels/data=!4m7!3m6!1s0x872b0bbf6b404be3:0xb87deb5d72b806f0!8m2!3d33.4942089!4d-111.9243015!16s%2Fg%2F1tm8ffx4!19sChIJ40tAa78LK4cR8Aa4cl3rfbg</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, bench, since-1984</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T193" s="2" t="inlineStr">
+        <is>
+          <t>https://oldtownjewels.com/</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr"/>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>2026-10-14T00:01:35+05:30</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr"/>
+      <c r="X193" t="inlineStr"/>
+      <c r="Y193" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z193" t="inlineStr"/>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>(480) 244-7635, (602) 350-4009, (602) 619-3314</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>https://instagram.com/oldtownjewels, https://facebook.com/OldTownJewels</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>The Diamond Guys</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Custom / bespoke jeweler</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Jewelry store</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>(480) 656-0652</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>info@thediamondguys.com</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thediamondguys.com</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>14601 N Scottsdale Rd, Scottsdale, AZ 85254, United States</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O194" t="n">
+        <v>5</v>
+      </c>
+      <c r="P194" t="n">
+        <v>498</v>
+      </c>
+      <c r="Q194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/The+Diamond+Guys/data=!4m7!3m6!1s0x872b75f04c774f63:0x7ecc626d464f970!8m2!3d33.6185368!4d-111.9250947!16s%2Fg%2F1w2yvb_p!19sChIJY093TPB1K4cRcPlk1CbG7Ac</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1931</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thediamondguys.com/</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr"/>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>2026-10-13T23:55:45+05:30</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr"/>
+      <c r="X194" t="inlineStr"/>
+      <c r="Y194" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z194" t="inlineStr"/>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>(213) 510-3555</t>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>https://instagram.com/thediamondguys, https://facebook.com/thediamondguysaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Leo Hamel Fine Jewelry &amp; Engagement Rings Store</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Estate &amp; antique jewelry</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Jewelry store</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>(619) 299-1500</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>contact@leohamel.com</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Chelsea Chelsea</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.leohamel.com</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>1851 San Diego Ave Ste 130, San Diego, CA 92110, United States</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>San Diego, CA</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O195" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P195" t="n">
+        <v>1550</v>
+      </c>
+      <c r="Q195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Leo+Hamel+Fine+Jewelry+%26+Engagement+Rings+Store/data=!4m7!3m6!1s0x80deab2f60fc98ab:0xca3b785b554965c1!8m2!3d32.74434!4d-117.1851937!16s%2Fg%2F1v8k_xyx!19sChIJq5j8YC-r3oARwWVJVVt4O8o</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, gia, bench, custom-design, since-2015</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.leohamel.com/</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr"/>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>2026-10-14T00:02:54+05:30</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr"/>
+      <c r="X195" t="inlineStr"/>
+      <c r="Y195" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z195" t="inlineStr"/>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>(619) 644-0000, (760) 757-2000, (858) 509-5900</t>
+        </is>
+      </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>https://instagram.com/leohamelfinejewelers, https://facebook.com/profile.php?id=100089904223194, https://x.com/leohamel, https://x.com/https://twitter.com/leohamel, https://twitter.com/leohamel</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Mervis</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>shop=jewelry</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>(202) 293-0600</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>concierge@mervisdiamond.com</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mervisdiamond.com</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>1700 K Street Northwest, Washington, DC 20006</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>Washington, DC</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr"/>
+      <c r="P196" t="inlineStr"/>
+      <c r="Q196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.openstreetmap.org/node/730833789</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, gia, custom-design</t>
+        </is>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mervisdiamond.com/pages/contact/</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr"/>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>2026-10-14T00:06:30+05:30</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr"/>
+      <c r="X196" t="inlineStr"/>
+      <c r="Y196" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z196" t="inlineStr"/>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>(301) 231-0030, (703) 448-9000</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>https://instagram.com/mervisdiamond, https://facebook.com/mervisdiamonds, https://twitter.com/mervisdiamonds</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB182"/>
+  <autoFilter ref="A1:AB196"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId2"/>
@@ -21005,6 +22517,48 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I182" r:id="rId569"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q182" r:id="rId570"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T182" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I183" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q183" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T183" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I184" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q184" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T184" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I185" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q185" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T185" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I186" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q186" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T186" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I187" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q187" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T187" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I188" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q188" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T188" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I189" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q189" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T189" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I190" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q190" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T190" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I191" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q191" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T191" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I192" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q192" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T192" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I193" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q193" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T193" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I194" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q194" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T194" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I195" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q195" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T195" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I196" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q196" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T196" r:id="rId613"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21016,7 +22570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -21099,7 +22653,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1055</v>
+        <v>1049</v>
       </c>
       <c r="C3" t="n">
         <v>28</v>
@@ -21288,21 +22842,21 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -21342,14 +22896,14 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C12" t="n">
         <v>4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -21369,21 +22923,21 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -21396,21 +22950,21 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>83</v>
+        <v>152</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -21419,27 +22973,108 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>San Diego, CA</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>142</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Denver, CO</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>69</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Washington, DC</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>39</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>7041</v>
-      </c>
-      <c r="C15" t="n">
-        <v>181</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>179</v>
-      </c>
-      <c r="F15" t="n">
-        <v>77</v>
-      </c>
-      <c r="G15" t="n">
+      <c r="B18" t="n">
+        <v>7354</v>
+      </c>
+      <c r="C18" t="n">
+        <v>195</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>193</v>
+      </c>
+      <c r="F18" t="n">
+        <v>84</v>
+      </c>
+      <c r="G18" t="n">
         <v>15</v>
       </c>
     </row>
@@ -21480,7 +23115,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3">
@@ -21490,7 +23125,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4">
@@ -21500,7 +23135,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -21510,7 +23145,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -21542,7 +23177,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10">
@@ -21552,7 +23187,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
@@ -21562,7 +23197,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -21591,7 +23226,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:55:36+05:30</t>
+          <t>2026-10-14T00:15:45+05:30</t>
         </is>
       </c>
     </row>
@@ -21602,7 +23237,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3">
@@ -21612,7 +23247,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>7041</v>
+        <v>7354</v>
       </c>
     </row>
     <row r="4">

--- a/leadrun_jewelry/jewelry_qualified.xlsx
+++ b/leadrun_jewelry/jewelry_qualified.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qualified Leads'!$A$1:$AB$213</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qualified Leads'!$A$1:$AB$218</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB213"/>
+  <dimension ref="A1:AB218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -23590,23 +23590,27 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>R.F. Moeller Jeweler</t>
+          <t>Darakjian Jewelers</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>shop=jewelry</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr"/>
+          <t>Jewelry store</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>(833) 327-2554</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>alexandra@rfmoeller.com</t>
+          <t>info@darakjian.com</t>
         </is>
       </c>
       <c r="F212" t="inlineStr"/>
@@ -23614,32 +23618,40 @@
       <c r="H212" t="inlineStr"/>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>https://rfmoeller.com</t>
-        </is>
-      </c>
-      <c r="J212" t="inlineStr"/>
+          <t>https://www.darakjian.com</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>101 Willits St, Birmingham, MI 48009, United States</t>
+        </is>
+      </c>
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr"/>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Minneapolis, MN</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>OpenStreetMap</t>
-        </is>
-      </c>
-      <c r="O212" t="inlineStr"/>
-      <c r="P212" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O212" t="n">
+        <v>5</v>
+      </c>
+      <c r="P212" t="n">
+        <v>872</v>
+      </c>
       <c r="Q212" s="2" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/12139116034</t>
+          <t>https://www.google.com/maps/place/Darakjian+Jewelers/data=!4m7!3m6!1s0x8824c7070f5beda7:0xfeec85b71df22c68!8m2!3d42.5474214!4d-83.2162268!16s%2Fg%2F1ptxrxwft!19sChIJp-1bDwfHJIgRaCzyHbeF7P4</t>
         </is>
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, ags, custom-design, since-1951</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S212" t="inlineStr">
@@ -23649,13 +23661,13 @@
       </c>
       <c r="T212" s="2" t="inlineStr">
         <is>
-          <t>https://rfmoeller.com/</t>
+          <t>https://www.darakjian.com/</t>
         </is>
       </c>
       <c r="U212" t="inlineStr"/>
       <c r="V212" t="inlineStr">
         <is>
-          <t>2026-10-14T00:26:23+05:30</t>
+          <t>2026-10-14T00:35:35+05:30</t>
         </is>
       </c>
       <c r="W212" t="inlineStr"/>
@@ -23665,40 +23677,40 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>no-address</t>
+          <t>toll-free</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>(651) 698-6321, (651) 698-6322</t>
-        </is>
-      </c>
-      <c r="AB212" t="inlineStr">
-        <is>
-          <t>https://facebook.com/rfmoellerjeweler, https://instagram.com/rfmoellerjeweler</t>
-        </is>
-      </c>
+          <t>(555) 555-5556</t>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Thomas Joseph &amp; Sons</t>
+          <t>Herman's Creations Ltd</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>shop=jewelry</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr"/>
+          <t>Jeweler</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>(248) 968-0515</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>gb@thomasjosephandsons.com</t>
+          <t>roseville@hermanscreations.com</t>
         </is>
       </c>
       <c r="F213" t="inlineStr"/>
@@ -23706,32 +23718,40 @@
       <c r="H213" t="inlineStr"/>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>https://thomasjosephandsons.com</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr"/>
+          <t>https://www.hermanscreations.com</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>Parking lot, 21700 Greenfield Rd #324, Oak Park, MI 48237, United States</t>
+        </is>
+      </c>
       <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr"/>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Minneapolis, MN</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>OpenStreetMap</t>
-        </is>
-      </c>
-      <c r="O213" t="inlineStr"/>
-      <c r="P213" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O213" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P213" t="n">
+        <v>86</v>
+      </c>
       <c r="Q213" s="2" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/12768888509</t>
+          <t>https://www.google.com/maps/place/Herman%27s+Creations+Ltd/data=!4m7!3m6!1s0x8824c90e6286a6b9:0x4d1025da82081043!8m2!3d42.4530864!4d-83.1999045!16s%2Fg%2F1tjrqlpw!19sChIJuaaGYg7JJIgRQxAIgtolEE0</t>
         </is>
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design, since-1950</t>
+          <t>2 of 3, direct-line, since-1974</t>
         </is>
       </c>
       <c r="S213" t="inlineStr">
@@ -23741,38 +23761,570 @@
       </c>
       <c r="T213" s="2" t="inlineStr">
         <is>
-          <t>https://thomasjosephandsons.com/staff/</t>
+          <t>https://www.hermanscreations.com/</t>
         </is>
       </c>
       <c r="U213" t="inlineStr"/>
       <c r="V213" t="inlineStr">
         <is>
-          <t>2026-10-14T00:26:23+05:30</t>
-        </is>
-      </c>
-      <c r="W213" t="inlineStr"/>
+          <t>2026-10-14T00:38:02+05:30</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>Herman's Creations Jewelers</t>
+        </is>
+      </c>
       <c r="X213" t="inlineStr"/>
       <c r="Y213" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z213" t="inlineStr"/>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>(248) 968-0519, (586) 776-3201</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>https://instagram.com/hermans_creations, https://facebook.com/Hermans-Creations-Jewelers-East-122894551100621</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Metals In Time</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Custom / bespoke jeweler</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Jeweler</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>(248) 582-9344</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>jalexis@metalsintime.com</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Sergio Basmajian</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metalsintime.com</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>301 S Main St, Royal Oak, MI 48067, United States</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>Detroit, MI</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O214" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P214" t="n">
+        <v>758</v>
+      </c>
+      <c r="Q214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Metals+In+Time/data=!4m7!3m6!1s0x8824cf41eeafdb85:0xc44753262c9afc53!8m2!3d42.487994!4d-83.1438463!16s%2Fg%2F1tj80lpt!19sChIJhduv7kHPJIgRU_yaLCZTR8Q</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>2 of 3, direct-line, custom-design</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metalsintime.com/meet-the-team/</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr"/>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>2026-10-14T00:34:10+05:30</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr"/>
+      <c r="X214" t="inlineStr"/>
+      <c r="Y214" t="n">
         <v>0</v>
       </c>
-      <c r="Z213" t="inlineStr">
-        <is>
-          <t>no-address</t>
-        </is>
-      </c>
-      <c r="AA213" t="inlineStr">
-        <is>
-          <t>(612) 339-4111</t>
-        </is>
-      </c>
-      <c r="AB213" t="inlineStr">
-        <is>
-          <t>https://facebook.com/ThomasJosephSons, https://instagram.com/thomasjosephandsons</t>
+      <c r="Z214" t="inlineStr"/>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>(248) 282-3733</t>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>https://facebook.com/Metalsintime, https://instagram.com/Metalsintimejewelers</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Radiant Made For Us</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Custom / bespoke jeweler</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Jewelry store</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>(313) 789-7480</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>allenpark@radiantmadeforus.com</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>https://radiantmadeforus.com</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>6634 Allen Rd, Allen Park, MI 48101, United States</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>Detroit, MI</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O215" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P215" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Radiant+Made+For+Us/data=!4m7!3m6!1s0x883b374334f03ef5:0xea62d7eb1e5918df!8m2!3d42.2582463!4d-83.2094467!16s%2Fg%2F11y5nttj61!19sChIJ9T7wNEM3O4gR3xhZHuvXYuo</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>2 of 3, direct-line, custom-design</t>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T215" s="2" t="inlineStr">
+        <is>
+          <t>https://radiantmadeforus.com/</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr"/>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>2026-10-14T00:40:08+05:30</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr"/>
+      <c r="X215" t="inlineStr"/>
+      <c r="Y215" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z215" t="inlineStr"/>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>(646) 649-4493</t>
+        </is>
+      </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>https://facebook.com/radiantmadeforus, https://instagram.com/radiantmadeforus, https://facebook.com/madeforusdiamonds, https://instagram.com/madeforusdiamonds</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Tapper's Jewelry</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Custom / bespoke jeweler</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Jewelry store</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>(248) 932-7700</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>sales@tappers.com</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Howard Tapper</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>https://tappers.com</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>6337 Orchard Lake Rd, West Bloomfield Township, MI 48322, United States</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>West Bloomfield</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>Detroit, MI</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O216" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P216" t="n">
+        <v>1036</v>
+      </c>
+      <c r="Q216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Tapper%27s+Jewelry/data=!4m7!3m6!1s0x8824ba48855706cf:0xec468d469a462bbd!8m2!3d42.5457394!4d-83.359087!16s%2Fg%2F1v3_397b!19sChIJzwZXhUi6JIgRvStGmkaNRuw</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1977</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T216" s="2" t="inlineStr">
+        <is>
+          <t>https://tappers.com/pages/contact</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr"/>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>2026-10-14T00:34:13+05:30</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr"/>
+      <c r="X216" t="inlineStr"/>
+      <c r="Y216" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z216" t="inlineStr"/>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>(248) 465-1800, (248) 649-2000, (248) 862-9700</t>
+        </is>
+      </c>
+      <c r="AB216" t="inlineStr">
+        <is>
+          <t>https://instagram.com/TappersJewelry, https://facebook.com/TappersJewelry</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Johantgen Jewelers</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Estate &amp; antique jewelry</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Jewelry store</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>(763) 319-2114</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>johantgen@live.com</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>https://www.johantgenjewelers.net</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>115 Willow Bend, Crystal, MN 55428, United States</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>MN</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O217" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P217" t="n">
+        <v>192</v>
+      </c>
+      <c r="Q217" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Johantgen+Jewelers/data=!4m7!3m6!1s0x52b336dca5ae27ad:0x54a13d67412de1ee!8m2!3d45.0537716!4d-93.3665038!16s%2Fg%2F1t_hymw_!19sChIJrSeupdw2s1IR7uEtQWc9oVQ</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>2 of 3, direct-line, custom-design</t>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T217" s="2" t="inlineStr">
+        <is>
+          <t>https://johantgenjewelers.net/</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr"/>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>2026-10-14T00:46:10+05:30</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr"/>
+      <c r="X217" t="inlineStr"/>
+      <c r="Y217" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z217" t="inlineStr"/>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>(763) 537-7233</t>
+        </is>
+      </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>https://facebook.com/johantgenjeweler, https://instagram.com/johantgenjewelers</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>R.F. Moeller Jeweler</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Jewelry store</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>(651) 698-6321</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>alexandra@rfmoeller.com</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>https://rfmoeller.com</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>2065 Ford Pkwy, St Paul, MN 55116, United States</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr"/>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O218" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P218" t="n">
+        <v>2186</v>
+      </c>
+      <c r="Q218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/R.F.+Moeller+Jeweler/data=!4m7!3m6!1s0x87f62978048ef94d:0xea9c4d97c5c2b259!8m2!3d44.9181574!4d-93.1877644!16s%2Fg%2F1v7pz0rd!19sChIJTfmOBHgp9ocRWbLCxZdNnOo</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>2 of 3, direct-line, ags, custom-design, since-1951</t>
+        </is>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T218" s="2" t="inlineStr">
+        <is>
+          <t>https://rfmoeller.com/</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr"/>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>2026-10-14T00:46:15+05:30</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr"/>
+      <c r="X218" t="inlineStr"/>
+      <c r="Y218" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z218" t="inlineStr"/>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>(651) 698-6322</t>
+        </is>
+      </c>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>https://facebook.com/rfmoellerjeweler, https://instagram.com/rfmoellerjeweler</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB213"/>
+  <autoFilter ref="A1:AB218"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId2"/>
@@ -24452,6 +25004,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I213" r:id="rId676"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q213" r:id="rId677"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T213" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I214" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q214" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T214" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I215" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q215" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T215" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I216" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q216" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T216" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I217" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q217" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T217" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I218" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q218" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T218" r:id="rId693"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24463,7 +25030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -24924,14 +25491,14 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C17" t="n">
         <v>3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -24951,21 +25518,21 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48</v>
+        <v>150</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -24978,14 +25545,14 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="C19" t="n">
         <v>2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -25001,27 +25568,54 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Charlotte, NC</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>74</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>7549</v>
-      </c>
-      <c r="C20" t="n">
-        <v>212</v>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="B21" t="n">
+        <v>7795</v>
+      </c>
+      <c r="C21" t="n">
+        <v>217</v>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>2.8%</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>210</v>
-      </c>
-      <c r="F20" t="n">
-        <v>91</v>
-      </c>
-      <c r="G20" t="n">
+      <c r="E21" t="n">
+        <v>215</v>
+      </c>
+      <c r="F21" t="n">
+        <v>93</v>
+      </c>
+      <c r="G21" t="n">
         <v>22</v>
       </c>
     </row>
@@ -25062,7 +25656,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3">
@@ -25072,7 +25666,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4">
@@ -25082,7 +25676,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -25124,7 +25718,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
@@ -25144,7 +25738,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -25173,7 +25767,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T00:35:55+05:30</t>
+          <t>2026-10-14T00:56:04+05:30</t>
         </is>
       </c>
     </row>
@@ -25184,7 +25778,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3">
@@ -25194,7 +25788,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>7549</v>
+        <v>7795</v>
       </c>
     </row>
     <row r="4">

--- a/leadrun_jewelry/jewelry_qualified.xlsx
+++ b/leadrun_jewelry/jewelry_qualified.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qualified Leads'!$A$1:$AB$306</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qualified Leads'!$A$1:$AB$305</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB306"/>
+  <dimension ref="A1:AB305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -24876,16 +24876,16 @@
       </c>
       <c r="W219" t="inlineStr">
         <is>
-          <t>Na Hoku - Hawaii's Finest Jewelers Since 1924, Na Hoku, The Pearl Factory, Na Hoku Jewelers, Pearl Factory</t>
+          <t>Na Hoku - Hawaii's Finest Jewelers Since 1924, Na Hoku, The Pearl Factory, Na Hoku Jewelers, Pearl Factory, Na Hoku Inc</t>
         </is>
       </c>
       <c r="X219" t="inlineStr">
         <is>
-          <t>Dallas, TX, San Diego, CA, San Francisco, CA, Seattle, WA</t>
+          <t>Dallas, TX, Denver, CO, San Diego, CA, San Francisco, CA, Seattle, WA</t>
         </is>
       </c>
       <c r="Y219" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Z219" t="inlineStr">
         <is>
@@ -27470,8 +27470,16 @@
         </is>
       </c>
       <c r="F243" t="inlineStr"/>
-      <c r="G243" t="inlineStr"/>
-      <c r="H243" t="inlineStr"/>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Larry Blauweiss</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
       <c r="I243" s="2" t="inlineStr">
         <is>
           <t>https://www.5thavenuedesigns.com</t>
@@ -27541,7 +27549,7 @@
       </c>
       <c r="X243" t="inlineStr"/>
       <c r="Y243" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z243" t="inlineStr"/>
       <c r="AA243" t="inlineStr">
@@ -27739,7 +27747,7 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, gia</t>
+          <t>2 of 3, role-email, gia, since-2011</t>
         </is>
       </c>
       <c r="S245" t="inlineStr">
@@ -27762,12 +27770,20 @@
           <t>2026-10-14T00:15:24+05:30</t>
         </is>
       </c>
-      <c r="W245" t="inlineStr"/>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>Benadato Trading Company</t>
+        </is>
+      </c>
       <c r="X245" t="inlineStr"/>
       <c r="Y245" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z245" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA245" t="inlineStr"/>
       <c r="AB245" t="inlineStr">
         <is>
@@ -27859,7 +27875,7 @@
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>2 of 3, gia, bench, custom-design</t>
+          <t>2 of 3, gia, bench, custom-design, since-1983</t>
         </is>
       </c>
       <c r="S246" t="inlineStr">
@@ -27889,7 +27905,7 @@
       </c>
       <c r="X246" t="inlineStr"/>
       <c r="Y246" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z246" t="inlineStr">
         <is>
@@ -28014,7 +28030,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>HD Custom</t>
+          <t>JK Diamond Co.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -28024,17 +28040,17 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jeweler</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>(303) 600-8716</t>
+          <t>(303) 305-5910</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>hdcustomjewelryandrepair@gmail.com</t>
+          <t>hello@jkdiamondco.com</t>
         </is>
       </c>
       <c r="F248" t="inlineStr"/>
@@ -28042,24 +28058,16 @@
       <c r="H248" t="inlineStr"/>
       <c r="I248" s="2" t="inlineStr">
         <is>
-          <t>https://hd-custom-jewelry-repair.ueniweb.com</t>
+          <t>https://www.jkdiamondco.com</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>10061 E Colfax Ave, Aurora, CO 80010</t>
-        </is>
-      </c>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t>Aurora</t>
-        </is>
-      </c>
-      <c r="L248" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
+          <t>2422 E 3rd Ave, Denver, CO 80206, United States</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr"/>
       <c r="M248" t="inlineStr">
         <is>
           <t>Denver, CO</t>
@@ -28067,19 +28075,23 @@
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O248" t="inlineStr"/>
-      <c r="P248" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O248" t="n">
+        <v>5</v>
+      </c>
+      <c r="P248" t="n">
+        <v>138</v>
+      </c>
       <c r="Q248" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/aurora-co/mip/hd-custom-577792287</t>
+          <t>https://www.google.com/maps/place/JK+Diamond+Co./data=!4m7!3m6!1s0x876c7f58603bd1a9:0xbbe855e447f0b9aa!8m2!3d39.7208718!4d-104.9576087!16s%2Fg%2F11f9ct4v4z!19sChIJqdE7YFh_bIcRqrnwR-RV6Ls</t>
         </is>
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design</t>
+          <t>2 of 3, role-email, direct-line</t>
         </is>
       </c>
       <c r="S248" t="inlineStr">
@@ -28089,13 +28101,13 @@
       </c>
       <c r="T248" s="2" t="inlineStr">
         <is>
-          <t>https://hd-custom-jewelry-repair.ueniweb.com/</t>
+          <t>https://www.jkdiamondco.com/</t>
         </is>
       </c>
       <c r="U248" t="inlineStr"/>
       <c r="V248" t="inlineStr">
         <is>
-          <t>2026-10-14T01:37:37+05:30</t>
+          <t>2026-10-14T00:17:54+05:30</t>
         </is>
       </c>
       <c r="W248" t="inlineStr"/>
@@ -28106,56 +28118,72 @@
       <c r="Z248" t="inlineStr"/>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>(323) 695-5020</t>
+          <t>(213) 761-5992</t>
         </is>
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>https://instagram.com/hd_customjewelry_</t>
+          <t>https://instagram.com/jkdiamondco</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>JK Diamond Co.</t>
+          <t>Ooh Ahh Jewelery</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Jeweler</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>(303) 305-5910</t>
+          <t>(720) 855-7241</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>hello@jkdiamondco.com</t>
+          <t>oohaahabq@gmail.com</t>
         </is>
       </c>
       <c r="F249" t="inlineStr"/>
-      <c r="G249" t="inlineStr"/>
-      <c r="H249" t="inlineStr"/>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Mary Vigil</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="I249" s="2" t="inlineStr">
         <is>
-          <t>https://www.jkdiamondco.com</t>
+          <t>https://www.oohaahjewelry.com</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>2422 E 3rd Ave, Denver, CO 80206, United States</t>
-        </is>
-      </c>
-      <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
+          <t>4318 Tennyson St, Denver, CO 80212</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
       <c r="M249" t="inlineStr">
         <is>
           <t>Denver, CO</t>
@@ -28163,23 +28191,19 @@
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O249" t="n">
-        <v>5</v>
-      </c>
-      <c r="P249" t="n">
-        <v>138</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr"/>
+      <c r="P249" t="inlineStr"/>
       <c r="Q249" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/JK+Diamond+Co./data=!4m7!3m6!1s0x876c7f58603bd1a9:0xbbe855e447f0b9aa!8m2!3d39.7208718!4d-104.9576087!16s%2Fg%2F11f9ct4v4z!19sChIJqdE7YFh_bIcRqrnwR-RV6Ls</t>
+          <t>https://www.yellowpages.com/denver-co/mip/ooh-ahh-jewelery-3791097</t>
         </is>
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line</t>
+          <t>2 of 3, direct-line, custom-design, since-1988</t>
         </is>
       </c>
       <c r="S249" t="inlineStr">
@@ -28189,77 +28213,85 @@
       </c>
       <c r="T249" s="2" t="inlineStr">
         <is>
-          <t>https://www.jkdiamondco.com/</t>
+          <t>https://oohaahjewelry.com/</t>
         </is>
       </c>
       <c r="U249" t="inlineStr"/>
       <c r="V249" t="inlineStr">
         <is>
-          <t>2026-10-14T00:17:54+05:30</t>
-        </is>
-      </c>
-      <c r="W249" t="inlineStr"/>
+          <t>2026-10-14T01:37:14+05:30</t>
+        </is>
+      </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>Ooh Aah Jewelry, Inc.</t>
+        </is>
+      </c>
       <c r="X249" t="inlineStr"/>
       <c r="Y249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z249" t="inlineStr"/>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>(213) 761-5992</t>
+          <t>(505) 265-7170</t>
         </is>
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>https://instagram.com/jkdiamondco</t>
+          <t>https://facebook.com/oohaahalbuquerque, https://instagram.com/oohaahjewelry</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Ooh Ahh Jewelery</t>
+          <t>Sowilo Artisan Jewelry</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>(720) 855-7241</t>
+          <t>(303) 548-5467</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>oohaahabq@gmail.com</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr"/>
+          <t>sowilollc@gmail.com</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/bonnie-startek-5122141b3</t>
+        </is>
+      </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Mary Vigil</t>
+          <t>Bonnie Startek</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="I250" s="2" t="inlineStr">
         <is>
-          <t>https://www.oohaahjewelry.com</t>
+          <t>https://sowiloartisanjewelry.com</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>4318 Tennyson St, Denver, CO 80212</t>
+          <t>999 Vallejo St Unit 3, Studio 4K, Denver, CO 80204, United States</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -28279,63 +28311,67 @@
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O250" t="inlineStr"/>
-      <c r="P250" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O250" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P250" t="n">
+        <v>60</v>
+      </c>
       <c r="Q250" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/denver-co/mip/ooh-ahh-jewelery-3791097</t>
+          <t>https://www.google.com/maps/place/Sowilo+Artisan+Jewelry/data=!4m7!3m6!1s0x876c7e540569644b:0xca2f5260ce1de685!8m2!3d39.7323841!4d-105.0133421!16s%2Fg%2F11c3s9631b!19sChIJS2RpBVR-bIcRheYdzmBSL8o</t>
         </is>
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design, since-1988</t>
+          <t>2 of 3, custom-design, since-2003</t>
         </is>
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T250" s="2" t="inlineStr">
         <is>
-          <t>https://oohaahjewelry.com/</t>
-        </is>
-      </c>
-      <c r="U250" t="inlineStr"/>
+          <t>https://sowiloartisanjewelry.com/</t>
+        </is>
+      </c>
+      <c r="U250" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Bonnie+Startek%22+Denver+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V250" t="inlineStr">
         <is>
-          <t>2026-10-14T01:37:14+05:30</t>
+          <t>2026-10-14T00:14:18+05:30</t>
         </is>
       </c>
       <c r="W250" t="inlineStr"/>
       <c r="X250" t="inlineStr"/>
       <c r="Y250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z250" t="inlineStr"/>
-      <c r="AA250" t="inlineStr">
-        <is>
-          <t>(505) 265-7170</t>
-        </is>
-      </c>
+      <c r="AA250" t="inlineStr"/>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>https://facebook.com/oohaahalbuquerque, https://instagram.com/oohaahjewelry</t>
+          <t>https://instagram.com/sowilo_artisan_jewelry, https://twitter.com/sowilo_jewelry, https://instagram.com/sowilo_artisan_jewelr, https://facebook.com/Sowilo-Artisan-Jewelry-790705241051708</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Sowilo Artisan Jewelry</t>
+          <t>The Diamond Reserve Denver</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -28345,37 +28381,25 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>(303) 548-5467</t>
+          <t>(303) 385-8449</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>sowilollc@gmail.com</t>
-        </is>
-      </c>
-      <c r="F251" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/bonnie-startek-5122141b3</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>Bonnie Startek</t>
-        </is>
-      </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
+          <t>hello@thediamondreserve.com</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr"/>
+      <c r="H251" t="inlineStr"/>
       <c r="I251" s="2" t="inlineStr">
         <is>
-          <t>https://sowiloartisanjewelry.com</t>
+          <t>https://www.thediamondreserve.com</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>999 Vallejo St Unit 3, Studio 4K, Denver, CO 80204, United States</t>
+          <t>Located in Fillmore Plaza, 100 Fillmore St #552, Denver, CO 80206, United States</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -28402,60 +28426,64 @@
         <v>4.9</v>
       </c>
       <c r="P251" t="n">
-        <v>60</v>
+        <v>1127</v>
       </c>
       <c r="Q251" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Sowilo+Artisan+Jewelry/data=!4m7!3m6!1s0x876c7e540569644b:0xca2f5260ce1de685!8m2!3d39.7323841!4d-105.0133421!16s%2Fg%2F11c3s9631b!19sChIJS2RpBVR-bIcRheYdzmBSL8o</t>
+          <t>https://www.google.com/maps/place/The+Diamond+Reserve+Denver/data=!4m7!3m6!1s0x876c7e977d1a8e6b:0x97af2573b585b30c!8m2!3d39.7186!4d-104.953081!16s%2Fg%2F113dvzskw!19sChIJa44afZd-bIcRDLOFtXMlr5c</t>
         </is>
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>2 of 3, custom-design</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-2015</t>
         </is>
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="T251" s="2" t="inlineStr">
         <is>
-          <t>https://sowiloartisanjewelry.com/</t>
-        </is>
-      </c>
-      <c r="U251" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=%22Bonnie+Startek%22+Denver+linkedin&amp;hl=en&amp;num=10</t>
-        </is>
-      </c>
+          <t>https://thediamondreserve.com/</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr"/>
       <c r="V251" t="inlineStr">
         <is>
-          <t>2026-10-14T00:14:18+05:30</t>
-        </is>
-      </c>
-      <c r="W251" t="inlineStr"/>
+          <t>2026-10-14T00:13:14+05:30</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>The Diamond Reserve</t>
+        </is>
+      </c>
       <c r="X251" t="inlineStr"/>
       <c r="Y251" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z251" t="inlineStr"/>
-      <c r="AA251" t="inlineStr"/>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>(720) 667-1593, (737) 738-5223</t>
+        </is>
+      </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>https://instagram.com/sowilo_artisan_jewelry, https://twitter.com/sowilo_jewelry, https://instagram.com/sowilo_artisan_jewelr, https://facebook.com/Sowilo-Artisan-Jewelry-790705241051708</t>
+          <t>https://instagram.com/thediamondreserve, https://facebook.com/thediamondreserve, https://twitter.com/diamondreserve</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>The Diamond Reserve Denver</t>
+          <t>Williams Jewelers</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -28465,30 +28493,38 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>(303) 385-8449</t>
+          <t>(303) 761-9700</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>hello@thediamondreserve.com</t>
+          <t>ccn@williamsjewelers.net</t>
         </is>
       </c>
       <c r="F252" t="inlineStr"/>
-      <c r="G252" t="inlineStr"/>
-      <c r="H252" t="inlineStr"/>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Steve Williams</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I252" s="2" t="inlineStr">
         <is>
-          <t>https://www.thediamondreserve.com</t>
+          <t>https://www.williamsdiamonds.com</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>Located in Fillmore Plaza, 100 Fillmore St #552, Denver, CO 80206, United States</t>
+          <t>5095 S Broadway, Englewood, CO 80113, United States</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>ENGLEWOOD</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -28510,16 +28546,16 @@
         <v>4.9</v>
       </c>
       <c r="P252" t="n">
-        <v>1127</v>
+        <v>1625</v>
       </c>
       <c r="Q252" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/The+Diamond+Reserve+Denver/data=!4m7!3m6!1s0x876c7e977d1a8e6b:0x97af2573b585b30c!8m2!3d39.7186!4d-104.953081!16s%2Fg%2F113dvzskw!19sChIJa44afZd-bIcRDLOFtXMlr5c</t>
+          <t>https://www.google.com/maps/place/Williams+Jewelers/data=!4m7!3m6!1s0x876c80563cc30911:0x2d1610a24c7c2752!8m2!3d39.624365!4d-104.9883621!16s%2Fg%2F1tftft9k!19sChIJEQnDPFaAbIcRUid8TKIQFi0</t>
         </is>
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, direct-line, bench, custom-design, since-1969</t>
         </is>
       </c>
       <c r="S252" t="inlineStr">
@@ -28529,105 +28565,121 @@
       </c>
       <c r="T252" s="2" t="inlineStr">
         <is>
-          <t>https://thediamondreserve.com/</t>
+          <t>https://williamsjewelers.net/</t>
         </is>
       </c>
       <c r="U252" t="inlineStr"/>
       <c r="V252" t="inlineStr">
         <is>
-          <t>2026-10-14T00:13:14+05:30</t>
-        </is>
-      </c>
-      <c r="W252" t="inlineStr"/>
+          <t>2026-10-14T00:18:37+05:30</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>Williams Jewelers of Cherry Creek North</t>
+        </is>
+      </c>
       <c r="X252" t="inlineStr"/>
       <c r="Y252" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z252" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA252" t="inlineStr">
         <is>
-          <t>(720) 667-1593, (737) 738-5223</t>
+          <t>(720) 794-8111</t>
         </is>
       </c>
       <c r="AB252" t="inlineStr">
         <is>
-          <t>https://instagram.com/thediamondreserve, https://facebook.com/thediamondreserve, https://twitter.com/diamondreserve</t>
+          <t>https://facebook.com/WilliamsJewelersEnglewood, https://instagram.com/williams.jewelers, https://facebook.com/WilliamsJewelersCherryCreek, https://instagram.com/williamsjewelersdenver, https://twitter.com/wjcherrycreek</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Williams Jewelers</t>
+          <t>Gold Works</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers, Jewelry Designers</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>(303) 761-9700</t>
+          <t>(703) 683-0333</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>ccn@williamsjewelers.net</t>
+          <t>david@goldworksusa.com</t>
         </is>
       </c>
       <c r="F253" t="inlineStr"/>
-      <c r="G253" t="inlineStr"/>
-      <c r="H253" t="inlineStr"/>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>David Martin</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Featured On About Page</t>
+        </is>
+      </c>
       <c r="I253" s="2" t="inlineStr">
         <is>
-          <t>https://www.williamsdiamonds.com</t>
+          <t>https://www.goldworksusa.com</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>5095 S Broadway, Englewood, CO 80113, United States</t>
+          <t>1400 King St, Alexandria, VA 22314</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>ENGLEWOOD</t>
+          <t>Alexandria</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O253" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P253" t="n">
-        <v>1625</v>
+        <v>5</v>
       </c>
       <c r="Q253" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Williams+Jewelers/data=!4m7!3m6!1s0x876c80563cc30911:0x2d1610a24c7c2752!8m2!3d39.624365!4d-104.9883621!16s%2Fg%2F1tftft9k!19sChIJEQnDPFaAbIcRUid8TKIQFi0</t>
+          <t>https://www.yellowpages.com/alexandria-va/mip/gold-works-3576887</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, bench, custom-design, since-1969</t>
+          <t>2 of 3, direct-line, gia, ja, custom-design, since-1983</t>
         </is>
       </c>
       <c r="S253" t="inlineStr">
@@ -28637,91 +28689,79 @@
       </c>
       <c r="T253" s="2" t="inlineStr">
         <is>
-          <t>https://williamsjewelers.net/</t>
+          <t>https://goldworksusa.com/</t>
         </is>
       </c>
       <c r="U253" t="inlineStr"/>
       <c r="V253" t="inlineStr">
         <is>
-          <t>2026-10-14T00:18:37+05:30</t>
-        </is>
-      </c>
-      <c r="W253" t="inlineStr">
-        <is>
-          <t>Williams Jewelers of Cherry Creek North</t>
-        </is>
-      </c>
+          <t>2026-10-14T01:39:49+05:30</t>
+        </is>
+      </c>
+      <c r="W253" t="inlineStr"/>
       <c r="X253" t="inlineStr"/>
       <c r="Y253" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z253" t="inlineStr"/>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>(720) 794-8111</t>
+          <t>(703) 216-6156</t>
         </is>
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>https://facebook.com/WilliamsJewelersEnglewood, https://instagram.com/williams.jewelers, https://facebook.com/WilliamsJewelersCherryCreek, https://instagram.com/williamsjewelersdenver, https://twitter.com/wjcherrycreek</t>
+          <t>https://facebook.com/goldworksusa, https://instagram.com/goldworksusa, https://twitter.com/urgoldguy</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Gold Works</t>
+          <t>Mervis</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers, Jewelry Designers</t>
+          <t>shop=jewelry</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>(703) 683-0333</t>
+          <t>(202) 293-0600</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>david@goldworksusa.com</t>
+          <t>concierge@mervisdiamond.com</t>
         </is>
       </c>
       <c r="F254" t="inlineStr"/>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>David Martin</t>
-        </is>
-      </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>Featured On About Page</t>
-        </is>
-      </c>
+      <c r="G254" t="inlineStr"/>
+      <c r="H254" t="inlineStr"/>
       <c r="I254" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldworksusa.com</t>
+          <t>https://www.mervisdiamond.com</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>1400 King St, Alexandria, VA 22314</t>
+          <t>1700 K Street Northwest, Washington, DC 20006</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>Alexandria</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -28731,23 +28771,19 @@
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O254" t="n">
-        <v>5</v>
-      </c>
-      <c r="P254" t="n">
-        <v>5</v>
-      </c>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr"/>
+      <c r="P254" t="inlineStr"/>
       <c r="Q254" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/alexandria-va/mip/gold-works-3576887</t>
+          <t>https://www.openstreetmap.org/node/730833789</t>
         </is>
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, ja, custom-design, since-1983</t>
+          <t>2 of 3, role-email, direct-line, gia, custom-design</t>
         </is>
       </c>
       <c r="S254" t="inlineStr">
@@ -28757,13 +28793,13 @@
       </c>
       <c r="T254" s="2" t="inlineStr">
         <is>
-          <t>https://goldworksusa.com/</t>
+          <t>https://www.mervisdiamond.com/pages/contact/</t>
         </is>
       </c>
       <c r="U254" t="inlineStr"/>
       <c r="V254" t="inlineStr">
         <is>
-          <t>2026-10-14T01:39:49+05:30</t>
+          <t>2026-10-14T00:06:30+05:30</t>
         </is>
       </c>
       <c r="W254" t="inlineStr"/>
@@ -28774,19 +28810,19 @@
       <c r="Z254" t="inlineStr"/>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>(703) 216-6156</t>
+          <t>(301) 231-0030, (703) 448-9000</t>
         </is>
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>https://facebook.com/goldworksusa, https://instagram.com/goldworksusa, https://twitter.com/urgoldguy</t>
+          <t>https://instagram.com/mervisdiamond, https://facebook.com/mervisdiamonds, https://twitter.com/mervisdiamonds</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Mervis</t>
+          <t>Mystique Jewelers of Old Town Alexandria</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -28796,17 +28832,17 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>shop=jewelry</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>(202) 293-0600</t>
+          <t>(703) 836-1401</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>concierge@mervisdiamond.com</t>
+          <t>mystique@mystiquejewelers.com</t>
         </is>
       </c>
       <c r="F255" t="inlineStr"/>
@@ -28814,22 +28850,22 @@
       <c r="H255" t="inlineStr"/>
       <c r="I255" s="2" t="inlineStr">
         <is>
-          <t>https://www.mervisdiamond.com</t>
+          <t>https://www.mystiquejewelers.com</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>1700 K Street Northwest, Washington, DC 20006</t>
+          <t>123 S Fairfax St, Alexandria, VA 22314, United States</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Middleburg</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
@@ -28839,19 +28875,23 @@
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>OpenStreetMap</t>
-        </is>
-      </c>
-      <c r="O255" t="inlineStr"/>
-      <c r="P255" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O255" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P255" t="n">
+        <v>150</v>
+      </c>
       <c r="Q255" s="2" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/730833789</t>
+          <t>https://www.google.com/maps/place/Mystique+Jewelers+of+Old+Town+Alexandria/data=!4m7!3m6!1s0x89b7b058c618240d:0xfb6ee0faa427cbad!8m2!3d38.8038272!4d-77.0427885!16s%2Fg%2F1262pbwr3!19sChIJDSQYxliwt4kRrcsnpPrgbvs</t>
         </is>
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, gia, custom-design</t>
+          <t>2 of 3, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S255" t="inlineStr">
@@ -28861,13 +28901,13 @@
       </c>
       <c r="T255" s="2" t="inlineStr">
         <is>
-          <t>https://www.mervisdiamond.com/pages/contact/</t>
+          <t>https://www.mystiquejewelers.com/</t>
         </is>
       </c>
       <c r="U255" t="inlineStr"/>
       <c r="V255" t="inlineStr">
         <is>
-          <t>2026-10-14T00:06:30+05:30</t>
+          <t>2026-10-14T00:29:13+05:30</t>
         </is>
       </c>
       <c r="W255" t="inlineStr"/>
@@ -28878,24 +28918,24 @@
       <c r="Z255" t="inlineStr"/>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>(301) 231-0030, (703) 448-9000</t>
+          <t>(540) 454-7009, (540) 687-3100</t>
         </is>
       </c>
       <c r="AB255" t="inlineStr">
         <is>
-          <t>https://instagram.com/mervisdiamond, https://facebook.com/mervisdiamonds, https://twitter.com/mervisdiamonds</t>
+          <t>https://facebook.com/mystique.jewelers, https://instagram.com/mystiquejewelers, https://x.com/MystiqueJewelry, https://twitter.com/MystiqueJewelry</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Mystique Jewelers of Old Town Alexandria</t>
+          <t>Secrète Fine Jewelry</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -28905,12 +28945,12 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>(703) 836-1401</t>
+          <t>(202) 588-7275</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>mystique@mystiquejewelers.com</t>
+          <t>contact@secrete.com</t>
         </is>
       </c>
       <c r="F256" t="inlineStr"/>
@@ -28918,22 +28958,22 @@
       <c r="H256" t="inlineStr"/>
       <c r="I256" s="2" t="inlineStr">
         <is>
-          <t>https://www.mystiquejewelers.com</t>
+          <t>https://www.secrete.com</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>123 S Fairfax St, Alexandria, VA 22314, United States</t>
+          <t>1607 Connecticut Ave NW, Washington, DC 20009, United States</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>Middleburg</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -28947,19 +28987,19 @@
         </is>
       </c>
       <c r="O256" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="P256" t="n">
-        <v>150</v>
+        <v>256</v>
       </c>
       <c r="Q256" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Mystique+Jewelers+of+Old+Town+Alexandria/data=!4m7!3m6!1s0x89b7b058c618240d:0xfb6ee0faa427cbad!8m2!3d38.8038272!4d-77.0427885!16s%2Fg%2F1262pbwr3!19sChIJDSQYxliwt4kRrcsnpPrgbvs</t>
+          <t>https://www.google.com/maps/place/Secr%C3%A8te+Fine+Jewelry/data=!4m7!3m6!1s0x89b7b7c61a67d5ed:0xb9e144573ac6af9!8m2!3d38.9115429!4d-77.0442796!16s%2Fg%2F1tz728l6!19sChIJ7dVnGsa3t4kR-Wqsc0UUngs</t>
         </is>
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design</t>
+          <t>2 of 3, role-email, direct-line, gia, bench, custom-design</t>
         </is>
       </c>
       <c r="S256" t="inlineStr">
@@ -28969,36 +29009,32 @@
       </c>
       <c r="T256" s="2" t="inlineStr">
         <is>
-          <t>https://www.mystiquejewelers.com/</t>
+          <t>https://www.secrete.com/</t>
         </is>
       </c>
       <c r="U256" t="inlineStr"/>
       <c r="V256" t="inlineStr">
         <is>
-          <t>2026-10-14T00:29:13+05:30</t>
+          <t>2026-10-14T00:23:44+05:30</t>
         </is>
       </c>
       <c r="W256" t="inlineStr"/>
       <c r="X256" t="inlineStr"/>
       <c r="Y256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z256" t="inlineStr"/>
       <c r="AA256" t="inlineStr">
         <is>
-          <t>(540) 454-7009, (540) 687-3100</t>
-        </is>
-      </c>
-      <c r="AB256" t="inlineStr">
-        <is>
-          <t>https://facebook.com/mystique.jewelers, https://instagram.com/mystiquejewelers, https://x.com/MystiqueJewelry, https://twitter.com/MystiqueJewelry</t>
-        </is>
-      </c>
+          <t>(301) 530-7892</t>
+        </is>
+      </c>
+      <c r="AB256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Secrète Fine Jewelry</t>
+          <t>The Intrepid Wendell</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -29008,30 +29044,38 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>(202) 588-7275</t>
+          <t>(202) 735-5973</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>contact@secrete.com</t>
+          <t>wendell@theintrepidwendell.com</t>
         </is>
       </c>
       <c r="F257" t="inlineStr"/>
-      <c r="G257" t="inlineStr"/>
-      <c r="H257" t="inlineStr"/>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Daniel Boettcher</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="I257" s="2" t="inlineStr">
         <is>
-          <t>https://www.secrete.com</t>
+          <t>https://theintrepidwendell.com</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>1607 Connecticut Ave NW, Washington, DC 20009, United States</t>
+          <t>1401 K St NW Ste 688, Washington, DC 20005</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -29051,23 +29095,19 @@
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O257" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="P257" t="n">
-        <v>256</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr"/>
+      <c r="P257" t="inlineStr"/>
       <c r="Q257" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Secr%C3%A8te+Fine+Jewelry/data=!4m7!3m6!1s0x89b7b7c61a67d5ed:0xb9e144573ac6af9!8m2!3d38.9115429!4d-77.0442796!16s%2Fg%2F1tz728l6!19sChIJ7dVnGsa3t4kR-Wqsc0UUngs</t>
+          <t>https://www.yellowpages.com/washington-dc/mip/the-intrepid-wendell-525132651</t>
         </is>
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, gia, bench, custom-design</t>
+          <t>2 of 3, direct-line, gia, custom-design</t>
         </is>
       </c>
       <c r="S257" t="inlineStr">
@@ -29077,32 +29117,36 @@
       </c>
       <c r="T257" s="2" t="inlineStr">
         <is>
-          <t>https://www.secrete.com/</t>
+          <t>https://theintrepidwendell.com/</t>
         </is>
       </c>
       <c r="U257" t="inlineStr"/>
       <c r="V257" t="inlineStr">
         <is>
-          <t>2026-10-14T00:23:44+05:30</t>
+          <t>2026-10-14T01:39:18+05:30</t>
         </is>
       </c>
       <c r="W257" t="inlineStr"/>
       <c r="X257" t="inlineStr"/>
       <c r="Y257" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z257" t="inlineStr"/>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>(301) 530-7892</t>
-        </is>
-      </c>
-      <c r="AB257" t="inlineStr"/>
+          <t>(202) 688-0545</t>
+        </is>
+      </c>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>https://instagram.com/theintrepidwendell</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>The Intrepid Wendell</t>
+          <t>WASHINGTON DIAMOND</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -29112,50 +29156,46 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers</t>
+          <t>Jeweler</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>(202) 735-5973</t>
+          <t>(703) 536-3600</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>wendell@theintrepidwendell.com</t>
-        </is>
-      </c>
-      <c r="F258" t="inlineStr"/>
+          <t>info@washingtondiamond.com</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tomdaube</t>
+        </is>
+      </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Daniel Boettcher</t>
+          <t>Tom Daube</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>President</t>
         </is>
       </c>
       <c r="I258" s="2" t="inlineStr">
         <is>
-          <t>https://theintrepidwendell.com</t>
+          <t>https://www.washingtondiamond.com</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>1401 K St NW Ste 688, Washington, DC 20005</t>
-        </is>
-      </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t>Washington</t>
-        </is>
-      </c>
-      <c r="L258" t="inlineStr">
-        <is>
-          <t>DC</t>
-        </is>
-      </c>
+          <t>1245 W Broad St, Falls Church, VA 22046, United States</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr"/>
       <c r="M258" t="inlineStr">
         <is>
           <t>Washington, DC</t>
@@ -29163,35 +29203,43 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O258" t="inlineStr"/>
-      <c r="P258" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O258" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P258" t="n">
+        <v>237</v>
+      </c>
       <c r="Q258" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/washington-dc/mip/the-intrepid-wendell-525132651</t>
+          <t>https://www.google.com/maps/place/WASHINGTON+DIAMOND/data=!4m7!3m6!1s0x89b7b4d23e29f109:0xab36956702e4de7c!8m2!3d38.8941055!4d-77.1900659!16s%2Fg%2F1tgnbhn7!19sChIJCfEpPtK0t4kRfN7kAmeVNqs</t>
         </is>
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design</t>
+          <t>2 of 3, role-email, gia, bench, custom-design, since-1969</t>
         </is>
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T258" s="2" t="inlineStr">
         <is>
-          <t>https://theintrepidwendell.com/</t>
-        </is>
-      </c>
-      <c r="U258" t="inlineStr"/>
+          <t>https://washingtondiamond.com/pages/contact-us</t>
+        </is>
+      </c>
+      <c r="U258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Tom+Daube%22+Washington+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V258" t="inlineStr">
         <is>
-          <t>2026-10-14T01:39:18+05:30</t>
+          <t>2026-10-14T00:28:26+05:30</t>
         </is>
       </c>
       <c r="W258" t="inlineStr"/>
@@ -29200,21 +29248,17 @@
         <v>0</v>
       </c>
       <c r="Z258" t="inlineStr"/>
-      <c r="AA258" t="inlineStr">
-        <is>
-          <t>(202) 688-0545</t>
-        </is>
-      </c>
+      <c r="AA258" t="inlineStr"/>
       <c r="AB258" t="inlineStr">
         <is>
-          <t>https://instagram.com/theintrepidwendell</t>
+          <t>https://instagram.com/mywashingtondiamond, https://facebook.com/WashingtonDiamondVA</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>WASHINGTON DIAMOND</t>
+          <t>Darakjian Jewelers</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -29224,49 +29268,37 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Jeweler</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>(703) 536-3600</t>
+          <t>(833) 327-2554</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>info@washingtondiamond.com</t>
-        </is>
-      </c>
-      <c r="F259" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/tomdaube</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>Tom Daube</t>
-        </is>
-      </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
+          <t>info@darakjian.com</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr"/>
+      <c r="H259" t="inlineStr"/>
       <c r="I259" s="2" t="inlineStr">
         <is>
-          <t>https://www.washingtondiamond.com</t>
+          <t>https://www.darakjian.com</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>1245 W Broad St, Falls Church, VA 22046, United States</t>
+          <t>101 Willits St, Birmingham, MI 48009, United States</t>
         </is>
       </c>
       <c r="K259" t="inlineStr"/>
       <c r="L259" t="inlineStr"/>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -29275,39 +29307,35 @@
         </is>
       </c>
       <c r="O259" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P259" t="n">
-        <v>237</v>
+        <v>872</v>
       </c>
       <c r="Q259" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/WASHINGTON+DIAMOND/data=!4m7!3m6!1s0x89b7b4d23e29f109:0xab36956702e4de7c!8m2!3d38.8941055!4d-77.1900659!16s%2Fg%2F1tgnbhn7!19sChIJCfEpPtK0t4kRfN7kAmeVNqs</t>
+          <t>https://www.google.com/maps/place/Darakjian+Jewelers/data=!4m7!3m6!1s0x8824c7070f5beda7:0xfeec85b71df22c68!8m2!3d42.5474214!4d-83.2162268!16s%2Fg%2F1ptxrxwft!19sChIJp-1bDwfHJIgRaCzyHbeF7P4</t>
         </is>
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, gia, bench, custom-design, since-1969</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="T259" s="2" t="inlineStr">
         <is>
-          <t>https://washingtondiamond.com/pages/contact-us</t>
-        </is>
-      </c>
-      <c r="U259" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=%22Tom+Daube%22+Washington+linkedin&amp;hl=en&amp;num=10</t>
-        </is>
-      </c>
+          <t>https://www.darakjian.com/</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr"/>
       <c r="V259" t="inlineStr">
         <is>
-          <t>2026-10-14T00:28:26+05:30</t>
+          <t>2026-10-14T00:35:35+05:30</t>
         </is>
       </c>
       <c r="W259" t="inlineStr"/>
@@ -29315,18 +29343,22 @@
       <c r="Y259" t="n">
         <v>0</v>
       </c>
-      <c r="Z259" t="inlineStr"/>
-      <c r="AA259" t="inlineStr"/>
-      <c r="AB259" t="inlineStr">
-        <is>
-          <t>https://instagram.com/mywashingtondiamond, https://facebook.com/WashingtonDiamondVA</t>
-        </is>
-      </c>
+      <c r="Z259" t="inlineStr">
+        <is>
+          <t>toll-free</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>(555) 555-5556</t>
+        </is>
+      </c>
+      <c r="AB259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Darakjian Jewelers</t>
+          <t>Golden Sun Jewelry</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -29336,17 +29368,17 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>(833) 327-2554</t>
+          <t>(248) 559-6289</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>info@darakjian.com</t>
+          <t>info@goldensunjewelry.com</t>
         </is>
       </c>
       <c r="F260" t="inlineStr"/>
@@ -29354,16 +29386,24 @@
       <c r="H260" t="inlineStr"/>
       <c r="I260" s="2" t="inlineStr">
         <is>
-          <t>https://www.darakjian.com</t>
+          <t>https://www.goldensunjewelry.com</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>101 Willits St, Birmingham, MI 48009, United States</t>
-        </is>
-      </c>
-      <c r="K260" t="inlineStr"/>
-      <c r="L260" t="inlineStr"/>
+          <t>23077 Greenfield Rd, Southfield, MI 48075</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Southfield</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
       <c r="M260" t="inlineStr">
         <is>
           <t>Detroit, MI</t>
@@ -29371,23 +29411,23 @@
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O260" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P260" t="n">
-        <v>872</v>
+        <v>1</v>
       </c>
       <c r="Q260" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Darakjian+Jewelers/data=!4m7!3m6!1s0x8824c7070f5beda7:0xfeec85b71df22c68!8m2!3d42.5474214!4d-83.2162268!16s%2Fg%2F1ptxrxwft!19sChIJp-1bDwfHJIgRaCzyHbeF7P4</t>
+          <t>https://www.yellowpages.com/southfield-mi/mip/golden-sun-jewelry-460257159</t>
         </is>
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-1989</t>
         </is>
       </c>
       <c r="S260" t="inlineStr">
@@ -29397,56 +29437,60 @@
       </c>
       <c r="T260" s="2" t="inlineStr">
         <is>
-          <t>https://www.darakjian.com/</t>
+          <t>https://www.goldensunjewelry.com/contacts/</t>
         </is>
       </c>
       <c r="U260" t="inlineStr"/>
       <c r="V260" t="inlineStr">
         <is>
-          <t>2026-10-14T00:35:35+05:30</t>
-        </is>
-      </c>
-      <c r="W260" t="inlineStr"/>
+          <t>2026-10-14T01:41:10+05:30</t>
+        </is>
+      </c>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>Golden Sun Jewlery</t>
+        </is>
+      </c>
       <c r="X260" t="inlineStr"/>
       <c r="Y260" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z260" t="inlineStr">
-        <is>
-          <t>toll-free</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Z260" t="inlineStr"/>
       <c r="AA260" t="inlineStr">
         <is>
-          <t>(555) 555-5556</t>
-        </is>
-      </c>
-      <c r="AB260" t="inlineStr"/>
+          <t>(248) 559-5142</t>
+        </is>
+      </c>
+      <c r="AB260" t="inlineStr">
+        <is>
+          <t>https://facebook.com/GoldenSunJewelry, https://instagram.com/goldensunjewelry, https://twitter.com/GSJ_Southfield</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Golden Sun Jewelry</t>
+          <t>Herman's Creations Jewelers Inc.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Jewelry Repairing, Diamond Setters</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>(248) 559-6289</t>
+          <t>(586) 776-3200</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>info@goldensunjewelry.com</t>
+          <t>roseville@hermanscreations.com</t>
         </is>
       </c>
       <c r="F261" t="inlineStr"/>
@@ -29454,17 +29498,17 @@
       <c r="H261" t="inlineStr"/>
       <c r="I261" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldensunjewelry.com</t>
+          <t>https://www.hermanscreations.com</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>23077 Greenfield Rd, Southfield, MI 48075</t>
+          <t>28885 Gratiot Ave, Roseville, MI 48066</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>Southfield</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -29483,19 +29527,19 @@
         </is>
       </c>
       <c r="O261" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P261" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q261" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/southfield-mi/mip/golden-sun-jewelry-460257159</t>
+          <t>https://www.yellowpages.com/roseville-mi/mip/hermans-creations-jewelers-inc-6517282</t>
         </is>
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-1989</t>
+          <t>2 of 3, direct-line, since-1974</t>
         </is>
       </c>
       <c r="S261" t="inlineStr">
@@ -29505,60 +29549,64 @@
       </c>
       <c r="T261" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldensunjewelry.com/contacts/</t>
+          <t>https://www.hermanscreations.com/</t>
         </is>
       </c>
       <c r="U261" t="inlineStr"/>
       <c r="V261" t="inlineStr">
         <is>
-          <t>2026-10-14T01:41:10+05:30</t>
+          <t>2026-10-14T01:41:15+05:30</t>
         </is>
       </c>
       <c r="W261" t="inlineStr">
         <is>
-          <t>Golden Sun Jewlery</t>
+          <t>Herman's Creations Ltd, Herman's Creations Jewelers, Steve's Creations</t>
         </is>
       </c>
       <c r="X261" t="inlineStr"/>
       <c r="Y261" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z261" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA261" t="inlineStr">
         <is>
-          <t>(248) 559-5142</t>
+          <t>(248) 968-0519, (586) 776-3201</t>
         </is>
       </c>
       <c r="AB261" t="inlineStr">
         <is>
-          <t>https://facebook.com/GoldenSunJewelry, https://instagram.com/goldensunjewelry, https://twitter.com/GSJ_Southfield</t>
+          <t>https://instagram.com/hermans_creations, https://facebook.com/Hermans-Creations-Jewelers-East-122894551100621</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Herman's Creations Jewelers Inc.</t>
+          <t>King Jewelers</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Repairing, Diamond Setters</t>
+          <t>Jeweler</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>(586) 776-3200</t>
+          <t>(248) 569-0793</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>roseville@hermanscreations.com</t>
+          <t>u003einfo@kingjewelers.com</t>
         </is>
       </c>
       <c r="F262" t="inlineStr"/>
@@ -29566,24 +29614,16 @@
       <c r="H262" t="inlineStr"/>
       <c r="I262" s="2" t="inlineStr">
         <is>
-          <t>https://www.hermanscreations.com</t>
+          <t>https://www.kingjewelers.com</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>28885 Gratiot Ave, Roseville, MI 48066</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t>Roseville</t>
-        </is>
-      </c>
-      <c r="L262" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
+          <t>23077 Greenfield Rd #300, Southfield, MI 48075, United States</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr"/>
       <c r="M262" t="inlineStr">
         <is>
           <t>Detroit, MI</t>
@@ -29591,23 +29631,23 @@
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O262" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P262" t="n">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="Q262" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/roseville-mi/mip/hermans-creations-jewelers-inc-6517282</t>
+          <t>https://www.google.com/maps/place/King+Jewelers/data=!4m7!3m6!1s0x8824c904292cee05:0xc371fcb68753dfa!8m2!3d42.460125!4d-83.2020227!16s%2Fg%2F1thfg1m3!19sChIJBe4sKQTJJIgR-j11aMsfNww</t>
         </is>
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, since-1974</t>
+          <t>2 of 3, direct-line, gia, custom-design</t>
         </is>
       </c>
       <c r="S262" t="inlineStr">
@@ -29617,64 +29657,56 @@
       </c>
       <c r="T262" s="2" t="inlineStr">
         <is>
-          <t>https://www.hermanscreations.com/</t>
+          <t>https://kingjewelers.com/pages/contact-us</t>
         </is>
       </c>
       <c r="U262" t="inlineStr"/>
       <c r="V262" t="inlineStr">
         <is>
-          <t>2026-10-14T01:41:15+05:30</t>
-        </is>
-      </c>
-      <c r="W262" t="inlineStr">
-        <is>
-          <t>Herman's Creations Ltd, Herman's Creations Jewelers, Steve's Creations</t>
-        </is>
-      </c>
+          <t>2026-10-14T00:36:20+05:30</t>
+        </is>
+      </c>
+      <c r="W262" t="inlineStr"/>
       <c r="X262" t="inlineStr"/>
       <c r="Y262" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z262" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z262" t="inlineStr"/>
       <c r="AA262" t="inlineStr">
         <is>
-          <t>(248) 968-0519, (586) 776-3201</t>
+          <t>(615) 224-2902</t>
         </is>
       </c>
       <c r="AB262" t="inlineStr">
         <is>
-          <t>https://instagram.com/hermans_creations, https://facebook.com/Hermans-Creations-Jewelers-East-122894551100621</t>
+          <t>https://facebook.com/kingjewelersnashville, https://instagram.com/kingjewelers, https://instagram.com/kingjewelers/</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>King Jewelers</t>
+          <t>M J Diamonds</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Jeweler</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>(248) 569-0793</t>
+          <t>(248) 577-0077</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>u003einfo@kingjewelers.com</t>
+          <t>contactus@mjdiamonds.com</t>
         </is>
       </c>
       <c r="F263" t="inlineStr"/>
@@ -29682,16 +29714,24 @@
       <c r="H263" t="inlineStr"/>
       <c r="I263" s="2" t="inlineStr">
         <is>
-          <t>https://www.kingjewelers.com</t>
+          <t>https://mjdiamonds456072858.localsearch.com</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>23077 Greenfield Rd #300, Southfield, MI 48075, United States</t>
-        </is>
-      </c>
-      <c r="K263" t="inlineStr"/>
-      <c r="L263" t="inlineStr"/>
+          <t>320 W 14 Mile Rd, Troy, MI 48083</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Troy</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
       <c r="M263" t="inlineStr">
         <is>
           <t>Detroit, MI</t>
@@ -29699,23 +29739,23 @@
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O263" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="P263" t="n">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="Q263" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/King+Jewelers/data=!4m7!3m6!1s0x8824c904292cee05:0xc371fcb68753dfa!8m2!3d42.460125!4d-83.2020227!16s%2Fg%2F1thfg1m3!19sChIJBe4sKQTJJIgR-j11aMsfNww</t>
+          <t>https://www.yellowpages.com/troy-mi/mip/m-j-diamonds-456072858</t>
         </is>
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design</t>
+          <t>2 of 3, direct-line, bench, custom-design, since-1976</t>
         </is>
       </c>
       <c r="S263" t="inlineStr">
@@ -29725,36 +29765,36 @@
       </c>
       <c r="T263" s="2" t="inlineStr">
         <is>
-          <t>https://kingjewelers.com/pages/contact-us</t>
+          <t>https://mjdiamonds.com/</t>
         </is>
       </c>
       <c r="U263" t="inlineStr"/>
       <c r="V263" t="inlineStr">
         <is>
-          <t>2026-10-14T00:36:20+05:30</t>
+          <t>2026-10-14T01:41:26+05:30</t>
         </is>
       </c>
       <c r="W263" t="inlineStr"/>
       <c r="X263" t="inlineStr"/>
       <c r="Y263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z263" t="inlineStr"/>
       <c r="AA263" t="inlineStr">
         <is>
-          <t>(615) 224-2902</t>
+          <t>(248) 956-1832, (248) 975-7894, (734) 462-7777, (734) 834-1155</t>
         </is>
       </c>
       <c r="AB263" t="inlineStr">
         <is>
-          <t>https://facebook.com/kingjewelersnashville, https://instagram.com/kingjewelers, https://instagram.com/kingjewelers/</t>
+          <t>https://facebook.com/mjdiamonds, https://twitter.com/mj_diamonds, https://instagram.com/mjdiamonds</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>M J Diamonds</t>
+          <t>Mac Enterprises</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -29769,12 +29809,12 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>(248) 577-0077</t>
+          <t>(313) 846-4567</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>contactus@mjdiamonds.com</t>
+          <t>brenda@macenterprisesinc.com</t>
         </is>
       </c>
       <c r="F264" t="inlineStr"/>
@@ -29782,17 +29822,17 @@
       <c r="H264" t="inlineStr"/>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>https://mjdiamonds456072858.localsearch.com</t>
+          <t>https://www.macenterprisesinc.com</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>320 W 14 Mile Rd, Troy, MI 48083</t>
+          <t>5141 Schaefer Rd, Dearborn, MI 48126</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>Troy</t>
+          <t>Dearborn</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -29810,20 +29850,16 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O264" t="n">
-        <v>5</v>
-      </c>
-      <c r="P264" t="n">
-        <v>1</v>
-      </c>
+      <c r="O264" t="inlineStr"/>
+      <c r="P264" t="inlineStr"/>
       <c r="Q264" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/troy-mi/mip/m-j-diamonds-456072858</t>
+          <t>https://www.yellowpages.com/dearborn-mi/mip/mac-enterprises-461011700</t>
         </is>
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, bench, custom-design, since-1976</t>
+          <t>2 of 3, direct-line, since-1982</t>
         </is>
       </c>
       <c r="S264" t="inlineStr">
@@ -29833,74 +29869,82 @@
       </c>
       <c r="T264" s="2" t="inlineStr">
         <is>
-          <t>https://mjdiamonds.com/</t>
+          <t>https://www.macenterprisesinc.com/contact</t>
         </is>
       </c>
       <c r="U264" t="inlineStr"/>
       <c r="V264" t="inlineStr">
         <is>
-          <t>2026-10-14T01:41:26+05:30</t>
+          <t>2026-10-14T01:40:32+05:30</t>
         </is>
       </c>
       <c r="W264" t="inlineStr"/>
       <c r="X264" t="inlineStr"/>
       <c r="Y264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z264" t="inlineStr"/>
       <c r="AA264" t="inlineStr">
         <is>
-          <t>(248) 956-1832, (248) 975-7894, (734) 462-7777, (734) 834-1155</t>
+          <t>(907) 359-4090</t>
         </is>
       </c>
       <c r="AB264" t="inlineStr">
         <is>
-          <t>https://facebook.com/mjdiamonds, https://twitter.com/mj_diamonds, https://instagram.com/mjdiamonds</t>
+          <t>https://facebook.com/wix, https://twitter.com/wix</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Mac Enterprises</t>
+          <t>Metals In Time</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Jewelry repair / goldsmith</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Watch Repair, Watches</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>(313) 846-4567</t>
+          <t>(248) 582-9344</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>brenda@macenterprisesinc.com</t>
+          <t>jalexis@metalsintime.com</t>
         </is>
       </c>
       <c r="F265" t="inlineStr"/>
-      <c r="G265" t="inlineStr"/>
-      <c r="H265" t="inlineStr"/>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Sergio Basmajian</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
       <c r="I265" s="2" t="inlineStr">
         <is>
-          <t>https://www.macenterprisesinc.com</t>
+          <t>https://www.metalsintime.com</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>5141 Schaefer Rd, Dearborn, MI 48126</t>
+          <t>400 S Main St, Royal Oak, MI 48067</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>Dearborn</t>
+          <t>Royal Oak</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -29918,16 +29962,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O265" t="inlineStr"/>
-      <c r="P265" t="inlineStr"/>
+      <c r="O265" t="n">
+        <v>4</v>
+      </c>
+      <c r="P265" t="n">
+        <v>3</v>
+      </c>
       <c r="Q265" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/dearborn-mi/mip/mac-enterprises-461011700</t>
+          <t>https://www.yellowpages.com/royal-oak-mi/mip/metals-in-time-473187148</t>
         </is>
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, since-1982</t>
+          <t>2 of 3, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S265" t="inlineStr">
@@ -29937,82 +29985,82 @@
       </c>
       <c r="T265" s="2" t="inlineStr">
         <is>
-          <t>https://www.macenterprisesinc.com/contact</t>
+          <t>https://www.metalsintime.com/meet-the-team/</t>
         </is>
       </c>
       <c r="U265" t="inlineStr"/>
       <c r="V265" t="inlineStr">
         <is>
-          <t>2026-10-14T01:40:32+05:30</t>
-        </is>
-      </c>
-      <c r="W265" t="inlineStr"/>
+          <t>2026-10-14T01:40:59+05:30</t>
+        </is>
+      </c>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>Metal In Time</t>
+        </is>
+      </c>
       <c r="X265" t="inlineStr"/>
       <c r="Y265" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z265" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA265" t="inlineStr">
         <is>
-          <t>(907) 359-4090</t>
+          <t>(248) 282-3733</t>
         </is>
       </c>
       <c r="AB265" t="inlineStr">
         <is>
-          <t>https://facebook.com/wix, https://twitter.com/wix</t>
+          <t>https://facebook.com/Metalsintime, https://instagram.com/Metalsintimejewelers</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Metals In Time</t>
+          <t>Motif Jewelers</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Jewelry repair / goldsmith</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Jewelers, Watch Repair, Watches</t>
+          <t>Jewelers, Jewelry Designers, Jewelry Engravers</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>(248) 582-9344</t>
+          <t>(734) 287-8300</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>jalexis@metalsintime.com</t>
+          <t>sales@motifjewelry.com</t>
         </is>
       </c>
       <c r="F266" t="inlineStr"/>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>Sergio Basmajian</t>
-        </is>
-      </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
+      <c r="G266" t="inlineStr"/>
+      <c r="H266" t="inlineStr"/>
       <c r="I266" s="2" t="inlineStr">
         <is>
-          <t>https://www.metalsintime.com</t>
+          <t>https://motifjewelersmi.localsearch.com</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>400 S Main St, Royal Oak, MI 48067</t>
+          <t>23000 Eureka Rd, Taylor, MI 48180</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>Royal Oak</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -30031,19 +30079,19 @@
         </is>
       </c>
       <c r="O266" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P266" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q266" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/royal-oak-mi/mip/metals-in-time-473187148</t>
+          <t>https://www.yellowpages.com/taylor-mi/mip/motif-jewelers-461726546</t>
         </is>
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design</t>
+          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1983</t>
         </is>
       </c>
       <c r="S266" t="inlineStr">
@@ -30053,44 +30101,40 @@
       </c>
       <c r="T266" s="2" t="inlineStr">
         <is>
-          <t>https://www.metalsintime.com/meet-the-team/</t>
+          <t>https://motifjewelersmi.localsearch.com/</t>
         </is>
       </c>
       <c r="U266" t="inlineStr"/>
       <c r="V266" t="inlineStr">
         <is>
-          <t>2026-10-14T01:40:59+05:30</t>
+          <t>2026-10-14T01:41:15+05:30</t>
         </is>
       </c>
       <c r="W266" t="inlineStr">
         <is>
-          <t>Metal In Time</t>
+          <t>Motif Diamond Designs Inc</t>
         </is>
       </c>
       <c r="X266" t="inlineStr"/>
       <c r="Y266" t="n">
         <v>2</v>
       </c>
-      <c r="Z266" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+      <c r="Z266" t="inlineStr"/>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>(248) 282-3733</t>
+          <t>(248) 676-0721</t>
         </is>
       </c>
       <c r="AB266" t="inlineStr">
         <is>
-          <t>https://facebook.com/Metalsintime, https://instagram.com/Metalsintimejewelers</t>
+          <t>https://facebook.com/MotifJewelry, https://instagram.com/motifjewelers, https://twitter.com/motifjewelers</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Motif Jewelers</t>
+          <t>Radiant Made For Us</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -30100,17 +30144,17 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Designers, Jewelry Engravers</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>(734) 287-8300</t>
+          <t>(313) 789-7480</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>sales@motifjewelry.com</t>
+          <t>allenpark@radiantmadeforus.com</t>
         </is>
       </c>
       <c r="F267" t="inlineStr"/>
@@ -30118,24 +30162,16 @@
       <c r="H267" t="inlineStr"/>
       <c r="I267" s="2" t="inlineStr">
         <is>
-          <t>https://motifjewelersmi.localsearch.com</t>
+          <t>https://radiantmadeforus.com</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>23000 Eureka Rd, Taylor, MI 48180</t>
-        </is>
-      </c>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="L267" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
+          <t>6634 Allen Rd, Allen Park, MI 48101, United States</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr"/>
       <c r="M267" t="inlineStr">
         <is>
           <t>Detroit, MI</t>
@@ -30143,23 +30179,23 @@
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O267" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P267" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="Q267" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/taylor-mi/mip/motif-jewelers-461726546</t>
+          <t>https://www.google.com/maps/place/Radiant+Made+For+Us/data=!4m7!3m6!1s0x883b374334f03ef5:0xea62d7eb1e5918df!8m2!3d42.2582463!4d-83.2094467!16s%2Fg%2F11y5nttj61!19sChIJ9T7wNEM3O4gR3xhZHuvXYuo</t>
         </is>
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1983</t>
+          <t>2 of 3, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S267" t="inlineStr">
@@ -30169,40 +30205,36 @@
       </c>
       <c r="T267" s="2" t="inlineStr">
         <is>
-          <t>https://motifjewelersmi.localsearch.com/</t>
+          <t>https://radiantmadeforus.com/</t>
         </is>
       </c>
       <c r="U267" t="inlineStr"/>
       <c r="V267" t="inlineStr">
         <is>
-          <t>2026-10-14T01:41:15+05:30</t>
-        </is>
-      </c>
-      <c r="W267" t="inlineStr">
-        <is>
-          <t>Motif Diamond Designs Inc</t>
-        </is>
-      </c>
+          <t>2026-10-14T00:40:08+05:30</t>
+        </is>
+      </c>
+      <c r="W267" t="inlineStr"/>
       <c r="X267" t="inlineStr"/>
       <c r="Y267" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z267" t="inlineStr"/>
       <c r="AA267" t="inlineStr">
         <is>
-          <t>(248) 676-0721</t>
+          <t>(646) 649-4493</t>
         </is>
       </c>
       <c r="AB267" t="inlineStr">
         <is>
-          <t>https://facebook.com/MotifJewelry, https://instagram.com/motifjewelers, https://twitter.com/motifjewelers</t>
+          <t>https://facebook.com/radiantmadeforus, https://instagram.com/radiantmadeforus, https://facebook.com/madeforusdiamonds, https://instagram.com/madeforusdiamonds</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Radiant Made For Us</t>
+          <t>Rare Diamonds Inc</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -30212,17 +30244,17 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>(313) 789-7480</t>
+          <t>(313) 826-7042</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>allenpark@radiantmadeforus.com</t>
+          <t>tony@rarediamond.com</t>
         </is>
       </c>
       <c r="F268" t="inlineStr"/>
@@ -30230,16 +30262,24 @@
       <c r="H268" t="inlineStr"/>
       <c r="I268" s="2" t="inlineStr">
         <is>
-          <t>https://radiantmadeforus.com</t>
+          <t>https://rarediamond.com</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>6634 Allen Rd, Allen Park, MI 48101, United States</t>
-        </is>
-      </c>
-      <c r="K268" t="inlineStr"/>
-      <c r="L268" t="inlineStr"/>
+          <t>2470 Collingwood St, Detroit, MI 48206</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Detroit</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
       <c r="M268" t="inlineStr">
         <is>
           <t>Detroit, MI</t>
@@ -30247,18 +30287,14 @@
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O268" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P268" t="n">
-        <v>21</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr"/>
+      <c r="P268" t="inlineStr"/>
       <c r="Q268" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Radiant+Made+For+Us/data=!4m7!3m6!1s0x883b374334f03ef5:0xea62d7eb1e5918df!8m2!3d42.2582463!4d-83.2094467!16s%2Fg%2F11y5nttj61!19sChIJ9T7wNEM3O4gR3xhZHuvXYuo</t>
+          <t>https://www.yellowpages.com/detroit-mi/mip/rare-diamonds-inc-551567325</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
@@ -30273,13 +30309,13 @@
       </c>
       <c r="T268" s="2" t="inlineStr">
         <is>
-          <t>https://radiantmadeforus.com/</t>
+          <t>https://rarediamond.com/</t>
         </is>
       </c>
       <c r="U268" t="inlineStr"/>
       <c r="V268" t="inlineStr">
         <is>
-          <t>2026-10-14T00:40:08+05:30</t>
+          <t>2026-10-14T01:40:22+05:30</t>
         </is>
       </c>
       <c r="W268" t="inlineStr"/>
@@ -30290,19 +30326,19 @@
       <c r="Z268" t="inlineStr"/>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>(646) 649-4493</t>
+          <t>(310) 880-2982</t>
         </is>
       </c>
       <c r="AB268" t="inlineStr">
         <is>
-          <t>https://facebook.com/radiantmadeforus, https://instagram.com/radiantmadeforus, https://facebook.com/madeforusdiamonds, https://instagram.com/madeforusdiamonds</t>
+          <t>https://instagram.com/rarediamond_official, https://facebook.com/profile.php?id=61568585367287, https://twitter.com/rarediamondusa</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Rare Diamonds Inc</t>
+          <t>Tapper's Jewelry</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -30312,35 +30348,43 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>(313) 826-7042</t>
+          <t>(248) 932-7700</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>tony@rarediamond.com</t>
+          <t>sales@tappers.com</t>
         </is>
       </c>
       <c r="F269" t="inlineStr"/>
-      <c r="G269" t="inlineStr"/>
-      <c r="H269" t="inlineStr"/>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Howard Tapper</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="I269" s="2" t="inlineStr">
         <is>
-          <t>https://rarediamond.com</t>
+          <t>https://tappers.com</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>2470 Collingwood St, Detroit, MI 48206</t>
+          <t>6337 Orchard Lake Rd, West Bloomfield Township, MI 48322, United States</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>West Bloomfield</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -30355,19 +30399,23 @@
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O269" t="inlineStr"/>
-      <c r="P269" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O269" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P269" t="n">
+        <v>1036</v>
+      </c>
       <c r="Q269" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/detroit-mi/mip/rare-diamonds-inc-551567325</t>
+          <t>https://www.google.com/maps/place/Tapper%27s+Jewelry/data=!4m7!3m6!1s0x8824ba48855706cf:0xec468d469a462bbd!8m2!3d42.5457394!4d-83.359087!16s%2Fg%2F1v3_397b!19sChIJzwZXhUi6JIgRvStGmkaNRuw</t>
         </is>
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design</t>
+          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1977</t>
         </is>
       </c>
       <c r="S269" t="inlineStr">
@@ -30377,13 +30425,13 @@
       </c>
       <c r="T269" s="2" t="inlineStr">
         <is>
-          <t>https://rarediamond.com/</t>
+          <t>https://tappers.com/pages/contact</t>
         </is>
       </c>
       <c r="U269" t="inlineStr"/>
       <c r="V269" t="inlineStr">
         <is>
-          <t>2026-10-14T01:40:22+05:30</t>
+          <t>2026-10-14T00:34:13+05:30</t>
         </is>
       </c>
       <c r="W269" t="inlineStr"/>
@@ -30394,75 +30442,59 @@
       <c r="Z269" t="inlineStr"/>
       <c r="AA269" t="inlineStr">
         <is>
-          <t>(310) 880-2982</t>
+          <t>(248) 465-1800, (248) 649-2000, (248) 862-9700</t>
         </is>
       </c>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>https://instagram.com/rarediamond_official, https://facebook.com/profile.php?id=61568585367287, https://twitter.com/rarediamondusa</t>
+          <t>https://instagram.com/TappersJewelry, https://facebook.com/TappersJewelry</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Tapper's Jewelry</t>
+          <t>Fixology Jewelry, Watch, and Smartphone Repair</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry repair / goldsmith</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Electronics repair shop</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>(248) 932-7700</t>
+          <t>(612) 330-9925</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>sales@tappers.com</t>
+          <t>bloomington@fixologyrepair.com</t>
         </is>
       </c>
       <c r="F270" t="inlineStr"/>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>Howard Tapper</t>
-        </is>
-      </c>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
+      <c r="G270" t="inlineStr"/>
+      <c r="H270" t="inlineStr"/>
       <c r="I270" s="2" t="inlineStr">
         <is>
-          <t>https://tappers.com</t>
+          <t>https://fixologyrepair.com</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>6337 Orchard Lake Rd, West Bloomfield Township, MI 48322, United States</t>
-        </is>
-      </c>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t>West Bloomfield</t>
-        </is>
-      </c>
-      <c r="L270" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
+          <t>651 Nicollet Mall #247, Minneapolis, MN 55402, United States</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr"/>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Detroit, MI</t>
+          <t>Minneapolis, MN</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -30471,19 +30503,19 @@
         </is>
       </c>
       <c r="O270" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="P270" t="n">
-        <v>1036</v>
+        <v>113</v>
       </c>
       <c r="Q270" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Tapper%27s+Jewelry/data=!4m7!3m6!1s0x8824ba48855706cf:0xec468d469a462bbd!8m2!3d42.5457394!4d-83.359087!16s%2Fg%2F1v3_397b!19sChIJzwZXhUi6JIgRvStGmkaNRuw</t>
+          <t>https://www.google.com/maps/place/Fixology+Jewelry,+Watch,+and+Smartphone+Repair/data=!4m7!3m6!1s0x52b3329a741033cd:0x422f1e9528fd8f0a!8m2!3d44.9773754!4d-93.2709679!16s%2Fg%2F11bwndn4z4!19sChIJzTMQdJoys1IRCo_9KJUeL0I</t>
         </is>
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1977</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S270" t="inlineStr">
@@ -30493,56 +30525,60 @@
       </c>
       <c r="T270" s="2" t="inlineStr">
         <is>
-          <t>https://tappers.com/pages/contact</t>
+          <t>https://fixologyrepair.com/contact/</t>
         </is>
       </c>
       <c r="U270" t="inlineStr"/>
       <c r="V270" t="inlineStr">
         <is>
-          <t>2026-10-14T00:34:13+05:30</t>
-        </is>
-      </c>
-      <c r="W270" t="inlineStr"/>
+          <t>2026-10-14T00:47:39+05:30</t>
+        </is>
+      </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>Fixology</t>
+        </is>
+      </c>
       <c r="X270" t="inlineStr"/>
       <c r="Y270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z270" t="inlineStr"/>
       <c r="AA270" t="inlineStr">
         <is>
-          <t>(248) 465-1800, (248) 649-2000, (248) 862-9700</t>
+          <t>(772) 692-3774</t>
         </is>
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>https://instagram.com/TappersJewelry, https://facebook.com/TappersJewelry</t>
+          <t>https://facebook.com/fixologytoledo, https://facebook.com/fixologyMallofAmerica</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Fixology Jewelry, Watch, and Smartphone Repair</t>
+          <t>R.F. Moeller Jeweler</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Jewelry repair / goldsmith</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Electronics repair shop</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>(612) 330-9925</t>
+          <t>(651) 698-6321</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>bloomington@fixologyrepair.com</t>
+          <t>alexandra@rfmoeller.com</t>
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
@@ -30550,16 +30586,24 @@
       <c r="H271" t="inlineStr"/>
       <c r="I271" s="2" t="inlineStr">
         <is>
-          <t>https://fixologyrepair.com</t>
+          <t>https://rfmoeller.com</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>651 Nicollet Mall #247, Minneapolis, MN 55402, United States</t>
-        </is>
-      </c>
-      <c r="K271" t="inlineStr"/>
-      <c r="L271" t="inlineStr"/>
+          <t>2065 Ford Pkwy, St Paul, MN 55116, United States</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Minneapolis</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>MN</t>
+        </is>
+      </c>
       <c r="M271" t="inlineStr">
         <is>
           <t>Minneapolis, MN</t>
@@ -30571,19 +30615,19 @@
         </is>
       </c>
       <c r="O271" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="P271" t="n">
-        <v>113</v>
+        <v>2186</v>
       </c>
       <c r="Q271" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Fixology+Jewelry,+Watch,+and+Smartphone+Repair/data=!4m7!3m6!1s0x52b3329a741033cd:0x422f1e9528fd8f0a!8m2!3d44.9773754!4d-93.2709679!16s%2Fg%2F11bwndn4z4!19sChIJzTMQdJoys1IRCo_9KJUeL0I</t>
+          <t>https://www.google.com/maps/place/R.F.+Moeller+Jeweler/data=!4m7!3m6!1s0x87f62978048ef94d:0xea9c4d97c5c2b259!8m2!3d44.9181574!4d-93.1877644!16s%2Fg%2F1v7pz0rd!19sChIJTfmOBHgp9ocRWbLCxZdNnOo</t>
         </is>
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, direct-line, ags, custom-design, since-1951</t>
         </is>
       </c>
       <c r="S271" t="inlineStr">
@@ -30593,45 +30637,41 @@
       </c>
       <c r="T271" s="2" t="inlineStr">
         <is>
-          <t>https://fixologyrepair.com/contact/</t>
+          <t>https://rfmoeller.com/</t>
         </is>
       </c>
       <c r="U271" t="inlineStr"/>
       <c r="V271" t="inlineStr">
         <is>
-          <t>2026-10-14T00:47:39+05:30</t>
-        </is>
-      </c>
-      <c r="W271" t="inlineStr">
-        <is>
-          <t>Fixology</t>
-        </is>
-      </c>
+          <t>2026-10-14T00:46:15+05:30</t>
+        </is>
+      </c>
+      <c r="W271" t="inlineStr"/>
       <c r="X271" t="inlineStr"/>
       <c r="Y271" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z271" t="inlineStr"/>
       <c r="AA271" t="inlineStr">
         <is>
-          <t>(772) 692-3774</t>
+          <t>(651) 698-6322</t>
         </is>
       </c>
       <c r="AB271" t="inlineStr">
         <is>
-          <t>https://facebook.com/fixologytoledo, https://facebook.com/fixologyMallofAmerica</t>
+          <t>https://facebook.com/rfmoellerjeweler, https://instagram.com/rfmoellerjeweler</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>R.F. Moeller Jeweler</t>
+          <t>Bailey's Fine Jewelry</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -30641,12 +30681,12 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>(651) 698-6321</t>
+          <t>(704) 332-1605</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>alexandra@rfmoeller.com</t>
+          <t>carysubs@baileybox.com</t>
         </is>
       </c>
       <c r="F272" t="inlineStr"/>
@@ -30654,27 +30694,27 @@
       <c r="H272" t="inlineStr"/>
       <c r="I272" s="2" t="inlineStr">
         <is>
-          <t>https://rfmoeller.com</t>
+          <t>https://www.baileybox.com</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>2065 Ford Pkwy, St Paul, MN 55116, United States</t>
+          <t>705 Providence Rd, Charlotte, NC 28207, United States</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Minneapolis, MN</t>
+          <t>Charlotte, NC</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -30683,19 +30723,19 @@
         </is>
       </c>
       <c r="O272" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P272" t="n">
-        <v>2186</v>
+        <v>775</v>
       </c>
       <c r="Q272" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/R.F.+Moeller+Jeweler/data=!4m7!3m6!1s0x87f62978048ef94d:0xea9c4d97c5c2b259!8m2!3d44.9181574!4d-93.1877644!16s%2Fg%2F1v7pz0rd!19sChIJTfmOBHgp9ocRWbLCxZdNnOo</t>
+          <t>https://www.google.com/maps/place/Bailey%27s+Fine+Jewelry/data=!4m7!3m6!1s0x88569fe931546195:0x4340ee15ce06892f!8m2!3d35.2006619!4d-80.8249664!16s%2Fg%2F1tlgynm1!19sChIJlWFUMemfVogRL4kGzhXuQEM</t>
         </is>
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, ags, custom-design, since-1951</t>
+          <t>2 of 3, direct-line, gia, ags, bench, custom-design, since-1948</t>
         </is>
       </c>
       <c r="S272" t="inlineStr">
@@ -30705,69 +30745,81 @@
       </c>
       <c r="T272" s="2" t="inlineStr">
         <is>
-          <t>https://rfmoeller.com/</t>
+          <t>https://baileybox.com/</t>
         </is>
       </c>
       <c r="U272" t="inlineStr"/>
       <c r="V272" t="inlineStr">
         <is>
-          <t>2026-10-14T00:46:15+05:30</t>
-        </is>
-      </c>
-      <c r="W272" t="inlineStr"/>
+          <t>2026-10-14T00:51:23+05:30</t>
+        </is>
+      </c>
+      <c r="W272" t="inlineStr">
+        <is>
+          <t>Morrison Smith Jewelers</t>
+        </is>
+      </c>
       <c r="X272" t="inlineStr"/>
       <c r="Y272" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z272" t="inlineStr"/>
       <c r="AA272" t="inlineStr">
         <is>
-          <t>(651) 698-6322</t>
+          <t>(252) 353-3434, (252) 443-7676, (919) 829-7337, (919) 892-3838</t>
         </is>
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>https://facebook.com/rfmoellerjeweler, https://instagram.com/rfmoellerjeweler</t>
+          <t>https://facebook.com/BaileysFineJewelry, https://instagram.com/baileysfinejewelry, https://instagram.com/morrisonsmithjewelers, https://facebook.com/MorrisonSmithJewelers, https://x.com/morrisonsmith, https://twitter.com/morrisonsmith</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Bailey's Fine Jewelry</t>
+          <t>Fink's Jewelers</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers, Fix-It Shops, Watches</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>(704) 332-1605</t>
+          <t>(704) 366-3120</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>carysubs@baileybox.com</t>
+          <t>ecommerce@finks.com</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
-      <c r="G273" t="inlineStr"/>
-      <c r="H273" t="inlineStr"/>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Nathan Fink</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="I273" s="2" t="inlineStr">
         <is>
-          <t>https://www.baileybox.com</t>
+          <t>https://www.finks.com</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>705 Providence Rd, Charlotte, NC 28207, United States</t>
+          <t>4400 Sharon Rd Ste 199, Charlotte, NC 28211</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
@@ -30787,23 +30839,23 @@
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O273" t="n">
         <v>5</v>
       </c>
       <c r="P273" t="n">
-        <v>775</v>
+        <v>1</v>
       </c>
       <c r="Q273" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Bailey%27s+Fine+Jewelry/data=!4m7!3m6!1s0x88569fe931546195:0x4340ee15ce06892f!8m2!3d35.2006619!4d-80.8249664!16s%2Fg%2F1tlgynm1!19sChIJlWFUMemfVogRL4kGzhXuQEM</t>
+          <t>https://www.yellowpages.com/charlotte-nc/mip/finks-jewelers-464773701</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, ags, bench, custom-design, since-1948</t>
+          <t>2 of 3, direct-line, custom-design, since-1930</t>
         </is>
       </c>
       <c r="S273" t="inlineStr">
@@ -30813,40 +30865,44 @@
       </c>
       <c r="T273" s="2" t="inlineStr">
         <is>
-          <t>https://baileybox.com/</t>
+          <t>https://www.finks.com/</t>
         </is>
       </c>
       <c r="U273" t="inlineStr"/>
       <c r="V273" t="inlineStr">
         <is>
-          <t>2026-10-14T00:51:23+05:30</t>
+          <t>2026-10-14T01:43:57+05:30</t>
         </is>
       </c>
       <c r="W273" t="inlineStr">
         <is>
-          <t>Morrison Smith Jewelers</t>
+          <t>John Paul Fine Jewelry</t>
         </is>
       </c>
       <c r="X273" t="inlineStr"/>
       <c r="Y273" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z273" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA273" t="inlineStr">
         <is>
-          <t>(252) 353-3434, (252) 443-7676, (919) 829-7337, (919) 892-3838</t>
+          <t>(423) 894-1188, (540) 342-2991, (540) 344-8697, (615) 236-8176, (704) 927-4888, (757) 640-1132, (804) 377-8589, (919) 881-8247</t>
         </is>
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>https://facebook.com/BaileysFineJewelry, https://instagram.com/baileysfinejewelry, https://instagram.com/morrisonsmithjewelers, https://facebook.com/MorrisonSmithJewelers, https://x.com/morrisonsmith, https://twitter.com/morrisonsmith</t>
+          <t>https://facebook.com/FinksJewelers, https://instagram.com/finksjewelers</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Fink's Jewelers</t>
+          <t>Windsor Jewelers</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -30856,48 +30912,48 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Jewelers, Fix-It Shops, Watches</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>(704) 366-3120</t>
+          <t>(704) 556-7747</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>ecommerce@finks.com</t>
+          <t>nfo@windsor-jewelers.com</t>
         </is>
       </c>
       <c r="F274" t="inlineStr"/>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Nathan Fink</t>
+          <t>Kevin Slusher</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>https://www.finks.com</t>
+          <t>https://www.windsor-jewelers.com</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>4400 Sharon Rd Ste 199, Charlotte, NC 28211</t>
+          <t>6809-D Phillips Pl Ct, Charlotte, NC 28210, United States</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Winston-Salem</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -30907,23 +30963,23 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O274" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P274" t="n">
-        <v>1</v>
+        <v>1846</v>
       </c>
       <c r="Q274" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/charlotte-nc/mip/finks-jewelers-464773701</t>
+          <t>https://www.google.com/maps/place/Windsor+Jewelers/data=!4m7!3m6!1s0x88569e13f91d1bb1:0x4b6448ed40c4d63c!8m2!3d35.1465046!4d-80.8269547!16s%2Fg%2F1tq8k7xj!19sChIJsRsd-ROeVogRPNbEQO1IZEs</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design, since-1930</t>
+          <t>2 of 3, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S274" t="inlineStr">
@@ -30933,44 +30989,36 @@
       </c>
       <c r="T274" s="2" t="inlineStr">
         <is>
-          <t>https://www.finks.com/</t>
+          <t>https://www.windsor-jewelers.com/</t>
         </is>
       </c>
       <c r="U274" t="inlineStr"/>
       <c r="V274" t="inlineStr">
         <is>
-          <t>2026-10-14T01:43:57+05:30</t>
-        </is>
-      </c>
-      <c r="W274" t="inlineStr">
-        <is>
-          <t>John Paul Fine Jewelry</t>
-        </is>
-      </c>
+          <t>2026-10-14T00:51:17+05:30</t>
+        </is>
+      </c>
+      <c r="W274" t="inlineStr"/>
       <c r="X274" t="inlineStr"/>
       <c r="Y274" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z274" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="Z274" t="inlineStr"/>
       <c r="AA274" t="inlineStr">
         <is>
-          <t>(423) 894-1188, (540) 342-2991, (540) 344-8697, (615) 236-8176, (704) 927-4888, (757) 640-1132, (804) 377-8589, (919) 881-8247</t>
+          <t>(336) 721-1768</t>
         </is>
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>https://facebook.com/FinksJewelers, https://instagram.com/finksjewelers</t>
+          <t>https://instagram.com/windsorjewelersnc/, https://facebook.com/OfficialWindsorJewelersNC</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Windsor Jewelers</t>
+          <t>Strings for Hope</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -30985,48 +31033,44 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>(704) 556-7747</t>
+          <t>(615) 891-4323</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>nfo@windsor-jewelers.com</t>
-        </is>
-      </c>
-      <c r="F275" t="inlineStr"/>
+          <t>emily@stringsforhope.com</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/emily-winters-182b7a219</t>
+        </is>
+      </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Kevin Slusher</t>
+          <t>Emily Winters</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>President</t>
         </is>
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>https://www.windsor-jewelers.com</t>
+          <t>https://stringsforhope.com</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>6809-D Phillips Pl Ct, Charlotte, NC 28210, United States</t>
-        </is>
-      </c>
-      <c r="K275" t="inlineStr">
-        <is>
-          <t>Winston-Salem</t>
-        </is>
-      </c>
-      <c r="L275" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>100 Taylor St, Nashville, TN 37208, United States</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Charlotte, NC</t>
+          <t>Nashville, TN</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -31035,58 +31079,58 @@
         </is>
       </c>
       <c r="O275" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P275" t="n">
-        <v>1846</v>
+        <v>23</v>
       </c>
       <c r="Q275" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Windsor+Jewelers/data=!4m7!3m6!1s0x88569e13f91d1bb1:0x4b6448ed40c4d63c!8m2!3d35.1465046!4d-80.8269547!16s%2Fg%2F1tq8k7xj!19sChIJsRsd-ROeVogRPNbEQO1IZEs</t>
+          <t>https://www.google.com/maps/place/Strings+for+Hope/data=!4m7!3m6!1s0x8864673b2485a245:0x7c5f1d365f1de575!8m2!3d36.1810664!4d-86.7859259!16s%2Fg%2F11p5x5j012!19sChIJRaKFJDtnZIgRdeUdXzYdX3w</t>
         </is>
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design</t>
+          <t>2 of 3, custom-design, since-2010</t>
         </is>
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T275" s="2" t="inlineStr">
         <is>
-          <t>https://www.windsor-jewelers.com/</t>
-        </is>
-      </c>
-      <c r="U275" t="inlineStr"/>
+          <t>https://stringsforhope.com/pages/about-us</t>
+        </is>
+      </c>
+      <c r="U275" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Emily+Winters%22+Nashville+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V275" t="inlineStr">
         <is>
-          <t>2026-10-14T00:51:17+05:30</t>
+          <t>2026-10-14T01:01:21+05:30</t>
         </is>
       </c>
       <c r="W275" t="inlineStr"/>
       <c r="X275" t="inlineStr"/>
       <c r="Y275" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z275" t="inlineStr"/>
-      <c r="AA275" t="inlineStr">
-        <is>
-          <t>(336) 721-1768</t>
-        </is>
-      </c>
+      <c r="AA275" t="inlineStr"/>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>https://instagram.com/windsorjewelersnc/, https://facebook.com/OfficialWindsorJewelersNC</t>
+          <t>https://facebook.com/Stringsforhope, https://instagram.com/stringsforhope</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Strings for Hope</t>
+          <t>Alltribes Indian Art</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -31096,90 +31140,86 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers, Native American Goods, Art Goods</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>(615) 891-4323</t>
+          <t>(800) 417-0024</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>emily@stringsforhope.com</t>
-        </is>
-      </c>
-      <c r="F276" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/emily-winters-182b7a219</t>
-        </is>
-      </c>
+          <t>admin@alltribes.com</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr"/>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Emily Winters</t>
+          <t>Richard Candy</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>https://stringsforhope.com</t>
+          <t>https://alltribes.com</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>100 Taylor St, Nashville, TN 37208, United States</t>
-        </is>
-      </c>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
+          <t>75 W Baseline Rd Ste 6, Gilbert, AZ 85233</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Gilbert</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Nashville, TN</t>
+          <t>Scottsdale, AZ</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O276" t="n">
-        <v>5</v>
-      </c>
-      <c r="P276" t="n">
-        <v>23</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr"/>
+      <c r="P276" t="inlineStr"/>
       <c r="Q276" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Strings+for+Hope/data=!4m7!3m6!1s0x8864673b2485a245:0x7c5f1d365f1de575!8m2!3d36.1810664!4d-86.7859259!16s%2Fg%2F11p5x5j012!19sChIJRaKFJDtnZIgRdeUdXzYdX3w</t>
+          <t>https://www.yellowpages.com/gilbert-az/mip/alltribes-indian-art-15755647</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>2 of 3, custom-design, since-2010</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="T276" s="2" t="inlineStr">
         <is>
-          <t>https://stringsforhope.com/pages/about-us</t>
-        </is>
-      </c>
-      <c r="U276" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=%22Emily+Winters%22+Nashville+linkedin&amp;hl=en&amp;num=10</t>
-        </is>
-      </c>
+          <t>https://alltribes.com/</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr"/>
       <c r="V276" t="inlineStr">
         <is>
-          <t>2026-10-14T01:01:21+05:30</t>
+          <t>2026-10-14T01:46:53+05:30</t>
         </is>
       </c>
       <c r="W276" t="inlineStr"/>
@@ -31187,64 +31227,60 @@
       <c r="Y276" t="n">
         <v>0</v>
       </c>
-      <c r="Z276" t="inlineStr"/>
-      <c r="AA276" t="inlineStr"/>
+      <c r="Z276" t="inlineStr">
+        <is>
+          <t>toll-free</t>
+        </is>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>(480) 963-2284</t>
+        </is>
+      </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>https://facebook.com/Stringsforhope, https://instagram.com/stringsforhope</t>
+          <t>https://facebook.com/alltribes, https://instagram.com/alltribes_indian_art, https://facebook.com/pg/alltribes/videos/</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Alltribes Indian Art</t>
+          <t>Diasparx</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Jewelers, Native American Goods, Art Goods</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>(800) 417-0024</t>
-        </is>
-      </c>
+          <t>Wholesale jeweler</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>admin@alltribes.com</t>
+          <t>daniel@diasparx.com</t>
         </is>
       </c>
       <c r="F277" t="inlineStr"/>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>Richard Candy</t>
-        </is>
-      </c>
-      <c r="H277" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
+      <c r="G277" t="inlineStr"/>
+      <c r="H277" t="inlineStr"/>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>https://alltribes.com</t>
+          <t>https://www.diasparx.com</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>75 W Baseline Rd Ste 6, Gilbert, AZ 85233</t>
+          <t>Camelback Tower, 6900 E Camelback Rd Suite 1050, Scottsdale, AZ 85251, United States</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>Gilbert</t>
+          <t>Scottsdale</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -31259,19 +31295,23 @@
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O277" t="inlineStr"/>
-      <c r="P277" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O277" t="n">
+        <v>5</v>
+      </c>
+      <c r="P277" t="n">
+        <v>22</v>
+      </c>
       <c r="Q277" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/gilbert-az/mip/alltribes-indian-art-15755647</t>
+          <t>https://www.google.com/maps/place/Diasparx/data=!4m7!3m6!1s0x872b0b6df95ae9b9:0x57de2ae948b26574!8m2!3d33.5025864!4d-111.9322129!16s%2Fg%2F11x19r328p!19sChIJuela-W0LK4cRdGWySOkq3lc</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, direct-line, gia, custom-design</t>
         </is>
       </c>
       <c r="S277" t="inlineStr">
@@ -31281,13 +31321,13 @@
       </c>
       <c r="T277" s="2" t="inlineStr">
         <is>
-          <t>https://alltribes.com/</t>
+          <t>https://www.diasparx.com/</t>
         </is>
       </c>
       <c r="U277" t="inlineStr"/>
       <c r="V277" t="inlineStr">
         <is>
-          <t>2026-10-14T01:46:53+05:30</t>
+          <t>2026-10-14T01:09:41+05:30</t>
         </is>
       </c>
       <c r="W277" t="inlineStr"/>
@@ -31295,42 +31335,42 @@
       <c r="Y277" t="n">
         <v>0</v>
       </c>
-      <c r="Z277" t="inlineStr">
-        <is>
-          <t>toll-free</t>
-        </is>
-      </c>
+      <c r="Z277" t="inlineStr"/>
       <c r="AA277" t="inlineStr">
         <is>
-          <t>(480) 963-2284</t>
+          <t>(212) 555-0134, (480) 640-0948</t>
         </is>
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>https://facebook.com/alltribes, https://instagram.com/alltribes_indian_art, https://facebook.com/pg/alltribes/videos/</t>
+          <t>https://instagram.com/diasparx, https://facebook.com/profile.php?id=100088561748204</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Diasparx</t>
+          <t>Expert Shoe Luggage Watch &amp; Jewelry Repair</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Jewelry repair / goldsmith</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Wholesale jeweler</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr"/>
+          <t>Shoe repair shop</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>(480) 451-1214</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>daniel@diasparx.com</t>
+          <t>info@expertshoerepair.com</t>
         </is>
       </c>
       <c r="F278" t="inlineStr"/>
@@ -31338,12 +31378,12 @@
       <c r="H278" t="inlineStr"/>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>https://www.diasparx.com</t>
+          <t>https://expertslwjrepair.com</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>Camelback Tower, 6900 E Camelback Rd Suite 1050, Scottsdale, AZ 85251, United States</t>
+          <t>10105 E Vía Linda Ste A- 105, Scottsdale, AZ 85258, United States</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
@@ -31367,19 +31407,19 @@
         </is>
       </c>
       <c r="O278" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P278" t="n">
-        <v>22</v>
+        <v>522</v>
       </c>
       <c r="Q278" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Diasparx/data=!4m7!3m6!1s0x872b0b6df95ae9b9:0x57de2ae948b26574!8m2!3d33.5025864!4d-111.9322129!16s%2Fg%2F11x19r328p!19sChIJuela-W0LK4cRdGWySOkq3lc</t>
+          <t>https://www.google.com/maps/place/Expert+Shoe+Luggage+Watch+%26+Jewelry+Repair/data=!4m7!3m6!1s0x872b6d13c4a490a7:0x78beb810dbe170f!8m2!3d33.573104!4d-111.8634771!16s%2Fg%2F11hzvcxvl9!19sChIJp5CkxBNtK4cRDxe-DYHriwc</t>
         </is>
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design</t>
+          <t>2 of 3, role-email, direct-line, since-1960</t>
         </is>
       </c>
       <c r="S278" t="inlineStr">
@@ -31389,56 +31429,56 @@
       </c>
       <c r="T278" s="2" t="inlineStr">
         <is>
-          <t>https://www.diasparx.com/</t>
+          <t>https://www.expertshoerepair.com/</t>
         </is>
       </c>
       <c r="U278" t="inlineStr"/>
       <c r="V278" t="inlineStr">
         <is>
-          <t>2026-10-14T01:09:41+05:30</t>
+          <t>2026-10-14T01:10:03+05:30</t>
         </is>
       </c>
       <c r="W278" t="inlineStr"/>
       <c r="X278" t="inlineStr"/>
       <c r="Y278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z278" t="inlineStr"/>
       <c r="AA278" t="inlineStr">
         <is>
-          <t>(212) 555-0134, (480) 640-0948</t>
+          <t>(480) 269-7591</t>
         </is>
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>https://instagram.com/diasparx, https://facebook.com/profile.php?id=100088561748204</t>
+          <t>https://facebook.com/expertshoerepair, https://instagram.com/expert_shoe_repair</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Expert Shoe Luggage Watch &amp; Jewelry Repair</t>
+          <t>Sunrise Jewelry &amp; Gallery</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Jewelry repair / goldsmith</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Shoe repair shop</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>(480) 451-1214</t>
+          <t>(480) 425-9944</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>info@expertshoerepair.com</t>
+          <t>info@sunrisejewelryusa.com</t>
         </is>
       </c>
       <c r="F279" t="inlineStr"/>
@@ -31446,12 +31486,12 @@
       <c r="H279" t="inlineStr"/>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>https://expertslwjrepair.com</t>
+          <t>https://www.sunrisejewelryusa.com</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>10105 E Vía Linda Ste A- 105, Scottsdale, AZ 85258, United States</t>
+          <t>7254 E Main St Suite 101, Scottsdale, AZ 85251, United States</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
@@ -31475,19 +31515,19 @@
         </is>
       </c>
       <c r="O279" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P279" t="n">
-        <v>522</v>
+        <v>98</v>
       </c>
       <c r="Q279" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Expert+Shoe+Luggage+Watch+%26+Jewelry+Repair/data=!4m7!3m6!1s0x872b6d13c4a490a7:0x78beb810dbe170f!8m2!3d33.573104!4d-111.8634771!16s%2Fg%2F11hzvcxvl9!19sChIJp5CkxBNtK4cRDxe-DYHriwc</t>
+          <t>https://www.google.com/maps/place/Sunrise+Jewelry+%26+Gallery/data=!4m7!3m6!1s0x872b0bd689ab1b37:0xfa243a0d0a63c6b6!8m2!3d33.4932392!4d-111.9247178!16s%2Fg%2F11q1rmxn64!19sChIJNxuridYLK4cRtsZjCg06JPo</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, since-1960</t>
+          <t>2 of 3, role-email, direct-line, since-2006</t>
         </is>
       </c>
       <c r="S279" t="inlineStr">
@@ -31497,16 +31537,20 @@
       </c>
       <c r="T279" s="2" t="inlineStr">
         <is>
-          <t>https://www.expertshoerepair.com/</t>
+          <t>https://sunrisejewelryusa.com/</t>
         </is>
       </c>
       <c r="U279" t="inlineStr"/>
       <c r="V279" t="inlineStr">
         <is>
-          <t>2026-10-14T01:10:03+05:30</t>
-        </is>
-      </c>
-      <c r="W279" t="inlineStr"/>
+          <t>2026-10-14T01:05:57+05:30</t>
+        </is>
+      </c>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>Sunrise Trading Post</t>
+        </is>
+      </c>
       <c r="X279" t="inlineStr"/>
       <c r="Y279" t="n">
         <v>1</v>
@@ -31514,19 +31558,19 @@
       <c r="Z279" t="inlineStr"/>
       <c r="AA279" t="inlineStr">
         <is>
-          <t>(480) 269-7591</t>
+          <t>(480) 994-0170</t>
         </is>
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>https://facebook.com/expertshoerepair, https://instagram.com/expert_shoe_repair</t>
+          <t>https://instagram.com/sunrisejewelryandgallery, https://facebook.com/sunrisejewelryusa</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Sunrise Jewelry &amp; Gallery</t>
+          <t>Exquisite Timepieces</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -31536,17 +31580,17 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers, Watches</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>(480) 425-9944</t>
+          <t>(239) 227-2932</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>info@sunrisejewelryusa.com</t>
+          <t>team@exquisitetimepieces.com</t>
         </is>
       </c>
       <c r="F280" t="inlineStr"/>
@@ -31554,48 +31598,48 @@
       <c r="H280" t="inlineStr"/>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>https://www.sunrisejewelryusa.com</t>
+          <t>https://www.exquisitetimepieces.com</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>7254 E Main St Suite 101, Scottsdale, AZ 85251, United States</t>
+          <t>4380 Gulf Shore Blvd N, Naples, FL 34103</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>Scottsdale</t>
+          <t>Naples</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ</t>
+          <t>Naples, FL</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O280" t="n">
         <v>5</v>
       </c>
       <c r="P280" t="n">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="Q280" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Sunrise+Jewelry+%26+Gallery/data=!4m7!3m6!1s0x872b0bd689ab1b37:0xfa243a0d0a63c6b6!8m2!3d33.4932392!4d-111.9247178!16s%2Fg%2F11q1rmxn64!19sChIJNxuridYLK4cRtsZjCg06JPo</t>
+          <t>https://www.yellowpages.com/naples-fl/mip/exquisite-timepieces-14306847</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, since-2006</t>
+          <t>2 of 3, role-email, direct-line, ja, since-1998</t>
         </is>
       </c>
       <c r="S280" t="inlineStr">
@@ -31605,40 +31649,36 @@
       </c>
       <c r="T280" s="2" t="inlineStr">
         <is>
-          <t>https://sunrisejewelryusa.com/</t>
+          <t>https://www.exquisitetimepieces.com/</t>
         </is>
       </c>
       <c r="U280" t="inlineStr"/>
       <c r="V280" t="inlineStr">
         <is>
-          <t>2026-10-14T01:05:57+05:30</t>
-        </is>
-      </c>
-      <c r="W280" t="inlineStr">
-        <is>
-          <t>Sunrise Trading Post</t>
-        </is>
-      </c>
+          <t>2026-10-14T01:47:28+05:30</t>
+        </is>
+      </c>
+      <c r="W280" t="inlineStr"/>
       <c r="X280" t="inlineStr"/>
       <c r="Y280" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z280" t="inlineStr"/>
       <c r="AA280" t="inlineStr">
         <is>
-          <t>(480) 994-0170</t>
+          <t>(239) 262-4545</t>
         </is>
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>https://instagram.com/sunrisejewelryandgallery, https://facebook.com/sunrisejewelryusa</t>
+          <t>https://facebook.com/pages/Exquisite-Timepieces/138888796144728, https://x.com/TimeExquisite, https://instagram.com/exquisitetimepieces, https://facebook.com/Exquisite-Timepieces-138888796144728, https://twitter.com/TimeExquisite</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Exquisite Timepieces</t>
+          <t>Gold Silver Naples</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -31648,17 +31688,17 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Jewelers, Watches</t>
+          <t>Gold dealer</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>(239) 227-2932</t>
+          <t>(239) 591-5999</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>team@exquisitetimepieces.com</t>
+          <t>goldsilvercoinsofnaples@gmail.com</t>
         </is>
       </c>
       <c r="F281" t="inlineStr"/>
@@ -31666,24 +31706,16 @@
       <c r="H281" t="inlineStr"/>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>https://www.exquisitetimepieces.com</t>
+          <t>https://www.goldsilvernaples.com</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>4380 Gulf Shore Blvd N, Naples, FL 34103</t>
-        </is>
-      </c>
-      <c r="K281" t="inlineStr">
-        <is>
-          <t>Naples</t>
-        </is>
-      </c>
-      <c r="L281" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
+          <t>1575 Pine Ridge Rd Ste 20, Naples, FL 34109, United States</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
       <c r="M281" t="inlineStr">
         <is>
           <t>Naples, FL</t>
@@ -31691,23 +31723,23 @@
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O281" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="P281" t="n">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="Q281" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/naples-fl/mip/exquisite-timepieces-14306847</t>
+          <t>https://www.google.com/maps/place/Gold+Silver+Naples/data=!4m7!3m6!1s0x88db1d7e5a7b7a49:0x324bd0e63a60dfad!8m2!3d26.2126153!4d-81.7867476!16s%2Fg%2F11k9ml4kb0!19sChIJSXp7Wn4d24gRrd9gOubQSzI</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, ja, since-1998</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S281" t="inlineStr">
@@ -31717,13 +31749,13 @@
       </c>
       <c r="T281" s="2" t="inlineStr">
         <is>
-          <t>https://www.exquisitetimepieces.com/</t>
+          <t>https://goldsilvernaples.com/</t>
         </is>
       </c>
       <c r="U281" t="inlineStr"/>
       <c r="V281" t="inlineStr">
         <is>
-          <t>2026-10-14T01:47:28+05:30</t>
+          <t>2026-10-14T01:13:03+05:30</t>
         </is>
       </c>
       <c r="W281" t="inlineStr"/>
@@ -31734,19 +31766,15 @@
       <c r="Z281" t="inlineStr"/>
       <c r="AA281" t="inlineStr">
         <is>
-          <t>(239) 262-4545</t>
-        </is>
-      </c>
-      <c r="AB281" t="inlineStr">
-        <is>
-          <t>https://facebook.com/pages/Exquisite-Timepieces/138888796144728, https://x.com/TimeExquisite, https://instagram.com/exquisitetimepieces, https://facebook.com/Exquisite-Timepieces-138888796144728, https://twitter.com/TimeExquisite</t>
-        </is>
-      </c>
+          <t>(239) 234-9588</t>
+        </is>
+      </c>
+      <c r="AB281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Gold Silver Naples</t>
+          <t>International Diamond Center</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -31756,30 +31784,38 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Gold dealer</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>(239) 591-5999</t>
+          <t>(239) 342-2550</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>goldsilvercoinsofnaples@gmail.com</t>
+          <t>u003emarketing@shopidc.com</t>
         </is>
       </c>
       <c r="F282" t="inlineStr"/>
-      <c r="G282" t="inlineStr"/>
-      <c r="H282" t="inlineStr"/>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Keith Leclerc</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldsilvernaples.com</t>
+          <t>https://shopidc.com</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>1575 Pine Ridge Rd Ste 20, Naples, FL 34109, United States</t>
+          <t>8840 Tamiami Trl N, Naples, FL 34108, United States</t>
         </is>
       </c>
       <c r="K282" t="inlineStr"/>
@@ -31795,19 +31831,19 @@
         </is>
       </c>
       <c r="O282" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="P282" t="n">
-        <v>75</v>
+        <v>278</v>
       </c>
       <c r="Q282" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Gold+Silver+Naples/data=!4m7!3m6!1s0x88db1d7e5a7b7a49:0x324bd0e63a60dfad!8m2!3d26.2126153!4d-81.7867476!16s%2Fg%2F11k9ml4kb0!19sChIJSXp7Wn4d24gRrd9gOubQSzI</t>
+          <t>https://www.google.com/maps/place/International+Diamond+Center/data=!4m7!3m6!1s0x88db1f3b506da15f:0xd38690aae0aec00b!8m2!3d26.2479716!4d-81.800361!16s%2Fg%2F11t8h0cjn9!19sChIJX6FtUDsf24gRC8Cu4KqQhtM</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S282" t="inlineStr">
@@ -31817,77 +31853,81 @@
       </c>
       <c r="T282" s="2" t="inlineStr">
         <is>
-          <t>https://goldsilvernaples.com/</t>
+          <t>https://shopidc.com/</t>
         </is>
       </c>
       <c r="U282" t="inlineStr"/>
       <c r="V282" t="inlineStr">
         <is>
-          <t>2026-10-14T01:13:03+05:30</t>
+          <t>2026-10-14T01:15:46+05:30</t>
         </is>
       </c>
       <c r="W282" t="inlineStr"/>
       <c r="X282" t="inlineStr"/>
       <c r="Y282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z282" t="inlineStr"/>
       <c r="AA282" t="inlineStr">
         <is>
-          <t>(239) 234-9588</t>
-        </is>
-      </c>
-      <c r="AB282" t="inlineStr"/>
+          <t>(239) 364-1799, (352) 681-4550, (407) 770-5991, (407) 862-8990, (407) 903-9494, (727) 572-6323, (772) 408-4640, (813) 961-0097, (863) 226-4400, (912) 354-4344, (941) 278-3900</t>
+        </is>
+      </c>
+      <c r="AB282" t="inlineStr">
+        <is>
+          <t>https://facebook.com/internationaldiamondcenter, https://instagram.com/internationaldiamondcenter_, https://twitter.com/shopidc</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>International Diamond Center</t>
+          <t>Mark Loren Design</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers, Jewelry Designers</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>(239) 342-2550</t>
+          <t>(239) 596-5820</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>u003emarketing@shopidc.com</t>
+          <t>contact@marklorendesigns.com</t>
         </is>
       </c>
       <c r="F283" t="inlineStr"/>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>Keith Leclerc</t>
-        </is>
-      </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
+      <c r="G283" t="inlineStr"/>
+      <c r="H283" t="inlineStr"/>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>https://shopidc.com</t>
+          <t>https://www.marklorendesigns.com</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>8840 Tamiami Trl N, Naples, FL 34108, United States</t>
-        </is>
-      </c>
-      <c r="K283" t="inlineStr"/>
-      <c r="L283" t="inlineStr"/>
+          <t>9118 Strada Pl Ste 8120, Naples, FL 34108</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Naples</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
       <c r="M283" t="inlineStr">
         <is>
           <t>Naples, FL</t>
@@ -31895,23 +31935,19 @@
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O283" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P283" t="n">
-        <v>278</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr"/>
+      <c r="P283" t="inlineStr"/>
       <c r="Q283" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/International+Diamond+Center/data=!4m7!3m6!1s0x88db1f3b506da15f:0xd38690aae0aec00b!8m2!3d26.2479716!4d-81.800361!16s%2Fg%2F11t8h0cjn9!19sChIJX6FtUDsf24gRC8Cu4KqQhtM</t>
+          <t>https://www.yellowpages.com/naples-fl/mip/mark-loren-design-475273503</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design</t>
+          <t>2 of 3, role-email, direct-line, bench, custom-design</t>
         </is>
       </c>
       <c r="S283" t="inlineStr">
@@ -31921,56 +31957,56 @@
       </c>
       <c r="T283" s="2" t="inlineStr">
         <is>
-          <t>https://shopidc.com/</t>
+          <t>https://marklorendesigns.com/</t>
         </is>
       </c>
       <c r="U283" t="inlineStr"/>
       <c r="V283" t="inlineStr">
         <is>
-          <t>2026-10-14T01:15:46+05:30</t>
+          <t>2026-10-14T01:47:36+05:30</t>
         </is>
       </c>
       <c r="W283" t="inlineStr"/>
       <c r="X283" t="inlineStr"/>
       <c r="Y283" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z283" t="inlineStr"/>
       <c r="AA283" t="inlineStr">
         <is>
-          <t>(239) 364-1799, (352) 681-4550, (407) 770-5991, (407) 862-8990, (407) 903-9494, (727) 572-6323, (772) 408-4640, (813) 961-0097, (863) 226-4400, (912) 354-4344, (941) 278-3900</t>
+          <t>(239) 482-4664</t>
         </is>
       </c>
       <c r="AB283" t="inlineStr">
         <is>
-          <t>https://facebook.com/internationaldiamondcenter, https://instagram.com/internationaldiamondcenter_, https://twitter.com/shopidc</t>
+          <t>https://facebook.com/marklorendesigns, https://instagram.com/marklorendesign</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Mark Loren Design</t>
+          <t>Black Rock Galleries</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Designers</t>
+          <t>Estate liquidator</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>(239) 596-5820</t>
+          <t>(203) 900-1110</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>contact@marklorendesigns.com</t>
+          <t>april@blackrockgalleries.com</t>
         </is>
       </c>
       <c r="F284" t="inlineStr"/>
@@ -31978,44 +32014,48 @@
       <c r="H284" t="inlineStr"/>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>https://www.marklorendesigns.com</t>
+          <t>https://www.blackrockgalleries.com</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>9118 Strada Pl Ste 8120, Naples, FL 34108</t>
+          <t>179 Hamilton Ave, Greenwich, CT 06830, United States</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>Naples</t>
+          <t>Cary</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Naples, FL</t>
+          <t>Greenwich, CT</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O284" t="inlineStr"/>
-      <c r="P284" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O284" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P284" t="n">
+        <v>25</v>
+      </c>
       <c r="Q284" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/naples-fl/mip/mark-loren-design-475273503</t>
+          <t>https://www.google.com/maps/place/Black+Rock+Galleries/data=!4m7!3m6!1s0x89c299cdad7d8901:0x806db5b713ec68d7!8m2!3d41.0179193!4d-73.6391571!16s%2Fg%2F11ckvlk1pv!19sChIJAYl9rc2ZwokR12jsE7e1bYA</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, bench, custom-design</t>
+          <t>2 of 3, direct-line, gia</t>
         </is>
       </c>
       <c r="S284" t="inlineStr">
@@ -32025,13 +32065,13 @@
       </c>
       <c r="T284" s="2" t="inlineStr">
         <is>
-          <t>https://marklorendesigns.com/</t>
+          <t>https://www.blackrockgalleries.com/contact</t>
         </is>
       </c>
       <c r="U284" t="inlineStr"/>
       <c r="V284" t="inlineStr">
         <is>
-          <t>2026-10-14T01:47:36+05:30</t>
+          <t>2026-10-14T01:19:56+05:30</t>
         </is>
       </c>
       <c r="W284" t="inlineStr"/>
@@ -32042,39 +32082,39 @@
       <c r="Z284" t="inlineStr"/>
       <c r="AA284" t="inlineStr">
         <is>
-          <t>(239) 482-4664</t>
+          <t>(203) 335-0000, (203) 335-4444, (919) 702-7000</t>
         </is>
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>https://facebook.com/marklorendesigns, https://instagram.com/marklorendesign</t>
+          <t>https://facebook.com/blackrockgalleries, https://twitter.com/BRGalleries, https://instagram.com/blackrockgalleries</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Black Rock Galleries</t>
+          <t>Fine Elegant Jewelry</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Estate liquidator</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>(203) 900-1110</t>
+          <t>(914) 937-2045</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>april@blackrockgalleries.com</t>
+          <t>elegantempirejewelers@gmail.com</t>
         </is>
       </c>
       <c r="F285" t="inlineStr"/>
@@ -32082,22 +32122,22 @@
       <c r="H285" t="inlineStr"/>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>https://www.blackrockgalleries.com</t>
+          <t>https://eejewelers.com</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>179 Hamilton Ave, Greenwich, CT 06830, United States</t>
+          <t>27 N Main St, Port Chester, NY 10573</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>Cary</t>
+          <t>Port Chester</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -32107,23 +32147,23 @@
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O285" t="n">
-        <v>2.7</v>
+        <v>4.9</v>
       </c>
       <c r="P285" t="n">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="Q285" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Black+Rock+Galleries/data=!4m7!3m6!1s0x89c299cdad7d8901:0x806db5b713ec68d7!8m2!3d41.0179193!4d-73.6391571!16s%2Fg%2F11ckvlk1pv!19sChIJAYl9rc2ZwokR12jsE7e1bYA</t>
+          <t>https://www.yellowpages.com/port-chester-ny/mip/fine-elegant-jewelry-482445004</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia</t>
+          <t>2 of 3, direct-line, gia, custom-design</t>
         </is>
       </c>
       <c r="S285" t="inlineStr">
@@ -32133,56 +32173,64 @@
       </c>
       <c r="T285" s="2" t="inlineStr">
         <is>
-          <t>https://www.blackrockgalleries.com/contact</t>
+          <t>https://eejewelers.com/</t>
         </is>
       </c>
       <c r="U285" t="inlineStr"/>
       <c r="V285" t="inlineStr">
         <is>
-          <t>2026-10-14T01:19:56+05:30</t>
-        </is>
-      </c>
-      <c r="W285" t="inlineStr"/>
+          <t>2026-10-14T01:48:10+05:30</t>
+        </is>
+      </c>
+      <c r="W285" t="inlineStr">
+        <is>
+          <t>Elegant Empire Jewelers</t>
+        </is>
+      </c>
       <c r="X285" t="inlineStr"/>
       <c r="Y285" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z285" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Z285" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA285" t="inlineStr">
         <is>
-          <t>(203) 335-0000, (203) 335-4444, (919) 702-7000</t>
+          <t>(914) 305-3385</t>
         </is>
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>https://facebook.com/blackrockgalleries, https://twitter.com/BRGalleries, https://instagram.com/blackrockgalleries</t>
+          <t>https://instagram.com/eejewelers/, https://facebook.com/EEJewelers</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Fine Elegant Jewelry</t>
+          <t>Steven Fox Jewelry</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>(914) 937-2045</t>
+          <t>(203) 344-5409</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>elegantempirejewelers@gmail.com</t>
+          <t>concierge@stevenfoxjewelry.com</t>
         </is>
       </c>
       <c r="F286" t="inlineStr"/>
@@ -32190,22 +32238,22 @@
       <c r="H286" t="inlineStr"/>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>https://eejewelers.com</t>
+          <t>https://www.stevenfoxjewelry.com</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>27 N Main St, Port Chester, NY 10573</t>
+          <t>8 Lewis St, Greenwich, CT 06830, United States</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>Port Chester</t>
+          <t>Greenwich</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -32215,23 +32263,23 @@
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O286" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P286" t="n">
-        <v>115</v>
+        <v>277</v>
       </c>
       <c r="Q286" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/port-chester-ny/mip/fine-elegant-jewelry-482445004</t>
+          <t>https://www.google.com/maps/place/Steven+Fox+Jewelry/data=!4m7!3m6!1s0x89c298489c931a41:0x67f0cb095f8447aa!8m2!3d41.0287029!4d-73.6255657!16s%2Fg%2F1thn6fp7!19sChIJQRqTnEiYwokRqkeEXwnL8Gc</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S286" t="inlineStr">
@@ -32241,64 +32289,56 @@
       </c>
       <c r="T286" s="2" t="inlineStr">
         <is>
-          <t>https://eejewelers.com/</t>
+          <t>https://www.stevenfoxjewelry.com/</t>
         </is>
       </c>
       <c r="U286" t="inlineStr"/>
       <c r="V286" t="inlineStr">
         <is>
-          <t>2026-10-14T01:48:10+05:30</t>
-        </is>
-      </c>
-      <c r="W286" t="inlineStr">
-        <is>
-          <t>Elegant Empire Jewelers</t>
-        </is>
-      </c>
+          <t>2026-10-14T01:17:44+05:30</t>
+        </is>
+      </c>
+      <c r="W286" t="inlineStr"/>
       <c r="X286" t="inlineStr"/>
       <c r="Y286" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z286" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Z286" t="inlineStr"/>
       <c r="AA286" t="inlineStr">
         <is>
-          <t>(914) 305-3385</t>
+          <t>(203) 629-3303</t>
         </is>
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>https://instagram.com/eejewelers/, https://facebook.com/EEJewelers</t>
+          <t>https://instagram.com/stevenfoxjewelry, https://facebook.com/stevenfoxjewelry</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Steven Fox Jewelry</t>
+          <t>Triple G Fine Jewelry Inc</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>shop=jewelry</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>(203) 344-5409</t>
+          <t>(914) 937-2931</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>concierge@stevenfoxjewelry.com</t>
+          <t>rakhmin20@icloud.com</t>
         </is>
       </c>
       <c r="F287" t="inlineStr"/>
@@ -32306,22 +32346,22 @@
       <c r="H287" t="inlineStr"/>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>https://www.stevenfoxjewelry.com</t>
+          <t>https://triplegjewelry.rafaelsjewelrystore.com</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>8 Lewis St, Greenwich, CT 06830, United States</t>
+          <t>38 South Main Street, Port Chester, NY 10573</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>Greenwich</t>
+          <t>Port Chester</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
@@ -32331,23 +32371,23 @@
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>OpenStreetMap</t>
         </is>
       </c>
       <c r="O287" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="P287" t="n">
-        <v>277</v>
+        <v>26</v>
       </c>
       <c r="Q287" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Steven+Fox+Jewelry/data=!4m7!3m6!1s0x89c298489c931a41:0x67f0cb095f8447aa!8m2!3d41.0287029!4d-73.6255657!16s%2Fg%2F1thn6fp7!19sChIJQRqTnEiYwokRqkeEXwnL8Gc</t>
+          <t>https://www.openstreetmap.org/node/10302134827</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S287" t="inlineStr">
@@ -32357,36 +32397,40 @@
       </c>
       <c r="T287" s="2" t="inlineStr">
         <is>
-          <t>https://www.stevenfoxjewelry.com/</t>
+          <t>https://triplegjewelry.rafaelsjewelrystore.com/</t>
         </is>
       </c>
       <c r="U287" t="inlineStr"/>
       <c r="V287" t="inlineStr">
         <is>
-          <t>2026-10-14T01:17:44+05:30</t>
-        </is>
-      </c>
-      <c r="W287" t="inlineStr"/>
+          <t>2026-10-14T01:19:19+05:30</t>
+        </is>
+      </c>
+      <c r="W287" t="inlineStr">
+        <is>
+          <t>Triple J Fine Jewelry Inc, Triple J Jew Jewelry</t>
+        </is>
+      </c>
       <c r="X287" t="inlineStr"/>
       <c r="Y287" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z287" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="Z287" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA287" t="inlineStr">
         <is>
-          <t>(203) 629-3303</t>
-        </is>
-      </c>
-      <c r="AB287" t="inlineStr">
-        <is>
-          <t>https://instagram.com/stevenfoxjewelry, https://facebook.com/stevenfoxjewelry</t>
-        </is>
-      </c>
+          <t>(917) 535-4155</t>
+        </is>
+      </c>
+      <c r="AB287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Triple G Fine Jewelry Inc</t>
+          <t>Arlex Jewelry Watches &amp; Clocks</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -32396,17 +32440,17 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>shop=jewelry</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>(914) 937-2931</t>
+          <t>(561) 641-8162</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>rakhmin20@icloud.com</t>
+          <t>info@arlexjewelry.com</t>
         </is>
       </c>
       <c r="F288" t="inlineStr"/>
@@ -32414,48 +32458,48 @@
       <c r="H288" t="inlineStr"/>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>https://triplegjewelry.rafaelsjewelrystore.com</t>
+          <t>https://arlexjewelry.com</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>38 South Main Street, Port Chester, NY 10573</t>
+          <t>808 Lake Ave, Lake Worth Beach, FL 33460, United States</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>Port Chester</t>
+          <t>Lake Worth Beach</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Greenwich, CT</t>
+          <t>Palm Beach, FL</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t>OpenStreetMap</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O288" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="P288" t="n">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="Q288" s="2" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/10302134827</t>
+          <t>https://www.google.com/maps/place/Arlex+Jewelry+Watches+%26+Clocks/data=!4m7!3m6!1s0x88d8d834517d5a4d:0x1255d4758f02268f!8m2!3d26.6160147!4d-80.0567684!16s%2Fg%2F1tkc2xb0!19sChIJTVp9UTTY2IgRjyYCj3XUVRI</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-1987</t>
         </is>
       </c>
       <c r="S288" t="inlineStr">
@@ -32465,18 +32509,18 @@
       </c>
       <c r="T288" s="2" t="inlineStr">
         <is>
-          <t>https://triplegjewelry.rafaelsjewelrystore.com/</t>
+          <t>https://arlexjewelry.com/contact/</t>
         </is>
       </c>
       <c r="U288" t="inlineStr"/>
       <c r="V288" t="inlineStr">
         <is>
-          <t>2026-10-14T01:19:19+05:30</t>
+          <t>2026-10-14T01:30:48+05:30</t>
         </is>
       </c>
       <c r="W288" t="inlineStr">
         <is>
-          <t>Triple J Fine Jewelry Inc, Triple J Jew Jewelry</t>
+          <t>Arlex Jewelry Watches, Arlex Clocks, Arlex Jewelry &amp; Clocks</t>
         </is>
       </c>
       <c r="X288" t="inlineStr"/>
@@ -32490,35 +32534,39 @@
       </c>
       <c r="AA288" t="inlineStr">
         <is>
-          <t>(917) 535-4155</t>
-        </is>
-      </c>
-      <c r="AB288" t="inlineStr"/>
+          <t>(561) 876-7030</t>
+        </is>
+      </c>
+      <c r="AB288" t="inlineStr">
+        <is>
+          <t>https://facebook.com/Arlex-Jewelry-Watches-Clocks-811607869050062, https://twitter.com/arlexclocks, https://instagram.com/arlexjewelry11, https://facebook.com/ArlexJewelry, https://twitter.com/ArlexClocks</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Arlex Jewelry Watches &amp; Clocks</t>
+          <t>Gemstone Gallery</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers, Jewelry Designers</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>(561) 641-8162</t>
+          <t>(561) 586-8868</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>info@arlexjewelry.com</t>
+          <t>info@mygemstonegallery.com</t>
         </is>
       </c>
       <c r="F289" t="inlineStr"/>
@@ -32526,24 +32574,12 @@
       <c r="H289" t="inlineStr"/>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>https://arlexjewelry.com</t>
-        </is>
-      </c>
-      <c r="J289" t="inlineStr">
-        <is>
-          <t>808 Lake Ave, Lake Worth Beach, FL 33460, United States</t>
-        </is>
-      </c>
-      <c r="K289" t="inlineStr">
-        <is>
-          <t>Lake Worth Beach</t>
-        </is>
-      </c>
-      <c r="L289" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
+          <t>https://www.mygemstonegallery.com</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr"/>
+      <c r="K289" t="inlineStr"/>
+      <c r="L289" t="inlineStr"/>
       <c r="M289" t="inlineStr">
         <is>
           <t>Palm Beach, FL</t>
@@ -32551,23 +32587,19 @@
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O289" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P289" t="n">
-        <v>105</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr"/>
+      <c r="P289" t="inlineStr"/>
       <c r="Q289" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Arlex+Jewelry+Watches+%26+Clocks/data=!4m7!3m6!1s0x88d8d834517d5a4d:0x1255d4758f02268f!8m2!3d26.6160147!4d-80.0567684!16s%2Fg%2F1tkc2xb0!19sChIJTVp9UTTY2IgRjyYCj3XUVRI</t>
+          <t>https://www.yellowpages.com/nationwide/mip/gemstone-gallery-451204537</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-1987</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S289" t="inlineStr">
@@ -32577,64 +32609,60 @@
       </c>
       <c r="T289" s="2" t="inlineStr">
         <is>
-          <t>https://arlexjewelry.com/contact/</t>
+          <t>https://www.mygemstonegallery.com/</t>
         </is>
       </c>
       <c r="U289" t="inlineStr"/>
       <c r="V289" t="inlineStr">
         <is>
-          <t>2026-10-14T01:30:48+05:30</t>
-        </is>
-      </c>
-      <c r="W289" t="inlineStr">
-        <is>
-          <t>Arlex Jewelry Watches, Arlex Clocks, Arlex Jewelry &amp; Clocks</t>
-        </is>
-      </c>
+          <t>2026-10-14T01:50:22+05:30</t>
+        </is>
+      </c>
+      <c r="W289" t="inlineStr"/>
       <c r="X289" t="inlineStr"/>
       <c r="Y289" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z289" t="inlineStr">
         <is>
-          <t>chain</t>
+          <t>no-address</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
         <is>
-          <t>(561) 876-7030</t>
+          <t>(917) 406-0779</t>
         </is>
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>https://facebook.com/Arlex-Jewelry-Watches-Clocks-811607869050062, https://twitter.com/arlexclocks, https://instagram.com/arlexjewelry11, https://facebook.com/ArlexJewelry, https://twitter.com/ArlexClocks</t>
+          <t>https://facebook.com/SuzanneHDeBow, https://twitter.com/GemstoneGallery, https://instagram.com/mygemstone_gallery</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Gemstone Gallery</t>
+          <t>Hamilton Jewelers</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Designers</t>
+          <t>Jeweler</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>(561) 586-8868</t>
+          <t>(561) 659-6788</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>info@mygemstonegallery.com</t>
+          <t>emartano@hamiltonjewelers.com</t>
         </is>
       </c>
       <c r="F290" t="inlineStr"/>
@@ -32642,12 +32670,24 @@
       <c r="H290" t="inlineStr"/>
       <c r="I290" s="2" t="inlineStr">
         <is>
-          <t>https://www.mygemstonegallery.com</t>
-        </is>
-      </c>
-      <c r="J290" t="inlineStr"/>
-      <c r="K290" t="inlineStr"/>
-      <c r="L290" t="inlineStr"/>
+          <t>https://hamiltonjewelers.com</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>215 Worth Ave, Palm Beach, FL 33480, United States</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Palm Beach Gardens</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
       <c r="M290" t="inlineStr">
         <is>
           <t>Palm Beach, FL</t>
@@ -32655,19 +32695,23 @@
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O290" t="inlineStr"/>
-      <c r="P290" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O290" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P290" t="n">
+        <v>77</v>
+      </c>
       <c r="Q290" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/nationwide/mip/gemstone-gallery-451204537</t>
+          <t>https://www.google.com/maps/place/Hamilton+Jewelers/data=!4m7!3m6!1s0x88d8d6ec71416949:0x1f20ced2ff0489d1!8m2!3d26.7009363!4d-80.0371549!16s%2Fg%2F1tfz0xfv!19sChIJSWlBcezW2IgR0YkE_9LOIB8</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, direct-line, gia, custom-design, since-1912</t>
         </is>
       </c>
       <c r="S290" t="inlineStr">
@@ -32677,60 +32721,56 @@
       </c>
       <c r="T290" s="2" t="inlineStr">
         <is>
-          <t>https://www.mygemstonegallery.com/</t>
+          <t>https://hamiltonjewelers.com/</t>
         </is>
       </c>
       <c r="U290" t="inlineStr"/>
       <c r="V290" t="inlineStr">
         <is>
-          <t>2026-10-14T01:50:22+05:30</t>
+          <t>2026-10-14T01:25:01+05:30</t>
         </is>
       </c>
       <c r="W290" t="inlineStr"/>
       <c r="X290" t="inlineStr"/>
       <c r="Y290" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z290" t="inlineStr">
-        <is>
-          <t>no-address</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Z290" t="inlineStr"/>
       <c r="AA290" t="inlineStr">
         <is>
-          <t>(917) 406-0779</t>
+          <t>(609) 375-8003</t>
         </is>
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>https://facebook.com/SuzanneHDeBow, https://twitter.com/GemstoneGallery, https://instagram.com/mygemstone_gallery</t>
+          <t>https://instagram.com/hamiltonjewelers, https://facebook.com/HamiltonJeweler</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Hamilton Jewelers</t>
+          <t>Raymond Lee Jewelers</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Jeweler</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>(561) 659-6788</t>
+          <t>(561) 622-7744</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>emartano@hamiltonjewelers.com</t>
+          <t>info@raymondleejewelers.net</t>
         </is>
       </c>
       <c r="F291" t="inlineStr"/>
@@ -32738,12 +32778,12 @@
       <c r="H291" t="inlineStr"/>
       <c r="I291" s="2" t="inlineStr">
         <is>
-          <t>https://hamiltonjewelers.com</t>
+          <t>https://www.raymondleejewelers.net</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>215 Worth Ave, Palm Beach, FL 33480, United States</t>
+          <t>500 Village Square Xing, Palm Beach Gardens, FL 33410</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
@@ -32763,23 +32803,19 @@
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O291" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P291" t="n">
-        <v>77</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr"/>
+      <c r="P291" t="inlineStr"/>
       <c r="Q291" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Hamilton+Jewelers/data=!4m7!3m6!1s0x88d8d6ec71416949:0x1f20ced2ff0489d1!8m2!3d26.7009363!4d-80.0371549!16s%2Fg%2F1tfz0xfv!19sChIJSWlBcezW2IgR0YkE_9LOIB8</t>
+          <t>https://www.yellowpages.com/palm-beach-gardens-fl/mip/raymond-lee-jewelers-3693798</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design, since-1912</t>
+          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1983</t>
         </is>
       </c>
       <c r="S291" t="inlineStr">
@@ -32789,56 +32825,56 @@
       </c>
       <c r="T291" s="2" t="inlineStr">
         <is>
-          <t>https://hamiltonjewelers.com/</t>
+          <t>https://raymondleejewelers.net/pages/contact</t>
         </is>
       </c>
       <c r="U291" t="inlineStr"/>
       <c r="V291" t="inlineStr">
         <is>
-          <t>2026-10-14T01:25:01+05:30</t>
+          <t>2026-10-14T01:50:37+05:30</t>
         </is>
       </c>
       <c r="W291" t="inlineStr"/>
       <c r="X291" t="inlineStr"/>
       <c r="Y291" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z291" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="Z291" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA291" t="inlineStr">
         <is>
-          <t>(609) 375-8003</t>
-        </is>
-      </c>
-      <c r="AB291" t="inlineStr">
-        <is>
-          <t>https://instagram.com/hamiltonjewelers, https://facebook.com/HamiltonJeweler</t>
-        </is>
-      </c>
+          <t>(561) 750-7808</t>
+        </is>
+      </c>
+      <c r="AB291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Raymond Lee Jewelers</t>
+          <t>Signature Diamonds</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Diamonds</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>(561) 622-7744</t>
+          <t>(561) 686-5730</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>info@raymondleejewelers.net</t>
+          <t>signaturebuyers@yahoo.com</t>
         </is>
       </c>
       <c r="F292" t="inlineStr"/>
@@ -32846,17 +32882,17 @@
       <c r="H292" t="inlineStr"/>
       <c r="I292" s="2" t="inlineStr">
         <is>
-          <t>https://www.raymondleejewelers.net</t>
+          <t>https://sellyourdiamondsflorida.com</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>500 Village Square Xing, Palm Beach Gardens, FL 33410</t>
+          <t>2200 N Florida Mango Rd, West Palm Beach, FL 33409</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>Palm Beach Gardens</t>
+          <t>West Palm Beach</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -32878,12 +32914,12 @@
       <c r="P292" t="inlineStr"/>
       <c r="Q292" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/palm-beach-gardens-fl/mip/raymond-lee-jewelers-3693798</t>
+          <t>https://www.yellowpages.com/west-palm-beach-fl/mip/signature-diamonds-538406637</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1983</t>
+          <t>2 of 3, direct-line, gia, custom-design, since-1945</t>
         </is>
       </c>
       <c r="S292" t="inlineStr">
@@ -32893,36 +32929,36 @@
       </c>
       <c r="T292" s="2" t="inlineStr">
         <is>
-          <t>https://raymondleejewelers.net/pages/contact</t>
+          <t>https://sellyourdiamondsflorida.com/</t>
         </is>
       </c>
       <c r="U292" t="inlineStr"/>
       <c r="V292" t="inlineStr">
         <is>
-          <t>2026-10-14T01:50:37+05:30</t>
+          <t>2026-10-14T01:50:22+05:30</t>
         </is>
       </c>
       <c r="W292" t="inlineStr"/>
       <c r="X292" t="inlineStr"/>
       <c r="Y292" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z292" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z292" t="inlineStr"/>
       <c r="AA292" t="inlineStr">
         <is>
-          <t>(561) 750-7808</t>
-        </is>
-      </c>
-      <c r="AB292" t="inlineStr"/>
+          <t>(772) 562-6893</t>
+        </is>
+      </c>
+      <c r="AB292" t="inlineStr">
+        <is>
+          <t>https://facebook.com/pages/Signature-Estate-Diamond-Buyers/699915383378286, https://twitter.com/signaturebuyer</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Signature Diamonds</t>
+          <t>YAFA Palm Beach</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -32932,17 +32968,17 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Jewelers, Diamonds</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>(561) 686-5730</t>
+          <t>(561) 331-8611</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>signaturebuyers@yahoo.com</t>
+          <t>inquire@yafajewelry.com</t>
         </is>
       </c>
       <c r="F293" t="inlineStr"/>
@@ -32950,17 +32986,17 @@
       <c r="H293" t="inlineStr"/>
       <c r="I293" s="2" t="inlineStr">
         <is>
-          <t>https://sellyourdiamondsflorida.com</t>
+          <t>https://yafasignedjewels.com</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>2200 N Florida Mango Rd, West Palm Beach, FL 33409</t>
+          <t>234 Worth Ave, Palm Beach, FL 33480, United States</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>West Palm Beach</t>
+          <t>Palm Beach</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
@@ -32975,19 +33011,23 @@
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O293" t="inlineStr"/>
-      <c r="P293" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O293" t="n">
+        <v>5</v>
+      </c>
+      <c r="P293" t="n">
+        <v>9</v>
+      </c>
       <c r="Q293" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/west-palm-beach-fl/mip/signature-diamonds-538406637</t>
+          <t>https://www.google.com/maps/place/YAFA+Palm+Beach/data=!4m7!3m6!1s0x89c258fef868bda1:0x84b1b16f5ab524a9!8m2!3d26.7006755!4d-80.0378935!16s%2Fg%2F1td4l0sf!19sChIJob1o-P5YwokRqSS1Wm-xsYQ</t>
         </is>
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design, since-1945</t>
+          <t>2 of 3, direct-line, since-1985</t>
         </is>
       </c>
       <c r="S293" t="inlineStr">
@@ -32997,56 +33037,60 @@
       </c>
       <c r="T293" s="2" t="inlineStr">
         <is>
-          <t>https://sellyourdiamondsflorida.com/</t>
+          <t>https://yafasignedjewels.com/pages/contact</t>
         </is>
       </c>
       <c r="U293" t="inlineStr"/>
       <c r="V293" t="inlineStr">
         <is>
-          <t>2026-10-14T01:50:22+05:30</t>
-        </is>
-      </c>
-      <c r="W293" t="inlineStr"/>
+          <t>2026-10-14T01:26:21+05:30</t>
+        </is>
+      </c>
+      <c r="W293" t="inlineStr">
+        <is>
+          <t>Yafa Signed Jewels</t>
+        </is>
+      </c>
       <c r="X293" t="inlineStr"/>
       <c r="Y293" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z293" t="inlineStr"/>
       <c r="AA293" t="inlineStr">
         <is>
-          <t>(772) 562-6893</t>
+          <t>(212) 719-9828, (516) 331-8611</t>
         </is>
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>https://facebook.com/pages/Signature-Estate-Diamond-Buyers/699915383378286, https://twitter.com/signaturebuyer</t>
+          <t>https://facebook.com/YafaSignedJewels, https://instagram.com/yafasignedjewels</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>YAFA Palm Beach</t>
+          <t>Gold Gods</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>(561) 331-8611</t>
+          <t>(816) 721-9850</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>inquire@yafajewelry.com</t>
+          <t>support@thegoldgods.com</t>
         </is>
       </c>
       <c r="F294" t="inlineStr"/>
@@ -33054,48 +33098,44 @@
       <c r="H294" t="inlineStr"/>
       <c r="I294" s="2" t="inlineStr">
         <is>
-          <t>https://yafasignedjewels.com</t>
+          <t>https://thegoldgods.com</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>234 Worth Ave, Palm Beach, FL 33480, United States</t>
+          <t>450 N Fairfax Ave, Los Angeles, CA 90036</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>Palm Beach</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Palm Beach, FL</t>
+          <t>Beverly Hills, CA</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O294" t="n">
-        <v>5</v>
-      </c>
-      <c r="P294" t="n">
-        <v>9</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr"/>
+      <c r="P294" t="inlineStr"/>
       <c r="Q294" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/YAFA+Palm+Beach/data=!4m7!3m6!1s0x89c258fef868bda1:0x84b1b16f5ab524a9!8m2!3d26.7006755!4d-80.0378935!16s%2Fg%2F1td4l0sf!19sChIJob1o-P5YwokRqSS1Wm-xsYQ</t>
+          <t>https://www.yellowpages.com/los-angeles-ca/mip/gold-gods-548160699</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, since-1985</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S294" t="inlineStr">
@@ -33105,60 +33145,52 @@
       </c>
       <c r="T294" s="2" t="inlineStr">
         <is>
-          <t>https://yafasignedjewels.com/pages/contact</t>
+          <t>https://thegoldgods.com/pages/contact</t>
         </is>
       </c>
       <c r="U294" t="inlineStr"/>
       <c r="V294" t="inlineStr">
         <is>
-          <t>2026-10-14T01:26:21+05:30</t>
-        </is>
-      </c>
-      <c r="W294" t="inlineStr">
-        <is>
-          <t>Yafa Signed Jewels</t>
-        </is>
-      </c>
+          <t>2026-10-14T01:52:07+05:30</t>
+        </is>
+      </c>
+      <c r="W294" t="inlineStr"/>
       <c r="X294" t="inlineStr"/>
       <c r="Y294" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z294" t="inlineStr"/>
       <c r="AA294" t="inlineStr">
         <is>
-          <t>(212) 719-9828, (516) 331-8611</t>
-        </is>
-      </c>
-      <c r="AB294" t="inlineStr">
-        <is>
-          <t>https://facebook.com/YafaSignedJewels, https://instagram.com/yafasignedjewels</t>
-        </is>
-      </c>
+          <t>(816) 323-6447</t>
+        </is>
+      </c>
+      <c r="AB294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Gold Gods</t>
+          <t>Golden State</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>(816) 721-9850</t>
+          <t>(213) 629-2130</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>support@thegoldgods.com</t>
+          <t>sales@goldenstatejewelry.com</t>
         </is>
       </c>
       <c r="F295" t="inlineStr"/>
@@ -33166,12 +33198,12 @@
       <c r="H295" t="inlineStr"/>
       <c r="I295" s="2" t="inlineStr">
         <is>
-          <t>https://thegoldgods.com</t>
+          <t>https://www.goldenstatejewelry.com</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>450 N Fairfax Ave, Los Angeles, CA 90036</t>
+          <t>550 S Hill St Ste 825, Los Angeles, CA 90013</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
@@ -33194,16 +33226,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O295" t="inlineStr"/>
-      <c r="P295" t="inlineStr"/>
+      <c r="O295" t="n">
+        <v>5</v>
+      </c>
+      <c r="P295" t="n">
+        <v>1</v>
+      </c>
       <c r="Q295" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/los-angeles-ca/mip/gold-gods-548160699</t>
+          <t>https://www.yellowpages.com/los-angeles-ca/mip/golden-state-467565356</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, role-email, direct-line, bench, custom-design, since-1978</t>
         </is>
       </c>
       <c r="S295" t="inlineStr">
@@ -33213,32 +33249,44 @@
       </c>
       <c r="T295" s="2" t="inlineStr">
         <is>
-          <t>https://thegoldgods.com/pages/contact</t>
+          <t>https://goldenstatejewelry.com/</t>
         </is>
       </c>
       <c r="U295" t="inlineStr"/>
       <c r="V295" t="inlineStr">
         <is>
-          <t>2026-10-14T01:52:07+05:30</t>
-        </is>
-      </c>
-      <c r="W295" t="inlineStr"/>
-      <c r="X295" t="inlineStr"/>
+          <t>2026-10-14T01:52:45+05:30</t>
+        </is>
+      </c>
+      <c r="W295" t="inlineStr">
+        <is>
+          <t>Golden Star Jewelry</t>
+        </is>
+      </c>
+      <c r="X295" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
       <c r="Y295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z295" t="inlineStr"/>
       <c r="AA295" t="inlineStr">
         <is>
-          <t>(816) 323-6447</t>
-        </is>
-      </c>
-      <c r="AB295" t="inlineStr"/>
+          <t>(213) 627-9677</t>
+        </is>
+      </c>
+      <c r="AB295" t="inlineStr">
+        <is>
+          <t>https://instagram.com/goldenstatejewelryla</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Golden State</t>
+          <t>Hoorsenbuhs</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -33248,17 +33296,17 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>(213) 629-2130</t>
+          <t>(888) 692-2997</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>sales@goldenstatejewelry.com</t>
+          <t>info@hoorsenbuhs.com</t>
         </is>
       </c>
       <c r="F296" t="inlineStr"/>
@@ -33266,17 +33314,17 @@
       <c r="H296" t="inlineStr"/>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldenstatejewelry.com</t>
+          <t>https://hoorsenbuhs.com</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>550 S Hill St Ste 825, Los Angeles, CA 90013</t>
+          <t>2217 Main St, Santa Monica, CA 90405</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
@@ -33294,20 +33342,16 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O296" t="n">
-        <v>5</v>
-      </c>
-      <c r="P296" t="n">
-        <v>1</v>
-      </c>
+      <c r="O296" t="inlineStr"/>
+      <c r="P296" t="inlineStr"/>
       <c r="Q296" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/los-angeles-ca/mip/golden-state-467565356</t>
+          <t>https://www.yellowpages.com/santa-monica-ca/mip/hoorsenbuhs-551622669</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, bench, custom-design, since-1978</t>
+          <t>2 of 3, role-email, direct-line</t>
         </is>
       </c>
       <c r="S296" t="inlineStr">
@@ -33317,44 +33361,40 @@
       </c>
       <c r="T296" s="2" t="inlineStr">
         <is>
-          <t>https://goldenstatejewelry.com/</t>
+          <t>https://hoorsenbuhs.com/</t>
         </is>
       </c>
       <c r="U296" t="inlineStr"/>
       <c r="V296" t="inlineStr">
         <is>
-          <t>2026-10-14T01:52:45+05:30</t>
-        </is>
-      </c>
-      <c r="W296" t="inlineStr">
-        <is>
-          <t>Golden Star Jewelry</t>
-        </is>
-      </c>
-      <c r="X296" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
+          <t>2026-10-14T01:53:36+05:30</t>
+        </is>
+      </c>
+      <c r="W296" t="inlineStr"/>
+      <c r="X296" t="inlineStr"/>
       <c r="Y296" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z296" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Z296" t="inlineStr">
+        <is>
+          <t>toll-free</t>
+        </is>
+      </c>
       <c r="AA296" t="inlineStr">
         <is>
-          <t>(213) 627-9677</t>
+          <t>(917) 206-9333</t>
         </is>
       </c>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>https://instagram.com/goldenstatejewelryla</t>
+          <t>https://instagram.com/hoorsenbuhs</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Hoorsenbuhs</t>
+          <t>Jennifer Fisher Jewelry</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -33364,17 +33404,17 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>(888) 692-2997</t>
+          <t>(424) 374-5303</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>info@hoorsenbuhs.com</t>
+          <t>la@jenniferfisher.com</t>
         </is>
       </c>
       <c r="F297" t="inlineStr"/>
@@ -33382,24 +33422,16 @@
       <c r="H297" t="inlineStr"/>
       <c r="I297" s="2" t="inlineStr">
         <is>
-          <t>https://hoorsenbuhs.com</t>
+          <t>https://jenniferfisher.com</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>2217 Main St, Santa Monica, CA 90405</t>
-        </is>
-      </c>
-      <c r="K297" t="inlineStr">
-        <is>
-          <t>Santa Monica</t>
-        </is>
-      </c>
-      <c r="L297" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
+          <t>363 N Beverly Dr, Beverly Hills, CA 90210, United States</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr"/>
+      <c r="L297" t="inlineStr"/>
       <c r="M297" t="inlineStr">
         <is>
           <t>Beverly Hills, CA</t>
@@ -33407,19 +33439,23 @@
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O297" t="inlineStr"/>
-      <c r="P297" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O297" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P297" t="n">
+        <v>44</v>
+      </c>
       <c r="Q297" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/santa-monica-ca/mip/hoorsenbuhs-551622669</t>
+          <t>https://www.google.com/maps/place/Jennifer+Fisher+Jewelry/data=!4m7!3m6!1s0x80c2bdd6ed684985:0xb8fbea746e91ad05!8m2!3d34.0695438!4d-118.4019104!16s%2Fg%2F11n12hvwn5!19sChIJhUlo7da9woARBa2RbnTq-7g</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S297" t="inlineStr">
@@ -33429,13 +33465,13 @@
       </c>
       <c r="T297" s="2" t="inlineStr">
         <is>
-          <t>https://hoorsenbuhs.com/</t>
+          <t>https://jenniferfisher.com/pages/stockists</t>
         </is>
       </c>
       <c r="U297" t="inlineStr"/>
       <c r="V297" t="inlineStr">
         <is>
-          <t>2026-10-14T01:53:36+05:30</t>
+          <t>2026-10-14T01:40:50+05:30</t>
         </is>
       </c>
       <c r="W297" t="inlineStr"/>
@@ -33443,26 +33479,22 @@
       <c r="Y297" t="n">
         <v>0</v>
       </c>
-      <c r="Z297" t="inlineStr">
-        <is>
-          <t>toll-free</t>
-        </is>
-      </c>
+      <c r="Z297" t="inlineStr"/>
       <c r="AA297" t="inlineStr">
         <is>
-          <t>(917) 206-9333</t>
+          <t>(646) 366-9375</t>
         </is>
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>https://instagram.com/hoorsenbuhs</t>
+          <t>https://instagram.com/jenniferfisherjewelry/, https://facebook.com/JenniferFisherJewelry, https://instagram.com/jenniferfisherjewelry</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Jennifer Fisher Jewelry</t>
+          <t>Jewelry &amp; Watch Buyers - Beverly Hills</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -33472,17 +33504,17 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelry buyer</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>(424) 374-5303</t>
+          <t>(310) 697-8177</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>la@jenniferfisher.com</t>
+          <t>info@watchbuyers.us</t>
         </is>
       </c>
       <c r="F298" t="inlineStr"/>
@@ -33490,12 +33522,12 @@
       <c r="H298" t="inlineStr"/>
       <c r="I298" s="2" t="inlineStr">
         <is>
-          <t>https://jenniferfisher.com</t>
+          <t>https://watchbuyers.us</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>363 N Beverly Dr, Beverly Hills, CA 90210, United States</t>
+          <t>468 N Camden Dr #205, Beverly Hills, CA 90210, United States</t>
         </is>
       </c>
       <c r="K298" t="inlineStr"/>
@@ -33511,19 +33543,19 @@
         </is>
       </c>
       <c r="O298" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="P298" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="Q298" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Jennifer+Fisher+Jewelry/data=!4m7!3m6!1s0x80c2bdd6ed684985:0xb8fbea746e91ad05!8m2!3d34.0695438!4d-118.4019104!16s%2Fg%2F11n12hvwn5!19sChIJhUlo7da9woARBa2RbnTq-7g</t>
+          <t>https://www.google.com/maps/place/Jewelry+%26+Watch+Buyers+-+Beverly+Hills/data=!4m7!3m6!1s0x80c2bdbde9baacdb:0xbbce1c74141b63ce!8m2!3d34.0698858!4d-118.404944!16s%2Fg%2F11xt1px272!19sChIJ26y66b29woARzmMbFHQczrs</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, role-email, direct-line</t>
         </is>
       </c>
       <c r="S298" t="inlineStr">
@@ -33533,13 +33565,13 @@
       </c>
       <c r="T298" s="2" t="inlineStr">
         <is>
-          <t>https://jenniferfisher.com/pages/stockists</t>
+          <t>https://watchbuyers.us/</t>
         </is>
       </c>
       <c r="U298" t="inlineStr"/>
       <c r="V298" t="inlineStr">
         <is>
-          <t>2026-10-14T01:40:50+05:30</t>
+          <t>2026-10-14T01:40:58+05:30</t>
         </is>
       </c>
       <c r="W298" t="inlineStr"/>
@@ -33550,39 +33582,31 @@
       <c r="Z298" t="inlineStr"/>
       <c r="AA298" t="inlineStr">
         <is>
-          <t>(646) 366-9375</t>
-        </is>
-      </c>
-      <c r="AB298" t="inlineStr">
-        <is>
-          <t>https://instagram.com/jenniferfisherjewelry/, https://facebook.com/JenniferFisherJewelry, https://instagram.com/jenniferfisherjewelry</t>
-        </is>
-      </c>
+          <t>(305) 989-9099, (646) 413-7757</t>
+        </is>
+      </c>
+      <c r="AB298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Jewelry &amp; Watch Buyers - Beverly Hills</t>
+          <t>Jewels Aficionado Beverly Hills</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Jewelry buyer</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>(310) 697-8177</t>
-        </is>
-      </c>
+          <t>Jewelry store</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr">
         <is>
-          <t>info@watchbuyers.us</t>
+          <t>sales@jewelsaficionado.com</t>
         </is>
       </c>
       <c r="F299" t="inlineStr"/>
@@ -33590,12 +33614,12 @@
       <c r="H299" t="inlineStr"/>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>https://watchbuyers.us</t>
+          <t>https://jewelsaficionado.com</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>468 N Camden Dr #205, Beverly Hills, CA 90210, United States</t>
+          <t>9850 Wilshire Blvd, Beverly Hills, CA 90210, United States</t>
         </is>
       </c>
       <c r="K299" t="inlineStr"/>
@@ -33610,20 +33634,16 @@
           <t>Google Maps</t>
         </is>
       </c>
-      <c r="O299" t="n">
-        <v>5</v>
-      </c>
-      <c r="P299" t="n">
-        <v>3</v>
-      </c>
+      <c r="O299" t="inlineStr"/>
+      <c r="P299" t="inlineStr"/>
       <c r="Q299" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Jewelry+%26+Watch+Buyers+-+Beverly+Hills/data=!4m7!3m6!1s0x80c2bdbde9baacdb:0xbbce1c74141b63ce!8m2!3d34.0698858!4d-118.404944!16s%2Fg%2F11xt1px272!19sChIJ26y66b29woARzmMbFHQczrs</t>
+          <t>https://www.google.com/maps/place/Jewels+Aficionado+Beverly+Hills/data=!4m7!3m6!1s0x80c2bb445801322d:0x4ee3ff18cd9446bc!8m2!3d34.0666649!4d-118.4114543!16s%2Fg%2F11z2xf_27b!19sChIJLTIBWES7woARvEaUzRj_404</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S299" t="inlineStr">
@@ -33633,13 +33653,13 @@
       </c>
       <c r="T299" s="2" t="inlineStr">
         <is>
-          <t>https://watchbuyers.us/</t>
+          <t>https://jewelsaficionado.com/</t>
         </is>
       </c>
       <c r="U299" t="inlineStr"/>
       <c r="V299" t="inlineStr">
         <is>
-          <t>2026-10-14T01:40:58+05:30</t>
+          <t>2026-10-14T01:42:22+05:30</t>
         </is>
       </c>
       <c r="W299" t="inlineStr"/>
@@ -33650,20 +33670,24 @@
       <c r="Z299" t="inlineStr"/>
       <c r="AA299" t="inlineStr">
         <is>
-          <t>(305) 989-9099, (646) 413-7757</t>
-        </is>
-      </c>
-      <c r="AB299" t="inlineStr"/>
+          <t>(212) 422-2600</t>
+        </is>
+      </c>
+      <c r="AB299" t="inlineStr">
+        <is>
+          <t>https://instagram.com/jewelsaficionado</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Jewels Aficionado Beverly Hills</t>
+          <t>Logan Hollowell Jewelry</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -33671,10 +33695,14 @@
           <t>Jewelry store</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>(323) 248-9685</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>sales@jewelsaficionado.com</t>
+          <t>info@loganhollowell.com</t>
         </is>
       </c>
       <c r="F300" t="inlineStr"/>
@@ -33682,12 +33710,12 @@
       <c r="H300" t="inlineStr"/>
       <c r="I300" s="2" t="inlineStr">
         <is>
-          <t>https://jewelsaficionado.com</t>
+          <t>https://www.loganhollowell.com</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>9850 Wilshire Blvd, Beverly Hills, CA 90210, United States</t>
+          <t>411 N Canon Dr, Beverly Hills, CA 90210, United States</t>
         </is>
       </c>
       <c r="K300" t="inlineStr"/>
@@ -33702,16 +33730,20 @@
           <t>Google Maps</t>
         </is>
       </c>
-      <c r="O300" t="inlineStr"/>
-      <c r="P300" t="inlineStr"/>
+      <c r="O300" t="n">
+        <v>5</v>
+      </c>
+      <c r="P300" t="n">
+        <v>1</v>
+      </c>
       <c r="Q300" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Jewels+Aficionado+Beverly+Hills/data=!4m7!3m6!1s0x80c2bb445801322d:0x4ee3ff18cd9446bc!8m2!3d34.0666649!4d-118.4114543!16s%2Fg%2F11z2xf_27b!19sChIJLTIBWES7woARvEaUzRj_404</t>
+          <t>https://www.google.com/maps/place/Logan+Hollowell+Jewelry/data=!4m7!3m6!1s0x80c2bd39cbc0865f:0x202c691c8504a898!8m2!3d34.07073!4d-118.4012945!16s%2Fg%2F11njp9zjzq!19sChIJX4bAyzm9woARmKgEhRxpLCA</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-2014</t>
         </is>
       </c>
       <c r="S300" t="inlineStr">
@@ -33721,13 +33753,13 @@
       </c>
       <c r="T300" s="2" t="inlineStr">
         <is>
-          <t>https://jewelsaficionado.com/</t>
+          <t>https://loganhollowell.com/</t>
         </is>
       </c>
       <c r="U300" t="inlineStr"/>
       <c r="V300" t="inlineStr">
         <is>
-          <t>2026-10-14T01:42:22+05:30</t>
+          <t>2026-10-14T01:41:31+05:30</t>
         </is>
       </c>
       <c r="W300" t="inlineStr"/>
@@ -33738,39 +33770,39 @@
       <c r="Z300" t="inlineStr"/>
       <c r="AA300" t="inlineStr">
         <is>
-          <t>(212) 422-2600</t>
+          <t>(323) 853-7844</t>
         </is>
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>https://instagram.com/jewelsaficionado</t>
+          <t>https://instagram.com/loganhollowell, https://facebook.com/loganhollowelljewelry</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Logan Hollowell Jewelry</t>
+          <t>Majestic Jewelry</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>(323) 248-9685</t>
+          <t>(323) 933-0288</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>info@loganhollowell.com</t>
+          <t>info@majesticjewelers.com</t>
         </is>
       </c>
       <c r="F301" t="inlineStr"/>
@@ -33778,16 +33810,24 @@
       <c r="H301" t="inlineStr"/>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>https://www.loganhollowell.com</t>
+          <t>https://majesticjewelers.com</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>411 N Canon Dr, Beverly Hills, CA 90210, United States</t>
-        </is>
-      </c>
-      <c r="K301" t="inlineStr"/>
-      <c r="L301" t="inlineStr"/>
+          <t>6333 W 3rd St, Los Angeles, CA 90036</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
       <c r="M301" t="inlineStr">
         <is>
           <t>Beverly Hills, CA</t>
@@ -33795,23 +33835,23 @@
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O301" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P301" t="n">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="Q301" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Logan+Hollowell+Jewelry/data=!4m7!3m6!1s0x80c2bd39cbc0865f:0x202c691c8504a898!8m2!3d34.07073!4d-118.4012945!16s%2Fg%2F11njp9zjzq!19sChIJX4bAyzm9woARmKgEhRxpLCA</t>
+          <t>https://www.yellowpages.com/los-angeles-ca/mip/majestic-jewelry-458143900</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-2014</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-1986</t>
         </is>
       </c>
       <c r="S301" t="inlineStr">
@@ -33821,41 +33861,49 @@
       </c>
       <c r="T301" s="2" t="inlineStr">
         <is>
-          <t>https://loganhollowell.com/</t>
+          <t>https://www.majesticjewelers.com/about-us/</t>
         </is>
       </c>
       <c r="U301" t="inlineStr"/>
       <c r="V301" t="inlineStr">
         <is>
-          <t>2026-10-14T01:41:31+05:30</t>
-        </is>
-      </c>
-      <c r="W301" t="inlineStr"/>
-      <c r="X301" t="inlineStr"/>
+          <t>2026-10-14T01:52:20+05:30</t>
+        </is>
+      </c>
+      <c r="W301" t="inlineStr">
+        <is>
+          <t>Majestic W.J.</t>
+        </is>
+      </c>
+      <c r="X301" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
       <c r="Y301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z301" t="inlineStr"/>
       <c r="AA301" t="inlineStr">
         <is>
-          <t>(323) 853-7844</t>
+          <t>(407) 644-4824</t>
         </is>
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>https://instagram.com/loganhollowell, https://facebook.com/loganhollowelljewelry</t>
+          <t>https://facebook.com/MajesticJewelersInc, https://instagram.com/majesticjewelerswp</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Majestic Jewelry</t>
+          <t>Raven Fine Jewelers</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -33865,12 +33913,12 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>(323) 933-0288</t>
+          <t>(310) 432-5234</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>info@majesticjewelers.com</t>
+          <t>info@ravenjewelers.com</t>
         </is>
       </c>
       <c r="F302" t="inlineStr"/>
@@ -33878,17 +33926,17 @@
       <c r="H302" t="inlineStr"/>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>https://majesticjewelers.com</t>
+          <t>https://ravenfinejewelers.localsearch.com</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>6333 W 3rd St, Los Angeles, CA 90036</t>
+          <t>8350 Wilshire Blvd, Beverly Hills, CA 90211</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Beverly Hills</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
@@ -33907,19 +33955,19 @@
         </is>
       </c>
       <c r="O302" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P302" t="n">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="Q302" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/los-angeles-ca/mip/majestic-jewelry-458143900</t>
+          <t>https://www.yellowpages.com/beverly-hills-ca/mip/raven-fine-jewelers-531865762</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-1986</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S302" t="inlineStr">
@@ -33929,64 +33977,56 @@
       </c>
       <c r="T302" s="2" t="inlineStr">
         <is>
-          <t>https://www.majesticjewelers.com/about-us/</t>
+          <t>https://ravendiamonds.com/</t>
         </is>
       </c>
       <c r="U302" t="inlineStr"/>
       <c r="V302" t="inlineStr">
         <is>
-          <t>2026-10-14T01:52:20+05:30</t>
-        </is>
-      </c>
-      <c r="W302" t="inlineStr">
-        <is>
-          <t>Majestic W.J.</t>
-        </is>
-      </c>
-      <c r="X302" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
+          <t>2026-10-14T01:51:20+05:30</t>
+        </is>
+      </c>
+      <c r="W302" t="inlineStr"/>
+      <c r="X302" t="inlineStr"/>
       <c r="Y302" t="n">
         <v>1</v>
       </c>
       <c r="Z302" t="inlineStr"/>
       <c r="AA302" t="inlineStr">
         <is>
-          <t>(407) 644-4824</t>
+          <t>(310) 887-1499</t>
         </is>
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>https://facebook.com/MajesticJewelersInc, https://instagram.com/majesticjewelerswp</t>
+          <t>https://instagram.com/ravenfinejewelers, https://facebook.com/RavenFineJewelers</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Raven Fine Jewelers</t>
+          <t>Sunset Plaza</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Watches, Real Estate Agents</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>(310) 432-5234</t>
+          <t>(310) 652-7137</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>info@ravenjewelers.com</t>
+          <t>info@sunsetplaza.com</t>
         </is>
       </c>
       <c r="F303" t="inlineStr"/>
@@ -33994,17 +34034,17 @@
       <c r="H303" t="inlineStr"/>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>https://ravenfinejewelers.localsearch.com</t>
+          <t>https://www.sunsetplaza.com</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>8350 Wilshire Blvd, Beverly Hills, CA 90211</t>
+          <t>8623 W Sunset Blvd, West Hollywood, CA 90069</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>Beverly Hills</t>
+          <t>West Hollywood</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -34022,20 +34062,16 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O303" t="n">
-        <v>5</v>
-      </c>
-      <c r="P303" t="n">
-        <v>1</v>
-      </c>
+      <c r="O303" t="inlineStr"/>
+      <c r="P303" t="inlineStr"/>
       <c r="Q303" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/beverly-hills-ca/mip/raven-fine-jewelers-531865762</t>
+          <t>https://www.yellowpages.com/west-hollywood-ca/mip/sunset-plaza-1562237</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, role-email, direct-line, since-1924</t>
         </is>
       </c>
       <c r="S303" t="inlineStr">
@@ -34045,81 +34081,81 @@
       </c>
       <c r="T303" s="2" t="inlineStr">
         <is>
-          <t>https://ravendiamonds.com/</t>
+          <t>https://www.sunsetplaza.com/</t>
         </is>
       </c>
       <c r="U303" t="inlineStr"/>
       <c r="V303" t="inlineStr">
         <is>
-          <t>2026-10-14T01:51:20+05:30</t>
+          <t>2026-10-14T01:52:13+05:30</t>
         </is>
       </c>
       <c r="W303" t="inlineStr"/>
       <c r="X303" t="inlineStr"/>
       <c r="Y303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z303" t="inlineStr"/>
       <c r="AA303" t="inlineStr">
         <is>
-          <t>(310) 887-1499</t>
+          <t>(213) 500-3098, (213) 709-2282, (310) 210-0975, (310) 248-3750, (310) 274-1602, (310) 275-2222, (310) 289-1104, (310) 289-1105, (310) 360-6900, (310) 360-8889, (310) 424-3690, (310) 616-7888, (310) 652-2680, (310) 652-6844, (310) 652-7039, (310) 652-8886, (310) 657-2553, (310) 657-5070, (310) 657-5469, (310) 659-4411, (310) 659-9089, (310) 734-7296, (310) 786-7417, (310) 849-7185, (310) 854-0299, (310) 854-7700, (310) 855-8044, (323) 253-6747, (323) 345-4525, (323) 507-3943, (323) 650-0475, (323) 937-0355, (424) 407-4606, (424) 542-7730, (424) 667-0036, (424) 722-8502, (747) 724-3595</t>
         </is>
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>https://instagram.com/ravenfinejewelers, https://facebook.com/RavenFineJewelers</t>
+          <t>https://instagram.com/affluette_, https://instagram.com/alchemy43, https://facebook.com/alchemy43, https://instagram.com/andreas.fashions, https://facebook.com/andreasfashions, https://instagram.com/bbcmcafe, https://instagram.com/bootstarusa, https://facebook.com/Boot-Star-106137407505929, https://instagram.com/bossanovarestaurant, https://facebook.com/BossaNovaLA, https://instagram.com/charliechoukair/, https://instagram.com/cristallini_official, https://facebook.com/CRISTALLINIOfficial, https://instagram.com/architectureforsale/, https://instagram.com/cupidlipsofbeverlyhills, https://facebook.com/profile.php?id=100083257576786, https://instagram.com/dandeutschoo, https://instagram.com/davidorgell, https://instagram.com/drybarshopsus, https://facebook.com/thedrybar, https://instagram.com/elainekimcollection/, https://instagram.com/entouragebarbershop, https://instagram.com/fpjourneofficial, https://instagram.com/guyfloralstudio, https://instagram.com/hotpilates, https://facebook.com/Hot-Pilates-1806940676211478, https://instagram.com/kojitoyodasalon, https://instagram.com/metaclinic/, https://instagram.com/milamoursiskincare, https://instagram.com/olehenriksenspa/, https://instagram.com/oliverpeoples, https://instagram.com/osklo.la, https://instagram.com/philippressjeweler, https://instagram.com/puravidamiami, https://facebook.com/PuraVidaMiami, https://instagram.com/queenbnailsalon_sunsetplaza, https://instagram.com/andywarholrevolvergallery, https://instagram.com/rondorff, https://instagram.com/saltiegirlla, https://instagram.com/samira13jewelry, https://instagram.com/sargondental, https://facebook.com/sargonlazarofdds, https://instagram.com/serenityonsunset, https://instagram.com/sheilaonsunset, https://instagram.com/solatesbysamantha, https://instagram.com/sousla_official, https://instagram.com/sunsetkidsla, https://instagram.com/theoppenheimgroup, https://facebook.com/theoppenheimgroup, https://instagram.com/whitegloveestates, https://instagram.com/xrcyze_ny, https://facebook.com/xrcycle, https://instagram.com/sunsetplazaca, https://facebook.com/SunsetPlazaCA</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Sunset Plaza</t>
+          <t>Westime Beverly Hills</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Jewelers, Watches, Real Estate Agents</t>
+          <t>Watch store</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>(310) 652-7137</t>
+          <t>(310) 888-8880</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>info@sunsetplaza.com</t>
+          <t>contact@westime.com</t>
         </is>
       </c>
       <c r="F304" t="inlineStr"/>
-      <c r="G304" t="inlineStr"/>
-      <c r="H304" t="inlineStr"/>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>Greg Simonian</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>https://www.sunsetplaza.com</t>
+          <t>https://westime.com</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>8623 W Sunset Blvd, West Hollywood, CA 90069</t>
-        </is>
-      </c>
-      <c r="K304" t="inlineStr">
-        <is>
-          <t>West Hollywood</t>
-        </is>
-      </c>
-      <c r="L304" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
+          <t>206 N Rodeo Dr, Beverly Hills, CA 90210, United States</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr"/>
+      <c r="L304" t="inlineStr"/>
       <c r="M304" t="inlineStr">
         <is>
           <t>Beverly Hills, CA</t>
@@ -34127,19 +34163,23 @@
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O304" t="inlineStr"/>
-      <c r="P304" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O304" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P304" t="n">
+        <v>274</v>
+      </c>
       <c r="Q304" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/west-hollywood-ca/mip/sunset-plaza-1562237</t>
+          <t>https://www.google.com/maps/place/Westime+Beverly+Hills/data=!4m7!3m6!1s0x80c2bc0ed6429065:0x2c357ea8ffa51b1f!8m2!3d34.067375!4d-118.4003799!16s%2Fg%2F11cfj2mg2!19sChIJZZBC1g68woARHxul_6h-NSw</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, since-1924</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-1987</t>
         </is>
       </c>
       <c r="S304" t="inlineStr">
@@ -34149,13 +34189,13 @@
       </c>
       <c r="T304" s="2" t="inlineStr">
         <is>
-          <t>https://www.sunsetplaza.com/</t>
+          <t>https://westime.com/contact</t>
         </is>
       </c>
       <c r="U304" t="inlineStr"/>
       <c r="V304" t="inlineStr">
         <is>
-          <t>2026-10-14T01:52:13+05:30</t>
+          <t>2026-10-14T01:39:33+05:30</t>
         </is>
       </c>
       <c r="W304" t="inlineStr"/>
@@ -34166,24 +34206,24 @@
       <c r="Z304" t="inlineStr"/>
       <c r="AA304" t="inlineStr">
         <is>
-          <t>(213) 500-3098, (213) 709-2282, (310) 210-0975, (310) 248-3750, (310) 274-1602, (310) 275-2222, (310) 289-1104, (310) 289-1105, (310) 360-6900, (310) 360-8889, (310) 424-3690, (310) 616-7888, (310) 652-2680, (310) 652-6844, (310) 652-7039, (310) 652-8886, (310) 657-2553, (310) 657-5070, (310) 657-5469, (310) 659-4411, (310) 659-9089, (310) 734-7296, (310) 786-7417, (310) 849-7185, (310) 854-0299, (310) 854-7700, (310) 855-8044, (323) 253-6747, (323) 345-4525, (323) 507-3943, (323) 650-0475, (323) 937-0355, (424) 407-4606, (424) 542-7730, (424) 667-0036, (424) 722-8502, (747) 724-3595</t>
+          <t>(786) 347-5353, (858) 459-2222</t>
         </is>
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>https://instagram.com/affluette_, https://instagram.com/alchemy43, https://facebook.com/alchemy43, https://instagram.com/andreas.fashions, https://facebook.com/andreasfashions, https://instagram.com/bbcmcafe, https://instagram.com/bootstarusa, https://facebook.com/Boot-Star-106137407505929, https://instagram.com/bossanovarestaurant, https://facebook.com/BossaNovaLA, https://instagram.com/charliechoukair/, https://instagram.com/cristallini_official, https://facebook.com/CRISTALLINIOfficial, https://instagram.com/architectureforsale/, https://instagram.com/cupidlipsofbeverlyhills, https://facebook.com/profile.php?id=100083257576786, https://instagram.com/dandeutschoo, https://instagram.com/davidorgell, https://instagram.com/drybarshopsus, https://facebook.com/thedrybar, https://instagram.com/elainekimcollection/, https://instagram.com/entouragebarbershop, https://instagram.com/fpjourneofficial, https://instagram.com/guyfloralstudio, https://instagram.com/hotpilates, https://facebook.com/Hot-Pilates-1806940676211478, https://instagram.com/kojitoyodasalon, https://instagram.com/metaclinic/, https://instagram.com/milamoursiskincare, https://instagram.com/olehenriksenspa/, https://instagram.com/oliverpeoples, https://instagram.com/osklo.la, https://instagram.com/philippressjeweler, https://instagram.com/puravidamiami, https://facebook.com/PuraVidaMiami, https://instagram.com/queenbnailsalon_sunsetplaza, https://instagram.com/andywarholrevolvergallery, https://instagram.com/rondorff, https://instagram.com/saltiegirlla, https://instagram.com/samira13jewelry, https://instagram.com/sargondental, https://facebook.com/sargonlazarofdds, https://instagram.com/serenityonsunset, https://instagram.com/sheilaonsunset, https://instagram.com/solatesbysamantha, https://instagram.com/sousla_official, https://instagram.com/sunsetkidsla, https://instagram.com/theoppenheimgroup, https://facebook.com/theoppenheimgroup, https://instagram.com/whitegloveestates, https://instagram.com/xrcyze_ny, https://facebook.com/xrcycle, https://instagram.com/sunsetplazaca, https://facebook.com/SunsetPlazaCA</t>
+          <t>https://instagram.com/westimewatches, https://facebook.com/Westime</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Westime Beverly Hills</t>
+          <t>Wrist Aficionado Beverly Hills</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -34193,37 +34233,37 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>(310) 888-8880</t>
+          <t>(310) 388-8201</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>contact@westime.com</t>
+          <t>sales@wristaficionado.com</t>
         </is>
       </c>
       <c r="F305" t="inlineStr"/>
-      <c r="G305" t="inlineStr">
-        <is>
-          <t>Greg Simonian</t>
-        </is>
-      </c>
-      <c r="H305" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
+      <c r="G305" t="inlineStr"/>
+      <c r="H305" t="inlineStr"/>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>https://westime.com</t>
+          <t>https://wristaficionado.com</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>206 N Rodeo Dr, Beverly Hills, CA 90210, United States</t>
-        </is>
-      </c>
-      <c r="K305" t="inlineStr"/>
-      <c r="L305" t="inlineStr"/>
+          <t>9850 Wilshire Blvd, Beverly Hills, CA 90210, United States</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Beverly Hills</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
       <c r="M305" t="inlineStr">
         <is>
           <t>Beverly Hills, CA</t>
@@ -34235,19 +34275,19 @@
         </is>
       </c>
       <c r="O305" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="P305" t="n">
-        <v>274</v>
+        <v>101</v>
       </c>
       <c r="Q305" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Westime+Beverly+Hills/data=!4m7!3m6!1s0x80c2bc0ed6429065:0x2c357ea8ffa51b1f!8m2!3d34.067375!4d-118.4003799!16s%2Fg%2F11cfj2mg2!19sChIJZZBC1g68woARHxul_6h-NSw</t>
+          <t>https://www.google.com/maps/place/Wrist+Aficionado+Beverly+Hills/data=!4m7!3m6!1s0x80c2bb67e5181fcf:0xde9cbdbb118a155c!8m2!3d34.0667288!4d-118.4113018!16s%2Fg%2F11v12tg_x0!19sChIJzx8Y5We7woARXBWKEbu9nN4</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-1987</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-2017</t>
         </is>
       </c>
       <c r="S305" t="inlineStr">
@@ -34257,13 +34297,13 @@
       </c>
       <c r="T305" s="2" t="inlineStr">
         <is>
-          <t>https://westime.com/contact</t>
+          <t>https://wristaficionado.com/</t>
         </is>
       </c>
       <c r="U305" t="inlineStr"/>
       <c r="V305" t="inlineStr">
         <is>
-          <t>2026-10-14T01:39:33+05:30</t>
+          <t>2026-10-14T01:43:17+05:30</t>
         </is>
       </c>
       <c r="W305" t="inlineStr"/>
@@ -34274,125 +34314,17 @@
       <c r="Z305" t="inlineStr"/>
       <c r="AA305" t="inlineStr">
         <is>
-          <t>(786) 347-5353, (858) 459-2222</t>
+          <t>(305) 680-3735, (310) 861-3485, (646) 693-9384, (786) 889-6892</t>
         </is>
       </c>
       <c r="AB305" t="inlineStr">
-        <is>
-          <t>https://instagram.com/westimewatches, https://facebook.com/Westime</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>Wrist Aficionado Beverly Hills</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>Jewelry retailer</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>Watch store</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>(310) 388-8201</t>
-        </is>
-      </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>sales@wristaficionado.com</t>
-        </is>
-      </c>
-      <c r="F306" t="inlineStr"/>
-      <c r="G306" t="inlineStr"/>
-      <c r="H306" t="inlineStr"/>
-      <c r="I306" s="2" t="inlineStr">
-        <is>
-          <t>https://wristaficionado.com</t>
-        </is>
-      </c>
-      <c r="J306" t="inlineStr">
-        <is>
-          <t>9850 Wilshire Blvd, Beverly Hills, CA 90210, United States</t>
-        </is>
-      </c>
-      <c r="K306" t="inlineStr">
-        <is>
-          <t>Beverly Hills</t>
-        </is>
-      </c>
-      <c r="L306" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M306" t="inlineStr">
-        <is>
-          <t>Beverly Hills, CA</t>
-        </is>
-      </c>
-      <c r="N306" t="inlineStr">
-        <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O306" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P306" t="n">
-        <v>101</v>
-      </c>
-      <c r="Q306" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/place/Wrist+Aficionado+Beverly+Hills/data=!4m7!3m6!1s0x80c2bb67e5181fcf:0xde9cbdbb118a155c!8m2!3d34.0667288!4d-118.4113018!16s%2Fg%2F11v12tg_x0!19sChIJzx8Y5We7woARXBWKEbu9nN4</t>
-        </is>
-      </c>
-      <c r="R306" t="inlineStr">
-        <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-2017</t>
-        </is>
-      </c>
-      <c r="S306" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="T306" s="2" t="inlineStr">
-        <is>
-          <t>https://wristaficionado.com/</t>
-        </is>
-      </c>
-      <c r="U306" t="inlineStr"/>
-      <c r="V306" t="inlineStr">
-        <is>
-          <t>2026-10-14T01:43:17+05:30</t>
-        </is>
-      </c>
-      <c r="W306" t="inlineStr"/>
-      <c r="X306" t="inlineStr"/>
-      <c r="Y306" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z306" t="inlineStr"/>
-      <c r="AA306" t="inlineStr">
-        <is>
-          <t>(305) 680-3735, (310) 861-3485, (646) 693-9384, (786) 889-6892</t>
-        </is>
-      </c>
-      <c r="AB306" t="inlineStr">
         <is>
           <t>https://instagram.com/wristaficionado, https://instagram.com/wristaficionado/, https://facebook.com/shopwristaficionado, https://twitter.com/wristaficionado</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB306"/>
+  <autoFilter ref="A1:AB305"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId2"/>
@@ -35227,14 +35159,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I249" r:id="rId831"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q249" r:id="rId832"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T249" r:id="rId833"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I250" r:id="rId834"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q250" r:id="rId835"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T250" r:id="rId836"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F251" r:id="rId837"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I251" r:id="rId838"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q251" r:id="rId839"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T251" r:id="rId840"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U251" r:id="rId841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F250" r:id="rId834"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I250" r:id="rId835"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q250" r:id="rId836"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T250" r:id="rId837"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U250" r:id="rId838"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I251" r:id="rId839"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q251" r:id="rId840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T251" r:id="rId841"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I252" r:id="rId842"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q252" r:id="rId843"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T252" r:id="rId844"/>
@@ -35253,14 +35185,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I257" r:id="rId857"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q257" r:id="rId858"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T257" r:id="rId859"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I258" r:id="rId860"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q258" r:id="rId861"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T258" r:id="rId862"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F259" r:id="rId863"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I259" r:id="rId864"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q259" r:id="rId865"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T259" r:id="rId866"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U259" r:id="rId867"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F258" r:id="rId860"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I258" r:id="rId861"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q258" r:id="rId862"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T258" r:id="rId863"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U258" r:id="rId864"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I259" r:id="rId865"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q259" r:id="rId866"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T259" r:id="rId867"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I260" r:id="rId868"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q260" r:id="rId869"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T260" r:id="rId870"/>
@@ -35306,14 +35238,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I274" r:id="rId910"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q274" r:id="rId911"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T274" r:id="rId912"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I275" r:id="rId913"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q275" r:id="rId914"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T275" r:id="rId915"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F276" r:id="rId916"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I276" r:id="rId917"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q276" r:id="rId918"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T276" r:id="rId919"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U276" r:id="rId920"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F275" r:id="rId913"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I275" r:id="rId914"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q275" r:id="rId915"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T275" r:id="rId916"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U275" r:id="rId917"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I276" r:id="rId918"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q276" r:id="rId919"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T276" r:id="rId920"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I277" r:id="rId921"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q277" r:id="rId922"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T277" r:id="rId923"/>
@@ -35401,9 +35333,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I305" r:id="rId1005"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q305" r:id="rId1006"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T305" r:id="rId1007"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I306" r:id="rId1008"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q306" r:id="rId1009"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T306" r:id="rId1010"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35822,7 +35751,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C15" t="n">
         <v>6</v>
@@ -35849,21 +35778,21 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>279</v>
+        <v>305</v>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G16" t="n">
         <v>3</v>
@@ -36146,21 +36075,21 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10671</v>
+        <v>10696</v>
       </c>
       <c r="C27" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F27" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G27" t="n">
         <v>50</v>
@@ -36213,7 +36142,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4">
@@ -36255,7 +36184,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9">
@@ -36314,7 +36243,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T03:46:01+05:30</t>
+          <t>2026-10-14T04:06:15+05:30</t>
         </is>
       </c>
     </row>
@@ -36325,7 +36254,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3">
@@ -36335,7 +36264,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>10671</v>
+        <v>10696</v>
       </c>
     </row>
     <row r="4">

--- a/leadrun_jewelry/jewelry_qualified.xlsx
+++ b/leadrun_jewelry/jewelry_qualified.xlsx
@@ -27875,7 +27875,7 @@
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>2 of 3, gia, bench, custom-design, since-1983</t>
+          <t>2 of 3, gia, bench, custom-design, since-1924</t>
         </is>
       </c>
       <c r="S246" t="inlineStr">
@@ -27900,12 +27900,12 @@
       </c>
       <c r="W246" t="inlineStr">
         <is>
-          <t>Bulow Jewelers, William Crow Jewelry Inc., Lupo Jewelers</t>
+          <t>Bulow Jewelers, William Crow Jewelry Inc., William Crow Jewelry, Inc., Lupo Jewelers</t>
         </is>
       </c>
       <c r="X246" t="inlineStr"/>
       <c r="Y246" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z246" t="inlineStr">
         <is>
@@ -27915,7 +27915,7 @@
       <c r="AA246" t="inlineStr"/>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>https://instagram.com/bulowjewelers/, https://facebook.com/pages/category/Jewelry---Watches-Store/Bulow-Jewelers-166292557387387</t>
+          <t>https://instagram.com/bulowjewelers/, https://facebook.com/pages/category/Jewelry---Watches-Store/Bulow-Jewelers-166292557387387, https://facebook.com/DomainMarketCom, https://instagram.com/domainmarketcom, https://x.com/domainmarketcom</t>
         </is>
       </c>
     </row>
@@ -35778,14 +35778,14 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>305</v>
+        <v>337</v>
       </c>
       <c r="C16" t="n">
         <v>10</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -36075,7 +36075,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10696</v>
+        <v>10728</v>
       </c>
       <c r="C27" t="n">
         <v>304</v>
@@ -36243,7 +36243,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T04:06:15+05:30</t>
+          <t>2026-10-14T04:26:28+05:30</t>
         </is>
       </c>
     </row>
@@ -36264,7 +36264,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>10696</v>
+        <v>10728</v>
       </c>
     </row>
     <row r="4">

--- a/leadrun_jewelry/jewelry_qualified.xlsx
+++ b/leadrun_jewelry/jewelry_qualified.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qualified Leads'!$A$1:$AB$305</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qualified Leads'!$A$1:$AB$307</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB305"/>
+  <dimension ref="A1:AB307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -27922,7 +27922,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Foster &amp; Son Fine Jewelry</t>
+          <t>Carleo Creations Inc</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -27932,35 +27932,47 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>(303) 377-1414</t>
+          <t>(719) 544-1809</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>fosterandsonjewelers@gmail.com</t>
-        </is>
-      </c>
-      <c r="F247" t="inlineStr"/>
-      <c r="G247" t="inlineStr"/>
-      <c r="H247" t="inlineStr"/>
+          <t>carleocreations@comcast.net</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cory-vetta-013b092b</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Cory Vetta</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>https://www.cherrycreekjewelry.com</t>
+          <t>https://carleocreations.com</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>2908 E 3rd Ave, Denver, CO 80206, United States</t>
+          <t>608 N Main St, Pueblo, CO 81003-3127</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Pueblo</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -27975,62 +27987,58 @@
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O247" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P247" t="n">
-        <v>75</v>
-      </c>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr"/>
+      <c r="P247" t="inlineStr"/>
       <c r="Q247" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Foster+%26+Son+Fine+Jewelry/data=!4m7!3m6!1s0x876c7e97b6c50b11:0x515a7f34e093b7dd!8m2!3d39.7208378!4d-104.9530302!16s%2Fg%2F1tdmkzsc!19sChIJEQvFtpd-bIcR3beT4DR_WlE</t>
+          <t>https://www.bbb.org/us/co/pueblo/profile/jewelry-stores/carleo-creations-inc-0785-50001923</t>
         </is>
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, bench, custom-design, since-1959</t>
+          <t>2 of 3, bench, custom-design, since-1986</t>
         </is>
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T247" s="2" t="inlineStr">
         <is>
-          <t>https://www.cherrycreekjewelry.com/</t>
-        </is>
-      </c>
-      <c r="U247" t="inlineStr"/>
+          <t>https://carleocreations.com/</t>
+        </is>
+      </c>
+      <c r="U247" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Cory+Vetta%22+Pueblo+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V247" t="inlineStr">
         <is>
-          <t>2026-10-14T00:13:37+05:30</t>
+          <t>2026-10-14T04:00:44+05:30</t>
         </is>
       </c>
       <c r="W247" t="inlineStr"/>
       <c r="X247" t="inlineStr"/>
       <c r="Y247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z247" t="inlineStr"/>
-      <c r="AA247" t="inlineStr">
-        <is>
-          <t>(720) 720-4403</t>
-        </is>
-      </c>
+      <c r="AA247" t="inlineStr"/>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>https://facebook.com/pages/Foster-Son/948696858488494, https://instagram.com/fosterandsonjewelers</t>
+          <t>https://facebook.com/CarleoCreationsPueblo, https://instagram.com/carleocreations</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>JK Diamond Co.</t>
+          <t>Foster &amp; Son Fine Jewelry</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -28040,17 +28048,17 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Jeweler</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>(303) 305-5910</t>
+          <t>(303) 377-1414</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>hello@jkdiamondco.com</t>
+          <t>fosterandsonjewelers@gmail.com</t>
         </is>
       </c>
       <c r="F248" t="inlineStr"/>
@@ -28058,16 +28066,24 @@
       <c r="H248" t="inlineStr"/>
       <c r="I248" s="2" t="inlineStr">
         <is>
-          <t>https://www.jkdiamondco.com</t>
+          <t>https://www.cherrycreekjewelry.com</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>2422 E 3rd Ave, Denver, CO 80206, United States</t>
-        </is>
-      </c>
-      <c r="K248" t="inlineStr"/>
-      <c r="L248" t="inlineStr"/>
+          <t>2908 E 3rd Ave, Denver, CO 80206, United States</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
       <c r="M248" t="inlineStr">
         <is>
           <t>Denver, CO</t>
@@ -28079,19 +28095,19 @@
         </is>
       </c>
       <c r="O248" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P248" t="n">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="Q248" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/JK+Diamond+Co./data=!4m7!3m6!1s0x876c7f58603bd1a9:0xbbe855e447f0b9aa!8m2!3d39.7208718!4d-104.9576087!16s%2Fg%2F11f9ct4v4z!19sChIJqdE7YFh_bIcRqrnwR-RV6Ls</t>
+          <t>https://www.google.com/maps/place/Foster+%26+Son+Fine+Jewelry/data=!4m7!3m6!1s0x876c7e97b6c50b11:0x515a7f34e093b7dd!8m2!3d39.7208378!4d-104.9530302!16s%2Fg%2F1tdmkzsc!19sChIJEQvFtpd-bIcR3beT4DR_WlE</t>
         </is>
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line</t>
+          <t>2 of 3, direct-line, bench, custom-design, since-1959</t>
         </is>
       </c>
       <c r="S248" t="inlineStr">
@@ -28101,89 +28117,73 @@
       </c>
       <c r="T248" s="2" t="inlineStr">
         <is>
-          <t>https://www.jkdiamondco.com/</t>
+          <t>https://www.cherrycreekjewelry.com/</t>
         </is>
       </c>
       <c r="U248" t="inlineStr"/>
       <c r="V248" t="inlineStr">
         <is>
-          <t>2026-10-14T00:17:54+05:30</t>
+          <t>2026-10-14T00:13:37+05:30</t>
         </is>
       </c>
       <c r="W248" t="inlineStr"/>
       <c r="X248" t="inlineStr"/>
       <c r="Y248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z248" t="inlineStr"/>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>(213) 761-5992</t>
+          <t>(720) 720-4403</t>
         </is>
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>https://instagram.com/jkdiamondco</t>
+          <t>https://facebook.com/pages/Foster-Son/948696858488494, https://instagram.com/fosterandsonjewelers</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Ooh Ahh Jewelery</t>
+          <t>JK Diamond Co.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jeweler</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>(720) 855-7241</t>
+          <t>(303) 305-5910</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>oohaahabq@gmail.com</t>
+          <t>hello@jkdiamondco.com</t>
         </is>
       </c>
       <c r="F249" t="inlineStr"/>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>Mary Vigil</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="inlineStr"/>
       <c r="I249" s="2" t="inlineStr">
         <is>
-          <t>https://www.oohaahjewelry.com</t>
+          <t>https://www.jkdiamondco.com</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>4318 Tennyson St, Denver, CO 80212</t>
-        </is>
-      </c>
-      <c r="K249" t="inlineStr">
-        <is>
-          <t>Denver</t>
-        </is>
-      </c>
-      <c r="L249" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
+          <t>2422 E 3rd Ave, Denver, CO 80206, United States</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
       <c r="M249" t="inlineStr">
         <is>
           <t>Denver, CO</t>
@@ -28191,19 +28191,23 @@
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O249" t="inlineStr"/>
-      <c r="P249" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O249" t="n">
+        <v>5</v>
+      </c>
+      <c r="P249" t="n">
+        <v>138</v>
+      </c>
       <c r="Q249" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/denver-co/mip/ooh-ahh-jewelery-3791097</t>
+          <t>https://www.google.com/maps/place/JK+Diamond+Co./data=!4m7!3m6!1s0x876c7f58603bd1a9:0xbbe855e447f0b9aa!8m2!3d39.7208718!4d-104.9576087!16s%2Fg%2F11f9ct4v4z!19sChIJqdE7YFh_bIcRqrnwR-RV6Ls</t>
         </is>
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design, since-1988</t>
+          <t>2 of 3, role-email, direct-line</t>
         </is>
       </c>
       <c r="S249" t="inlineStr">
@@ -28213,85 +28217,77 @@
       </c>
       <c r="T249" s="2" t="inlineStr">
         <is>
-          <t>https://oohaahjewelry.com/</t>
+          <t>https://www.jkdiamondco.com/</t>
         </is>
       </c>
       <c r="U249" t="inlineStr"/>
       <c r="V249" t="inlineStr">
         <is>
-          <t>2026-10-14T01:37:14+05:30</t>
-        </is>
-      </c>
-      <c r="W249" t="inlineStr">
-        <is>
-          <t>Ooh Aah Jewelry, Inc.</t>
-        </is>
-      </c>
+          <t>2026-10-14T00:17:54+05:30</t>
+        </is>
+      </c>
+      <c r="W249" t="inlineStr"/>
       <c r="X249" t="inlineStr"/>
       <c r="Y249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z249" t="inlineStr"/>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>(505) 265-7170</t>
+          <t>(213) 761-5992</t>
         </is>
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>https://facebook.com/oohaahalbuquerque, https://instagram.com/oohaahjewelry</t>
+          <t>https://instagram.com/jkdiamondco</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Sowilo Artisan Jewelry</t>
+          <t>Ooh Ahh Jewelery</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>(303) 548-5467</t>
+          <t>(720) 855-7241</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>sowilollc@gmail.com</t>
-        </is>
-      </c>
-      <c r="F250" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/bonnie-startek-5122141b3</t>
-        </is>
-      </c>
+          <t>oohaahabq@gmail.com</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr"/>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Bonnie Startek</t>
+          <t>Mary Vigil</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="I250" s="2" t="inlineStr">
         <is>
-          <t>https://sowiloartisanjewelry.com</t>
+          <t>https://www.oohaahjewelry.com</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>999 Vallejo St Unit 3, Studio 4K, Denver, CO 80204, United States</t>
+          <t>4318 Tennyson St, Denver, CO 80212</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -28311,100 +28307,108 @@
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O250" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P250" t="n">
-        <v>60</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr"/>
+      <c r="P250" t="inlineStr"/>
       <c r="Q250" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Sowilo+Artisan+Jewelry/data=!4m7!3m6!1s0x876c7e540569644b:0xca2f5260ce1de685!8m2!3d39.7323841!4d-105.0133421!16s%2Fg%2F11c3s9631b!19sChIJS2RpBVR-bIcRheYdzmBSL8o</t>
+          <t>https://www.yellowpages.com/denver-co/mip/ooh-ahh-jewelery-3791097</t>
         </is>
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>2 of 3, custom-design, since-2003</t>
+          <t>2 of 3, direct-line, custom-design, since-1988</t>
         </is>
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="T250" s="2" t="inlineStr">
         <is>
-          <t>https://sowiloartisanjewelry.com/</t>
-        </is>
-      </c>
-      <c r="U250" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=%22Bonnie+Startek%22+Denver+linkedin&amp;hl=en&amp;num=10</t>
-        </is>
-      </c>
+          <t>https://oohaahjewelry.com/</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr"/>
       <c r="V250" t="inlineStr">
         <is>
-          <t>2026-10-14T00:14:18+05:30</t>
-        </is>
-      </c>
-      <c r="W250" t="inlineStr"/>
+          <t>2026-10-14T01:37:14+05:30</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>Ooh Aah Jewelry, Inc.</t>
+        </is>
+      </c>
       <c r="X250" t="inlineStr"/>
       <c r="Y250" t="n">
         <v>1</v>
       </c>
       <c r="Z250" t="inlineStr"/>
-      <c r="AA250" t="inlineStr"/>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>(505) 265-7170</t>
+        </is>
+      </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>https://instagram.com/sowilo_artisan_jewelry, https://twitter.com/sowilo_jewelry, https://instagram.com/sowilo_artisan_jewelr, https://facebook.com/Sowilo-Artisan-Jewelry-790705241051708</t>
+          <t>https://facebook.com/oohaahalbuquerque, https://instagram.com/oohaahjewelry</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>The Diamond Reserve Denver</t>
+          <t>Portofino Jewelry &amp; Gems LTD</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>(303) 385-8449</t>
-        </is>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>hello@thediamondreserve.com</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr"/>
-      <c r="G251" t="inlineStr"/>
-      <c r="H251" t="inlineStr"/>
+          <t>(970) 949-1404</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jenny-hetei-b2112b10</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Jenny Hetei</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I251" s="2" t="inlineStr">
         <is>
-          <t>https://www.thediamondreserve.com</t>
+          <t>https://portofinojewelry.com</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Located in Fillmore Plaza, 100 Fillmore St #552, Denver, CO 80206, United States</t>
+          <t>240 Chapel Pl B117, Eagle, CO 81631</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Eagle</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -28419,71 +28423,63 @@
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O251" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P251" t="n">
-        <v>1127</v>
-      </c>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr"/>
+      <c r="P251" t="inlineStr"/>
       <c r="Q251" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/The+Diamond+Reserve+Denver/data=!4m7!3m6!1s0x876c7e977d1a8e6b:0x97af2573b585b30c!8m2!3d39.7186!4d-104.953081!16s%2Fg%2F113dvzskw!19sChIJa44afZd-bIcRDLOFtXMlr5c</t>
+          <t>https://www.bbb.org/us/co/eagle/profile/jewelry-stores/portofino-jewelry-gems-ltd-0805-46014741</t>
         </is>
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-2015</t>
+          <t>2 of 3, direct-line, custom-design, since-1998</t>
         </is>
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="T251" s="2" t="inlineStr">
-        <is>
-          <t>https://thediamondreserve.com/</t>
-        </is>
-      </c>
-      <c r="U251" t="inlineStr"/>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="T251" t="inlineStr"/>
+      <c r="U251" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Jenny+Hetei%22+Eagle+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V251" t="inlineStr">
         <is>
-          <t>2026-10-14T00:13:14+05:30</t>
-        </is>
-      </c>
-      <c r="W251" t="inlineStr">
-        <is>
-          <t>The Diamond Reserve</t>
-        </is>
-      </c>
+          <t>2026-10-14T04:00:40+05:30</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr"/>
       <c r="X251" t="inlineStr"/>
       <c r="Y251" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z251" t="inlineStr"/>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>(720) 667-1593, (737) 738-5223</t>
+          <t>(970) 676-6068</t>
         </is>
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>https://instagram.com/thediamondreserve, https://facebook.com/thediamondreserve, https://twitter.com/diamondreserve</t>
+          <t>https://facebook.com/jenhetei/reviews, https://facebook.com/jenhetei</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Williams Jewelers</t>
+          <t>Sowilo Artisan Jewelry</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -28493,18 +28489,22 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>(303) 761-9700</t>
+          <t>(303) 548-5467</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>ccn@williamsjewelers.net</t>
-        </is>
-      </c>
-      <c r="F252" t="inlineStr"/>
+          <t>sowilollc@gmail.com</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/bonnie-startek-5122141b3</t>
+        </is>
+      </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Steve Williams</t>
+          <t>Bonnie Startek</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -28514,17 +28514,17 @@
       </c>
       <c r="I252" s="2" t="inlineStr">
         <is>
-          <t>https://www.williamsdiamonds.com</t>
+          <t>https://sowiloartisanjewelry.com</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>5095 S Broadway, Englewood, CO 80113, United States</t>
+          <t>999 Vallejo St Unit 3, Studio 4K, Denver, CO 80204, United States</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>ENGLEWOOD</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -28546,140 +28546,124 @@
         <v>4.9</v>
       </c>
       <c r="P252" t="n">
-        <v>1625</v>
+        <v>60</v>
       </c>
       <c r="Q252" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Williams+Jewelers/data=!4m7!3m6!1s0x876c80563cc30911:0x2d1610a24c7c2752!8m2!3d39.624365!4d-104.9883621!16s%2Fg%2F1tftft9k!19sChIJEQnDPFaAbIcRUid8TKIQFi0</t>
+          <t>https://www.google.com/maps/place/Sowilo+Artisan+Jewelry/data=!4m7!3m6!1s0x876c7e540569644b:0xca2f5260ce1de685!8m2!3d39.7323841!4d-105.0133421!16s%2Fg%2F11c3s9631b!19sChIJS2RpBVR-bIcRheYdzmBSL8o</t>
         </is>
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, bench, custom-design, since-1969</t>
+          <t>2 of 3, custom-design, since-2003</t>
         </is>
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T252" s="2" t="inlineStr">
         <is>
-          <t>https://williamsjewelers.net/</t>
-        </is>
-      </c>
-      <c r="U252" t="inlineStr"/>
+          <t>https://sowiloartisanjewelry.com/</t>
+        </is>
+      </c>
+      <c r="U252" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Bonnie+Startek%22+Denver+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V252" t="inlineStr">
         <is>
-          <t>2026-10-14T00:18:37+05:30</t>
-        </is>
-      </c>
-      <c r="W252" t="inlineStr">
-        <is>
-          <t>Williams Jewelers of Cherry Creek North</t>
-        </is>
-      </c>
+          <t>2026-10-14T00:14:18+05:30</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr"/>
       <c r="X252" t="inlineStr"/>
       <c r="Y252" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z252" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
-      <c r="AA252" t="inlineStr">
-        <is>
-          <t>(720) 794-8111</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Z252" t="inlineStr"/>
+      <c r="AA252" t="inlineStr"/>
       <c r="AB252" t="inlineStr">
         <is>
-          <t>https://facebook.com/WilliamsJewelersEnglewood, https://instagram.com/williams.jewelers, https://facebook.com/WilliamsJewelersCherryCreek, https://instagram.com/williamsjewelersdenver, https://twitter.com/wjcherrycreek</t>
+          <t>https://instagram.com/sowilo_artisan_jewelry, https://twitter.com/sowilo_jewelry, https://instagram.com/sowilo_artisan_jewelr, https://facebook.com/Sowilo-Artisan-Jewelry-790705241051708</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Gold Works</t>
+          <t>The Diamond Reserve Denver</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers, Jewelry Designers</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>(703) 683-0333</t>
+          <t>(303) 385-8449</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>david@goldworksusa.com</t>
+          <t>hello@thediamondreserve.com</t>
         </is>
       </c>
       <c r="F253" t="inlineStr"/>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>David Martin</t>
-        </is>
-      </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>Featured On About Page</t>
-        </is>
-      </c>
+      <c r="G253" t="inlineStr"/>
+      <c r="H253" t="inlineStr"/>
       <c r="I253" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldworksusa.com</t>
+          <t>https://www.thediamondreserve.com</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>1400 King St, Alexandria, VA 22314</t>
+          <t>Located in Fillmore Plaza, 100 Fillmore St #552, Denver, CO 80206, United States</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>Alexandria</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O253" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P253" t="n">
-        <v>5</v>
+        <v>1127</v>
       </c>
       <c r="Q253" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/alexandria-va/mip/gold-works-3576887</t>
+          <t>https://www.google.com/maps/place/The+Diamond+Reserve+Denver/data=!4m7!3m6!1s0x876c7e977d1a8e6b:0x97af2573b585b30c!8m2!3d39.7186!4d-104.953081!16s%2Fg%2F113dvzskw!19sChIJa44afZd-bIcRDLOFtXMlr5c</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, ja, custom-design, since-1983</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-2015</t>
         </is>
       </c>
       <c r="S253" t="inlineStr">
@@ -28689,101 +28673,117 @@
       </c>
       <c r="T253" s="2" t="inlineStr">
         <is>
-          <t>https://goldworksusa.com/</t>
+          <t>https://thediamondreserve.com/</t>
         </is>
       </c>
       <c r="U253" t="inlineStr"/>
       <c r="V253" t="inlineStr">
         <is>
-          <t>2026-10-14T01:39:49+05:30</t>
-        </is>
-      </c>
-      <c r="W253" t="inlineStr"/>
+          <t>2026-10-14T00:13:14+05:30</t>
+        </is>
+      </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>The Diamond Reserve</t>
+        </is>
+      </c>
       <c r="X253" t="inlineStr"/>
       <c r="Y253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z253" t="inlineStr"/>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>(703) 216-6156</t>
+          <t>(720) 667-1593, (737) 738-5223</t>
         </is>
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>https://facebook.com/goldworksusa, https://instagram.com/goldworksusa, https://twitter.com/urgoldguy</t>
+          <t>https://instagram.com/thediamondreserve, https://facebook.com/thediamondreserve, https://twitter.com/diamondreserve</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Mervis</t>
+          <t>Williams Jewelers</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>shop=jewelry</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>(202) 293-0600</t>
+          <t>(303) 761-9700</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>concierge@mervisdiamond.com</t>
+          <t>ccn@williamsjewelers.net</t>
         </is>
       </c>
       <c r="F254" t="inlineStr"/>
-      <c r="G254" t="inlineStr"/>
-      <c r="H254" t="inlineStr"/>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Steve Williams</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I254" s="2" t="inlineStr">
         <is>
-          <t>https://www.mervisdiamond.com</t>
+          <t>https://www.williamsdiamonds.com</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>1700 K Street Northwest, Washington, DC 20006</t>
+          <t>5095 S Broadway, Englewood, CO 80113, United States</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>ENGLEWOOD</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>OpenStreetMap</t>
-        </is>
-      </c>
-      <c r="O254" t="inlineStr"/>
-      <c r="P254" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O254" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P254" t="n">
+        <v>1625</v>
+      </c>
       <c r="Q254" s="2" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/730833789</t>
+          <t>https://www.google.com/maps/place/Williams+Jewelers/data=!4m7!3m6!1s0x876c80563cc30911:0x2d1610a24c7c2752!8m2!3d39.624365!4d-104.9883621!16s%2Fg%2F1tftft9k!19sChIJEQnDPFaAbIcRUid8TKIQFi0</t>
         </is>
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, gia, custom-design</t>
+          <t>2 of 3, direct-line, bench, custom-design, since-1969</t>
         </is>
       </c>
       <c r="S254" t="inlineStr">
@@ -28793,74 +28793,90 @@
       </c>
       <c r="T254" s="2" t="inlineStr">
         <is>
-          <t>https://www.mervisdiamond.com/pages/contact/</t>
+          <t>https://williamsjewelers.net/</t>
         </is>
       </c>
       <c r="U254" t="inlineStr"/>
       <c r="V254" t="inlineStr">
         <is>
-          <t>2026-10-14T00:06:30+05:30</t>
-        </is>
-      </c>
-      <c r="W254" t="inlineStr"/>
+          <t>2026-10-14T00:18:37+05:30</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>Williams Jewelers of Cherry Creek North</t>
+        </is>
+      </c>
       <c r="X254" t="inlineStr"/>
       <c r="Y254" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z254" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>(301) 231-0030, (703) 448-9000</t>
+          <t>(720) 794-8111</t>
         </is>
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>https://instagram.com/mervisdiamond, https://facebook.com/mervisdiamonds, https://twitter.com/mervisdiamonds</t>
+          <t>https://facebook.com/WilliamsJewelersEnglewood, https://instagram.com/williams.jewelers, https://facebook.com/WilliamsJewelersCherryCreek, https://instagram.com/williamsjewelersdenver, https://twitter.com/wjcherrycreek</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Mystique Jewelers of Old Town Alexandria</t>
+          <t>Gold Works</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers, Jewelry Designers</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>(703) 836-1401</t>
+          <t>(703) 683-0333</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>mystique@mystiquejewelers.com</t>
+          <t>david@goldworksusa.com</t>
         </is>
       </c>
       <c r="F255" t="inlineStr"/>
-      <c r="G255" t="inlineStr"/>
-      <c r="H255" t="inlineStr"/>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>David Martin</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Featured On About Page</t>
+        </is>
+      </c>
       <c r="I255" s="2" t="inlineStr">
         <is>
-          <t>https://www.mystiquejewelers.com</t>
+          <t>https://www.goldworksusa.com</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>123 S Fairfax St, Alexandria, VA 22314, United States</t>
+          <t>1400 King St, Alexandria, VA 22314</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>Middleburg</t>
+          <t>Alexandria</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -28875,23 +28891,23 @@
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O255" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P255" t="n">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="Q255" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Mystique+Jewelers+of+Old+Town+Alexandria/data=!4m7!3m6!1s0x89b7b058c618240d:0xfb6ee0faa427cbad!8m2!3d38.8038272!4d-77.0427885!16s%2Fg%2F1262pbwr3!19sChIJDSQYxliwt4kRrcsnpPrgbvs</t>
+          <t>https://www.yellowpages.com/alexandria-va/mip/gold-works-3576887</t>
         </is>
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design</t>
+          <t>2 of 3, direct-line, gia, ja, custom-design, since-1983</t>
         </is>
       </c>
       <c r="S255" t="inlineStr">
@@ -28901,13 +28917,13 @@
       </c>
       <c r="T255" s="2" t="inlineStr">
         <is>
-          <t>https://www.mystiquejewelers.com/</t>
+          <t>https://goldworksusa.com/</t>
         </is>
       </c>
       <c r="U255" t="inlineStr"/>
       <c r="V255" t="inlineStr">
         <is>
-          <t>2026-10-14T00:29:13+05:30</t>
+          <t>2026-10-14T01:39:49+05:30</t>
         </is>
       </c>
       <c r="W255" t="inlineStr"/>
@@ -28918,39 +28934,39 @@
       <c r="Z255" t="inlineStr"/>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>(540) 454-7009, (540) 687-3100</t>
+          <t>(703) 216-6156</t>
         </is>
       </c>
       <c r="AB255" t="inlineStr">
         <is>
-          <t>https://facebook.com/mystique.jewelers, https://instagram.com/mystiquejewelers, https://x.com/MystiqueJewelry, https://twitter.com/MystiqueJewelry</t>
+          <t>https://facebook.com/goldworksusa, https://instagram.com/goldworksusa, https://twitter.com/urgoldguy</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Secrète Fine Jewelry</t>
+          <t>Mervis</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>shop=jewelry</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>(202) 588-7275</t>
+          <t>(202) 293-0600</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>contact@secrete.com</t>
+          <t>concierge@mervisdiamond.com</t>
         </is>
       </c>
       <c r="F256" t="inlineStr"/>
@@ -28958,12 +28974,12 @@
       <c r="H256" t="inlineStr"/>
       <c r="I256" s="2" t="inlineStr">
         <is>
-          <t>https://www.secrete.com</t>
+          <t>https://www.mervisdiamond.com</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>1607 Connecticut Ave NW, Washington, DC 20009, United States</t>
+          <t>1700 K Street Northwest, Washington, DC 20006</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -28983,23 +28999,19 @@
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O256" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="P256" t="n">
-        <v>256</v>
-      </c>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr"/>
+      <c r="P256" t="inlineStr"/>
       <c r="Q256" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Secr%C3%A8te+Fine+Jewelry/data=!4m7!3m6!1s0x89b7b7c61a67d5ed:0xb9e144573ac6af9!8m2!3d38.9115429!4d-77.0442796!16s%2Fg%2F1tz728l6!19sChIJ7dVnGsa3t4kR-Wqsc0UUngs</t>
+          <t>https://www.openstreetmap.org/node/730833789</t>
         </is>
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, gia, bench, custom-design</t>
+          <t>2 of 3, role-email, direct-line, gia, custom-design</t>
         </is>
       </c>
       <c r="S256" t="inlineStr">
@@ -29009,83 +29021,79 @@
       </c>
       <c r="T256" s="2" t="inlineStr">
         <is>
-          <t>https://www.secrete.com/</t>
+          <t>https://www.mervisdiamond.com/pages/contact/</t>
         </is>
       </c>
       <c r="U256" t="inlineStr"/>
       <c r="V256" t="inlineStr">
         <is>
-          <t>2026-10-14T00:23:44+05:30</t>
+          <t>2026-10-14T00:06:30+05:30</t>
         </is>
       </c>
       <c r="W256" t="inlineStr"/>
       <c r="X256" t="inlineStr"/>
       <c r="Y256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z256" t="inlineStr"/>
       <c r="AA256" t="inlineStr">
         <is>
-          <t>(301) 530-7892</t>
-        </is>
-      </c>
-      <c r="AB256" t="inlineStr"/>
+          <t>(301) 231-0030, (703) 448-9000</t>
+        </is>
+      </c>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>https://instagram.com/mervisdiamond, https://facebook.com/mervisdiamonds, https://twitter.com/mervisdiamonds</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>The Intrepid Wendell</t>
+          <t>Mystique Jewelers of Old Town Alexandria</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>(202) 735-5973</t>
+          <t>(703) 836-1401</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>wendell@theintrepidwendell.com</t>
+          <t>mystique@mystiquejewelers.com</t>
         </is>
       </c>
       <c r="F257" t="inlineStr"/>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>Daniel Boettcher</t>
-        </is>
-      </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="inlineStr"/>
       <c r="I257" s="2" t="inlineStr">
         <is>
-          <t>https://theintrepidwendell.com</t>
+          <t>https://www.mystiquejewelers.com</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>1401 K St NW Ste 688, Washington, DC 20005</t>
+          <t>123 S Fairfax St, Alexandria, VA 22314, United States</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Middleburg</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -29095,19 +29103,23 @@
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O257" t="inlineStr"/>
-      <c r="P257" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O257" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P257" t="n">
+        <v>150</v>
+      </c>
       <c r="Q257" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/washington-dc/mip/the-intrepid-wendell-525132651</t>
+          <t>https://www.google.com/maps/place/Mystique+Jewelers+of+Old+Town+Alexandria/data=!4m7!3m6!1s0x89b7b058c618240d:0xfb6ee0faa427cbad!8m2!3d38.8038272!4d-77.0427885!16s%2Fg%2F1262pbwr3!19sChIJDSQYxliwt4kRrcsnpPrgbvs</t>
         </is>
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design</t>
+          <t>2 of 3, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S257" t="inlineStr">
@@ -29117,13 +29129,13 @@
       </c>
       <c r="T257" s="2" t="inlineStr">
         <is>
-          <t>https://theintrepidwendell.com/</t>
+          <t>https://www.mystiquejewelers.com/</t>
         </is>
       </c>
       <c r="U257" t="inlineStr"/>
       <c r="V257" t="inlineStr">
         <is>
-          <t>2026-10-14T01:39:18+05:30</t>
+          <t>2026-10-14T00:29:13+05:30</t>
         </is>
       </c>
       <c r="W257" t="inlineStr"/>
@@ -29134,19 +29146,19 @@
       <c r="Z257" t="inlineStr"/>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>(202) 688-0545</t>
+          <t>(540) 454-7009, (540) 687-3100</t>
         </is>
       </c>
       <c r="AB257" t="inlineStr">
         <is>
-          <t>https://instagram.com/theintrepidwendell</t>
+          <t>https://facebook.com/mystique.jewelers, https://instagram.com/mystiquejewelers, https://x.com/MystiqueJewelry, https://twitter.com/MystiqueJewelry</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>WASHINGTON DIAMOND</t>
+          <t>Secrète Fine Jewelry</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -29156,46 +29168,42 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Jeweler</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>(703) 536-3600</t>
+          <t>(202) 588-7275</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>info@washingtondiamond.com</t>
-        </is>
-      </c>
-      <c r="F258" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/tomdaube</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>Tom Daube</t>
-        </is>
-      </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
+          <t>contact@secrete.com</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="inlineStr"/>
       <c r="I258" s="2" t="inlineStr">
         <is>
-          <t>https://www.washingtondiamond.com</t>
+          <t>https://www.secrete.com</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>1245 W Broad St, Falls Church, VA 22046, United States</t>
-        </is>
-      </c>
-      <c r="K258" t="inlineStr"/>
-      <c r="L258" t="inlineStr"/>
+          <t>1607 Connecticut Ave NW, Washington, DC 20009, United States</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
       <c r="M258" t="inlineStr">
         <is>
           <t>Washington, DC</t>
@@ -29207,58 +29215,54 @@
         </is>
       </c>
       <c r="O258" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="P258" t="n">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="Q258" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/WASHINGTON+DIAMOND/data=!4m7!3m6!1s0x89b7b4d23e29f109:0xab36956702e4de7c!8m2!3d38.8941055!4d-77.1900659!16s%2Fg%2F1tgnbhn7!19sChIJCfEpPtK0t4kRfN7kAmeVNqs</t>
+          <t>https://www.google.com/maps/place/Secr%C3%A8te+Fine+Jewelry/data=!4m7!3m6!1s0x89b7b7c61a67d5ed:0xb9e144573ac6af9!8m2!3d38.9115429!4d-77.0442796!16s%2Fg%2F1tz728l6!19sChIJ7dVnGsa3t4kR-Wqsc0UUngs</t>
         </is>
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, gia, bench, custom-design, since-1969</t>
+          <t>2 of 3, role-email, direct-line, gia, bench, custom-design</t>
         </is>
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="T258" s="2" t="inlineStr">
         <is>
-          <t>https://washingtondiamond.com/pages/contact-us</t>
-        </is>
-      </c>
-      <c r="U258" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=%22Tom+Daube%22+Washington+linkedin&amp;hl=en&amp;num=10</t>
-        </is>
-      </c>
+          <t>https://www.secrete.com/</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr"/>
       <c r="V258" t="inlineStr">
         <is>
-          <t>2026-10-14T00:28:26+05:30</t>
+          <t>2026-10-14T00:23:44+05:30</t>
         </is>
       </c>
       <c r="W258" t="inlineStr"/>
       <c r="X258" t="inlineStr"/>
       <c r="Y258" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z258" t="inlineStr"/>
-      <c r="AA258" t="inlineStr"/>
-      <c r="AB258" t="inlineStr">
-        <is>
-          <t>https://instagram.com/mywashingtondiamond, https://facebook.com/WashingtonDiamondVA</t>
-        </is>
-      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>(301) 530-7892</t>
+        </is>
+      </c>
+      <c r="AB258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Darakjian Jewelers</t>
+          <t>The Intrepid Wendell</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -29268,58 +29272,70 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>(833) 327-2554</t>
+          <t>(202) 735-5973</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>info@darakjian.com</t>
+          <t>wendell@theintrepidwendell.com</t>
         </is>
       </c>
       <c r="F259" t="inlineStr"/>
-      <c r="G259" t="inlineStr"/>
-      <c r="H259" t="inlineStr"/>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Daniel Boettcher</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="I259" s="2" t="inlineStr">
         <is>
-          <t>https://www.darakjian.com</t>
+          <t>https://theintrepidwendell.com</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>101 Willits St, Birmingham, MI 48009, United States</t>
-        </is>
-      </c>
-      <c r="K259" t="inlineStr"/>
-      <c r="L259" t="inlineStr"/>
+          <t>1401 K St NW Ste 688, Washington, DC 20005</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Detroit, MI</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O259" t="n">
-        <v>5</v>
-      </c>
-      <c r="P259" t="n">
-        <v>872</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr"/>
+      <c r="P259" t="inlineStr"/>
       <c r="Q259" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Darakjian+Jewelers/data=!4m7!3m6!1s0x8824c7070f5beda7:0xfeec85b71df22c68!8m2!3d42.5474214!4d-83.2162268!16s%2Fg%2F1ptxrxwft!19sChIJp-1bDwfHJIgRaCzyHbeF7P4</t>
+          <t>https://www.yellowpages.com/washington-dc/mip/the-intrepid-wendell-525132651</t>
         </is>
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, direct-line, gia, custom-design</t>
         </is>
       </c>
       <c r="S259" t="inlineStr">
@@ -29329,13 +29345,13 @@
       </c>
       <c r="T259" s="2" t="inlineStr">
         <is>
-          <t>https://www.darakjian.com/</t>
+          <t>https://theintrepidwendell.com/</t>
         </is>
       </c>
       <c r="U259" t="inlineStr"/>
       <c r="V259" t="inlineStr">
         <is>
-          <t>2026-10-14T00:35:35+05:30</t>
+          <t>2026-10-14T01:39:18+05:30</t>
         </is>
       </c>
       <c r="W259" t="inlineStr"/>
@@ -29343,22 +29359,22 @@
       <c r="Y259" t="n">
         <v>0</v>
       </c>
-      <c r="Z259" t="inlineStr">
-        <is>
-          <t>toll-free</t>
-        </is>
-      </c>
+      <c r="Z259" t="inlineStr"/>
       <c r="AA259" t="inlineStr">
         <is>
-          <t>(555) 555-5556</t>
-        </is>
-      </c>
-      <c r="AB259" t="inlineStr"/>
+          <t>(202) 688-0545</t>
+        </is>
+      </c>
+      <c r="AB259" t="inlineStr">
+        <is>
+          <t>https://instagram.com/theintrepidwendell</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Golden Sun Jewelry</t>
+          <t>WASHINGTON DIAMOND</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -29368,129 +29384,129 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jeweler</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>(248) 559-6289</t>
+          <t>(703) 536-3600</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>info@goldensunjewelry.com</t>
-        </is>
-      </c>
-      <c r="F260" t="inlineStr"/>
-      <c r="G260" t="inlineStr"/>
-      <c r="H260" t="inlineStr"/>
+          <t>info@washingtondiamond.com</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tomdaube</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Tom Daube</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
       <c r="I260" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldensunjewelry.com</t>
+          <t>https://www.washingtondiamond.com</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>23077 Greenfield Rd, Southfield, MI 48075</t>
-        </is>
-      </c>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t>Southfield</t>
-        </is>
-      </c>
-      <c r="L260" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
+          <t>1245 W Broad St, Falls Church, VA 22046, United States</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr"/>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Detroit, MI</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O260" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="P260" t="n">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="Q260" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/southfield-mi/mip/golden-sun-jewelry-460257159</t>
+          <t>https://www.google.com/maps/place/WASHINGTON+DIAMOND/data=!4m7!3m6!1s0x89b7b4d23e29f109:0xab36956702e4de7c!8m2!3d38.8941055!4d-77.1900659!16s%2Fg%2F1tgnbhn7!19sChIJCfEpPtK0t4kRfN7kAmeVNqs</t>
         </is>
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-1989</t>
+          <t>2 of 3, role-email, gia, bench, custom-design, since-1969</t>
         </is>
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T260" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldensunjewelry.com/contacts/</t>
-        </is>
-      </c>
-      <c r="U260" t="inlineStr"/>
+          <t>https://washingtondiamond.com/pages/contact-us</t>
+        </is>
+      </c>
+      <c r="U260" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Tom+Daube%22+Washington+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V260" t="inlineStr">
         <is>
-          <t>2026-10-14T01:41:10+05:30</t>
-        </is>
-      </c>
-      <c r="W260" t="inlineStr">
-        <is>
-          <t>Golden Sun Jewlery</t>
-        </is>
-      </c>
+          <t>2026-10-14T00:28:26+05:30</t>
+        </is>
+      </c>
+      <c r="W260" t="inlineStr"/>
       <c r="X260" t="inlineStr"/>
       <c r="Y260" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z260" t="inlineStr"/>
-      <c r="AA260" t="inlineStr">
-        <is>
-          <t>(248) 559-5142</t>
-        </is>
-      </c>
+      <c r="AA260" t="inlineStr"/>
       <c r="AB260" t="inlineStr">
         <is>
-          <t>https://facebook.com/GoldenSunJewelry, https://instagram.com/goldensunjewelry, https://twitter.com/GSJ_Southfield</t>
+          <t>https://instagram.com/mywashingtondiamond, https://facebook.com/WashingtonDiamondVA</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Herman's Creations Jewelers Inc.</t>
+          <t>Darakjian Jewelers</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Repairing, Diamond Setters</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>(586) 776-3200</t>
+          <t>(833) 327-2554</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>roseville@hermanscreations.com</t>
+          <t>info@darakjian.com</t>
         </is>
       </c>
       <c r="F261" t="inlineStr"/>
@@ -29498,24 +29514,16 @@
       <c r="H261" t="inlineStr"/>
       <c r="I261" s="2" t="inlineStr">
         <is>
-          <t>https://www.hermanscreations.com</t>
+          <t>https://www.darakjian.com</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>28885 Gratiot Ave, Roseville, MI 48066</t>
-        </is>
-      </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t>Roseville</t>
-        </is>
-      </c>
-      <c r="L261" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
+          <t>101 Willits St, Birmingham, MI 48009, United States</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
       <c r="M261" t="inlineStr">
         <is>
           <t>Detroit, MI</t>
@@ -29523,23 +29531,23 @@
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O261" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P261" t="n">
-        <v>8</v>
+        <v>872</v>
       </c>
       <c r="Q261" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/roseville-mi/mip/hermans-creations-jewelers-inc-6517282</t>
+          <t>https://www.google.com/maps/place/Darakjian+Jewelers/data=!4m7!3m6!1s0x8824c7070f5beda7:0xfeec85b71df22c68!8m2!3d42.5474214!4d-83.2162268!16s%2Fg%2F1ptxrxwft!19sChIJp-1bDwfHJIgRaCzyHbeF7P4</t>
         </is>
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, since-1974</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S261" t="inlineStr">
@@ -29549,44 +29557,36 @@
       </c>
       <c r="T261" s="2" t="inlineStr">
         <is>
-          <t>https://www.hermanscreations.com/</t>
+          <t>https://www.darakjian.com/</t>
         </is>
       </c>
       <c r="U261" t="inlineStr"/>
       <c r="V261" t="inlineStr">
         <is>
-          <t>2026-10-14T01:41:15+05:30</t>
-        </is>
-      </c>
-      <c r="W261" t="inlineStr">
-        <is>
-          <t>Herman's Creations Ltd, Herman's Creations Jewelers, Steve's Creations</t>
-        </is>
-      </c>
+          <t>2026-10-14T00:35:35+05:30</t>
+        </is>
+      </c>
+      <c r="W261" t="inlineStr"/>
       <c r="X261" t="inlineStr"/>
       <c r="Y261" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z261" t="inlineStr">
         <is>
-          <t>chain</t>
+          <t>toll-free</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
         <is>
-          <t>(248) 968-0519, (586) 776-3201</t>
-        </is>
-      </c>
-      <c r="AB261" t="inlineStr">
-        <is>
-          <t>https://instagram.com/hermans_creations, https://facebook.com/Hermans-Creations-Jewelers-East-122894551100621</t>
-        </is>
-      </c>
+          <t>(555) 555-5556</t>
+        </is>
+      </c>
+      <c r="AB261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>King Jewelers</t>
+          <t>Golden Sun Jewelry</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -29596,17 +29596,17 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Jeweler</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>(248) 569-0793</t>
+          <t>(248) 559-6289</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>u003einfo@kingjewelers.com</t>
+          <t>info@goldensunjewelry.com</t>
         </is>
       </c>
       <c r="F262" t="inlineStr"/>
@@ -29614,16 +29614,24 @@
       <c r="H262" t="inlineStr"/>
       <c r="I262" s="2" t="inlineStr">
         <is>
-          <t>https://www.kingjewelers.com</t>
+          <t>https://www.goldensunjewelry.com</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>23077 Greenfield Rd #300, Southfield, MI 48075, United States</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr"/>
-      <c r="L262" t="inlineStr"/>
+          <t>23077 Greenfield Rd, Southfield, MI 48075</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Southfield</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
       <c r="M262" t="inlineStr">
         <is>
           <t>Detroit, MI</t>
@@ -29631,23 +29639,23 @@
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O262" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="P262" t="n">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="Q262" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/King+Jewelers/data=!4m7!3m6!1s0x8824c904292cee05:0xc371fcb68753dfa!8m2!3d42.460125!4d-83.2020227!16s%2Fg%2F1thfg1m3!19sChIJBe4sKQTJJIgR-j11aMsfNww</t>
+          <t>https://www.yellowpages.com/southfield-mi/mip/golden-sun-jewelry-460257159</t>
         </is>
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-1989</t>
         </is>
       </c>
       <c r="S262" t="inlineStr">
@@ -29657,36 +29665,40 @@
       </c>
       <c r="T262" s="2" t="inlineStr">
         <is>
-          <t>https://kingjewelers.com/pages/contact-us</t>
+          <t>https://www.goldensunjewelry.com/contacts/</t>
         </is>
       </c>
       <c r="U262" t="inlineStr"/>
       <c r="V262" t="inlineStr">
         <is>
-          <t>2026-10-14T00:36:20+05:30</t>
-        </is>
-      </c>
-      <c r="W262" t="inlineStr"/>
+          <t>2026-10-14T01:41:10+05:30</t>
+        </is>
+      </c>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>Golden Sun Jewlery</t>
+        </is>
+      </c>
       <c r="X262" t="inlineStr"/>
       <c r="Y262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z262" t="inlineStr"/>
       <c r="AA262" t="inlineStr">
         <is>
-          <t>(615) 224-2902</t>
+          <t>(248) 559-5142</t>
         </is>
       </c>
       <c r="AB262" t="inlineStr">
         <is>
-          <t>https://facebook.com/kingjewelersnashville, https://instagram.com/kingjewelers, https://instagram.com/kingjewelers/</t>
+          <t>https://facebook.com/GoldenSunJewelry, https://instagram.com/goldensunjewelry, https://twitter.com/GSJ_Southfield</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>M J Diamonds</t>
+          <t>Herman's Creations Jewelers Inc.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -29696,17 +29708,17 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Jewelry Repairing, Diamond Setters</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>(248) 577-0077</t>
+          <t>(586) 776-3200</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>contactus@mjdiamonds.com</t>
+          <t>roseville@hermanscreations.com</t>
         </is>
       </c>
       <c r="F263" t="inlineStr"/>
@@ -29714,17 +29726,17 @@
       <c r="H263" t="inlineStr"/>
       <c r="I263" s="2" t="inlineStr">
         <is>
-          <t>https://mjdiamonds456072858.localsearch.com</t>
+          <t>https://www.hermanscreations.com</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>320 W 14 Mile Rd, Troy, MI 48083</t>
+          <t>28885 Gratiot Ave, Roseville, MI 48066</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>Troy</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -29743,19 +29755,19 @@
         </is>
       </c>
       <c r="O263" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P263" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q263" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/troy-mi/mip/m-j-diamonds-456072858</t>
+          <t>https://www.yellowpages.com/roseville-mi/mip/hermans-creations-jewelers-inc-6517282</t>
         </is>
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, bench, custom-design, since-1976</t>
+          <t>2 of 3, direct-line, since-1974</t>
         </is>
       </c>
       <c r="S263" t="inlineStr">
@@ -29765,56 +29777,64 @@
       </c>
       <c r="T263" s="2" t="inlineStr">
         <is>
-          <t>https://mjdiamonds.com/</t>
+          <t>https://www.hermanscreations.com/</t>
         </is>
       </c>
       <c r="U263" t="inlineStr"/>
       <c r="V263" t="inlineStr">
         <is>
-          <t>2026-10-14T01:41:26+05:30</t>
-        </is>
-      </c>
-      <c r="W263" t="inlineStr"/>
+          <t>2026-10-14T01:41:15+05:30</t>
+        </is>
+      </c>
+      <c r="W263" t="inlineStr">
+        <is>
+          <t>Herman's Creations Ltd, Herman's Creations Jewelers, Steve's Creations</t>
+        </is>
+      </c>
       <c r="X263" t="inlineStr"/>
       <c r="Y263" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z263" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA263" t="inlineStr">
         <is>
-          <t>(248) 956-1832, (248) 975-7894, (734) 462-7777, (734) 834-1155</t>
+          <t>(248) 968-0519, (586) 776-3201</t>
         </is>
       </c>
       <c r="AB263" t="inlineStr">
         <is>
-          <t>https://facebook.com/mjdiamonds, https://twitter.com/mj_diamonds, https://instagram.com/mjdiamonds</t>
+          <t>https://instagram.com/hermans_creations, https://facebook.com/Hermans-Creations-Jewelers-East-122894551100621</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Mac Enterprises</t>
+          <t>King Jewelers</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jeweler</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>(313) 846-4567</t>
+          <t>(248) 569-0793</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>brenda@macenterprisesinc.com</t>
+          <t>u003einfo@kingjewelers.com</t>
         </is>
       </c>
       <c r="F264" t="inlineStr"/>
@@ -29822,24 +29842,16 @@
       <c r="H264" t="inlineStr"/>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>https://www.macenterprisesinc.com</t>
+          <t>https://www.kingjewelers.com</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>5141 Schaefer Rd, Dearborn, MI 48126</t>
-        </is>
-      </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t>Dearborn</t>
-        </is>
-      </c>
-      <c r="L264" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
+          <t>23077 Greenfield Rd #300, Southfield, MI 48075, United States</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr"/>
       <c r="M264" t="inlineStr">
         <is>
           <t>Detroit, MI</t>
@@ -29847,19 +29859,23 @@
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O264" t="inlineStr"/>
-      <c r="P264" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O264" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P264" t="n">
+        <v>83</v>
+      </c>
       <c r="Q264" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/dearborn-mi/mip/mac-enterprises-461011700</t>
+          <t>https://www.google.com/maps/place/King+Jewelers/data=!4m7!3m6!1s0x8824c904292cee05:0xc371fcb68753dfa!8m2!3d42.460125!4d-83.2020227!16s%2Fg%2F1thfg1m3!19sChIJBe4sKQTJJIgR-j11aMsfNww</t>
         </is>
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, since-1982</t>
+          <t>2 of 3, direct-line, gia, custom-design</t>
         </is>
       </c>
       <c r="S264" t="inlineStr">
@@ -29869,13 +29885,13 @@
       </c>
       <c r="T264" s="2" t="inlineStr">
         <is>
-          <t>https://www.macenterprisesinc.com/contact</t>
+          <t>https://kingjewelers.com/pages/contact-us</t>
         </is>
       </c>
       <c r="U264" t="inlineStr"/>
       <c r="V264" t="inlineStr">
         <is>
-          <t>2026-10-14T01:40:32+05:30</t>
+          <t>2026-10-14T00:36:20+05:30</t>
         </is>
       </c>
       <c r="W264" t="inlineStr"/>
@@ -29886,65 +29902,57 @@
       <c r="Z264" t="inlineStr"/>
       <c r="AA264" t="inlineStr">
         <is>
-          <t>(907) 359-4090</t>
+          <t>(615) 224-2902</t>
         </is>
       </c>
       <c r="AB264" t="inlineStr">
         <is>
-          <t>https://facebook.com/wix, https://twitter.com/wix</t>
+          <t>https://facebook.com/kingjewelersnashville, https://instagram.com/kingjewelers, https://instagram.com/kingjewelers/</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Metals In Time</t>
+          <t>M J Diamonds</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Jewelry repair / goldsmith</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Jewelers, Watch Repair, Watches</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>(248) 582-9344</t>
+          <t>(248) 577-0077</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>jalexis@metalsintime.com</t>
+          <t>contactus@mjdiamonds.com</t>
         </is>
       </c>
       <c r="F265" t="inlineStr"/>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>Sergio Basmajian</t>
-        </is>
-      </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
+      <c r="G265" t="inlineStr"/>
+      <c r="H265" t="inlineStr"/>
       <c r="I265" s="2" t="inlineStr">
         <is>
-          <t>https://www.metalsintime.com</t>
+          <t>https://mjdiamonds456072858.localsearch.com</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>400 S Main St, Royal Oak, MI 48067</t>
+          <t>320 W 14 Mile Rd, Troy, MI 48083</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>Royal Oak</t>
+          <t>Troy</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -29963,19 +29971,19 @@
         </is>
       </c>
       <c r="O265" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P265" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q265" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/royal-oak-mi/mip/metals-in-time-473187148</t>
+          <t>https://www.yellowpages.com/troy-mi/mip/m-j-diamonds-456072858</t>
         </is>
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design</t>
+          <t>2 of 3, direct-line, bench, custom-design, since-1976</t>
         </is>
       </c>
       <c r="S265" t="inlineStr">
@@ -29985,64 +29993,56 @@
       </c>
       <c r="T265" s="2" t="inlineStr">
         <is>
-          <t>https://www.metalsintime.com/meet-the-team/</t>
+          <t>https://mjdiamonds.com/</t>
         </is>
       </c>
       <c r="U265" t="inlineStr"/>
       <c r="V265" t="inlineStr">
         <is>
-          <t>2026-10-14T01:40:59+05:30</t>
-        </is>
-      </c>
-      <c r="W265" t="inlineStr">
-        <is>
-          <t>Metal In Time</t>
-        </is>
-      </c>
+          <t>2026-10-14T01:41:26+05:30</t>
+        </is>
+      </c>
+      <c r="W265" t="inlineStr"/>
       <c r="X265" t="inlineStr"/>
       <c r="Y265" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z265" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Z265" t="inlineStr"/>
       <c r="AA265" t="inlineStr">
         <is>
-          <t>(248) 282-3733</t>
+          <t>(248) 956-1832, (248) 975-7894, (734) 462-7777, (734) 834-1155</t>
         </is>
       </c>
       <c r="AB265" t="inlineStr">
         <is>
-          <t>https://facebook.com/Metalsintime, https://instagram.com/Metalsintimejewelers</t>
+          <t>https://facebook.com/mjdiamonds, https://twitter.com/mj_diamonds, https://instagram.com/mjdiamonds</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Motif Jewelers</t>
+          <t>Mac Enterprises</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Designers, Jewelry Engravers</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>(734) 287-8300</t>
+          <t>(313) 846-4567</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>sales@motifjewelry.com</t>
+          <t>brenda@macenterprisesinc.com</t>
         </is>
       </c>
       <c r="F266" t="inlineStr"/>
@@ -30050,17 +30050,17 @@
       <c r="H266" t="inlineStr"/>
       <c r="I266" s="2" t="inlineStr">
         <is>
-          <t>https://motifjewelersmi.localsearch.com</t>
+          <t>https://www.macenterprisesinc.com</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>23000 Eureka Rd, Taylor, MI 48180</t>
+          <t>5141 Schaefer Rd, Dearborn, MI 48126</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Dearborn</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -30078,20 +30078,16 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O266" t="n">
-        <v>5</v>
-      </c>
-      <c r="P266" t="n">
-        <v>5</v>
-      </c>
+      <c r="O266" t="inlineStr"/>
+      <c r="P266" t="inlineStr"/>
       <c r="Q266" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/taylor-mi/mip/motif-jewelers-461726546</t>
+          <t>https://www.yellowpages.com/dearborn-mi/mip/mac-enterprises-461011700</t>
         </is>
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1983</t>
+          <t>2 of 3, direct-line, since-1982</t>
         </is>
       </c>
       <c r="S266" t="inlineStr">
@@ -30101,77 +30097,89 @@
       </c>
       <c r="T266" s="2" t="inlineStr">
         <is>
-          <t>https://motifjewelersmi.localsearch.com/</t>
+          <t>https://www.macenterprisesinc.com/contact</t>
         </is>
       </c>
       <c r="U266" t="inlineStr"/>
       <c r="V266" t="inlineStr">
         <is>
-          <t>2026-10-14T01:41:15+05:30</t>
-        </is>
-      </c>
-      <c r="W266" t="inlineStr">
-        <is>
-          <t>Motif Diamond Designs Inc</t>
-        </is>
-      </c>
+          <t>2026-10-14T01:40:32+05:30</t>
+        </is>
+      </c>
+      <c r="W266" t="inlineStr"/>
       <c r="X266" t="inlineStr"/>
       <c r="Y266" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z266" t="inlineStr"/>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>(248) 676-0721</t>
+          <t>(907) 359-4090</t>
         </is>
       </c>
       <c r="AB266" t="inlineStr">
         <is>
-          <t>https://facebook.com/MotifJewelry, https://instagram.com/motifjewelers, https://twitter.com/motifjewelers</t>
+          <t>https://facebook.com/wix, https://twitter.com/wix</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Radiant Made For Us</t>
+          <t>Metals In Time</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry repair / goldsmith</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers, Watch Repair, Watches</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>(313) 789-7480</t>
+          <t>(248) 582-9344</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>allenpark@radiantmadeforus.com</t>
+          <t>jalexis@metalsintime.com</t>
         </is>
       </c>
       <c r="F267" t="inlineStr"/>
-      <c r="G267" t="inlineStr"/>
-      <c r="H267" t="inlineStr"/>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Sergio Basmajian</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
       <c r="I267" s="2" t="inlineStr">
         <is>
-          <t>https://radiantmadeforus.com</t>
+          <t>https://www.metalsintime.com</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>6634 Allen Rd, Allen Park, MI 48101, United States</t>
-        </is>
-      </c>
-      <c r="K267" t="inlineStr"/>
-      <c r="L267" t="inlineStr"/>
+          <t>400 S Main St, Royal Oak, MI 48067</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Royal Oak</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
       <c r="M267" t="inlineStr">
         <is>
           <t>Detroit, MI</t>
@@ -30179,18 +30187,18 @@
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O267" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="P267" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="Q267" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Radiant+Made+For+Us/data=!4m7!3m6!1s0x883b374334f03ef5:0xea62d7eb1e5918df!8m2!3d42.2582463!4d-83.2094467!16s%2Fg%2F11y5nttj61!19sChIJ9T7wNEM3O4gR3xhZHuvXYuo</t>
+          <t>https://www.yellowpages.com/royal-oak-mi/mip/metals-in-time-473187148</t>
         </is>
       </c>
       <c r="R267" t="inlineStr">
@@ -30205,36 +30213,44 @@
       </c>
       <c r="T267" s="2" t="inlineStr">
         <is>
-          <t>https://radiantmadeforus.com/</t>
+          <t>https://www.metalsintime.com/meet-the-team/</t>
         </is>
       </c>
       <c r="U267" t="inlineStr"/>
       <c r="V267" t="inlineStr">
         <is>
-          <t>2026-10-14T00:40:08+05:30</t>
-        </is>
-      </c>
-      <c r="W267" t="inlineStr"/>
+          <t>2026-10-14T01:40:59+05:30</t>
+        </is>
+      </c>
+      <c r="W267" t="inlineStr">
+        <is>
+          <t>Metal In Time</t>
+        </is>
+      </c>
       <c r="X267" t="inlineStr"/>
       <c r="Y267" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z267" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Z267" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA267" t="inlineStr">
         <is>
-          <t>(646) 649-4493</t>
+          <t>(248) 282-3733</t>
         </is>
       </c>
       <c r="AB267" t="inlineStr">
         <is>
-          <t>https://facebook.com/radiantmadeforus, https://instagram.com/radiantmadeforus, https://facebook.com/madeforusdiamonds, https://instagram.com/madeforusdiamonds</t>
+          <t>https://facebook.com/Metalsintime, https://instagram.com/Metalsintimejewelers</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Rare Diamonds Inc</t>
+          <t>Motif Jewelers</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -30244,17 +30260,17 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Jewelry Designers, Jewelry Engravers</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>(313) 826-7042</t>
+          <t>(734) 287-8300</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>tony@rarediamond.com</t>
+          <t>sales@motifjewelry.com</t>
         </is>
       </c>
       <c r="F268" t="inlineStr"/>
@@ -30262,17 +30278,17 @@
       <c r="H268" t="inlineStr"/>
       <c r="I268" s="2" t="inlineStr">
         <is>
-          <t>https://rarediamond.com</t>
+          <t>https://motifjewelersmi.localsearch.com</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>2470 Collingwood St, Detroit, MI 48206</t>
+          <t>23000 Eureka Rd, Taylor, MI 48180</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -30290,16 +30306,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O268" t="inlineStr"/>
-      <c r="P268" t="inlineStr"/>
+      <c r="O268" t="n">
+        <v>5</v>
+      </c>
+      <c r="P268" t="n">
+        <v>5</v>
+      </c>
       <c r="Q268" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/detroit-mi/mip/rare-diamonds-inc-551567325</t>
+          <t>https://www.yellowpages.com/taylor-mi/mip/motif-jewelers-461726546</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design</t>
+          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1983</t>
         </is>
       </c>
       <c r="S268" t="inlineStr">
@@ -30309,36 +30329,40 @@
       </c>
       <c r="T268" s="2" t="inlineStr">
         <is>
-          <t>https://rarediamond.com/</t>
+          <t>https://motifjewelersmi.localsearch.com/</t>
         </is>
       </c>
       <c r="U268" t="inlineStr"/>
       <c r="V268" t="inlineStr">
         <is>
-          <t>2026-10-14T01:40:22+05:30</t>
-        </is>
-      </c>
-      <c r="W268" t="inlineStr"/>
+          <t>2026-10-14T01:41:15+05:30</t>
+        </is>
+      </c>
+      <c r="W268" t="inlineStr">
+        <is>
+          <t>Motif Diamond Designs Inc</t>
+        </is>
+      </c>
       <c r="X268" t="inlineStr"/>
       <c r="Y268" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z268" t="inlineStr"/>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>(310) 880-2982</t>
+          <t>(248) 676-0721</t>
         </is>
       </c>
       <c r="AB268" t="inlineStr">
         <is>
-          <t>https://instagram.com/rarediamond_official, https://facebook.com/profile.php?id=61568585367287, https://twitter.com/rarediamondusa</t>
+          <t>https://facebook.com/MotifJewelry, https://instagram.com/motifjewelers, https://twitter.com/motifjewelers</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Tapper's Jewelry</t>
+          <t>Radiant Made For Us</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -30353,45 +30377,29 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>(248) 932-7700</t>
+          <t>(313) 789-7480</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>sales@tappers.com</t>
+          <t>allenpark@radiantmadeforus.com</t>
         </is>
       </c>
       <c r="F269" t="inlineStr"/>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>Howard Tapper</t>
-        </is>
-      </c>
-      <c r="H269" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
+      <c r="G269" t="inlineStr"/>
+      <c r="H269" t="inlineStr"/>
       <c r="I269" s="2" t="inlineStr">
         <is>
-          <t>https://tappers.com</t>
+          <t>https://radiantmadeforus.com</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>6337 Orchard Lake Rd, West Bloomfield Township, MI 48322, United States</t>
-        </is>
-      </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t>West Bloomfield</t>
-        </is>
-      </c>
-      <c r="L269" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
+          <t>6634 Allen Rd, Allen Park, MI 48101, United States</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr"/>
       <c r="M269" t="inlineStr">
         <is>
           <t>Detroit, MI</t>
@@ -30406,16 +30414,16 @@
         <v>4.9</v>
       </c>
       <c r="P269" t="n">
-        <v>1036</v>
+        <v>21</v>
       </c>
       <c r="Q269" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Tapper%27s+Jewelry/data=!4m7!3m6!1s0x8824ba48855706cf:0xec468d469a462bbd!8m2!3d42.5457394!4d-83.359087!16s%2Fg%2F1v3_397b!19sChIJzwZXhUi6JIgRvStGmkaNRuw</t>
+          <t>https://www.google.com/maps/place/Radiant+Made+For+Us/data=!4m7!3m6!1s0x883b374334f03ef5:0xea62d7eb1e5918df!8m2!3d42.2582463!4d-83.2094467!16s%2Fg%2F11y5nttj61!19sChIJ9T7wNEM3O4gR3xhZHuvXYuo</t>
         </is>
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1977</t>
+          <t>2 of 3, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S269" t="inlineStr">
@@ -30425,13 +30433,13 @@
       </c>
       <c r="T269" s="2" t="inlineStr">
         <is>
-          <t>https://tappers.com/pages/contact</t>
+          <t>https://radiantmadeforus.com/</t>
         </is>
       </c>
       <c r="U269" t="inlineStr"/>
       <c r="V269" t="inlineStr">
         <is>
-          <t>2026-10-14T00:34:13+05:30</t>
+          <t>2026-10-14T00:40:08+05:30</t>
         </is>
       </c>
       <c r="W269" t="inlineStr"/>
@@ -30442,39 +30450,39 @@
       <c r="Z269" t="inlineStr"/>
       <c r="AA269" t="inlineStr">
         <is>
-          <t>(248) 465-1800, (248) 649-2000, (248) 862-9700</t>
+          <t>(646) 649-4493</t>
         </is>
       </c>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>https://instagram.com/TappersJewelry, https://facebook.com/TappersJewelry</t>
+          <t>https://facebook.com/radiantmadeforus, https://instagram.com/radiantmadeforus, https://facebook.com/madeforusdiamonds, https://instagram.com/madeforusdiamonds</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Fixology Jewelry, Watch, and Smartphone Repair</t>
+          <t>Rare Diamonds Inc</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Jewelry repair / goldsmith</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Electronics repair shop</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>(612) 330-9925</t>
+          <t>(313) 826-7042</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>bloomington@fixologyrepair.com</t>
+          <t>tony@rarediamond.com</t>
         </is>
       </c>
       <c r="F270" t="inlineStr"/>
@@ -30482,40 +30490,44 @@
       <c r="H270" t="inlineStr"/>
       <c r="I270" s="2" t="inlineStr">
         <is>
-          <t>https://fixologyrepair.com</t>
+          <t>https://rarediamond.com</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>651 Nicollet Mall #247, Minneapolis, MN 55402, United States</t>
-        </is>
-      </c>
-      <c r="K270" t="inlineStr"/>
-      <c r="L270" t="inlineStr"/>
+          <t>2470 Collingwood St, Detroit, MI 48206</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Detroit</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Minneapolis, MN</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O270" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P270" t="n">
-        <v>113</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr"/>
+      <c r="P270" t="inlineStr"/>
       <c r="Q270" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Fixology+Jewelry,+Watch,+and+Smartphone+Repair/data=!4m7!3m6!1s0x52b3329a741033cd:0x422f1e9528fd8f0a!8m2!3d44.9773754!4d-93.2709679!16s%2Fg%2F11bwndn4z4!19sChIJzTMQdJoys1IRCo_9KJUeL0I</t>
+          <t>https://www.yellowpages.com/detroit-mi/mip/rare-diamonds-inc-551567325</t>
         </is>
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S270" t="inlineStr">
@@ -30525,45 +30537,41 @@
       </c>
       <c r="T270" s="2" t="inlineStr">
         <is>
-          <t>https://fixologyrepair.com/contact/</t>
+          <t>https://rarediamond.com/</t>
         </is>
       </c>
       <c r="U270" t="inlineStr"/>
       <c r="V270" t="inlineStr">
         <is>
-          <t>2026-10-14T00:47:39+05:30</t>
-        </is>
-      </c>
-      <c r="W270" t="inlineStr">
-        <is>
-          <t>Fixology</t>
-        </is>
-      </c>
+          <t>2026-10-14T01:40:22+05:30</t>
+        </is>
+      </c>
+      <c r="W270" t="inlineStr"/>
       <c r="X270" t="inlineStr"/>
       <c r="Y270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z270" t="inlineStr"/>
       <c r="AA270" t="inlineStr">
         <is>
-          <t>(772) 692-3774</t>
+          <t>(310) 880-2982</t>
         </is>
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>https://facebook.com/fixologytoledo, https://facebook.com/fixologyMallofAmerica</t>
+          <t>https://instagram.com/rarediamond_official, https://facebook.com/profile.php?id=61568585367287, https://twitter.com/rarediamondusa</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>R.F. Moeller Jeweler</t>
+          <t>Tapper's Jewelry</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -30573,40 +30581,48 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>(651) 698-6321</t>
+          <t>(248) 932-7700</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>alexandra@rfmoeller.com</t>
+          <t>sales@tappers.com</t>
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
-      <c r="G271" t="inlineStr"/>
-      <c r="H271" t="inlineStr"/>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Howard Tapper</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="I271" s="2" t="inlineStr">
         <is>
-          <t>https://rfmoeller.com</t>
+          <t>https://tappers.com</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>2065 Ford Pkwy, St Paul, MN 55116, United States</t>
+          <t>6337 Orchard Lake Rd, West Bloomfield Township, MI 48322, United States</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>West Bloomfield</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Minneapolis, MN</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -30618,16 +30634,16 @@
         <v>4.9</v>
       </c>
       <c r="P271" t="n">
-        <v>2186</v>
+        <v>1036</v>
       </c>
       <c r="Q271" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/R.F.+Moeller+Jeweler/data=!4m7!3m6!1s0x87f62978048ef94d:0xea9c4d97c5c2b259!8m2!3d44.9181574!4d-93.1877644!16s%2Fg%2F1v7pz0rd!19sChIJTfmOBHgp9ocRWbLCxZdNnOo</t>
+          <t>https://www.google.com/maps/place/Tapper%27s+Jewelry/data=!4m7!3m6!1s0x8824ba48855706cf:0xec468d469a462bbd!8m2!3d42.5457394!4d-83.359087!16s%2Fg%2F1v3_397b!19sChIJzwZXhUi6JIgRvStGmkaNRuw</t>
         </is>
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, ags, custom-design, since-1951</t>
+          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1977</t>
         </is>
       </c>
       <c r="S271" t="inlineStr">
@@ -30637,56 +30653,56 @@
       </c>
       <c r="T271" s="2" t="inlineStr">
         <is>
-          <t>https://rfmoeller.com/</t>
+          <t>https://tappers.com/pages/contact</t>
         </is>
       </c>
       <c r="U271" t="inlineStr"/>
       <c r="V271" t="inlineStr">
         <is>
-          <t>2026-10-14T00:46:15+05:30</t>
+          <t>2026-10-14T00:34:13+05:30</t>
         </is>
       </c>
       <c r="W271" t="inlineStr"/>
       <c r="X271" t="inlineStr"/>
       <c r="Y271" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z271" t="inlineStr"/>
       <c r="AA271" t="inlineStr">
         <is>
-          <t>(651) 698-6322</t>
+          <t>(248) 465-1800, (248) 649-2000, (248) 862-9700</t>
         </is>
       </c>
       <c r="AB271" t="inlineStr">
         <is>
-          <t>https://facebook.com/rfmoellerjeweler, https://instagram.com/rfmoellerjeweler</t>
+          <t>https://instagram.com/TappersJewelry, https://facebook.com/TappersJewelry</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Bailey's Fine Jewelry</t>
+          <t>Fixology Jewelry, Watch, and Smartphone Repair</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry repair / goldsmith</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Electronics repair shop</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>(704) 332-1605</t>
+          <t>(612) 330-9925</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>carysubs@baileybox.com</t>
+          <t>bloomington@fixologyrepair.com</t>
         </is>
       </c>
       <c r="F272" t="inlineStr"/>
@@ -30694,27 +30710,19 @@
       <c r="H272" t="inlineStr"/>
       <c r="I272" s="2" t="inlineStr">
         <is>
-          <t>https://www.baileybox.com</t>
+          <t>https://fixologyrepair.com</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>705 Providence Rd, Charlotte, NC 28207, United States</t>
-        </is>
-      </c>
-      <c r="K272" t="inlineStr">
-        <is>
-          <t>Charlotte</t>
-        </is>
-      </c>
-      <c r="L272" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
+          <t>651 Nicollet Mall #247, Minneapolis, MN 55402, United States</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Charlotte, NC</t>
+          <t>Minneapolis, MN</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -30723,19 +30731,19 @@
         </is>
       </c>
       <c r="O272" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="P272" t="n">
-        <v>775</v>
+        <v>113</v>
       </c>
       <c r="Q272" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Bailey%27s+Fine+Jewelry/data=!4m7!3m6!1s0x88569fe931546195:0x4340ee15ce06892f!8m2!3d35.2006619!4d-80.8249664!16s%2Fg%2F1tlgynm1!19sChIJlWFUMemfVogRL4kGzhXuQEM</t>
+          <t>https://www.google.com/maps/place/Fixology+Jewelry,+Watch,+and+Smartphone+Repair/data=!4m7!3m6!1s0x52b3329a741033cd:0x422f1e9528fd8f0a!8m2!3d44.9773754!4d-93.2709679!16s%2Fg%2F11bwndn4z4!19sChIJzTMQdJoys1IRCo_9KJUeL0I</t>
         </is>
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, ags, bench, custom-design, since-1948</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S272" t="inlineStr">
@@ -30745,18 +30753,18 @@
       </c>
       <c r="T272" s="2" t="inlineStr">
         <is>
-          <t>https://baileybox.com/</t>
+          <t>https://fixologyrepair.com/contact/</t>
         </is>
       </c>
       <c r="U272" t="inlineStr"/>
       <c r="V272" t="inlineStr">
         <is>
-          <t>2026-10-14T00:51:23+05:30</t>
+          <t>2026-10-14T00:47:39+05:30</t>
         </is>
       </c>
       <c r="W272" t="inlineStr">
         <is>
-          <t>Morrison Smith Jewelers</t>
+          <t>Fixology</t>
         </is>
       </c>
       <c r="X272" t="inlineStr"/>
@@ -30766,19 +30774,19 @@
       <c r="Z272" t="inlineStr"/>
       <c r="AA272" t="inlineStr">
         <is>
-          <t>(252) 353-3434, (252) 443-7676, (919) 829-7337, (919) 892-3838</t>
+          <t>(772) 692-3774</t>
         </is>
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>https://facebook.com/BaileysFineJewelry, https://instagram.com/baileysfinejewelry, https://instagram.com/morrisonsmithjewelers, https://facebook.com/MorrisonSmithJewelers, https://x.com/morrisonsmith, https://twitter.com/morrisonsmith</t>
+          <t>https://facebook.com/fixologytoledo, https://facebook.com/fixologyMallofAmerica</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Fink's Jewelers</t>
+          <t>R.F. Moeller Jeweler</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -30788,74 +30796,66 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Jewelers, Fix-It Shops, Watches</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>(704) 366-3120</t>
+          <t>(651) 698-6321</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>ecommerce@finks.com</t>
+          <t>alexandra@rfmoeller.com</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>Nathan Fink</t>
-        </is>
-      </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
+      <c r="G273" t="inlineStr"/>
+      <c r="H273" t="inlineStr"/>
       <c r="I273" s="2" t="inlineStr">
         <is>
-          <t>https://www.finks.com</t>
+          <t>https://rfmoeller.com</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>4400 Sharon Rd Ste 199, Charlotte, NC 28211</t>
+          <t>2065 Ford Pkwy, St Paul, MN 55116, United States</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Charlotte, NC</t>
+          <t>Minneapolis, MN</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O273" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P273" t="n">
-        <v>1</v>
+        <v>2186</v>
       </c>
       <c r="Q273" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/charlotte-nc/mip/finks-jewelers-464773701</t>
+          <t>https://www.google.com/maps/place/R.F.+Moeller+Jeweler/data=!4m7!3m6!1s0x87f62978048ef94d:0xea9c4d97c5c2b259!8m2!3d44.9181574!4d-93.1877644!16s%2Fg%2F1v7pz0rd!19sChIJTfmOBHgp9ocRWbLCxZdNnOo</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design, since-1930</t>
+          <t>2 of 3, direct-line, ags, custom-design, since-1951</t>
         </is>
       </c>
       <c r="S273" t="inlineStr">
@@ -30865,49 +30865,41 @@
       </c>
       <c r="T273" s="2" t="inlineStr">
         <is>
-          <t>https://www.finks.com/</t>
+          <t>https://rfmoeller.com/</t>
         </is>
       </c>
       <c r="U273" t="inlineStr"/>
       <c r="V273" t="inlineStr">
         <is>
-          <t>2026-10-14T01:43:57+05:30</t>
-        </is>
-      </c>
-      <c r="W273" t="inlineStr">
-        <is>
-          <t>John Paul Fine Jewelry</t>
-        </is>
-      </c>
+          <t>2026-10-14T00:46:15+05:30</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr"/>
       <c r="X273" t="inlineStr"/>
       <c r="Y273" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z273" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="Z273" t="inlineStr"/>
       <c r="AA273" t="inlineStr">
         <is>
-          <t>(423) 894-1188, (540) 342-2991, (540) 344-8697, (615) 236-8176, (704) 927-4888, (757) 640-1132, (804) 377-8589, (919) 881-8247</t>
+          <t>(651) 698-6322</t>
         </is>
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>https://facebook.com/FinksJewelers, https://instagram.com/finksjewelers</t>
+          <t>https://facebook.com/rfmoellerjeweler, https://instagram.com/rfmoellerjeweler</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Windsor Jewelers</t>
+          <t>Bailey's Fine Jewelry</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -30917,43 +30909,35 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>(704) 556-7747</t>
+          <t>(704) 332-1605</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>nfo@windsor-jewelers.com</t>
+          <t>carysubs@baileybox.com</t>
         </is>
       </c>
       <c r="F274" t="inlineStr"/>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>Kevin Slusher</t>
-        </is>
-      </c>
-      <c r="H274" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
+      <c r="G274" t="inlineStr"/>
+      <c r="H274" t="inlineStr"/>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>https://www.windsor-jewelers.com</t>
+          <t>https://www.baileybox.com</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>6809-D Phillips Pl Ct, Charlotte, NC 28210, United States</t>
+          <t>705 Providence Rd, Charlotte, NC 28207, United States</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>Winston-Salem</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -30967,19 +30951,19 @@
         </is>
       </c>
       <c r="O274" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P274" t="n">
-        <v>1846</v>
+        <v>775</v>
       </c>
       <c r="Q274" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Windsor+Jewelers/data=!4m7!3m6!1s0x88569e13f91d1bb1:0x4b6448ed40c4d63c!8m2!3d35.1465046!4d-80.8269547!16s%2Fg%2F1tq8k7xj!19sChIJsRsd-ROeVogRPNbEQO1IZEs</t>
+          <t>https://www.google.com/maps/place/Bailey%27s+Fine+Jewelry/data=!4m7!3m6!1s0x88569fe931546195:0x4340ee15ce06892f!8m2!3d35.2006619!4d-80.8249664!16s%2Fg%2F1tlgynm1!19sChIJlWFUMemfVogRL4kGzhXuQEM</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design</t>
+          <t>2 of 3, direct-line, gia, ags, bench, custom-design, since-1948</t>
         </is>
       </c>
       <c r="S274" t="inlineStr">
@@ -30989,36 +30973,40 @@
       </c>
       <c r="T274" s="2" t="inlineStr">
         <is>
-          <t>https://www.windsor-jewelers.com/</t>
+          <t>https://baileybox.com/</t>
         </is>
       </c>
       <c r="U274" t="inlineStr"/>
       <c r="V274" t="inlineStr">
         <is>
-          <t>2026-10-14T00:51:17+05:30</t>
-        </is>
-      </c>
-      <c r="W274" t="inlineStr"/>
+          <t>2026-10-14T00:51:23+05:30</t>
+        </is>
+      </c>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>Morrison Smith Jewelers</t>
+        </is>
+      </c>
       <c r="X274" t="inlineStr"/>
       <c r="Y274" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z274" t="inlineStr"/>
       <c r="AA274" t="inlineStr">
         <is>
-          <t>(336) 721-1768</t>
+          <t>(252) 353-3434, (252) 443-7676, (919) 829-7337, (919) 892-3838</t>
         </is>
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>https://instagram.com/windsorjewelersnc/, https://facebook.com/OfficialWindsorJewelersNC</t>
+          <t>https://facebook.com/BaileysFineJewelry, https://instagram.com/baileysfinejewelry, https://instagram.com/morrisonsmithjewelers, https://facebook.com/MorrisonSmithJewelers, https://x.com/morrisonsmith, https://twitter.com/morrisonsmith</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Strings for Hope</t>
+          <t>Fink's Jewelers</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -31028,109 +31016,121 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers, Fix-It Shops, Watches</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>(615) 891-4323</t>
+          <t>(704) 366-3120</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>emily@stringsforhope.com</t>
-        </is>
-      </c>
-      <c r="F275" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/emily-winters-182b7a219</t>
-        </is>
-      </c>
+          <t>ecommerce@finks.com</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr"/>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Emily Winters</t>
+          <t>Nathan Fink</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>https://stringsforhope.com</t>
+          <t>https://www.finks.com</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>100 Taylor St, Nashville, TN 37208, United States</t>
-        </is>
-      </c>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
+          <t>4400 Sharon Rd Ste 199, Charlotte, NC 28211</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Nashville, TN</t>
+          <t>Charlotte, NC</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O275" t="n">
         <v>5</v>
       </c>
       <c r="P275" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="Q275" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Strings+for+Hope/data=!4m7!3m6!1s0x8864673b2485a245:0x7c5f1d365f1de575!8m2!3d36.1810664!4d-86.7859259!16s%2Fg%2F11p5x5j012!19sChIJRaKFJDtnZIgRdeUdXzYdX3w</t>
+          <t>https://www.yellowpages.com/charlotte-nc/mip/finks-jewelers-464773701</t>
         </is>
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>2 of 3, custom-design, since-2010</t>
+          <t>2 of 3, direct-line, custom-design, since-1930</t>
         </is>
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="T275" s="2" t="inlineStr">
         <is>
-          <t>https://stringsforhope.com/pages/about-us</t>
-        </is>
-      </c>
-      <c r="U275" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=%22Emily+Winters%22+Nashville+linkedin&amp;hl=en&amp;num=10</t>
-        </is>
-      </c>
+          <t>https://www.finks.com/</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr"/>
       <c r="V275" t="inlineStr">
         <is>
-          <t>2026-10-14T01:01:21+05:30</t>
-        </is>
-      </c>
-      <c r="W275" t="inlineStr"/>
+          <t>2026-10-14T01:43:57+05:30</t>
+        </is>
+      </c>
+      <c r="W275" t="inlineStr">
+        <is>
+          <t>John Paul Fine Jewelry</t>
+        </is>
+      </c>
       <c r="X275" t="inlineStr"/>
       <c r="Y275" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z275" t="inlineStr"/>
-      <c r="AA275" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="Z275" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>(423) 894-1188, (540) 342-2991, (540) 344-8697, (615) 236-8176, (704) 927-4888, (757) 640-1132, (804) 377-8589, (919) 881-8247</t>
+        </is>
+      </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>https://facebook.com/Stringsforhope, https://instagram.com/stringsforhope</t>
+          <t>https://facebook.com/FinksJewelers, https://instagram.com/finksjewelers</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Alltribes Indian Art</t>
+          <t>Windsor Jewelers</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -31140,70 +31140,74 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Jewelers, Native American Goods, Art Goods</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>(800) 417-0024</t>
+          <t>(704) 556-7747</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>admin@alltribes.com</t>
+          <t>nfo@windsor-jewelers.com</t>
         </is>
       </c>
       <c r="F276" t="inlineStr"/>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Richard Candy</t>
+          <t>Kevin Slusher</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>https://alltribes.com</t>
+          <t>https://www.windsor-jewelers.com</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>75 W Baseline Rd Ste 6, Gilbert, AZ 85233</t>
+          <t>6809-D Phillips Pl Ct, Charlotte, NC 28210, United States</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>Gilbert</t>
+          <t>Winston-Salem</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ</t>
+          <t>Charlotte, NC</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O276" t="inlineStr"/>
-      <c r="P276" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O276" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P276" t="n">
+        <v>1846</v>
+      </c>
       <c r="Q276" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/gilbert-az/mip/alltribes-indian-art-15755647</t>
+          <t>https://www.google.com/maps/place/Windsor+Jewelers/data=!4m7!3m6!1s0x88569e13f91d1bb1:0x4b6448ed40c4d63c!8m2!3d35.1465046!4d-80.8269547!16s%2Fg%2F1tq8k7xj!19sChIJsRsd-ROeVogRPNbEQO1IZEs</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S276" t="inlineStr">
@@ -31213,84 +31217,88 @@
       </c>
       <c r="T276" s="2" t="inlineStr">
         <is>
-          <t>https://alltribes.com/</t>
+          <t>https://www.windsor-jewelers.com/</t>
         </is>
       </c>
       <c r="U276" t="inlineStr"/>
       <c r="V276" t="inlineStr">
         <is>
-          <t>2026-10-14T01:46:53+05:30</t>
+          <t>2026-10-14T00:51:17+05:30</t>
         </is>
       </c>
       <c r="W276" t="inlineStr"/>
       <c r="X276" t="inlineStr"/>
       <c r="Y276" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z276" t="inlineStr">
-        <is>
-          <t>toll-free</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="Z276" t="inlineStr"/>
       <c r="AA276" t="inlineStr">
         <is>
-          <t>(480) 963-2284</t>
+          <t>(336) 721-1768</t>
         </is>
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>https://facebook.com/alltribes, https://instagram.com/alltribes_indian_art, https://facebook.com/pg/alltribes/videos/</t>
+          <t>https://instagram.com/windsorjewelersnc/, https://facebook.com/OfficialWindsorJewelersNC</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Diasparx</t>
+          <t>Strings for Hope</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Wholesale jeweler</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr"/>
+          <t>Jewelry store</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>(615) 891-4323</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>daniel@diasparx.com</t>
-        </is>
-      </c>
-      <c r="F277" t="inlineStr"/>
-      <c r="G277" t="inlineStr"/>
-      <c r="H277" t="inlineStr"/>
+          <t>emily@stringsforhope.com</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/emily-winters-182b7a219</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Emily Winters</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>https://www.diasparx.com</t>
+          <t>https://stringsforhope.com</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>Camelback Tower, 6900 E Camelback Rd Suite 1050, Scottsdale, AZ 85251, United States</t>
-        </is>
-      </c>
-      <c r="K277" t="inlineStr">
-        <is>
-          <t>Scottsdale</t>
-        </is>
-      </c>
-      <c r="L277" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
+          <t>100 Taylor St, Nashville, TN 37208, United States</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ</t>
+          <t>Nashville, TN</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -31302,32 +31310,36 @@
         <v>5</v>
       </c>
       <c r="P277" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q277" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Diasparx/data=!4m7!3m6!1s0x872b0b6df95ae9b9:0x57de2ae948b26574!8m2!3d33.5025864!4d-111.9322129!16s%2Fg%2F11x19r328p!19sChIJuela-W0LK4cRdGWySOkq3lc</t>
+          <t>https://www.google.com/maps/place/Strings+for+Hope/data=!4m7!3m6!1s0x8864673b2485a245:0x7c5f1d365f1de575!8m2!3d36.1810664!4d-86.7859259!16s%2Fg%2F11p5x5j012!19sChIJRaKFJDtnZIgRdeUdXzYdX3w</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design</t>
+          <t>2 of 3, custom-design, since-2010</t>
         </is>
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T277" s="2" t="inlineStr">
         <is>
-          <t>https://www.diasparx.com/</t>
-        </is>
-      </c>
-      <c r="U277" t="inlineStr"/>
+          <t>https://stringsforhope.com/pages/about-us</t>
+        </is>
+      </c>
+      <c r="U277" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Emily+Winters%22+Nashville+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V277" t="inlineStr">
         <is>
-          <t>2026-10-14T01:09:41+05:30</t>
+          <t>2026-10-14T01:01:21+05:30</t>
         </is>
       </c>
       <c r="W277" t="inlineStr"/>
@@ -31336,59 +31348,63 @@
         <v>0</v>
       </c>
       <c r="Z277" t="inlineStr"/>
-      <c r="AA277" t="inlineStr">
-        <is>
-          <t>(212) 555-0134, (480) 640-0948</t>
-        </is>
-      </c>
+      <c r="AA277" t="inlineStr"/>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>https://instagram.com/diasparx, https://facebook.com/profile.php?id=100088561748204</t>
+          <t>https://facebook.com/Stringsforhope, https://instagram.com/stringsforhope</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Expert Shoe Luggage Watch &amp; Jewelry Repair</t>
+          <t>Alltribes Indian Art</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Jewelry repair / goldsmith</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Shoe repair shop</t>
+          <t>Jewelers, Native American Goods, Art Goods</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>(480) 451-1214</t>
+          <t>(800) 417-0024</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>info@expertshoerepair.com</t>
+          <t>admin@alltribes.com</t>
         </is>
       </c>
       <c r="F278" t="inlineStr"/>
-      <c r="G278" t="inlineStr"/>
-      <c r="H278" t="inlineStr"/>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Richard Candy</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>https://expertslwjrepair.com</t>
+          <t>https://alltribes.com</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>10105 E Vía Linda Ste A- 105, Scottsdale, AZ 85258, United States</t>
+          <t>75 W Baseline Rd Ste 6, Gilbert, AZ 85233</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>Scottsdale</t>
+          <t>Gilbert</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -31403,23 +31419,19 @@
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O278" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P278" t="n">
-        <v>522</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr"/>
+      <c r="P278" t="inlineStr"/>
       <c r="Q278" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Expert+Shoe+Luggage+Watch+%26+Jewelry+Repair/data=!4m7!3m6!1s0x872b6d13c4a490a7:0x78beb810dbe170f!8m2!3d33.573104!4d-111.8634771!16s%2Fg%2F11hzvcxvl9!19sChIJp5CkxBNtK4cRDxe-DYHriwc</t>
+          <t>https://www.yellowpages.com/gilbert-az/mip/alltribes-indian-art-15755647</t>
         </is>
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, since-1960</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S278" t="inlineStr">
@@ -31429,56 +31441,56 @@
       </c>
       <c r="T278" s="2" t="inlineStr">
         <is>
-          <t>https://www.expertshoerepair.com/</t>
+          <t>https://alltribes.com/</t>
         </is>
       </c>
       <c r="U278" t="inlineStr"/>
       <c r="V278" t="inlineStr">
         <is>
-          <t>2026-10-14T01:10:03+05:30</t>
+          <t>2026-10-14T01:46:53+05:30</t>
         </is>
       </c>
       <c r="W278" t="inlineStr"/>
       <c r="X278" t="inlineStr"/>
       <c r="Y278" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z278" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Z278" t="inlineStr">
+        <is>
+          <t>toll-free</t>
+        </is>
+      </c>
       <c r="AA278" t="inlineStr">
         <is>
-          <t>(480) 269-7591</t>
+          <t>(480) 963-2284</t>
         </is>
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>https://facebook.com/expertshoerepair, https://instagram.com/expert_shoe_repair</t>
+          <t>https://facebook.com/alltribes, https://instagram.com/alltribes_indian_art, https://facebook.com/pg/alltribes/videos/</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Sunrise Jewelry &amp; Gallery</t>
+          <t>Diasparx</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>(480) 425-9944</t>
-        </is>
-      </c>
+          <t>Wholesale jeweler</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
-          <t>info@sunrisejewelryusa.com</t>
+          <t>daniel@diasparx.com</t>
         </is>
       </c>
       <c r="F279" t="inlineStr"/>
@@ -31486,12 +31498,12 @@
       <c r="H279" t="inlineStr"/>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>https://www.sunrisejewelryusa.com</t>
+          <t>https://www.diasparx.com</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>7254 E Main St Suite 101, Scottsdale, AZ 85251, United States</t>
+          <t>Camelback Tower, 6900 E Camelback Rd Suite 1050, Scottsdale, AZ 85251, United States</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
@@ -31518,16 +31530,16 @@
         <v>5</v>
       </c>
       <c r="P279" t="n">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="Q279" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Sunrise+Jewelry+%26+Gallery/data=!4m7!3m6!1s0x872b0bd689ab1b37:0xfa243a0d0a63c6b6!8m2!3d33.4932392!4d-111.9247178!16s%2Fg%2F11q1rmxn64!19sChIJNxuridYLK4cRtsZjCg06JPo</t>
+          <t>https://www.google.com/maps/place/Diasparx/data=!4m7!3m6!1s0x872b0b6df95ae9b9:0x57de2ae948b26574!8m2!3d33.5025864!4d-111.9322129!16s%2Fg%2F11x19r328p!19sChIJuela-W0LK4cRdGWySOkq3lc</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, since-2006</t>
+          <t>2 of 3, direct-line, gia, custom-design</t>
         </is>
       </c>
       <c r="S279" t="inlineStr">
@@ -31537,60 +31549,56 @@
       </c>
       <c r="T279" s="2" t="inlineStr">
         <is>
-          <t>https://sunrisejewelryusa.com/</t>
+          <t>https://www.diasparx.com/</t>
         </is>
       </c>
       <c r="U279" t="inlineStr"/>
       <c r="V279" t="inlineStr">
         <is>
-          <t>2026-10-14T01:05:57+05:30</t>
-        </is>
-      </c>
-      <c r="W279" t="inlineStr">
-        <is>
-          <t>Sunrise Trading Post</t>
-        </is>
-      </c>
+          <t>2026-10-14T01:09:41+05:30</t>
+        </is>
+      </c>
+      <c r="W279" t="inlineStr"/>
       <c r="X279" t="inlineStr"/>
       <c r="Y279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z279" t="inlineStr"/>
       <c r="AA279" t="inlineStr">
         <is>
-          <t>(480) 994-0170</t>
+          <t>(212) 555-0134, (480) 640-0948</t>
         </is>
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>https://instagram.com/sunrisejewelryandgallery, https://facebook.com/sunrisejewelryusa</t>
+          <t>https://instagram.com/diasparx, https://facebook.com/profile.php?id=100088561748204</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Exquisite Timepieces</t>
+          <t>Expert Shoe Luggage Watch &amp; Jewelry Repair</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Jewelry repair / goldsmith</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Jewelers, Watches</t>
+          <t>Shoe repair shop</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>(239) 227-2932</t>
+          <t>(480) 451-1214</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>team@exquisitetimepieces.com</t>
+          <t>info@expertshoerepair.com</t>
         </is>
       </c>
       <c r="F280" t="inlineStr"/>
@@ -31598,48 +31606,48 @@
       <c r="H280" t="inlineStr"/>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>https://www.exquisitetimepieces.com</t>
+          <t>https://expertslwjrepair.com</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>4380 Gulf Shore Blvd N, Naples, FL 34103</t>
+          <t>10105 E Vía Linda Ste A- 105, Scottsdale, AZ 85258, United States</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>Naples</t>
+          <t>Scottsdale</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Naples, FL</t>
+          <t>Scottsdale, AZ</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O280" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P280" t="n">
-        <v>31</v>
+        <v>522</v>
       </c>
       <c r="Q280" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/naples-fl/mip/exquisite-timepieces-14306847</t>
+          <t>https://www.google.com/maps/place/Expert+Shoe+Luggage+Watch+%26+Jewelry+Repair/data=!4m7!3m6!1s0x872b6d13c4a490a7:0x78beb810dbe170f!8m2!3d33.573104!4d-111.8634771!16s%2Fg%2F11hzvcxvl9!19sChIJp5CkxBNtK4cRDxe-DYHriwc</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, ja, since-1998</t>
+          <t>2 of 3, role-email, direct-line, since-1960</t>
         </is>
       </c>
       <c r="S280" t="inlineStr">
@@ -31649,36 +31657,36 @@
       </c>
       <c r="T280" s="2" t="inlineStr">
         <is>
-          <t>https://www.exquisitetimepieces.com/</t>
+          <t>https://www.expertshoerepair.com/</t>
         </is>
       </c>
       <c r="U280" t="inlineStr"/>
       <c r="V280" t="inlineStr">
         <is>
-          <t>2026-10-14T01:47:28+05:30</t>
+          <t>2026-10-14T01:10:03+05:30</t>
         </is>
       </c>
       <c r="W280" t="inlineStr"/>
       <c r="X280" t="inlineStr"/>
       <c r="Y280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z280" t="inlineStr"/>
       <c r="AA280" t="inlineStr">
         <is>
-          <t>(239) 262-4545</t>
+          <t>(480) 269-7591</t>
         </is>
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>https://facebook.com/pages/Exquisite-Timepieces/138888796144728, https://x.com/TimeExquisite, https://instagram.com/exquisitetimepieces, https://facebook.com/Exquisite-Timepieces-138888796144728, https://twitter.com/TimeExquisite</t>
+          <t>https://facebook.com/expertshoerepair, https://instagram.com/expert_shoe_repair</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Gold Silver Naples</t>
+          <t>Sunrise Jewelry &amp; Gallery</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -31688,17 +31696,17 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Gold dealer</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>(239) 591-5999</t>
+          <t>(480) 425-9944</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>goldsilvercoinsofnaples@gmail.com</t>
+          <t>info@sunrisejewelryusa.com</t>
         </is>
       </c>
       <c r="F281" t="inlineStr"/>
@@ -31706,19 +31714,27 @@
       <c r="H281" t="inlineStr"/>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldsilvernaples.com</t>
+          <t>https://www.sunrisejewelryusa.com</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>1575 Pine Ridge Rd Ste 20, Naples, FL 34109, United States</t>
-        </is>
-      </c>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
+          <t>7254 E Main St Suite 101, Scottsdale, AZ 85251, United States</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Scottsdale</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Naples, FL</t>
+          <t>Scottsdale, AZ</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -31727,19 +31743,19 @@
         </is>
       </c>
       <c r="O281" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="P281" t="n">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="Q281" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Gold+Silver+Naples/data=!4m7!3m6!1s0x88db1d7e5a7b7a49:0x324bd0e63a60dfad!8m2!3d26.2126153!4d-81.7867476!16s%2Fg%2F11k9ml4kb0!19sChIJSXp7Wn4d24gRrd9gOubQSzI</t>
+          <t>https://www.google.com/maps/place/Sunrise+Jewelry+%26+Gallery/data=!4m7!3m6!1s0x872b0bd689ab1b37:0xfa243a0d0a63c6b6!8m2!3d33.4932392!4d-111.9247178!16s%2Fg%2F11q1rmxn64!19sChIJNxuridYLK4cRtsZjCg06JPo</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, role-email, direct-line, since-2006</t>
         </is>
       </c>
       <c r="S281" t="inlineStr">
@@ -31749,32 +31765,40 @@
       </c>
       <c r="T281" s="2" t="inlineStr">
         <is>
-          <t>https://goldsilvernaples.com/</t>
+          <t>https://sunrisejewelryusa.com/</t>
         </is>
       </c>
       <c r="U281" t="inlineStr"/>
       <c r="V281" t="inlineStr">
         <is>
-          <t>2026-10-14T01:13:03+05:30</t>
-        </is>
-      </c>
-      <c r="W281" t="inlineStr"/>
+          <t>2026-10-14T01:05:57+05:30</t>
+        </is>
+      </c>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>Sunrise Trading Post</t>
+        </is>
+      </c>
       <c r="X281" t="inlineStr"/>
       <c r="Y281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z281" t="inlineStr"/>
       <c r="AA281" t="inlineStr">
         <is>
-          <t>(239) 234-9588</t>
-        </is>
-      </c>
-      <c r="AB281" t="inlineStr"/>
+          <t>(480) 994-0170</t>
+        </is>
+      </c>
+      <c r="AB281" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sunrisejewelryandgallery, https://facebook.com/sunrisejewelryusa</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>International Diamond Center</t>
+          <t>Exquisite Timepieces</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -31784,42 +31808,42 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers, Watches</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>(239) 342-2550</t>
+          <t>(239) 227-2932</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>u003emarketing@shopidc.com</t>
+          <t>team@exquisitetimepieces.com</t>
         </is>
       </c>
       <c r="F282" t="inlineStr"/>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>Keith Leclerc</t>
-        </is>
-      </c>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
+      <c r="G282" t="inlineStr"/>
+      <c r="H282" t="inlineStr"/>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>https://shopidc.com</t>
+          <t>https://www.exquisitetimepieces.com</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>8840 Tamiami Trl N, Naples, FL 34108, United States</t>
-        </is>
-      </c>
-      <c r="K282" t="inlineStr"/>
-      <c r="L282" t="inlineStr"/>
+          <t>4380 Gulf Shore Blvd N, Naples, FL 34103</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Naples</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
       <c r="M282" t="inlineStr">
         <is>
           <t>Naples, FL</t>
@@ -31827,23 +31851,23 @@
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O282" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P282" t="n">
-        <v>278</v>
+        <v>31</v>
       </c>
       <c r="Q282" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/International+Diamond+Center/data=!4m7!3m6!1s0x88db1f3b506da15f:0xd38690aae0aec00b!8m2!3d26.2479716!4d-81.800361!16s%2Fg%2F11t8h0cjn9!19sChIJX6FtUDsf24gRC8Cu4KqQhtM</t>
+          <t>https://www.yellowpages.com/naples-fl/mip/exquisite-timepieces-14306847</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design</t>
+          <t>2 of 3, role-email, direct-line, ja, since-1998</t>
         </is>
       </c>
       <c r="S282" t="inlineStr">
@@ -31853,56 +31877,56 @@
       </c>
       <c r="T282" s="2" t="inlineStr">
         <is>
-          <t>https://shopidc.com/</t>
+          <t>https://www.exquisitetimepieces.com/</t>
         </is>
       </c>
       <c r="U282" t="inlineStr"/>
       <c r="V282" t="inlineStr">
         <is>
-          <t>2026-10-14T01:15:46+05:30</t>
+          <t>2026-10-14T01:47:28+05:30</t>
         </is>
       </c>
       <c r="W282" t="inlineStr"/>
       <c r="X282" t="inlineStr"/>
       <c r="Y282" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z282" t="inlineStr"/>
       <c r="AA282" t="inlineStr">
         <is>
-          <t>(239) 364-1799, (352) 681-4550, (407) 770-5991, (407) 862-8990, (407) 903-9494, (727) 572-6323, (772) 408-4640, (813) 961-0097, (863) 226-4400, (912) 354-4344, (941) 278-3900</t>
+          <t>(239) 262-4545</t>
         </is>
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>https://facebook.com/internationaldiamondcenter, https://instagram.com/internationaldiamondcenter_, https://twitter.com/shopidc</t>
+          <t>https://facebook.com/pages/Exquisite-Timepieces/138888796144728, https://x.com/TimeExquisite, https://instagram.com/exquisitetimepieces, https://facebook.com/Exquisite-Timepieces-138888796144728, https://twitter.com/TimeExquisite</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Mark Loren Design</t>
+          <t>Gold Silver Naples</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Designers</t>
+          <t>Gold dealer</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>(239) 596-5820</t>
+          <t>(239) 591-5999</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>contact@marklorendesigns.com</t>
+          <t>goldsilvercoinsofnaples@gmail.com</t>
         </is>
       </c>
       <c r="F283" t="inlineStr"/>
@@ -31910,24 +31934,16 @@
       <c r="H283" t="inlineStr"/>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>https://www.marklorendesigns.com</t>
+          <t>https://www.goldsilvernaples.com</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>9118 Strada Pl Ste 8120, Naples, FL 34108</t>
-        </is>
-      </c>
-      <c r="K283" t="inlineStr">
-        <is>
-          <t>Naples</t>
-        </is>
-      </c>
-      <c r="L283" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
+          <t>1575 Pine Ridge Rd Ste 20, Naples, FL 34109, United States</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr"/>
       <c r="M283" t="inlineStr">
         <is>
           <t>Naples, FL</t>
@@ -31935,19 +31951,23 @@
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O283" t="inlineStr"/>
-      <c r="P283" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O283" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P283" t="n">
+        <v>75</v>
+      </c>
       <c r="Q283" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/naples-fl/mip/mark-loren-design-475273503</t>
+          <t>https://www.google.com/maps/place/Gold+Silver+Naples/data=!4m7!3m6!1s0x88db1d7e5a7b7a49:0x324bd0e63a60dfad!8m2!3d26.2126153!4d-81.7867476!16s%2Fg%2F11k9ml4kb0!19sChIJSXp7Wn4d24gRrd9gOubQSzI</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, bench, custom-design</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S283" t="inlineStr">
@@ -31957,13 +31977,13 @@
       </c>
       <c r="T283" s="2" t="inlineStr">
         <is>
-          <t>https://marklorendesigns.com/</t>
+          <t>https://goldsilvernaples.com/</t>
         </is>
       </c>
       <c r="U283" t="inlineStr"/>
       <c r="V283" t="inlineStr">
         <is>
-          <t>2026-10-14T01:47:36+05:30</t>
+          <t>2026-10-14T01:13:03+05:30</t>
         </is>
       </c>
       <c r="W283" t="inlineStr"/>
@@ -31974,67 +31994,63 @@
       <c r="Z283" t="inlineStr"/>
       <c r="AA283" t="inlineStr">
         <is>
-          <t>(239) 482-4664</t>
-        </is>
-      </c>
-      <c r="AB283" t="inlineStr">
-        <is>
-          <t>https://facebook.com/marklorendesigns, https://instagram.com/marklorendesign</t>
-        </is>
-      </c>
+          <t>(239) 234-9588</t>
+        </is>
+      </c>
+      <c r="AB283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Black Rock Galleries</t>
+          <t>International Diamond Center</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Estate liquidator</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>(203) 900-1110</t>
+          <t>(239) 342-2550</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>april@blackrockgalleries.com</t>
+          <t>u003emarketing@shopidc.com</t>
         </is>
       </c>
       <c r="F284" t="inlineStr"/>
-      <c r="G284" t="inlineStr"/>
-      <c r="H284" t="inlineStr"/>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Keith Leclerc</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>https://www.blackrockgalleries.com</t>
+          <t>https://shopidc.com</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>179 Hamilton Ave, Greenwich, CT 06830, United States</t>
-        </is>
-      </c>
-      <c r="K284" t="inlineStr">
-        <is>
-          <t>Cary</t>
-        </is>
-      </c>
-      <c r="L284" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
+          <t>8840 Tamiami Trl N, Naples, FL 34108, United States</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr"/>
+      <c r="L284" t="inlineStr"/>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Greenwich, CT</t>
+          <t>Naples, FL</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -32043,19 +32059,19 @@
         </is>
       </c>
       <c r="O284" t="n">
-        <v>2.7</v>
+        <v>4.9</v>
       </c>
       <c r="P284" t="n">
-        <v>25</v>
+        <v>278</v>
       </c>
       <c r="Q284" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Black+Rock+Galleries/data=!4m7!3m6!1s0x89c299cdad7d8901:0x806db5b713ec68d7!8m2!3d41.0179193!4d-73.6391571!16s%2Fg%2F11ckvlk1pv!19sChIJAYl9rc2ZwokR12jsE7e1bYA</t>
+          <t>https://www.google.com/maps/place/International+Diamond+Center/data=!4m7!3m6!1s0x88db1f3b506da15f:0xd38690aae0aec00b!8m2!3d26.2479716!4d-81.800361!16s%2Fg%2F11t8h0cjn9!19sChIJX6FtUDsf24gRC8Cu4KqQhtM</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia</t>
+          <t>2 of 3, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S284" t="inlineStr">
@@ -32065,56 +32081,56 @@
       </c>
       <c r="T284" s="2" t="inlineStr">
         <is>
-          <t>https://www.blackrockgalleries.com/contact</t>
+          <t>https://shopidc.com/</t>
         </is>
       </c>
       <c r="U284" t="inlineStr"/>
       <c r="V284" t="inlineStr">
         <is>
-          <t>2026-10-14T01:19:56+05:30</t>
+          <t>2026-10-14T01:15:46+05:30</t>
         </is>
       </c>
       <c r="W284" t="inlineStr"/>
       <c r="X284" t="inlineStr"/>
       <c r="Y284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z284" t="inlineStr"/>
       <c r="AA284" t="inlineStr">
         <is>
-          <t>(203) 335-0000, (203) 335-4444, (919) 702-7000</t>
+          <t>(239) 364-1799, (352) 681-4550, (407) 770-5991, (407) 862-8990, (407) 903-9494, (727) 572-6323, (772) 408-4640, (813) 961-0097, (863) 226-4400, (912) 354-4344, (941) 278-3900</t>
         </is>
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>https://facebook.com/blackrockgalleries, https://twitter.com/BRGalleries, https://instagram.com/blackrockgalleries</t>
+          <t>https://facebook.com/internationaldiamondcenter, https://instagram.com/internationaldiamondcenter_, https://twitter.com/shopidc</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Fine Elegant Jewelry</t>
+          <t>Mark Loren Design</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Jewelry Designers</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>(914) 937-2045</t>
+          <t>(239) 596-5820</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>elegantempirejewelers@gmail.com</t>
+          <t>contact@marklorendesigns.com</t>
         </is>
       </c>
       <c r="F285" t="inlineStr"/>
@@ -32122,27 +32138,27 @@
       <c r="H285" t="inlineStr"/>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>https://eejewelers.com</t>
+          <t>https://www.marklorendesigns.com</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>27 N Main St, Port Chester, NY 10573</t>
+          <t>9118 Strada Pl Ste 8120, Naples, FL 34108</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>Port Chester</t>
+          <t>Naples</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Greenwich, CT</t>
+          <t>Naples, FL</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -32150,20 +32166,16 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O285" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P285" t="n">
-        <v>115</v>
-      </c>
+      <c r="O285" t="inlineStr"/>
+      <c r="P285" t="inlineStr"/>
       <c r="Q285" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/port-chester-ny/mip/fine-elegant-jewelry-482445004</t>
+          <t>https://www.yellowpages.com/naples-fl/mip/mark-loren-design-475273503</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design</t>
+          <t>2 of 3, role-email, direct-line, bench, custom-design</t>
         </is>
       </c>
       <c r="S285" t="inlineStr">
@@ -32173,44 +32185,36 @@
       </c>
       <c r="T285" s="2" t="inlineStr">
         <is>
-          <t>https://eejewelers.com/</t>
+          <t>https://marklorendesigns.com/</t>
         </is>
       </c>
       <c r="U285" t="inlineStr"/>
       <c r="V285" t="inlineStr">
         <is>
-          <t>2026-10-14T01:48:10+05:30</t>
-        </is>
-      </c>
-      <c r="W285" t="inlineStr">
-        <is>
-          <t>Elegant Empire Jewelers</t>
-        </is>
-      </c>
+          <t>2026-10-14T01:47:36+05:30</t>
+        </is>
+      </c>
+      <c r="W285" t="inlineStr"/>
       <c r="X285" t="inlineStr"/>
       <c r="Y285" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z285" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z285" t="inlineStr"/>
       <c r="AA285" t="inlineStr">
         <is>
-          <t>(914) 305-3385</t>
+          <t>(239) 482-4664</t>
         </is>
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>https://instagram.com/eejewelers/, https://facebook.com/EEJewelers</t>
+          <t>https://facebook.com/marklorendesigns, https://instagram.com/marklorendesign</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Steven Fox Jewelry</t>
+          <t>Black Rock Galleries</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -32220,17 +32224,17 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Estate liquidator</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>(203) 344-5409</t>
+          <t>(203) 900-1110</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>concierge@stevenfoxjewelry.com</t>
+          <t>april@blackrockgalleries.com</t>
         </is>
       </c>
       <c r="F286" t="inlineStr"/>
@@ -32238,22 +32242,22 @@
       <c r="H286" t="inlineStr"/>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>https://www.stevenfoxjewelry.com</t>
+          <t>https://www.blackrockgalleries.com</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>8 Lewis St, Greenwich, CT 06830, United States</t>
+          <t>179 Hamilton Ave, Greenwich, CT 06830, United States</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>Greenwich</t>
+          <t>Cary</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -32267,19 +32271,19 @@
         </is>
       </c>
       <c r="O286" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="P286" t="n">
-        <v>277</v>
+        <v>25</v>
       </c>
       <c r="Q286" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Steven+Fox+Jewelry/data=!4m7!3m6!1s0x89c298489c931a41:0x67f0cb095f8447aa!8m2!3d41.0287029!4d-73.6255657!16s%2Fg%2F1thn6fp7!19sChIJQRqTnEiYwokRqkeEXwnL8Gc</t>
+          <t>https://www.google.com/maps/place/Black+Rock+Galleries/data=!4m7!3m6!1s0x89c299cdad7d8901:0x806db5b713ec68d7!8m2!3d41.0179193!4d-73.6391571!16s%2Fg%2F11ckvlk1pv!19sChIJAYl9rc2ZwokR12jsE7e1bYA</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, direct-line, gia</t>
         </is>
       </c>
       <c r="S286" t="inlineStr">
@@ -32289,36 +32293,36 @@
       </c>
       <c r="T286" s="2" t="inlineStr">
         <is>
-          <t>https://www.stevenfoxjewelry.com/</t>
+          <t>https://www.blackrockgalleries.com/contact</t>
         </is>
       </c>
       <c r="U286" t="inlineStr"/>
       <c r="V286" t="inlineStr">
         <is>
-          <t>2026-10-14T01:17:44+05:30</t>
+          <t>2026-10-14T01:19:56+05:30</t>
         </is>
       </c>
       <c r="W286" t="inlineStr"/>
       <c r="X286" t="inlineStr"/>
       <c r="Y286" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z286" t="inlineStr"/>
       <c r="AA286" t="inlineStr">
         <is>
-          <t>(203) 629-3303</t>
+          <t>(203) 335-0000, (203) 335-4444, (919) 702-7000</t>
         </is>
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>https://instagram.com/stevenfoxjewelry, https://facebook.com/stevenfoxjewelry</t>
+          <t>https://facebook.com/blackrockgalleries, https://twitter.com/BRGalleries, https://instagram.com/blackrockgalleries</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Triple G Fine Jewelry Inc</t>
+          <t>Fine Elegant Jewelry</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -32328,17 +32332,17 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>shop=jewelry</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>(914) 937-2931</t>
+          <t>(914) 937-2045</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>rakhmin20@icloud.com</t>
+          <t>elegantempirejewelers@gmail.com</t>
         </is>
       </c>
       <c r="F287" t="inlineStr"/>
@@ -32346,12 +32350,12 @@
       <c r="H287" t="inlineStr"/>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>https://triplegjewelry.rafaelsjewelrystore.com</t>
+          <t>https://eejewelers.com</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>38 South Main Street, Port Chester, NY 10573</t>
+          <t>27 N Main St, Port Chester, NY 10573</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
@@ -32371,23 +32375,23 @@
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>OpenStreetMap</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O287" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="P287" t="n">
-        <v>26</v>
+        <v>115</v>
       </c>
       <c r="Q287" s="2" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/10302134827</t>
+          <t>https://www.yellowpages.com/port-chester-ny/mip/fine-elegant-jewelry-482445004</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, direct-line, gia, custom-design</t>
         </is>
       </c>
       <c r="S287" t="inlineStr">
@@ -32397,23 +32401,23 @@
       </c>
       <c r="T287" s="2" t="inlineStr">
         <is>
-          <t>https://triplegjewelry.rafaelsjewelrystore.com/</t>
+          <t>https://eejewelers.com/</t>
         </is>
       </c>
       <c r="U287" t="inlineStr"/>
       <c r="V287" t="inlineStr">
         <is>
-          <t>2026-10-14T01:19:19+05:30</t>
+          <t>2026-10-14T01:48:10+05:30</t>
         </is>
       </c>
       <c r="W287" t="inlineStr">
         <is>
-          <t>Triple J Fine Jewelry Inc, Triple J Jew Jewelry</t>
+          <t>Elegant Empire Jewelers</t>
         </is>
       </c>
       <c r="X287" t="inlineStr"/>
       <c r="Y287" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z287" t="inlineStr">
         <is>
@@ -32422,20 +32426,24 @@
       </c>
       <c r="AA287" t="inlineStr">
         <is>
-          <t>(917) 535-4155</t>
-        </is>
-      </c>
-      <c r="AB287" t="inlineStr"/>
+          <t>(914) 305-3385</t>
+        </is>
+      </c>
+      <c r="AB287" t="inlineStr">
+        <is>
+          <t>https://instagram.com/eejewelers/, https://facebook.com/EEJewelers</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Arlex Jewelry Watches &amp; Clocks</t>
+          <t>Steven Fox Jewelry</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -32445,12 +32453,12 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>(561) 641-8162</t>
+          <t>(203) 344-5409</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>info@arlexjewelry.com</t>
+          <t>concierge@stevenfoxjewelry.com</t>
         </is>
       </c>
       <c r="F288" t="inlineStr"/>
@@ -32458,27 +32466,27 @@
       <c r="H288" t="inlineStr"/>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>https://arlexjewelry.com</t>
+          <t>https://www.stevenfoxjewelry.com</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>808 Lake Ave, Lake Worth Beach, FL 33460, United States</t>
+          <t>8 Lewis St, Greenwich, CT 06830, United States</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>Lake Worth Beach</t>
+          <t>Greenwich</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Palm Beach, FL</t>
+          <t>Greenwich, CT</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -32487,19 +32495,19 @@
         </is>
       </c>
       <c r="O288" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="P288" t="n">
-        <v>105</v>
+        <v>277</v>
       </c>
       <c r="Q288" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Arlex+Jewelry+Watches+%26+Clocks/data=!4m7!3m6!1s0x88d8d834517d5a4d:0x1255d4758f02268f!8m2!3d26.6160147!4d-80.0567684!16s%2Fg%2F1tkc2xb0!19sChIJTVp9UTTY2IgRjyYCj3XUVRI</t>
+          <t>https://www.google.com/maps/place/Steven+Fox+Jewelry/data=!4m7!3m6!1s0x89c298489c931a41:0x67f0cb095f8447aa!8m2!3d41.0287029!4d-73.6255657!16s%2Fg%2F1thn6fp7!19sChIJQRqTnEiYwokRqkeEXwnL8Gc</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-1987</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S288" t="inlineStr">
@@ -32509,64 +32517,56 @@
       </c>
       <c r="T288" s="2" t="inlineStr">
         <is>
-          <t>https://arlexjewelry.com/contact/</t>
+          <t>https://www.stevenfoxjewelry.com/</t>
         </is>
       </c>
       <c r="U288" t="inlineStr"/>
       <c r="V288" t="inlineStr">
         <is>
-          <t>2026-10-14T01:30:48+05:30</t>
-        </is>
-      </c>
-      <c r="W288" t="inlineStr">
-        <is>
-          <t>Arlex Jewelry Watches, Arlex Clocks, Arlex Jewelry &amp; Clocks</t>
-        </is>
-      </c>
+          <t>2026-10-14T01:17:44+05:30</t>
+        </is>
+      </c>
+      <c r="W288" t="inlineStr"/>
       <c r="X288" t="inlineStr"/>
       <c r="Y288" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z288" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Z288" t="inlineStr"/>
       <c r="AA288" t="inlineStr">
         <is>
-          <t>(561) 876-7030</t>
+          <t>(203) 629-3303</t>
         </is>
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>https://facebook.com/Arlex-Jewelry-Watches-Clocks-811607869050062, https://twitter.com/arlexclocks, https://instagram.com/arlexjewelry11, https://facebook.com/ArlexJewelry, https://twitter.com/ArlexClocks</t>
+          <t>https://instagram.com/stevenfoxjewelry, https://facebook.com/stevenfoxjewelry</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Gemstone Gallery</t>
+          <t>Triple G Fine Jewelry Inc</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Designers</t>
+          <t>shop=jewelry</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>(561) 586-8868</t>
+          <t>(914) 937-2931</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>info@mygemstonegallery.com</t>
+          <t>rakhmin20@icloud.com</t>
         </is>
       </c>
       <c r="F289" t="inlineStr"/>
@@ -32574,32 +32574,48 @@
       <c r="H289" t="inlineStr"/>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>https://www.mygemstonegallery.com</t>
-        </is>
-      </c>
-      <c r="J289" t="inlineStr"/>
-      <c r="K289" t="inlineStr"/>
-      <c r="L289" t="inlineStr"/>
+          <t>https://triplegjewelry.rafaelsjewelrystore.com</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>38 South Main Street, Port Chester, NY 10573</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Port Chester</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Palm Beach, FL</t>
+          <t>Greenwich, CT</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O289" t="inlineStr"/>
-      <c r="P289" t="inlineStr"/>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="O289" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P289" t="n">
+        <v>26</v>
+      </c>
       <c r="Q289" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/nationwide/mip/gemstone-gallery-451204537</t>
+          <t>https://www.openstreetmap.org/node/10302134827</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S289" t="inlineStr">
@@ -32609,40 +32625,40 @@
       </c>
       <c r="T289" s="2" t="inlineStr">
         <is>
-          <t>https://www.mygemstonegallery.com/</t>
+          <t>https://triplegjewelry.rafaelsjewelrystore.com/</t>
         </is>
       </c>
       <c r="U289" t="inlineStr"/>
       <c r="V289" t="inlineStr">
         <is>
-          <t>2026-10-14T01:50:22+05:30</t>
-        </is>
-      </c>
-      <c r="W289" t="inlineStr"/>
+          <t>2026-10-14T01:19:19+05:30</t>
+        </is>
+      </c>
+      <c r="W289" t="inlineStr">
+        <is>
+          <t>Triple J Fine Jewelry Inc, Triple J Jew Jewelry</t>
+        </is>
+      </c>
       <c r="X289" t="inlineStr"/>
       <c r="Y289" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z289" t="inlineStr">
         <is>
-          <t>no-address</t>
+          <t>chain</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
         <is>
-          <t>(917) 406-0779</t>
-        </is>
-      </c>
-      <c r="AB289" t="inlineStr">
-        <is>
-          <t>https://facebook.com/SuzanneHDeBow, https://twitter.com/GemstoneGallery, https://instagram.com/mygemstone_gallery</t>
-        </is>
-      </c>
+          <t>(917) 535-4155</t>
+        </is>
+      </c>
+      <c r="AB289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Hamilton Jewelers</t>
+          <t>Arlex Jewelry Watches &amp; Clocks</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -32652,17 +32668,17 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Jeweler</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>(561) 659-6788</t>
+          <t>(561) 641-8162</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>emartano@hamiltonjewelers.com</t>
+          <t>info@arlexjewelry.com</t>
         </is>
       </c>
       <c r="F290" t="inlineStr"/>
@@ -32670,17 +32686,17 @@
       <c r="H290" t="inlineStr"/>
       <c r="I290" s="2" t="inlineStr">
         <is>
-          <t>https://hamiltonjewelers.com</t>
+          <t>https://arlexjewelry.com</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>215 Worth Ave, Palm Beach, FL 33480, United States</t>
+          <t>808 Lake Ave, Lake Worth Beach, FL 33460, United States</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>Palm Beach Gardens</t>
+          <t>Lake Worth Beach</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -32699,19 +32715,19 @@
         </is>
       </c>
       <c r="O290" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="P290" t="n">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="Q290" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Hamilton+Jewelers/data=!4m7!3m6!1s0x88d8d6ec71416949:0x1f20ced2ff0489d1!8m2!3d26.7009363!4d-80.0371549!16s%2Fg%2F1tfz0xfv!19sChIJSWlBcezW2IgR0YkE_9LOIB8</t>
+          <t>https://www.google.com/maps/place/Arlex+Jewelry+Watches+%26+Clocks/data=!4m7!3m6!1s0x88d8d834517d5a4d:0x1255d4758f02268f!8m2!3d26.6160147!4d-80.0567684!16s%2Fg%2F1tkc2xb0!19sChIJTVp9UTTY2IgRjyYCj3XUVRI</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design, since-1912</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-1987</t>
         </is>
       </c>
       <c r="S290" t="inlineStr">
@@ -32721,36 +32737,44 @@
       </c>
       <c r="T290" s="2" t="inlineStr">
         <is>
-          <t>https://hamiltonjewelers.com/</t>
+          <t>https://arlexjewelry.com/contact/</t>
         </is>
       </c>
       <c r="U290" t="inlineStr"/>
       <c r="V290" t="inlineStr">
         <is>
-          <t>2026-10-14T01:25:01+05:30</t>
-        </is>
-      </c>
-      <c r="W290" t="inlineStr"/>
+          <t>2026-10-14T01:30:48+05:30</t>
+        </is>
+      </c>
+      <c r="W290" t="inlineStr">
+        <is>
+          <t>Arlex Jewelry Watches, Arlex Clocks, Arlex Jewelry &amp; Clocks</t>
+        </is>
+      </c>
       <c r="X290" t="inlineStr"/>
       <c r="Y290" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z290" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="Z290" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA290" t="inlineStr">
         <is>
-          <t>(609) 375-8003</t>
+          <t>(561) 876-7030</t>
         </is>
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>https://instagram.com/hamiltonjewelers, https://facebook.com/HamiltonJeweler</t>
+          <t>https://facebook.com/Arlex-Jewelry-Watches-Clocks-811607869050062, https://twitter.com/arlexclocks, https://instagram.com/arlexjewelry11, https://facebook.com/ArlexJewelry, https://twitter.com/ArlexClocks</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Raymond Lee Jewelers</t>
+          <t>Gemstone Gallery</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -32760,17 +32784,17 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Jewelry Designers</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>(561) 622-7744</t>
+          <t>(561) 586-8868</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>info@raymondleejewelers.net</t>
+          <t>info@mygemstonegallery.com</t>
         </is>
       </c>
       <c r="F291" t="inlineStr"/>
@@ -32778,24 +32802,12 @@
       <c r="H291" t="inlineStr"/>
       <c r="I291" s="2" t="inlineStr">
         <is>
-          <t>https://www.raymondleejewelers.net</t>
-        </is>
-      </c>
-      <c r="J291" t="inlineStr">
-        <is>
-          <t>500 Village Square Xing, Palm Beach Gardens, FL 33410</t>
-        </is>
-      </c>
-      <c r="K291" t="inlineStr">
-        <is>
-          <t>Palm Beach Gardens</t>
-        </is>
-      </c>
-      <c r="L291" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
+          <t>https://www.mygemstonegallery.com</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr"/>
+      <c r="K291" t="inlineStr"/>
+      <c r="L291" t="inlineStr"/>
       <c r="M291" t="inlineStr">
         <is>
           <t>Palm Beach, FL</t>
@@ -32810,12 +32822,12 @@
       <c r="P291" t="inlineStr"/>
       <c r="Q291" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/palm-beach-gardens-fl/mip/raymond-lee-jewelers-3693798</t>
+          <t>https://www.yellowpages.com/nationwide/mip/gemstone-gallery-451204537</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1983</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S291" t="inlineStr">
@@ -32825,36 +32837,40 @@
       </c>
       <c r="T291" s="2" t="inlineStr">
         <is>
-          <t>https://raymondleejewelers.net/pages/contact</t>
+          <t>https://www.mygemstonegallery.com/</t>
         </is>
       </c>
       <c r="U291" t="inlineStr"/>
       <c r="V291" t="inlineStr">
         <is>
-          <t>2026-10-14T01:50:37+05:30</t>
+          <t>2026-10-14T01:50:22+05:30</t>
         </is>
       </c>
       <c r="W291" t="inlineStr"/>
       <c r="X291" t="inlineStr"/>
       <c r="Y291" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z291" t="inlineStr">
         <is>
-          <t>chain</t>
+          <t>no-address</t>
         </is>
       </c>
       <c r="AA291" t="inlineStr">
         <is>
-          <t>(561) 750-7808</t>
-        </is>
-      </c>
-      <c r="AB291" t="inlineStr"/>
+          <t>(917) 406-0779</t>
+        </is>
+      </c>
+      <c r="AB291" t="inlineStr">
+        <is>
+          <t>https://facebook.com/SuzanneHDeBow, https://twitter.com/GemstoneGallery, https://instagram.com/mygemstone_gallery</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Signature Diamonds</t>
+          <t>Hamilton Jewelers</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -32864,17 +32880,17 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Jewelers, Diamonds</t>
+          <t>Jeweler</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>(561) 686-5730</t>
+          <t>(561) 659-6788</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>signaturebuyers@yahoo.com</t>
+          <t>emartano@hamiltonjewelers.com</t>
         </is>
       </c>
       <c r="F292" t="inlineStr"/>
@@ -32882,17 +32898,17 @@
       <c r="H292" t="inlineStr"/>
       <c r="I292" s="2" t="inlineStr">
         <is>
-          <t>https://sellyourdiamondsflorida.com</t>
+          <t>https://hamiltonjewelers.com</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>2200 N Florida Mango Rd, West Palm Beach, FL 33409</t>
+          <t>215 Worth Ave, Palm Beach, FL 33480, United States</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>West Palm Beach</t>
+          <t>Palm Beach Gardens</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -32907,19 +32923,23 @@
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O292" t="inlineStr"/>
-      <c r="P292" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O292" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P292" t="n">
+        <v>77</v>
+      </c>
       <c r="Q292" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/west-palm-beach-fl/mip/signature-diamonds-538406637</t>
+          <t>https://www.google.com/maps/place/Hamilton+Jewelers/data=!4m7!3m6!1s0x88d8d6ec71416949:0x1f20ced2ff0489d1!8m2!3d26.7009363!4d-80.0371549!16s%2Fg%2F1tfz0xfv!19sChIJSWlBcezW2IgR0YkE_9LOIB8</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design, since-1945</t>
+          <t>2 of 3, direct-line, gia, custom-design, since-1912</t>
         </is>
       </c>
       <c r="S292" t="inlineStr">
@@ -32929,56 +32949,56 @@
       </c>
       <c r="T292" s="2" t="inlineStr">
         <is>
-          <t>https://sellyourdiamondsflorida.com/</t>
+          <t>https://hamiltonjewelers.com/</t>
         </is>
       </c>
       <c r="U292" t="inlineStr"/>
       <c r="V292" t="inlineStr">
         <is>
-          <t>2026-10-14T01:50:22+05:30</t>
+          <t>2026-10-14T01:25:01+05:30</t>
         </is>
       </c>
       <c r="W292" t="inlineStr"/>
       <c r="X292" t="inlineStr"/>
       <c r="Y292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z292" t="inlineStr"/>
       <c r="AA292" t="inlineStr">
         <is>
-          <t>(772) 562-6893</t>
+          <t>(609) 375-8003</t>
         </is>
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>https://facebook.com/pages/Signature-Estate-Diamond-Buyers/699915383378286, https://twitter.com/signaturebuyer</t>
+          <t>https://instagram.com/hamiltonjewelers, https://facebook.com/HamiltonJeweler</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>YAFA Palm Beach</t>
+          <t>Raymond Lee Jewelers</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>(561) 331-8611</t>
+          <t>(561) 622-7744</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>inquire@yafajewelry.com</t>
+          <t>info@raymondleejewelers.net</t>
         </is>
       </c>
       <c r="F293" t="inlineStr"/>
@@ -32986,17 +33006,17 @@
       <c r="H293" t="inlineStr"/>
       <c r="I293" s="2" t="inlineStr">
         <is>
-          <t>https://yafasignedjewels.com</t>
+          <t>https://www.raymondleejewelers.net</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>234 Worth Ave, Palm Beach, FL 33480, United States</t>
+          <t>500 Village Square Xing, Palm Beach Gardens, FL 33410</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>Palm Beach</t>
+          <t>Palm Beach Gardens</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
@@ -33011,23 +33031,19 @@
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O293" t="n">
-        <v>5</v>
-      </c>
-      <c r="P293" t="n">
-        <v>9</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr"/>
+      <c r="P293" t="inlineStr"/>
       <c r="Q293" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/YAFA+Palm+Beach/data=!4m7!3m6!1s0x89c258fef868bda1:0x84b1b16f5ab524a9!8m2!3d26.7006755!4d-80.0378935!16s%2Fg%2F1td4l0sf!19sChIJob1o-P5YwokRqSS1Wm-xsYQ</t>
+          <t>https://www.yellowpages.com/palm-beach-gardens-fl/mip/raymond-lee-jewelers-3693798</t>
         </is>
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, since-1985</t>
+          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1983</t>
         </is>
       </c>
       <c r="S293" t="inlineStr">
@@ -33037,60 +33053,56 @@
       </c>
       <c r="T293" s="2" t="inlineStr">
         <is>
-          <t>https://yafasignedjewels.com/pages/contact</t>
+          <t>https://raymondleejewelers.net/pages/contact</t>
         </is>
       </c>
       <c r="U293" t="inlineStr"/>
       <c r="V293" t="inlineStr">
         <is>
-          <t>2026-10-14T01:26:21+05:30</t>
-        </is>
-      </c>
-      <c r="W293" t="inlineStr">
-        <is>
-          <t>Yafa Signed Jewels</t>
-        </is>
-      </c>
+          <t>2026-10-14T01:50:37+05:30</t>
+        </is>
+      </c>
+      <c r="W293" t="inlineStr"/>
       <c r="X293" t="inlineStr"/>
       <c r="Y293" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z293" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="Z293" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA293" t="inlineStr">
         <is>
-          <t>(212) 719-9828, (516) 331-8611</t>
-        </is>
-      </c>
-      <c r="AB293" t="inlineStr">
-        <is>
-          <t>https://facebook.com/YafaSignedJewels, https://instagram.com/yafasignedjewels</t>
-        </is>
-      </c>
+          <t>(561) 750-7808</t>
+        </is>
+      </c>
+      <c r="AB293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Gold Gods</t>
+          <t>Signature Diamonds</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Diamonds</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>(816) 721-9850</t>
+          <t>(561) 686-5730</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>support@thegoldgods.com</t>
+          <t>signaturebuyers@yahoo.com</t>
         </is>
       </c>
       <c r="F294" t="inlineStr"/>
@@ -33098,27 +33110,27 @@
       <c r="H294" t="inlineStr"/>
       <c r="I294" s="2" t="inlineStr">
         <is>
-          <t>https://thegoldgods.com</t>
+          <t>https://sellyourdiamondsflorida.com</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>450 N Fairfax Ave, Los Angeles, CA 90036</t>
+          <t>2200 N Florida Mango Rd, West Palm Beach, FL 33409</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>West Palm Beach</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Beverly Hills, CA</t>
+          <t>Palm Beach, FL</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -33130,12 +33142,12 @@
       <c r="P294" t="inlineStr"/>
       <c r="Q294" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/los-angeles-ca/mip/gold-gods-548160699</t>
+          <t>https://www.yellowpages.com/west-palm-beach-fl/mip/signature-diamonds-538406637</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, direct-line, gia, custom-design, since-1945</t>
         </is>
       </c>
       <c r="S294" t="inlineStr">
@@ -33145,13 +33157,13 @@
       </c>
       <c r="T294" s="2" t="inlineStr">
         <is>
-          <t>https://thegoldgods.com/pages/contact</t>
+          <t>https://sellyourdiamondsflorida.com/</t>
         </is>
       </c>
       <c r="U294" t="inlineStr"/>
       <c r="V294" t="inlineStr">
         <is>
-          <t>2026-10-14T01:52:07+05:30</t>
+          <t>2026-10-14T01:50:22+05:30</t>
         </is>
       </c>
       <c r="W294" t="inlineStr"/>
@@ -33162,15 +33174,19 @@
       <c r="Z294" t="inlineStr"/>
       <c r="AA294" t="inlineStr">
         <is>
-          <t>(816) 323-6447</t>
-        </is>
-      </c>
-      <c r="AB294" t="inlineStr"/>
+          <t>(772) 562-6893</t>
+        </is>
+      </c>
+      <c r="AB294" t="inlineStr">
+        <is>
+          <t>https://facebook.com/pages/Signature-Estate-Diamond-Buyers/699915383378286, https://twitter.com/signaturebuyer</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Golden State</t>
+          <t>YAFA Palm Beach</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -33180,17 +33196,17 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>(213) 629-2130</t>
+          <t>(561) 331-8611</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>sales@goldenstatejewelry.com</t>
+          <t>inquire@yafajewelry.com</t>
         </is>
       </c>
       <c r="F295" t="inlineStr"/>
@@ -33198,48 +33214,48 @@
       <c r="H295" t="inlineStr"/>
       <c r="I295" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldenstatejewelry.com</t>
+          <t>https://yafasignedjewels.com</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>550 S Hill St Ste 825, Los Angeles, CA 90013</t>
+          <t>234 Worth Ave, Palm Beach, FL 33480, United States</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Palm Beach</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Beverly Hills, CA</t>
+          <t>Palm Beach, FL</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O295" t="n">
         <v>5</v>
       </c>
       <c r="P295" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Q295" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/los-angeles-ca/mip/golden-state-467565356</t>
+          <t>https://www.google.com/maps/place/YAFA+Palm+Beach/data=!4m7!3m6!1s0x89c258fef868bda1:0x84b1b16f5ab524a9!8m2!3d26.7006755!4d-80.0378935!16s%2Fg%2F1td4l0sf!19sChIJob1o-P5YwokRqSS1Wm-xsYQ</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, bench, custom-design, since-1978</t>
+          <t>2 of 3, direct-line, since-1985</t>
         </is>
       </c>
       <c r="S295" t="inlineStr">
@@ -33249,49 +33265,45 @@
       </c>
       <c r="T295" s="2" t="inlineStr">
         <is>
-          <t>https://goldenstatejewelry.com/</t>
+          <t>https://yafasignedjewels.com/pages/contact</t>
         </is>
       </c>
       <c r="U295" t="inlineStr"/>
       <c r="V295" t="inlineStr">
         <is>
-          <t>2026-10-14T01:52:45+05:30</t>
+          <t>2026-10-14T01:26:21+05:30</t>
         </is>
       </c>
       <c r="W295" t="inlineStr">
         <is>
-          <t>Golden Star Jewelry</t>
-        </is>
-      </c>
-      <c r="X295" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
+          <t>Yafa Signed Jewels</t>
+        </is>
+      </c>
+      <c r="X295" t="inlineStr"/>
       <c r="Y295" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z295" t="inlineStr"/>
       <c r="AA295" t="inlineStr">
         <is>
-          <t>(213) 627-9677</t>
+          <t>(212) 719-9828, (516) 331-8611</t>
         </is>
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>https://instagram.com/goldenstatejewelryla</t>
+          <t>https://facebook.com/YafaSignedJewels, https://instagram.com/yafasignedjewels</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Hoorsenbuhs</t>
+          <t>Gold Gods</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -33301,12 +33313,12 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>(888) 692-2997</t>
+          <t>(816) 721-9850</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>info@hoorsenbuhs.com</t>
+          <t>support@thegoldgods.com</t>
         </is>
       </c>
       <c r="F296" t="inlineStr"/>
@@ -33314,17 +33326,17 @@
       <c r="H296" t="inlineStr"/>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>https://hoorsenbuhs.com</t>
+          <t>https://thegoldgods.com</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>2217 Main St, Santa Monica, CA 90405</t>
+          <t>450 N Fairfax Ave, Los Angeles, CA 90036</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
@@ -33346,12 +33358,12 @@
       <c r="P296" t="inlineStr"/>
       <c r="Q296" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/santa-monica-ca/mip/hoorsenbuhs-551622669</t>
+          <t>https://www.yellowpages.com/los-angeles-ca/mip/gold-gods-548160699</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S296" t="inlineStr">
@@ -33361,13 +33373,13 @@
       </c>
       <c r="T296" s="2" t="inlineStr">
         <is>
-          <t>https://hoorsenbuhs.com/</t>
+          <t>https://thegoldgods.com/pages/contact</t>
         </is>
       </c>
       <c r="U296" t="inlineStr"/>
       <c r="V296" t="inlineStr">
         <is>
-          <t>2026-10-14T01:53:36+05:30</t>
+          <t>2026-10-14T01:52:07+05:30</t>
         </is>
       </c>
       <c r="W296" t="inlineStr"/>
@@ -33375,26 +33387,18 @@
       <c r="Y296" t="n">
         <v>0</v>
       </c>
-      <c r="Z296" t="inlineStr">
-        <is>
-          <t>toll-free</t>
-        </is>
-      </c>
+      <c r="Z296" t="inlineStr"/>
       <c r="AA296" t="inlineStr">
         <is>
-          <t>(917) 206-9333</t>
-        </is>
-      </c>
-      <c r="AB296" t="inlineStr">
-        <is>
-          <t>https://instagram.com/hoorsenbuhs</t>
-        </is>
-      </c>
+          <t>(816) 323-6447</t>
+        </is>
+      </c>
+      <c r="AB296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Jennifer Fisher Jewelry</t>
+          <t>Golden State</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -33404,17 +33408,17 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>(424) 374-5303</t>
+          <t>(213) 629-2130</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>la@jenniferfisher.com</t>
+          <t>sales@goldenstatejewelry.com</t>
         </is>
       </c>
       <c r="F297" t="inlineStr"/>
@@ -33422,16 +33426,24 @@
       <c r="H297" t="inlineStr"/>
       <c r="I297" s="2" t="inlineStr">
         <is>
-          <t>https://jenniferfisher.com</t>
+          <t>https://www.goldenstatejewelry.com</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>363 N Beverly Dr, Beverly Hills, CA 90210, United States</t>
-        </is>
-      </c>
-      <c r="K297" t="inlineStr"/>
-      <c r="L297" t="inlineStr"/>
+          <t>550 S Hill St Ste 825, Los Angeles, CA 90013</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
       <c r="M297" t="inlineStr">
         <is>
           <t>Beverly Hills, CA</t>
@@ -33439,23 +33451,23 @@
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O297" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="P297" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="Q297" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Jennifer+Fisher+Jewelry/data=!4m7!3m6!1s0x80c2bdd6ed684985:0xb8fbea746e91ad05!8m2!3d34.0695438!4d-118.4019104!16s%2Fg%2F11n12hvwn5!19sChIJhUlo7da9woARBa2RbnTq-7g</t>
+          <t>https://www.yellowpages.com/los-angeles-ca/mip/golden-state-467565356</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, role-email, direct-line, bench, custom-design, since-1978</t>
         </is>
       </c>
       <c r="S297" t="inlineStr">
@@ -33465,36 +33477,44 @@
       </c>
       <c r="T297" s="2" t="inlineStr">
         <is>
-          <t>https://jenniferfisher.com/pages/stockists</t>
+          <t>https://goldenstatejewelry.com/</t>
         </is>
       </c>
       <c r="U297" t="inlineStr"/>
       <c r="V297" t="inlineStr">
         <is>
-          <t>2026-10-14T01:40:50+05:30</t>
-        </is>
-      </c>
-      <c r="W297" t="inlineStr"/>
-      <c r="X297" t="inlineStr"/>
+          <t>2026-10-14T01:52:45+05:30</t>
+        </is>
+      </c>
+      <c r="W297" t="inlineStr">
+        <is>
+          <t>Golden Star Jewelry</t>
+        </is>
+      </c>
+      <c r="X297" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
       <c r="Y297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z297" t="inlineStr"/>
       <c r="AA297" t="inlineStr">
         <is>
-          <t>(646) 366-9375</t>
+          <t>(213) 627-9677</t>
         </is>
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>https://instagram.com/jenniferfisherjewelry/, https://facebook.com/JenniferFisherJewelry, https://instagram.com/jenniferfisherjewelry</t>
+          <t>https://instagram.com/goldenstatejewelryla</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Jewelry &amp; Watch Buyers - Beverly Hills</t>
+          <t>Hoorsenbuhs</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -33504,17 +33524,17 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Jewelry buyer</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>(310) 697-8177</t>
+          <t>(888) 692-2997</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>info@watchbuyers.us</t>
+          <t>info@hoorsenbuhs.com</t>
         </is>
       </c>
       <c r="F298" t="inlineStr"/>
@@ -33522,16 +33542,24 @@
       <c r="H298" t="inlineStr"/>
       <c r="I298" s="2" t="inlineStr">
         <is>
-          <t>https://watchbuyers.us</t>
+          <t>https://hoorsenbuhs.com</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>468 N Camden Dr #205, Beverly Hills, CA 90210, United States</t>
-        </is>
-      </c>
-      <c r="K298" t="inlineStr"/>
-      <c r="L298" t="inlineStr"/>
+          <t>2217 Main St, Santa Monica, CA 90405</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Santa Monica</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
       <c r="M298" t="inlineStr">
         <is>
           <t>Beverly Hills, CA</t>
@@ -33539,18 +33567,14 @@
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O298" t="n">
-        <v>5</v>
-      </c>
-      <c r="P298" t="n">
-        <v>3</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr"/>
+      <c r="P298" t="inlineStr"/>
       <c r="Q298" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Jewelry+%26+Watch+Buyers+-+Beverly+Hills/data=!4m7!3m6!1s0x80c2bdbde9baacdb:0xbbce1c74141b63ce!8m2!3d34.0698858!4d-118.404944!16s%2Fg%2F11xt1px272!19sChIJ26y66b29woARzmMbFHQczrs</t>
+          <t>https://www.yellowpages.com/santa-monica-ca/mip/hoorsenbuhs-551622669</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
@@ -33565,13 +33589,13 @@
       </c>
       <c r="T298" s="2" t="inlineStr">
         <is>
-          <t>https://watchbuyers.us/</t>
+          <t>https://hoorsenbuhs.com/</t>
         </is>
       </c>
       <c r="U298" t="inlineStr"/>
       <c r="V298" t="inlineStr">
         <is>
-          <t>2026-10-14T01:40:58+05:30</t>
+          <t>2026-10-14T01:53:36+05:30</t>
         </is>
       </c>
       <c r="W298" t="inlineStr"/>
@@ -33579,23 +33603,31 @@
       <c r="Y298" t="n">
         <v>0</v>
       </c>
-      <c r="Z298" t="inlineStr"/>
+      <c r="Z298" t="inlineStr">
+        <is>
+          <t>toll-free</t>
+        </is>
+      </c>
       <c r="AA298" t="inlineStr">
         <is>
-          <t>(305) 989-9099, (646) 413-7757</t>
-        </is>
-      </c>
-      <c r="AB298" t="inlineStr"/>
+          <t>(917) 206-9333</t>
+        </is>
+      </c>
+      <c r="AB298" t="inlineStr">
+        <is>
+          <t>https://instagram.com/hoorsenbuhs</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Jewels Aficionado Beverly Hills</t>
+          <t>Jennifer Fisher Jewelry</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -33603,10 +33635,14 @@
           <t>Jewelry store</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>(424) 374-5303</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>sales@jewelsaficionado.com</t>
+          <t>la@jenniferfisher.com</t>
         </is>
       </c>
       <c r="F299" t="inlineStr"/>
@@ -33614,12 +33650,12 @@
       <c r="H299" t="inlineStr"/>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>https://jewelsaficionado.com</t>
+          <t>https://jenniferfisher.com</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>9850 Wilshire Blvd, Beverly Hills, CA 90210, United States</t>
+          <t>363 N Beverly Dr, Beverly Hills, CA 90210, United States</t>
         </is>
       </c>
       <c r="K299" t="inlineStr"/>
@@ -33634,16 +33670,20 @@
           <t>Google Maps</t>
         </is>
       </c>
-      <c r="O299" t="inlineStr"/>
-      <c r="P299" t="inlineStr"/>
+      <c r="O299" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P299" t="n">
+        <v>44</v>
+      </c>
       <c r="Q299" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Jewels+Aficionado+Beverly+Hills/data=!4m7!3m6!1s0x80c2bb445801322d:0x4ee3ff18cd9446bc!8m2!3d34.0666649!4d-118.4114543!16s%2Fg%2F11z2xf_27b!19sChIJLTIBWES7woARvEaUzRj_404</t>
+          <t>https://www.google.com/maps/place/Jennifer+Fisher+Jewelry/data=!4m7!3m6!1s0x80c2bdd6ed684985:0xb8fbea746e91ad05!8m2!3d34.0695438!4d-118.4019104!16s%2Fg%2F11n12hvwn5!19sChIJhUlo7da9woARBa2RbnTq-7g</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S299" t="inlineStr">
@@ -33653,13 +33693,13 @@
       </c>
       <c r="T299" s="2" t="inlineStr">
         <is>
-          <t>https://jewelsaficionado.com/</t>
+          <t>https://jenniferfisher.com/pages/stockists</t>
         </is>
       </c>
       <c r="U299" t="inlineStr"/>
       <c r="V299" t="inlineStr">
         <is>
-          <t>2026-10-14T01:42:22+05:30</t>
+          <t>2026-10-14T01:40:50+05:30</t>
         </is>
       </c>
       <c r="W299" t="inlineStr"/>
@@ -33670,19 +33710,19 @@
       <c r="Z299" t="inlineStr"/>
       <c r="AA299" t="inlineStr">
         <is>
-          <t>(212) 422-2600</t>
+          <t>(646) 366-9375</t>
         </is>
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>https://instagram.com/jewelsaficionado</t>
+          <t>https://instagram.com/jenniferfisherjewelry/, https://facebook.com/JenniferFisherJewelry, https://instagram.com/jenniferfisherjewelry</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Logan Hollowell Jewelry</t>
+          <t>Jewelry &amp; Watch Buyers - Beverly Hills</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -33692,17 +33732,17 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelry buyer</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>(323) 248-9685</t>
+          <t>(310) 697-8177</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>info@loganhollowell.com</t>
+          <t>info@watchbuyers.us</t>
         </is>
       </c>
       <c r="F300" t="inlineStr"/>
@@ -33710,12 +33750,12 @@
       <c r="H300" t="inlineStr"/>
       <c r="I300" s="2" t="inlineStr">
         <is>
-          <t>https://www.loganhollowell.com</t>
+          <t>https://watchbuyers.us</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>411 N Canon Dr, Beverly Hills, CA 90210, United States</t>
+          <t>468 N Camden Dr #205, Beverly Hills, CA 90210, United States</t>
         </is>
       </c>
       <c r="K300" t="inlineStr"/>
@@ -33734,16 +33774,16 @@
         <v>5</v>
       </c>
       <c r="P300" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q300" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Logan+Hollowell+Jewelry/data=!4m7!3m6!1s0x80c2bd39cbc0865f:0x202c691c8504a898!8m2!3d34.07073!4d-118.4012945!16s%2Fg%2F11njp9zjzq!19sChIJX4bAyzm9woARmKgEhRxpLCA</t>
+          <t>https://www.google.com/maps/place/Jewelry+%26+Watch+Buyers+-+Beverly+Hills/data=!4m7!3m6!1s0x80c2bdbde9baacdb:0xbbce1c74141b63ce!8m2!3d34.0698858!4d-118.404944!16s%2Fg%2F11xt1px272!19sChIJ26y66b29woARzmMbFHQczrs</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-2014</t>
+          <t>2 of 3, role-email, direct-line</t>
         </is>
       </c>
       <c r="S300" t="inlineStr">
@@ -33753,13 +33793,13 @@
       </c>
       <c r="T300" s="2" t="inlineStr">
         <is>
-          <t>https://loganhollowell.com/</t>
+          <t>https://watchbuyers.us/</t>
         </is>
       </c>
       <c r="U300" t="inlineStr"/>
       <c r="V300" t="inlineStr">
         <is>
-          <t>2026-10-14T01:41:31+05:30</t>
+          <t>2026-10-14T01:40:58+05:30</t>
         </is>
       </c>
       <c r="W300" t="inlineStr"/>
@@ -33770,19 +33810,15 @@
       <c r="Z300" t="inlineStr"/>
       <c r="AA300" t="inlineStr">
         <is>
-          <t>(323) 853-7844</t>
-        </is>
-      </c>
-      <c r="AB300" t="inlineStr">
-        <is>
-          <t>https://instagram.com/loganhollowell, https://facebook.com/loganhollowelljewelry</t>
-        </is>
-      </c>
+          <t>(305) 989-9099, (646) 413-7757</t>
+        </is>
+      </c>
+      <c r="AB300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Majestic Jewelry</t>
+          <t>Jewels Aficionado Beverly Hills</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -33792,17 +33828,13 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Jewelers</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>(323) 933-0288</t>
-        </is>
-      </c>
+          <t>Jewelry store</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr">
         <is>
-          <t>info@majesticjewelers.com</t>
+          <t>sales@jewelsaficionado.com</t>
         </is>
       </c>
       <c r="F301" t="inlineStr"/>
@@ -33810,24 +33842,16 @@
       <c r="H301" t="inlineStr"/>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>https://majesticjewelers.com</t>
+          <t>https://jewelsaficionado.com</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>6333 W 3rd St, Los Angeles, CA 90036</t>
-        </is>
-      </c>
-      <c r="K301" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="L301" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
+          <t>9850 Wilshire Blvd, Beverly Hills, CA 90210, United States</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr"/>
+      <c r="L301" t="inlineStr"/>
       <c r="M301" t="inlineStr">
         <is>
           <t>Beverly Hills, CA</t>
@@ -33835,23 +33859,19 @@
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O301" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P301" t="n">
-        <v>90</v>
-      </c>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr"/>
+      <c r="P301" t="inlineStr"/>
       <c r="Q301" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/los-angeles-ca/mip/majestic-jewelry-458143900</t>
+          <t>https://www.google.com/maps/place/Jewels+Aficionado+Beverly+Hills/data=!4m7!3m6!1s0x80c2bb445801322d:0x4ee3ff18cd9446bc!8m2!3d34.0666649!4d-118.4114543!16s%2Fg%2F11z2xf_27b!19sChIJLTIBWES7woARvEaUzRj_404</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-1986</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S301" t="inlineStr">
@@ -33861,44 +33881,36 @@
       </c>
       <c r="T301" s="2" t="inlineStr">
         <is>
-          <t>https://www.majesticjewelers.com/about-us/</t>
+          <t>https://jewelsaficionado.com/</t>
         </is>
       </c>
       <c r="U301" t="inlineStr"/>
       <c r="V301" t="inlineStr">
         <is>
-          <t>2026-10-14T01:52:20+05:30</t>
-        </is>
-      </c>
-      <c r="W301" t="inlineStr">
-        <is>
-          <t>Majestic W.J.</t>
-        </is>
-      </c>
-      <c r="X301" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
+          <t>2026-10-14T01:42:22+05:30</t>
+        </is>
+      </c>
+      <c r="W301" t="inlineStr"/>
+      <c r="X301" t="inlineStr"/>
       <c r="Y301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z301" t="inlineStr"/>
       <c r="AA301" t="inlineStr">
         <is>
-          <t>(407) 644-4824</t>
+          <t>(212) 422-2600</t>
         </is>
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>https://facebook.com/MajesticJewelersInc, https://instagram.com/majesticjewelerswp</t>
+          <t>https://instagram.com/jewelsaficionado</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Raven Fine Jewelers</t>
+          <t>Logan Hollowell Jewelry</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -33908,17 +33920,17 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>(310) 432-5234</t>
+          <t>(323) 248-9685</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>info@ravenjewelers.com</t>
+          <t>info@loganhollowell.com</t>
         </is>
       </c>
       <c r="F302" t="inlineStr"/>
@@ -33926,24 +33938,16 @@
       <c r="H302" t="inlineStr"/>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>https://ravenfinejewelers.localsearch.com</t>
+          <t>https://www.loganhollowell.com</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>8350 Wilshire Blvd, Beverly Hills, CA 90211</t>
-        </is>
-      </c>
-      <c r="K302" t="inlineStr">
-        <is>
-          <t>Beverly Hills</t>
-        </is>
-      </c>
-      <c r="L302" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
+          <t>411 N Canon Dr, Beverly Hills, CA 90210, United States</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr"/>
+      <c r="L302" t="inlineStr"/>
       <c r="M302" t="inlineStr">
         <is>
           <t>Beverly Hills, CA</t>
@@ -33951,7 +33955,7 @@
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O302" t="n">
@@ -33962,12 +33966,12 @@
       </c>
       <c r="Q302" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/beverly-hills-ca/mip/raven-fine-jewelers-531865762</t>
+          <t>https://www.google.com/maps/place/Logan+Hollowell+Jewelry/data=!4m7!3m6!1s0x80c2bd39cbc0865f:0x202c691c8504a898!8m2!3d34.07073!4d-118.4012945!16s%2Fg%2F11njp9zjzq!19sChIJX4bAyzm9woARmKgEhRxpLCA</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-2014</t>
         </is>
       </c>
       <c r="S302" t="inlineStr">
@@ -33977,56 +33981,56 @@
       </c>
       <c r="T302" s="2" t="inlineStr">
         <is>
-          <t>https://ravendiamonds.com/</t>
+          <t>https://loganhollowell.com/</t>
         </is>
       </c>
       <c r="U302" t="inlineStr"/>
       <c r="V302" t="inlineStr">
         <is>
-          <t>2026-10-14T01:51:20+05:30</t>
+          <t>2026-10-14T01:41:31+05:30</t>
         </is>
       </c>
       <c r="W302" t="inlineStr"/>
       <c r="X302" t="inlineStr"/>
       <c r="Y302" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z302" t="inlineStr"/>
       <c r="AA302" t="inlineStr">
         <is>
-          <t>(310) 887-1499</t>
+          <t>(323) 853-7844</t>
         </is>
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>https://instagram.com/ravenfinejewelers, https://facebook.com/RavenFineJewelers</t>
+          <t>https://instagram.com/loganhollowell, https://facebook.com/loganhollowelljewelry</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Sunset Plaza</t>
+          <t>Majestic Jewelry</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Jewelers, Watches, Real Estate Agents</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>(310) 652-7137</t>
+          <t>(323) 933-0288</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>info@sunsetplaza.com</t>
+          <t>info@majesticjewelers.com</t>
         </is>
       </c>
       <c r="F303" t="inlineStr"/>
@@ -34034,17 +34038,17 @@
       <c r="H303" t="inlineStr"/>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>https://www.sunsetplaza.com</t>
+          <t>https://majesticjewelers.com</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>8623 W Sunset Blvd, West Hollywood, CA 90069</t>
+          <t>6333 W 3rd St, Los Angeles, CA 90036</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>West Hollywood</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -34062,16 +34066,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O303" t="inlineStr"/>
-      <c r="P303" t="inlineStr"/>
+      <c r="O303" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P303" t="n">
+        <v>90</v>
+      </c>
       <c r="Q303" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/west-hollywood-ca/mip/sunset-plaza-1562237</t>
+          <t>https://www.yellowpages.com/los-angeles-ca/mip/majestic-jewelry-458143900</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, since-1924</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-1986</t>
         </is>
       </c>
       <c r="S303" t="inlineStr">
@@ -34081,81 +34089,89 @@
       </c>
       <c r="T303" s="2" t="inlineStr">
         <is>
-          <t>https://www.sunsetplaza.com/</t>
+          <t>https://www.majesticjewelers.com/about-us/</t>
         </is>
       </c>
       <c r="U303" t="inlineStr"/>
       <c r="V303" t="inlineStr">
         <is>
-          <t>2026-10-14T01:52:13+05:30</t>
-        </is>
-      </c>
-      <c r="W303" t="inlineStr"/>
-      <c r="X303" t="inlineStr"/>
+          <t>2026-10-14T01:52:20+05:30</t>
+        </is>
+      </c>
+      <c r="W303" t="inlineStr">
+        <is>
+          <t>Majestic W.J.</t>
+        </is>
+      </c>
+      <c r="X303" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
       <c r="Y303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z303" t="inlineStr"/>
       <c r="AA303" t="inlineStr">
         <is>
-          <t>(213) 500-3098, (213) 709-2282, (310) 210-0975, (310) 248-3750, (310) 274-1602, (310) 275-2222, (310) 289-1104, (310) 289-1105, (310) 360-6900, (310) 360-8889, (310) 424-3690, (310) 616-7888, (310) 652-2680, (310) 652-6844, (310) 652-7039, (310) 652-8886, (310) 657-2553, (310) 657-5070, (310) 657-5469, (310) 659-4411, (310) 659-9089, (310) 734-7296, (310) 786-7417, (310) 849-7185, (310) 854-0299, (310) 854-7700, (310) 855-8044, (323) 253-6747, (323) 345-4525, (323) 507-3943, (323) 650-0475, (323) 937-0355, (424) 407-4606, (424) 542-7730, (424) 667-0036, (424) 722-8502, (747) 724-3595</t>
+          <t>(407) 644-4824</t>
         </is>
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>https://instagram.com/affluette_, https://instagram.com/alchemy43, https://facebook.com/alchemy43, https://instagram.com/andreas.fashions, https://facebook.com/andreasfashions, https://instagram.com/bbcmcafe, https://instagram.com/bootstarusa, https://facebook.com/Boot-Star-106137407505929, https://instagram.com/bossanovarestaurant, https://facebook.com/BossaNovaLA, https://instagram.com/charliechoukair/, https://instagram.com/cristallini_official, https://facebook.com/CRISTALLINIOfficial, https://instagram.com/architectureforsale/, https://instagram.com/cupidlipsofbeverlyhills, https://facebook.com/profile.php?id=100083257576786, https://instagram.com/dandeutschoo, https://instagram.com/davidorgell, https://instagram.com/drybarshopsus, https://facebook.com/thedrybar, https://instagram.com/elainekimcollection/, https://instagram.com/entouragebarbershop, https://instagram.com/fpjourneofficial, https://instagram.com/guyfloralstudio, https://instagram.com/hotpilates, https://facebook.com/Hot-Pilates-1806940676211478, https://instagram.com/kojitoyodasalon, https://instagram.com/metaclinic/, https://instagram.com/milamoursiskincare, https://instagram.com/olehenriksenspa/, https://instagram.com/oliverpeoples, https://instagram.com/osklo.la, https://instagram.com/philippressjeweler, https://instagram.com/puravidamiami, https://facebook.com/PuraVidaMiami, https://instagram.com/queenbnailsalon_sunsetplaza, https://instagram.com/andywarholrevolvergallery, https://instagram.com/rondorff, https://instagram.com/saltiegirlla, https://instagram.com/samira13jewelry, https://instagram.com/sargondental, https://facebook.com/sargonlazarofdds, https://instagram.com/serenityonsunset, https://instagram.com/sheilaonsunset, https://instagram.com/solatesbysamantha, https://instagram.com/sousla_official, https://instagram.com/sunsetkidsla, https://instagram.com/theoppenheimgroup, https://facebook.com/theoppenheimgroup, https://instagram.com/whitegloveestates, https://instagram.com/xrcyze_ny, https://facebook.com/xrcycle, https://instagram.com/sunsetplazaca, https://facebook.com/SunsetPlazaCA</t>
+          <t>https://facebook.com/MajesticJewelersInc, https://instagram.com/majesticjewelerswp</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Westime Beverly Hills</t>
+          <t>Raven Fine Jewelers</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Watch store</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>(310) 888-8880</t>
+          <t>(310) 432-5234</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>contact@westime.com</t>
+          <t>info@ravenjewelers.com</t>
         </is>
       </c>
       <c r="F304" t="inlineStr"/>
-      <c r="G304" t="inlineStr">
-        <is>
-          <t>Greg Simonian</t>
-        </is>
-      </c>
-      <c r="H304" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
+      <c r="G304" t="inlineStr"/>
+      <c r="H304" t="inlineStr"/>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>https://westime.com</t>
+          <t>https://ravenfinejewelers.localsearch.com</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>206 N Rodeo Dr, Beverly Hills, CA 90210, United States</t>
-        </is>
-      </c>
-      <c r="K304" t="inlineStr"/>
-      <c r="L304" t="inlineStr"/>
+          <t>8350 Wilshire Blvd, Beverly Hills, CA 90211</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Beverly Hills</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
       <c r="M304" t="inlineStr">
         <is>
           <t>Beverly Hills, CA</t>
@@ -34163,23 +34179,23 @@
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O304" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P304" t="n">
-        <v>274</v>
+        <v>1</v>
       </c>
       <c r="Q304" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Westime+Beverly+Hills/data=!4m7!3m6!1s0x80c2bc0ed6429065:0x2c357ea8ffa51b1f!8m2!3d34.067375!4d-118.4003799!16s%2Fg%2F11cfj2mg2!19sChIJZZBC1g68woARHxul_6h-NSw</t>
+          <t>https://www.yellowpages.com/beverly-hills-ca/mip/raven-fine-jewelers-531865762</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-1987</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S304" t="inlineStr">
@@ -34189,56 +34205,56 @@
       </c>
       <c r="T304" s="2" t="inlineStr">
         <is>
-          <t>https://westime.com/contact</t>
+          <t>https://ravendiamonds.com/</t>
         </is>
       </c>
       <c r="U304" t="inlineStr"/>
       <c r="V304" t="inlineStr">
         <is>
-          <t>2026-10-14T01:39:33+05:30</t>
+          <t>2026-10-14T01:51:20+05:30</t>
         </is>
       </c>
       <c r="W304" t="inlineStr"/>
       <c r="X304" t="inlineStr"/>
       <c r="Y304" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z304" t="inlineStr"/>
       <c r="AA304" t="inlineStr">
         <is>
-          <t>(786) 347-5353, (858) 459-2222</t>
+          <t>(310) 887-1499</t>
         </is>
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>https://instagram.com/westimewatches, https://facebook.com/Westime</t>
+          <t>https://instagram.com/ravenfinejewelers, https://facebook.com/RavenFineJewelers</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Wrist Aficionado Beverly Hills</t>
+          <t>Sunset Plaza</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Watch store</t>
+          <t>Jewelers, Watches, Real Estate Agents</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>(310) 388-8201</t>
+          <t>(310) 652-7137</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>sales@wristaficionado.com</t>
+          <t>info@sunsetplaza.com</t>
         </is>
       </c>
       <c r="F305" t="inlineStr"/>
@@ -34246,17 +34262,17 @@
       <c r="H305" t="inlineStr"/>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>https://wristaficionado.com</t>
+          <t>https://www.sunsetplaza.com</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>9850 Wilshire Blvd, Beverly Hills, CA 90210, United States</t>
+          <t>8623 W Sunset Blvd, West Hollywood, CA 90069</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>Beverly Hills</t>
+          <t>West Hollywood</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -34271,23 +34287,19 @@
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O305" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P305" t="n">
-        <v>101</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr"/>
+      <c r="P305" t="inlineStr"/>
       <c r="Q305" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Wrist+Aficionado+Beverly+Hills/data=!4m7!3m6!1s0x80c2bb67e5181fcf:0xde9cbdbb118a155c!8m2!3d34.0667288!4d-118.4113018!16s%2Fg%2F11v12tg_x0!19sChIJzx8Y5We7woARXBWKEbu9nN4</t>
+          <t>https://www.yellowpages.com/west-hollywood-ca/mip/sunset-plaza-1562237</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-2017</t>
+          <t>2 of 3, role-email, direct-line, since-1924</t>
         </is>
       </c>
       <c r="S305" t="inlineStr">
@@ -34297,13 +34309,13 @@
       </c>
       <c r="T305" s="2" t="inlineStr">
         <is>
-          <t>https://wristaficionado.com/</t>
+          <t>https://www.sunsetplaza.com/</t>
         </is>
       </c>
       <c r="U305" t="inlineStr"/>
       <c r="V305" t="inlineStr">
         <is>
-          <t>2026-10-14T01:43:17+05:30</t>
+          <t>2026-10-14T01:52:13+05:30</t>
         </is>
       </c>
       <c r="W305" t="inlineStr"/>
@@ -34314,17 +34326,233 @@
       <c r="Z305" t="inlineStr"/>
       <c r="AA305" t="inlineStr">
         <is>
+          <t>(213) 500-3098, (213) 709-2282, (310) 210-0975, (310) 248-3750, (310) 274-1602, (310) 275-2222, (310) 289-1104, (310) 289-1105, (310) 360-6900, (310) 360-8889, (310) 424-3690, (310) 616-7888, (310) 652-2680, (310) 652-6844, (310) 652-7039, (310) 652-8886, (310) 657-2553, (310) 657-5070, (310) 657-5469, (310) 659-4411, (310) 659-9089, (310) 734-7296, (310) 786-7417, (310) 849-7185, (310) 854-0299, (310) 854-7700, (310) 855-8044, (323) 253-6747, (323) 345-4525, (323) 507-3943, (323) 650-0475, (323) 937-0355, (424) 407-4606, (424) 542-7730, (424) 667-0036, (424) 722-8502, (747) 724-3595</t>
+        </is>
+      </c>
+      <c r="AB305" t="inlineStr">
+        <is>
+          <t>https://instagram.com/affluette_, https://instagram.com/alchemy43, https://facebook.com/alchemy43, https://instagram.com/andreas.fashions, https://facebook.com/andreasfashions, https://instagram.com/bbcmcafe, https://instagram.com/bootstarusa, https://facebook.com/Boot-Star-106137407505929, https://instagram.com/bossanovarestaurant, https://facebook.com/BossaNovaLA, https://instagram.com/charliechoukair/, https://instagram.com/cristallini_official, https://facebook.com/CRISTALLINIOfficial, https://instagram.com/architectureforsale/, https://instagram.com/cupidlipsofbeverlyhills, https://facebook.com/profile.php?id=100083257576786, https://instagram.com/dandeutschoo, https://instagram.com/davidorgell, https://instagram.com/drybarshopsus, https://facebook.com/thedrybar, https://instagram.com/elainekimcollection/, https://instagram.com/entouragebarbershop, https://instagram.com/fpjourneofficial, https://instagram.com/guyfloralstudio, https://instagram.com/hotpilates, https://facebook.com/Hot-Pilates-1806940676211478, https://instagram.com/kojitoyodasalon, https://instagram.com/metaclinic/, https://instagram.com/milamoursiskincare, https://instagram.com/olehenriksenspa/, https://instagram.com/oliverpeoples, https://instagram.com/osklo.la, https://instagram.com/philippressjeweler, https://instagram.com/puravidamiami, https://facebook.com/PuraVidaMiami, https://instagram.com/queenbnailsalon_sunsetplaza, https://instagram.com/andywarholrevolvergallery, https://instagram.com/rondorff, https://instagram.com/saltiegirlla, https://instagram.com/samira13jewelry, https://instagram.com/sargondental, https://facebook.com/sargonlazarofdds, https://instagram.com/serenityonsunset, https://instagram.com/sheilaonsunset, https://instagram.com/solatesbysamantha, https://instagram.com/sousla_official, https://instagram.com/sunsetkidsla, https://instagram.com/theoppenheimgroup, https://facebook.com/theoppenheimgroup, https://instagram.com/whitegloveestates, https://instagram.com/xrcyze_ny, https://facebook.com/xrcycle, https://instagram.com/sunsetplazaca, https://facebook.com/SunsetPlazaCA</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Westime Beverly Hills</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Custom / bespoke jeweler</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Watch store</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>(310) 888-8880</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>contact@westime.com</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr"/>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>Greg Simonian</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="I306" s="2" t="inlineStr">
+        <is>
+          <t>https://westime.com</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>206 N Rodeo Dr, Beverly Hills, CA 90210, United States</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr"/>
+      <c r="L306" t="inlineStr"/>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>Beverly Hills, CA</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O306" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P306" t="n">
+        <v>274</v>
+      </c>
+      <c r="Q306" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Westime+Beverly+Hills/data=!4m7!3m6!1s0x80c2bc0ed6429065:0x2c357ea8ffa51b1f!8m2!3d34.067375!4d-118.4003799!16s%2Fg%2F11cfj2mg2!19sChIJZZBC1g68woARHxul_6h-NSw</t>
+        </is>
+      </c>
+      <c r="R306" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, custom-design, since-1987</t>
+        </is>
+      </c>
+      <c r="S306" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T306" s="2" t="inlineStr">
+        <is>
+          <t>https://westime.com/contact</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr"/>
+      <c r="V306" t="inlineStr">
+        <is>
+          <t>2026-10-14T01:39:33+05:30</t>
+        </is>
+      </c>
+      <c r="W306" t="inlineStr"/>
+      <c r="X306" t="inlineStr"/>
+      <c r="Y306" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z306" t="inlineStr"/>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>(786) 347-5353, (858) 459-2222</t>
+        </is>
+      </c>
+      <c r="AB306" t="inlineStr">
+        <is>
+          <t>https://instagram.com/westimewatches, https://facebook.com/Westime</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Wrist Aficionado Beverly Hills</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Watch store</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>(310) 388-8201</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>sales@wristaficionado.com</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr"/>
+      <c r="G307" t="inlineStr"/>
+      <c r="H307" t="inlineStr"/>
+      <c r="I307" s="2" t="inlineStr">
+        <is>
+          <t>https://wristaficionado.com</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>9850 Wilshire Blvd, Beverly Hills, CA 90210, United States</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Beverly Hills</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>Beverly Hills, CA</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O307" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P307" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q307" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Wrist+Aficionado+Beverly+Hills/data=!4m7!3m6!1s0x80c2bb67e5181fcf:0xde9cbdbb118a155c!8m2!3d34.0667288!4d-118.4113018!16s%2Fg%2F11v12tg_x0!19sChIJzx8Y5We7woARXBWKEbu9nN4</t>
+        </is>
+      </c>
+      <c r="R307" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, custom-design, since-2017</t>
+        </is>
+      </c>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T307" s="2" t="inlineStr">
+        <is>
+          <t>https://wristaficionado.com/</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr"/>
+      <c r="V307" t="inlineStr">
+        <is>
+          <t>2026-10-14T01:43:17+05:30</t>
+        </is>
+      </c>
+      <c r="W307" t="inlineStr"/>
+      <c r="X307" t="inlineStr"/>
+      <c r="Y307" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z307" t="inlineStr"/>
+      <c r="AA307" t="inlineStr">
+        <is>
           <t>(305) 680-3735, (310) 861-3485, (646) 693-9384, (786) 889-6892</t>
         </is>
       </c>
-      <c r="AB305" t="inlineStr">
+      <c r="AB307" t="inlineStr">
         <is>
           <t>https://instagram.com/wristaficionado, https://instagram.com/wristaficionado/, https://facebook.com/shopwristaficionado, https://twitter.com/wristaficionado</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB305"/>
+  <autoFilter ref="A1:AB307"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId2"/>
@@ -35150,189 +35378,198 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q246" r:id="rId822"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T246" r:id="rId823"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U246" r:id="rId824"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I247" r:id="rId825"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q247" r:id="rId826"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T247" r:id="rId827"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I248" r:id="rId828"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q248" r:id="rId829"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T248" r:id="rId830"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I249" r:id="rId831"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q249" r:id="rId832"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T249" r:id="rId833"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F250" r:id="rId834"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I250" r:id="rId835"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q250" r:id="rId836"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T250" r:id="rId837"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U250" r:id="rId838"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I251" r:id="rId839"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q251" r:id="rId840"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T251" r:id="rId841"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I252" r:id="rId842"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q252" r:id="rId843"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T252" r:id="rId844"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I253" r:id="rId845"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q253" r:id="rId846"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T253" r:id="rId847"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I254" r:id="rId848"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q254" r:id="rId849"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T254" r:id="rId850"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I255" r:id="rId851"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q255" r:id="rId852"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T255" r:id="rId853"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I256" r:id="rId854"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q256" r:id="rId855"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T256" r:id="rId856"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I257" r:id="rId857"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q257" r:id="rId858"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T257" r:id="rId859"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F258" r:id="rId860"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I258" r:id="rId861"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q258" r:id="rId862"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T258" r:id="rId863"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U258" r:id="rId864"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I259" r:id="rId865"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q259" r:id="rId866"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T259" r:id="rId867"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I260" r:id="rId868"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q260" r:id="rId869"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T260" r:id="rId870"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I261" r:id="rId871"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q261" r:id="rId872"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T261" r:id="rId873"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I262" r:id="rId874"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q262" r:id="rId875"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T262" r:id="rId876"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I263" r:id="rId877"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q263" r:id="rId878"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T263" r:id="rId879"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I264" r:id="rId880"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q264" r:id="rId881"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T264" r:id="rId882"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I265" r:id="rId883"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q265" r:id="rId884"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T265" r:id="rId885"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I266" r:id="rId886"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q266" r:id="rId887"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T266" r:id="rId888"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I267" r:id="rId889"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q267" r:id="rId890"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T267" r:id="rId891"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I268" r:id="rId892"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q268" r:id="rId893"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T268" r:id="rId894"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I269" r:id="rId895"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q269" r:id="rId896"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T269" r:id="rId897"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I270" r:id="rId898"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q270" r:id="rId899"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T270" r:id="rId900"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I271" r:id="rId901"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q271" r:id="rId902"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T271" r:id="rId903"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I272" r:id="rId904"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q272" r:id="rId905"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T272" r:id="rId906"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I273" r:id="rId907"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q273" r:id="rId908"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T273" r:id="rId909"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I274" r:id="rId910"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q274" r:id="rId911"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T274" r:id="rId912"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F275" r:id="rId913"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I275" r:id="rId914"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q275" r:id="rId915"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T275" r:id="rId916"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U275" r:id="rId917"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I276" r:id="rId918"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q276" r:id="rId919"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T276" r:id="rId920"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I277" r:id="rId921"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q277" r:id="rId922"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T277" r:id="rId923"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I278" r:id="rId924"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q278" r:id="rId925"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T278" r:id="rId926"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I279" r:id="rId927"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q279" r:id="rId928"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T279" r:id="rId929"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I280" r:id="rId930"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q280" r:id="rId931"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T280" r:id="rId932"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I281" r:id="rId933"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q281" r:id="rId934"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T281" r:id="rId935"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I282" r:id="rId936"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q282" r:id="rId937"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T282" r:id="rId938"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I283" r:id="rId939"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q283" r:id="rId940"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T283" r:id="rId941"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I284" r:id="rId942"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q284" r:id="rId943"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T284" r:id="rId944"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I285" r:id="rId945"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q285" r:id="rId946"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T285" r:id="rId947"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I286" r:id="rId948"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q286" r:id="rId949"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T286" r:id="rId950"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I287" r:id="rId951"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q287" r:id="rId952"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T287" r:id="rId953"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I288" r:id="rId954"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q288" r:id="rId955"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T288" r:id="rId956"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I289" r:id="rId957"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q289" r:id="rId958"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T289" r:id="rId959"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I290" r:id="rId960"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q290" r:id="rId961"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T290" r:id="rId962"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I291" r:id="rId963"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q291" r:id="rId964"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T291" r:id="rId965"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I292" r:id="rId966"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q292" r:id="rId967"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T292" r:id="rId968"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I293" r:id="rId969"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q293" r:id="rId970"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T293" r:id="rId971"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I294" r:id="rId972"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q294" r:id="rId973"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T294" r:id="rId974"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I295" r:id="rId975"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q295" r:id="rId976"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T295" r:id="rId977"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I296" r:id="rId978"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q296" r:id="rId979"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T296" r:id="rId980"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I297" r:id="rId981"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q297" r:id="rId982"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T297" r:id="rId983"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I298" r:id="rId984"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q298" r:id="rId985"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T298" r:id="rId986"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I299" r:id="rId987"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q299" r:id="rId988"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T299" r:id="rId989"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I300" r:id="rId990"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q300" r:id="rId991"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T300" r:id="rId992"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I301" r:id="rId993"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q301" r:id="rId994"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T301" r:id="rId995"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I302" r:id="rId996"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q302" r:id="rId997"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T302" r:id="rId998"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I303" r:id="rId999"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q303" r:id="rId1000"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T303" r:id="rId1001"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I304" r:id="rId1002"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q304" r:id="rId1003"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T304" r:id="rId1004"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I305" r:id="rId1005"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q305" r:id="rId1006"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T305" r:id="rId1007"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F247" r:id="rId825"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I247" r:id="rId826"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q247" r:id="rId827"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T247" r:id="rId828"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U247" r:id="rId829"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I248" r:id="rId830"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q248" r:id="rId831"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T248" r:id="rId832"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I249" r:id="rId833"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q249" r:id="rId834"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T249" r:id="rId835"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I250" r:id="rId836"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q250" r:id="rId837"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T250" r:id="rId838"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F251" r:id="rId839"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I251" r:id="rId840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q251" r:id="rId841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U251" r:id="rId842"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F252" r:id="rId843"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I252" r:id="rId844"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q252" r:id="rId845"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T252" r:id="rId846"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U252" r:id="rId847"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I253" r:id="rId848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q253" r:id="rId849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T253" r:id="rId850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I254" r:id="rId851"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q254" r:id="rId852"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T254" r:id="rId853"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I255" r:id="rId854"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q255" r:id="rId855"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T255" r:id="rId856"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I256" r:id="rId857"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q256" r:id="rId858"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T256" r:id="rId859"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I257" r:id="rId860"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q257" r:id="rId861"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T257" r:id="rId862"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I258" r:id="rId863"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q258" r:id="rId864"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T258" r:id="rId865"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I259" r:id="rId866"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q259" r:id="rId867"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T259" r:id="rId868"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F260" r:id="rId869"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I260" r:id="rId870"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q260" r:id="rId871"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T260" r:id="rId872"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U260" r:id="rId873"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I261" r:id="rId874"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q261" r:id="rId875"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T261" r:id="rId876"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I262" r:id="rId877"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q262" r:id="rId878"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T262" r:id="rId879"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I263" r:id="rId880"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q263" r:id="rId881"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T263" r:id="rId882"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I264" r:id="rId883"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q264" r:id="rId884"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T264" r:id="rId885"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I265" r:id="rId886"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q265" r:id="rId887"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T265" r:id="rId888"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I266" r:id="rId889"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q266" r:id="rId890"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T266" r:id="rId891"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I267" r:id="rId892"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q267" r:id="rId893"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T267" r:id="rId894"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I268" r:id="rId895"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q268" r:id="rId896"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T268" r:id="rId897"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I269" r:id="rId898"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q269" r:id="rId899"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T269" r:id="rId900"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I270" r:id="rId901"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q270" r:id="rId902"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T270" r:id="rId903"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I271" r:id="rId904"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q271" r:id="rId905"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T271" r:id="rId906"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I272" r:id="rId907"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q272" r:id="rId908"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T272" r:id="rId909"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I273" r:id="rId910"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q273" r:id="rId911"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T273" r:id="rId912"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I274" r:id="rId913"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q274" r:id="rId914"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T274" r:id="rId915"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I275" r:id="rId916"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q275" r:id="rId917"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T275" r:id="rId918"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I276" r:id="rId919"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q276" r:id="rId920"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T276" r:id="rId921"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F277" r:id="rId922"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I277" r:id="rId923"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q277" r:id="rId924"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T277" r:id="rId925"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U277" r:id="rId926"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I278" r:id="rId927"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q278" r:id="rId928"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T278" r:id="rId929"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I279" r:id="rId930"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q279" r:id="rId931"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T279" r:id="rId932"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I280" r:id="rId933"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q280" r:id="rId934"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T280" r:id="rId935"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I281" r:id="rId936"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q281" r:id="rId937"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T281" r:id="rId938"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I282" r:id="rId939"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q282" r:id="rId940"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T282" r:id="rId941"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I283" r:id="rId942"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q283" r:id="rId943"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T283" r:id="rId944"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I284" r:id="rId945"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q284" r:id="rId946"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T284" r:id="rId947"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I285" r:id="rId948"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q285" r:id="rId949"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T285" r:id="rId950"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I286" r:id="rId951"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q286" r:id="rId952"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T286" r:id="rId953"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I287" r:id="rId954"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q287" r:id="rId955"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T287" r:id="rId956"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I288" r:id="rId957"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q288" r:id="rId958"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T288" r:id="rId959"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I289" r:id="rId960"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q289" r:id="rId961"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T289" r:id="rId962"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I290" r:id="rId963"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q290" r:id="rId964"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T290" r:id="rId965"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I291" r:id="rId966"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q291" r:id="rId967"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T291" r:id="rId968"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I292" r:id="rId969"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q292" r:id="rId970"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T292" r:id="rId971"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I293" r:id="rId972"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q293" r:id="rId973"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T293" r:id="rId974"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I294" r:id="rId975"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q294" r:id="rId976"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T294" r:id="rId977"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I295" r:id="rId978"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q295" r:id="rId979"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T295" r:id="rId980"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I296" r:id="rId981"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q296" r:id="rId982"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T296" r:id="rId983"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I297" r:id="rId984"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q297" r:id="rId985"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T297" r:id="rId986"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I298" r:id="rId987"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q298" r:id="rId988"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T298" r:id="rId989"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I299" r:id="rId990"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q299" r:id="rId991"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T299" r:id="rId992"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I300" r:id="rId993"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q300" r:id="rId994"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T300" r:id="rId995"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I301" r:id="rId996"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q301" r:id="rId997"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T301" r:id="rId998"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I302" r:id="rId999"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q302" r:id="rId1000"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T302" r:id="rId1001"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I303" r:id="rId1002"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q303" r:id="rId1003"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T303" r:id="rId1004"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I304" r:id="rId1005"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q304" r:id="rId1006"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T304" r:id="rId1007"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I305" r:id="rId1008"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q305" r:id="rId1009"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T305" r:id="rId1010"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I306" r:id="rId1011"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q306" r:id="rId1012"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T306" r:id="rId1013"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I307" r:id="rId1014"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q307" r:id="rId1015"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T307" r:id="rId1016"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35400,7 +35637,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="C2" t="n">
         <v>34</v>
@@ -35427,7 +35664,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="C3" t="n">
         <v>30</v>
@@ -35481,7 +35718,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C5" t="n">
         <v>22</v>
@@ -35508,7 +35745,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C6" t="n">
         <v>9</v>
@@ -35535,7 +35772,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C7" t="n">
         <v>32</v>
@@ -35589,7 +35826,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C9" t="n">
         <v>13</v>
@@ -35643,7 +35880,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C11" t="n">
         <v>16</v>
@@ -35670,7 +35907,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
@@ -35697,7 +35934,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C13" t="n">
         <v>12</v>
@@ -35724,14 +35961,14 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -35778,24 +36015,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -35805,14 +36042,14 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="C17" t="n">
         <v>6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -35832,7 +36069,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C18" t="n">
         <v>11</v>
@@ -35967,7 +36204,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C23" t="n">
         <v>4</v>
@@ -36021,7 +36258,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C25" t="n">
         <v>6</v>
@@ -36075,24 +36312,24 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10728</v>
+        <v>10733</v>
       </c>
       <c r="C27" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F27" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G27" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -36142,7 +36379,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4">
@@ -36152,7 +36389,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
@@ -36204,7 +36441,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11">
@@ -36243,7 +36480,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T04:26:28+05:30</t>
+          <t>2026-10-14T04:46:41+05:30</t>
         </is>
       </c>
     </row>
@@ -36254,7 +36491,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3">
@@ -36264,7 +36501,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>10728</v>
+        <v>10733</v>
       </c>
     </row>
     <row r="4">

--- a/leadrun_jewelry/jewelry_qualified.xlsx
+++ b/leadrun_jewelry/jewelry_qualified.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qualified Leads'!$A$1:$AB$320</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qualified Leads'!$A$1:$AB$321</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB320"/>
+  <dimension ref="A1:AB321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -31818,45 +31818,53 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>R.F. Moeller Jeweler</t>
+          <t>Johnson Jewelers</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>(651) 698-6321</t>
+          <t>(651) 735-4400</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>alexandra@rfmoeller.com</t>
+          <t>ryan@johnsonjewelers.com</t>
         </is>
       </c>
       <c r="F282" t="inlineStr"/>
-      <c r="G282" t="inlineStr"/>
-      <c r="H282" t="inlineStr"/>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Bob Johnson</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>https://rfmoeller.com</t>
+          <t>https://johnsonjewelers.com</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>2065 Ford Pkwy, St Paul, MN 55116, United States</t>
+          <t>783 Radio Dr Ste 100D, Saint Paul, MN 55125-5402</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Saint Paul</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -31871,23 +31879,19 @@
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O282" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P282" t="n">
-        <v>2186</v>
-      </c>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr"/>
+      <c r="P282" t="inlineStr"/>
       <c r="Q282" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/R.F.+Moeller+Jeweler/data=!4m7!3m6!1s0x87f62978048ef94d:0xea9c4d97c5c2b259!8m2!3d44.9181574!4d-93.1877644!16s%2Fg%2F1v7pz0rd!19sChIJTfmOBHgp9ocRWbLCxZdNnOo</t>
+          <t>https://www.bbb.org/us/mn/saint-paul/profile/jewelry-stores/johnson-jewelers-0704-9000723</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, ags, custom-design, since-1951</t>
+          <t>2 of 3, direct-line, custom-design, since-1976</t>
         </is>
       </c>
       <c r="S282" t="inlineStr">
@@ -31897,49 +31901,41 @@
       </c>
       <c r="T282" s="2" t="inlineStr">
         <is>
-          <t>https://rfmoeller.com/</t>
+          <t>https://johnsonjewelers.com/about/employment/</t>
         </is>
       </c>
       <c r="U282" t="inlineStr"/>
       <c r="V282" t="inlineStr">
         <is>
-          <t>2026-10-14T00:46:15+05:30</t>
-        </is>
-      </c>
-      <c r="W282" t="inlineStr">
-        <is>
-          <t>Moeller Jeweler R. F.</t>
-        </is>
-      </c>
+          <t>2026-10-14T05:42:57+05:30</t>
+        </is>
+      </c>
+      <c r="W282" t="inlineStr"/>
       <c r="X282" t="inlineStr"/>
       <c r="Y282" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z282" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Z282" t="inlineStr"/>
       <c r="AA282" t="inlineStr">
         <is>
-          <t>(651) 698-6322</t>
+          <t>(651) 345-3825</t>
         </is>
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>https://facebook.com/rfmoellerjeweler, https://instagram.com/rfmoellerjeweler</t>
+          <t>https://facebook.com/JohnsonJewelersInc, https://facebook.com/JohnsonJewelersofLakeCity</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Bailey's Fine Jewelry</t>
+          <t>R.F. Moeller Jeweler</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -31949,12 +31945,12 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>(704) 332-1605</t>
+          <t>(651) 698-6321</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>carysubs@baileybox.com</t>
+          <t>alexandra@rfmoeller.com</t>
         </is>
       </c>
       <c r="F283" t="inlineStr"/>
@@ -31962,27 +31958,27 @@
       <c r="H283" t="inlineStr"/>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>https://www.baileybox.com</t>
+          <t>https://rfmoeller.com</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>705 Providence Rd, Charlotte, NC 28207, United States</t>
+          <t>2065 Ford Pkwy, St Paul, MN 55116, United States</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Charlotte, NC</t>
+          <t>Minneapolis, MN</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -31991,19 +31987,19 @@
         </is>
       </c>
       <c r="O283" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P283" t="n">
-        <v>775</v>
+        <v>2186</v>
       </c>
       <c r="Q283" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Bailey%27s+Fine+Jewelry/data=!4m7!3m6!1s0x88569fe931546195:0x4340ee15ce06892f!8m2!3d35.2006619!4d-80.8249664!16s%2Fg%2F1tlgynm1!19sChIJlWFUMemfVogRL4kGzhXuQEM</t>
+          <t>https://www.google.com/maps/place/R.F.+Moeller+Jeweler/data=!4m7!3m6!1s0x87f62978048ef94d:0xea9c4d97c5c2b259!8m2!3d44.9181574!4d-93.1877644!16s%2Fg%2F1v7pz0rd!19sChIJTfmOBHgp9ocRWbLCxZdNnOo</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, ags, bench, custom-design, since-1948</t>
+          <t>2 of 3, direct-line, ags, custom-design, since-1951</t>
         </is>
       </c>
       <c r="S283" t="inlineStr">
@@ -32013,81 +32009,77 @@
       </c>
       <c r="T283" s="2" t="inlineStr">
         <is>
-          <t>https://baileybox.com/</t>
+          <t>https://rfmoeller.com/</t>
         </is>
       </c>
       <c r="U283" t="inlineStr"/>
       <c r="V283" t="inlineStr">
         <is>
-          <t>2026-10-14T00:51:23+05:30</t>
+          <t>2026-10-14T00:46:15+05:30</t>
         </is>
       </c>
       <c r="W283" t="inlineStr">
         <is>
-          <t>Morrison Smith Jewelers</t>
+          <t>Moeller Jeweler R. F.</t>
         </is>
       </c>
       <c r="X283" t="inlineStr"/>
       <c r="Y283" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z283" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="Z283" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA283" t="inlineStr">
         <is>
-          <t>(252) 353-3434, (252) 443-7676, (919) 829-7337, (919) 892-3838</t>
+          <t>(651) 698-6322</t>
         </is>
       </c>
       <c r="AB283" t="inlineStr">
         <is>
-          <t>https://facebook.com/BaileysFineJewelry, https://instagram.com/baileysfinejewelry, https://instagram.com/morrisonsmithjewelers, https://facebook.com/MorrisonSmithJewelers, https://x.com/morrisonsmith, https://twitter.com/morrisonsmith</t>
+          <t>https://facebook.com/rfmoellerjeweler, https://instagram.com/rfmoellerjeweler</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Fink's Jewelers</t>
+          <t>Bailey's Fine Jewelry</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Jewelers, Fix-It Shops, Watches</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>(704) 366-3120</t>
+          <t>(704) 332-1605</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>ecommerce@finks.com</t>
+          <t>carysubs@baileybox.com</t>
         </is>
       </c>
       <c r="F284" t="inlineStr"/>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>Nathan Fink</t>
-        </is>
-      </c>
-      <c r="H284" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
+      <c r="G284" t="inlineStr"/>
+      <c r="H284" t="inlineStr"/>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>https://www.finks.com</t>
+          <t>https://www.baileybox.com</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>4400 Sharon Rd Ste 199, Charlotte, NC 28211</t>
+          <t>705 Providence Rd, Charlotte, NC 28207, United States</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -32107,23 +32099,23 @@
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O284" t="n">
         <v>5</v>
       </c>
       <c r="P284" t="n">
-        <v>1</v>
+        <v>775</v>
       </c>
       <c r="Q284" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/charlotte-nc/mip/finks-jewelers-464773701</t>
+          <t>https://www.google.com/maps/place/Bailey%27s+Fine+Jewelry/data=!4m7!3m6!1s0x88569fe931546195:0x4340ee15ce06892f!8m2!3d35.2006619!4d-80.8249664!16s%2Fg%2F1tlgynm1!19sChIJlWFUMemfVogRL4kGzhXuQEM</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design, since-1930</t>
+          <t>2 of 3, direct-line, gia, ags, bench, custom-design, since-1948</t>
         </is>
       </c>
       <c r="S284" t="inlineStr">
@@ -32133,44 +32125,40 @@
       </c>
       <c r="T284" s="2" t="inlineStr">
         <is>
-          <t>https://www.finks.com/</t>
+          <t>https://baileybox.com/</t>
         </is>
       </c>
       <c r="U284" t="inlineStr"/>
       <c r="V284" t="inlineStr">
         <is>
-          <t>2026-10-14T01:43:57+05:30</t>
+          <t>2026-10-14T00:51:23+05:30</t>
         </is>
       </c>
       <c r="W284" t="inlineStr">
         <is>
-          <t>John Paul Fine Jewelry</t>
+          <t>Morrison Smith Jewelers</t>
         </is>
       </c>
       <c r="X284" t="inlineStr"/>
       <c r="Y284" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z284" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Z284" t="inlineStr"/>
       <c r="AA284" t="inlineStr">
         <is>
-          <t>(423) 894-1188, (540) 342-2991, (540) 344-8697, (615) 236-8176, (704) 927-4888, (757) 640-1132, (804) 377-8589, (919) 881-8247</t>
+          <t>(252) 353-3434, (252) 443-7676, (919) 829-7337, (919) 892-3838</t>
         </is>
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>https://facebook.com/FinksJewelers, https://instagram.com/finksjewelers</t>
+          <t>https://facebook.com/BaileysFineJewelry, https://instagram.com/baileysfinejewelry, https://instagram.com/morrisonsmithjewelers, https://facebook.com/MorrisonSmithJewelers, https://x.com/morrisonsmith, https://twitter.com/morrisonsmith</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Windsor Jewelers</t>
+          <t>Fink's Jewelers</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -32180,48 +32168,48 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers, Fix-It Shops, Watches</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>(704) 556-7747</t>
+          <t>(704) 366-3120</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>nfo@windsor-jewelers.com</t>
+          <t>ecommerce@finks.com</t>
         </is>
       </c>
       <c r="F285" t="inlineStr"/>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Kevin Slusher</t>
+          <t>Nathan Fink</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>https://www.windsor-jewelers.com</t>
+          <t>https://www.finks.com</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>6809-D Phillips Pl Ct, Charlotte, NC 28210, United States</t>
+          <t>4400 Sharon Rd Ste 199, Charlotte, NC 28211</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>Winston-Salem</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -32231,23 +32219,23 @@
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O285" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P285" t="n">
-        <v>1846</v>
+        <v>1</v>
       </c>
       <c r="Q285" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Windsor+Jewelers/data=!4m7!3m6!1s0x88569e13f91d1bb1:0x4b6448ed40c4d63c!8m2!3d35.1465046!4d-80.8269547!16s%2Fg%2F1tq8k7xj!19sChIJsRsd-ROeVogRPNbEQO1IZEs</t>
+          <t>https://www.yellowpages.com/charlotte-nc/mip/finks-jewelers-464773701</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design</t>
+          <t>2 of 3, direct-line, custom-design, since-1930</t>
         </is>
       </c>
       <c r="S285" t="inlineStr">
@@ -32257,36 +32245,44 @@
       </c>
       <c r="T285" s="2" t="inlineStr">
         <is>
-          <t>https://www.windsor-jewelers.com/</t>
+          <t>https://www.finks.com/</t>
         </is>
       </c>
       <c r="U285" t="inlineStr"/>
       <c r="V285" t="inlineStr">
         <is>
-          <t>2026-10-14T00:51:17+05:30</t>
-        </is>
-      </c>
-      <c r="W285" t="inlineStr"/>
+          <t>2026-10-14T01:43:57+05:30</t>
+        </is>
+      </c>
+      <c r="W285" t="inlineStr">
+        <is>
+          <t>John Paul Fine Jewelry</t>
+        </is>
+      </c>
       <c r="X285" t="inlineStr"/>
       <c r="Y285" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z285" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="Z285" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA285" t="inlineStr">
         <is>
-          <t>(336) 721-1768</t>
+          <t>(423) 894-1188, (540) 342-2991, (540) 344-8697, (615) 236-8176, (704) 927-4888, (757) 640-1132, (804) 377-8589, (919) 881-8247</t>
         </is>
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>https://instagram.com/windsorjewelersnc/, https://facebook.com/OfficialWindsorJewelersNC</t>
+          <t>https://facebook.com/FinksJewelers, https://instagram.com/finksjewelers</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Lindell Jewelers &amp; Appraisers</t>
+          <t>Windsor Jewelers</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -32301,44 +32297,48 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>(615) 373-7922</t>
+          <t>(704) 556-7747</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>lindelljewels@gmail.com</t>
-        </is>
-      </c>
-      <c r="F286" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/carolyn-linder-19ab1a80</t>
-        </is>
-      </c>
+          <t>nfo@windsor-jewelers.com</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr"/>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Carolyn A. Linder</t>
+          <t>Kevin Slusher</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>https://www.lindelljewelers.com</t>
+          <t>https://www.windsor-jewelers.com</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>7028 Church St E Ste 106, Brentwood, TN 37027, United States</t>
-        </is>
-      </c>
-      <c r="K286" t="inlineStr"/>
-      <c r="L286" t="inlineStr"/>
+          <t>6809-D Phillips Pl Ct, Charlotte, NC 28210, United States</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Winston-Salem</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Nashville, TN</t>
+          <t>Charlotte, NC</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -32350,51 +32350,55 @@
         <v>4.9</v>
       </c>
       <c r="P286" t="n">
-        <v>56</v>
+        <v>1846</v>
       </c>
       <c r="Q286" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Lindell+Jewelers+%26+Appraisers/data=!4m7!3m6!1s0x88647b266e6cc441:0xa03113da3f7ec814!8m2!3d36.0335009!4d-86.7862323!16s%2Fg%2F1tdjrwp3!19sChIJQcRsbiZ7ZIgRFMh-P9oTMaA</t>
+          <t>https://www.google.com/maps/place/Windsor+Jewelers/data=!4m7!3m6!1s0x88569e13f91d1bb1:0x4b6448ed40c4d63c!8m2!3d35.1465046!4d-80.8269547!16s%2Fg%2F1tq8k7xj!19sChIJsRsd-ROeVogRPNbEQO1IZEs</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>2 of 3, custom-design, since-1991</t>
+          <t>2 of 3, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="T286" s="2" t="inlineStr">
         <is>
-          <t>https://www.lindelljewelers.com/about-us</t>
-        </is>
-      </c>
-      <c r="U286" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=%22Carolyn+A.+Linder%22+Nashville+linkedin&amp;hl=en&amp;num=10</t>
-        </is>
-      </c>
+          <t>https://www.windsor-jewelers.com/</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr"/>
       <c r="V286" t="inlineStr">
         <is>
-          <t>2026-10-14T01:03:10+05:30</t>
+          <t>2026-10-14T00:51:17+05:30</t>
         </is>
       </c>
       <c r="W286" t="inlineStr"/>
       <c r="X286" t="inlineStr"/>
       <c r="Y286" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z286" t="inlineStr"/>
-      <c r="AA286" t="inlineStr"/>
-      <c r="AB286" t="inlineStr"/>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>(336) 721-1768</t>
+        </is>
+      </c>
+      <c r="AB286" t="inlineStr">
+        <is>
+          <t>https://instagram.com/windsorjewelersnc/, https://facebook.com/OfficialWindsorJewelersNC</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Strings for Hope</t>
+          <t>Lindell Jewelers &amp; Appraisers</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -32409,37 +32413,37 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>(615) 891-4323</t>
+          <t>(615) 373-7922</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>emily@stringsforhope.com</t>
+          <t>lindelljewels@gmail.com</t>
         </is>
       </c>
       <c r="F287" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/emily-winters-182b7a219</t>
+          <t>https://www.linkedin.com/in/carolyn-linder-19ab1a80</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Emily Winters</t>
+          <t>Carolyn A. Linder</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>https://stringsforhope.com</t>
+          <t>https://www.lindelljewelers.com</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>100 Taylor St, Nashville, TN 37208, United States</t>
+          <t>7028 Church St E Ste 106, Brentwood, TN 37027, United States</t>
         </is>
       </c>
       <c r="K287" t="inlineStr"/>
@@ -32455,19 +32459,19 @@
         </is>
       </c>
       <c r="O287" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P287" t="n">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="Q287" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Strings+for+Hope/data=!4m7!3m6!1s0x8864673b2485a245:0x7c5f1d365f1de575!8m2!3d36.1810664!4d-86.7859259!16s%2Fg%2F11p5x5j012!19sChIJRaKFJDtnZIgRdeUdXzYdX3w</t>
+          <t>https://www.google.com/maps/place/Lindell+Jewelers+%26+Appraisers/data=!4m7!3m6!1s0x88647b266e6cc441:0xa03113da3f7ec814!8m2!3d36.0335009!4d-86.7862323!16s%2Fg%2F1tdjrwp3!19sChIJQcRsbiZ7ZIgRFMh-P9oTMaA</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>2 of 3, custom-design, since-2010</t>
+          <t>2 of 3, custom-design, since-1991</t>
         </is>
       </c>
       <c r="S287" t="inlineStr">
@@ -32477,17 +32481,17 @@
       </c>
       <c r="T287" s="2" t="inlineStr">
         <is>
-          <t>https://stringsforhope.com/pages/about-us</t>
+          <t>https://www.lindelljewelers.com/about-us</t>
         </is>
       </c>
       <c r="U287" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=%22Emily+Winters%22+Nashville+linkedin&amp;hl=en&amp;num=10</t>
+          <t>https://www.google.com/search?q=%22Carolyn+A.+Linder%22+Nashville+linkedin&amp;hl=en&amp;num=10</t>
         </is>
       </c>
       <c r="V287" t="inlineStr">
         <is>
-          <t>2026-10-14T01:01:21+05:30</t>
+          <t>2026-10-14T01:03:10+05:30</t>
         </is>
       </c>
       <c r="W287" t="inlineStr"/>
@@ -32497,16 +32501,12 @@
       </c>
       <c r="Z287" t="inlineStr"/>
       <c r="AA287" t="inlineStr"/>
-      <c r="AB287" t="inlineStr">
-        <is>
-          <t>https://facebook.com/Stringsforhope, https://instagram.com/stringsforhope</t>
-        </is>
-      </c>
+      <c r="AB287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Alltribes Indian Art</t>
+          <t>Strings for Hope</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -32516,86 +32516,90 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Jewelers, Native American Goods, Art Goods</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>(800) 417-0024</t>
+          <t>(615) 891-4323</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>admin@alltribes.com</t>
-        </is>
-      </c>
-      <c r="F288" t="inlineStr"/>
+          <t>emily@stringsforhope.com</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/emily-winters-182b7a219</t>
+        </is>
+      </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Richard Candy</t>
+          <t>Emily Winters</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>President</t>
         </is>
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>https://alltribes.com</t>
+          <t>https://stringsforhope.com</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>75 W Baseline Rd Ste 6, Gilbert, AZ 85233</t>
-        </is>
-      </c>
-      <c r="K288" t="inlineStr">
-        <is>
-          <t>Gilbert</t>
-        </is>
-      </c>
-      <c r="L288" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
+          <t>100 Taylor St, Nashville, TN 37208, United States</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr"/>
+      <c r="L288" t="inlineStr"/>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ</t>
+          <t>Nashville, TN</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O288" t="inlineStr"/>
-      <c r="P288" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O288" t="n">
+        <v>5</v>
+      </c>
+      <c r="P288" t="n">
+        <v>23</v>
+      </c>
       <c r="Q288" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/gilbert-az/mip/alltribes-indian-art-15755647</t>
+          <t>https://www.google.com/maps/place/Strings+for+Hope/data=!4m7!3m6!1s0x8864673b2485a245:0x7c5f1d365f1de575!8m2!3d36.1810664!4d-86.7859259!16s%2Fg%2F11p5x5j012!19sChIJRaKFJDtnZIgRdeUdXzYdX3w</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, custom-design, since-2010</t>
         </is>
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T288" s="2" t="inlineStr">
         <is>
-          <t>https://alltribes.com/</t>
-        </is>
-      </c>
-      <c r="U288" t="inlineStr"/>
+          <t>https://stringsforhope.com/pages/about-us</t>
+        </is>
+      </c>
+      <c r="U288" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Emily+Winters%22+Nashville+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V288" t="inlineStr">
         <is>
-          <t>2026-10-14T01:46:53+05:30</t>
+          <t>2026-10-14T01:01:21+05:30</t>
         </is>
       </c>
       <c r="W288" t="inlineStr"/>
@@ -32603,60 +32607,64 @@
       <c r="Y288" t="n">
         <v>0</v>
       </c>
-      <c r="Z288" t="inlineStr">
-        <is>
-          <t>toll-free</t>
-        </is>
-      </c>
-      <c r="AA288" t="inlineStr">
-        <is>
-          <t>(480) 963-2284</t>
-        </is>
-      </c>
+      <c r="Z288" t="inlineStr"/>
+      <c r="AA288" t="inlineStr"/>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>https://facebook.com/alltribes, https://instagram.com/alltribes_indian_art, https://facebook.com/pg/alltribes/videos/</t>
+          <t>https://facebook.com/Stringsforhope, https://instagram.com/stringsforhope</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Diasparx</t>
+          <t>Alltribes Indian Art</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Wholesale jeweler</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr"/>
+          <t>Jewelers, Native American Goods, Art Goods</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>(800) 417-0024</t>
+        </is>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>daniel@diasparx.com</t>
+          <t>admin@alltribes.com</t>
         </is>
       </c>
       <c r="F289" t="inlineStr"/>
-      <c r="G289" t="inlineStr"/>
-      <c r="H289" t="inlineStr"/>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Richard Candy</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>https://www.diasparx.com</t>
+          <t>https://alltribes.com</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>Camelback Tower, 6900 E Camelback Rd Suite 1050, Scottsdale, AZ 85251, United States</t>
+          <t>75 W Baseline Rd Ste 6, Gilbert, AZ 85233</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>Scottsdale</t>
+          <t>Gilbert</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
@@ -32671,23 +32679,19 @@
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O289" t="n">
-        <v>5</v>
-      </c>
-      <c r="P289" t="n">
-        <v>22</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr"/>
+      <c r="P289" t="inlineStr"/>
       <c r="Q289" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Diasparx/data=!4m7!3m6!1s0x872b0b6df95ae9b9:0x57de2ae948b26574!8m2!3d33.5025864!4d-111.9322129!16s%2Fg%2F11x19r328p!19sChIJuela-W0LK4cRdGWySOkq3lc</t>
+          <t>https://www.yellowpages.com/gilbert-az/mip/alltribes-indian-art-15755647</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S289" t="inlineStr">
@@ -32697,13 +32701,13 @@
       </c>
       <c r="T289" s="2" t="inlineStr">
         <is>
-          <t>https://www.diasparx.com/</t>
+          <t>https://alltribes.com/</t>
         </is>
       </c>
       <c r="U289" t="inlineStr"/>
       <c r="V289" t="inlineStr">
         <is>
-          <t>2026-10-14T01:09:41+05:30</t>
+          <t>2026-10-14T01:46:53+05:30</t>
         </is>
       </c>
       <c r="W289" t="inlineStr"/>
@@ -32711,42 +32715,42 @@
       <c r="Y289" t="n">
         <v>0</v>
       </c>
-      <c r="Z289" t="inlineStr"/>
+      <c r="Z289" t="inlineStr">
+        <is>
+          <t>toll-free</t>
+        </is>
+      </c>
       <c r="AA289" t="inlineStr">
         <is>
-          <t>(212) 555-0134, (480) 640-0948</t>
+          <t>(480) 963-2284</t>
         </is>
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>https://instagram.com/diasparx, https://facebook.com/profile.php?id=100088561748204</t>
+          <t>https://facebook.com/alltribes, https://instagram.com/alltribes_indian_art, https://facebook.com/pg/alltribes/videos/</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Expert Shoe Luggage Watch &amp; Jewelry Repair</t>
+          <t>Diasparx</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Jewelry repair / goldsmith</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Shoe repair shop</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>(480) 451-1214</t>
-        </is>
-      </c>
+          <t>Wholesale jeweler</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr">
         <is>
-          <t>info@expertshoerepair.com</t>
+          <t>daniel@diasparx.com</t>
         </is>
       </c>
       <c r="F290" t="inlineStr"/>
@@ -32754,12 +32758,12 @@
       <c r="H290" t="inlineStr"/>
       <c r="I290" s="2" t="inlineStr">
         <is>
-          <t>https://expertslwjrepair.com</t>
+          <t>https://www.diasparx.com</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>10105 E Vía Linda Ste A- 105, Scottsdale, AZ 85258, United States</t>
+          <t>Camelback Tower, 6900 E Camelback Rd Suite 1050, Scottsdale, AZ 85251, United States</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
@@ -32783,19 +32787,19 @@
         </is>
       </c>
       <c r="O290" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P290" t="n">
-        <v>522</v>
+        <v>22</v>
       </c>
       <c r="Q290" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Expert+Shoe+Luggage+Watch+%26+Jewelry+Repair/data=!4m7!3m6!1s0x872b6d13c4a490a7:0x78beb810dbe170f!8m2!3d33.573104!4d-111.8634771!16s%2Fg%2F11hzvcxvl9!19sChIJp5CkxBNtK4cRDxe-DYHriwc</t>
+          <t>https://www.google.com/maps/place/Diasparx/data=!4m7!3m6!1s0x872b0b6df95ae9b9:0x57de2ae948b26574!8m2!3d33.5025864!4d-111.9322129!16s%2Fg%2F11x19r328p!19sChIJuela-W0LK4cRdGWySOkq3lc</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, since-1960</t>
+          <t>2 of 3, direct-line, gia, custom-design</t>
         </is>
       </c>
       <c r="S290" t="inlineStr">
@@ -32805,56 +32809,56 @@
       </c>
       <c r="T290" s="2" t="inlineStr">
         <is>
-          <t>https://www.expertshoerepair.com/</t>
+          <t>https://www.diasparx.com/</t>
         </is>
       </c>
       <c r="U290" t="inlineStr"/>
       <c r="V290" t="inlineStr">
         <is>
-          <t>2026-10-14T01:10:03+05:30</t>
+          <t>2026-10-14T01:09:41+05:30</t>
         </is>
       </c>
       <c r="W290" t="inlineStr"/>
       <c r="X290" t="inlineStr"/>
       <c r="Y290" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z290" t="inlineStr"/>
       <c r="AA290" t="inlineStr">
         <is>
-          <t>(480) 269-7591</t>
+          <t>(212) 555-0134, (480) 640-0948</t>
         </is>
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>https://facebook.com/expertshoerepair, https://instagram.com/expert_shoe_repair</t>
+          <t>https://instagram.com/diasparx, https://facebook.com/profile.php?id=100088561748204</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Sunrise Jewelry &amp; Gallery</t>
+          <t>Expert Shoe Luggage Watch &amp; Jewelry Repair</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Jewelry repair / goldsmith</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Shoe repair shop</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>(480) 425-9944</t>
+          <t>(480) 451-1214</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>info@sunrisejewelryusa.com</t>
+          <t>info@expertshoerepair.com</t>
         </is>
       </c>
       <c r="F291" t="inlineStr"/>
@@ -32862,12 +32866,12 @@
       <c r="H291" t="inlineStr"/>
       <c r="I291" s="2" t="inlineStr">
         <is>
-          <t>https://www.sunrisejewelryusa.com</t>
+          <t>https://expertslwjrepair.com</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>7254 E Main St Suite 101, Scottsdale, AZ 85251, United States</t>
+          <t>10105 E Vía Linda Ste A- 105, Scottsdale, AZ 85258, United States</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
@@ -32891,19 +32895,19 @@
         </is>
       </c>
       <c r="O291" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P291" t="n">
-        <v>98</v>
+        <v>522</v>
       </c>
       <c r="Q291" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Sunrise+Jewelry+%26+Gallery/data=!4m7!3m6!1s0x872b0bd689ab1b37:0xfa243a0d0a63c6b6!8m2!3d33.4932392!4d-111.9247178!16s%2Fg%2F11q1rmxn64!19sChIJNxuridYLK4cRtsZjCg06JPo</t>
+          <t>https://www.google.com/maps/place/Expert+Shoe+Luggage+Watch+%26+Jewelry+Repair/data=!4m7!3m6!1s0x872b6d13c4a490a7:0x78beb810dbe170f!8m2!3d33.573104!4d-111.8634771!16s%2Fg%2F11hzvcxvl9!19sChIJp5CkxBNtK4cRDxe-DYHriwc</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, since-2006</t>
+          <t>2 of 3, role-email, direct-line, since-1960</t>
         </is>
       </c>
       <c r="S291" t="inlineStr">
@@ -32913,20 +32917,16 @@
       </c>
       <c r="T291" s="2" t="inlineStr">
         <is>
-          <t>https://sunrisejewelryusa.com/</t>
+          <t>https://www.expertshoerepair.com/</t>
         </is>
       </c>
       <c r="U291" t="inlineStr"/>
       <c r="V291" t="inlineStr">
         <is>
-          <t>2026-10-14T01:05:57+05:30</t>
-        </is>
-      </c>
-      <c r="W291" t="inlineStr">
-        <is>
-          <t>Sunrise Trading Post</t>
-        </is>
-      </c>
+          <t>2026-10-14T01:10:03+05:30</t>
+        </is>
+      </c>
+      <c r="W291" t="inlineStr"/>
       <c r="X291" t="inlineStr"/>
       <c r="Y291" t="n">
         <v>1</v>
@@ -32934,19 +32934,19 @@
       <c r="Z291" t="inlineStr"/>
       <c r="AA291" t="inlineStr">
         <is>
-          <t>(480) 994-0170</t>
+          <t>(480) 269-7591</t>
         </is>
       </c>
       <c r="AB291" t="inlineStr">
         <is>
-          <t>https://instagram.com/sunrisejewelryandgallery, https://facebook.com/sunrisejewelryusa</t>
+          <t>https://facebook.com/expertshoerepair, https://instagram.com/expert_shoe_repair</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Truly Blessed Jewels - Scottsdale</t>
+          <t>Sunrise Jewelry &amp; Gallery</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -32961,37 +32961,25 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>(480) 306-4296</t>
+          <t>(480) 425-9944</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>becky@trulyblessedjewels.com</t>
-        </is>
-      </c>
-      <c r="F292" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/lisa-valenzuela-801071264</t>
-        </is>
-      </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>Lisa Valenzuela</t>
-        </is>
-      </c>
-      <c r="H292" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
+          <t>info@sunrisejewelryusa.com</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr"/>
+      <c r="H292" t="inlineStr"/>
       <c r="I292" s="2" t="inlineStr">
         <is>
-          <t>https://trulyblessedjewels.com</t>
+          <t>https://www.sunrisejewelryusa.com</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>7058 E 5th Ave, Scottsdale, AZ 85251, United States</t>
+          <t>7254 E Main St Suite 101, Scottsdale, AZ 85251, United States</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
@@ -33001,7 +32989,7 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
@@ -33015,66 +33003,62 @@
         </is>
       </c>
       <c r="O292" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P292" t="n">
-        <v>1244</v>
+        <v>98</v>
       </c>
       <c r="Q292" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Truly+Blessed+Jewels+-+Scottsdale/data=!4m7!3m6!1s0x872b0bbd075f72f5:0xe625e386ff4966fb!8m2!3d33.498152!4d-111.9292942!16s%2Fg%2F11hf00j2kh!19sChIJ9XJfB70LK4cR-2ZJ_4bjJeY</t>
+          <t>https://www.google.com/maps/place/Sunrise+Jewelry+%26+Gallery/data=!4m7!3m6!1s0x872b0bd689ab1b37:0xfa243a0d0a63c6b6!8m2!3d33.4932392!4d-111.9247178!16s%2Fg%2F11q1rmxn64!19sChIJNxuridYLK4cRtsZjCg06JPo</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>2 of 3</t>
+          <t>2 of 3, role-email, direct-line, since-2006</t>
         </is>
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="T292" s="2" t="inlineStr">
         <is>
-          <t>https://trulyblessedjewels.com/pages/contact-us-1</t>
-        </is>
-      </c>
-      <c r="U292" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=%22Lisa+Valenzuela%22+Scottsdale+linkedin&amp;hl=en&amp;num=10</t>
-        </is>
-      </c>
+          <t>https://sunrisejewelryusa.com/</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr"/>
       <c r="V292" t="inlineStr">
         <is>
-          <t>2026-10-14T01:05:54+05:30</t>
+          <t>2026-10-14T01:05:57+05:30</t>
         </is>
       </c>
       <c r="W292" t="inlineStr">
         <is>
-          <t>Truly Blessed Jewels</t>
-        </is>
-      </c>
-      <c r="X292" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ</t>
-        </is>
-      </c>
+          <t>Sunrise Trading Post</t>
+        </is>
+      </c>
+      <c r="X292" t="inlineStr"/>
       <c r="Y292" t="n">
         <v>1</v>
       </c>
       <c r="Z292" t="inlineStr"/>
-      <c r="AA292" t="inlineStr"/>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>(480) 994-0170</t>
+        </is>
+      </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>https://instagram.com/trulyblessedjewels, https://facebook.com/Truly Blessed Jewels</t>
+          <t>https://instagram.com/sunrisejewelryandgallery, https://facebook.com/sunrisejewelryusa</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Exquisite Timepieces</t>
+          <t>Truly Blessed Jewels - Scottsdale</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -33084,105 +33068,125 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Jewelers, Watches</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>(239) 227-2932</t>
+          <t>(480) 306-4296</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>team@exquisitetimepieces.com</t>
-        </is>
-      </c>
-      <c r="F293" t="inlineStr"/>
-      <c r="G293" t="inlineStr"/>
-      <c r="H293" t="inlineStr"/>
+          <t>becky@trulyblessedjewels.com</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lisa-valenzuela-801071264</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Lisa Valenzuela</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="I293" s="2" t="inlineStr">
         <is>
-          <t>https://www.exquisitetimepieces.com</t>
+          <t>https://trulyblessedjewels.com</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>4380 Gulf Shore Blvd N, Naples, FL 34103</t>
+          <t>7058 E 5th Ave, Scottsdale, AZ 85251, United States</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>Naples</t>
+          <t>Scottsdale</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Naples, FL</t>
+          <t>Scottsdale, AZ</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O293" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P293" t="n">
-        <v>31</v>
+        <v>1244</v>
       </c>
       <c r="Q293" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/naples-fl/mip/exquisite-timepieces-14306847</t>
+          <t>https://www.google.com/maps/place/Truly+Blessed+Jewels+-+Scottsdale/data=!4m7!3m6!1s0x872b0bbd075f72f5:0xe625e386ff4966fb!8m2!3d33.498152!4d-111.9292942!16s%2Fg%2F11hf00j2kh!19sChIJ9XJfB70LK4cR-2ZJ_4bjJeY</t>
         </is>
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, ja, since-1998</t>
+          <t>2 of 3</t>
         </is>
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T293" s="2" t="inlineStr">
         <is>
-          <t>https://www.exquisitetimepieces.com/</t>
-        </is>
-      </c>
-      <c r="U293" t="inlineStr"/>
+          <t>https://trulyblessedjewels.com/pages/contact-us-1</t>
+        </is>
+      </c>
+      <c r="U293" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Lisa+Valenzuela%22+Scottsdale+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V293" t="inlineStr">
         <is>
-          <t>2026-10-14T01:47:28+05:30</t>
-        </is>
-      </c>
-      <c r="W293" t="inlineStr"/>
-      <c r="X293" t="inlineStr"/>
+          <t>2026-10-14T01:05:54+05:30</t>
+        </is>
+      </c>
+      <c r="W293" t="inlineStr">
+        <is>
+          <t>Truly Blessed Jewels</t>
+        </is>
+      </c>
+      <c r="X293" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ</t>
+        </is>
+      </c>
       <c r="Y293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z293" t="inlineStr"/>
-      <c r="AA293" t="inlineStr">
-        <is>
-          <t>(239) 262-4545</t>
-        </is>
-      </c>
+      <c r="AA293" t="inlineStr"/>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>https://facebook.com/pages/Exquisite-Timepieces/138888796144728, https://x.com/TimeExquisite, https://instagram.com/exquisitetimepieces, https://facebook.com/Exquisite-Timepieces-138888796144728, https://twitter.com/TimeExquisite</t>
+          <t>https://instagram.com/trulyblessedjewels, https://facebook.com/Truly Blessed Jewels</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Gold Silver Naples</t>
+          <t>Exquisite Timepieces</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -33192,17 +33196,17 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Gold dealer</t>
+          <t>Jewelers, Watches</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>(239) 591-5999</t>
+          <t>(239) 227-2932</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>goldsilvercoinsofnaples@gmail.com</t>
+          <t>team@exquisitetimepieces.com</t>
         </is>
       </c>
       <c r="F294" t="inlineStr"/>
@@ -33210,16 +33214,24 @@
       <c r="H294" t="inlineStr"/>
       <c r="I294" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldsilvernaples.com</t>
+          <t>https://www.exquisitetimepieces.com</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>1575 Pine Ridge Rd Ste 20, Naples, FL 34109, United States</t>
-        </is>
-      </c>
-      <c r="K294" t="inlineStr"/>
-      <c r="L294" t="inlineStr"/>
+          <t>4380 Gulf Shore Blvd N, Naples, FL 34103</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Naples</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
       <c r="M294" t="inlineStr">
         <is>
           <t>Naples, FL</t>
@@ -33227,23 +33239,23 @@
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O294" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="P294" t="n">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="Q294" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Gold+Silver+Naples/data=!4m7!3m6!1s0x88db1d7e5a7b7a49:0x324bd0e63a60dfad!8m2!3d26.2126153!4d-81.7867476!16s%2Fg%2F11k9ml4kb0!19sChIJSXp7Wn4d24gRrd9gOubQSzI</t>
+          <t>https://www.yellowpages.com/naples-fl/mip/exquisite-timepieces-14306847</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, role-email, direct-line, ja, since-1998</t>
         </is>
       </c>
       <c r="S294" t="inlineStr">
@@ -33253,13 +33265,13 @@
       </c>
       <c r="T294" s="2" t="inlineStr">
         <is>
-          <t>https://goldsilvernaples.com/</t>
+          <t>https://www.exquisitetimepieces.com/</t>
         </is>
       </c>
       <c r="U294" t="inlineStr"/>
       <c r="V294" t="inlineStr">
         <is>
-          <t>2026-10-14T01:13:03+05:30</t>
+          <t>2026-10-14T01:47:28+05:30</t>
         </is>
       </c>
       <c r="W294" t="inlineStr"/>
@@ -33270,15 +33282,19 @@
       <c r="Z294" t="inlineStr"/>
       <c r="AA294" t="inlineStr">
         <is>
-          <t>(239) 234-9588</t>
-        </is>
-      </c>
-      <c r="AB294" t="inlineStr"/>
+          <t>(239) 262-4545</t>
+        </is>
+      </c>
+      <c r="AB294" t="inlineStr">
+        <is>
+          <t>https://facebook.com/pages/Exquisite-Timepieces/138888796144728, https://x.com/TimeExquisite, https://instagram.com/exquisitetimepieces, https://facebook.com/Exquisite-Timepieces-138888796144728, https://twitter.com/TimeExquisite</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>International Diamond Center</t>
+          <t>Gold Silver Naples</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -33288,38 +33304,30 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Gold dealer</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>(239) 342-2550</t>
+          <t>(239) 591-5999</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>u003emarketing@shopidc.com</t>
+          <t>goldsilvercoinsofnaples@gmail.com</t>
         </is>
       </c>
       <c r="F295" t="inlineStr"/>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>Keith Leclerc</t>
-        </is>
-      </c>
-      <c r="H295" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
+      <c r="G295" t="inlineStr"/>
+      <c r="H295" t="inlineStr"/>
       <c r="I295" s="2" t="inlineStr">
         <is>
-          <t>https://shopidc.com</t>
+          <t>https://www.goldsilvernaples.com</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>8840 Tamiami Trl N, Naples, FL 34108, United States</t>
+          <t>1575 Pine Ridge Rd Ste 20, Naples, FL 34109, United States</t>
         </is>
       </c>
       <c r="K295" t="inlineStr"/>
@@ -33335,19 +33343,19 @@
         </is>
       </c>
       <c r="O295" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="P295" t="n">
-        <v>278</v>
+        <v>75</v>
       </c>
       <c r="Q295" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/International+Diamond+Center/data=!4m7!3m6!1s0x88db1f3b506da15f:0xd38690aae0aec00b!8m2!3d26.2479716!4d-81.800361!16s%2Fg%2F11t8h0cjn9!19sChIJX6FtUDsf24gRC8Cu4KqQhtM</t>
+          <t>https://www.google.com/maps/place/Gold+Silver+Naples/data=!4m7!3m6!1s0x88db1d7e5a7b7a49:0x324bd0e63a60dfad!8m2!3d26.2126153!4d-81.7867476!16s%2Fg%2F11k9ml4kb0!19sChIJSXp7Wn4d24gRrd9gOubQSzI</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S295" t="inlineStr">
@@ -33357,81 +33365,77 @@
       </c>
       <c r="T295" s="2" t="inlineStr">
         <is>
-          <t>https://shopidc.com/</t>
+          <t>https://goldsilvernaples.com/</t>
         </is>
       </c>
       <c r="U295" t="inlineStr"/>
       <c r="V295" t="inlineStr">
         <is>
-          <t>2026-10-14T01:15:46+05:30</t>
+          <t>2026-10-14T01:13:03+05:30</t>
         </is>
       </c>
       <c r="W295" t="inlineStr"/>
       <c r="X295" t="inlineStr"/>
       <c r="Y295" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z295" t="inlineStr"/>
       <c r="AA295" t="inlineStr">
         <is>
-          <t>(239) 364-1799, (352) 681-4550, (407) 770-5991, (407) 862-8990, (407) 903-9494, (727) 572-6323, (772) 408-4640, (813) 961-0097, (863) 226-4400, (912) 354-4344, (941) 278-3900</t>
-        </is>
-      </c>
-      <c r="AB295" t="inlineStr">
-        <is>
-          <t>https://facebook.com/internationaldiamondcenter, https://instagram.com/internationaldiamondcenter_, https://twitter.com/shopidc</t>
-        </is>
-      </c>
+          <t>(239) 234-9588</t>
+        </is>
+      </c>
+      <c r="AB295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Mark Loren Design</t>
+          <t>International Diamond Center</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Designers</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>(239) 596-5820</t>
+          <t>(239) 342-2550</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>contact@marklorendesigns.com</t>
+          <t>u003emarketing@shopidc.com</t>
         </is>
       </c>
       <c r="F296" t="inlineStr"/>
-      <c r="G296" t="inlineStr"/>
-      <c r="H296" t="inlineStr"/>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Keith Leclerc</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>https://www.marklorendesigns.com</t>
+          <t>https://shopidc.com</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>9118 Strada Pl Ste 8120, Naples, FL 34108</t>
-        </is>
-      </c>
-      <c r="K296" t="inlineStr">
-        <is>
-          <t>Naples</t>
-        </is>
-      </c>
-      <c r="L296" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
+          <t>8840 Tamiami Trl N, Naples, FL 34108, United States</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr"/>
+      <c r="L296" t="inlineStr"/>
       <c r="M296" t="inlineStr">
         <is>
           <t>Naples, FL</t>
@@ -33439,19 +33443,23 @@
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O296" t="inlineStr"/>
-      <c r="P296" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O296" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P296" t="n">
+        <v>278</v>
+      </c>
       <c r="Q296" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/naples-fl/mip/mark-loren-design-475273503</t>
+          <t>https://www.google.com/maps/place/International+Diamond+Center/data=!4m7!3m6!1s0x88db1f3b506da15f:0xd38690aae0aec00b!8m2!3d26.2479716!4d-81.800361!16s%2Fg%2F11t8h0cjn9!19sChIJX6FtUDsf24gRC8Cu4KqQhtM</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, bench, custom-design</t>
+          <t>2 of 3, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S296" t="inlineStr">
@@ -33461,56 +33469,56 @@
       </c>
       <c r="T296" s="2" t="inlineStr">
         <is>
-          <t>https://marklorendesigns.com/</t>
+          <t>https://shopidc.com/</t>
         </is>
       </c>
       <c r="U296" t="inlineStr"/>
       <c r="V296" t="inlineStr">
         <is>
-          <t>2026-10-14T01:47:36+05:30</t>
+          <t>2026-10-14T01:15:46+05:30</t>
         </is>
       </c>
       <c r="W296" t="inlineStr"/>
       <c r="X296" t="inlineStr"/>
       <c r="Y296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z296" t="inlineStr"/>
       <c r="AA296" t="inlineStr">
         <is>
-          <t>(239) 482-4664</t>
+          <t>(239) 364-1799, (352) 681-4550, (407) 770-5991, (407) 862-8990, (407) 903-9494, (727) 572-6323, (772) 408-4640, (813) 961-0097, (863) 226-4400, (912) 354-4344, (941) 278-3900</t>
         </is>
       </c>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>https://facebook.com/marklorendesigns, https://instagram.com/marklorendesign</t>
+          <t>https://facebook.com/internationaldiamondcenter, https://instagram.com/internationaldiamondcenter_, https://twitter.com/shopidc</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Black Rock Galleries</t>
+          <t>Mark Loren Design</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Estate liquidator</t>
+          <t>Jewelers, Jewelry Designers</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>(203) 900-1110</t>
+          <t>(239) 596-5820</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>april@blackrockgalleries.com</t>
+          <t>contact@marklorendesigns.com</t>
         </is>
       </c>
       <c r="F297" t="inlineStr"/>
@@ -33518,48 +33526,44 @@
       <c r="H297" t="inlineStr"/>
       <c r="I297" s="2" t="inlineStr">
         <is>
-          <t>https://www.blackrockgalleries.com</t>
+          <t>https://www.marklorendesigns.com</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>179 Hamilton Ave, Greenwich, CT 06830, United States</t>
+          <t>9118 Strada Pl Ste 8120, Naples, FL 34108</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>Cary</t>
+          <t>Naples</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Greenwich, CT</t>
+          <t>Naples, FL</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O297" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P297" t="n">
-        <v>25</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr"/>
+      <c r="P297" t="inlineStr"/>
       <c r="Q297" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Black+Rock+Galleries/data=!4m7!3m6!1s0x89c299cdad7d8901:0x806db5b713ec68d7!8m2!3d41.0179193!4d-73.6391571!16s%2Fg%2F11ckvlk1pv!19sChIJAYl9rc2ZwokR12jsE7e1bYA</t>
+          <t>https://www.yellowpages.com/naples-fl/mip/mark-loren-design-475273503</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia</t>
+          <t>2 of 3, role-email, direct-line, bench, custom-design</t>
         </is>
       </c>
       <c r="S297" t="inlineStr">
@@ -33569,13 +33573,13 @@
       </c>
       <c r="T297" s="2" t="inlineStr">
         <is>
-          <t>https://www.blackrockgalleries.com/contact</t>
+          <t>https://marklorendesigns.com/</t>
         </is>
       </c>
       <c r="U297" t="inlineStr"/>
       <c r="V297" t="inlineStr">
         <is>
-          <t>2026-10-14T01:19:56+05:30</t>
+          <t>2026-10-14T01:47:36+05:30</t>
         </is>
       </c>
       <c r="W297" t="inlineStr"/>
@@ -33586,19 +33590,19 @@
       <c r="Z297" t="inlineStr"/>
       <c r="AA297" t="inlineStr">
         <is>
-          <t>(203) 335-0000, (203) 335-4444, (919) 702-7000</t>
+          <t>(239) 482-4664</t>
         </is>
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>https://facebook.com/blackrockgalleries, https://twitter.com/BRGalleries, https://instagram.com/blackrockgalleries</t>
+          <t>https://facebook.com/marklorendesigns, https://instagram.com/marklorendesign</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Estate Treasures of Greenwich</t>
+          <t>Black Rock Galleries</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -33608,46 +33612,42 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Furniture store</t>
+          <t>Estate liquidator</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>(203) 637-4200</t>
+          <t>(203) 900-1110</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>hjantiques@aol.com</t>
-        </is>
-      </c>
-      <c r="F298" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/harriet-roughan-8982a220</t>
-        </is>
-      </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>Harriet Roughan</t>
-        </is>
-      </c>
-      <c r="H298" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
+          <t>april@blackrockgalleries.com</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr"/>
+      <c r="G298" t="inlineStr"/>
+      <c r="H298" t="inlineStr"/>
       <c r="I298" s="2" t="inlineStr">
         <is>
-          <t>https://www.estatetreasures.com</t>
+          <t>https://www.blackrockgalleries.com</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>1381 E Putnam Ave, Old Greenwich, CT 06870, United States</t>
-        </is>
-      </c>
-      <c r="K298" t="inlineStr"/>
-      <c r="L298" t="inlineStr"/>
+          <t>179 Hamilton Ave, Greenwich, CT 06830, United States</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Cary</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
       <c r="M298" t="inlineStr">
         <is>
           <t>Greenwich, CT</t>
@@ -33659,39 +33659,35 @@
         </is>
       </c>
       <c r="O298" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="P298" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="Q298" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Estate+Treasures+of+Greenwich/data=!4m7!3m6!1s0x89c298bd469b9045:0x4341ef96fb235d28!8m2!3d41.0447405!4d-73.5728257!16s%2Fg%2F1tg4xsb0!19sChIJRZCbRr2YwokRKF0j-5bvQUM</t>
+          <t>https://www.google.com/maps/place/Black+Rock+Galleries/data=!4m7!3m6!1s0x89c299cdad7d8901:0x806db5b713ec68d7!8m2!3d41.0179193!4d-73.6391571!16s%2Fg%2F11ckvlk1pv!19sChIJAYl9rc2ZwokR12jsE7e1bYA</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>2 of 3, custom-design</t>
+          <t>2 of 3, direct-line, gia</t>
         </is>
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="T298" s="2" t="inlineStr">
         <is>
-          <t>https://estatetreasures.com/</t>
-        </is>
-      </c>
-      <c r="U298" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=%22Harriet+Roughan%22+Greenwich+linkedin&amp;hl=en&amp;num=10</t>
-        </is>
-      </c>
+          <t>https://www.blackrockgalleries.com/contact</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr"/>
       <c r="V298" t="inlineStr">
         <is>
-          <t>2026-10-14T01:18:54+05:30</t>
+          <t>2026-10-14T01:19:56+05:30</t>
         </is>
       </c>
       <c r="W298" t="inlineStr"/>
@@ -33700,62 +33696,70 @@
         <v>0</v>
       </c>
       <c r="Z298" t="inlineStr"/>
-      <c r="AA298" t="inlineStr"/>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>(203) 335-0000, (203) 335-4444, (919) 702-7000</t>
+        </is>
+      </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>https://facebook.com/EstateTreasuresGreenwich, https://instagram.com/estatetreasuresgreenwich</t>
+          <t>https://facebook.com/blackrockgalleries, https://twitter.com/BRGalleries, https://instagram.com/blackrockgalleries</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Fine Elegant Jewelry</t>
+          <t>Estate Treasures of Greenwich</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Furniture store</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>(914) 937-2045</t>
+          <t>(203) 637-4200</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>elegantempirejewelers@gmail.com</t>
-        </is>
-      </c>
-      <c r="F299" t="inlineStr"/>
-      <c r="G299" t="inlineStr"/>
-      <c r="H299" t="inlineStr"/>
+          <t>hjantiques@aol.com</t>
+        </is>
+      </c>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/harriet-roughan-8982a220</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>Harriet Roughan</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>https://eejewelers.com</t>
+          <t>https://www.estatetreasures.com</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>27 N Main St, Port Chester, NY 10573</t>
-        </is>
-      </c>
-      <c r="K299" t="inlineStr">
-        <is>
-          <t>Port Chester</t>
-        </is>
-      </c>
-      <c r="L299" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
+          <t>1381 E Putnam Ave, Old Greenwich, CT 06870, United States</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr"/>
+      <c r="L299" t="inlineStr"/>
       <c r="M299" t="inlineStr">
         <is>
           <t>Greenwich, CT</t>
@@ -33763,90 +33767,82 @@
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O299" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="P299" t="n">
-        <v>115</v>
+        <v>45</v>
       </c>
       <c r="Q299" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/port-chester-ny/mip/fine-elegant-jewelry-482445004</t>
+          <t>https://www.google.com/maps/place/Estate+Treasures+of+Greenwich/data=!4m7!3m6!1s0x89c298bd469b9045:0x4341ef96fb235d28!8m2!3d41.0447405!4d-73.5728257!16s%2Fg%2F1tg4xsb0!19sChIJRZCbRr2YwokRKF0j-5bvQUM</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design</t>
+          <t>2 of 3, custom-design</t>
         </is>
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T299" s="2" t="inlineStr">
         <is>
-          <t>https://eejewelers.com/</t>
-        </is>
-      </c>
-      <c r="U299" t="inlineStr"/>
+          <t>https://estatetreasures.com/</t>
+        </is>
+      </c>
+      <c r="U299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Harriet+Roughan%22+Greenwich+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V299" t="inlineStr">
         <is>
-          <t>2026-10-14T01:48:10+05:30</t>
-        </is>
-      </c>
-      <c r="W299" t="inlineStr">
-        <is>
-          <t>Elegant Empire Jewelers</t>
-        </is>
-      </c>
+          <t>2026-10-14T01:18:54+05:30</t>
+        </is>
+      </c>
+      <c r="W299" t="inlineStr"/>
       <c r="X299" t="inlineStr"/>
       <c r="Y299" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z299" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
-      <c r="AA299" t="inlineStr">
-        <is>
-          <t>(914) 305-3385</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z299" t="inlineStr"/>
+      <c r="AA299" t="inlineStr"/>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>https://instagram.com/eejewelers/, https://facebook.com/EEJewelers</t>
+          <t>https://facebook.com/EstateTreasuresGreenwich, https://instagram.com/estatetreasuresgreenwich</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Steven Fox Jewelry</t>
+          <t>Fine Elegant Jewelry</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>(203) 344-5409</t>
+          <t>(914) 937-2045</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>concierge@stevenfoxjewelry.com</t>
+          <t>elegantempirejewelers@gmail.com</t>
         </is>
       </c>
       <c r="F300" t="inlineStr"/>
@@ -33854,22 +33850,22 @@
       <c r="H300" t="inlineStr"/>
       <c r="I300" s="2" t="inlineStr">
         <is>
-          <t>https://www.stevenfoxjewelry.com</t>
+          <t>https://eejewelers.com</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>8 Lewis St, Greenwich, CT 06830, United States</t>
+          <t>27 N Main St, Port Chester, NY 10573</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>Greenwich</t>
+          <t>Port Chester</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -33879,23 +33875,23 @@
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O300" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P300" t="n">
-        <v>277</v>
+        <v>115</v>
       </c>
       <c r="Q300" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Steven+Fox+Jewelry/data=!4m7!3m6!1s0x89c298489c931a41:0x67f0cb095f8447aa!8m2!3d41.0287029!4d-73.6255657!16s%2Fg%2F1thn6fp7!19sChIJQRqTnEiYwokRqkeEXwnL8Gc</t>
+          <t>https://www.yellowpages.com/port-chester-ny/mip/fine-elegant-jewelry-482445004</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, direct-line, gia, custom-design</t>
         </is>
       </c>
       <c r="S300" t="inlineStr">
@@ -33905,56 +33901,64 @@
       </c>
       <c r="T300" s="2" t="inlineStr">
         <is>
-          <t>https://www.stevenfoxjewelry.com/</t>
+          <t>https://eejewelers.com/</t>
         </is>
       </c>
       <c r="U300" t="inlineStr"/>
       <c r="V300" t="inlineStr">
         <is>
-          <t>2026-10-14T01:17:44+05:30</t>
-        </is>
-      </c>
-      <c r="W300" t="inlineStr"/>
+          <t>2026-10-14T01:48:10+05:30</t>
+        </is>
+      </c>
+      <c r="W300" t="inlineStr">
+        <is>
+          <t>Elegant Empire Jewelers</t>
+        </is>
+      </c>
       <c r="X300" t="inlineStr"/>
       <c r="Y300" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z300" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Z300" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA300" t="inlineStr">
         <is>
-          <t>(203) 629-3303</t>
+          <t>(914) 305-3385</t>
         </is>
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>https://instagram.com/stevenfoxjewelry, https://facebook.com/stevenfoxjewelry</t>
+          <t>https://instagram.com/eejewelers/, https://facebook.com/EEJewelers</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Triple G Fine Jewelry Inc</t>
+          <t>Steven Fox Jewelry</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>shop=jewelry</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>(914) 937-2931</t>
+          <t>(203) 344-5409</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>rakhmin20@icloud.com</t>
+          <t>concierge@stevenfoxjewelry.com</t>
         </is>
       </c>
       <c r="F301" t="inlineStr"/>
@@ -33962,22 +33966,22 @@
       <c r="H301" t="inlineStr"/>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>https://triplegjewelry.rafaelsjewelrystore.com</t>
+          <t>https://www.stevenfoxjewelry.com</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>38 South Main Street, Port Chester, NY 10573</t>
+          <t>8 Lewis St, Greenwich, CT 06830, United States</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>Port Chester</t>
+          <t>Greenwich</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
@@ -33987,23 +33991,23 @@
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>OpenStreetMap</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O301" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="P301" t="n">
-        <v>26</v>
+        <v>277</v>
       </c>
       <c r="Q301" s="2" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/10302134827</t>
+          <t>https://www.google.com/maps/place/Steven+Fox+Jewelry/data=!4m7!3m6!1s0x89c298489c931a41:0x67f0cb095f8447aa!8m2!3d41.0287029!4d-73.6255657!16s%2Fg%2F1thn6fp7!19sChIJQRqTnEiYwokRqkeEXwnL8Gc</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S301" t="inlineStr">
@@ -34013,40 +34017,36 @@
       </c>
       <c r="T301" s="2" t="inlineStr">
         <is>
-          <t>https://triplegjewelry.rafaelsjewelrystore.com/</t>
+          <t>https://www.stevenfoxjewelry.com/</t>
         </is>
       </c>
       <c r="U301" t="inlineStr"/>
       <c r="V301" t="inlineStr">
         <is>
-          <t>2026-10-14T01:19:19+05:30</t>
-        </is>
-      </c>
-      <c r="W301" t="inlineStr">
-        <is>
-          <t>Triple J Fine Jewelry Inc, Triple J Jew Jewelry</t>
-        </is>
-      </c>
+          <t>2026-10-14T01:17:44+05:30</t>
+        </is>
+      </c>
+      <c r="W301" t="inlineStr"/>
       <c r="X301" t="inlineStr"/>
       <c r="Y301" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z301" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Z301" t="inlineStr"/>
       <c r="AA301" t="inlineStr">
         <is>
-          <t>(917) 535-4155</t>
-        </is>
-      </c>
-      <c r="AB301" t="inlineStr"/>
+          <t>(203) 629-3303</t>
+        </is>
+      </c>
+      <c r="AB301" t="inlineStr">
+        <is>
+          <t>https://instagram.com/stevenfoxjewelry, https://facebook.com/stevenfoxjewelry</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Arlex Jewelry Watches &amp; Clocks</t>
+          <t>Triple G Fine Jewelry Inc</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -34056,17 +34056,17 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>shop=jewelry</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>(561) 641-8162</t>
+          <t>(914) 937-2931</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>info@arlexjewelry.com</t>
+          <t>rakhmin20@icloud.com</t>
         </is>
       </c>
       <c r="F302" t="inlineStr"/>
@@ -34074,48 +34074,48 @@
       <c r="H302" t="inlineStr"/>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>https://arlexjewelry.com</t>
+          <t>https://triplegjewelry.rafaelsjewelrystore.com</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>808 Lake Ave, Lake Worth Beach, FL 33460, United States</t>
+          <t>38 South Main Street, Port Chester, NY 10573</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>Lake Worth Beach</t>
+          <t>Port Chester</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Palm Beach, FL</t>
+          <t>Greenwich, CT</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>OpenStreetMap</t>
         </is>
       </c>
       <c r="O302" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="P302" t="n">
-        <v>105</v>
+        <v>26</v>
       </c>
       <c r="Q302" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Arlex+Jewelry+Watches+%26+Clocks/data=!4m7!3m6!1s0x88d8d834517d5a4d:0x1255d4758f02268f!8m2!3d26.6160147!4d-80.0567684!16s%2Fg%2F1tkc2xb0!19sChIJTVp9UTTY2IgRjyYCj3XUVRI</t>
+          <t>https://www.openstreetmap.org/node/10302134827</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-1987</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S302" t="inlineStr">
@@ -34125,18 +34125,18 @@
       </c>
       <c r="T302" s="2" t="inlineStr">
         <is>
-          <t>https://arlexjewelry.com/contact/</t>
+          <t>https://triplegjewelry.rafaelsjewelrystore.com/</t>
         </is>
       </c>
       <c r="U302" t="inlineStr"/>
       <c r="V302" t="inlineStr">
         <is>
-          <t>2026-10-14T01:30:48+05:30</t>
+          <t>2026-10-14T01:19:19+05:30</t>
         </is>
       </c>
       <c r="W302" t="inlineStr">
         <is>
-          <t>Arlex Jewelry Watches, Arlex Clocks, Arlex Jewelry &amp; Clocks</t>
+          <t>Triple J Fine Jewelry Inc, Triple J Jew Jewelry</t>
         </is>
       </c>
       <c r="X302" t="inlineStr"/>
@@ -34150,39 +34150,35 @@
       </c>
       <c r="AA302" t="inlineStr">
         <is>
-          <t>(561) 876-7030</t>
-        </is>
-      </c>
-      <c r="AB302" t="inlineStr">
-        <is>
-          <t>https://facebook.com/Arlex-Jewelry-Watches-Clocks-811607869050062, https://twitter.com/arlexclocks, https://instagram.com/arlexjewelry11, https://facebook.com/ArlexJewelry, https://twitter.com/ArlexClocks</t>
-        </is>
-      </c>
+          <t>(917) 535-4155</t>
+        </is>
+      </c>
+      <c r="AB302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Gemstone Gallery</t>
+          <t>Arlex Jewelry Watches &amp; Clocks</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Designers</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>(561) 586-8868</t>
+          <t>(561) 641-8162</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>info@mygemstonegallery.com</t>
+          <t>info@arlexjewelry.com</t>
         </is>
       </c>
       <c r="F303" t="inlineStr"/>
@@ -34190,12 +34186,24 @@
       <c r="H303" t="inlineStr"/>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>https://www.mygemstonegallery.com</t>
-        </is>
-      </c>
-      <c r="J303" t="inlineStr"/>
-      <c r="K303" t="inlineStr"/>
-      <c r="L303" t="inlineStr"/>
+          <t>https://arlexjewelry.com</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>808 Lake Ave, Lake Worth Beach, FL 33460, United States</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Lake Worth Beach</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
       <c r="M303" t="inlineStr">
         <is>
           <t>Palm Beach, FL</t>
@@ -34203,19 +34211,23 @@
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O303" t="inlineStr"/>
-      <c r="P303" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O303" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P303" t="n">
+        <v>105</v>
+      </c>
       <c r="Q303" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/nationwide/mip/gemstone-gallery-451204537</t>
+          <t>https://www.google.com/maps/place/Arlex+Jewelry+Watches+%26+Clocks/data=!4m7!3m6!1s0x88d8d834517d5a4d:0x1255d4758f02268f!8m2!3d26.6160147!4d-80.0567684!16s%2Fg%2F1tkc2xb0!19sChIJTVp9UTTY2IgRjyYCj3XUVRI</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-1987</t>
         </is>
       </c>
       <c r="S303" t="inlineStr">
@@ -34225,60 +34237,64 @@
       </c>
       <c r="T303" s="2" t="inlineStr">
         <is>
-          <t>https://www.mygemstonegallery.com/</t>
+          <t>https://arlexjewelry.com/contact/</t>
         </is>
       </c>
       <c r="U303" t="inlineStr"/>
       <c r="V303" t="inlineStr">
         <is>
-          <t>2026-10-14T01:50:22+05:30</t>
-        </is>
-      </c>
-      <c r="W303" t="inlineStr"/>
+          <t>2026-10-14T01:30:48+05:30</t>
+        </is>
+      </c>
+      <c r="W303" t="inlineStr">
+        <is>
+          <t>Arlex Jewelry Watches, Arlex Clocks, Arlex Jewelry &amp; Clocks</t>
+        </is>
+      </c>
       <c r="X303" t="inlineStr"/>
       <c r="Y303" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z303" t="inlineStr">
         <is>
-          <t>no-address</t>
+          <t>chain</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr">
         <is>
-          <t>(917) 406-0779</t>
+          <t>(561) 876-7030</t>
         </is>
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>https://facebook.com/SuzanneHDeBow, https://twitter.com/GemstoneGallery, https://instagram.com/mygemstone_gallery</t>
+          <t>https://facebook.com/Arlex-Jewelry-Watches-Clocks-811607869050062, https://twitter.com/arlexclocks, https://instagram.com/arlexjewelry11, https://facebook.com/ArlexJewelry, https://twitter.com/ArlexClocks</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Hamilton Jewelers</t>
+          <t>Gemstone Gallery</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Jeweler</t>
+          <t>Jewelers, Jewelry Designers</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>(561) 659-6788</t>
+          <t>(561) 586-8868</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>emartano@hamiltonjewelers.com</t>
+          <t>info@mygemstonegallery.com</t>
         </is>
       </c>
       <c r="F304" t="inlineStr"/>
@@ -34286,24 +34302,12 @@
       <c r="H304" t="inlineStr"/>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>https://hamiltonjewelers.com</t>
-        </is>
-      </c>
-      <c r="J304" t="inlineStr">
-        <is>
-          <t>215 Worth Ave, Palm Beach, FL 33480, United States</t>
-        </is>
-      </c>
-      <c r="K304" t="inlineStr">
-        <is>
-          <t>Palm Beach Gardens</t>
-        </is>
-      </c>
-      <c r="L304" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
+          <t>https://www.mygemstonegallery.com</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr"/>
+      <c r="K304" t="inlineStr"/>
+      <c r="L304" t="inlineStr"/>
       <c r="M304" t="inlineStr">
         <is>
           <t>Palm Beach, FL</t>
@@ -34311,23 +34315,19 @@
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O304" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P304" t="n">
-        <v>77</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr"/>
+      <c r="P304" t="inlineStr"/>
       <c r="Q304" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Hamilton+Jewelers/data=!4m7!3m6!1s0x88d8d6ec71416949:0x1f20ced2ff0489d1!8m2!3d26.7009363!4d-80.0371549!16s%2Fg%2F1tfz0xfv!19sChIJSWlBcezW2IgR0YkE_9LOIB8</t>
+          <t>https://www.yellowpages.com/nationwide/mip/gemstone-gallery-451204537</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design, since-1912</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S304" t="inlineStr">
@@ -34337,56 +34337,60 @@
       </c>
       <c r="T304" s="2" t="inlineStr">
         <is>
-          <t>https://hamiltonjewelers.com/</t>
+          <t>https://www.mygemstonegallery.com/</t>
         </is>
       </c>
       <c r="U304" t="inlineStr"/>
       <c r="V304" t="inlineStr">
         <is>
-          <t>2026-10-14T01:25:01+05:30</t>
+          <t>2026-10-14T01:50:22+05:30</t>
         </is>
       </c>
       <c r="W304" t="inlineStr"/>
       <c r="X304" t="inlineStr"/>
       <c r="Y304" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z304" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Z304" t="inlineStr">
+        <is>
+          <t>no-address</t>
+        </is>
+      </c>
       <c r="AA304" t="inlineStr">
         <is>
-          <t>(609) 375-8003</t>
+          <t>(917) 406-0779</t>
         </is>
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>https://instagram.com/hamiltonjewelers, https://facebook.com/HamiltonJeweler</t>
+          <t>https://facebook.com/SuzanneHDeBow, https://twitter.com/GemstoneGallery, https://instagram.com/mygemstone_gallery</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Raymond Lee Jewelers</t>
+          <t>Hamilton Jewelers</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jeweler</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>(561) 622-7744</t>
+          <t>(561) 659-6788</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>info@raymondleejewelers.net</t>
+          <t>emartano@hamiltonjewelers.com</t>
         </is>
       </c>
       <c r="F305" t="inlineStr"/>
@@ -34394,12 +34398,12 @@
       <c r="H305" t="inlineStr"/>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>https://www.raymondleejewelers.net</t>
+          <t>https://hamiltonjewelers.com</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>500 Village Square Xing, Palm Beach Gardens, FL 33410</t>
+          <t>215 Worth Ave, Palm Beach, FL 33480, United States</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
@@ -34419,19 +34423,23 @@
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O305" t="inlineStr"/>
-      <c r="P305" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O305" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P305" t="n">
+        <v>77</v>
+      </c>
       <c r="Q305" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/palm-beach-gardens-fl/mip/raymond-lee-jewelers-3693798</t>
+          <t>https://www.google.com/maps/place/Hamilton+Jewelers/data=!4m7!3m6!1s0x88d8d6ec71416949:0x1f20ced2ff0489d1!8m2!3d26.7009363!4d-80.0371549!16s%2Fg%2F1tfz0xfv!19sChIJSWlBcezW2IgR0YkE_9LOIB8</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1983</t>
+          <t>2 of 3, direct-line, gia, custom-design, since-1912</t>
         </is>
       </c>
       <c r="S305" t="inlineStr">
@@ -34441,56 +34449,56 @@
       </c>
       <c r="T305" s="2" t="inlineStr">
         <is>
-          <t>https://raymondleejewelers.net/pages/contact</t>
+          <t>https://hamiltonjewelers.com/</t>
         </is>
       </c>
       <c r="U305" t="inlineStr"/>
       <c r="V305" t="inlineStr">
         <is>
-          <t>2026-10-14T01:50:37+05:30</t>
+          <t>2026-10-14T01:25:01+05:30</t>
         </is>
       </c>
       <c r="W305" t="inlineStr"/>
       <c r="X305" t="inlineStr"/>
       <c r="Y305" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z305" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Z305" t="inlineStr"/>
       <c r="AA305" t="inlineStr">
         <is>
-          <t>(561) 750-7808</t>
-        </is>
-      </c>
-      <c r="AB305" t="inlineStr"/>
+          <t>(609) 375-8003</t>
+        </is>
+      </c>
+      <c r="AB305" t="inlineStr">
+        <is>
+          <t>https://instagram.com/hamiltonjewelers, https://facebook.com/HamiltonJeweler</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Signature Diamonds</t>
+          <t>Raymond Lee Jewelers</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Jewelers, Diamonds</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>(561) 686-5730</t>
+          <t>(561) 622-7744</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>signaturebuyers@yahoo.com</t>
+          <t>info@raymondleejewelers.net</t>
         </is>
       </c>
       <c r="F306" t="inlineStr"/>
@@ -34498,17 +34506,17 @@
       <c r="H306" t="inlineStr"/>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>https://sellyourdiamondsflorida.com</t>
+          <t>https://www.raymondleejewelers.net</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>2200 N Florida Mango Rd, West Palm Beach, FL 33409</t>
+          <t>500 Village Square Xing, Palm Beach Gardens, FL 33410</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>West Palm Beach</t>
+          <t>Palm Beach Gardens</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -34530,12 +34538,12 @@
       <c r="P306" t="inlineStr"/>
       <c r="Q306" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/west-palm-beach-fl/mip/signature-diamonds-538406637</t>
+          <t>https://www.yellowpages.com/palm-beach-gardens-fl/mip/raymond-lee-jewelers-3693798</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design, since-1945</t>
+          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1983</t>
         </is>
       </c>
       <c r="S306" t="inlineStr">
@@ -34545,36 +34553,36 @@
       </c>
       <c r="T306" s="2" t="inlineStr">
         <is>
-          <t>https://sellyourdiamondsflorida.com/</t>
+          <t>https://raymondleejewelers.net/pages/contact</t>
         </is>
       </c>
       <c r="U306" t="inlineStr"/>
       <c r="V306" t="inlineStr">
         <is>
-          <t>2026-10-14T01:50:22+05:30</t>
+          <t>2026-10-14T01:50:37+05:30</t>
         </is>
       </c>
       <c r="W306" t="inlineStr"/>
       <c r="X306" t="inlineStr"/>
       <c r="Y306" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z306" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="Z306" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA306" t="inlineStr">
         <is>
-          <t>(772) 562-6893</t>
-        </is>
-      </c>
-      <c r="AB306" t="inlineStr">
-        <is>
-          <t>https://facebook.com/pages/Signature-Estate-Diamond-Buyers/699915383378286, https://twitter.com/signaturebuyer</t>
-        </is>
-      </c>
+          <t>(561) 750-7808</t>
+        </is>
+      </c>
+      <c r="AB306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>WPBWatchCo</t>
+          <t>Signature Diamonds</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -34584,42 +34592,30 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Watch store</t>
+          <t>Jewelers, Diamonds</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>(561) 220-9107</t>
+          <t>(561) 686-5730</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>arinaldi@wpbwatchco.com</t>
-        </is>
-      </c>
-      <c r="F307" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/anthony-rinaldi-0293451b</t>
-        </is>
-      </c>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t>Anthony Rinaldi</t>
-        </is>
-      </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
+          <t>signaturebuyers@yahoo.com</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr"/>
+      <c r="G307" t="inlineStr"/>
+      <c r="H307" t="inlineStr"/>
       <c r="I307" s="2" t="inlineStr">
         <is>
-          <t>https://www.wpbwatchco.com</t>
+          <t>https://sellyourdiamondsflorida.com</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>1601 Forum Pl #1010, West Palm Beach, FL 33401, United States</t>
+          <t>2200 N Florida Mango Rd, West Palm Beach, FL 33409</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
@@ -34639,62 +34635,58 @@
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O307" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P307" t="n">
-        <v>622</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr"/>
+      <c r="P307" t="inlineStr"/>
       <c r="Q307" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/WPBWatchCo/data=!4m7!3m6!1s0x88d91e304542d111:0xdd417b5f344332dc!8m2!3d26.7271055!4d-80.0794774!16s%2Fg%2F11dymb1krc!19sChIJEdFCRTAe2YgR3DJDNF97Qd0</t>
+          <t>https://www.yellowpages.com/west-palm-beach-fl/mip/signature-diamonds-538406637</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>2 of 3, since-2015</t>
+          <t>2 of 3, direct-line, gia, custom-design, since-1945</t>
         </is>
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="T307" s="2" t="inlineStr">
         <is>
-          <t>https://wpbwatchco.com/</t>
-        </is>
-      </c>
-      <c r="U307" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=%22Anthony+Rinaldi%22+Palm+Beach+linkedin&amp;hl=en&amp;num=10</t>
-        </is>
-      </c>
+          <t>https://sellyourdiamondsflorida.com/</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr"/>
       <c r="V307" t="inlineStr">
         <is>
-          <t>2026-10-14T01:27:35+05:30</t>
+          <t>2026-10-14T01:50:22+05:30</t>
         </is>
       </c>
       <c r="W307" t="inlineStr"/>
       <c r="X307" t="inlineStr"/>
       <c r="Y307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z307" t="inlineStr"/>
-      <c r="AA307" t="inlineStr"/>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>(772) 562-6893</t>
+        </is>
+      </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>https://instagram.com/wpb_watch_co, https://facebook.com/anthony.rinaldi.7370</t>
+          <t>https://facebook.com/pages/Signature-Estate-Diamond-Buyers/699915383378286, https://twitter.com/signaturebuyer</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>YAFA Palm Beach</t>
+          <t>WPBWatchCo</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -34704,35 +34696,47 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Watch store</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>(561) 331-8611</t>
+          <t>(561) 220-9107</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>inquire@yafajewelry.com</t>
-        </is>
-      </c>
-      <c r="F308" t="inlineStr"/>
-      <c r="G308" t="inlineStr"/>
-      <c r="H308" t="inlineStr"/>
+          <t>arinaldi@wpbwatchco.com</t>
+        </is>
+      </c>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anthony-rinaldi-0293451b</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>Anthony Rinaldi</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="I308" s="2" t="inlineStr">
         <is>
-          <t>https://yafasignedjewels.com</t>
+          <t>https://www.wpbwatchco.com</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>234 Worth Ave, Palm Beach, FL 33480, United States</t>
+          <t>1601 Forum Pl #1010, West Palm Beach, FL 33401, United States</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>Palm Beach</t>
+          <t>West Palm Beach</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
@@ -34751,82 +34755,78 @@
         </is>
       </c>
       <c r="O308" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P308" t="n">
-        <v>9</v>
+        <v>622</v>
       </c>
       <c r="Q308" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/YAFA+Palm+Beach/data=!4m7!3m6!1s0x89c258fef868bda1:0x84b1b16f5ab524a9!8m2!3d26.7006755!4d-80.0378935!16s%2Fg%2F1td4l0sf!19sChIJob1o-P5YwokRqSS1Wm-xsYQ</t>
+          <t>https://www.google.com/maps/place/WPBWatchCo/data=!4m7!3m6!1s0x88d91e304542d111:0xdd417b5f344332dc!8m2!3d26.7271055!4d-80.0794774!16s%2Fg%2F11dymb1krc!19sChIJEdFCRTAe2YgR3DJDNF97Qd0</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, since-1985</t>
+          <t>2 of 3, since-2015</t>
         </is>
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T308" s="2" t="inlineStr">
         <is>
-          <t>https://yafasignedjewels.com/pages/contact</t>
-        </is>
-      </c>
-      <c r="U308" t="inlineStr"/>
+          <t>https://wpbwatchco.com/</t>
+        </is>
+      </c>
+      <c r="U308" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Anthony+Rinaldi%22+Palm+Beach+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V308" t="inlineStr">
         <is>
-          <t>2026-10-14T01:26:21+05:30</t>
-        </is>
-      </c>
-      <c r="W308" t="inlineStr">
-        <is>
-          <t>Yafa Signed Jewels</t>
-        </is>
-      </c>
+          <t>2026-10-14T01:27:35+05:30</t>
+        </is>
+      </c>
+      <c r="W308" t="inlineStr"/>
       <c r="X308" t="inlineStr"/>
       <c r="Y308" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z308" t="inlineStr"/>
-      <c r="AA308" t="inlineStr">
-        <is>
-          <t>(212) 719-9828, (516) 331-8611</t>
-        </is>
-      </c>
+      <c r="AA308" t="inlineStr"/>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>https://facebook.com/YafaSignedJewels, https://instagram.com/yafasignedjewels</t>
+          <t>https://instagram.com/wpb_watch_co, https://facebook.com/anthony.rinaldi.7370</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Gold Gods</t>
+          <t>YAFA Palm Beach</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>(816) 721-9850</t>
+          <t>(561) 331-8611</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>support@thegoldgods.com</t>
+          <t>inquire@yafajewelry.com</t>
         </is>
       </c>
       <c r="F309" t="inlineStr"/>
@@ -34834,44 +34834,48 @@
       <c r="H309" t="inlineStr"/>
       <c r="I309" s="2" t="inlineStr">
         <is>
-          <t>https://thegoldgods.com</t>
+          <t>https://yafasignedjewels.com</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>450 N Fairfax Ave, Los Angeles, CA 90036</t>
+          <t>234 Worth Ave, Palm Beach, FL 33480, United States</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Palm Beach</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Beverly Hills, CA</t>
+          <t>Palm Beach, FL</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O309" t="inlineStr"/>
-      <c r="P309" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O309" t="n">
+        <v>5</v>
+      </c>
+      <c r="P309" t="n">
+        <v>9</v>
+      </c>
       <c r="Q309" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/los-angeles-ca/mip/gold-gods-548160699</t>
+          <t>https://www.google.com/maps/place/YAFA+Palm+Beach/data=!4m7!3m6!1s0x89c258fef868bda1:0x84b1b16f5ab524a9!8m2!3d26.7006755!4d-80.0378935!16s%2Fg%2F1td4l0sf!19sChIJob1o-P5YwokRqSS1Wm-xsYQ</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, direct-line, since-1985</t>
         </is>
       </c>
       <c r="S309" t="inlineStr">
@@ -34881,52 +34885,60 @@
       </c>
       <c r="T309" s="2" t="inlineStr">
         <is>
-          <t>https://thegoldgods.com/pages/contact</t>
+          <t>https://yafasignedjewels.com/pages/contact</t>
         </is>
       </c>
       <c r="U309" t="inlineStr"/>
       <c r="V309" t="inlineStr">
         <is>
-          <t>2026-10-14T01:52:07+05:30</t>
-        </is>
-      </c>
-      <c r="W309" t="inlineStr"/>
+          <t>2026-10-14T01:26:21+05:30</t>
+        </is>
+      </c>
+      <c r="W309" t="inlineStr">
+        <is>
+          <t>Yafa Signed Jewels</t>
+        </is>
+      </c>
       <c r="X309" t="inlineStr"/>
       <c r="Y309" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z309" t="inlineStr"/>
       <c r="AA309" t="inlineStr">
         <is>
-          <t>(816) 323-6447</t>
-        </is>
-      </c>
-      <c r="AB309" t="inlineStr"/>
+          <t>(212) 719-9828, (516) 331-8611</t>
+        </is>
+      </c>
+      <c r="AB309" t="inlineStr">
+        <is>
+          <t>https://facebook.com/YafaSignedJewels, https://instagram.com/yafasignedjewels</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Golden State</t>
+          <t>Gold Gods</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>(213) 629-2130</t>
+          <t>(816) 721-9850</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>sales@goldenstatejewelry.com</t>
+          <t>support@thegoldgods.com</t>
         </is>
       </c>
       <c r="F310" t="inlineStr"/>
@@ -34934,12 +34946,12 @@
       <c r="H310" t="inlineStr"/>
       <c r="I310" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldenstatejewelry.com</t>
+          <t>https://thegoldgods.com</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>550 S Hill St Ste 825, Los Angeles, CA 90013</t>
+          <t>450 N Fairfax Ave, Los Angeles, CA 90036</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
@@ -34962,20 +34974,16 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O310" t="n">
-        <v>5</v>
-      </c>
-      <c r="P310" t="n">
-        <v>1</v>
-      </c>
+      <c r="O310" t="inlineStr"/>
+      <c r="P310" t="inlineStr"/>
       <c r="Q310" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/los-angeles-ca/mip/golden-state-467565356</t>
+          <t>https://www.yellowpages.com/los-angeles-ca/mip/gold-gods-548160699</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, bench, custom-design, since-1978</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S310" t="inlineStr">
@@ -34985,44 +34993,32 @@
       </c>
       <c r="T310" s="2" t="inlineStr">
         <is>
-          <t>https://goldenstatejewelry.com/</t>
+          <t>https://thegoldgods.com/pages/contact</t>
         </is>
       </c>
       <c r="U310" t="inlineStr"/>
       <c r="V310" t="inlineStr">
         <is>
-          <t>2026-10-14T01:52:45+05:30</t>
-        </is>
-      </c>
-      <c r="W310" t="inlineStr">
-        <is>
-          <t>Golden Star Jewelry</t>
-        </is>
-      </c>
-      <c r="X310" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
+          <t>2026-10-14T01:52:07+05:30</t>
+        </is>
+      </c>
+      <c r="W310" t="inlineStr"/>
+      <c r="X310" t="inlineStr"/>
       <c r="Y310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z310" t="inlineStr"/>
       <c r="AA310" t="inlineStr">
         <is>
-          <t>(213) 627-9677</t>
-        </is>
-      </c>
-      <c r="AB310" t="inlineStr">
-        <is>
-          <t>https://instagram.com/goldenstatejewelryla</t>
-        </is>
-      </c>
+          <t>(816) 323-6447</t>
+        </is>
+      </c>
+      <c r="AB310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Hoorsenbuhs</t>
+          <t>Golden State</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -35032,17 +35028,17 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>(888) 692-2997</t>
+          <t>(213) 629-2130</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>info@hoorsenbuhs.com</t>
+          <t>sales@goldenstatejewelry.com</t>
         </is>
       </c>
       <c r="F311" t="inlineStr"/>
@@ -35050,17 +35046,17 @@
       <c r="H311" t="inlineStr"/>
       <c r="I311" s="2" t="inlineStr">
         <is>
-          <t>https://hoorsenbuhs.com</t>
+          <t>https://www.goldenstatejewelry.com</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>2217 Main St, Santa Monica, CA 90405</t>
+          <t>550 S Hill St Ste 825, Los Angeles, CA 90013</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
@@ -35078,16 +35074,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O311" t="inlineStr"/>
-      <c r="P311" t="inlineStr"/>
+      <c r="O311" t="n">
+        <v>5</v>
+      </c>
+      <c r="P311" t="n">
+        <v>1</v>
+      </c>
       <c r="Q311" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/santa-monica-ca/mip/hoorsenbuhs-551622669</t>
+          <t>https://www.yellowpages.com/los-angeles-ca/mip/golden-state-467565356</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line</t>
+          <t>2 of 3, role-email, direct-line, bench, custom-design, since-1978</t>
         </is>
       </c>
       <c r="S311" t="inlineStr">
@@ -35097,40 +35097,44 @@
       </c>
       <c r="T311" s="2" t="inlineStr">
         <is>
-          <t>https://hoorsenbuhs.com/</t>
+          <t>https://goldenstatejewelry.com/</t>
         </is>
       </c>
       <c r="U311" t="inlineStr"/>
       <c r="V311" t="inlineStr">
         <is>
-          <t>2026-10-14T01:53:36+05:30</t>
-        </is>
-      </c>
-      <c r="W311" t="inlineStr"/>
-      <c r="X311" t="inlineStr"/>
+          <t>2026-10-14T01:52:45+05:30</t>
+        </is>
+      </c>
+      <c r="W311" t="inlineStr">
+        <is>
+          <t>Golden Star Jewelry</t>
+        </is>
+      </c>
+      <c r="X311" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
       <c r="Y311" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z311" t="inlineStr">
-        <is>
-          <t>toll-free</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Z311" t="inlineStr"/>
       <c r="AA311" t="inlineStr">
         <is>
-          <t>(917) 206-9333</t>
+          <t>(213) 627-9677</t>
         </is>
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>https://instagram.com/hoorsenbuhs</t>
+          <t>https://instagram.com/goldenstatejewelryla</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Jennifer Fisher Jewelry</t>
+          <t>Hoorsenbuhs</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -35140,17 +35144,17 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>(424) 374-5303</t>
+          <t>(888) 692-2997</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>la@jenniferfisher.com</t>
+          <t>info@hoorsenbuhs.com</t>
         </is>
       </c>
       <c r="F312" t="inlineStr"/>
@@ -35158,16 +35162,24 @@
       <c r="H312" t="inlineStr"/>
       <c r="I312" s="2" t="inlineStr">
         <is>
-          <t>https://jenniferfisher.com</t>
+          <t>https://hoorsenbuhs.com</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>363 N Beverly Dr, Beverly Hills, CA 90210, United States</t>
-        </is>
-      </c>
-      <c r="K312" t="inlineStr"/>
-      <c r="L312" t="inlineStr"/>
+          <t>2217 Main St, Santa Monica, CA 90405</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Santa Monica</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
       <c r="M312" t="inlineStr">
         <is>
           <t>Beverly Hills, CA</t>
@@ -35175,23 +35187,19 @@
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O312" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P312" t="n">
-        <v>44</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr"/>
+      <c r="P312" t="inlineStr"/>
       <c r="Q312" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Jennifer+Fisher+Jewelry/data=!4m7!3m6!1s0x80c2bdd6ed684985:0xb8fbea746e91ad05!8m2!3d34.0695438!4d-118.4019104!16s%2Fg%2F11n12hvwn5!19sChIJhUlo7da9woARBa2RbnTq-7g</t>
+          <t>https://www.yellowpages.com/santa-monica-ca/mip/hoorsenbuhs-551622669</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, role-email, direct-line</t>
         </is>
       </c>
       <c r="S312" t="inlineStr">
@@ -35201,13 +35209,13 @@
       </c>
       <c r="T312" s="2" t="inlineStr">
         <is>
-          <t>https://jenniferfisher.com/pages/stockists</t>
+          <t>https://hoorsenbuhs.com/</t>
         </is>
       </c>
       <c r="U312" t="inlineStr"/>
       <c r="V312" t="inlineStr">
         <is>
-          <t>2026-10-14T01:40:50+05:30</t>
+          <t>2026-10-14T01:53:36+05:30</t>
         </is>
       </c>
       <c r="W312" t="inlineStr"/>
@@ -35215,22 +35223,26 @@
       <c r="Y312" t="n">
         <v>0</v>
       </c>
-      <c r="Z312" t="inlineStr"/>
+      <c r="Z312" t="inlineStr">
+        <is>
+          <t>toll-free</t>
+        </is>
+      </c>
       <c r="AA312" t="inlineStr">
         <is>
-          <t>(646) 366-9375</t>
+          <t>(917) 206-9333</t>
         </is>
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>https://instagram.com/jenniferfisherjewelry/, https://facebook.com/JenniferFisherJewelry, https://instagram.com/jenniferfisherjewelry</t>
+          <t>https://instagram.com/hoorsenbuhs</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Jewelry &amp; Watch Buyers - Beverly Hills</t>
+          <t>Jennifer Fisher Jewelry</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -35240,17 +35252,17 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Jewelry buyer</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>(310) 697-8177</t>
+          <t>(424) 374-5303</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>info@watchbuyers.us</t>
+          <t>la@jenniferfisher.com</t>
         </is>
       </c>
       <c r="F313" t="inlineStr"/>
@@ -35258,12 +35270,12 @@
       <c r="H313" t="inlineStr"/>
       <c r="I313" s="2" t="inlineStr">
         <is>
-          <t>https://watchbuyers.us</t>
+          <t>https://jenniferfisher.com</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>468 N Camden Dr #205, Beverly Hills, CA 90210, United States</t>
+          <t>363 N Beverly Dr, Beverly Hills, CA 90210, United States</t>
         </is>
       </c>
       <c r="K313" t="inlineStr"/>
@@ -35279,19 +35291,19 @@
         </is>
       </c>
       <c r="O313" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="P313" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="Q313" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Jewelry+%26+Watch+Buyers+-+Beverly+Hills/data=!4m7!3m6!1s0x80c2bdbde9baacdb:0xbbce1c74141b63ce!8m2!3d34.0698858!4d-118.404944!16s%2Fg%2F11xt1px272!19sChIJ26y66b29woARzmMbFHQczrs</t>
+          <t>https://www.google.com/maps/place/Jennifer+Fisher+Jewelry/data=!4m7!3m6!1s0x80c2bdd6ed684985:0xb8fbea746e91ad05!8m2!3d34.0695438!4d-118.4019104!16s%2Fg%2F11n12hvwn5!19sChIJhUlo7da9woARBa2RbnTq-7g</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S313" t="inlineStr">
@@ -35301,13 +35313,13 @@
       </c>
       <c r="T313" s="2" t="inlineStr">
         <is>
-          <t>https://watchbuyers.us/</t>
+          <t>https://jenniferfisher.com/pages/stockists</t>
         </is>
       </c>
       <c r="U313" t="inlineStr"/>
       <c r="V313" t="inlineStr">
         <is>
-          <t>2026-10-14T01:40:58+05:30</t>
+          <t>2026-10-14T01:40:50+05:30</t>
         </is>
       </c>
       <c r="W313" t="inlineStr"/>
@@ -35318,31 +35330,39 @@
       <c r="Z313" t="inlineStr"/>
       <c r="AA313" t="inlineStr">
         <is>
-          <t>(305) 989-9099, (646) 413-7757</t>
-        </is>
-      </c>
-      <c r="AB313" t="inlineStr"/>
+          <t>(646) 366-9375</t>
+        </is>
+      </c>
+      <c r="AB313" t="inlineStr">
+        <is>
+          <t>https://instagram.com/jenniferfisherjewelry/, https://facebook.com/JenniferFisherJewelry, https://instagram.com/jenniferfisherjewelry</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Jewels Aficionado Beverly Hills</t>
+          <t>Jewelry &amp; Watch Buyers - Beverly Hills</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr"/>
+          <t>Jewelry buyer</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>(310) 697-8177</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>sales@jewelsaficionado.com</t>
+          <t>info@watchbuyers.us</t>
         </is>
       </c>
       <c r="F314" t="inlineStr"/>
@@ -35350,12 +35370,12 @@
       <c r="H314" t="inlineStr"/>
       <c r="I314" s="2" t="inlineStr">
         <is>
-          <t>https://jewelsaficionado.com</t>
+          <t>https://watchbuyers.us</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>9850 Wilshire Blvd, Beverly Hills, CA 90210, United States</t>
+          <t>468 N Camden Dr #205, Beverly Hills, CA 90210, United States</t>
         </is>
       </c>
       <c r="K314" t="inlineStr"/>
@@ -35370,16 +35390,20 @@
           <t>Google Maps</t>
         </is>
       </c>
-      <c r="O314" t="inlineStr"/>
-      <c r="P314" t="inlineStr"/>
+      <c r="O314" t="n">
+        <v>5</v>
+      </c>
+      <c r="P314" t="n">
+        <v>3</v>
+      </c>
       <c r="Q314" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Jewels+Aficionado+Beverly+Hills/data=!4m7!3m6!1s0x80c2bb445801322d:0x4ee3ff18cd9446bc!8m2!3d34.0666649!4d-118.4114543!16s%2Fg%2F11z2xf_27b!19sChIJLTIBWES7woARvEaUzRj_404</t>
+          <t>https://www.google.com/maps/place/Jewelry+%26+Watch+Buyers+-+Beverly+Hills/data=!4m7!3m6!1s0x80c2bdbde9baacdb:0xbbce1c74141b63ce!8m2!3d34.0698858!4d-118.404944!16s%2Fg%2F11xt1px272!19sChIJ26y66b29woARzmMbFHQczrs</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, role-email, direct-line</t>
         </is>
       </c>
       <c r="S314" t="inlineStr">
@@ -35389,13 +35413,13 @@
       </c>
       <c r="T314" s="2" t="inlineStr">
         <is>
-          <t>https://jewelsaficionado.com/</t>
+          <t>https://watchbuyers.us/</t>
         </is>
       </c>
       <c r="U314" t="inlineStr"/>
       <c r="V314" t="inlineStr">
         <is>
-          <t>2026-10-14T01:42:22+05:30</t>
+          <t>2026-10-14T01:40:58+05:30</t>
         </is>
       </c>
       <c r="W314" t="inlineStr"/>
@@ -35406,24 +35430,20 @@
       <c r="Z314" t="inlineStr"/>
       <c r="AA314" t="inlineStr">
         <is>
-          <t>(212) 422-2600</t>
-        </is>
-      </c>
-      <c r="AB314" t="inlineStr">
-        <is>
-          <t>https://instagram.com/jewelsaficionado</t>
-        </is>
-      </c>
+          <t>(305) 989-9099, (646) 413-7757</t>
+        </is>
+      </c>
+      <c r="AB314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Logan Hollowell Jewelry</t>
+          <t>Jewels Aficionado Beverly Hills</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -35431,14 +35451,10 @@
           <t>Jewelry store</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>(323) 248-9685</t>
-        </is>
-      </c>
+      <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>info@loganhollowell.com</t>
+          <t>sales@jewelsaficionado.com</t>
         </is>
       </c>
       <c r="F315" t="inlineStr"/>
@@ -35446,12 +35462,12 @@
       <c r="H315" t="inlineStr"/>
       <c r="I315" s="2" t="inlineStr">
         <is>
-          <t>https://www.loganhollowell.com</t>
+          <t>https://jewelsaficionado.com</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>411 N Canon Dr, Beverly Hills, CA 90210, United States</t>
+          <t>9850 Wilshire Blvd, Beverly Hills, CA 90210, United States</t>
         </is>
       </c>
       <c r="K315" t="inlineStr"/>
@@ -35466,20 +35482,16 @@
           <t>Google Maps</t>
         </is>
       </c>
-      <c r="O315" t="n">
-        <v>5</v>
-      </c>
-      <c r="P315" t="n">
-        <v>1</v>
-      </c>
+      <c r="O315" t="inlineStr"/>
+      <c r="P315" t="inlineStr"/>
       <c r="Q315" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Logan+Hollowell+Jewelry/data=!4m7!3m6!1s0x80c2bd39cbc0865f:0x202c691c8504a898!8m2!3d34.07073!4d-118.4012945!16s%2Fg%2F11njp9zjzq!19sChIJX4bAyzm9woARmKgEhRxpLCA</t>
+          <t>https://www.google.com/maps/place/Jewels+Aficionado+Beverly+Hills/data=!4m7!3m6!1s0x80c2bb445801322d:0x4ee3ff18cd9446bc!8m2!3d34.0666649!4d-118.4114543!16s%2Fg%2F11z2xf_27b!19sChIJLTIBWES7woARvEaUzRj_404</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-2014</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S315" t="inlineStr">
@@ -35489,13 +35501,13 @@
       </c>
       <c r="T315" s="2" t="inlineStr">
         <is>
-          <t>https://loganhollowell.com/</t>
+          <t>https://jewelsaficionado.com/</t>
         </is>
       </c>
       <c r="U315" t="inlineStr"/>
       <c r="V315" t="inlineStr">
         <is>
-          <t>2026-10-14T01:41:31+05:30</t>
+          <t>2026-10-14T01:42:22+05:30</t>
         </is>
       </c>
       <c r="W315" t="inlineStr"/>
@@ -35506,39 +35518,39 @@
       <c r="Z315" t="inlineStr"/>
       <c r="AA315" t="inlineStr">
         <is>
-          <t>(323) 853-7844</t>
+          <t>(212) 422-2600</t>
         </is>
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>https://instagram.com/loganhollowell, https://facebook.com/loganhollowelljewelry</t>
+          <t>https://instagram.com/jewelsaficionado</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Majestic Jewelry</t>
+          <t>Logan Hollowell Jewelry</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>(323) 933-0288</t>
+          <t>(323) 248-9685</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>info@majesticjewelers.com</t>
+          <t>info@loganhollowell.com</t>
         </is>
       </c>
       <c r="F316" t="inlineStr"/>
@@ -35546,24 +35558,16 @@
       <c r="H316" t="inlineStr"/>
       <c r="I316" s="2" t="inlineStr">
         <is>
-          <t>https://majesticjewelers.com</t>
+          <t>https://www.loganhollowell.com</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>6333 W 3rd St, Los Angeles, CA 90036</t>
-        </is>
-      </c>
-      <c r="K316" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="L316" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
+          <t>411 N Canon Dr, Beverly Hills, CA 90210, United States</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr"/>
+      <c r="L316" t="inlineStr"/>
       <c r="M316" t="inlineStr">
         <is>
           <t>Beverly Hills, CA</t>
@@ -35571,23 +35575,23 @@
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O316" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P316" t="n">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="Q316" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/los-angeles-ca/mip/majestic-jewelry-458143900</t>
+          <t>https://www.google.com/maps/place/Logan+Hollowell+Jewelry/data=!4m7!3m6!1s0x80c2bd39cbc0865f:0x202c691c8504a898!8m2!3d34.07073!4d-118.4012945!16s%2Fg%2F11njp9zjzq!19sChIJX4bAyzm9woARmKgEhRxpLCA</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-1986</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-2014</t>
         </is>
       </c>
       <c r="S316" t="inlineStr">
@@ -35597,49 +35601,41 @@
       </c>
       <c r="T316" s="2" t="inlineStr">
         <is>
-          <t>https://www.majesticjewelers.com/about-us/</t>
+          <t>https://loganhollowell.com/</t>
         </is>
       </c>
       <c r="U316" t="inlineStr"/>
       <c r="V316" t="inlineStr">
         <is>
-          <t>2026-10-14T01:52:20+05:30</t>
-        </is>
-      </c>
-      <c r="W316" t="inlineStr">
-        <is>
-          <t>Majestic W.J.</t>
-        </is>
-      </c>
-      <c r="X316" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
+          <t>2026-10-14T01:41:31+05:30</t>
+        </is>
+      </c>
+      <c r="W316" t="inlineStr"/>
+      <c r="X316" t="inlineStr"/>
       <c r="Y316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z316" t="inlineStr"/>
       <c r="AA316" t="inlineStr">
         <is>
-          <t>(407) 644-4824</t>
+          <t>(323) 853-7844</t>
         </is>
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>https://facebook.com/MajesticJewelersInc, https://instagram.com/majesticjewelerswp</t>
+          <t>https://instagram.com/loganhollowell, https://facebook.com/loganhollowelljewelry</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Raven Fine Jewelers</t>
+          <t>Majestic Jewelry</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -35649,12 +35645,12 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>(310) 432-5234</t>
+          <t>(323) 933-0288</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>info@ravenjewelers.com</t>
+          <t>info@majesticjewelers.com</t>
         </is>
       </c>
       <c r="F317" t="inlineStr"/>
@@ -35662,17 +35658,17 @@
       <c r="H317" t="inlineStr"/>
       <c r="I317" s="2" t="inlineStr">
         <is>
-          <t>https://ravenfinejewelers.localsearch.com</t>
+          <t>https://majesticjewelers.com</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>8350 Wilshire Blvd, Beverly Hills, CA 90211</t>
+          <t>6333 W 3rd St, Los Angeles, CA 90036</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>Beverly Hills</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
@@ -35691,19 +35687,19 @@
         </is>
       </c>
       <c r="O317" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P317" t="n">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="Q317" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/beverly-hills-ca/mip/raven-fine-jewelers-531865762</t>
+          <t>https://www.yellowpages.com/los-angeles-ca/mip/majestic-jewelry-458143900</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-1986</t>
         </is>
       </c>
       <c r="S317" t="inlineStr">
@@ -35713,56 +35709,64 @@
       </c>
       <c r="T317" s="2" t="inlineStr">
         <is>
-          <t>https://ravendiamonds.com/</t>
+          <t>https://www.majesticjewelers.com/about-us/</t>
         </is>
       </c>
       <c r="U317" t="inlineStr"/>
       <c r="V317" t="inlineStr">
         <is>
-          <t>2026-10-14T01:51:20+05:30</t>
-        </is>
-      </c>
-      <c r="W317" t="inlineStr"/>
-      <c r="X317" t="inlineStr"/>
+          <t>2026-10-14T01:52:20+05:30</t>
+        </is>
+      </c>
+      <c r="W317" t="inlineStr">
+        <is>
+          <t>Majestic W.J.</t>
+        </is>
+      </c>
+      <c r="X317" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
       <c r="Y317" t="n">
         <v>1</v>
       </c>
       <c r="Z317" t="inlineStr"/>
       <c r="AA317" t="inlineStr">
         <is>
-          <t>(310) 887-1499</t>
+          <t>(407) 644-4824</t>
         </is>
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>https://instagram.com/ravenfinejewelers, https://facebook.com/RavenFineJewelers</t>
+          <t>https://facebook.com/MajesticJewelersInc, https://instagram.com/majesticjewelerswp</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Sunset Plaza</t>
+          <t>Raven Fine Jewelers</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Jewelers, Watches, Real Estate Agents</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>(310) 652-7137</t>
+          <t>(310) 432-5234</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>info@sunsetplaza.com</t>
+          <t>info@ravenjewelers.com</t>
         </is>
       </c>
       <c r="F318" t="inlineStr"/>
@@ -35770,17 +35774,17 @@
       <c r="H318" t="inlineStr"/>
       <c r="I318" s="2" t="inlineStr">
         <is>
-          <t>https://www.sunsetplaza.com</t>
+          <t>https://ravenfinejewelers.localsearch.com</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>8623 W Sunset Blvd, West Hollywood, CA 90069</t>
+          <t>8350 Wilshire Blvd, Beverly Hills, CA 90211</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>West Hollywood</t>
+          <t>Beverly Hills</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
@@ -35798,16 +35802,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O318" t="inlineStr"/>
-      <c r="P318" t="inlineStr"/>
+      <c r="O318" t="n">
+        <v>5</v>
+      </c>
+      <c r="P318" t="n">
+        <v>1</v>
+      </c>
       <c r="Q318" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/west-hollywood-ca/mip/sunset-plaza-1562237</t>
+          <t>https://www.yellowpages.com/beverly-hills-ca/mip/raven-fine-jewelers-531865762</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, since-1924</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S318" t="inlineStr">
@@ -35817,81 +35825,81 @@
       </c>
       <c r="T318" s="2" t="inlineStr">
         <is>
-          <t>https://www.sunsetplaza.com/</t>
+          <t>https://ravendiamonds.com/</t>
         </is>
       </c>
       <c r="U318" t="inlineStr"/>
       <c r="V318" t="inlineStr">
         <is>
-          <t>2026-10-14T01:52:13+05:30</t>
+          <t>2026-10-14T01:51:20+05:30</t>
         </is>
       </c>
       <c r="W318" t="inlineStr"/>
       <c r="X318" t="inlineStr"/>
       <c r="Y318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z318" t="inlineStr"/>
       <c r="AA318" t="inlineStr">
         <is>
-          <t>(213) 500-3098, (213) 709-2282, (310) 210-0975, (310) 248-3750, (310) 274-1602, (310) 275-2222, (310) 289-1104, (310) 289-1105, (310) 360-6900, (310) 360-8889, (310) 424-3690, (310) 616-7888, (310) 652-2680, (310) 652-6844, (310) 652-7039, (310) 652-8886, (310) 657-2553, (310) 657-5070, (310) 657-5469, (310) 659-4411, (310) 659-9089, (310) 734-7296, (310) 786-7417, (310) 849-7185, (310) 854-0299, (310) 854-7700, (310) 855-8044, (323) 253-6747, (323) 345-4525, (323) 507-3943, (323) 650-0475, (323) 937-0355, (424) 407-4606, (424) 542-7730, (424) 667-0036, (424) 722-8502, (747) 724-3595</t>
+          <t>(310) 887-1499</t>
         </is>
       </c>
       <c r="AB318" t="inlineStr">
         <is>
-          <t>https://instagram.com/affluette_, https://instagram.com/alchemy43, https://facebook.com/alchemy43, https://instagram.com/andreas.fashions, https://facebook.com/andreasfashions, https://instagram.com/bbcmcafe, https://instagram.com/bootstarusa, https://facebook.com/Boot-Star-106137407505929, https://instagram.com/bossanovarestaurant, https://facebook.com/BossaNovaLA, https://instagram.com/charliechoukair/, https://instagram.com/cristallini_official, https://facebook.com/CRISTALLINIOfficial, https://instagram.com/architectureforsale/, https://instagram.com/cupidlipsofbeverlyhills, https://facebook.com/profile.php?id=100083257576786, https://instagram.com/dandeutschoo, https://instagram.com/davidorgell, https://instagram.com/drybarshopsus, https://facebook.com/thedrybar, https://instagram.com/elainekimcollection/, https://instagram.com/entouragebarbershop, https://instagram.com/fpjourneofficial, https://instagram.com/guyfloralstudio, https://instagram.com/hotpilates, https://facebook.com/Hot-Pilates-1806940676211478, https://instagram.com/kojitoyodasalon, https://instagram.com/metaclinic/, https://instagram.com/milamoursiskincare, https://instagram.com/olehenriksenspa/, https://instagram.com/oliverpeoples, https://instagram.com/osklo.la, https://instagram.com/philippressjeweler, https://instagram.com/puravidamiami, https://facebook.com/PuraVidaMiami, https://instagram.com/queenbnailsalon_sunsetplaza, https://instagram.com/andywarholrevolvergallery, https://instagram.com/rondorff, https://instagram.com/saltiegirlla, https://instagram.com/samira13jewelry, https://instagram.com/sargondental, https://facebook.com/sargonlazarofdds, https://instagram.com/serenityonsunset, https://instagram.com/sheilaonsunset, https://instagram.com/solatesbysamantha, https://instagram.com/sousla_official, https://instagram.com/sunsetkidsla, https://instagram.com/theoppenheimgroup, https://facebook.com/theoppenheimgroup, https://instagram.com/whitegloveestates, https://instagram.com/xrcyze_ny, https://facebook.com/xrcycle, https://instagram.com/sunsetplazaca, https://facebook.com/SunsetPlazaCA</t>
+          <t>https://instagram.com/ravenfinejewelers, https://facebook.com/RavenFineJewelers</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Westime Beverly Hills</t>
+          <t>Sunset Plaza</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Watch store</t>
+          <t>Jewelers, Watches, Real Estate Agents</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>(310) 888-8880</t>
+          <t>(310) 652-7137</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>contact@westime.com</t>
+          <t>info@sunsetplaza.com</t>
         </is>
       </c>
       <c r="F319" t="inlineStr"/>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>Greg Simonian</t>
-        </is>
-      </c>
-      <c r="H319" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
+      <c r="G319" t="inlineStr"/>
+      <c r="H319" t="inlineStr"/>
       <c r="I319" s="2" t="inlineStr">
         <is>
-          <t>https://westime.com</t>
+          <t>https://www.sunsetplaza.com</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>206 N Rodeo Dr, Beverly Hills, CA 90210, United States</t>
-        </is>
-      </c>
-      <c r="K319" t="inlineStr"/>
-      <c r="L319" t="inlineStr"/>
+          <t>8623 W Sunset Blvd, West Hollywood, CA 90069</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>West Hollywood</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
       <c r="M319" t="inlineStr">
         <is>
           <t>Beverly Hills, CA</t>
@@ -35899,23 +35907,19 @@
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O319" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P319" t="n">
-        <v>274</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr"/>
+      <c r="P319" t="inlineStr"/>
       <c r="Q319" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Westime+Beverly+Hills/data=!4m7!3m6!1s0x80c2bc0ed6429065:0x2c357ea8ffa51b1f!8m2!3d34.067375!4d-118.4003799!16s%2Fg%2F11cfj2mg2!19sChIJZZBC1g68woARHxul_6h-NSw</t>
+          <t>https://www.yellowpages.com/west-hollywood-ca/mip/sunset-plaza-1562237</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-1987</t>
+          <t>2 of 3, role-email, direct-line, since-1924</t>
         </is>
       </c>
       <c r="S319" t="inlineStr">
@@ -35925,13 +35929,13 @@
       </c>
       <c r="T319" s="2" t="inlineStr">
         <is>
-          <t>https://westime.com/contact</t>
+          <t>https://www.sunsetplaza.com/</t>
         </is>
       </c>
       <c r="U319" t="inlineStr"/>
       <c r="V319" t="inlineStr">
         <is>
-          <t>2026-10-14T01:39:33+05:30</t>
+          <t>2026-10-14T01:52:13+05:30</t>
         </is>
       </c>
       <c r="W319" t="inlineStr"/>
@@ -35942,24 +35946,24 @@
       <c r="Z319" t="inlineStr"/>
       <c r="AA319" t="inlineStr">
         <is>
-          <t>(786) 347-5353, (858) 459-2222</t>
+          <t>(213) 500-3098, (213) 709-2282, (310) 210-0975, (310) 248-3750, (310) 274-1602, (310) 275-2222, (310) 289-1104, (310) 289-1105, (310) 360-6900, (310) 360-8889, (310) 424-3690, (310) 616-7888, (310) 652-2680, (310) 652-6844, (310) 652-7039, (310) 652-8886, (310) 657-2553, (310) 657-5070, (310) 657-5469, (310) 659-4411, (310) 659-9089, (310) 734-7296, (310) 786-7417, (310) 849-7185, (310) 854-0299, (310) 854-7700, (310) 855-8044, (323) 253-6747, (323) 345-4525, (323) 507-3943, (323) 650-0475, (323) 937-0355, (424) 407-4606, (424) 542-7730, (424) 667-0036, (424) 722-8502, (747) 724-3595</t>
         </is>
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>https://instagram.com/westimewatches, https://facebook.com/Westime</t>
+          <t>https://instagram.com/affluette_, https://instagram.com/alchemy43, https://facebook.com/alchemy43, https://instagram.com/andreas.fashions, https://facebook.com/andreasfashions, https://instagram.com/bbcmcafe, https://instagram.com/bootstarusa, https://facebook.com/Boot-Star-106137407505929, https://instagram.com/bossanovarestaurant, https://facebook.com/BossaNovaLA, https://instagram.com/charliechoukair/, https://instagram.com/cristallini_official, https://facebook.com/CRISTALLINIOfficial, https://instagram.com/architectureforsale/, https://instagram.com/cupidlipsofbeverlyhills, https://facebook.com/profile.php?id=100083257576786, https://instagram.com/dandeutschoo, https://instagram.com/davidorgell, https://instagram.com/drybarshopsus, https://facebook.com/thedrybar, https://instagram.com/elainekimcollection/, https://instagram.com/entouragebarbershop, https://instagram.com/fpjourneofficial, https://instagram.com/guyfloralstudio, https://instagram.com/hotpilates, https://facebook.com/Hot-Pilates-1806940676211478, https://instagram.com/kojitoyodasalon, https://instagram.com/metaclinic/, https://instagram.com/milamoursiskincare, https://instagram.com/olehenriksenspa/, https://instagram.com/oliverpeoples, https://instagram.com/osklo.la, https://instagram.com/philippressjeweler, https://instagram.com/puravidamiami, https://facebook.com/PuraVidaMiami, https://instagram.com/queenbnailsalon_sunsetplaza, https://instagram.com/andywarholrevolvergallery, https://instagram.com/rondorff, https://instagram.com/saltiegirlla, https://instagram.com/samira13jewelry, https://instagram.com/sargondental, https://facebook.com/sargonlazarofdds, https://instagram.com/serenityonsunset, https://instagram.com/sheilaonsunset, https://instagram.com/solatesbysamantha, https://instagram.com/sousla_official, https://instagram.com/sunsetkidsla, https://instagram.com/theoppenheimgroup, https://facebook.com/theoppenheimgroup, https://instagram.com/whitegloveestates, https://instagram.com/xrcyze_ny, https://facebook.com/xrcycle, https://instagram.com/sunsetplazaca, https://facebook.com/SunsetPlazaCA</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Wrist Aficionado Beverly Hills</t>
+          <t>Westime Beverly Hills</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -35969,37 +35973,37 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>(310) 388-8201</t>
+          <t>(310) 888-8880</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>sales@wristaficionado.com</t>
+          <t>contact@westime.com</t>
         </is>
       </c>
       <c r="F320" t="inlineStr"/>
-      <c r="G320" t="inlineStr"/>
-      <c r="H320" t="inlineStr"/>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>Greg Simonian</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
       <c r="I320" s="2" t="inlineStr">
         <is>
-          <t>https://wristaficionado.com</t>
+          <t>https://westime.com</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>9850 Wilshire Blvd, Beverly Hills, CA 90210, United States</t>
-        </is>
-      </c>
-      <c r="K320" t="inlineStr">
-        <is>
-          <t>Beverly Hills</t>
-        </is>
-      </c>
-      <c r="L320" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
+          <t>206 N Rodeo Dr, Beverly Hills, CA 90210, United States</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr"/>
+      <c r="L320" t="inlineStr"/>
       <c r="M320" t="inlineStr">
         <is>
           <t>Beverly Hills, CA</t>
@@ -36011,19 +36015,19 @@
         </is>
       </c>
       <c r="O320" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="P320" t="n">
-        <v>101</v>
+        <v>274</v>
       </c>
       <c r="Q320" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Wrist+Aficionado+Beverly+Hills/data=!4m7!3m6!1s0x80c2bb67e5181fcf:0xde9cbdbb118a155c!8m2!3d34.0667288!4d-118.4113018!16s%2Fg%2F11v12tg_x0!19sChIJzx8Y5We7woARXBWKEbu9nN4</t>
+          <t>https://www.google.com/maps/place/Westime+Beverly+Hills/data=!4m7!3m6!1s0x80c2bc0ed6429065:0x2c357ea8ffa51b1f!8m2!3d34.067375!4d-118.4003799!16s%2Fg%2F11cfj2mg2!19sChIJZZBC1g68woARHxul_6h-NSw</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-2017</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-1987</t>
         </is>
       </c>
       <c r="S320" t="inlineStr">
@@ -36033,13 +36037,13 @@
       </c>
       <c r="T320" s="2" t="inlineStr">
         <is>
-          <t>https://wristaficionado.com/</t>
+          <t>https://westime.com/contact</t>
         </is>
       </c>
       <c r="U320" t="inlineStr"/>
       <c r="V320" t="inlineStr">
         <is>
-          <t>2026-10-14T01:43:17+05:30</t>
+          <t>2026-10-14T01:39:33+05:30</t>
         </is>
       </c>
       <c r="W320" t="inlineStr"/>
@@ -36050,17 +36054,125 @@
       <c r="Z320" t="inlineStr"/>
       <c r="AA320" t="inlineStr">
         <is>
+          <t>(786) 347-5353, (858) 459-2222</t>
+        </is>
+      </c>
+      <c r="AB320" t="inlineStr">
+        <is>
+          <t>https://instagram.com/westimewatches, https://facebook.com/Westime</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Wrist Aficionado Beverly Hills</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Watch store</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>(310) 388-8201</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>sales@wristaficionado.com</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr"/>
+      <c r="G321" t="inlineStr"/>
+      <c r="H321" t="inlineStr"/>
+      <c r="I321" s="2" t="inlineStr">
+        <is>
+          <t>https://wristaficionado.com</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>9850 Wilshire Blvd, Beverly Hills, CA 90210, United States</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Beverly Hills</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>Beverly Hills, CA</t>
+        </is>
+      </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O321" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P321" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q321" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Wrist+Aficionado+Beverly+Hills/data=!4m7!3m6!1s0x80c2bb67e5181fcf:0xde9cbdbb118a155c!8m2!3d34.0667288!4d-118.4113018!16s%2Fg%2F11v12tg_x0!19sChIJzx8Y5We7woARXBWKEbu9nN4</t>
+        </is>
+      </c>
+      <c r="R321" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, custom-design, since-2017</t>
+        </is>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T321" s="2" t="inlineStr">
+        <is>
+          <t>https://wristaficionado.com/</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr"/>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>2026-10-14T01:43:17+05:30</t>
+        </is>
+      </c>
+      <c r="W321" t="inlineStr"/>
+      <c r="X321" t="inlineStr"/>
+      <c r="Y321" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z321" t="inlineStr"/>
+      <c r="AA321" t="inlineStr">
+        <is>
           <t>(305) 680-3735, (310) 861-3485, (646) 693-9384, (786) 889-6892</t>
         </is>
       </c>
-      <c r="AB320" t="inlineStr">
+      <c r="AB321" t="inlineStr">
         <is>
           <t>https://instagram.com/wristaficionado, https://instagram.com/wristaficionado/, https://facebook.com/shopwristaficionado, https://twitter.com/wristaficionado</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB320"/>
+  <autoFilter ref="A1:AB321"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId2"/>
@@ -37024,19 +37136,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I285" r:id="rId960"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q285" r:id="rId961"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T285" r:id="rId962"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F286" r:id="rId963"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I286" r:id="rId964"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q286" r:id="rId965"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T286" r:id="rId966"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U286" r:id="rId967"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F287" r:id="rId968"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I287" r:id="rId969"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q287" r:id="rId970"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T287" r:id="rId971"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U287" r:id="rId972"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I288" r:id="rId973"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q288" r:id="rId974"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T288" r:id="rId975"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I286" r:id="rId963"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q286" r:id="rId964"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T286" r:id="rId965"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F287" r:id="rId966"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I287" r:id="rId967"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q287" r:id="rId968"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T287" r:id="rId969"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U287" r:id="rId970"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F288" r:id="rId971"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I288" r:id="rId972"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q288" r:id="rId973"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T288" r:id="rId974"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U288" r:id="rId975"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I289" r:id="rId976"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q289" r:id="rId977"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T289" r:id="rId978"/>
@@ -37046,14 +37158,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I291" r:id="rId982"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q291" r:id="rId983"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T291" r:id="rId984"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F292" r:id="rId985"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I292" r:id="rId986"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q292" r:id="rId987"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T292" r:id="rId988"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U292" r:id="rId989"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I293" r:id="rId990"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q293" r:id="rId991"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T293" r:id="rId992"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I292" r:id="rId985"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q292" r:id="rId986"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T292" r:id="rId987"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F293" r:id="rId988"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I293" r:id="rId989"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q293" r:id="rId990"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T293" r:id="rId991"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U293" r:id="rId992"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I294" r:id="rId993"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q294" r:id="rId994"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T294" r:id="rId995"/>
@@ -37066,14 +37178,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I297" r:id="rId1002"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q297" r:id="rId1003"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T297" r:id="rId1004"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F298" r:id="rId1005"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I298" r:id="rId1006"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q298" r:id="rId1007"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T298" r:id="rId1008"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U298" r:id="rId1009"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I299" r:id="rId1010"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q299" r:id="rId1011"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T299" r:id="rId1012"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I298" r:id="rId1005"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q298" r:id="rId1006"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T298" r:id="rId1007"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F299" r:id="rId1008"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I299" r:id="rId1009"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q299" r:id="rId1010"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T299" r:id="rId1011"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U299" r:id="rId1012"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I300" r:id="rId1013"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q300" r:id="rId1014"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T300" r:id="rId1015"/>
@@ -37095,14 +37207,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I306" r:id="rId1031"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q306" r:id="rId1032"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T306" r:id="rId1033"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F307" r:id="rId1034"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I307" r:id="rId1035"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q307" r:id="rId1036"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T307" r:id="rId1037"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U307" r:id="rId1038"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I308" r:id="rId1039"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q308" r:id="rId1040"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T308" r:id="rId1041"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I307" r:id="rId1034"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q307" r:id="rId1035"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T307" r:id="rId1036"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F308" r:id="rId1037"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I308" r:id="rId1038"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q308" r:id="rId1039"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T308" r:id="rId1040"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U308" r:id="rId1041"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I309" r:id="rId1042"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q309" r:id="rId1043"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T309" r:id="rId1044"/>
@@ -37139,6 +37251,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I320" r:id="rId1075"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q320" r:id="rId1076"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T320" r:id="rId1077"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I321" r:id="rId1078"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q321" r:id="rId1079"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T321" r:id="rId1080"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -37665,21 +37780,21 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -37692,14 +37807,14 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="C20" t="n">
         <v>3</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -37881,10 +37996,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10850</v>
+        <v>10879</v>
       </c>
       <c r="C27" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -37892,10 +38007,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F27" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G27" t="n">
         <v>63</v>
@@ -37948,7 +38063,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4">
@@ -38010,7 +38125,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11">
@@ -38049,7 +38164,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T05:41:04+05:30</t>
+          <t>2026-10-14T06:01:18+05:30</t>
         </is>
       </c>
     </row>
@@ -38060,7 +38175,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3">
@@ -38070,7 +38185,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>10850</v>
+        <v>10879</v>
       </c>
     </row>
     <row r="4">

--- a/leadrun_jewelry/jewelry_qualified.xlsx
+++ b/leadrun_jewelry/jewelry_qualified.xlsx
@@ -32056,12 +32056,12 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>(704) 332-1605</t>
+          <t>(919) 829-7337</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -32070,8 +32070,16 @@
         </is>
       </c>
       <c r="F284" t="inlineStr"/>
-      <c r="G284" t="inlineStr"/>
-      <c r="H284" t="inlineStr"/>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Jane Bailey</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
           <t>https://www.baileybox.com</t>
@@ -32079,12 +32087,12 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>705 Providence Rd, Charlotte, NC 28207, United States</t>
+          <t>415 Daniels St, Raleigh, NC 27605-1314</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Raleigh</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -32099,7 +32107,7 @@
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="O284" t="n">
@@ -32110,7 +32118,7 @@
       </c>
       <c r="Q284" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Bailey%27s+Fine+Jewelry/data=!4m7!3m6!1s0x88569fe931546195:0x4340ee15ce06892f!8m2!3d35.2006619!4d-80.8249664!16s%2Fg%2F1tlgynm1!19sChIJlWFUMemfVogRL4kGzhXuQEM</t>
+          <t>https://www.bbb.org/us/nc/raleigh/profile/jewelry-stores/baileys-fine-jewelry-0593-20988</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
@@ -32131,7 +32139,7 @@
       <c r="U284" t="inlineStr"/>
       <c r="V284" t="inlineStr">
         <is>
-          <t>2026-10-14T00:51:23+05:30</t>
+          <t>2026-10-14T06:02:43+05:30</t>
         </is>
       </c>
       <c r="W284" t="inlineStr">
@@ -32141,12 +32149,12 @@
       </c>
       <c r="X284" t="inlineStr"/>
       <c r="Y284" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z284" t="inlineStr"/>
       <c r="AA284" t="inlineStr">
         <is>
-          <t>(252) 353-3434, (252) 443-7676, (919) 829-7337, (919) 892-3838</t>
+          <t>(252) 353-3434, (252) 443-7676, (919) 892-3838</t>
         </is>
       </c>
       <c r="AB284" t="inlineStr">
@@ -37429,7 +37437,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C6" t="n">
         <v>9</v>
@@ -37807,21 +37815,21 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="C20" t="n">
         <v>3</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="E20" t="n">
         <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -37834,14 +37842,14 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="C21" t="n">
         <v>2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -37996,7 +38004,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10879</v>
+        <v>10911</v>
       </c>
       <c r="C27" t="n">
         <v>320</v>
@@ -38010,7 +38018,7 @@
         <v>314</v>
       </c>
       <c r="F27" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G27" t="n">
         <v>63</v>
@@ -38101,17 +38109,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -38125,7 +38133,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11">
@@ -38164,7 +38172,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T06:01:18+05:30</t>
+          <t>2026-10-14T06:21:31+05:30</t>
         </is>
       </c>
     </row>
@@ -38185,7 +38193,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>10879</v>
+        <v>10911</v>
       </c>
     </row>
     <row r="4">

--- a/leadrun_jewelry/jewelry_qualified.xlsx
+++ b/leadrun_jewelry/jewelry_qualified.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qualified Leads'!$A$1:$AB$321</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qualified Leads'!$A$1:$AB$329</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB321"/>
+  <dimension ref="A1:AB329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -18375,7 +18375,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>3 of 3, role-email, direct-line, gia, since-1976</t>
+          <t>2 of 3, role-email, gia, since-1976</t>
         </is>
       </c>
       <c r="S161" t="inlineStr">
@@ -18398,17 +18398,21 @@
           <t>2026-10-13T22:39:14+05:30</t>
         </is>
       </c>
-      <c r="W161" t="inlineStr"/>
-      <c r="X161" t="inlineStr"/>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Markman's Diamonds &amp; Fine Jewelry</t>
+        </is>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>Nashville, TN</t>
+        </is>
+      </c>
       <c r="Y161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z161" t="inlineStr"/>
-      <c r="AA161" t="inlineStr">
-        <is>
-          <t>(865) 584-0247</t>
-        </is>
-      </c>
+      <c r="AA161" t="inlineStr"/>
       <c r="AB161" t="inlineStr">
         <is>
           <t>https://instagram.com/markmansdiamonds, https://facebook.com/MarkmansDiamonds, https://instagram.com/markmansdiamonds/</t>
@@ -30322,44 +30326,64 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Darakjian Jewelers</t>
+          <t>Aebischer's Jewelry Inc.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>(833) 327-2554</t>
+          <t>(330) 757-4685</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>info@darakjian.com</t>
-        </is>
-      </c>
-      <c r="F268" t="inlineStr"/>
-      <c r="G268" t="inlineStr"/>
-      <c r="H268" t="inlineStr"/>
+          <t>adam@aebischersjewelry.com</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/doug-aebischer-977970b5</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Doug Aebischer</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I268" s="2" t="inlineStr">
         <is>
-          <t>https://www.darakjian.com</t>
+          <t>https://aebischersjewelry.com</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>101 Willits St, Birmingham, MI 48009, United States</t>
-        </is>
-      </c>
-      <c r="K268" t="inlineStr"/>
-      <c r="L268" t="inlineStr"/>
+          <t>68 S Main St, Poland, OH 44514-1914</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
       <c r="M268" t="inlineStr">
         <is>
           <t>Detroit, MI</t>
@@ -30367,105 +30391,113 @@
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O268" t="n">
-        <v>5</v>
-      </c>
-      <c r="P268" t="n">
-        <v>872</v>
-      </c>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr"/>
+      <c r="P268" t="inlineStr"/>
       <c r="Q268" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Darakjian+Jewelers/data=!4m7!3m6!1s0x8824c7070f5beda7:0xfeec85b71df22c68!8m2!3d42.5474214!4d-83.2162268!16s%2Fg%2F1ptxrxwft!19sChIJp-1bDwfHJIgRaCzyHbeF7P4</t>
+          <t>https://www.bbb.org/us/oh/poland/profile/jewelry-stores/aebischers-jewelry-inc-0432-1761</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, gia, bench, custom-design, since-1928</t>
         </is>
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T268" s="2" t="inlineStr">
         <is>
-          <t>https://www.darakjian.com/</t>
-        </is>
-      </c>
-      <c r="U268" t="inlineStr"/>
+          <t>https://aebischersjewelry.com/</t>
+        </is>
+      </c>
+      <c r="U268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Doug+Aebischer%22+Poland+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V268" t="inlineStr">
         <is>
-          <t>2026-10-14T00:35:35+05:30</t>
+          <t>2026-10-14T05:12:22+05:30</t>
         </is>
       </c>
       <c r="W268" t="inlineStr"/>
       <c r="X268" t="inlineStr"/>
       <c r="Y268" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z268" t="inlineStr">
-        <is>
-          <t>toll-free</t>
-        </is>
-      </c>
-      <c r="AA268" t="inlineStr">
-        <is>
-          <t>(555) 555-5556</t>
-        </is>
-      </c>
-      <c r="AB268" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Z268" t="inlineStr"/>
+      <c r="AA268" t="inlineStr"/>
+      <c r="AB268" t="inlineStr">
+        <is>
+          <t>https://instagram.com/aebischers_jewelry, https://facebook.com/aebischersjewelry, https://instagram.com/aebischers_jewelry/</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Golden Sun Jewelry</t>
+          <t>Broer-Freeman Jewelers</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>(248) 559-6289</t>
+          <t>(419) 536-5272</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>info@goldensunjewelry.com</t>
-        </is>
-      </c>
-      <c r="F269" t="inlineStr"/>
-      <c r="G269" t="inlineStr"/>
-      <c r="H269" t="inlineStr"/>
+          <t>broerfreeman@aol.com</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/david-cameron-69542654</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>David Cameron</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
       <c r="I269" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldensunjewelry.com</t>
+          <t>https://broerfreemanjewelers.com</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>23077 Greenfield Rd, Southfield, MI 48075</t>
+          <t>4328 W. Central Avenue, Toledo, OH 43615</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>Southfield</t>
+          <t>Toledo</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
@@ -30475,66 +30507,58 @@
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O269" t="n">
-        <v>1</v>
-      </c>
-      <c r="P269" t="n">
-        <v>1</v>
-      </c>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr"/>
+      <c r="P269" t="inlineStr"/>
       <c r="Q269" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/southfield-mi/mip/golden-sun-jewelry-460257159</t>
+          <t>https://www.bbb.org/us/oh/toledo/profile/jewelry-stores/broer-freeman-jewelers-0422-1143</t>
         </is>
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-1989</t>
+          <t>2 of 3, gia, ags, bench, custom-design, since-2005</t>
         </is>
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T269" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldensunjewelry.com/contacts/</t>
-        </is>
-      </c>
-      <c r="U269" t="inlineStr"/>
+          <t>https://broerfreemanjewelers.com/</t>
+        </is>
+      </c>
+      <c r="U269" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22David+Cameron%22+Toledo+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V269" t="inlineStr">
         <is>
-          <t>2026-10-14T01:41:10+05:30</t>
-        </is>
-      </c>
-      <c r="W269" t="inlineStr">
-        <is>
-          <t>Golden Sun Jewlery</t>
-        </is>
-      </c>
+          <t>2026-10-14T04:55:17+05:30</t>
+        </is>
+      </c>
+      <c r="W269" t="inlineStr"/>
       <c r="X269" t="inlineStr"/>
       <c r="Y269" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z269" t="inlineStr"/>
-      <c r="AA269" t="inlineStr">
-        <is>
-          <t>(248) 559-5142</t>
-        </is>
-      </c>
+      <c r="AA269" t="inlineStr"/>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>https://facebook.com/GoldenSunJewelry, https://instagram.com/goldensunjewelry, https://twitter.com/GSJ_Southfield</t>
+          <t>https://facebook.com/BroerFreemanJewelersToledo, https://instagram.com/broer.freeman.jewelers</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Gwens Artistic Beadwork &amp; More, LLC.</t>
+          <t>Darakjian Jewelers</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -30544,17 +30568,17 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Jewelry Designers</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>(216) 262-6862</t>
+          <t>(833) 327-2554</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>gwen@gwensartisticbeads.com</t>
+          <t>info@darakjian.com</t>
         </is>
       </c>
       <c r="F270" t="inlineStr"/>
@@ -30562,24 +30586,16 @@
       <c r="H270" t="inlineStr"/>
       <c r="I270" s="2" t="inlineStr">
         <is>
-          <t>https://gwensartisticbeads.com</t>
+          <t>https://www.darakjian.com</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>101 5th St SE Ste E, Barberton, OH 44203-4225</t>
-        </is>
-      </c>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t>Barberton</t>
-        </is>
-      </c>
-      <c r="L270" t="inlineStr">
-        <is>
-          <t>OH</t>
-        </is>
-      </c>
+          <t>101 Willits St, Birmingham, MI 48009, United States</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr"/>
       <c r="M270" t="inlineStr">
         <is>
           <t>Detroit, MI</t>
@@ -30587,19 +30603,23 @@
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t>BBB</t>
-        </is>
-      </c>
-      <c r="O270" t="inlineStr"/>
-      <c r="P270" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O270" t="n">
+        <v>5</v>
+      </c>
+      <c r="P270" t="n">
+        <v>872</v>
+      </c>
       <c r="Q270" s="2" t="inlineStr">
         <is>
-          <t>https://www.bbb.org/us/oh/barberton/profile/jewelry-designers/gwens-artistic-beadwork-more-llc-0272-235860864</t>
+          <t>https://www.google.com/maps/place/Darakjian+Jewelers/data=!4m7!3m6!1s0x8824c7070f5beda7:0xfeec85b71df22c68!8m2!3d42.5474214!4d-83.2162268!16s%2Fg%2F1ptxrxwft!19sChIJp-1bDwfHJIgRaCzyHbeF7P4</t>
         </is>
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design, since-2019</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S270" t="inlineStr">
@@ -30609,13 +30629,13 @@
       </c>
       <c r="T270" s="2" t="inlineStr">
         <is>
-          <t>https://gwensartisticbeads.com/</t>
+          <t>https://www.darakjian.com/</t>
         </is>
       </c>
       <c r="U270" t="inlineStr"/>
       <c r="V270" t="inlineStr">
         <is>
-          <t>2026-10-14T05:04:01+05:30</t>
+          <t>2026-10-14T00:35:35+05:30</t>
         </is>
       </c>
       <c r="W270" t="inlineStr"/>
@@ -30623,22 +30643,22 @@
       <c r="Y270" t="n">
         <v>0</v>
       </c>
-      <c r="Z270" t="inlineStr"/>
+      <c r="Z270" t="inlineStr">
+        <is>
+          <t>toll-free</t>
+        </is>
+      </c>
       <c r="AA270" t="inlineStr">
         <is>
-          <t>(234) 571-0730</t>
-        </is>
-      </c>
-      <c r="AB270" t="inlineStr">
-        <is>
-          <t>https://facebook.com/profile.php?id=100067370501007, https://instagram.com/gwensartisticbeadwork, https://instagram.com/gwenbeads/</t>
-        </is>
-      </c>
+          <t>(555) 555-5556</t>
+        </is>
+      </c>
+      <c r="AB270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Herman's Creations Jewelers Inc.</t>
+          <t>Diamond Castle Jewelers Inc</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -30648,35 +30668,43 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Repairing, Diamond Setters</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>(586) 776-3200</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>roseville@hermanscreations.com</t>
-        </is>
-      </c>
-      <c r="F271" t="inlineStr"/>
-      <c r="G271" t="inlineStr"/>
-      <c r="H271" t="inlineStr"/>
+          <t>(248) 442-2440</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr"/>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kevin-ansara-22845328</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Kevin Ansara</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
       <c r="I271" s="2" t="inlineStr">
         <is>
-          <t>https://www.hermanscreations.com</t>
+          <t>https://www.diamondcastlejewelers.com</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>28885 Gratiot Ave, Roseville, MI 48066</t>
+          <t>39955 Grand River Ave, Novi, MI 48375-2111</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Novi</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -30691,70 +30719,66 @@
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="O271" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="P271" t="n">
-        <v>8</v>
+        <v>228</v>
       </c>
       <c r="Q271" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/roseville-mi/mip/hermans-creations-jewelers-inc-6517282</t>
+          <t>https://www.bbb.org/us/mi/plymouth/profile/jewelry-stores/diamond-castle-jewelers-inc-0372-3000014</t>
         </is>
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, since-1974</t>
+          <t>2 of 3, direct-line, gia, bench, custom-design, since-1902</t>
         </is>
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="T271" s="2" t="inlineStr">
-        <is>
-          <t>https://www.hermanscreations.com/</t>
-        </is>
-      </c>
-      <c r="U271" t="inlineStr"/>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="T271" t="inlineStr"/>
+      <c r="U271" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Kevin+Ansara%22+Novi+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V271" t="inlineStr">
         <is>
-          <t>2026-10-14T01:41:15+05:30</t>
+          <t>2026-10-14T04:51:53+05:30</t>
         </is>
       </c>
       <c r="W271" t="inlineStr">
         <is>
-          <t>Herman's Creations Ltd, Herman's Creations Jewelers, Steve's Creations</t>
+          <t>Diamond Castle Jewelers</t>
         </is>
       </c>
       <c r="X271" t="inlineStr"/>
       <c r="Y271" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z271" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="Z271" t="inlineStr"/>
       <c r="AA271" t="inlineStr">
         <is>
-          <t>(248) 968-0519, (586) 776-3201</t>
+          <t>(248) 442-7148</t>
         </is>
       </c>
       <c r="AB271" t="inlineStr">
         <is>
-          <t>https://instagram.com/hermans_creations, https://facebook.com/Hermans-Creations-Jewelers-East-122894551100621</t>
+          <t>https://twitter.com/dcjnovi, https://facebook.com/dcjnovi, https://instagram.com/diamondcastlenovi, https://x.com/dcjnovi</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>King Jewelers</t>
+          <t>Eichhorn Jewelry, Inc.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -30764,34 +30788,54 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Jeweler</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>(248) 569-0793</t>
+          <t>(260) 724-2621</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>u003einfo@kingjewelers.com</t>
-        </is>
-      </c>
-      <c r="F272" t="inlineStr"/>
-      <c r="G272" t="inlineStr"/>
-      <c r="H272" t="inlineStr"/>
+          <t>katedyer@eichhornjewelry.com</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/eileen-eichhorn-8a598510</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Eileen Eichhorn</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
       <c r="I272" s="2" t="inlineStr">
         <is>
-          <t>https://www.kingjewelers.com</t>
+          <t>https://www.eichhornjewelry.com</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>23077 Greenfield Rd #300, Southfield, MI 48075, United States</t>
-        </is>
-      </c>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
+          <t>130 N 2nd St, Decatur, IN 46733-1609</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Decatur</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
       <c r="M272" t="inlineStr">
         <is>
           <t>Detroit, MI</t>
@@ -30799,39 +30843,39 @@
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O272" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P272" t="n">
-        <v>83</v>
-      </c>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr"/>
+      <c r="P272" t="inlineStr"/>
       <c r="Q272" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/King+Jewelers/data=!4m7!3m6!1s0x8824c904292cee05:0xc371fcb68753dfa!8m2!3d42.460125!4d-83.2020227!16s%2Fg%2F1thfg1m3!19sChIJBe4sKQTJJIgR-j11aMsfNww</t>
+          <t>https://www.bbb.org/us/in/decatur/profile/jewelry-stores/eichhorn-jewelry-inc-0352-1947</t>
         </is>
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design</t>
+          <t>2 of 3, gia, custom-design, since-1965</t>
         </is>
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T272" s="2" t="inlineStr">
         <is>
-          <t>https://kingjewelers.com/pages/contact-us</t>
-        </is>
-      </c>
-      <c r="U272" t="inlineStr"/>
+          <t>https://www.eichhornjewelry.com/contact</t>
+        </is>
+      </c>
+      <c r="U272" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Eileen+Eichhorn%22+Decatur+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V272" t="inlineStr">
         <is>
-          <t>2026-10-14T00:36:20+05:30</t>
+          <t>2026-10-14T05:06:53+05:30</t>
         </is>
       </c>
       <c r="W272" t="inlineStr"/>
@@ -30840,26 +30884,22 @@
         <v>0</v>
       </c>
       <c r="Z272" t="inlineStr"/>
-      <c r="AA272" t="inlineStr">
-        <is>
-          <t>(615) 224-2902</t>
-        </is>
-      </c>
+      <c r="AA272" t="inlineStr"/>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>https://facebook.com/kingjewelersnashville, https://instagram.com/kingjewelers, https://instagram.com/kingjewelers/</t>
+          <t>https://facebook.com/eichhornjewelry, https://instagram.com/eichhorn_jewelry, https://twitter.com/eichhornjewelry</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>M J Diamonds</t>
+          <t>Golden Sun Jewelry</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -30869,12 +30909,12 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>(248) 577-0077</t>
+          <t>(248) 559-6289</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>contactus@mjdiamonds.com</t>
+          <t>info@goldensunjewelry.com</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
@@ -30882,17 +30922,17 @@
       <c r="H273" t="inlineStr"/>
       <c r="I273" s="2" t="inlineStr">
         <is>
-          <t>https://mjdiamonds456072858.localsearch.com</t>
+          <t>https://www.goldensunjewelry.com</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>320 W 14 Mile Rd, Troy, MI 48083</t>
+          <t>23077 Greenfield Rd, Southfield, MI 48075</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>Troy</t>
+          <t>Southfield</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -30911,19 +30951,19 @@
         </is>
       </c>
       <c r="O273" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P273" t="n">
         <v>1</v>
       </c>
       <c r="Q273" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/troy-mi/mip/m-j-diamonds-456072858</t>
+          <t>https://www.yellowpages.com/southfield-mi/mip/golden-sun-jewelry-460257159</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, bench, custom-design, since-1976</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-1989</t>
         </is>
       </c>
       <c r="S273" t="inlineStr">
@@ -30933,16 +30973,20 @@
       </c>
       <c r="T273" s="2" t="inlineStr">
         <is>
-          <t>https://mjdiamonds.com/</t>
+          <t>https://www.goldensunjewelry.com/contacts/</t>
         </is>
       </c>
       <c r="U273" t="inlineStr"/>
       <c r="V273" t="inlineStr">
         <is>
-          <t>2026-10-14T01:41:26+05:30</t>
-        </is>
-      </c>
-      <c r="W273" t="inlineStr"/>
+          <t>2026-10-14T01:41:10+05:30</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>Golden Sun Jewlery</t>
+        </is>
+      </c>
       <c r="X273" t="inlineStr"/>
       <c r="Y273" t="n">
         <v>1</v>
@@ -30950,39 +30994,39 @@
       <c r="Z273" t="inlineStr"/>
       <c r="AA273" t="inlineStr">
         <is>
-          <t>(248) 956-1832, (248) 975-7894, (734) 462-7777, (734) 834-1155</t>
+          <t>(248) 559-5142</t>
         </is>
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>https://facebook.com/mjdiamonds, https://twitter.com/mj_diamonds, https://instagram.com/mjdiamonds</t>
+          <t>https://facebook.com/GoldenSunJewelry, https://instagram.com/goldensunjewelry, https://twitter.com/GSJ_Southfield</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Mac Enterprises</t>
+          <t>Gwens Artistic Beadwork &amp; More, LLC.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelry Designers</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>(313) 846-4567</t>
+          <t>(216) 262-6862</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>brenda@macenterprisesinc.com</t>
+          <t>gwen@gwensartisticbeads.com</t>
         </is>
       </c>
       <c r="F274" t="inlineStr"/>
@@ -30990,22 +31034,22 @@
       <c r="H274" t="inlineStr"/>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>https://www.macenterprisesinc.com</t>
+          <t>https://gwensartisticbeads.com</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>5141 Schaefer Rd, Dearborn, MI 48126</t>
+          <t>101 5th St SE Ste E, Barberton, OH 44203-4225</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>Dearborn</t>
+          <t>Barberton</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -31015,19 +31059,19 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="O274" t="inlineStr"/>
       <c r="P274" t="inlineStr"/>
       <c r="Q274" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/dearborn-mi/mip/mac-enterprises-461011700</t>
+          <t>https://www.bbb.org/us/oh/barberton/profile/jewelry-designers/gwens-artistic-beadwork-more-llc-0272-235860864</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, since-1982</t>
+          <t>2 of 3, direct-line, custom-design, since-2019</t>
         </is>
       </c>
       <c r="S274" t="inlineStr">
@@ -31037,13 +31081,13 @@
       </c>
       <c r="T274" s="2" t="inlineStr">
         <is>
-          <t>https://www.macenterprisesinc.com/contact</t>
+          <t>https://gwensartisticbeads.com/</t>
         </is>
       </c>
       <c r="U274" t="inlineStr"/>
       <c r="V274" t="inlineStr">
         <is>
-          <t>2026-10-14T01:40:32+05:30</t>
+          <t>2026-10-14T05:04:01+05:30</t>
         </is>
       </c>
       <c r="W274" t="inlineStr"/>
@@ -31054,65 +31098,57 @@
       <c r="Z274" t="inlineStr"/>
       <c r="AA274" t="inlineStr">
         <is>
-          <t>(907) 359-4090</t>
+          <t>(234) 571-0730</t>
         </is>
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>https://facebook.com/wix, https://twitter.com/wix</t>
+          <t>https://facebook.com/profile.php?id=100067370501007, https://instagram.com/gwensartisticbeadwork, https://instagram.com/gwenbeads/</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Metals In Time</t>
+          <t>Herman's Creations Jewelers Inc.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Jewelry repair / goldsmith</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Jewelers, Watch Repair, Watches</t>
+          <t>Jewelers, Jewelry Repairing, Diamond Setters</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>(248) 582-9344</t>
+          <t>(586) 776-3200</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>jalexis@metalsintime.com</t>
+          <t>roseville@hermanscreations.com</t>
         </is>
       </c>
       <c r="F275" t="inlineStr"/>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>Sergio Basmajian</t>
-        </is>
-      </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
+      <c r="G275" t="inlineStr"/>
+      <c r="H275" t="inlineStr"/>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>https://www.metalsintime.com</t>
+          <t>https://www.hermanscreations.com</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>400 S Main St, Royal Oak, MI 48067</t>
+          <t>28885 Gratiot Ave, Roseville, MI 48066</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>Royal Oak</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -31134,16 +31170,16 @@
         <v>4</v>
       </c>
       <c r="P275" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q275" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/royal-oak-mi/mip/metals-in-time-473187148</t>
+          <t>https://www.yellowpages.com/roseville-mi/mip/hermans-creations-jewelers-inc-6517282</t>
         </is>
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design</t>
+          <t>2 of 3, direct-line, since-1974</t>
         </is>
       </c>
       <c r="S275" t="inlineStr">
@@ -31153,23 +31189,23 @@
       </c>
       <c r="T275" s="2" t="inlineStr">
         <is>
-          <t>https://www.metalsintime.com/meet-the-team/</t>
+          <t>https://www.hermanscreations.com/</t>
         </is>
       </c>
       <c r="U275" t="inlineStr"/>
       <c r="V275" t="inlineStr">
         <is>
-          <t>2026-10-14T01:40:59+05:30</t>
+          <t>2026-10-14T01:41:15+05:30</t>
         </is>
       </c>
       <c r="W275" t="inlineStr">
         <is>
-          <t>Metal In Time</t>
+          <t>Herman's Creations Ltd, Herman's Creations Jewelers, Steve's Creations</t>
         </is>
       </c>
       <c r="X275" t="inlineStr"/>
       <c r="Y275" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z275" t="inlineStr">
         <is>
@@ -31178,62 +31214,74 @@
       </c>
       <c r="AA275" t="inlineStr">
         <is>
-          <t>(248) 282-3733</t>
+          <t>(248) 968-0519, (586) 776-3201</t>
         </is>
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>https://facebook.com/Metalsintime, https://instagram.com/Metalsintimejewelers</t>
+          <t>https://instagram.com/hermans_creations, https://facebook.com/Hermans-Creations-Jewelers-East-122894551100621</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Motif Jewelers</t>
+          <t>Leo Marks Jewelers</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Designers, Jewelry Engravers</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>(734) 287-8300</t>
+          <t>(419) 531-1223</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>sales@motifjewelry.com</t>
-        </is>
-      </c>
-      <c r="F276" t="inlineStr"/>
-      <c r="G276" t="inlineStr"/>
-      <c r="H276" t="inlineStr"/>
+          <t>sales@leomarksjewelers.com</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/joewasserstrom</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Joe Wasserstrom</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>https://motifjewelersmi.localsearch.com</t>
+          <t>https://www.leomarksjewelers.com</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>23000 Eureka Rd, Taylor, MI 48180</t>
+          <t>3435 Secor Rd, Toledo, OH 43606-1502</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Toledo</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
@@ -31243,86 +31291,78 @@
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O276" t="n">
-        <v>5</v>
-      </c>
-      <c r="P276" t="n">
-        <v>5</v>
-      </c>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr"/>
+      <c r="P276" t="inlineStr"/>
       <c r="Q276" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/taylor-mi/mip/motif-jewelers-461726546</t>
+          <t>https://www.bbb.org/us/oh/toledo/profile/jewelry-stores/leo-marks-jewelers-0422-23000782</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1983</t>
+          <t>2 of 3, role-email, custom-design, since-1916</t>
         </is>
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T276" s="2" t="inlineStr">
         <is>
-          <t>https://motifjewelersmi.localsearch.com/</t>
-        </is>
-      </c>
-      <c r="U276" t="inlineStr"/>
+          <t>https://leomarksjewelers.com/</t>
+        </is>
+      </c>
+      <c r="U276" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Joe+Wasserstrom%22+Toledo+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V276" t="inlineStr">
         <is>
-          <t>2026-10-14T01:41:15+05:30</t>
-        </is>
-      </c>
-      <c r="W276" t="inlineStr">
-        <is>
-          <t>Motif Diamond Designs Inc</t>
-        </is>
-      </c>
+          <t>2026-10-14T04:55:04+05:30</t>
+        </is>
+      </c>
+      <c r="W276" t="inlineStr"/>
       <c r="X276" t="inlineStr"/>
       <c r="Y276" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z276" t="inlineStr"/>
-      <c r="AA276" t="inlineStr">
-        <is>
-          <t>(248) 676-0721</t>
-        </is>
-      </c>
+      <c r="AA276" t="inlineStr"/>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>https://facebook.com/MotifJewelry, https://instagram.com/motifjewelers, https://twitter.com/motifjewelers</t>
+          <t>https://facebook.com/LeoMarksJewelers, https://instagram.com/leomarksjewelers</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Parker Pretties Jewelry</t>
+          <t>M J Diamonds</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Jewelry Designers</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>(419) 871-5767</t>
+          <t>(248) 577-0077</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>purpleprincessjewels@gmail.com</t>
+          <t>contactus@mjdiamonds.com</t>
         </is>
       </c>
       <c r="F277" t="inlineStr"/>
@@ -31330,12 +31370,24 @@
       <c r="H277" t="inlineStr"/>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>https://www.parkerprettiesjewelry.com</t>
-        </is>
-      </c>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
+          <t>https://mjdiamonds456072858.localsearch.com</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>320 W 14 Mile Rd, Troy, MI 48083</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Troy</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
       <c r="M277" t="inlineStr">
         <is>
           <t>Detroit, MI</t>
@@ -31343,19 +31395,23 @@
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t>BBB</t>
-        </is>
-      </c>
-      <c r="O277" t="inlineStr"/>
-      <c r="P277" t="inlineStr"/>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O277" t="n">
+        <v>5</v>
+      </c>
+      <c r="P277" t="n">
+        <v>1</v>
+      </c>
       <c r="Q277" s="2" t="inlineStr">
         <is>
-          <t>https://www.bbb.org/us/oh/toledo/profile/jewelry-designers/parker-pretties-jewelry-0422-211020898</t>
+          <t>https://www.yellowpages.com/troy-mi/mip/m-j-diamonds-456072858</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design, since-2019</t>
+          <t>2 of 3, direct-line, bench, custom-design, since-1976</t>
         </is>
       </c>
       <c r="S277" t="inlineStr">
@@ -31365,56 +31421,56 @@
       </c>
       <c r="T277" s="2" t="inlineStr">
         <is>
-          <t>https://www.parkerprettiesjewelry.com/</t>
+          <t>https://mjdiamonds.com/</t>
         </is>
       </c>
       <c r="U277" t="inlineStr"/>
       <c r="V277" t="inlineStr">
         <is>
-          <t>2026-10-14T05:09:40+05:30</t>
+          <t>2026-10-14T01:41:26+05:30</t>
         </is>
       </c>
       <c r="W277" t="inlineStr"/>
       <c r="X277" t="inlineStr"/>
       <c r="Y277" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z277" t="inlineStr">
-        <is>
-          <t>no-address</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Z277" t="inlineStr"/>
       <c r="AA277" t="inlineStr">
         <is>
-          <t>(567) 218-1282</t>
-        </is>
-      </c>
-      <c r="AB277" t="inlineStr"/>
+          <t>(248) 956-1832, (248) 975-7894, (734) 462-7777, (734) 834-1155</t>
+        </is>
+      </c>
+      <c r="AB277" t="inlineStr">
+        <is>
+          <t>https://facebook.com/mjdiamonds, https://twitter.com/mj_diamonds, https://instagram.com/mjdiamonds</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Radiant Made For Us</t>
+          <t>Mac Enterprises</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>(313) 789-7480</t>
+          <t>(313) 846-4567</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>allenpark@radiantmadeforus.com</t>
+          <t>brenda@macenterprisesinc.com</t>
         </is>
       </c>
       <c r="F278" t="inlineStr"/>
@@ -31422,16 +31478,24 @@
       <c r="H278" t="inlineStr"/>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>https://radiantmadeforus.com</t>
+          <t>https://www.macenterprisesinc.com</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>6634 Allen Rd, Allen Park, MI 48101, United States</t>
-        </is>
-      </c>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
+          <t>5141 Schaefer Rd, Dearborn, MI 48126</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Dearborn</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
       <c r="M278" t="inlineStr">
         <is>
           <t>Detroit, MI</t>
@@ -31439,23 +31503,19 @@
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O278" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P278" t="n">
-        <v>21</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr"/>
+      <c r="P278" t="inlineStr"/>
       <c r="Q278" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Radiant+Made+For+Us/data=!4m7!3m6!1s0x883b374334f03ef5:0xea62d7eb1e5918df!8m2!3d42.2582463!4d-83.2094467!16s%2Fg%2F11y5nttj61!19sChIJ9T7wNEM3O4gR3xhZHuvXYuo</t>
+          <t>https://www.yellowpages.com/dearborn-mi/mip/mac-enterprises-461011700</t>
         </is>
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design</t>
+          <t>2 of 3, direct-line, since-1982</t>
         </is>
       </c>
       <c r="S278" t="inlineStr">
@@ -31465,13 +31525,13 @@
       </c>
       <c r="T278" s="2" t="inlineStr">
         <is>
-          <t>https://radiantmadeforus.com/</t>
+          <t>https://www.macenterprisesinc.com/contact</t>
         </is>
       </c>
       <c r="U278" t="inlineStr"/>
       <c r="V278" t="inlineStr">
         <is>
-          <t>2026-10-14T00:40:08+05:30</t>
+          <t>2026-10-14T01:40:32+05:30</t>
         </is>
       </c>
       <c r="W278" t="inlineStr"/>
@@ -31482,57 +31542,65 @@
       <c r="Z278" t="inlineStr"/>
       <c r="AA278" t="inlineStr">
         <is>
-          <t>(646) 649-4493</t>
+          <t>(907) 359-4090</t>
         </is>
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>https://facebook.com/radiantmadeforus, https://instagram.com/radiantmadeforus, https://facebook.com/madeforusdiamonds, https://instagram.com/madeforusdiamonds</t>
+          <t>https://facebook.com/wix, https://twitter.com/wix</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Rare Diamonds Inc</t>
+          <t>Metals In Time</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry repair / goldsmith</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Watch Repair, Watches</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>(313) 826-7042</t>
+          <t>(248) 582-9344</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>tony@rarediamond.com</t>
+          <t>jalexis@metalsintime.com</t>
         </is>
       </c>
       <c r="F279" t="inlineStr"/>
-      <c r="G279" t="inlineStr"/>
-      <c r="H279" t="inlineStr"/>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Sergio Basmajian</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>https://rarediamond.com</t>
+          <t>https://www.metalsintime.com</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>2470 Collingwood St, Detroit, MI 48206</t>
+          <t>400 S Main St, Royal Oak, MI 48067</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Royal Oak</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -31550,11 +31618,15 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O279" t="inlineStr"/>
-      <c r="P279" t="inlineStr"/>
+      <c r="O279" t="n">
+        <v>4</v>
+      </c>
+      <c r="P279" t="n">
+        <v>3</v>
+      </c>
       <c r="Q279" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/detroit-mi/mip/rare-diamonds-inc-551567325</t>
+          <t>https://www.yellowpages.com/royal-oak-mi/mip/metals-in-time-473187148</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
@@ -31569,36 +31641,44 @@
       </c>
       <c r="T279" s="2" t="inlineStr">
         <is>
-          <t>https://rarediamond.com/</t>
+          <t>https://www.metalsintime.com/meet-the-team/</t>
         </is>
       </c>
       <c r="U279" t="inlineStr"/>
       <c r="V279" t="inlineStr">
         <is>
-          <t>2026-10-14T01:40:22+05:30</t>
-        </is>
-      </c>
-      <c r="W279" t="inlineStr"/>
+          <t>2026-10-14T01:40:59+05:30</t>
+        </is>
+      </c>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>Metal In Time</t>
+        </is>
+      </c>
       <c r="X279" t="inlineStr"/>
       <c r="Y279" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z279" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Z279" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA279" t="inlineStr">
         <is>
-          <t>(310) 880-2982</t>
+          <t>(248) 282-3733</t>
         </is>
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>https://instagram.com/rarediamond_official, https://facebook.com/profile.php?id=61568585367287, https://twitter.com/rarediamondusa</t>
+          <t>https://facebook.com/Metalsintime, https://instagram.com/Metalsintimejewelers</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Tapper's Jewelry</t>
+          <t>Motif Jewelers</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -31608,43 +31688,35 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers, Jewelry Designers, Jewelry Engravers</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>(248) 932-7700</t>
+          <t>(734) 287-8300</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>sales@tappers.com</t>
+          <t>sales@motifjewelry.com</t>
         </is>
       </c>
       <c r="F280" t="inlineStr"/>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>Howard Tapper</t>
-        </is>
-      </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
+      <c r="G280" t="inlineStr"/>
+      <c r="H280" t="inlineStr"/>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>https://tappers.com</t>
+          <t>https://motifjewelersmi.localsearch.com</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>6337 Orchard Lake Rd, West Bloomfield Township, MI 48322, United States</t>
+          <t>23000 Eureka Rd, Taylor, MI 48180</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>West Bloomfield</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -31659,23 +31731,23 @@
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O280" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P280" t="n">
-        <v>1036</v>
+        <v>5</v>
       </c>
       <c r="Q280" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Tapper%27s+Jewelry/data=!4m7!3m6!1s0x8824ba48855706cf:0xec468d469a462bbd!8m2!3d42.5457394!4d-83.359087!16s%2Fg%2F1v3_397b!19sChIJzwZXhUi6JIgRvStGmkaNRuw</t>
+          <t>https://www.yellowpages.com/taylor-mi/mip/motif-jewelers-461726546</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1977</t>
+          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1983</t>
         </is>
       </c>
       <c r="S280" t="inlineStr">
@@ -31685,56 +31757,60 @@
       </c>
       <c r="T280" s="2" t="inlineStr">
         <is>
-          <t>https://tappers.com/pages/contact</t>
+          <t>https://motifjewelersmi.localsearch.com/</t>
         </is>
       </c>
       <c r="U280" t="inlineStr"/>
       <c r="V280" t="inlineStr">
         <is>
-          <t>2026-10-14T00:34:13+05:30</t>
-        </is>
-      </c>
-      <c r="W280" t="inlineStr"/>
+          <t>2026-10-14T01:41:15+05:30</t>
+        </is>
+      </c>
+      <c r="W280" t="inlineStr">
+        <is>
+          <t>Motif Diamond Designs Inc</t>
+        </is>
+      </c>
       <c r="X280" t="inlineStr"/>
       <c r="Y280" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z280" t="inlineStr"/>
       <c r="AA280" t="inlineStr">
         <is>
-          <t>(248) 465-1800, (248) 649-2000, (248) 862-9700</t>
+          <t>(248) 676-0721</t>
         </is>
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>https://instagram.com/TappersJewelry, https://facebook.com/TappersJewelry</t>
+          <t>https://facebook.com/MotifJewelry, https://instagram.com/motifjewelers, https://twitter.com/motifjewelers</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Fixology Jewelry, Watch, and Smartphone Repair</t>
+          <t>Parker Pretties Jewelry</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Jewelry repair / goldsmith</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Electronics repair shop</t>
+          <t>Jewelry Designers</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>(612) 330-9925</t>
+          <t>(419) 871-5767</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>bloomington@fixologyrepair.com</t>
+          <t>purpleprincessjewels@gmail.com</t>
         </is>
       </c>
       <c r="F281" t="inlineStr"/>
@@ -31742,40 +31818,32 @@
       <c r="H281" t="inlineStr"/>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>https://fixologyrepair.com</t>
-        </is>
-      </c>
-      <c r="J281" t="inlineStr">
-        <is>
-          <t>651 Nicollet Mall #247, Minneapolis, MN 55402, United States</t>
-        </is>
-      </c>
+          <t>https://www.parkerprettiesjewelry.com</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Minneapolis, MN</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O281" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P281" t="n">
-        <v>113</v>
-      </c>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr"/>
+      <c r="P281" t="inlineStr"/>
       <c r="Q281" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Fixology+Jewelry,+Watch,+and+Smartphone+Repair/data=!4m7!3m6!1s0x52b3329a741033cd:0x422f1e9528fd8f0a!8m2!3d44.9773754!4d-93.2709679!16s%2Fg%2F11bwndn4z4!19sChIJzTMQdJoys1IRCo_9KJUeL0I</t>
+          <t>https://www.bbb.org/us/oh/toledo/profile/jewelry-designers/parker-pretties-jewelry-0422-211020898</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, direct-line, custom-design, since-2019</t>
         </is>
       </c>
       <c r="S281" t="inlineStr">
@@ -31785,40 +31853,36 @@
       </c>
       <c r="T281" s="2" t="inlineStr">
         <is>
-          <t>https://fixologyrepair.com/contact/</t>
+          <t>https://www.parkerprettiesjewelry.com/</t>
         </is>
       </c>
       <c r="U281" t="inlineStr"/>
       <c r="V281" t="inlineStr">
         <is>
-          <t>2026-10-14T00:47:39+05:30</t>
-        </is>
-      </c>
-      <c r="W281" t="inlineStr">
-        <is>
-          <t>Fixology</t>
-        </is>
-      </c>
+          <t>2026-10-14T05:09:40+05:30</t>
+        </is>
+      </c>
+      <c r="W281" t="inlineStr"/>
       <c r="X281" t="inlineStr"/>
       <c r="Y281" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z281" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Z281" t="inlineStr">
+        <is>
+          <t>no-address</t>
+        </is>
+      </c>
       <c r="AA281" t="inlineStr">
         <is>
-          <t>(772) 692-3774</t>
-        </is>
-      </c>
-      <c r="AB281" t="inlineStr">
-        <is>
-          <t>https://facebook.com/fixologytoledo, https://facebook.com/fixologyMallofAmerica</t>
-        </is>
-      </c>
+          <t>(567) 218-1282</t>
+        </is>
+      </c>
+      <c r="AB281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Johnson Jewelers</t>
+          <t>Radiant Made For Us</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -31828,70 +31892,58 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Jewelry Stores</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>(651) 735-4400</t>
+          <t>(313) 789-7480</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>ryan@johnsonjewelers.com</t>
+          <t>allenpark@radiantmadeforus.com</t>
         </is>
       </c>
       <c r="F282" t="inlineStr"/>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>Bob Johnson</t>
-        </is>
-      </c>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
+      <c r="G282" t="inlineStr"/>
+      <c r="H282" t="inlineStr"/>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>https://johnsonjewelers.com</t>
+          <t>https://radiantmadeforus.com</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>783 Radio Dr Ste 100D, Saint Paul, MN 55125-5402</t>
-        </is>
-      </c>
-      <c r="K282" t="inlineStr">
-        <is>
-          <t>Saint Paul</t>
-        </is>
-      </c>
-      <c r="L282" t="inlineStr">
-        <is>
-          <t>MN</t>
-        </is>
-      </c>
+          <t>6634 Allen Rd, Allen Park, MI 48101, United States</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr"/>
+      <c r="L282" t="inlineStr"/>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Minneapolis, MN</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t>BBB</t>
-        </is>
-      </c>
-      <c r="O282" t="inlineStr"/>
-      <c r="P282" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O282" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P282" t="n">
+        <v>21</v>
+      </c>
       <c r="Q282" s="2" t="inlineStr">
         <is>
-          <t>https://www.bbb.org/us/mn/saint-paul/profile/jewelry-stores/johnson-jewelers-0704-9000723</t>
+          <t>https://www.google.com/maps/place/Radiant+Made+For+Us/data=!4m7!3m6!1s0x883b374334f03ef5:0xea62d7eb1e5918df!8m2!3d42.2582463!4d-83.2094467!16s%2Fg%2F11y5nttj61!19sChIJ9T7wNEM3O4gR3xhZHuvXYuo</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design, since-1976</t>
+          <t>2 of 3, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S282" t="inlineStr">
@@ -31901,56 +31953,56 @@
       </c>
       <c r="T282" s="2" t="inlineStr">
         <is>
-          <t>https://johnsonjewelers.com/about/employment/</t>
+          <t>https://radiantmadeforus.com/</t>
         </is>
       </c>
       <c r="U282" t="inlineStr"/>
       <c r="V282" t="inlineStr">
         <is>
-          <t>2026-10-14T05:42:57+05:30</t>
+          <t>2026-10-14T00:40:08+05:30</t>
         </is>
       </c>
       <c r="W282" t="inlineStr"/>
       <c r="X282" t="inlineStr"/>
       <c r="Y282" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z282" t="inlineStr"/>
       <c r="AA282" t="inlineStr">
         <is>
-          <t>(651) 345-3825</t>
+          <t>(646) 649-4493</t>
         </is>
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>https://facebook.com/JohnsonJewelersInc, https://facebook.com/JohnsonJewelersofLakeCity</t>
+          <t>https://facebook.com/radiantmadeforus, https://instagram.com/radiantmadeforus, https://facebook.com/madeforusdiamonds, https://instagram.com/madeforusdiamonds</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>R.F. Moeller Jeweler</t>
+          <t>Rare Diamonds Inc</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>(651) 698-6321</t>
+          <t>(313) 826-7042</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>alexandra@rfmoeller.com</t>
+          <t>tony@rarediamond.com</t>
         </is>
       </c>
       <c r="F283" t="inlineStr"/>
@@ -31958,48 +32010,44 @@
       <c r="H283" t="inlineStr"/>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>https://rfmoeller.com</t>
+          <t>https://rarediamond.com</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>2065 Ford Pkwy, St Paul, MN 55116, United States</t>
+          <t>2470 Collingwood St, Detroit, MI 48206</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Minneapolis, MN</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O283" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P283" t="n">
-        <v>2186</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr"/>
+      <c r="P283" t="inlineStr"/>
       <c r="Q283" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/R.F.+Moeller+Jeweler/data=!4m7!3m6!1s0x87f62978048ef94d:0xea9c4d97c5c2b259!8m2!3d44.9181574!4d-93.1877644!16s%2Fg%2F1v7pz0rd!19sChIJTfmOBHgp9ocRWbLCxZdNnOo</t>
+          <t>https://www.yellowpages.com/detroit-mi/mip/rare-diamonds-inc-551567325</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, ags, custom-design, since-1951</t>
+          <t>2 of 3, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S283" t="inlineStr">
@@ -32009,44 +32057,36 @@
       </c>
       <c r="T283" s="2" t="inlineStr">
         <is>
-          <t>https://rfmoeller.com/</t>
+          <t>https://rarediamond.com/</t>
         </is>
       </c>
       <c r="U283" t="inlineStr"/>
       <c r="V283" t="inlineStr">
         <is>
-          <t>2026-10-14T00:46:15+05:30</t>
-        </is>
-      </c>
-      <c r="W283" t="inlineStr">
-        <is>
-          <t>Moeller Jeweler R. F.</t>
-        </is>
-      </c>
+          <t>2026-10-14T01:40:22+05:30</t>
+        </is>
+      </c>
+      <c r="W283" t="inlineStr"/>
       <c r="X283" t="inlineStr"/>
       <c r="Y283" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z283" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z283" t="inlineStr"/>
       <c r="AA283" t="inlineStr">
         <is>
-          <t>(651) 698-6322</t>
+          <t>(310) 880-2982</t>
         </is>
       </c>
       <c r="AB283" t="inlineStr">
         <is>
-          <t>https://facebook.com/rfmoellerjeweler, https://instagram.com/rfmoellerjeweler</t>
+          <t>https://instagram.com/rarediamond_official, https://facebook.com/profile.php?id=61568585367287, https://twitter.com/rarediamondusa</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Bailey's Fine Jewelry</t>
+          <t>Tapper's Jewelry</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -32056,74 +32096,74 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Jewelry Stores</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>(919) 829-7337</t>
+          <t>(248) 932-7700</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>carysubs@baileybox.com</t>
+          <t>sales@tappers.com</t>
         </is>
       </c>
       <c r="F284" t="inlineStr"/>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Jane Bailey</t>
+          <t>Howard Tapper</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>https://www.baileybox.com</t>
+          <t>https://tappers.com</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>415 Daniels St, Raleigh, NC 27605-1314</t>
+          <t>6337 Orchard Lake Rd, West Bloomfield Township, MI 48322, United States</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>Raleigh</t>
+          <t>West Bloomfield</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Charlotte, NC</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t>BBB</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O284" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P284" t="n">
-        <v>775</v>
+        <v>1036</v>
       </c>
       <c r="Q284" s="2" t="inlineStr">
         <is>
-          <t>https://www.bbb.org/us/nc/raleigh/profile/jewelry-stores/baileys-fine-jewelry-0593-20988</t>
+          <t>https://www.google.com/maps/place/Tapper%27s+Jewelry/data=!4m7!3m6!1s0x8824ba48855706cf:0xec468d469a462bbd!8m2!3d42.5457394!4d-83.359087!16s%2Fg%2F1v3_397b!19sChIJzwZXhUi6JIgRvStGmkaNRuw</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, ags, bench, custom-design, since-1948</t>
+          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1977</t>
         </is>
       </c>
       <c r="S284" t="inlineStr">
@@ -32133,220 +32173,192 @@
       </c>
       <c r="T284" s="2" t="inlineStr">
         <is>
-          <t>https://baileybox.com/</t>
+          <t>https://tappers.com/pages/contact</t>
         </is>
       </c>
       <c r="U284" t="inlineStr"/>
       <c r="V284" t="inlineStr">
         <is>
-          <t>2026-10-14T06:02:43+05:30</t>
-        </is>
-      </c>
-      <c r="W284" t="inlineStr">
-        <is>
-          <t>Morrison Smith Jewelers</t>
-        </is>
-      </c>
+          <t>2026-10-14T00:34:13+05:30</t>
+        </is>
+      </c>
+      <c r="W284" t="inlineStr"/>
       <c r="X284" t="inlineStr"/>
       <c r="Y284" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z284" t="inlineStr"/>
       <c r="AA284" t="inlineStr">
         <is>
-          <t>(252) 353-3434, (252) 443-7676, (919) 892-3838</t>
+          <t>(248) 465-1800, (248) 649-2000, (248) 862-9700</t>
         </is>
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>https://facebook.com/BaileysFineJewelry, https://instagram.com/baileysfinejewelry, https://instagram.com/morrisonsmithjewelers, https://facebook.com/MorrisonSmithJewelers, https://x.com/morrisonsmith, https://twitter.com/morrisonsmith</t>
+          <t>https://instagram.com/TappersJewelry, https://facebook.com/TappersJewelry</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Fink's Jewelers</t>
+          <t>Embellir Gallery of Gems, LLC</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Jewelers, Fix-It Shops, Watches</t>
+          <t>Jewelry Designers</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>(704) 366-3120</t>
+          <t>(651) 905-1168</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>ecommerce@finks.com</t>
-        </is>
-      </c>
-      <c r="F285" t="inlineStr"/>
+          <t>brenda@embellirgems.com</t>
+        </is>
+      </c>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/brenda-machnik-94544a76</t>
+        </is>
+      </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Nathan Fink</t>
+          <t>Brenda S. Machnik</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>https://www.finks.com</t>
+          <t>https://www.embellirgems.com</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>4400 Sharon Rd Ste 199, Charlotte, NC 28211</t>
+          <t>750 Main St Ste 111, Mendota Heights, MN 55118-3765</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Mendota Heights</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Charlotte, NC</t>
+          <t>Minneapolis, MN</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O285" t="n">
-        <v>5</v>
-      </c>
-      <c r="P285" t="n">
-        <v>1</v>
-      </c>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr"/>
+      <c r="P285" t="inlineStr"/>
       <c r="Q285" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/charlotte-nc/mip/finks-jewelers-464773701</t>
+          <t>https://www.bbb.org/us/mn/mendota-heights/profile/jewelry-designers/embellir-gallery-of-gems-llc-0704-7000375</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design, since-1930</t>
+          <t>2 of 3, gia, custom-design, since-1998</t>
         </is>
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T285" s="2" t="inlineStr">
         <is>
-          <t>https://www.finks.com/</t>
-        </is>
-      </c>
-      <c r="U285" t="inlineStr"/>
+          <t>https://www.embellirgems.com/</t>
+        </is>
+      </c>
+      <c r="U285" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Brenda+S.+Machnik%22+Mendota+Heights+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V285" t="inlineStr">
         <is>
-          <t>2026-10-14T01:43:57+05:30</t>
-        </is>
-      </c>
-      <c r="W285" t="inlineStr">
-        <is>
-          <t>John Paul Fine Jewelry</t>
-        </is>
-      </c>
+          <t>2026-10-14T05:14:02+05:30</t>
+        </is>
+      </c>
+      <c r="W285" t="inlineStr"/>
       <c r="X285" t="inlineStr"/>
       <c r="Y285" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z285" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
-      <c r="AA285" t="inlineStr">
-        <is>
-          <t>(423) 894-1188, (540) 342-2991, (540) 344-8697, (615) 236-8176, (704) 927-4888, (757) 640-1132, (804) 377-8589, (919) 881-8247</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Z285" t="inlineStr"/>
+      <c r="AA285" t="inlineStr"/>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>https://facebook.com/FinksJewelers, https://instagram.com/finksjewelers</t>
+          <t>https://facebook.com/EmbellirGallery</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Windsor Jewelers</t>
+          <t>Fixology Jewelry, Watch, and Smartphone Repair</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Jewelry repair / goldsmith</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Electronics repair shop</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>(704) 556-7747</t>
+          <t>(612) 330-9925</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>nfo@windsor-jewelers.com</t>
+          <t>bloomington@fixologyrepair.com</t>
         </is>
       </c>
       <c r="F286" t="inlineStr"/>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>Kevin Slusher</t>
-        </is>
-      </c>
-      <c r="H286" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
+      <c r="G286" t="inlineStr"/>
+      <c r="H286" t="inlineStr"/>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>https://www.windsor-jewelers.com</t>
+          <t>https://fixologyrepair.com</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>6809-D Phillips Pl Ct, Charlotte, NC 28210, United States</t>
-        </is>
-      </c>
-      <c r="K286" t="inlineStr">
-        <is>
-          <t>Winston-Salem</t>
-        </is>
-      </c>
-      <c r="L286" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>651 Nicollet Mall #247, Minneapolis, MN 55402, United States</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr"/>
+      <c r="L286" t="inlineStr"/>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Charlotte, NC</t>
+          <t>Minneapolis, MN</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -32355,19 +32367,19 @@
         </is>
       </c>
       <c r="O286" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="P286" t="n">
-        <v>1846</v>
+        <v>113</v>
       </c>
       <c r="Q286" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Windsor+Jewelers/data=!4m7!3m6!1s0x88569e13f91d1bb1:0x4b6448ed40c4d63c!8m2!3d35.1465046!4d-80.8269547!16s%2Fg%2F1tq8k7xj!19sChIJsRsd-ROeVogRPNbEQO1IZEs</t>
+          <t>https://www.google.com/maps/place/Fixology+Jewelry,+Watch,+and+Smartphone+Repair/data=!4m7!3m6!1s0x52b3329a741033cd:0x422f1e9528fd8f0a!8m2!3d44.9773754!4d-93.2709679!16s%2Fg%2F11bwndn4z4!19sChIJzTMQdJoys1IRCo_9KJUeL0I</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S286" t="inlineStr">
@@ -32377,109 +32389,121 @@
       </c>
       <c r="T286" s="2" t="inlineStr">
         <is>
-          <t>https://www.windsor-jewelers.com/</t>
+          <t>https://fixologyrepair.com/contact/</t>
         </is>
       </c>
       <c r="U286" t="inlineStr"/>
       <c r="V286" t="inlineStr">
         <is>
-          <t>2026-10-14T00:51:17+05:30</t>
-        </is>
-      </c>
-      <c r="W286" t="inlineStr"/>
+          <t>2026-10-14T00:47:39+05:30</t>
+        </is>
+      </c>
+      <c r="W286" t="inlineStr">
+        <is>
+          <t>Fixology</t>
+        </is>
+      </c>
       <c r="X286" t="inlineStr"/>
       <c r="Y286" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z286" t="inlineStr"/>
       <c r="AA286" t="inlineStr">
         <is>
-          <t>(336) 721-1768</t>
+          <t>(772) 692-3774</t>
         </is>
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>https://instagram.com/windsorjewelersnc/, https://facebook.com/OfficialWindsorJewelersNC</t>
+          <t>https://facebook.com/fixologytoledo, https://facebook.com/fixologyMallofAmerica</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Lindell Jewelers &amp; Appraisers</t>
+          <t>Gold'n Treasures, Inc.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>(615) 373-7922</t>
+          <t>(651) 227-2711</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>lindelljewels@gmail.com</t>
+          <t>agreene@goldn-treasures.com</t>
         </is>
       </c>
       <c r="F287" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/carolyn-linder-19ab1a80</t>
+          <t>https://www.linkedin.com/in/todd-gimble-944a965</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Carolyn A. Linder</t>
+          <t>Todd Gimble</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>President</t>
         </is>
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>https://www.lindelljewelers.com</t>
+          <t>https://www.goldn-treasures.com</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>7028 Church St E Ste 106, Brentwood, TN 37027, United States</t>
-        </is>
-      </c>
-      <c r="K287" t="inlineStr"/>
-      <c r="L287" t="inlineStr"/>
+          <t>805 Grand Ave, Saint Paul, MN 55105-3311</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Saint Paul</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>MN</t>
+        </is>
+      </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Nashville, TN</t>
+          <t>Minneapolis, MN</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="O287" t="n">
         <v>4.9</v>
       </c>
       <c r="P287" t="n">
-        <v>56</v>
+        <v>368</v>
       </c>
       <c r="Q287" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Lindell+Jewelers+%26+Appraisers/data=!4m7!3m6!1s0x88647b266e6cc441:0xa03113da3f7ec814!8m2!3d36.0335009!4d-86.7862323!16s%2Fg%2F1tdjrwp3!19sChIJQcRsbiZ7ZIgRFMh-P9oTMaA</t>
+          <t>https://www.bbb.org/us/mn/saint-paul/profile/jewelry-stores/goldn-treasures-inc-0704-24001102</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>2 of 3, custom-design, since-1991</t>
+          <t>2 of 3, gia, custom-design, since-1997</t>
         </is>
       </c>
       <c r="S287" t="inlineStr">
@@ -32489,170 +32513,182 @@
       </c>
       <c r="T287" s="2" t="inlineStr">
         <is>
-          <t>https://www.lindelljewelers.com/about-us</t>
+          <t>https://www.goldn-treasures.com/</t>
         </is>
       </c>
       <c r="U287" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=%22Carolyn+A.+Linder%22+Nashville+linkedin&amp;hl=en&amp;num=10</t>
+          <t>https://www.google.com/search?q=%22Todd+Gimble%22+Saint+Paul+linkedin&amp;hl=en&amp;num=10</t>
         </is>
       </c>
       <c r="V287" t="inlineStr">
         <is>
-          <t>2026-10-14T01:03:10+05:30</t>
-        </is>
-      </c>
-      <c r="W287" t="inlineStr"/>
+          <t>2026-10-14T05:29:52+05:30</t>
+        </is>
+      </c>
+      <c r="W287" t="inlineStr">
+        <is>
+          <t>Gold'n Treasures</t>
+        </is>
+      </c>
       <c r="X287" t="inlineStr"/>
       <c r="Y287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z287" t="inlineStr"/>
       <c r="AA287" t="inlineStr"/>
-      <c r="AB287" t="inlineStr"/>
+      <c r="AB287" t="inlineStr">
+        <is>
+          <t>https://facebook.com/GoldTreasures, https://X.com/goldn_treasures, https://instagram.com/goldn_treasures</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Strings for Hope</t>
+          <t>Johnson Jewelers</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>(615) 891-4323</t>
+          <t>(651) 735-4400</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>emily@stringsforhope.com</t>
-        </is>
-      </c>
-      <c r="F288" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/emily-winters-182b7a219</t>
-        </is>
-      </c>
+          <t>ryan@johnsonjewelers.com</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr"/>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Emily Winters</t>
+          <t>Bob Johnson</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>https://stringsforhope.com</t>
+          <t>https://johnsonjewelers.com</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>100 Taylor St, Nashville, TN 37208, United States</t>
-        </is>
-      </c>
-      <c r="K288" t="inlineStr"/>
-      <c r="L288" t="inlineStr"/>
+          <t>783 Radio Dr Ste 100D, Saint Paul, MN 55125-5402</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Saint Paul</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>MN</t>
+        </is>
+      </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Nashville, TN</t>
+          <t>Minneapolis, MN</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O288" t="n">
-        <v>5</v>
-      </c>
-      <c r="P288" t="n">
-        <v>23</v>
-      </c>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr"/>
+      <c r="P288" t="inlineStr"/>
       <c r="Q288" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Strings+for+Hope/data=!4m7!3m6!1s0x8864673b2485a245:0x7c5f1d365f1de575!8m2!3d36.1810664!4d-86.7859259!16s%2Fg%2F11p5x5j012!19sChIJRaKFJDtnZIgRdeUdXzYdX3w</t>
+          <t>https://www.bbb.org/us/mn/saint-paul/profile/jewelry-stores/johnson-jewelers-0704-9000723</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>2 of 3, custom-design, since-2010</t>
+          <t>2 of 3, direct-line, custom-design, since-1976</t>
         </is>
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="T288" s="2" t="inlineStr">
         <is>
-          <t>https://stringsforhope.com/pages/about-us</t>
-        </is>
-      </c>
-      <c r="U288" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=%22Emily+Winters%22+Nashville+linkedin&amp;hl=en&amp;num=10</t>
-        </is>
-      </c>
+          <t>https://johnsonjewelers.com/about/employment/</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr"/>
       <c r="V288" t="inlineStr">
         <is>
-          <t>2026-10-14T01:01:21+05:30</t>
+          <t>2026-10-14T05:42:57+05:30</t>
         </is>
       </c>
       <c r="W288" t="inlineStr"/>
       <c r="X288" t="inlineStr"/>
       <c r="Y288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z288" t="inlineStr"/>
-      <c r="AA288" t="inlineStr"/>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>(651) 345-3825</t>
+        </is>
+      </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>https://facebook.com/Stringsforhope, https://instagram.com/stringsforhope</t>
+          <t>https://facebook.com/JohnsonJewelersInc, https://facebook.com/JohnsonJewelersofLakeCity</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Alltribes Indian Art</t>
+          <t>Linden Hills Jewelers LLC</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Jewelers, Native American Goods, Art Goods</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>(800) 417-0024</t>
+          <t>(612) 512-4548</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>admin@alltribes.com</t>
-        </is>
-      </c>
-      <c r="F289" t="inlineStr"/>
+          <t>lindenhillsjewelers@gmail.com</t>
+        </is>
+      </c>
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jason-eurich-58b46614b</t>
+        </is>
+      </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Richard Candy</t>
+          <t>Jason Eurich</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -32662,103 +32698,107 @@
       </c>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>https://alltribes.com</t>
+          <t>https://www.lindenhillsjewelers.com</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>75 W Baseline Rd Ste 6, Gilbert, AZ 85233</t>
+          <t>4305 Upton Ave S, Minneapolis, MN 55410-1556</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>Gilbert</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ</t>
+          <t>Minneapolis, MN</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O289" t="inlineStr"/>
-      <c r="P289" t="inlineStr"/>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="O289" t="n">
+        <v>5</v>
+      </c>
+      <c r="P289" t="n">
+        <v>117</v>
+      </c>
       <c r="Q289" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/gilbert-az/mip/alltribes-indian-art-15755647</t>
+          <t>https://www.bbb.org/us/mn/minneapolis/profile/jewelry-stores/linden-hills-jewelers-llc-0704-1000068648</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, custom-design, since-2023</t>
         </is>
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T289" s="2" t="inlineStr">
         <is>
-          <t>https://alltribes.com/</t>
-        </is>
-      </c>
-      <c r="U289" t="inlineStr"/>
+          <t>https://www.lindenhillsjewelers.com/</t>
+        </is>
+      </c>
+      <c r="U289" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Jason+Eurich%22+Minneapolis+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V289" t="inlineStr">
         <is>
-          <t>2026-10-14T01:46:53+05:30</t>
-        </is>
-      </c>
-      <c r="W289" t="inlineStr"/>
+          <t>2026-10-14T05:12:48+05:30</t>
+        </is>
+      </c>
+      <c r="W289" t="inlineStr">
+        <is>
+          <t>Linden Hills Jewelers</t>
+        </is>
+      </c>
       <c r="X289" t="inlineStr"/>
       <c r="Y289" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z289" t="inlineStr">
-        <is>
-          <t>toll-free</t>
-        </is>
-      </c>
-      <c r="AA289" t="inlineStr">
-        <is>
-          <t>(480) 963-2284</t>
-        </is>
-      </c>
-      <c r="AB289" t="inlineStr">
-        <is>
-          <t>https://facebook.com/alltribes, https://instagram.com/alltribes_indian_art, https://facebook.com/pg/alltribes/videos/</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="Z289" t="inlineStr"/>
+      <c r="AA289" t="inlineStr"/>
+      <c r="AB289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Diasparx</t>
+          <t>R.F. Moeller Jeweler</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Wholesale jeweler</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr"/>
+          <t>Jewelry store</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>(651) 698-6321</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>daniel@diasparx.com</t>
+          <t>alexandra@rfmoeller.com</t>
         </is>
       </c>
       <c r="F290" t="inlineStr"/>
@@ -32766,27 +32806,27 @@
       <c r="H290" t="inlineStr"/>
       <c r="I290" s="2" t="inlineStr">
         <is>
-          <t>https://www.diasparx.com</t>
+          <t>https://rfmoeller.com</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>Camelback Tower, 6900 E Camelback Rd Suite 1050, Scottsdale, AZ 85251, United States</t>
+          <t>2065 Ford Pkwy, St Paul, MN 55116, United States</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>Scottsdale</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ</t>
+          <t>Minneapolis, MN</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -32795,19 +32835,19 @@
         </is>
       </c>
       <c r="O290" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P290" t="n">
-        <v>22</v>
+        <v>2186</v>
       </c>
       <c r="Q290" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Diasparx/data=!4m7!3m6!1s0x872b0b6df95ae9b9:0x57de2ae948b26574!8m2!3d33.5025864!4d-111.9322129!16s%2Fg%2F11x19r328p!19sChIJuela-W0LK4cRdGWySOkq3lc</t>
+          <t>https://www.google.com/maps/place/R.F.+Moeller+Jeweler/data=!4m7!3m6!1s0x87f62978048ef94d:0xea9c4d97c5c2b259!8m2!3d44.9181574!4d-93.1877644!16s%2Fg%2F1v7pz0rd!19sChIJTfmOBHgp9ocRWbLCxZdNnOo</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design</t>
+          <t>2 of 3, direct-line, ags, custom-design, since-1951</t>
         </is>
       </c>
       <c r="S290" t="inlineStr">
@@ -32817,213 +32857,245 @@
       </c>
       <c r="T290" s="2" t="inlineStr">
         <is>
-          <t>https://www.diasparx.com/</t>
+          <t>https://rfmoeller.com/</t>
         </is>
       </c>
       <c r="U290" t="inlineStr"/>
       <c r="V290" t="inlineStr">
         <is>
-          <t>2026-10-14T01:09:41+05:30</t>
-        </is>
-      </c>
-      <c r="W290" t="inlineStr"/>
+          <t>2026-10-14T00:46:15+05:30</t>
+        </is>
+      </c>
+      <c r="W290" t="inlineStr">
+        <is>
+          <t>Moeller Jeweler R. F.</t>
+        </is>
+      </c>
       <c r="X290" t="inlineStr"/>
       <c r="Y290" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z290" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="Z290" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA290" t="inlineStr">
         <is>
-          <t>(212) 555-0134, (480) 640-0948</t>
+          <t>(651) 698-6322</t>
         </is>
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>https://instagram.com/diasparx, https://facebook.com/profile.php?id=100088561748204</t>
+          <t>https://facebook.com/rfmoellerjeweler, https://instagram.com/rfmoellerjeweler</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Expert Shoe Luggage Watch &amp; Jewelry Repair</t>
+          <t>Wayzata Jewelers LLC</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Jewelry repair / goldsmith</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Shoe repair shop</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>(480) 451-1214</t>
+          <t>(952) 239-0099</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>info@expertshoerepair.com</t>
-        </is>
-      </c>
-      <c r="F291" t="inlineStr"/>
-      <c r="G291" t="inlineStr"/>
-      <c r="H291" t="inlineStr"/>
+          <t>jon@wayzatajewelers.com</t>
+        </is>
+      </c>
+      <c r="F291" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jon-gilbert-7a93944b</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Jon Gilbert</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I291" s="2" t="inlineStr">
         <is>
-          <t>https://expertslwjrepair.com</t>
+          <t>https://wayzatajewelers.com</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>10105 E Vía Linda Ste A- 105, Scottsdale, AZ 85258, United States</t>
+          <t>1250 Wayzata Blvd E, Wayzata, MN 55391</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>Scottsdale</t>
+          <t>Wayzata</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ</t>
+          <t>Minneapolis, MN</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="O291" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="P291" t="n">
-        <v>522</v>
+        <v>48</v>
       </c>
       <c r="Q291" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Expert+Shoe+Luggage+Watch+%26+Jewelry+Repair/data=!4m7!3m6!1s0x872b6d13c4a490a7:0x78beb810dbe170f!8m2!3d33.573104!4d-111.8634771!16s%2Fg%2F11hzvcxvl9!19sChIJp5CkxBNtK4cRDxe-DYHriwc</t>
+          <t>https://www.bbb.org/us/mn/wayzata/profile/jewelry-stores/wayzata-jewelers-llc-0704-96346501</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, since-1960</t>
+          <t>2 of 3, custom-design, since-2002</t>
         </is>
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T291" s="2" t="inlineStr">
         <is>
-          <t>https://www.expertshoerepair.com/</t>
-        </is>
-      </c>
-      <c r="U291" t="inlineStr"/>
+          <t>https://wayzatajewelers.com/pages/contact-us</t>
+        </is>
+      </c>
+      <c r="U291" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Jon+Gilbert%22+Wayzata+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V291" t="inlineStr">
         <is>
-          <t>2026-10-14T01:10:03+05:30</t>
-        </is>
-      </c>
-      <c r="W291" t="inlineStr"/>
+          <t>2026-10-14T05:34:51+05:30</t>
+        </is>
+      </c>
+      <c r="W291" t="inlineStr">
+        <is>
+          <t>Wayzata Jewelers</t>
+        </is>
+      </c>
       <c r="X291" t="inlineStr"/>
       <c r="Y291" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z291" t="inlineStr"/>
-      <c r="AA291" t="inlineStr">
-        <is>
-          <t>(480) 269-7591</t>
-        </is>
-      </c>
+      <c r="AA291" t="inlineStr"/>
       <c r="AB291" t="inlineStr">
         <is>
-          <t>https://facebook.com/expertshoerepair, https://instagram.com/expert_shoe_repair</t>
+          <t>https://facebook.com/wayzatajewelers, https://instagram.com/wayzatajewelers</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Sunrise Jewelry &amp; Gallery</t>
+          <t>Bailey's Fine Jewelry</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>(480) 425-9944</t>
+          <t>(919) 829-7337</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>info@sunrisejewelryusa.com</t>
+          <t>carysubs@baileybox.com</t>
         </is>
       </c>
       <c r="F292" t="inlineStr"/>
-      <c r="G292" t="inlineStr"/>
-      <c r="H292" t="inlineStr"/>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Jane Bailey</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
       <c r="I292" s="2" t="inlineStr">
         <is>
-          <t>https://www.sunrisejewelryusa.com</t>
+          <t>https://www.baileybox.com</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>7254 E Main St Suite 101, Scottsdale, AZ 85251, United States</t>
+          <t>415 Daniels St, Raleigh, NC 27605-1314</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>Scottsdale</t>
+          <t>Raleigh</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ</t>
+          <t>Charlotte, NC</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="O292" t="n">
         <v>5</v>
       </c>
       <c r="P292" t="n">
-        <v>98</v>
+        <v>775</v>
       </c>
       <c r="Q292" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Sunrise+Jewelry+%26+Gallery/data=!4m7!3m6!1s0x872b0bd689ab1b37:0xfa243a0d0a63c6b6!8m2!3d33.4932392!4d-111.9247178!16s%2Fg%2F11q1rmxn64!19sChIJNxuridYLK4cRtsZjCg06JPo</t>
+          <t>https://www.bbb.org/us/nc/raleigh/profile/jewelry-stores/baileys-fine-jewelry-0593-20988</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, since-2006</t>
+          <t>2 of 3, direct-line, gia, ags, bench, custom-design, since-1948</t>
         </is>
       </c>
       <c r="S292" t="inlineStr">
@@ -33033,40 +33105,40 @@
       </c>
       <c r="T292" s="2" t="inlineStr">
         <is>
-          <t>https://sunrisejewelryusa.com/</t>
+          <t>https://baileybox.com/</t>
         </is>
       </c>
       <c r="U292" t="inlineStr"/>
       <c r="V292" t="inlineStr">
         <is>
-          <t>2026-10-14T01:05:57+05:30</t>
+          <t>2026-10-14T06:02:43+05:30</t>
         </is>
       </c>
       <c r="W292" t="inlineStr">
         <is>
-          <t>Sunrise Trading Post</t>
+          <t>Morrison Smith Jewelers</t>
         </is>
       </c>
       <c r="X292" t="inlineStr"/>
       <c r="Y292" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z292" t="inlineStr"/>
       <c r="AA292" t="inlineStr">
         <is>
-          <t>(480) 994-0170</t>
+          <t>(252) 353-3434, (252) 443-7676, (919) 892-3838</t>
         </is>
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>https://instagram.com/sunrisejewelryandgallery, https://facebook.com/sunrisejewelryusa</t>
+          <t>https://facebook.com/BaileysFineJewelry, https://instagram.com/baileysfinejewelry, https://instagram.com/morrisonsmithjewelers, https://facebook.com/MorrisonSmithJewelers, https://x.com/morrisonsmith, https://twitter.com/morrisonsmith</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Truly Blessed Jewels - Scottsdale</t>
+          <t>Fink's Jewelers</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -33076,27 +33148,23 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers, Fix-It Shops, Watches</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>(480) 306-4296</t>
+          <t>(704) 366-3120</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>becky@trulyblessedjewels.com</t>
-        </is>
-      </c>
-      <c r="F293" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/lisa-valenzuela-801071264</t>
-        </is>
-      </c>
+          <t>ecommerce@finks.com</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr"/>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Lisa Valenzuela</t>
+          <t>Nathan Fink</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -33106,95 +33174,95 @@
       </c>
       <c r="I293" s="2" t="inlineStr">
         <is>
-          <t>https://trulyblessedjewels.com</t>
+          <t>https://www.finks.com</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>7058 E 5th Ave, Scottsdale, AZ 85251, United States</t>
+          <t>4400 Sharon Rd Ste 199, Charlotte, NC 28211</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>Scottsdale</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ</t>
+          <t>Charlotte, NC</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O293" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P293" t="n">
-        <v>1244</v>
+        <v>1</v>
       </c>
       <c r="Q293" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Truly+Blessed+Jewels+-+Scottsdale/data=!4m7!3m6!1s0x872b0bbd075f72f5:0xe625e386ff4966fb!8m2!3d33.498152!4d-111.9292942!16s%2Fg%2F11hf00j2kh!19sChIJ9XJfB70LK4cR-2ZJ_4bjJeY</t>
+          <t>https://www.yellowpages.com/charlotte-nc/mip/finks-jewelers-464773701</t>
         </is>
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>2 of 3</t>
+          <t>2 of 3, direct-line, custom-design, since-1930</t>
         </is>
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="T293" s="2" t="inlineStr">
         <is>
-          <t>https://trulyblessedjewels.com/pages/contact-us-1</t>
-        </is>
-      </c>
-      <c r="U293" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=%22Lisa+Valenzuela%22+Scottsdale+linkedin&amp;hl=en&amp;num=10</t>
-        </is>
-      </c>
+          <t>https://www.finks.com/</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr"/>
       <c r="V293" t="inlineStr">
         <is>
-          <t>2026-10-14T01:05:54+05:30</t>
+          <t>2026-10-14T01:43:57+05:30</t>
         </is>
       </c>
       <c r="W293" t="inlineStr">
         <is>
-          <t>Truly Blessed Jewels</t>
-        </is>
-      </c>
-      <c r="X293" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ</t>
-        </is>
-      </c>
+          <t>John Paul Fine Jewelry</t>
+        </is>
+      </c>
+      <c r="X293" t="inlineStr"/>
       <c r="Y293" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z293" t="inlineStr"/>
-      <c r="AA293" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="Z293" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>(423) 894-1188, (540) 342-2991, (540) 344-8697, (615) 236-8176, (704) 927-4888, (757) 640-1132, (804) 377-8589, (919) 881-8247</t>
+        </is>
+      </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>https://instagram.com/trulyblessedjewels, https://facebook.com/Truly Blessed Jewels</t>
+          <t>https://facebook.com/FinksJewelers, https://instagram.com/finksjewelers</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Exquisite Timepieces</t>
+          <t>Windsor Jewelers</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -33204,66 +33272,74 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Jewelers, Watches</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>(239) 227-2932</t>
+          <t>(704) 556-7747</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>team@exquisitetimepieces.com</t>
+          <t>nfo@windsor-jewelers.com</t>
         </is>
       </c>
       <c r="F294" t="inlineStr"/>
-      <c r="G294" t="inlineStr"/>
-      <c r="H294" t="inlineStr"/>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Kevin Slusher</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
       <c r="I294" s="2" t="inlineStr">
         <is>
-          <t>https://www.exquisitetimepieces.com</t>
+          <t>https://www.windsor-jewelers.com</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>4380 Gulf Shore Blvd N, Naples, FL 34103</t>
+          <t>6809-D Phillips Pl Ct, Charlotte, NC 28210, United States</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>Naples</t>
+          <t>Winston-Salem</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Naples, FL</t>
+          <t>Charlotte, NC</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O294" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P294" t="n">
-        <v>31</v>
+        <v>1846</v>
       </c>
       <c r="Q294" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/naples-fl/mip/exquisite-timepieces-14306847</t>
+          <t>https://www.google.com/maps/place/Windsor+Jewelers/data=!4m7!3m6!1s0x88569e13f91d1bb1:0x4b6448ed40c4d63c!8m2!3d35.1465046!4d-80.8269547!16s%2Fg%2F1tq8k7xj!19sChIJsRsd-ROeVogRPNbEQO1IZEs</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, ja, since-1998</t>
+          <t>2 of 3, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S294" t="inlineStr">
@@ -33273,36 +33349,36 @@
       </c>
       <c r="T294" s="2" t="inlineStr">
         <is>
-          <t>https://www.exquisitetimepieces.com/</t>
+          <t>https://www.windsor-jewelers.com/</t>
         </is>
       </c>
       <c r="U294" t="inlineStr"/>
       <c r="V294" t="inlineStr">
         <is>
-          <t>2026-10-14T01:47:28+05:30</t>
+          <t>2026-10-14T00:51:17+05:30</t>
         </is>
       </c>
       <c r="W294" t="inlineStr"/>
       <c r="X294" t="inlineStr"/>
       <c r="Y294" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z294" t="inlineStr"/>
       <c r="AA294" t="inlineStr">
         <is>
-          <t>(239) 262-4545</t>
+          <t>(336) 721-1768</t>
         </is>
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>https://facebook.com/pages/Exquisite-Timepieces/138888796144728, https://x.com/TimeExquisite, https://instagram.com/exquisitetimepieces, https://facebook.com/Exquisite-Timepieces-138888796144728, https://twitter.com/TimeExquisite</t>
+          <t>https://instagram.com/windsorjewelersnc/, https://facebook.com/OfficialWindsorJewelersNC</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Gold Silver Naples</t>
+          <t>Lindell Jewelers &amp; Appraisers</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -33312,37 +33388,57 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Gold dealer</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>(239) 591-5999</t>
+          <t>(615) 373-7922</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>goldsilvercoinsofnaples@gmail.com</t>
-        </is>
-      </c>
-      <c r="F295" t="inlineStr"/>
-      <c r="G295" t="inlineStr"/>
-      <c r="H295" t="inlineStr"/>
+          <t>lindelljewels@gmail.com</t>
+        </is>
+      </c>
+      <c r="F295" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/carolyn-linder-19ab1a80</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>Carolyn A. Linder</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I295" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldsilvernaples.com</t>
+          <t>https://www.lindelljewelers.com</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>1575 Pine Ridge Rd Ste 20, Naples, FL 34109, United States</t>
-        </is>
-      </c>
-      <c r="K295" t="inlineStr"/>
-      <c r="L295" t="inlineStr"/>
+          <t>7028 Church St E Ste 106, Brentwood, TN 37027, United States</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Brentwood</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Naples, FL</t>
+          <t>Nashville, TN</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -33351,54 +33447,54 @@
         </is>
       </c>
       <c r="O295" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="P295" t="n">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="Q295" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Gold+Silver+Naples/data=!4m7!3m6!1s0x88db1d7e5a7b7a49:0x324bd0e63a60dfad!8m2!3d26.2126153!4d-81.7867476!16s%2Fg%2F11k9ml4kb0!19sChIJSXp7Wn4d24gRrd9gOubQSzI</t>
+          <t>https://www.google.com/maps/place/Lindell+Jewelers+%26+Appraisers/data=!4m7!3m6!1s0x88647b266e6cc441:0xa03113da3f7ec814!8m2!3d36.0335009!4d-86.7862323!16s%2Fg%2F1tdjrwp3!19sChIJQcRsbiZ7ZIgRFMh-P9oTMaA</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, custom-design, since-1991</t>
         </is>
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T295" s="2" t="inlineStr">
         <is>
-          <t>https://goldsilvernaples.com/</t>
-        </is>
-      </c>
-      <c r="U295" t="inlineStr"/>
+          <t>https://www.lindelljewelers.com/about-us</t>
+        </is>
+      </c>
+      <c r="U295" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Carolyn+A.+Linder%22+Nashville+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V295" t="inlineStr">
         <is>
-          <t>2026-10-14T01:13:03+05:30</t>
+          <t>2026-10-14T01:03:10+05:30</t>
         </is>
       </c>
       <c r="W295" t="inlineStr"/>
       <c r="X295" t="inlineStr"/>
       <c r="Y295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z295" t="inlineStr"/>
-      <c r="AA295" t="inlineStr">
-        <is>
-          <t>(239) 234-9588</t>
-        </is>
-      </c>
+      <c r="AA295" t="inlineStr"/>
       <c r="AB295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>International Diamond Center</t>
+          <t>Strings for Hope</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -33413,40 +33509,44 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>(239) 342-2550</t>
+          <t>(615) 891-4323</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>u003emarketing@shopidc.com</t>
-        </is>
-      </c>
-      <c r="F296" t="inlineStr"/>
+          <t>emily@stringsforhope.com</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/emily-winters-182b7a219</t>
+        </is>
+      </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Keith Leclerc</t>
+          <t>Emily Winters</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>President</t>
         </is>
       </c>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>https://shopidc.com</t>
+          <t>https://stringsforhope.com</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>8840 Tamiami Trl N, Naples, FL 34108, United States</t>
+          <t>100 Taylor St, Nashville, TN 37208, United States</t>
         </is>
       </c>
       <c r="K296" t="inlineStr"/>
       <c r="L296" t="inlineStr"/>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Naples, FL</t>
+          <t>Nashville, TN</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -33455,106 +33555,114 @@
         </is>
       </c>
       <c r="O296" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P296" t="n">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="Q296" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/International+Diamond+Center/data=!4m7!3m6!1s0x88db1f3b506da15f:0xd38690aae0aec00b!8m2!3d26.2479716!4d-81.800361!16s%2Fg%2F11t8h0cjn9!19sChIJX6FtUDsf24gRC8Cu4KqQhtM</t>
+          <t>https://www.google.com/maps/place/Strings+for+Hope/data=!4m7!3m6!1s0x8864673b2485a245:0x7c5f1d365f1de575!8m2!3d36.1810664!4d-86.7859259!16s%2Fg%2F11p5x5j012!19sChIJRaKFJDtnZIgRdeUdXzYdX3w</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design</t>
+          <t>2 of 3, custom-design, since-2010</t>
         </is>
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T296" s="2" t="inlineStr">
         <is>
-          <t>https://shopidc.com/</t>
-        </is>
-      </c>
-      <c r="U296" t="inlineStr"/>
+          <t>https://stringsforhope.com/pages/about-us</t>
+        </is>
+      </c>
+      <c r="U296" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Emily+Winters%22+Nashville+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V296" t="inlineStr">
         <is>
-          <t>2026-10-14T01:15:46+05:30</t>
+          <t>2026-10-14T01:01:21+05:30</t>
         </is>
       </c>
       <c r="W296" t="inlineStr"/>
       <c r="X296" t="inlineStr"/>
       <c r="Y296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z296" t="inlineStr"/>
-      <c r="AA296" t="inlineStr">
-        <is>
-          <t>(239) 364-1799, (352) 681-4550, (407) 770-5991, (407) 862-8990, (407) 903-9494, (727) 572-6323, (772) 408-4640, (813) 961-0097, (863) 226-4400, (912) 354-4344, (941) 278-3900</t>
-        </is>
-      </c>
+      <c r="AA296" t="inlineStr"/>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>https://facebook.com/internationaldiamondcenter, https://instagram.com/internationaldiamondcenter_, https://twitter.com/shopidc</t>
+          <t>https://facebook.com/Stringsforhope, https://instagram.com/stringsforhope</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Mark Loren Design</t>
+          <t>Alltribes Indian Art</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Designers</t>
+          <t>Jewelers, Native American Goods, Art Goods</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>(239) 596-5820</t>
+          <t>(800) 417-0024</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>contact@marklorendesigns.com</t>
+          <t>admin@alltribes.com</t>
         </is>
       </c>
       <c r="F297" t="inlineStr"/>
-      <c r="G297" t="inlineStr"/>
-      <c r="H297" t="inlineStr"/>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Richard Candy</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I297" s="2" t="inlineStr">
         <is>
-          <t>https://www.marklorendesigns.com</t>
+          <t>https://alltribes.com</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>9118 Strada Pl Ste 8120, Naples, FL 34108</t>
+          <t>75 W Baseline Rd Ste 6, Gilbert, AZ 85233</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>Naples</t>
+          <t>Gilbert</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Naples, FL</t>
+          <t>Scottsdale, AZ</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -33566,12 +33674,12 @@
       <c r="P297" t="inlineStr"/>
       <c r="Q297" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/naples-fl/mip/mark-loren-design-475273503</t>
+          <t>https://www.yellowpages.com/gilbert-az/mip/alltribes-indian-art-15755647</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, bench, custom-design</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S297" t="inlineStr">
@@ -33581,13 +33689,13 @@
       </c>
       <c r="T297" s="2" t="inlineStr">
         <is>
-          <t>https://marklorendesigns.com/</t>
+          <t>https://alltribes.com/</t>
         </is>
       </c>
       <c r="U297" t="inlineStr"/>
       <c r="V297" t="inlineStr">
         <is>
-          <t>2026-10-14T01:47:36+05:30</t>
+          <t>2026-10-14T01:46:53+05:30</t>
         </is>
       </c>
       <c r="W297" t="inlineStr"/>
@@ -33595,22 +33703,26 @@
       <c r="Y297" t="n">
         <v>0</v>
       </c>
-      <c r="Z297" t="inlineStr"/>
+      <c r="Z297" t="inlineStr">
+        <is>
+          <t>toll-free</t>
+        </is>
+      </c>
       <c r="AA297" t="inlineStr">
         <is>
-          <t>(239) 482-4664</t>
+          <t>(480) 963-2284</t>
         </is>
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>https://facebook.com/marklorendesigns, https://instagram.com/marklorendesign</t>
+          <t>https://facebook.com/alltribes, https://instagram.com/alltribes_indian_art, https://facebook.com/pg/alltribes/videos/</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Black Rock Galleries</t>
+          <t>Diasparx</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -33620,17 +33732,13 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Estate liquidator</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>(203) 900-1110</t>
-        </is>
-      </c>
+          <t>Wholesale jeweler</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr">
         <is>
-          <t>april@blackrockgalleries.com</t>
+          <t>daniel@diasparx.com</t>
         </is>
       </c>
       <c r="F298" t="inlineStr"/>
@@ -33638,27 +33746,27 @@
       <c r="H298" t="inlineStr"/>
       <c r="I298" s="2" t="inlineStr">
         <is>
-          <t>https://www.blackrockgalleries.com</t>
+          <t>https://www.diasparx.com</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>179 Hamilton Ave, Greenwich, CT 06830, United States</t>
+          <t>Camelback Tower, 6900 E Camelback Rd Suite 1050, Scottsdale, AZ 85251, United States</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>Cary</t>
+          <t>Scottsdale</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Greenwich, CT</t>
+          <t>Scottsdale, AZ</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -33667,19 +33775,19 @@
         </is>
       </c>
       <c r="O298" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="P298" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Q298" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Black+Rock+Galleries/data=!4m7!3m6!1s0x89c299cdad7d8901:0x806db5b713ec68d7!8m2!3d41.0179193!4d-73.6391571!16s%2Fg%2F11ckvlk1pv!19sChIJAYl9rc2ZwokR12jsE7e1bYA</t>
+          <t>https://www.google.com/maps/place/Diasparx/data=!4m7!3m6!1s0x872b0b6df95ae9b9:0x57de2ae948b26574!8m2!3d33.5025864!4d-111.9322129!16s%2Fg%2F11x19r328p!19sChIJuela-W0LK4cRdGWySOkq3lc</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia</t>
+          <t>2 of 3, direct-line, gia, custom-design</t>
         </is>
       </c>
       <c r="S298" t="inlineStr">
@@ -33689,13 +33797,13 @@
       </c>
       <c r="T298" s="2" t="inlineStr">
         <is>
-          <t>https://www.blackrockgalleries.com/contact</t>
+          <t>https://www.diasparx.com/</t>
         </is>
       </c>
       <c r="U298" t="inlineStr"/>
       <c r="V298" t="inlineStr">
         <is>
-          <t>2026-10-14T01:19:56+05:30</t>
+          <t>2026-10-14T01:09:41+05:30</t>
         </is>
       </c>
       <c r="W298" t="inlineStr"/>
@@ -33706,71 +33814,67 @@
       <c r="Z298" t="inlineStr"/>
       <c r="AA298" t="inlineStr">
         <is>
-          <t>(203) 335-0000, (203) 335-4444, (919) 702-7000</t>
+          <t>(212) 555-0134, (480) 640-0948</t>
         </is>
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>https://facebook.com/blackrockgalleries, https://twitter.com/BRGalleries, https://instagram.com/blackrockgalleries</t>
+          <t>https://instagram.com/diasparx, https://facebook.com/profile.php?id=100088561748204</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Estate Treasures of Greenwich</t>
+          <t>Expert Shoe Luggage Watch &amp; Jewelry Repair</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Jewelry repair / goldsmith</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Furniture store</t>
+          <t>Shoe repair shop</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>(203) 637-4200</t>
+          <t>(480) 451-1214</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>hjantiques@aol.com</t>
-        </is>
-      </c>
-      <c r="F299" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/harriet-roughan-8982a220</t>
-        </is>
-      </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>Harriet Roughan</t>
-        </is>
-      </c>
-      <c r="H299" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
+          <t>info@expertshoerepair.com</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr"/>
+      <c r="G299" t="inlineStr"/>
+      <c r="H299" t="inlineStr"/>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>https://www.estatetreasures.com</t>
+          <t>https://expertslwjrepair.com</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>1381 E Putnam Ave, Old Greenwich, CT 06870, United States</t>
-        </is>
-      </c>
-      <c r="K299" t="inlineStr"/>
-      <c r="L299" t="inlineStr"/>
+          <t>10105 E Vía Linda Ste A- 105, Scottsdale, AZ 85258, United States</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Scottsdale</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Greenwich, CT</t>
+          <t>Scottsdale, AZ</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -33779,58 +33883,58 @@
         </is>
       </c>
       <c r="O299" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="P299" t="n">
-        <v>45</v>
+        <v>522</v>
       </c>
       <c r="Q299" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Estate+Treasures+of+Greenwich/data=!4m7!3m6!1s0x89c298bd469b9045:0x4341ef96fb235d28!8m2!3d41.0447405!4d-73.5728257!16s%2Fg%2F1tg4xsb0!19sChIJRZCbRr2YwokRKF0j-5bvQUM</t>
+          <t>https://www.google.com/maps/place/Expert+Shoe+Luggage+Watch+%26+Jewelry+Repair/data=!4m7!3m6!1s0x872b6d13c4a490a7:0x78beb810dbe170f!8m2!3d33.573104!4d-111.8634771!16s%2Fg%2F11hzvcxvl9!19sChIJp5CkxBNtK4cRDxe-DYHriwc</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>2 of 3, custom-design</t>
+          <t>2 of 3, role-email, direct-line, since-1960</t>
         </is>
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="T299" s="2" t="inlineStr">
         <is>
-          <t>https://estatetreasures.com/</t>
-        </is>
-      </c>
-      <c r="U299" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=%22Harriet+Roughan%22+Greenwich+linkedin&amp;hl=en&amp;num=10</t>
-        </is>
-      </c>
+          <t>https://www.expertshoerepair.com/</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr"/>
       <c r="V299" t="inlineStr">
         <is>
-          <t>2026-10-14T01:18:54+05:30</t>
+          <t>2026-10-14T01:10:03+05:30</t>
         </is>
       </c>
       <c r="W299" t="inlineStr"/>
       <c r="X299" t="inlineStr"/>
       <c r="Y299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z299" t="inlineStr"/>
-      <c r="AA299" t="inlineStr"/>
+      <c r="AA299" t="inlineStr">
+        <is>
+          <t>(480) 269-7591</t>
+        </is>
+      </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>https://facebook.com/EstateTreasuresGreenwich, https://instagram.com/estatetreasuresgreenwich</t>
+          <t>https://facebook.com/expertshoerepair, https://instagram.com/expert_shoe_repair</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Fine Elegant Jewelry</t>
+          <t>Sunrise Jewelry &amp; Gallery</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -33840,17 +33944,17 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>(914) 937-2045</t>
+          <t>(480) 425-9944</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>elegantempirejewelers@gmail.com</t>
+          <t>info@sunrisejewelryusa.com</t>
         </is>
       </c>
       <c r="F300" t="inlineStr"/>
@@ -33858,48 +33962,48 @@
       <c r="H300" t="inlineStr"/>
       <c r="I300" s="2" t="inlineStr">
         <is>
-          <t>https://eejewelers.com</t>
+          <t>https://www.sunrisejewelryusa.com</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>27 N Main St, Port Chester, NY 10573</t>
+          <t>7254 E Main St Suite 101, Scottsdale, AZ 85251, United States</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>Port Chester</t>
+          <t>Scottsdale</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Greenwich, CT</t>
+          <t>Scottsdale, AZ</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O300" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P300" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="Q300" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/port-chester-ny/mip/fine-elegant-jewelry-482445004</t>
+          <t>https://www.google.com/maps/place/Sunrise+Jewelry+%26+Gallery/data=!4m7!3m6!1s0x872b0bd689ab1b37:0xfa243a0d0a63c6b6!8m2!3d33.4932392!4d-111.9247178!16s%2Fg%2F11q1rmxn64!19sChIJNxuridYLK4cRtsZjCg06JPo</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design</t>
+          <t>2 of 3, role-email, direct-line, since-2006</t>
         </is>
       </c>
       <c r="S300" t="inlineStr">
@@ -33909,49 +34013,45 @@
       </c>
       <c r="T300" s="2" t="inlineStr">
         <is>
-          <t>https://eejewelers.com/</t>
+          <t>https://sunrisejewelryusa.com/</t>
         </is>
       </c>
       <c r="U300" t="inlineStr"/>
       <c r="V300" t="inlineStr">
         <is>
-          <t>2026-10-14T01:48:10+05:30</t>
+          <t>2026-10-14T01:05:57+05:30</t>
         </is>
       </c>
       <c r="W300" t="inlineStr">
         <is>
-          <t>Elegant Empire Jewelers</t>
+          <t>Sunrise Trading Post</t>
         </is>
       </c>
       <c r="X300" t="inlineStr"/>
       <c r="Y300" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z300" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Z300" t="inlineStr"/>
       <c r="AA300" t="inlineStr">
         <is>
-          <t>(914) 305-3385</t>
+          <t>(480) 994-0170</t>
         </is>
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>https://instagram.com/eejewelers/, https://facebook.com/EEJewelers</t>
+          <t>https://instagram.com/sunrisejewelryandgallery, https://facebook.com/sunrisejewelryusa</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Steven Fox Jewelry</t>
+          <t>Truly Blessed Jewels - Scottsdale</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -33961,40 +34061,52 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>(203) 344-5409</t>
+          <t>(480) 306-4296</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>concierge@stevenfoxjewelry.com</t>
-        </is>
-      </c>
-      <c r="F301" t="inlineStr"/>
-      <c r="G301" t="inlineStr"/>
-      <c r="H301" t="inlineStr"/>
+          <t>becky@trulyblessedjewels.com</t>
+        </is>
+      </c>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lisa-valenzuela-801071264</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>Lisa Valenzuela</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>https://www.stevenfoxjewelry.com</t>
+          <t>https://trulyblessedjewels.com</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>8 Lewis St, Greenwich, CT 06830, United States</t>
+          <t>7058 E 5th Ave, Scottsdale, AZ 85251, United States</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>Greenwich</t>
+          <t>Scottsdale</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Greenwich, CT</t>
+          <t>Scottsdale, AZ</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -34003,58 +34115,66 @@
         </is>
       </c>
       <c r="O301" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P301" t="n">
-        <v>277</v>
+        <v>1244</v>
       </c>
       <c r="Q301" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Steven+Fox+Jewelry/data=!4m7!3m6!1s0x89c298489c931a41:0x67f0cb095f8447aa!8m2!3d41.0287029!4d-73.6255657!16s%2Fg%2F1thn6fp7!19sChIJQRqTnEiYwokRqkeEXwnL8Gc</t>
+          <t>https://www.google.com/maps/place/Truly+Blessed+Jewels+-+Scottsdale/data=!4m7!3m6!1s0x872b0bbd075f72f5:0xe625e386ff4966fb!8m2!3d33.498152!4d-111.9292942!16s%2Fg%2F11hf00j2kh!19sChIJ9XJfB70LK4cR-2ZJ_4bjJeY</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3</t>
         </is>
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T301" s="2" t="inlineStr">
         <is>
-          <t>https://www.stevenfoxjewelry.com/</t>
-        </is>
-      </c>
-      <c r="U301" t="inlineStr"/>
+          <t>https://trulyblessedjewels.com/pages/contact-us-1</t>
+        </is>
+      </c>
+      <c r="U301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Lisa+Valenzuela%22+Scottsdale+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V301" t="inlineStr">
         <is>
-          <t>2026-10-14T01:17:44+05:30</t>
-        </is>
-      </c>
-      <c r="W301" t="inlineStr"/>
-      <c r="X301" t="inlineStr"/>
+          <t>2026-10-14T01:05:54+05:30</t>
+        </is>
+      </c>
+      <c r="W301" t="inlineStr">
+        <is>
+          <t>Truly Blessed Jewels</t>
+        </is>
+      </c>
+      <c r="X301" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ</t>
+        </is>
+      </c>
       <c r="Y301" t="n">
         <v>1</v>
       </c>
       <c r="Z301" t="inlineStr"/>
-      <c r="AA301" t="inlineStr">
-        <is>
-          <t>(203) 629-3303</t>
-        </is>
-      </c>
+      <c r="AA301" t="inlineStr"/>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>https://instagram.com/stevenfoxjewelry, https://facebook.com/stevenfoxjewelry</t>
+          <t>https://instagram.com/trulyblessedjewels, https://facebook.com/Truly Blessed Jewels</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Triple G Fine Jewelry Inc</t>
+          <t>Exquisite Timepieces</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -34064,17 +34184,17 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>shop=jewelry</t>
+          <t>Jewelers, Watches</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>(914) 937-2931</t>
+          <t>(239) 227-2932</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>rakhmin20@icloud.com</t>
+          <t>team@exquisitetimepieces.com</t>
         </is>
       </c>
       <c r="F302" t="inlineStr"/>
@@ -34082,48 +34202,48 @@
       <c r="H302" t="inlineStr"/>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>https://triplegjewelry.rafaelsjewelrystore.com</t>
+          <t>https://www.exquisitetimepieces.com</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>38 South Main Street, Port Chester, NY 10573</t>
+          <t>4380 Gulf Shore Blvd N, Naples, FL 34103</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>Port Chester</t>
+          <t>Naples</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Greenwich, CT</t>
+          <t>Naples, FL</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>OpenStreetMap</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O302" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="P302" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="Q302" s="2" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/10302134827</t>
+          <t>https://www.yellowpages.com/naples-fl/mip/exquisite-timepieces-14306847</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, role-email, direct-line, ja, since-1998</t>
         </is>
       </c>
       <c r="S302" t="inlineStr">
@@ -34133,40 +34253,36 @@
       </c>
       <c r="T302" s="2" t="inlineStr">
         <is>
-          <t>https://triplegjewelry.rafaelsjewelrystore.com/</t>
+          <t>https://www.exquisitetimepieces.com/</t>
         </is>
       </c>
       <c r="U302" t="inlineStr"/>
       <c r="V302" t="inlineStr">
         <is>
-          <t>2026-10-14T01:19:19+05:30</t>
-        </is>
-      </c>
-      <c r="W302" t="inlineStr">
-        <is>
-          <t>Triple J Fine Jewelry Inc, Triple J Jew Jewelry</t>
-        </is>
-      </c>
+          <t>2026-10-14T01:47:28+05:30</t>
+        </is>
+      </c>
+      <c r="W302" t="inlineStr"/>
       <c r="X302" t="inlineStr"/>
       <c r="Y302" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z302" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z302" t="inlineStr"/>
       <c r="AA302" t="inlineStr">
         <is>
-          <t>(917) 535-4155</t>
-        </is>
-      </c>
-      <c r="AB302" t="inlineStr"/>
+          <t>(239) 262-4545</t>
+        </is>
+      </c>
+      <c r="AB302" t="inlineStr">
+        <is>
+          <t>https://facebook.com/pages/Exquisite-Timepieces/138888796144728, https://x.com/TimeExquisite, https://instagram.com/exquisitetimepieces, https://facebook.com/Exquisite-Timepieces-138888796144728, https://twitter.com/TimeExquisite</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Arlex Jewelry Watches &amp; Clocks</t>
+          <t>Gold Silver Naples</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -34176,17 +34292,17 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Gold dealer</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>(561) 641-8162</t>
+          <t>(239) 591-5999</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>info@arlexjewelry.com</t>
+          <t>goldsilvercoinsofnaples@gmail.com</t>
         </is>
       </c>
       <c r="F303" t="inlineStr"/>
@@ -34194,27 +34310,19 @@
       <c r="H303" t="inlineStr"/>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>https://arlexjewelry.com</t>
+          <t>https://www.goldsilvernaples.com</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>808 Lake Ave, Lake Worth Beach, FL 33460, United States</t>
-        </is>
-      </c>
-      <c r="K303" t="inlineStr">
-        <is>
-          <t>Lake Worth Beach</t>
-        </is>
-      </c>
-      <c r="L303" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
+          <t>1575 Pine Ridge Rd Ste 20, Naples, FL 34109, United States</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr"/>
+      <c r="L303" t="inlineStr"/>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Palm Beach, FL</t>
+          <t>Naples, FL</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -34223,19 +34331,19 @@
         </is>
       </c>
       <c r="O303" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="P303" t="n">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="Q303" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Arlex+Jewelry+Watches+%26+Clocks/data=!4m7!3m6!1s0x88d8d834517d5a4d:0x1255d4758f02268f!8m2!3d26.6160147!4d-80.0567684!16s%2Fg%2F1tkc2xb0!19sChIJTVp9UTTY2IgRjyYCj3XUVRI</t>
+          <t>https://www.google.com/maps/place/Gold+Silver+Naples/data=!4m7!3m6!1s0x88db1d7e5a7b7a49:0x324bd0e63a60dfad!8m2!3d26.2126153!4d-81.7867476!16s%2Fg%2F11k9ml4kb0!19sChIJSXp7Wn4d24gRrd9gOubQSzI</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-1987</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S303" t="inlineStr">
@@ -34245,97 +34353,101 @@
       </c>
       <c r="T303" s="2" t="inlineStr">
         <is>
-          <t>https://arlexjewelry.com/contact/</t>
+          <t>https://goldsilvernaples.com/</t>
         </is>
       </c>
       <c r="U303" t="inlineStr"/>
       <c r="V303" t="inlineStr">
         <is>
-          <t>2026-10-14T01:30:48+05:30</t>
-        </is>
-      </c>
-      <c r="W303" t="inlineStr">
-        <is>
-          <t>Arlex Jewelry Watches, Arlex Clocks, Arlex Jewelry &amp; Clocks</t>
-        </is>
-      </c>
+          <t>2026-10-14T01:13:03+05:30</t>
+        </is>
+      </c>
+      <c r="W303" t="inlineStr"/>
       <c r="X303" t="inlineStr"/>
       <c r="Y303" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z303" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z303" t="inlineStr"/>
       <c r="AA303" t="inlineStr">
         <is>
-          <t>(561) 876-7030</t>
-        </is>
-      </c>
-      <c r="AB303" t="inlineStr">
-        <is>
-          <t>https://facebook.com/Arlex-Jewelry-Watches-Clocks-811607869050062, https://twitter.com/arlexclocks, https://instagram.com/arlexjewelry11, https://facebook.com/ArlexJewelry, https://twitter.com/ArlexClocks</t>
-        </is>
-      </c>
+          <t>(239) 234-9588</t>
+        </is>
+      </c>
+      <c r="AB303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Gemstone Gallery</t>
+          <t>International Diamond Center</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Designers</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>(561) 586-8868</t>
+          <t>(239) 342-2550</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>info@mygemstonegallery.com</t>
+          <t>u003emarketing@shopidc.com</t>
         </is>
       </c>
       <c r="F304" t="inlineStr"/>
-      <c r="G304" t="inlineStr"/>
-      <c r="H304" t="inlineStr"/>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>Keith Leclerc</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>https://www.mygemstonegallery.com</t>
-        </is>
-      </c>
-      <c r="J304" t="inlineStr"/>
+          <t>https://shopidc.com</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>8840 Tamiami Trl N, Naples, FL 34108, United States</t>
+        </is>
+      </c>
       <c r="K304" t="inlineStr"/>
       <c r="L304" t="inlineStr"/>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Palm Beach, FL</t>
+          <t>Naples, FL</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O304" t="inlineStr"/>
-      <c r="P304" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O304" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P304" t="n">
+        <v>278</v>
+      </c>
       <c r="Q304" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/nationwide/mip/gemstone-gallery-451204537</t>
+          <t>https://www.google.com/maps/place/International+Diamond+Center/data=!4m7!3m6!1s0x88db1f3b506da15f:0xd38690aae0aec00b!8m2!3d26.2479716!4d-81.800361!16s%2Fg%2F11t8h0cjn9!19sChIJX6FtUDsf24gRC8Cu4KqQhtM</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S304" t="inlineStr">
@@ -34345,60 +34457,56 @@
       </c>
       <c r="T304" s="2" t="inlineStr">
         <is>
-          <t>https://www.mygemstonegallery.com/</t>
+          <t>https://shopidc.com/</t>
         </is>
       </c>
       <c r="U304" t="inlineStr"/>
       <c r="V304" t="inlineStr">
         <is>
-          <t>2026-10-14T01:50:22+05:30</t>
+          <t>2026-10-14T01:15:46+05:30</t>
         </is>
       </c>
       <c r="W304" t="inlineStr"/>
       <c r="X304" t="inlineStr"/>
       <c r="Y304" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z304" t="inlineStr">
-        <is>
-          <t>no-address</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Z304" t="inlineStr"/>
       <c r="AA304" t="inlineStr">
         <is>
-          <t>(917) 406-0779</t>
+          <t>(239) 364-1799, (352) 681-4550, (407) 770-5991, (407) 862-8990, (407) 903-9494, (727) 572-6323, (772) 408-4640, (813) 961-0097, (863) 226-4400, (912) 354-4344, (941) 278-3900</t>
         </is>
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>https://facebook.com/SuzanneHDeBow, https://twitter.com/GemstoneGallery, https://instagram.com/mygemstone_gallery</t>
+          <t>https://facebook.com/internationaldiamondcenter, https://instagram.com/internationaldiamondcenter_, https://twitter.com/shopidc</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Hamilton Jewelers</t>
+          <t>Mark Loren Design</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Jeweler</t>
+          <t>Jewelers, Jewelry Designers</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>(561) 659-6788</t>
+          <t>(239) 596-5820</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>emartano@hamiltonjewelers.com</t>
+          <t>contact@marklorendesigns.com</t>
         </is>
       </c>
       <c r="F305" t="inlineStr"/>
@@ -34406,17 +34514,17 @@
       <c r="H305" t="inlineStr"/>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>https://hamiltonjewelers.com</t>
+          <t>https://www.marklorendesigns.com</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>215 Worth Ave, Palm Beach, FL 33480, United States</t>
+          <t>9118 Strada Pl Ste 8120, Naples, FL 34108</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>Palm Beach Gardens</t>
+          <t>Naples</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -34426,28 +34534,24 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Palm Beach, FL</t>
+          <t>Naples, FL</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O305" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P305" t="n">
-        <v>77</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr"/>
+      <c r="P305" t="inlineStr"/>
       <c r="Q305" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Hamilton+Jewelers/data=!4m7!3m6!1s0x88d8d6ec71416949:0x1f20ced2ff0489d1!8m2!3d26.7009363!4d-80.0371549!16s%2Fg%2F1tfz0xfv!19sChIJSWlBcezW2IgR0YkE_9LOIB8</t>
+          <t>https://www.yellowpages.com/naples-fl/mip/mark-loren-design-475273503</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design, since-1912</t>
+          <t>2 of 3, role-email, direct-line, bench, custom-design</t>
         </is>
       </c>
       <c r="S305" t="inlineStr">
@@ -34457,56 +34561,56 @@
       </c>
       <c r="T305" s="2" t="inlineStr">
         <is>
-          <t>https://hamiltonjewelers.com/</t>
+          <t>https://marklorendesigns.com/</t>
         </is>
       </c>
       <c r="U305" t="inlineStr"/>
       <c r="V305" t="inlineStr">
         <is>
-          <t>2026-10-14T01:25:01+05:30</t>
+          <t>2026-10-14T01:47:36+05:30</t>
         </is>
       </c>
       <c r="W305" t="inlineStr"/>
       <c r="X305" t="inlineStr"/>
       <c r="Y305" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z305" t="inlineStr"/>
       <c r="AA305" t="inlineStr">
         <is>
-          <t>(609) 375-8003</t>
+          <t>(239) 482-4664</t>
         </is>
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>https://instagram.com/hamiltonjewelers, https://facebook.com/HamiltonJeweler</t>
+          <t>https://facebook.com/marklorendesigns, https://instagram.com/marklorendesign</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Raymond Lee Jewelers</t>
+          <t>Black Rock Galleries</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Estate liquidator</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>(561) 622-7744</t>
+          <t>(203) 900-1110</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>info@raymondleejewelers.net</t>
+          <t>april@blackrockgalleries.com</t>
         </is>
       </c>
       <c r="F306" t="inlineStr"/>
@@ -34514,44 +34618,48 @@
       <c r="H306" t="inlineStr"/>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>https://www.raymondleejewelers.net</t>
+          <t>https://www.blackrockgalleries.com</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>500 Village Square Xing, Palm Beach Gardens, FL 33410</t>
+          <t>179 Hamilton Ave, Greenwich, CT 06830, United States</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>Palm Beach Gardens</t>
+          <t>Cary</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Palm Beach, FL</t>
+          <t>Greenwich, CT</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O306" t="inlineStr"/>
-      <c r="P306" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O306" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P306" t="n">
+        <v>25</v>
+      </c>
       <c r="Q306" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/palm-beach-gardens-fl/mip/raymond-lee-jewelers-3693798</t>
+          <t>https://www.google.com/maps/place/Black+Rock+Galleries/data=!4m7!3m6!1s0x89c299cdad7d8901:0x806db5b713ec68d7!8m2!3d41.0179193!4d-73.6391571!16s%2Fg%2F11ckvlk1pv!19sChIJAYl9rc2ZwokR12jsE7e1bYA</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1983</t>
+          <t>2 of 3, direct-line, gia</t>
         </is>
       </c>
       <c r="S306" t="inlineStr">
@@ -34561,117 +34669,129 @@
       </c>
       <c r="T306" s="2" t="inlineStr">
         <is>
-          <t>https://raymondleejewelers.net/pages/contact</t>
+          <t>https://www.blackrockgalleries.com/contact</t>
         </is>
       </c>
       <c r="U306" t="inlineStr"/>
       <c r="V306" t="inlineStr">
         <is>
-          <t>2026-10-14T01:50:37+05:30</t>
+          <t>2026-10-14T01:19:56+05:30</t>
         </is>
       </c>
       <c r="W306" t="inlineStr"/>
       <c r="X306" t="inlineStr"/>
       <c r="Y306" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z306" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z306" t="inlineStr"/>
       <c r="AA306" t="inlineStr">
         <is>
-          <t>(561) 750-7808</t>
-        </is>
-      </c>
-      <c r="AB306" t="inlineStr"/>
+          <t>(203) 335-0000, (203) 335-4444, (919) 702-7000</t>
+        </is>
+      </c>
+      <c r="AB306" t="inlineStr">
+        <is>
+          <t>https://facebook.com/blackrockgalleries, https://twitter.com/BRGalleries, https://instagram.com/blackrockgalleries</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Signature Diamonds</t>
+          <t>Estate Treasures of Greenwich</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Jewelers, Diamonds</t>
+          <t>Furniture store</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>(561) 686-5730</t>
+          <t>(203) 637-4200</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>signaturebuyers@yahoo.com</t>
-        </is>
-      </c>
-      <c r="F307" t="inlineStr"/>
-      <c r="G307" t="inlineStr"/>
-      <c r="H307" t="inlineStr"/>
+          <t>hjantiques@aol.com</t>
+        </is>
+      </c>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/harriet-roughan-8982a220</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>Harriet Roughan</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I307" s="2" t="inlineStr">
         <is>
-          <t>https://sellyourdiamondsflorida.com</t>
+          <t>https://www.estatetreasures.com</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>2200 N Florida Mango Rd, West Palm Beach, FL 33409</t>
-        </is>
-      </c>
-      <c r="K307" t="inlineStr">
-        <is>
-          <t>West Palm Beach</t>
-        </is>
-      </c>
-      <c r="L307" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
+          <t>1381 E Putnam Ave, Old Greenwich, CT 06870, United States</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr"/>
+      <c r="L307" t="inlineStr"/>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Palm Beach, FL</t>
+          <t>Greenwich, CT</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O307" t="inlineStr"/>
-      <c r="P307" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O307" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P307" t="n">
+        <v>45</v>
+      </c>
       <c r="Q307" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/west-palm-beach-fl/mip/signature-diamonds-538406637</t>
+          <t>https://www.google.com/maps/place/Estate+Treasures+of+Greenwich/data=!4m7!3m6!1s0x89c298bd469b9045:0x4341ef96fb235d28!8m2!3d41.0447405!4d-73.5728257!16s%2Fg%2F1tg4xsb0!19sChIJRZCbRr2YwokRKF0j-5bvQUM</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design, since-1945</t>
+          <t>2 of 3, custom-design</t>
         </is>
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T307" s="2" t="inlineStr">
         <is>
-          <t>https://sellyourdiamondsflorida.com/</t>
-        </is>
-      </c>
-      <c r="U307" t="inlineStr"/>
+          <t>https://estatetreasures.com/</t>
+        </is>
+      </c>
+      <c r="U307" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Harriet+Roughan%22+Greenwich+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V307" t="inlineStr">
         <is>
-          <t>2026-10-14T01:50:22+05:30</t>
+          <t>2026-10-14T01:18:54+05:30</t>
         </is>
       </c>
       <c r="W307" t="inlineStr"/>
@@ -34680,21 +34800,17 @@
         <v>0</v>
       </c>
       <c r="Z307" t="inlineStr"/>
-      <c r="AA307" t="inlineStr">
-        <is>
-          <t>(772) 562-6893</t>
-        </is>
-      </c>
+      <c r="AA307" t="inlineStr"/>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>https://facebook.com/pages/Signature-Estate-Diamond-Buyers/699915383378286, https://twitter.com/signaturebuyer</t>
+          <t>https://facebook.com/EstateTreasuresGreenwich, https://instagram.com/estatetreasuresgreenwich</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>WPBWatchCo</t>
+          <t>Fine Elegant Jewelry</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -34704,122 +34820,118 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Watch store</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>(561) 220-9107</t>
+          <t>(914) 937-2045</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>arinaldi@wpbwatchco.com</t>
-        </is>
-      </c>
-      <c r="F308" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/anthony-rinaldi-0293451b</t>
-        </is>
-      </c>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>Anthony Rinaldi</t>
-        </is>
-      </c>
-      <c r="H308" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
+          <t>elegantempirejewelers@gmail.com</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr"/>
+      <c r="G308" t="inlineStr"/>
+      <c r="H308" t="inlineStr"/>
       <c r="I308" s="2" t="inlineStr">
         <is>
-          <t>https://www.wpbwatchco.com</t>
+          <t>https://eejewelers.com</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>1601 Forum Pl #1010, West Palm Beach, FL 33401, United States</t>
+          <t>27 N Main St, Port Chester, NY 10573</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>West Palm Beach</t>
+          <t>Port Chester</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Palm Beach, FL</t>
+          <t>Greenwich, CT</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O308" t="n">
         <v>4.9</v>
       </c>
       <c r="P308" t="n">
-        <v>622</v>
+        <v>115</v>
       </c>
       <c r="Q308" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/WPBWatchCo/data=!4m7!3m6!1s0x88d91e304542d111:0xdd417b5f344332dc!8m2!3d26.7271055!4d-80.0794774!16s%2Fg%2F11dymb1krc!19sChIJEdFCRTAe2YgR3DJDNF97Qd0</t>
+          <t>https://www.yellowpages.com/port-chester-ny/mip/fine-elegant-jewelry-482445004</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>2 of 3, since-2015</t>
+          <t>2 of 3, direct-line, gia, custom-design</t>
         </is>
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="T308" s="2" t="inlineStr">
         <is>
-          <t>https://wpbwatchco.com/</t>
-        </is>
-      </c>
-      <c r="U308" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=%22Anthony+Rinaldi%22+Palm+Beach+linkedin&amp;hl=en&amp;num=10</t>
-        </is>
-      </c>
+          <t>https://eejewelers.com/</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr"/>
       <c r="V308" t="inlineStr">
         <is>
-          <t>2026-10-14T01:27:35+05:30</t>
-        </is>
-      </c>
-      <c r="W308" t="inlineStr"/>
+          <t>2026-10-14T01:48:10+05:30</t>
+        </is>
+      </c>
+      <c r="W308" t="inlineStr">
+        <is>
+          <t>Elegant Empire Jewelers</t>
+        </is>
+      </c>
       <c r="X308" t="inlineStr"/>
       <c r="Y308" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z308" t="inlineStr"/>
-      <c r="AA308" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Z308" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>(914) 305-3385</t>
+        </is>
+      </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>https://instagram.com/wpb_watch_co, https://facebook.com/anthony.rinaldi.7370</t>
+          <t>https://instagram.com/eejewelers/, https://facebook.com/EEJewelers</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>YAFA Palm Beach</t>
+          <t>Steven Fox Jewelry</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -34829,12 +34941,12 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>(561) 331-8611</t>
+          <t>(203) 344-5409</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>inquire@yafajewelry.com</t>
+          <t>concierge@stevenfoxjewelry.com</t>
         </is>
       </c>
       <c r="F309" t="inlineStr"/>
@@ -34842,27 +34954,27 @@
       <c r="H309" t="inlineStr"/>
       <c r="I309" s="2" t="inlineStr">
         <is>
-          <t>https://yafasignedjewels.com</t>
+          <t>https://www.stevenfoxjewelry.com</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>234 Worth Ave, Palm Beach, FL 33480, United States</t>
+          <t>8 Lewis St, Greenwich, CT 06830, United States</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>Palm Beach</t>
+          <t>Greenwich</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Palm Beach, FL</t>
+          <t>Greenwich, CT</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -34874,16 +34986,16 @@
         <v>5</v>
       </c>
       <c r="P309" t="n">
-        <v>9</v>
+        <v>277</v>
       </c>
       <c r="Q309" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/YAFA+Palm+Beach/data=!4m7!3m6!1s0x89c258fef868bda1:0x84b1b16f5ab524a9!8m2!3d26.7006755!4d-80.0378935!16s%2Fg%2F1td4l0sf!19sChIJob1o-P5YwokRqSS1Wm-xsYQ</t>
+          <t>https://www.google.com/maps/place/Steven+Fox+Jewelry/data=!4m7!3m6!1s0x89c298489c931a41:0x67f0cb095f8447aa!8m2!3d41.0287029!4d-73.6255657!16s%2Fg%2F1thn6fp7!19sChIJQRqTnEiYwokRqkeEXwnL8Gc</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, since-1985</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S309" t="inlineStr">
@@ -34893,60 +35005,56 @@
       </c>
       <c r="T309" s="2" t="inlineStr">
         <is>
-          <t>https://yafasignedjewels.com/pages/contact</t>
+          <t>https://www.stevenfoxjewelry.com/</t>
         </is>
       </c>
       <c r="U309" t="inlineStr"/>
       <c r="V309" t="inlineStr">
         <is>
-          <t>2026-10-14T01:26:21+05:30</t>
-        </is>
-      </c>
-      <c r="W309" t="inlineStr">
-        <is>
-          <t>Yafa Signed Jewels</t>
-        </is>
-      </c>
+          <t>2026-10-14T01:17:44+05:30</t>
+        </is>
+      </c>
+      <c r="W309" t="inlineStr"/>
       <c r="X309" t="inlineStr"/>
       <c r="Y309" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z309" t="inlineStr"/>
       <c r="AA309" t="inlineStr">
         <is>
-          <t>(212) 719-9828, (516) 331-8611</t>
+          <t>(203) 629-3303</t>
         </is>
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>https://facebook.com/YafaSignedJewels, https://instagram.com/yafasignedjewels</t>
+          <t>https://instagram.com/stevenfoxjewelry, https://facebook.com/stevenfoxjewelry</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Gold Gods</t>
+          <t>Triple G Fine Jewelry Inc</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>shop=jewelry</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>(816) 721-9850</t>
+          <t>(914) 937-2931</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>support@thegoldgods.com</t>
+          <t>rakhmin20@icloud.com</t>
         </is>
       </c>
       <c r="F310" t="inlineStr"/>
@@ -34954,44 +35062,48 @@
       <c r="H310" t="inlineStr"/>
       <c r="I310" s="2" t="inlineStr">
         <is>
-          <t>https://thegoldgods.com</t>
+          <t>https://triplegjewelry.rafaelsjewelrystore.com</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>450 N Fairfax Ave, Los Angeles, CA 90036</t>
+          <t>38 South Main Street, Port Chester, NY 10573</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Port Chester</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Beverly Hills, CA</t>
+          <t>Greenwich, CT</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O310" t="inlineStr"/>
-      <c r="P310" t="inlineStr"/>
+          <t>OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="O310" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P310" t="n">
+        <v>26</v>
+      </c>
       <c r="Q310" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/los-angeles-ca/mip/gold-gods-548160699</t>
+          <t>https://www.openstreetmap.org/node/10302134827</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S310" t="inlineStr">
@@ -35001,24 +35113,32 @@
       </c>
       <c r="T310" s="2" t="inlineStr">
         <is>
-          <t>https://thegoldgods.com/pages/contact</t>
+          <t>https://triplegjewelry.rafaelsjewelrystore.com/</t>
         </is>
       </c>
       <c r="U310" t="inlineStr"/>
       <c r="V310" t="inlineStr">
         <is>
-          <t>2026-10-14T01:52:07+05:30</t>
-        </is>
-      </c>
-      <c r="W310" t="inlineStr"/>
+          <t>2026-10-14T01:19:19+05:30</t>
+        </is>
+      </c>
+      <c r="W310" t="inlineStr">
+        <is>
+          <t>Triple J Fine Jewelry Inc, Triple J Jew Jewelry</t>
+        </is>
+      </c>
       <c r="X310" t="inlineStr"/>
       <c r="Y310" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z310" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="Z310" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA310" t="inlineStr">
         <is>
-          <t>(816) 323-6447</t>
+          <t>(917) 535-4155</t>
         </is>
       </c>
       <c r="AB310" t="inlineStr"/>
@@ -35026,7 +35146,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Golden State</t>
+          <t>Arlex Jewelry Watches &amp; Clocks</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -35036,17 +35156,17 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>(213) 629-2130</t>
+          <t>(561) 641-8162</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>sales@goldenstatejewelry.com</t>
+          <t>info@arlexjewelry.com</t>
         </is>
       </c>
       <c r="F311" t="inlineStr"/>
@@ -35054,48 +35174,48 @@
       <c r="H311" t="inlineStr"/>
       <c r="I311" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldenstatejewelry.com</t>
+          <t>https://arlexjewelry.com</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>550 S Hill St Ste 825, Los Angeles, CA 90013</t>
+          <t>808 Lake Ave, Lake Worth Beach, FL 33460, United States</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Lake Worth Beach</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Beverly Hills, CA</t>
+          <t>Palm Beach, FL</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O311" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="P311" t="n">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="Q311" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/los-angeles-ca/mip/golden-state-467565356</t>
+          <t>https://www.google.com/maps/place/Arlex+Jewelry+Watches+%26+Clocks/data=!4m7!3m6!1s0x88d8d834517d5a4d:0x1255d4758f02268f!8m2!3d26.6160147!4d-80.0567684!16s%2Fg%2F1tkc2xb0!19sChIJTVp9UTTY2IgRjyYCj3XUVRI</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, bench, custom-design, since-1978</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-1987</t>
         </is>
       </c>
       <c r="S311" t="inlineStr">
@@ -35105,64 +35225,64 @@
       </c>
       <c r="T311" s="2" t="inlineStr">
         <is>
-          <t>https://goldenstatejewelry.com/</t>
+          <t>https://arlexjewelry.com/contact/</t>
         </is>
       </c>
       <c r="U311" t="inlineStr"/>
       <c r="V311" t="inlineStr">
         <is>
-          <t>2026-10-14T01:52:45+05:30</t>
+          <t>2026-10-14T01:30:48+05:30</t>
         </is>
       </c>
       <c r="W311" t="inlineStr">
         <is>
-          <t>Golden Star Jewelry</t>
-        </is>
-      </c>
-      <c r="X311" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
+          <t>Arlex Jewelry Watches, Arlex Clocks, Arlex Jewelry &amp; Clocks</t>
+        </is>
+      </c>
+      <c r="X311" t="inlineStr"/>
       <c r="Y311" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z311" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="Z311" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA311" t="inlineStr">
         <is>
-          <t>(213) 627-9677</t>
+          <t>(561) 876-7030</t>
         </is>
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>https://instagram.com/goldenstatejewelryla</t>
+          <t>https://facebook.com/Arlex-Jewelry-Watches-Clocks-811607869050062, https://twitter.com/arlexclocks, https://instagram.com/arlexjewelry11, https://facebook.com/ArlexJewelry, https://twitter.com/ArlexClocks</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Hoorsenbuhs</t>
+          <t>Gemstone Gallery</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Jewelry Designers</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>(888) 692-2997</t>
+          <t>(561) 586-8868</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>info@hoorsenbuhs.com</t>
+          <t>info@mygemstonegallery.com</t>
         </is>
       </c>
       <c r="F312" t="inlineStr"/>
@@ -35170,27 +35290,15 @@
       <c r="H312" t="inlineStr"/>
       <c r="I312" s="2" t="inlineStr">
         <is>
-          <t>https://hoorsenbuhs.com</t>
-        </is>
-      </c>
-      <c r="J312" t="inlineStr">
-        <is>
-          <t>2217 Main St, Santa Monica, CA 90405</t>
-        </is>
-      </c>
-      <c r="K312" t="inlineStr">
-        <is>
-          <t>Santa Monica</t>
-        </is>
-      </c>
-      <c r="L312" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
+          <t>https://www.mygemstonegallery.com</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr"/>
+      <c r="K312" t="inlineStr"/>
+      <c r="L312" t="inlineStr"/>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Beverly Hills, CA</t>
+          <t>Palm Beach, FL</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -35202,12 +35310,12 @@
       <c r="P312" t="inlineStr"/>
       <c r="Q312" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/santa-monica-ca/mip/hoorsenbuhs-551622669</t>
+          <t>https://www.yellowpages.com/nationwide/mip/gemstone-gallery-451204537</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S312" t="inlineStr">
@@ -35217,13 +35325,13 @@
       </c>
       <c r="T312" s="2" t="inlineStr">
         <is>
-          <t>https://hoorsenbuhs.com/</t>
+          <t>https://www.mygemstonegallery.com/</t>
         </is>
       </c>
       <c r="U312" t="inlineStr"/>
       <c r="V312" t="inlineStr">
         <is>
-          <t>2026-10-14T01:53:36+05:30</t>
+          <t>2026-10-14T01:50:22+05:30</t>
         </is>
       </c>
       <c r="W312" t="inlineStr"/>
@@ -35233,24 +35341,24 @@
       </c>
       <c r="Z312" t="inlineStr">
         <is>
-          <t>toll-free</t>
+          <t>no-address</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
         <is>
-          <t>(917) 206-9333</t>
+          <t>(917) 406-0779</t>
         </is>
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>https://instagram.com/hoorsenbuhs</t>
+          <t>https://facebook.com/SuzanneHDeBow, https://twitter.com/GemstoneGallery, https://instagram.com/mygemstone_gallery</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Jennifer Fisher Jewelry</t>
+          <t>Hamilton Jewelers</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -35260,17 +35368,17 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jeweler</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>(424) 374-5303</t>
+          <t>(561) 659-6788</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>la@jenniferfisher.com</t>
+          <t>emartano@hamiltonjewelers.com</t>
         </is>
       </c>
       <c r="F313" t="inlineStr"/>
@@ -35278,19 +35386,27 @@
       <c r="H313" t="inlineStr"/>
       <c r="I313" s="2" t="inlineStr">
         <is>
-          <t>https://jenniferfisher.com</t>
+          <t>https://hamiltonjewelers.com</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>363 N Beverly Dr, Beverly Hills, CA 90210, United States</t>
-        </is>
-      </c>
-      <c r="K313" t="inlineStr"/>
-      <c r="L313" t="inlineStr"/>
+          <t>215 Worth Ave, Palm Beach, FL 33480, United States</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Palm Beach Gardens</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Beverly Hills, CA</t>
+          <t>Palm Beach, FL</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -35299,19 +35415,19 @@
         </is>
       </c>
       <c r="O313" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="P313" t="n">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="Q313" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Jennifer+Fisher+Jewelry/data=!4m7!3m6!1s0x80c2bdd6ed684985:0xb8fbea746e91ad05!8m2!3d34.0695438!4d-118.4019104!16s%2Fg%2F11n12hvwn5!19sChIJhUlo7da9woARBa2RbnTq-7g</t>
+          <t>https://www.google.com/maps/place/Hamilton+Jewelers/data=!4m7!3m6!1s0x88d8d6ec71416949:0x1f20ced2ff0489d1!8m2!3d26.7009363!4d-80.0371549!16s%2Fg%2F1tfz0xfv!19sChIJSWlBcezW2IgR0YkE_9LOIB8</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, direct-line, gia, custom-design, since-1912</t>
         </is>
       </c>
       <c r="S313" t="inlineStr">
@@ -35321,56 +35437,56 @@
       </c>
       <c r="T313" s="2" t="inlineStr">
         <is>
-          <t>https://jenniferfisher.com/pages/stockists</t>
+          <t>https://hamiltonjewelers.com/</t>
         </is>
       </c>
       <c r="U313" t="inlineStr"/>
       <c r="V313" t="inlineStr">
         <is>
-          <t>2026-10-14T01:40:50+05:30</t>
+          <t>2026-10-14T01:25:01+05:30</t>
         </is>
       </c>
       <c r="W313" t="inlineStr"/>
       <c r="X313" t="inlineStr"/>
       <c r="Y313" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z313" t="inlineStr"/>
       <c r="AA313" t="inlineStr">
         <is>
-          <t>(646) 366-9375</t>
+          <t>(609) 375-8003</t>
         </is>
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>https://instagram.com/jenniferfisherjewelry/, https://facebook.com/JenniferFisherJewelry, https://instagram.com/jenniferfisherjewelry</t>
+          <t>https://instagram.com/hamiltonjewelers, https://facebook.com/HamiltonJeweler</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Jewelry &amp; Watch Buyers - Beverly Hills</t>
+          <t>Raymond Lee Jewelers</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Jewelry buyer</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>(310) 697-8177</t>
+          <t>(561) 622-7744</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>info@watchbuyers.us</t>
+          <t>info@raymondleejewelers.net</t>
         </is>
       </c>
       <c r="F314" t="inlineStr"/>
@@ -35378,40 +35494,44 @@
       <c r="H314" t="inlineStr"/>
       <c r="I314" s="2" t="inlineStr">
         <is>
-          <t>https://watchbuyers.us</t>
+          <t>https://www.raymondleejewelers.net</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>468 N Camden Dr #205, Beverly Hills, CA 90210, United States</t>
-        </is>
-      </c>
-      <c r="K314" t="inlineStr"/>
-      <c r="L314" t="inlineStr"/>
+          <t>500 Village Square Xing, Palm Beach Gardens, FL 33410</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Palm Beach Gardens</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Beverly Hills, CA</t>
+          <t>Palm Beach, FL</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O314" t="n">
-        <v>5</v>
-      </c>
-      <c r="P314" t="n">
-        <v>3</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr"/>
+      <c r="P314" t="inlineStr"/>
       <c r="Q314" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Jewelry+%26+Watch+Buyers+-+Beverly+Hills/data=!4m7!3m6!1s0x80c2bdbde9baacdb:0xbbce1c74141b63ce!8m2!3d34.0698858!4d-118.404944!16s%2Fg%2F11xt1px272!19sChIJ26y66b29woARzmMbFHQczrs</t>
+          <t>https://www.yellowpages.com/palm-beach-gardens-fl/mip/raymond-lee-jewelers-3693798</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line</t>
+          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1983</t>
         </is>
       </c>
       <c r="S314" t="inlineStr">
@@ -35421,24 +35541,28 @@
       </c>
       <c r="T314" s="2" t="inlineStr">
         <is>
-          <t>https://watchbuyers.us/</t>
+          <t>https://raymondleejewelers.net/pages/contact</t>
         </is>
       </c>
       <c r="U314" t="inlineStr"/>
       <c r="V314" t="inlineStr">
         <is>
-          <t>2026-10-14T01:40:58+05:30</t>
+          <t>2026-10-14T01:50:37+05:30</t>
         </is>
       </c>
       <c r="W314" t="inlineStr"/>
       <c r="X314" t="inlineStr"/>
       <c r="Y314" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z314" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="Z314" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA314" t="inlineStr">
         <is>
-          <t>(305) 989-9099, (646) 413-7757</t>
+          <t>(561) 750-7808</t>
         </is>
       </c>
       <c r="AB314" t="inlineStr"/>
@@ -35446,23 +35570,27 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Jewels Aficionado Beverly Hills</t>
+          <t>Signature Diamonds</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr"/>
+          <t>Jewelers, Diamonds</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>(561) 686-5730</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>sales@jewelsaficionado.com</t>
+          <t>signaturebuyers@yahoo.com</t>
         </is>
       </c>
       <c r="F315" t="inlineStr"/>
@@ -35470,36 +35598,44 @@
       <c r="H315" t="inlineStr"/>
       <c r="I315" s="2" t="inlineStr">
         <is>
-          <t>https://jewelsaficionado.com</t>
+          <t>https://sellyourdiamondsflorida.com</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>9850 Wilshire Blvd, Beverly Hills, CA 90210, United States</t>
-        </is>
-      </c>
-      <c r="K315" t="inlineStr"/>
-      <c r="L315" t="inlineStr"/>
+          <t>2200 N Florida Mango Rd, West Palm Beach, FL 33409</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>West Palm Beach</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Beverly Hills, CA</t>
+          <t>Palm Beach, FL</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O315" t="inlineStr"/>
       <c r="P315" t="inlineStr"/>
       <c r="Q315" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Jewels+Aficionado+Beverly+Hills/data=!4m7!3m6!1s0x80c2bb445801322d:0x4ee3ff18cd9446bc!8m2!3d34.0666649!4d-118.4114543!16s%2Fg%2F11z2xf_27b!19sChIJLTIBWES7woARvEaUzRj_404</t>
+          <t>https://www.yellowpages.com/west-palm-beach-fl/mip/signature-diamonds-538406637</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, direct-line, gia, custom-design, since-1945</t>
         </is>
       </c>
       <c r="S315" t="inlineStr">
@@ -35509,13 +35645,13 @@
       </c>
       <c r="T315" s="2" t="inlineStr">
         <is>
-          <t>https://jewelsaficionado.com/</t>
+          <t>https://sellyourdiamondsflorida.com/</t>
         </is>
       </c>
       <c r="U315" t="inlineStr"/>
       <c r="V315" t="inlineStr">
         <is>
-          <t>2026-10-14T01:42:22+05:30</t>
+          <t>2026-10-14T01:50:22+05:30</t>
         </is>
       </c>
       <c r="W315" t="inlineStr"/>
@@ -35526,19 +35662,19 @@
       <c r="Z315" t="inlineStr"/>
       <c r="AA315" t="inlineStr">
         <is>
-          <t>(212) 422-2600</t>
+          <t>(772) 562-6893</t>
         </is>
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>https://instagram.com/jewelsaficionado</t>
+          <t>https://facebook.com/pages/Signature-Estate-Diamond-Buyers/699915383378286, https://twitter.com/signaturebuyer</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Logan Hollowell Jewelry</t>
+          <t>WPBWatchCo</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -35548,37 +35684,57 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Watch store</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>(323) 248-9685</t>
+          <t>(561) 220-9107</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>info@loganhollowell.com</t>
-        </is>
-      </c>
-      <c r="F316" t="inlineStr"/>
-      <c r="G316" t="inlineStr"/>
-      <c r="H316" t="inlineStr"/>
+          <t>arinaldi@wpbwatchco.com</t>
+        </is>
+      </c>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anthony-rinaldi-0293451b</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>Anthony Rinaldi</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="I316" s="2" t="inlineStr">
         <is>
-          <t>https://www.loganhollowell.com</t>
+          <t>https://www.wpbwatchco.com</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>411 N Canon Dr, Beverly Hills, CA 90210, United States</t>
-        </is>
-      </c>
-      <c r="K316" t="inlineStr"/>
-      <c r="L316" t="inlineStr"/>
+          <t>1601 Forum Pl #1010, West Palm Beach, FL 33401, United States</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>West Palm Beach</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Beverly Hills, CA</t>
+          <t>Palm Beach, FL</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -35587,78 +35743,78 @@
         </is>
       </c>
       <c r="O316" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P316" t="n">
-        <v>1</v>
+        <v>622</v>
       </c>
       <c r="Q316" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Logan+Hollowell+Jewelry/data=!4m7!3m6!1s0x80c2bd39cbc0865f:0x202c691c8504a898!8m2!3d34.07073!4d-118.4012945!16s%2Fg%2F11njp9zjzq!19sChIJX4bAyzm9woARmKgEhRxpLCA</t>
+          <t>https://www.google.com/maps/place/WPBWatchCo/data=!4m7!3m6!1s0x88d91e304542d111:0xdd417b5f344332dc!8m2!3d26.7271055!4d-80.0794774!16s%2Fg%2F11dymb1krc!19sChIJEdFCRTAe2YgR3DJDNF97Qd0</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-2014</t>
+          <t>2 of 3, since-2015</t>
         </is>
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T316" s="2" t="inlineStr">
         <is>
-          <t>https://loganhollowell.com/</t>
-        </is>
-      </c>
-      <c r="U316" t="inlineStr"/>
+          <t>https://wpbwatchco.com/</t>
+        </is>
+      </c>
+      <c r="U316" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Anthony+Rinaldi%22+Palm+Beach+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V316" t="inlineStr">
         <is>
-          <t>2026-10-14T01:41:31+05:30</t>
+          <t>2026-10-14T01:27:35+05:30</t>
         </is>
       </c>
       <c r="W316" t="inlineStr"/>
       <c r="X316" t="inlineStr"/>
       <c r="Y316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z316" t="inlineStr"/>
-      <c r="AA316" t="inlineStr">
-        <is>
-          <t>(323) 853-7844</t>
-        </is>
-      </c>
+      <c r="AA316" t="inlineStr"/>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>https://instagram.com/loganhollowell, https://facebook.com/loganhollowelljewelry</t>
+          <t>https://instagram.com/wpb_watch_co, https://facebook.com/anthony.rinaldi.7370</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Majestic Jewelry</t>
+          <t>YAFA Palm Beach</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>(323) 933-0288</t>
+          <t>(561) 331-8611</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>info@majesticjewelers.com</t>
+          <t>inquire@yafajewelry.com</t>
         </is>
       </c>
       <c r="F317" t="inlineStr"/>
@@ -35666,48 +35822,48 @@
       <c r="H317" t="inlineStr"/>
       <c r="I317" s="2" t="inlineStr">
         <is>
-          <t>https://majesticjewelers.com</t>
+          <t>https://yafasignedjewels.com</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>6333 W 3rd St, Los Angeles, CA 90036</t>
+          <t>234 Worth Ave, Palm Beach, FL 33480, United States</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Palm Beach</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Beverly Hills, CA</t>
+          <t>Palm Beach, FL</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O317" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P317" t="n">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="Q317" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/los-angeles-ca/mip/majestic-jewelry-458143900</t>
+          <t>https://www.google.com/maps/place/YAFA+Palm+Beach/data=!4m7!3m6!1s0x89c258fef868bda1:0x84b1b16f5ab524a9!8m2!3d26.7006755!4d-80.0378935!16s%2Fg%2F1td4l0sf!19sChIJob1o-P5YwokRqSS1Wm-xsYQ</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-1986</t>
+          <t>2 of 3, direct-line, since-1985</t>
         </is>
       </c>
       <c r="S317" t="inlineStr">
@@ -35717,49 +35873,45 @@
       </c>
       <c r="T317" s="2" t="inlineStr">
         <is>
-          <t>https://www.majesticjewelers.com/about-us/</t>
+          <t>https://yafasignedjewels.com/pages/contact</t>
         </is>
       </c>
       <c r="U317" t="inlineStr"/>
       <c r="V317" t="inlineStr">
         <is>
-          <t>2026-10-14T01:52:20+05:30</t>
+          <t>2026-10-14T01:26:21+05:30</t>
         </is>
       </c>
       <c r="W317" t="inlineStr">
         <is>
-          <t>Majestic W.J.</t>
-        </is>
-      </c>
-      <c r="X317" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
+          <t>Yafa Signed Jewels</t>
+        </is>
+      </c>
+      <c r="X317" t="inlineStr"/>
       <c r="Y317" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z317" t="inlineStr"/>
       <c r="AA317" t="inlineStr">
         <is>
-          <t>(407) 644-4824</t>
+          <t>(212) 719-9828, (516) 331-8611</t>
         </is>
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>https://facebook.com/MajesticJewelersInc, https://instagram.com/majesticjewelerswp</t>
+          <t>https://facebook.com/YafaSignedJewels, https://instagram.com/yafasignedjewels</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Raven Fine Jewelers</t>
+          <t>Gold Gods</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -35769,12 +35921,12 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>(310) 432-5234</t>
+          <t>(816) 721-9850</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>info@ravenjewelers.com</t>
+          <t>support@thegoldgods.com</t>
         </is>
       </c>
       <c r="F318" t="inlineStr"/>
@@ -35782,17 +35934,17 @@
       <c r="H318" t="inlineStr"/>
       <c r="I318" s="2" t="inlineStr">
         <is>
-          <t>https://ravenfinejewelers.localsearch.com</t>
+          <t>https://thegoldgods.com</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>8350 Wilshire Blvd, Beverly Hills, CA 90211</t>
+          <t>450 N Fairfax Ave, Los Angeles, CA 90036</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>Beverly Hills</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
@@ -35810,15 +35962,11 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O318" t="n">
-        <v>5</v>
-      </c>
-      <c r="P318" t="n">
-        <v>1</v>
-      </c>
+      <c r="O318" t="inlineStr"/>
+      <c r="P318" t="inlineStr"/>
       <c r="Q318" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/beverly-hills-ca/mip/raven-fine-jewelers-531865762</t>
+          <t>https://www.yellowpages.com/los-angeles-ca/mip/gold-gods-548160699</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
@@ -35833,56 +35981,52 @@
       </c>
       <c r="T318" s="2" t="inlineStr">
         <is>
-          <t>https://ravendiamonds.com/</t>
+          <t>https://thegoldgods.com/pages/contact</t>
         </is>
       </c>
       <c r="U318" t="inlineStr"/>
       <c r="V318" t="inlineStr">
         <is>
-          <t>2026-10-14T01:51:20+05:30</t>
+          <t>2026-10-14T01:52:07+05:30</t>
         </is>
       </c>
       <c r="W318" t="inlineStr"/>
       <c r="X318" t="inlineStr"/>
       <c r="Y318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z318" t="inlineStr"/>
       <c r="AA318" t="inlineStr">
         <is>
-          <t>(310) 887-1499</t>
-        </is>
-      </c>
-      <c r="AB318" t="inlineStr">
-        <is>
-          <t>https://instagram.com/ravenfinejewelers, https://facebook.com/RavenFineJewelers</t>
-        </is>
-      </c>
+          <t>(816) 323-6447</t>
+        </is>
+      </c>
+      <c r="AB318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Sunset Plaza</t>
+          <t>Golden State</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Jewelers, Watches, Real Estate Agents</t>
+          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>(310) 652-7137</t>
+          <t>(213) 629-2130</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>info@sunsetplaza.com</t>
+          <t>sales@goldenstatejewelry.com</t>
         </is>
       </c>
       <c r="F319" t="inlineStr"/>
@@ -35890,17 +36034,17 @@
       <c r="H319" t="inlineStr"/>
       <c r="I319" s="2" t="inlineStr">
         <is>
-          <t>https://www.sunsetplaza.com</t>
+          <t>https://www.goldenstatejewelry.com</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>8623 W Sunset Blvd, West Hollywood, CA 90069</t>
+          <t>550 S Hill St Ste 825, Los Angeles, CA 90013</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>West Hollywood</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
@@ -35918,16 +36062,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O319" t="inlineStr"/>
-      <c r="P319" t="inlineStr"/>
+      <c r="O319" t="n">
+        <v>5</v>
+      </c>
+      <c r="P319" t="n">
+        <v>1</v>
+      </c>
       <c r="Q319" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/west-hollywood-ca/mip/sunset-plaza-1562237</t>
+          <t>https://www.yellowpages.com/los-angeles-ca/mip/golden-state-467565356</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, since-1924</t>
+          <t>2 of 3, role-email, direct-line, bench, custom-design, since-1978</t>
         </is>
       </c>
       <c r="S319" t="inlineStr">
@@ -35937,81 +36085,89 @@
       </c>
       <c r="T319" s="2" t="inlineStr">
         <is>
-          <t>https://www.sunsetplaza.com/</t>
+          <t>https://goldenstatejewelry.com/</t>
         </is>
       </c>
       <c r="U319" t="inlineStr"/>
       <c r="V319" t="inlineStr">
         <is>
-          <t>2026-10-14T01:52:13+05:30</t>
-        </is>
-      </c>
-      <c r="W319" t="inlineStr"/>
-      <c r="X319" t="inlineStr"/>
+          <t>2026-10-14T01:52:45+05:30</t>
+        </is>
+      </c>
+      <c r="W319" t="inlineStr">
+        <is>
+          <t>Golden Star Jewelry</t>
+        </is>
+      </c>
+      <c r="X319" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
       <c r="Y319" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z319" t="inlineStr"/>
       <c r="AA319" t="inlineStr">
         <is>
-          <t>(213) 500-3098, (213) 709-2282, (310) 210-0975, (310) 248-3750, (310) 274-1602, (310) 275-2222, (310) 289-1104, (310) 289-1105, (310) 360-6900, (310) 360-8889, (310) 424-3690, (310) 616-7888, (310) 652-2680, (310) 652-6844, (310) 652-7039, (310) 652-8886, (310) 657-2553, (310) 657-5070, (310) 657-5469, (310) 659-4411, (310) 659-9089, (310) 734-7296, (310) 786-7417, (310) 849-7185, (310) 854-0299, (310) 854-7700, (310) 855-8044, (323) 253-6747, (323) 345-4525, (323) 507-3943, (323) 650-0475, (323) 937-0355, (424) 407-4606, (424) 542-7730, (424) 667-0036, (424) 722-8502, (747) 724-3595</t>
+          <t>(213) 627-9677</t>
         </is>
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>https://instagram.com/affluette_, https://instagram.com/alchemy43, https://facebook.com/alchemy43, https://instagram.com/andreas.fashions, https://facebook.com/andreasfashions, https://instagram.com/bbcmcafe, https://instagram.com/bootstarusa, https://facebook.com/Boot-Star-106137407505929, https://instagram.com/bossanovarestaurant, https://facebook.com/BossaNovaLA, https://instagram.com/charliechoukair/, https://instagram.com/cristallini_official, https://facebook.com/CRISTALLINIOfficial, https://instagram.com/architectureforsale/, https://instagram.com/cupidlipsofbeverlyhills, https://facebook.com/profile.php?id=100083257576786, https://instagram.com/dandeutschoo, https://instagram.com/davidorgell, https://instagram.com/drybarshopsus, https://facebook.com/thedrybar, https://instagram.com/elainekimcollection/, https://instagram.com/entouragebarbershop, https://instagram.com/fpjourneofficial, https://instagram.com/guyfloralstudio, https://instagram.com/hotpilates, https://facebook.com/Hot-Pilates-1806940676211478, https://instagram.com/kojitoyodasalon, https://instagram.com/metaclinic/, https://instagram.com/milamoursiskincare, https://instagram.com/olehenriksenspa/, https://instagram.com/oliverpeoples, https://instagram.com/osklo.la, https://instagram.com/philippressjeweler, https://instagram.com/puravidamiami, https://facebook.com/PuraVidaMiami, https://instagram.com/queenbnailsalon_sunsetplaza, https://instagram.com/andywarholrevolvergallery, https://instagram.com/rondorff, https://instagram.com/saltiegirlla, https://instagram.com/samira13jewelry, https://instagram.com/sargondental, https://facebook.com/sargonlazarofdds, https://instagram.com/serenityonsunset, https://instagram.com/sheilaonsunset, https://instagram.com/solatesbysamantha, https://instagram.com/sousla_official, https://instagram.com/sunsetkidsla, https://instagram.com/theoppenheimgroup, https://facebook.com/theoppenheimgroup, https://instagram.com/whitegloveestates, https://instagram.com/xrcyze_ny, https://facebook.com/xrcycle, https://instagram.com/sunsetplazaca, https://facebook.com/SunsetPlazaCA</t>
+          <t>https://instagram.com/goldenstatejewelryla</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Westime Beverly Hills</t>
+          <t>Hoorsenbuhs</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Watch store</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>(310) 888-8880</t>
+          <t>(888) 692-2997</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>contact@westime.com</t>
+          <t>info@hoorsenbuhs.com</t>
         </is>
       </c>
       <c r="F320" t="inlineStr"/>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>Greg Simonian</t>
-        </is>
-      </c>
-      <c r="H320" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
+      <c r="G320" t="inlineStr"/>
+      <c r="H320" t="inlineStr"/>
       <c r="I320" s="2" t="inlineStr">
         <is>
-          <t>https://westime.com</t>
+          <t>https://hoorsenbuhs.com</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>206 N Rodeo Dr, Beverly Hills, CA 90210, United States</t>
-        </is>
-      </c>
-      <c r="K320" t="inlineStr"/>
-      <c r="L320" t="inlineStr"/>
+          <t>2217 Main St, Santa Monica, CA 90405</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Santa Monica</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
       <c r="M320" t="inlineStr">
         <is>
           <t>Beverly Hills, CA</t>
@@ -36019,23 +36175,19 @@
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O320" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P320" t="n">
-        <v>274</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr"/>
+      <c r="P320" t="inlineStr"/>
       <c r="Q320" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Westime+Beverly+Hills/data=!4m7!3m6!1s0x80c2bc0ed6429065:0x2c357ea8ffa51b1f!8m2!3d34.067375!4d-118.4003799!16s%2Fg%2F11cfj2mg2!19sChIJZZBC1g68woARHxul_6h-NSw</t>
+          <t>https://www.yellowpages.com/santa-monica-ca/mip/hoorsenbuhs-551622669</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-1987</t>
+          <t>2 of 3, role-email, direct-line</t>
         </is>
       </c>
       <c r="S320" t="inlineStr">
@@ -36045,13 +36197,13 @@
       </c>
       <c r="T320" s="2" t="inlineStr">
         <is>
-          <t>https://westime.com/contact</t>
+          <t>https://hoorsenbuhs.com/</t>
         </is>
       </c>
       <c r="U320" t="inlineStr"/>
       <c r="V320" t="inlineStr">
         <is>
-          <t>2026-10-14T01:39:33+05:30</t>
+          <t>2026-10-14T01:53:36+05:30</t>
         </is>
       </c>
       <c r="W320" t="inlineStr"/>
@@ -36059,22 +36211,26 @@
       <c r="Y320" t="n">
         <v>0</v>
       </c>
-      <c r="Z320" t="inlineStr"/>
+      <c r="Z320" t="inlineStr">
+        <is>
+          <t>toll-free</t>
+        </is>
+      </c>
       <c r="AA320" t="inlineStr">
         <is>
-          <t>(786) 347-5353, (858) 459-2222</t>
+          <t>(917) 206-9333</t>
         </is>
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>https://instagram.com/westimewatches, https://facebook.com/Westime</t>
+          <t>https://instagram.com/hoorsenbuhs</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Wrist Aficionado Beverly Hills</t>
+          <t>Jennifer Fisher Jewelry</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -36084,17 +36240,17 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Watch store</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>(310) 388-8201</t>
+          <t>(424) 374-5303</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>sales@wristaficionado.com</t>
+          <t>la@jenniferfisher.com</t>
         </is>
       </c>
       <c r="F321" t="inlineStr"/>
@@ -36102,24 +36258,16 @@
       <c r="H321" t="inlineStr"/>
       <c r="I321" s="2" t="inlineStr">
         <is>
-          <t>https://wristaficionado.com</t>
+          <t>https://jenniferfisher.com</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>9850 Wilshire Blvd, Beverly Hills, CA 90210, United States</t>
-        </is>
-      </c>
-      <c r="K321" t="inlineStr">
-        <is>
-          <t>Beverly Hills</t>
-        </is>
-      </c>
-      <c r="L321" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
+          <t>363 N Beverly Dr, Beverly Hills, CA 90210, United States</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr"/>
+      <c r="L321" t="inlineStr"/>
       <c r="M321" t="inlineStr">
         <is>
           <t>Beverly Hills, CA</t>
@@ -36131,19 +36279,19 @@
         </is>
       </c>
       <c r="O321" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="P321" t="n">
-        <v>101</v>
+        <v>44</v>
       </c>
       <c r="Q321" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Wrist+Aficionado+Beverly+Hills/data=!4m7!3m6!1s0x80c2bb67e5181fcf:0xde9cbdbb118a155c!8m2!3d34.0667288!4d-118.4113018!16s%2Fg%2F11v12tg_x0!19sChIJzx8Y5We7woARXBWKEbu9nN4</t>
+          <t>https://www.google.com/maps/place/Jennifer+Fisher+Jewelry/data=!4m7!3m6!1s0x80c2bdd6ed684985:0xb8fbea746e91ad05!8m2!3d34.0695438!4d-118.4019104!16s%2Fg%2F11n12hvwn5!19sChIJhUlo7da9woARBa2RbnTq-7g</t>
         </is>
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-2017</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S321" t="inlineStr">
@@ -36153,13 +36301,13 @@
       </c>
       <c r="T321" s="2" t="inlineStr">
         <is>
-          <t>https://wristaficionado.com/</t>
+          <t>https://jenniferfisher.com/pages/stockists</t>
         </is>
       </c>
       <c r="U321" t="inlineStr"/>
       <c r="V321" t="inlineStr">
         <is>
-          <t>2026-10-14T01:43:17+05:30</t>
+          <t>2026-10-14T01:40:50+05:30</t>
         </is>
       </c>
       <c r="W321" t="inlineStr"/>
@@ -36170,17 +36318,849 @@
       <c r="Z321" t="inlineStr"/>
       <c r="AA321" t="inlineStr">
         <is>
+          <t>(646) 366-9375</t>
+        </is>
+      </c>
+      <c r="AB321" t="inlineStr">
+        <is>
+          <t>https://instagram.com/jenniferfisherjewelry/, https://facebook.com/JenniferFisherJewelry, https://instagram.com/jenniferfisherjewelry</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Jewelry &amp; Watch Buyers - Beverly Hills</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Jewelry buyer</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>(310) 697-8177</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>info@watchbuyers.us</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr"/>
+      <c r="G322" t="inlineStr"/>
+      <c r="H322" t="inlineStr"/>
+      <c r="I322" s="2" t="inlineStr">
+        <is>
+          <t>https://watchbuyers.us</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>468 N Camden Dr #205, Beverly Hills, CA 90210, United States</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr"/>
+      <c r="L322" t="inlineStr"/>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>Beverly Hills, CA</t>
+        </is>
+      </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O322" t="n">
+        <v>5</v>
+      </c>
+      <c r="P322" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q322" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Jewelry+%26+Watch+Buyers+-+Beverly+Hills/data=!4m7!3m6!1s0x80c2bdbde9baacdb:0xbbce1c74141b63ce!8m2!3d34.0698858!4d-118.404944!16s%2Fg%2F11xt1px272!19sChIJ26y66b29woARzmMbFHQczrs</t>
+        </is>
+      </c>
+      <c r="R322" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line</t>
+        </is>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T322" s="2" t="inlineStr">
+        <is>
+          <t>https://watchbuyers.us/</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr"/>
+      <c r="V322" t="inlineStr">
+        <is>
+          <t>2026-10-14T01:40:58+05:30</t>
+        </is>
+      </c>
+      <c r="W322" t="inlineStr"/>
+      <c r="X322" t="inlineStr"/>
+      <c r="Y322" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z322" t="inlineStr"/>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>(305) 989-9099, (646) 413-7757</t>
+        </is>
+      </c>
+      <c r="AB322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Jewels Aficionado Beverly Hills</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Custom / bespoke jeweler</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Jewelry store</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr"/>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>sales@jewelsaficionado.com</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr"/>
+      <c r="G323" t="inlineStr"/>
+      <c r="H323" t="inlineStr"/>
+      <c r="I323" s="2" t="inlineStr">
+        <is>
+          <t>https://jewelsaficionado.com</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>9850 Wilshire Blvd, Beverly Hills, CA 90210, United States</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr"/>
+      <c r="L323" t="inlineStr"/>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>Beverly Hills, CA</t>
+        </is>
+      </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr"/>
+      <c r="P323" t="inlineStr"/>
+      <c r="Q323" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Jewels+Aficionado+Beverly+Hills/data=!4m7!3m6!1s0x80c2bb445801322d:0x4ee3ff18cd9446bc!8m2!3d34.0666649!4d-118.4114543!16s%2Fg%2F11z2xf_27b!19sChIJLTIBWES7woARvEaUzRj_404</t>
+        </is>
+      </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
+        </is>
+      </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T323" s="2" t="inlineStr">
+        <is>
+          <t>https://jewelsaficionado.com/</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr"/>
+      <c r="V323" t="inlineStr">
+        <is>
+          <t>2026-10-14T01:42:22+05:30</t>
+        </is>
+      </c>
+      <c r="W323" t="inlineStr"/>
+      <c r="X323" t="inlineStr"/>
+      <c r="Y323" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z323" t="inlineStr"/>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>(212) 422-2600</t>
+        </is>
+      </c>
+      <c r="AB323" t="inlineStr">
+        <is>
+          <t>https://instagram.com/jewelsaficionado</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Logan Hollowell Jewelry</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Jewelry store</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>(323) 248-9685</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>info@loganhollowell.com</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr"/>
+      <c r="G324" t="inlineStr"/>
+      <c r="H324" t="inlineStr"/>
+      <c r="I324" s="2" t="inlineStr">
+        <is>
+          <t>https://www.loganhollowell.com</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>411 N Canon Dr, Beverly Hills, CA 90210, United States</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr"/>
+      <c r="L324" t="inlineStr"/>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>Beverly Hills, CA</t>
+        </is>
+      </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O324" t="n">
+        <v>5</v>
+      </c>
+      <c r="P324" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q324" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Logan+Hollowell+Jewelry/data=!4m7!3m6!1s0x80c2bd39cbc0865f:0x202c691c8504a898!8m2!3d34.07073!4d-118.4012945!16s%2Fg%2F11njp9zjzq!19sChIJX4bAyzm9woARmKgEhRxpLCA</t>
+        </is>
+      </c>
+      <c r="R324" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, custom-design, since-2014</t>
+        </is>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T324" s="2" t="inlineStr">
+        <is>
+          <t>https://loganhollowell.com/</t>
+        </is>
+      </c>
+      <c r="U324" t="inlineStr"/>
+      <c r="V324" t="inlineStr">
+        <is>
+          <t>2026-10-14T01:41:31+05:30</t>
+        </is>
+      </c>
+      <c r="W324" t="inlineStr"/>
+      <c r="X324" t="inlineStr"/>
+      <c r="Y324" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z324" t="inlineStr"/>
+      <c r="AA324" t="inlineStr">
+        <is>
+          <t>(323) 853-7844</t>
+        </is>
+      </c>
+      <c r="AB324" t="inlineStr">
+        <is>
+          <t>https://instagram.com/loganhollowell, https://facebook.com/loganhollowelljewelry</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Majestic Jewelry</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Custom / bespoke jeweler</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Jewelers</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>(323) 933-0288</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>info@majesticjewelers.com</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr"/>
+      <c r="G325" t="inlineStr"/>
+      <c r="H325" t="inlineStr"/>
+      <c r="I325" s="2" t="inlineStr">
+        <is>
+          <t>https://majesticjewelers.com</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>6333 W 3rd St, Los Angeles, CA 90036</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>Beverly Hills, CA</t>
+        </is>
+      </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O325" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P325" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q325" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/los-angeles-ca/mip/majestic-jewelry-458143900</t>
+        </is>
+      </c>
+      <c r="R325" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, custom-design, since-1986</t>
+        </is>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T325" s="2" t="inlineStr">
+        <is>
+          <t>https://www.majesticjewelers.com/about-us/</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr"/>
+      <c r="V325" t="inlineStr">
+        <is>
+          <t>2026-10-14T01:52:20+05:30</t>
+        </is>
+      </c>
+      <c r="W325" t="inlineStr">
+        <is>
+          <t>Majestic W.J.</t>
+        </is>
+      </c>
+      <c r="X325" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="Y325" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z325" t="inlineStr"/>
+      <c r="AA325" t="inlineStr">
+        <is>
+          <t>(407) 644-4824</t>
+        </is>
+      </c>
+      <c r="AB325" t="inlineStr">
+        <is>
+          <t>https://facebook.com/MajesticJewelersInc, https://instagram.com/majesticjewelerswp</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Raven Fine Jewelers</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Jewelers</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>(310) 432-5234</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>info@ravenjewelers.com</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr"/>
+      <c r="G326" t="inlineStr"/>
+      <c r="H326" t="inlineStr"/>
+      <c r="I326" s="2" t="inlineStr">
+        <is>
+          <t>https://ravenfinejewelers.localsearch.com</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>8350 Wilshire Blvd, Beverly Hills, CA 90211</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Beverly Hills</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>Beverly Hills, CA</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O326" t="n">
+        <v>5</v>
+      </c>
+      <c r="P326" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/beverly-hills-ca/mip/raven-fine-jewelers-531865762</t>
+        </is>
+      </c>
+      <c r="R326" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
+        </is>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T326" s="2" t="inlineStr">
+        <is>
+          <t>https://ravendiamonds.com/</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr"/>
+      <c r="V326" t="inlineStr">
+        <is>
+          <t>2026-10-14T01:51:20+05:30</t>
+        </is>
+      </c>
+      <c r="W326" t="inlineStr"/>
+      <c r="X326" t="inlineStr"/>
+      <c r="Y326" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z326" t="inlineStr"/>
+      <c r="AA326" t="inlineStr">
+        <is>
+          <t>(310) 887-1499</t>
+        </is>
+      </c>
+      <c r="AB326" t="inlineStr">
+        <is>
+          <t>https://instagram.com/ravenfinejewelers, https://facebook.com/RavenFineJewelers</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Sunset Plaza</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Estate &amp; antique jewelry</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Jewelers, Watches, Real Estate Agents</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>(310) 652-7137</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>info@sunsetplaza.com</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr"/>
+      <c r="G327" t="inlineStr"/>
+      <c r="H327" t="inlineStr"/>
+      <c r="I327" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sunsetplaza.com</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>8623 W Sunset Blvd, West Hollywood, CA 90069</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>West Hollywood</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>Beverly Hills, CA</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr"/>
+      <c r="P327" t="inlineStr"/>
+      <c r="Q327" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/west-hollywood-ca/mip/sunset-plaza-1562237</t>
+        </is>
+      </c>
+      <c r="R327" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, since-1924</t>
+        </is>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T327" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sunsetplaza.com/</t>
+        </is>
+      </c>
+      <c r="U327" t="inlineStr"/>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>2026-10-14T01:52:13+05:30</t>
+        </is>
+      </c>
+      <c r="W327" t="inlineStr"/>
+      <c r="X327" t="inlineStr"/>
+      <c r="Y327" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z327" t="inlineStr"/>
+      <c r="AA327" t="inlineStr">
+        <is>
+          <t>(213) 500-3098, (213) 709-2282, (310) 210-0975, (310) 248-3750, (310) 274-1602, (310) 275-2222, (310) 289-1104, (310) 289-1105, (310) 360-6900, (310) 360-8889, (310) 424-3690, (310) 616-7888, (310) 652-2680, (310) 652-6844, (310) 652-7039, (310) 652-8886, (310) 657-2553, (310) 657-5070, (310) 657-5469, (310) 659-4411, (310) 659-9089, (310) 734-7296, (310) 786-7417, (310) 849-7185, (310) 854-0299, (310) 854-7700, (310) 855-8044, (323) 253-6747, (323) 345-4525, (323) 507-3943, (323) 650-0475, (323) 937-0355, (424) 407-4606, (424) 542-7730, (424) 667-0036, (424) 722-8502, (747) 724-3595</t>
+        </is>
+      </c>
+      <c r="AB327" t="inlineStr">
+        <is>
+          <t>https://instagram.com/affluette_, https://instagram.com/alchemy43, https://facebook.com/alchemy43, https://instagram.com/andreas.fashions, https://facebook.com/andreasfashions, https://instagram.com/bbcmcafe, https://instagram.com/bootstarusa, https://facebook.com/Boot-Star-106137407505929, https://instagram.com/bossanovarestaurant, https://facebook.com/BossaNovaLA, https://instagram.com/charliechoukair/, https://instagram.com/cristallini_official, https://facebook.com/CRISTALLINIOfficial, https://instagram.com/architectureforsale/, https://instagram.com/cupidlipsofbeverlyhills, https://facebook.com/profile.php?id=100083257576786, https://instagram.com/dandeutschoo, https://instagram.com/davidorgell, https://instagram.com/drybarshopsus, https://facebook.com/thedrybar, https://instagram.com/elainekimcollection/, https://instagram.com/entouragebarbershop, https://instagram.com/fpjourneofficial, https://instagram.com/guyfloralstudio, https://instagram.com/hotpilates, https://facebook.com/Hot-Pilates-1806940676211478, https://instagram.com/kojitoyodasalon, https://instagram.com/metaclinic/, https://instagram.com/milamoursiskincare, https://instagram.com/olehenriksenspa/, https://instagram.com/oliverpeoples, https://instagram.com/osklo.la, https://instagram.com/philippressjeweler, https://instagram.com/puravidamiami, https://facebook.com/PuraVidaMiami, https://instagram.com/queenbnailsalon_sunsetplaza, https://instagram.com/andywarholrevolvergallery, https://instagram.com/rondorff, https://instagram.com/saltiegirlla, https://instagram.com/samira13jewelry, https://instagram.com/sargondental, https://facebook.com/sargonlazarofdds, https://instagram.com/serenityonsunset, https://instagram.com/sheilaonsunset, https://instagram.com/solatesbysamantha, https://instagram.com/sousla_official, https://instagram.com/sunsetkidsla, https://instagram.com/theoppenheimgroup, https://facebook.com/theoppenheimgroup, https://instagram.com/whitegloveestates, https://instagram.com/xrcyze_ny, https://facebook.com/xrcycle, https://instagram.com/sunsetplazaca, https://facebook.com/SunsetPlazaCA</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Westime Beverly Hills</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Custom / bespoke jeweler</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Watch store</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>(310) 888-8880</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>contact@westime.com</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr"/>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>Greg Simonian</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="I328" s="2" t="inlineStr">
+        <is>
+          <t>https://westime.com</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>206 N Rodeo Dr, Beverly Hills, CA 90210, United States</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr"/>
+      <c r="L328" t="inlineStr"/>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>Beverly Hills, CA</t>
+        </is>
+      </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O328" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P328" t="n">
+        <v>274</v>
+      </c>
+      <c r="Q328" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Westime+Beverly+Hills/data=!4m7!3m6!1s0x80c2bc0ed6429065:0x2c357ea8ffa51b1f!8m2!3d34.067375!4d-118.4003799!16s%2Fg%2F11cfj2mg2!19sChIJZZBC1g68woARHxul_6h-NSw</t>
+        </is>
+      </c>
+      <c r="R328" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, custom-design, since-1987</t>
+        </is>
+      </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T328" s="2" t="inlineStr">
+        <is>
+          <t>https://westime.com/contact</t>
+        </is>
+      </c>
+      <c r="U328" t="inlineStr"/>
+      <c r="V328" t="inlineStr">
+        <is>
+          <t>2026-10-14T01:39:33+05:30</t>
+        </is>
+      </c>
+      <c r="W328" t="inlineStr"/>
+      <c r="X328" t="inlineStr"/>
+      <c r="Y328" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z328" t="inlineStr"/>
+      <c r="AA328" t="inlineStr">
+        <is>
+          <t>(786) 347-5353, (858) 459-2222</t>
+        </is>
+      </c>
+      <c r="AB328" t="inlineStr">
+        <is>
+          <t>https://instagram.com/westimewatches, https://facebook.com/Westime</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Wrist Aficionado Beverly Hills</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Watch store</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>(310) 388-8201</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>sales@wristaficionado.com</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr"/>
+      <c r="G329" t="inlineStr"/>
+      <c r="H329" t="inlineStr"/>
+      <c r="I329" s="2" t="inlineStr">
+        <is>
+          <t>https://wristaficionado.com</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>9850 Wilshire Blvd, Beverly Hills, CA 90210, United States</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Beverly Hills</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>Beverly Hills, CA</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O329" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P329" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q329" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Wrist+Aficionado+Beverly+Hills/data=!4m7!3m6!1s0x80c2bb67e5181fcf:0xde9cbdbb118a155c!8m2!3d34.0667288!4d-118.4113018!16s%2Fg%2F11v12tg_x0!19sChIJzx8Y5We7woARXBWKEbu9nN4</t>
+        </is>
+      </c>
+      <c r="R329" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, custom-design, since-2017</t>
+        </is>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T329" s="2" t="inlineStr">
+        <is>
+          <t>https://wristaficionado.com/</t>
+        </is>
+      </c>
+      <c r="U329" t="inlineStr"/>
+      <c r="V329" t="inlineStr">
+        <is>
+          <t>2026-10-14T01:43:17+05:30</t>
+        </is>
+      </c>
+      <c r="W329" t="inlineStr"/>
+      <c r="X329" t="inlineStr"/>
+      <c r="Y329" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z329" t="inlineStr"/>
+      <c r="AA329" t="inlineStr">
+        <is>
           <t>(305) 680-3735, (310) 861-3485, (646) 693-9384, (786) 889-6892</t>
         </is>
       </c>
-      <c r="AB321" t="inlineStr">
+      <c r="AB329" t="inlineStr">
         <is>
           <t>https://instagram.com/wristaficionado, https://instagram.com/wristaficionado/, https://facebook.com/shopwristaficionado, https://twitter.com/wristaficionado</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB321"/>
+  <autoFilter ref="A1:AB329"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId2"/>
@@ -37090,178 +38070,219 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q267" r:id="rId906"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T267" r:id="rId907"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U267" r:id="rId908"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I268" r:id="rId909"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q268" r:id="rId910"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T268" r:id="rId911"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I269" r:id="rId912"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q269" r:id="rId913"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T269" r:id="rId914"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I270" r:id="rId915"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q270" r:id="rId916"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T270" r:id="rId917"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I271" r:id="rId918"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q271" r:id="rId919"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T271" r:id="rId920"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I272" r:id="rId921"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q272" r:id="rId922"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T272" r:id="rId923"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I273" r:id="rId924"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q273" r:id="rId925"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T273" r:id="rId926"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I274" r:id="rId927"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q274" r:id="rId928"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T274" r:id="rId929"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I275" r:id="rId930"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q275" r:id="rId931"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T275" r:id="rId932"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I276" r:id="rId933"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q276" r:id="rId934"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T276" r:id="rId935"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I277" r:id="rId936"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q277" r:id="rId937"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T277" r:id="rId938"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I278" r:id="rId939"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q278" r:id="rId940"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T278" r:id="rId941"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I279" r:id="rId942"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q279" r:id="rId943"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T279" r:id="rId944"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I280" r:id="rId945"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q280" r:id="rId946"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T280" r:id="rId947"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I281" r:id="rId948"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q281" r:id="rId949"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T281" r:id="rId950"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I282" r:id="rId951"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q282" r:id="rId952"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T282" r:id="rId953"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I283" r:id="rId954"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q283" r:id="rId955"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T283" r:id="rId956"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I284" r:id="rId957"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q284" r:id="rId958"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T284" r:id="rId959"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I285" r:id="rId960"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q285" r:id="rId961"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T285" r:id="rId962"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I286" r:id="rId963"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q286" r:id="rId964"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T286" r:id="rId965"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F287" r:id="rId966"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I287" r:id="rId967"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q287" r:id="rId968"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T287" r:id="rId969"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U287" r:id="rId970"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F288" r:id="rId971"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I288" r:id="rId972"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q288" r:id="rId973"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T288" r:id="rId974"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U288" r:id="rId975"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I289" r:id="rId976"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q289" r:id="rId977"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T289" r:id="rId978"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I290" r:id="rId979"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q290" r:id="rId980"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T290" r:id="rId981"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I291" r:id="rId982"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q291" r:id="rId983"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T291" r:id="rId984"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I292" r:id="rId985"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q292" r:id="rId986"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T292" r:id="rId987"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F293" r:id="rId988"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I293" r:id="rId989"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q293" r:id="rId990"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T293" r:id="rId991"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U293" r:id="rId992"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I294" r:id="rId993"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q294" r:id="rId994"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T294" r:id="rId995"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I295" r:id="rId996"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q295" r:id="rId997"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T295" r:id="rId998"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I296" r:id="rId999"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q296" r:id="rId1000"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T296" r:id="rId1001"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I297" r:id="rId1002"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q297" r:id="rId1003"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T297" r:id="rId1004"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I298" r:id="rId1005"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q298" r:id="rId1006"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T298" r:id="rId1007"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F299" r:id="rId1008"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I299" r:id="rId1009"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q299" r:id="rId1010"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T299" r:id="rId1011"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U299" r:id="rId1012"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I300" r:id="rId1013"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q300" r:id="rId1014"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T300" r:id="rId1015"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I301" r:id="rId1016"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q301" r:id="rId1017"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T301" r:id="rId1018"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I302" r:id="rId1019"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q302" r:id="rId1020"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T302" r:id="rId1021"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I303" r:id="rId1022"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q303" r:id="rId1023"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T303" r:id="rId1024"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I304" r:id="rId1025"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q304" r:id="rId1026"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T304" r:id="rId1027"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I305" r:id="rId1028"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q305" r:id="rId1029"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T305" r:id="rId1030"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I306" r:id="rId1031"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q306" r:id="rId1032"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T306" r:id="rId1033"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I307" r:id="rId1034"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q307" r:id="rId1035"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T307" r:id="rId1036"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F308" r:id="rId1037"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I308" r:id="rId1038"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q308" r:id="rId1039"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T308" r:id="rId1040"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U308" r:id="rId1041"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I309" r:id="rId1042"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q309" r:id="rId1043"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T309" r:id="rId1044"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I310" r:id="rId1045"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q310" r:id="rId1046"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T310" r:id="rId1047"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I311" r:id="rId1048"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q311" r:id="rId1049"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T311" r:id="rId1050"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I312" r:id="rId1051"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q312" r:id="rId1052"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T312" r:id="rId1053"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I313" r:id="rId1054"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q313" r:id="rId1055"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T313" r:id="rId1056"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I314" r:id="rId1057"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q314" r:id="rId1058"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T314" r:id="rId1059"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I315" r:id="rId1060"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q315" r:id="rId1061"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T315" r:id="rId1062"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I316" r:id="rId1063"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q316" r:id="rId1064"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T316" r:id="rId1065"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I317" r:id="rId1066"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q317" r:id="rId1067"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T317" r:id="rId1068"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I318" r:id="rId1069"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q318" r:id="rId1070"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T318" r:id="rId1071"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I319" r:id="rId1072"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q319" r:id="rId1073"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T319" r:id="rId1074"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I320" r:id="rId1075"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q320" r:id="rId1076"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T320" r:id="rId1077"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I321" r:id="rId1078"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q321" r:id="rId1079"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T321" r:id="rId1080"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F268" r:id="rId909"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I268" r:id="rId910"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q268" r:id="rId911"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T268" r:id="rId912"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U268" r:id="rId913"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F269" r:id="rId914"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I269" r:id="rId915"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q269" r:id="rId916"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T269" r:id="rId917"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U269" r:id="rId918"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I270" r:id="rId919"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q270" r:id="rId920"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T270" r:id="rId921"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F271" r:id="rId922"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I271" r:id="rId923"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q271" r:id="rId924"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U271" r:id="rId925"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F272" r:id="rId926"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I272" r:id="rId927"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q272" r:id="rId928"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T272" r:id="rId929"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U272" r:id="rId930"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I273" r:id="rId931"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q273" r:id="rId932"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T273" r:id="rId933"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I274" r:id="rId934"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q274" r:id="rId935"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T274" r:id="rId936"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I275" r:id="rId937"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q275" r:id="rId938"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T275" r:id="rId939"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F276" r:id="rId940"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I276" r:id="rId941"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q276" r:id="rId942"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T276" r:id="rId943"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U276" r:id="rId944"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I277" r:id="rId945"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q277" r:id="rId946"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T277" r:id="rId947"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I278" r:id="rId948"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q278" r:id="rId949"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T278" r:id="rId950"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I279" r:id="rId951"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q279" r:id="rId952"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T279" r:id="rId953"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I280" r:id="rId954"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q280" r:id="rId955"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T280" r:id="rId956"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I281" r:id="rId957"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q281" r:id="rId958"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T281" r:id="rId959"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I282" r:id="rId960"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q282" r:id="rId961"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T282" r:id="rId962"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I283" r:id="rId963"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q283" r:id="rId964"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T283" r:id="rId965"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I284" r:id="rId966"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q284" r:id="rId967"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T284" r:id="rId968"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F285" r:id="rId969"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I285" r:id="rId970"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q285" r:id="rId971"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T285" r:id="rId972"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U285" r:id="rId973"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I286" r:id="rId974"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q286" r:id="rId975"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T286" r:id="rId976"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F287" r:id="rId977"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I287" r:id="rId978"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q287" r:id="rId979"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T287" r:id="rId980"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U287" r:id="rId981"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I288" r:id="rId982"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q288" r:id="rId983"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T288" r:id="rId984"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F289" r:id="rId985"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I289" r:id="rId986"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q289" r:id="rId987"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T289" r:id="rId988"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U289" r:id="rId989"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I290" r:id="rId990"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q290" r:id="rId991"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T290" r:id="rId992"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F291" r:id="rId993"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I291" r:id="rId994"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q291" r:id="rId995"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T291" r:id="rId996"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U291" r:id="rId997"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I292" r:id="rId998"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q292" r:id="rId999"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T292" r:id="rId1000"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I293" r:id="rId1001"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q293" r:id="rId1002"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T293" r:id="rId1003"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I294" r:id="rId1004"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q294" r:id="rId1005"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T294" r:id="rId1006"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F295" r:id="rId1007"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I295" r:id="rId1008"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q295" r:id="rId1009"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T295" r:id="rId1010"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U295" r:id="rId1011"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F296" r:id="rId1012"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I296" r:id="rId1013"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q296" r:id="rId1014"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T296" r:id="rId1015"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U296" r:id="rId1016"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I297" r:id="rId1017"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q297" r:id="rId1018"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T297" r:id="rId1019"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I298" r:id="rId1020"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q298" r:id="rId1021"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T298" r:id="rId1022"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I299" r:id="rId1023"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q299" r:id="rId1024"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T299" r:id="rId1025"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I300" r:id="rId1026"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q300" r:id="rId1027"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T300" r:id="rId1028"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F301" r:id="rId1029"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I301" r:id="rId1030"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q301" r:id="rId1031"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T301" r:id="rId1032"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U301" r:id="rId1033"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I302" r:id="rId1034"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q302" r:id="rId1035"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T302" r:id="rId1036"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I303" r:id="rId1037"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q303" r:id="rId1038"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T303" r:id="rId1039"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I304" r:id="rId1040"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q304" r:id="rId1041"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T304" r:id="rId1042"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I305" r:id="rId1043"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q305" r:id="rId1044"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T305" r:id="rId1045"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I306" r:id="rId1046"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q306" r:id="rId1047"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T306" r:id="rId1048"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F307" r:id="rId1049"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I307" r:id="rId1050"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q307" r:id="rId1051"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T307" r:id="rId1052"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U307" r:id="rId1053"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I308" r:id="rId1054"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q308" r:id="rId1055"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T308" r:id="rId1056"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I309" r:id="rId1057"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q309" r:id="rId1058"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T309" r:id="rId1059"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I310" r:id="rId1060"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q310" r:id="rId1061"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T310" r:id="rId1062"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I311" r:id="rId1063"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q311" r:id="rId1064"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T311" r:id="rId1065"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I312" r:id="rId1066"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q312" r:id="rId1067"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T312" r:id="rId1068"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I313" r:id="rId1069"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q313" r:id="rId1070"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T313" r:id="rId1071"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I314" r:id="rId1072"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q314" r:id="rId1073"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T314" r:id="rId1074"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I315" r:id="rId1075"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q315" r:id="rId1076"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T315" r:id="rId1077"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F316" r:id="rId1078"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I316" r:id="rId1079"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q316" r:id="rId1080"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T316" r:id="rId1081"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U316" r:id="rId1082"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I317" r:id="rId1083"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q317" r:id="rId1084"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T317" r:id="rId1085"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I318" r:id="rId1086"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q318" r:id="rId1087"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T318" r:id="rId1088"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I319" r:id="rId1089"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q319" r:id="rId1090"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T319" r:id="rId1091"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I320" r:id="rId1092"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q320" r:id="rId1093"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T320" r:id="rId1094"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I321" r:id="rId1095"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q321" r:id="rId1096"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T321" r:id="rId1097"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I322" r:id="rId1098"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q322" r:id="rId1099"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T322" r:id="rId1100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I323" r:id="rId1101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q323" r:id="rId1102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T323" r:id="rId1103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I324" r:id="rId1104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q324" r:id="rId1105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T324" r:id="rId1106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I325" r:id="rId1107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q325" r:id="rId1108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T325" r:id="rId1109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I326" r:id="rId1110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q326" r:id="rId1111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T326" r:id="rId1112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I327" r:id="rId1113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q327" r:id="rId1114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T327" r:id="rId1115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I328" r:id="rId1116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q328" r:id="rId1117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T328" r:id="rId1118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I329" r:id="rId1119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q329" r:id="rId1120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T329" r:id="rId1121"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -37761,24 +38782,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C18" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -37791,21 +38812,21 @@
         <v>245</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -37842,14 +38863,14 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="C21" t="n">
         <v>2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -37869,14 +38890,14 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="C22" t="n">
         <v>5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -38004,24 +39025,24 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10911</v>
+        <v>10953</v>
       </c>
       <c r="C27" t="n">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="F27" t="n">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="G27" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -38061,7 +39082,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3">
@@ -38071,7 +39092,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4">
@@ -38081,7 +39102,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
@@ -38123,7 +39144,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10">
@@ -38133,7 +39154,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11">
@@ -38172,7 +39193,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T06:21:31+05:30</t>
+          <t>2026-10-14T06:41:44+05:30</t>
         </is>
       </c>
     </row>
@@ -38183,7 +39204,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3">
@@ -38193,7 +39214,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>10911</v>
+        <v>10953</v>
       </c>
     </row>
     <row r="4">

--- a/leadrun_jewelry/jewelry_qualified.xlsx
+++ b/leadrun_jewelry/jewelry_qualified.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qualified Leads'!$A$1:$AB$329</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qualified Leads'!$A$1:$AB$335</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB329"/>
+  <dimension ref="A1:AB335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -26730,8 +26730,16 @@
         </is>
       </c>
       <c r="F236" t="inlineStr"/>
-      <c r="G236" t="inlineStr"/>
-      <c r="H236" t="inlineStr"/>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Jeffrey Hamra</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
       <c r="I236" s="2" t="inlineStr">
         <is>
           <t>https://hamra.com</t>
@@ -26775,7 +26783,7 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-1985</t>
         </is>
       </c>
       <c r="S236" t="inlineStr">
@@ -26801,7 +26809,7 @@
         </is>
       </c>
       <c r="Y236" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z236" t="inlineStr"/>
       <c r="AA236" t="inlineStr">
@@ -32202,7 +32210,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Embellir Gallery of Gems, LLC</t>
+          <t>Taylor Made Jewelry, Inc.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -32212,27 +32220,27 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Jewelry Designers</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>(651) 905-1168</t>
+          <t>(330) 733-8000</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>brenda@embellirgems.com</t>
+          <t>taylormadejewelry@sbcglobal.net</t>
         </is>
       </c>
       <c r="F285" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/brenda-machnik-94544a76</t>
+          <t>https://www.linkedin.com/in/ruth-anne-penca-861a958</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Brenda S. Machnik</t>
+          <t>Anne Penca</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -32242,27 +32250,27 @@
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>https://www.embellirgems.com</t>
+          <t>https://taylormadejewelry.com</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>750 Main St Ste 111, Mendota Heights, MN 55118-3765</t>
+          <t>2492 Wedgewood Dr., Akron, OH 44312</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>Mendota Heights</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Minneapolis, MN</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -32274,12 +32282,12 @@
       <c r="P285" t="inlineStr"/>
       <c r="Q285" s="2" t="inlineStr">
         <is>
-          <t>https://www.bbb.org/us/mn/mendota-heights/profile/jewelry-designers/embellir-gallery-of-gems-llc-0704-7000375</t>
+          <t>https://www.bbb.org/us/oh/akron/profile/jewelry-stores/taylor-made-jewelry-inc-0272-20000095</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2 of 3, gia, custom-design, since-1998</t>
+          <t>2 of 3, gia, bench, custom-design, since-1991</t>
         </is>
       </c>
       <c r="S285" t="inlineStr">
@@ -32289,17 +32297,17 @@
       </c>
       <c r="T285" s="2" t="inlineStr">
         <is>
-          <t>https://www.embellirgems.com/</t>
+          <t>https://taylormadejewelry.com/</t>
         </is>
       </c>
       <c r="U285" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=%22Brenda+S.+Machnik%22+Mendota+Heights+linkedin&amp;hl=en&amp;num=10</t>
+          <t>https://www.google.com/search?q=%22Anne+Penca%22+Akron+linkedin&amp;hl=en&amp;num=10</t>
         </is>
       </c>
       <c r="V285" t="inlineStr">
         <is>
-          <t>2026-10-14T05:14:02+05:30</t>
+          <t>2026-10-14T05:04:28+05:30</t>
         </is>
       </c>
       <c r="W285" t="inlineStr"/>
@@ -32311,51 +32319,71 @@
       <c r="AA285" t="inlineStr"/>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>https://facebook.com/EmbellirGallery</t>
+          <t>https://facebook.com/TMJAkron, https://instagram.com/taylormadejewelryakron, https://x.com/TaylorMadeJewel</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Fixology Jewelry, Watch, and Smartphone Repair</t>
+          <t>Embellir Gallery of Gems, LLC</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Jewelry repair / goldsmith</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Electronics repair shop</t>
+          <t>Jewelry Designers</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>(612) 330-9925</t>
+          <t>(651) 905-1168</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>bloomington@fixologyrepair.com</t>
-        </is>
-      </c>
-      <c r="F286" t="inlineStr"/>
-      <c r="G286" t="inlineStr"/>
-      <c r="H286" t="inlineStr"/>
+          <t>brenda@embellirgems.com</t>
+        </is>
+      </c>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/brenda-machnik-94544a76</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Brenda S. Machnik</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>https://fixologyrepair.com</t>
+          <t>https://www.embellirgems.com</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>651 Nicollet Mall #247, Minneapolis, MN 55402, United States</t>
-        </is>
-      </c>
-      <c r="K286" t="inlineStr"/>
-      <c r="L286" t="inlineStr"/>
+          <t>750 Main St Ste 111, Mendota Heights, MN 55118-3765</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Mendota Heights</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>MN</t>
+        </is>
+      </c>
       <c r="M286" t="inlineStr">
         <is>
           <t>Minneapolis, MN</t>
@@ -32363,123 +32391,95 @@
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O286" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P286" t="n">
-        <v>113</v>
-      </c>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr"/>
+      <c r="P286" t="inlineStr"/>
       <c r="Q286" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Fixology+Jewelry,+Watch,+and+Smartphone+Repair/data=!4m7!3m6!1s0x52b3329a741033cd:0x422f1e9528fd8f0a!8m2!3d44.9773754!4d-93.2709679!16s%2Fg%2F11bwndn4z4!19sChIJzTMQdJoys1IRCo_9KJUeL0I</t>
+          <t>https://www.bbb.org/us/mn/mendota-heights/profile/jewelry-designers/embellir-gallery-of-gems-llc-0704-7000375</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, gia, custom-design, since-1998</t>
         </is>
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T286" s="2" t="inlineStr">
         <is>
-          <t>https://fixologyrepair.com/contact/</t>
-        </is>
-      </c>
-      <c r="U286" t="inlineStr"/>
+          <t>https://www.embellirgems.com/</t>
+        </is>
+      </c>
+      <c r="U286" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Brenda+S.+Machnik%22+Mendota+Heights+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V286" t="inlineStr">
         <is>
-          <t>2026-10-14T00:47:39+05:30</t>
-        </is>
-      </c>
-      <c r="W286" t="inlineStr">
-        <is>
-          <t>Fixology</t>
-        </is>
-      </c>
+          <t>2026-10-14T05:14:02+05:30</t>
+        </is>
+      </c>
+      <c r="W286" t="inlineStr"/>
       <c r="X286" t="inlineStr"/>
       <c r="Y286" t="n">
         <v>1</v>
       </c>
       <c r="Z286" t="inlineStr"/>
-      <c r="AA286" t="inlineStr">
-        <is>
-          <t>(772) 692-3774</t>
-        </is>
-      </c>
+      <c r="AA286" t="inlineStr"/>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>https://facebook.com/fixologytoledo, https://facebook.com/fixologyMallofAmerica</t>
+          <t>https://facebook.com/EmbellirGallery</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Gold'n Treasures, Inc.</t>
+          <t>Fixology Jewelry, Watch, and Smartphone Repair</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry repair / goldsmith</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Jewelry Stores</t>
+          <t>Electronics repair shop</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>(651) 227-2711</t>
+          <t>(612) 330-9925</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>agreene@goldn-treasures.com</t>
-        </is>
-      </c>
-      <c r="F287" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/todd-gimble-944a965</t>
-        </is>
-      </c>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>Todd Gimble</t>
-        </is>
-      </c>
-      <c r="H287" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
+          <t>bloomington@fixologyrepair.com</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr"/>
+      <c r="H287" t="inlineStr"/>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldn-treasures.com</t>
+          <t>https://fixologyrepair.com</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>805 Grand Ave, Saint Paul, MN 55105-3311</t>
-        </is>
-      </c>
-      <c r="K287" t="inlineStr">
-        <is>
-          <t>Saint Paul</t>
-        </is>
-      </c>
-      <c r="L287" t="inlineStr">
-        <is>
-          <t>MN</t>
-        </is>
-      </c>
+          <t>651 Nicollet Mall #247, Minneapolis, MN 55402, United States</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr"/>
+      <c r="L287" t="inlineStr"/>
       <c r="M287" t="inlineStr">
         <is>
           <t>Minneapolis, MN</t>
@@ -32487,48 +32487,44 @@
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>BBB</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O287" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="P287" t="n">
-        <v>368</v>
+        <v>113</v>
       </c>
       <c r="Q287" s="2" t="inlineStr">
         <is>
-          <t>https://www.bbb.org/us/mn/saint-paul/profile/jewelry-stores/goldn-treasures-inc-0704-24001102</t>
+          <t>https://www.google.com/maps/place/Fixology+Jewelry,+Watch,+and+Smartphone+Repair/data=!4m7!3m6!1s0x52b3329a741033cd:0x422f1e9528fd8f0a!8m2!3d44.9773754!4d-93.2709679!16s%2Fg%2F11bwndn4z4!19sChIJzTMQdJoys1IRCo_9KJUeL0I</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>2 of 3, gia, custom-design, since-1997</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="T287" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldn-treasures.com/</t>
-        </is>
-      </c>
-      <c r="U287" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=%22Todd+Gimble%22+Saint+Paul+linkedin&amp;hl=en&amp;num=10</t>
-        </is>
-      </c>
+          <t>https://fixologyrepair.com/contact/</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr"/>
       <c r="V287" t="inlineStr">
         <is>
-          <t>2026-10-14T05:29:52+05:30</t>
+          <t>2026-10-14T00:47:39+05:30</t>
         </is>
       </c>
       <c r="W287" t="inlineStr">
         <is>
-          <t>Gold'n Treasures</t>
+          <t>Fixology</t>
         </is>
       </c>
       <c r="X287" t="inlineStr"/>
@@ -32536,17 +32532,21 @@
         <v>1</v>
       </c>
       <c r="Z287" t="inlineStr"/>
-      <c r="AA287" t="inlineStr"/>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>(772) 692-3774</t>
+        </is>
+      </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>https://facebook.com/GoldTreasures, https://X.com/goldn_treasures, https://instagram.com/goldn_treasures</t>
+          <t>https://facebook.com/fixologytoledo, https://facebook.com/fixologyMallofAmerica</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Johnson Jewelers</t>
+          <t>Gold'n Treasures, Inc.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -32561,33 +32561,37 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>(651) 735-4400</t>
+          <t>(651) 227-2711</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>ryan@johnsonjewelers.com</t>
-        </is>
-      </c>
-      <c r="F288" t="inlineStr"/>
+          <t>agreene@goldn-treasures.com</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/todd-gimble-944a965</t>
+        </is>
+      </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Bob Johnson</t>
+          <t>Todd Gimble</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>President</t>
         </is>
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>https://johnsonjewelers.com</t>
+          <t>https://www.goldn-treasures.com</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>783 Radio Dr Ste 100D, Saint Paul, MN 55125-5402</t>
+          <t>805 Grand Ave, Saint Paul, MN 55105-3311</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -32610,55 +32614,63 @@
           <t>BBB</t>
         </is>
       </c>
-      <c r="O288" t="inlineStr"/>
-      <c r="P288" t="inlineStr"/>
+      <c r="O288" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P288" t="n">
+        <v>368</v>
+      </c>
       <c r="Q288" s="2" t="inlineStr">
         <is>
-          <t>https://www.bbb.org/us/mn/saint-paul/profile/jewelry-stores/johnson-jewelers-0704-9000723</t>
+          <t>https://www.bbb.org/us/mn/saint-paul/profile/jewelry-stores/goldn-treasures-inc-0704-24001102</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design, since-1976</t>
+          <t>2 of 3, gia, custom-design, since-1997</t>
         </is>
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T288" s="2" t="inlineStr">
         <is>
-          <t>https://johnsonjewelers.com/about/employment/</t>
-        </is>
-      </c>
-      <c r="U288" t="inlineStr"/>
+          <t>https://www.goldn-treasures.com/</t>
+        </is>
+      </c>
+      <c r="U288" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Todd+Gimble%22+Saint+Paul+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V288" t="inlineStr">
         <is>
-          <t>2026-10-14T05:42:57+05:30</t>
-        </is>
-      </c>
-      <c r="W288" t="inlineStr"/>
+          <t>2026-10-14T05:29:52+05:30</t>
+        </is>
+      </c>
+      <c r="W288" t="inlineStr">
+        <is>
+          <t>Gold'n Treasures</t>
+        </is>
+      </c>
       <c r="X288" t="inlineStr"/>
       <c r="Y288" t="n">
         <v>1</v>
       </c>
       <c r="Z288" t="inlineStr"/>
-      <c r="AA288" t="inlineStr">
-        <is>
-          <t>(651) 345-3825</t>
-        </is>
-      </c>
+      <c r="AA288" t="inlineStr"/>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>https://facebook.com/JohnsonJewelersInc, https://facebook.com/JohnsonJewelersofLakeCity</t>
+          <t>https://facebook.com/GoldTreasures, https://X.com/goldn_treasures, https://instagram.com/goldn_treasures</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Linden Hills Jewelers LLC</t>
+          <t>Johnson Jewelers</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -32673,22 +32685,18 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>(612) 512-4548</t>
+          <t>(651) 735-4400</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>lindenhillsjewelers@gmail.com</t>
-        </is>
-      </c>
-      <c r="F289" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/jason-eurich-58b46614b</t>
-        </is>
-      </c>
+          <t>ryan@johnsonjewelers.com</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr"/>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Jason Eurich</t>
+          <t>Bob Johnson</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -32698,17 +32706,17 @@
       </c>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>https://www.lindenhillsjewelers.com</t>
+          <t>https://johnsonjewelers.com</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>4305 Upton Ave S, Minneapolis, MN 55410-1556</t>
+          <t>783 Radio Dr Ste 100D, Saint Paul, MN 55125-5402</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Saint Paul</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
@@ -32726,59 +32734,55 @@
           <t>BBB</t>
         </is>
       </c>
-      <c r="O289" t="n">
-        <v>5</v>
-      </c>
-      <c r="P289" t="n">
-        <v>117</v>
-      </c>
+      <c r="O289" t="inlineStr"/>
+      <c r="P289" t="inlineStr"/>
       <c r="Q289" s="2" t="inlineStr">
         <is>
-          <t>https://www.bbb.org/us/mn/minneapolis/profile/jewelry-stores/linden-hills-jewelers-llc-0704-1000068648</t>
+          <t>https://www.bbb.org/us/mn/saint-paul/profile/jewelry-stores/johnson-jewelers-0704-9000723</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2 of 3, custom-design, since-2023</t>
+          <t>2 of 3, direct-line, custom-design, since-1976</t>
         </is>
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="T289" s="2" t="inlineStr">
         <is>
-          <t>https://www.lindenhillsjewelers.com/</t>
-        </is>
-      </c>
-      <c r="U289" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=%22Jason+Eurich%22+Minneapolis+linkedin&amp;hl=en&amp;num=10</t>
-        </is>
-      </c>
+          <t>https://johnsonjewelers.com/about/employment/</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr"/>
       <c r="V289" t="inlineStr">
         <is>
-          <t>2026-10-14T05:12:48+05:30</t>
-        </is>
-      </c>
-      <c r="W289" t="inlineStr">
-        <is>
-          <t>Linden Hills Jewelers</t>
-        </is>
-      </c>
+          <t>2026-10-14T05:42:57+05:30</t>
+        </is>
+      </c>
+      <c r="W289" t="inlineStr"/>
       <c r="X289" t="inlineStr"/>
       <c r="Y289" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z289" t="inlineStr"/>
-      <c r="AA289" t="inlineStr"/>
-      <c r="AB289" t="inlineStr"/>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>(651) 345-3825</t>
+        </is>
+      </c>
+      <c r="AB289" t="inlineStr">
+        <is>
+          <t>https://facebook.com/JohnsonJewelersInc, https://facebook.com/JohnsonJewelersofLakeCity</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>R.F. Moeller Jeweler</t>
+          <t>Landmark Jewelers, Inc.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -32788,35 +32792,47 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>(651) 698-6321</t>
+          <t>(651) 222-2282</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>alexandra@rfmoeller.com</t>
-        </is>
-      </c>
-      <c r="F290" t="inlineStr"/>
-      <c r="G290" t="inlineStr"/>
-      <c r="H290" t="inlineStr"/>
+          <t>info@landmarkjewelers.net</t>
+        </is>
+      </c>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tamara-sparrow-937177107</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Tamara Sparrow</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I290" s="2" t="inlineStr">
         <is>
-          <t>https://rfmoeller.com</t>
+          <t>https://landmarkjewelers.net</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>2065 Ford Pkwy, St Paul, MN 55116, United States</t>
+          <t>402 Saint Peter St, Saint Paul, MN 55102-1105</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Saint Paul</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -32831,70 +32847,58 @@
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O290" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P290" t="n">
-        <v>2186</v>
-      </c>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr"/>
+      <c r="P290" t="inlineStr"/>
       <c r="Q290" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/R.F.+Moeller+Jeweler/data=!4m7!3m6!1s0x87f62978048ef94d:0xea9c4d97c5c2b259!8m2!3d44.9181574!4d-93.1877644!16s%2Fg%2F1v7pz0rd!19sChIJTfmOBHgp9ocRWbLCxZdNnOo</t>
+          <t>https://www.bbb.org/us/mn/saint-paul/profile/jewelry-stores/landmark-jewelers-inc-0704-1000011124</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, ags, custom-design, since-1951</t>
+          <t>2 of 3, role-email, since-2007</t>
         </is>
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T290" s="2" t="inlineStr">
         <is>
-          <t>https://rfmoeller.com/</t>
-        </is>
-      </c>
-      <c r="U290" t="inlineStr"/>
+          <t>https://landmarkjewelers.net/</t>
+        </is>
+      </c>
+      <c r="U290" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Tamara+Sparrow%22+Saint+Paul+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V290" t="inlineStr">
         <is>
-          <t>2026-10-14T00:46:15+05:30</t>
-        </is>
-      </c>
-      <c r="W290" t="inlineStr">
-        <is>
-          <t>Moeller Jeweler R. F.</t>
-        </is>
-      </c>
+          <t>2026-10-14T05:34:24+05:30</t>
+        </is>
+      </c>
+      <c r="W290" t="inlineStr"/>
       <c r="X290" t="inlineStr"/>
       <c r="Y290" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z290" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
-      <c r="AA290" t="inlineStr">
-        <is>
-          <t>(651) 698-6322</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Z290" t="inlineStr"/>
+      <c r="AA290" t="inlineStr"/>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>https://facebook.com/rfmoellerjeweler, https://instagram.com/rfmoellerjeweler</t>
+          <t>https://instagram.com/landmarkjewelersmn, https://facebook.com/LandmarkJewelersCo, https://instagram.com/finch.engraving</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Wayzata Jewelers LLC</t>
+          <t>Linden Hills Jewelers LLC</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -32909,22 +32913,22 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>(952) 239-0099</t>
+          <t>(612) 512-4548</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>jon@wayzatajewelers.com</t>
+          <t>lindenhillsjewelers@gmail.com</t>
         </is>
       </c>
       <c r="F291" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/jon-gilbert-7a93944b</t>
+          <t>https://www.linkedin.com/in/jason-eurich-58b46614b</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Jon Gilbert</t>
+          <t>Jason Eurich</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -32934,17 +32938,17 @@
       </c>
       <c r="I291" s="2" t="inlineStr">
         <is>
-          <t>https://wayzatajewelers.com</t>
+          <t>https://www.lindenhillsjewelers.com</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>1250 Wayzata Blvd E, Wayzata, MN 55391</t>
+          <t>4305 Upton Ave S, Minneapolis, MN 55410-1556</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>Wayzata</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -32963,19 +32967,19 @@
         </is>
       </c>
       <c r="O291" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="P291" t="n">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="Q291" s="2" t="inlineStr">
         <is>
-          <t>https://www.bbb.org/us/mn/wayzata/profile/jewelry-stores/wayzata-jewelers-llc-0704-96346501</t>
+          <t>https://www.bbb.org/us/mn/minneapolis/profile/jewelry-stores/linden-hills-jewelers-llc-0704-1000068648</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2 of 3, custom-design, since-2002</t>
+          <t>2 of 3, custom-design, since-2023</t>
         </is>
       </c>
       <c r="S291" t="inlineStr">
@@ -32985,117 +32989,105 @@
       </c>
       <c r="T291" s="2" t="inlineStr">
         <is>
-          <t>https://wayzatajewelers.com/pages/contact-us</t>
+          <t>https://www.lindenhillsjewelers.com/</t>
         </is>
       </c>
       <c r="U291" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=%22Jon+Gilbert%22+Wayzata+linkedin&amp;hl=en&amp;num=10</t>
+          <t>https://www.google.com/search?q=%22Jason+Eurich%22+Minneapolis+linkedin&amp;hl=en&amp;num=10</t>
         </is>
       </c>
       <c r="V291" t="inlineStr">
         <is>
-          <t>2026-10-14T05:34:51+05:30</t>
+          <t>2026-10-14T05:12:48+05:30</t>
         </is>
       </c>
       <c r="W291" t="inlineStr">
         <is>
-          <t>Wayzata Jewelers</t>
+          <t>Linden Hills Jewelers</t>
         </is>
       </c>
       <c r="X291" t="inlineStr"/>
       <c r="Y291" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z291" t="inlineStr"/>
       <c r="AA291" t="inlineStr"/>
-      <c r="AB291" t="inlineStr">
-        <is>
-          <t>https://facebook.com/wayzatajewelers, https://instagram.com/wayzatajewelers</t>
-        </is>
-      </c>
+      <c r="AB291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Bailey's Fine Jewelry</t>
+          <t>R.F. Moeller Jeweler</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Jewelry Stores</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>(919) 829-7337</t>
+          <t>(651) 698-6321</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>carysubs@baileybox.com</t>
+          <t>alexandra@rfmoeller.com</t>
         </is>
       </c>
       <c r="F292" t="inlineStr"/>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>Jane Bailey</t>
-        </is>
-      </c>
-      <c r="H292" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
+      <c r="G292" t="inlineStr"/>
+      <c r="H292" t="inlineStr"/>
       <c r="I292" s="2" t="inlineStr">
         <is>
-          <t>https://www.baileybox.com</t>
+          <t>https://rfmoeller.com</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>415 Daniels St, Raleigh, NC 27605-1314</t>
+          <t>2065 Ford Pkwy, St Paul, MN 55116, United States</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>Raleigh</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Charlotte, NC</t>
+          <t>Minneapolis, MN</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t>BBB</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O292" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P292" t="n">
-        <v>775</v>
+        <v>2186</v>
       </c>
       <c r="Q292" s="2" t="inlineStr">
         <is>
-          <t>https://www.bbb.org/us/nc/raleigh/profile/jewelry-stores/baileys-fine-jewelry-0593-20988</t>
+          <t>https://www.google.com/maps/place/R.F.+Moeller+Jeweler/data=!4m7!3m6!1s0x87f62978048ef94d:0xea9c4d97c5c2b259!8m2!3d44.9181574!4d-93.1877644!16s%2Fg%2F1v7pz0rd!19sChIJTfmOBHgp9ocRWbLCxZdNnOo</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, ags, bench, custom-design, since-1948</t>
+          <t>2 of 3, direct-line, ags, custom-design, since-1951</t>
         </is>
       </c>
       <c r="S292" t="inlineStr">
@@ -33105,215 +33097,219 @@
       </c>
       <c r="T292" s="2" t="inlineStr">
         <is>
-          <t>https://baileybox.com/</t>
+          <t>https://rfmoeller.com/</t>
         </is>
       </c>
       <c r="U292" t="inlineStr"/>
       <c r="V292" t="inlineStr">
         <is>
-          <t>2026-10-14T06:02:43+05:30</t>
+          <t>2026-10-14T00:46:15+05:30</t>
         </is>
       </c>
       <c r="W292" t="inlineStr">
         <is>
-          <t>Morrison Smith Jewelers</t>
+          <t>Moeller Jeweler R. F.</t>
         </is>
       </c>
       <c r="X292" t="inlineStr"/>
       <c r="Y292" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z292" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="Z292" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA292" t="inlineStr">
         <is>
-          <t>(252) 353-3434, (252) 443-7676, (919) 892-3838</t>
+          <t>(651) 698-6322</t>
         </is>
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>https://facebook.com/BaileysFineJewelry, https://instagram.com/baileysfinejewelry, https://instagram.com/morrisonsmithjewelers, https://facebook.com/MorrisonSmithJewelers, https://x.com/morrisonsmith, https://twitter.com/morrisonsmith</t>
+          <t>https://facebook.com/rfmoellerjeweler, https://instagram.com/rfmoellerjeweler</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Fink's Jewelers</t>
+          <t>Wayzata Jewelers LLC</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Jewelers, Fix-It Shops, Watches</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>(704) 366-3120</t>
+          <t>(952) 239-0099</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>ecommerce@finks.com</t>
-        </is>
-      </c>
-      <c r="F293" t="inlineStr"/>
+          <t>jon@wayzatajewelers.com</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jon-gilbert-7a93944b</t>
+        </is>
+      </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Nathan Fink</t>
+          <t>Jon Gilbert</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="I293" s="2" t="inlineStr">
         <is>
-          <t>https://www.finks.com</t>
+          <t>https://wayzatajewelers.com</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>4400 Sharon Rd Ste 199, Charlotte, NC 28211</t>
+          <t>1250 Wayzata Blvd E, Wayzata, MN 55391</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Wayzata</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Charlotte, NC</t>
+          <t>Minneapolis, MN</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="O293" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="P293" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="Q293" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/charlotte-nc/mip/finks-jewelers-464773701</t>
+          <t>https://www.bbb.org/us/mn/wayzata/profile/jewelry-stores/wayzata-jewelers-llc-0704-96346501</t>
         </is>
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design, since-1930</t>
+          <t>2 of 3, custom-design, since-2002</t>
         </is>
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T293" s="2" t="inlineStr">
         <is>
-          <t>https://www.finks.com/</t>
-        </is>
-      </c>
-      <c r="U293" t="inlineStr"/>
+          <t>https://wayzatajewelers.com/pages/contact-us</t>
+        </is>
+      </c>
+      <c r="U293" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Jon+Gilbert%22+Wayzata+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V293" t="inlineStr">
         <is>
-          <t>2026-10-14T01:43:57+05:30</t>
+          <t>2026-10-14T05:34:51+05:30</t>
         </is>
       </c>
       <c r="W293" t="inlineStr">
         <is>
-          <t>John Paul Fine Jewelry</t>
+          <t>Wayzata Jewelers</t>
         </is>
       </c>
       <c r="X293" t="inlineStr"/>
       <c r="Y293" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z293" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
-      <c r="AA293" t="inlineStr">
-        <is>
-          <t>(423) 894-1188, (540) 342-2991, (540) 344-8697, (615) 236-8176, (704) 927-4888, (757) 640-1132, (804) 377-8589, (919) 881-8247</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="Z293" t="inlineStr"/>
+      <c r="AA293" t="inlineStr"/>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>https://facebook.com/FinksJewelers, https://instagram.com/finksjewelers</t>
+          <t>https://facebook.com/wayzatajewelers, https://instagram.com/wayzatajewelers</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Windsor Jewelers</t>
+          <t>Bailey's Fine Jewelry</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>(704) 556-7747</t>
+          <t>(919) 829-7337</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>nfo@windsor-jewelers.com</t>
+          <t>carysubs@baileybox.com</t>
         </is>
       </c>
       <c r="F294" t="inlineStr"/>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Kevin Slusher</t>
+          <t>Jane Bailey</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>President</t>
         </is>
       </c>
       <c r="I294" s="2" t="inlineStr">
         <is>
-          <t>https://www.windsor-jewelers.com</t>
+          <t>https://www.baileybox.com</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>6809-D Phillips Pl Ct, Charlotte, NC 28210, United States</t>
+          <t>415 Daniels St, Raleigh, NC 27605-1314</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>Winston-Salem</t>
+          <t>Raleigh</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
@@ -33323,23 +33319,23 @@
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="O294" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P294" t="n">
-        <v>1846</v>
+        <v>775</v>
       </c>
       <c r="Q294" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Windsor+Jewelers/data=!4m7!3m6!1s0x88569e13f91d1bb1:0x4b6448ed40c4d63c!8m2!3d35.1465046!4d-80.8269547!16s%2Fg%2F1tq8k7xj!19sChIJsRsd-ROeVogRPNbEQO1IZEs</t>
+          <t>https://www.bbb.org/us/nc/raleigh/profile/jewelry-stores/baileys-fine-jewelry-0593-20988</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design</t>
+          <t>2 of 3, direct-line, gia, ags, bench, custom-design, since-1948</t>
         </is>
       </c>
       <c r="S294" t="inlineStr">
@@ -33349,16 +33345,20 @@
       </c>
       <c r="T294" s="2" t="inlineStr">
         <is>
-          <t>https://www.windsor-jewelers.com/</t>
+          <t>https://baileybox.com/</t>
         </is>
       </c>
       <c r="U294" t="inlineStr"/>
       <c r="V294" t="inlineStr">
         <is>
-          <t>2026-10-14T00:51:17+05:30</t>
-        </is>
-      </c>
-      <c r="W294" t="inlineStr"/>
+          <t>2026-10-14T06:02:43+05:30</t>
+        </is>
+      </c>
+      <c r="W294" t="inlineStr">
+        <is>
+          <t>Morrison Smith Jewelers</t>
+        </is>
+      </c>
       <c r="X294" t="inlineStr"/>
       <c r="Y294" t="n">
         <v>2</v>
@@ -33366,19 +33366,19 @@
       <c r="Z294" t="inlineStr"/>
       <c r="AA294" t="inlineStr">
         <is>
-          <t>(336) 721-1768</t>
+          <t>(252) 353-3434, (252) 443-7676, (919) 892-3838</t>
         </is>
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>https://instagram.com/windsorjewelersnc/, https://facebook.com/OfficialWindsorJewelersNC</t>
+          <t>https://facebook.com/BaileysFineJewelry, https://instagram.com/baileysfinejewelry, https://instagram.com/morrisonsmithjewelers, https://facebook.com/MorrisonSmithJewelers, https://x.com/morrisonsmith, https://twitter.com/morrisonsmith</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Lindell Jewelers &amp; Appraisers</t>
+          <t>Fink's Jewelers</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -33388,113 +33388,121 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers, Fix-It Shops, Watches</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>(615) 373-7922</t>
+          <t>(704) 366-3120</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>lindelljewels@gmail.com</t>
-        </is>
-      </c>
-      <c r="F295" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/carolyn-linder-19ab1a80</t>
-        </is>
-      </c>
+          <t>ecommerce@finks.com</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr"/>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Carolyn A. Linder</t>
+          <t>Nathan Fink</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="I295" s="2" t="inlineStr">
         <is>
-          <t>https://www.lindelljewelers.com</t>
+          <t>https://www.finks.com</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>7028 Church St E Ste 106, Brentwood, TN 37027, United States</t>
+          <t>4400 Sharon Rd Ste 199, Charlotte, NC 28211</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>Brentwood</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Nashville, TN</t>
+          <t>Charlotte, NC</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O295" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P295" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="Q295" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Lindell+Jewelers+%26+Appraisers/data=!4m7!3m6!1s0x88647b266e6cc441:0xa03113da3f7ec814!8m2!3d36.0335009!4d-86.7862323!16s%2Fg%2F1tdjrwp3!19sChIJQcRsbiZ7ZIgRFMh-P9oTMaA</t>
+          <t>https://www.yellowpages.com/charlotte-nc/mip/finks-jewelers-464773701</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>2 of 3, custom-design, since-1991</t>
+          <t>2 of 3, direct-line, custom-design, since-1930</t>
         </is>
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="T295" s="2" t="inlineStr">
         <is>
-          <t>https://www.lindelljewelers.com/about-us</t>
-        </is>
-      </c>
-      <c r="U295" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=%22Carolyn+A.+Linder%22+Nashville+linkedin&amp;hl=en&amp;num=10</t>
-        </is>
-      </c>
+          <t>https://www.finks.com/</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr"/>
       <c r="V295" t="inlineStr">
         <is>
-          <t>2026-10-14T01:03:10+05:30</t>
-        </is>
-      </c>
-      <c r="W295" t="inlineStr"/>
+          <t>2026-10-14T01:43:57+05:30</t>
+        </is>
+      </c>
+      <c r="W295" t="inlineStr">
+        <is>
+          <t>John Paul Fine Jewelry</t>
+        </is>
+      </c>
       <c r="X295" t="inlineStr"/>
       <c r="Y295" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z295" t="inlineStr"/>
-      <c r="AA295" t="inlineStr"/>
-      <c r="AB295" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="Z295" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>(423) 894-1188, (540) 342-2991, (540) 344-8697, (615) 236-8176, (704) 927-4888, (757) 640-1132, (804) 377-8589, (919) 881-8247</t>
+        </is>
+      </c>
+      <c r="AB295" t="inlineStr">
+        <is>
+          <t>https://facebook.com/FinksJewelers, https://instagram.com/finksjewelers</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Strings for Hope</t>
+          <t>Main Street Jewelers</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -33504,27 +33512,27 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>(615) 891-4323</t>
+          <t>(919) 553-0803</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>emily@stringsforhope.com</t>
+          <t>mainstjewelers@aol.com</t>
         </is>
       </c>
       <c r="F296" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/emily-winters-182b7a219</t>
+          <t>https://www.linkedin.com/in/ed-austermuehle-2a101835</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Emily Winters</t>
+          <t>Ed Austermuehle</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -33534,40 +33542,44 @@
       </c>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>https://stringsforhope.com</t>
+          <t>https://www.mainstreet-jewelers.com</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>100 Taylor St, Nashville, TN 37208, United States</t>
-        </is>
-      </c>
-      <c r="K296" t="inlineStr"/>
-      <c r="L296" t="inlineStr"/>
+          <t>236 E Main St, Clayton, NC 27520-2450</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Clayton</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Nashville, TN</t>
+          <t>Charlotte, NC</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O296" t="n">
-        <v>5</v>
-      </c>
-      <c r="P296" t="n">
-        <v>23</v>
-      </c>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr"/>
+      <c r="P296" t="inlineStr"/>
       <c r="Q296" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Strings+for+Hope/data=!4m7!3m6!1s0x8864673b2485a245:0x7c5f1d365f1de575!8m2!3d36.1810664!4d-86.7859259!16s%2Fg%2F11p5x5j012!19sChIJRaKFJDtnZIgRdeUdXzYdX3w</t>
+          <t>https://www.bbb.org/us/nc/clayton/profile/jewelry-stores/main-street-jewelers-0593-90037571</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2 of 3, custom-design, since-2010</t>
+          <t>2 of 3, custom-design, since-2006</t>
         </is>
       </c>
       <c r="S296" t="inlineStr">
@@ -33577,17 +33589,17 @@
       </c>
       <c r="T296" s="2" t="inlineStr">
         <is>
-          <t>https://stringsforhope.com/pages/about-us</t>
+          <t>https://www.mainstreet-jewelers.com/contact</t>
         </is>
       </c>
       <c r="U296" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=%22Emily+Winters%22+Nashville+linkedin&amp;hl=en&amp;num=10</t>
+          <t>https://www.google.com/search?q=%22Ed+Austermuehle%22+Clayton+linkedin&amp;hl=en&amp;num=10</t>
         </is>
       </c>
       <c r="V296" t="inlineStr">
         <is>
-          <t>2026-10-14T01:01:21+05:30</t>
+          <t>2026-10-14T06:03:59+05:30</t>
         </is>
       </c>
       <c r="W296" t="inlineStr"/>
@@ -33599,174 +33611,182 @@
       <c r="AA296" t="inlineStr"/>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>https://facebook.com/Stringsforhope, https://instagram.com/stringsforhope</t>
+          <t>https://facebook.com/MainStreetJewelers, https://instagram.com/mainstreetjewelersclayton, https://facebook.com/wix</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Alltribes Indian Art</t>
+          <t>P. R. Sturgill Fine Jewelry, LLC</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Jewelers, Native American Goods, Art Goods</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>(800) 417-0024</t>
-        </is>
-      </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>admin@alltribes.com</t>
-        </is>
-      </c>
-      <c r="F297" t="inlineStr"/>
+          <t>(540) 639-6391</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr"/>
+      <c r="F297" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jeremy-jones-34502a55</t>
+        </is>
+      </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Richard Candy</t>
+          <t>Jeremy Jones</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="I297" s="2" t="inlineStr">
         <is>
-          <t>https://alltribes.com</t>
+          <t>https://prsturgills.com</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>75 W Baseline Rd Ste 6, Gilbert, AZ 85233</t>
+          <t>1037 E. Main Street, Radford, VA 24141</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>Gilbert</t>
+          <t>Radford</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ</t>
+          <t>Charlotte, NC</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="O297" t="inlineStr"/>
       <c r="P297" t="inlineStr"/>
       <c r="Q297" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/gilbert-az/mip/alltribes-indian-art-15755647</t>
+          <t>https://www.bbb.org/us/va/wytheville/profile/jewelry-stores/p-r-sturgill-fine-jewelry-llc-0613-9001663</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, direct-line, bench, custom-design, since-1963</t>
         </is>
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="T297" s="2" t="inlineStr">
-        <is>
-          <t>https://alltribes.com/</t>
-        </is>
-      </c>
-      <c r="U297" t="inlineStr"/>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="T297" t="inlineStr"/>
+      <c r="U297" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Jeremy+Jones%22+Radford+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V297" t="inlineStr">
         <is>
-          <t>2026-10-14T01:46:53+05:30</t>
+          <t>2026-10-14T06:00:17+05:30</t>
         </is>
       </c>
       <c r="W297" t="inlineStr"/>
       <c r="X297" t="inlineStr"/>
       <c r="Y297" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z297" t="inlineStr">
-        <is>
-          <t>toll-free</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Z297" t="inlineStr"/>
       <c r="AA297" t="inlineStr">
         <is>
-          <t>(480) 963-2284</t>
+          <t>(276) 335-2131</t>
         </is>
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>https://facebook.com/alltribes, https://instagram.com/alltribes_indian_art, https://facebook.com/pg/alltribes/videos/</t>
+          <t>https://instagram.com/prsturgill_radford, https://instagram.com/prsturgill_wytheville, https://facebook.com/PRSturgill</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Diasparx</t>
+          <t>Windsor Jewelers</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Wholesale jeweler</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr"/>
+          <t>Jewelry store</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>(704) 556-7747</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>daniel@diasparx.com</t>
+          <t>nfo@windsor-jewelers.com</t>
         </is>
       </c>
       <c r="F298" t="inlineStr"/>
-      <c r="G298" t="inlineStr"/>
-      <c r="H298" t="inlineStr"/>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>Kevin Slusher</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
       <c r="I298" s="2" t="inlineStr">
         <is>
-          <t>https://www.diasparx.com</t>
+          <t>https://www.windsor-jewelers.com</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>Camelback Tower, 6900 E Camelback Rd Suite 1050, Scottsdale, AZ 85251, United States</t>
+          <t>6809-D Phillips Pl Ct, Charlotte, NC 28210, United States</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>Scottsdale</t>
+          <t>Winston-Salem</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ</t>
+          <t>Charlotte, NC</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -33775,19 +33795,19 @@
         </is>
       </c>
       <c r="O298" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P298" t="n">
-        <v>22</v>
+        <v>1846</v>
       </c>
       <c r="Q298" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Diasparx/data=!4m7!3m6!1s0x872b0b6df95ae9b9:0x57de2ae948b26574!8m2!3d33.5025864!4d-111.9322129!16s%2Fg%2F11x19r328p!19sChIJuela-W0LK4cRdGWySOkq3lc</t>
+          <t>https://www.google.com/maps/place/Windsor+Jewelers/data=!4m7!3m6!1s0x88569e13f91d1bb1:0x4b6448ed40c4d63c!8m2!3d35.1465046!4d-80.8269547!16s%2Fg%2F1tq8k7xj!19sChIJsRsd-ROeVogRPNbEQO1IZEs</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design</t>
+          <t>2 of 3, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S298" t="inlineStr">
@@ -33797,36 +33817,36 @@
       </c>
       <c r="T298" s="2" t="inlineStr">
         <is>
-          <t>https://www.diasparx.com/</t>
+          <t>https://www.windsor-jewelers.com/</t>
         </is>
       </c>
       <c r="U298" t="inlineStr"/>
       <c r="V298" t="inlineStr">
         <is>
-          <t>2026-10-14T01:09:41+05:30</t>
+          <t>2026-10-14T00:51:17+05:30</t>
         </is>
       </c>
       <c r="W298" t="inlineStr"/>
       <c r="X298" t="inlineStr"/>
       <c r="Y298" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z298" t="inlineStr"/>
       <c r="AA298" t="inlineStr">
         <is>
-          <t>(212) 555-0134, (480) 640-0948</t>
+          <t>(336) 721-1768</t>
         </is>
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>https://instagram.com/diasparx, https://facebook.com/profile.php?id=100088561748204</t>
+          <t>https://instagram.com/windsorjewelersnc/, https://facebook.com/OfficialWindsorJewelersNC</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Expert Shoe Luggage Watch &amp; Jewelry Repair</t>
+          <t>Belle Meade Jewelry &amp; Repair, LLC</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -33836,105 +33856,125 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Shoe repair shop</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>(480) 451-1214</t>
+          <t>(615) 269-3288</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>info@expertshoerepair.com</t>
-        </is>
-      </c>
-      <c r="F299" t="inlineStr"/>
-      <c r="G299" t="inlineStr"/>
-      <c r="H299" t="inlineStr"/>
+          <t>castgold@gmail.com</t>
+        </is>
+      </c>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/scott-isaacs-22b47074</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>Scott Isaacs</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>https://expertslwjrepair.com</t>
+          <t>https://bellemeadejewelry.com</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>10105 E Vía Linda Ste A- 105, Scottsdale, AZ 85258, United States</t>
+          <t>4515 Harding Pike Ste. 112, Nashville, TN 37205</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>Scottsdale</t>
+          <t>Nashville</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ</t>
+          <t>Nashville, TN</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="O299" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="P299" t="n">
-        <v>522</v>
+        <v>223</v>
       </c>
       <c r="Q299" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Expert+Shoe+Luggage+Watch+%26+Jewelry+Repair/data=!4m7!3m6!1s0x872b6d13c4a490a7:0x78beb810dbe170f!8m2!3d33.573104!4d-111.8634771!16s%2Fg%2F11hzvcxvl9!19sChIJp5CkxBNtK4cRDxe-DYHriwc</t>
+          <t>https://www.bbb.org/us/tn/nashville/profile/jewelry-stores/belle-meade-jewelry-repair-llc-0573-37040765</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, since-1960</t>
+          <t>2 of 3, custom-design, since-2006</t>
         </is>
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T299" s="2" t="inlineStr">
         <is>
-          <t>https://www.expertshoerepair.com/</t>
-        </is>
-      </c>
-      <c r="U299" t="inlineStr"/>
+          <t>https://bellemeadejewelry.com/</t>
+        </is>
+      </c>
+      <c r="U299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Scott+Isaacs%22+Nashville+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V299" t="inlineStr">
         <is>
-          <t>2026-10-14T01:10:03+05:30</t>
-        </is>
-      </c>
-      <c r="W299" t="inlineStr"/>
+          <t>2026-10-14T06:14:46+05:30</t>
+        </is>
+      </c>
+      <c r="W299" t="inlineStr">
+        <is>
+          <t>Belle Meade Jewelry &amp; Repair, Belle Meade Jewelry And Repair</t>
+        </is>
+      </c>
       <c r="X299" t="inlineStr"/>
       <c r="Y299" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z299" t="inlineStr"/>
-      <c r="AA299" t="inlineStr">
-        <is>
-          <t>(480) 269-7591</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="Z299" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="AA299" t="inlineStr"/>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>https://facebook.com/expertshoerepair, https://instagram.com/expert_shoe_repair</t>
+          <t>https://instagram.com/bellemeadefinejewelry, https://instagram.com/squarespace, https://x.com/squarespace, https://facebook.com/squarespace</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Sunrise Jewelry &amp; Gallery</t>
+          <t>Lindell Jewelers &amp; Appraisers</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -33949,40 +33989,52 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>(480) 425-9944</t>
+          <t>(615) 373-7922</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>info@sunrisejewelryusa.com</t>
-        </is>
-      </c>
-      <c r="F300" t="inlineStr"/>
-      <c r="G300" t="inlineStr"/>
-      <c r="H300" t="inlineStr"/>
+          <t>lindelljewels@gmail.com</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/carolyn-linder-19ab1a80</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>Carolyn A. Linder</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I300" s="2" t="inlineStr">
         <is>
-          <t>https://www.sunrisejewelryusa.com</t>
+          <t>https://www.lindelljewelers.com</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>7254 E Main St Suite 101, Scottsdale, AZ 85251, United States</t>
+          <t>7028 Church St E Ste 106, Brentwood, TN 37027, United States</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>Scottsdale</t>
+          <t>Brentwood</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ</t>
+          <t>Nashville, TN</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -33991,62 +34043,54 @@
         </is>
       </c>
       <c r="O300" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P300" t="n">
-        <v>98</v>
+        <v>56</v>
       </c>
       <c r="Q300" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Sunrise+Jewelry+%26+Gallery/data=!4m7!3m6!1s0x872b0bd689ab1b37:0xfa243a0d0a63c6b6!8m2!3d33.4932392!4d-111.9247178!16s%2Fg%2F11q1rmxn64!19sChIJNxuridYLK4cRtsZjCg06JPo</t>
+          <t>https://www.google.com/maps/place/Lindell+Jewelers+%26+Appraisers/data=!4m7!3m6!1s0x88647b266e6cc441:0xa03113da3f7ec814!8m2!3d36.0335009!4d-86.7862323!16s%2Fg%2F1tdjrwp3!19sChIJQcRsbiZ7ZIgRFMh-P9oTMaA</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, since-2006</t>
+          <t>2 of 3, custom-design, since-1991</t>
         </is>
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T300" s="2" t="inlineStr">
         <is>
-          <t>https://sunrisejewelryusa.com/</t>
-        </is>
-      </c>
-      <c r="U300" t="inlineStr"/>
+          <t>https://www.lindelljewelers.com/about-us</t>
+        </is>
+      </c>
+      <c r="U300" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Carolyn+A.+Linder%22+Nashville+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V300" t="inlineStr">
         <is>
-          <t>2026-10-14T01:05:57+05:30</t>
-        </is>
-      </c>
-      <c r="W300" t="inlineStr">
-        <is>
-          <t>Sunrise Trading Post</t>
-        </is>
-      </c>
+          <t>2026-10-14T01:03:10+05:30</t>
+        </is>
+      </c>
+      <c r="W300" t="inlineStr"/>
       <c r="X300" t="inlineStr"/>
       <c r="Y300" t="n">
         <v>1</v>
       </c>
       <c r="Z300" t="inlineStr"/>
-      <c r="AA300" t="inlineStr">
-        <is>
-          <t>(480) 994-0170</t>
-        </is>
-      </c>
-      <c r="AB300" t="inlineStr">
-        <is>
-          <t>https://instagram.com/sunrisejewelryandgallery, https://facebook.com/sunrisejewelryusa</t>
-        </is>
-      </c>
+      <c r="AA300" t="inlineStr"/>
+      <c r="AB300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Truly Blessed Jewels - Scottsdale</t>
+          <t>Strings for Hope</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -34061,52 +34105,44 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>(480) 306-4296</t>
+          <t>(615) 891-4323</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>becky@trulyblessedjewels.com</t>
+          <t>emily@stringsforhope.com</t>
         </is>
       </c>
       <c r="F301" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/lisa-valenzuela-801071264</t>
+          <t>https://www.linkedin.com/in/emily-winters-182b7a219</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Lisa Valenzuela</t>
+          <t>Emily Winters</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>President</t>
         </is>
       </c>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>https://trulyblessedjewels.com</t>
+          <t>https://stringsforhope.com</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>7058 E 5th Ave, Scottsdale, AZ 85251, United States</t>
-        </is>
-      </c>
-      <c r="K301" t="inlineStr">
-        <is>
-          <t>Scottsdale</t>
-        </is>
-      </c>
-      <c r="L301" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
+          <t>100 Taylor St, Nashville, TN 37208, United States</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr"/>
+      <c r="L301" t="inlineStr"/>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ</t>
+          <t>Nashville, TN</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -34115,19 +34151,19 @@
         </is>
       </c>
       <c r="O301" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P301" t="n">
-        <v>1244</v>
+        <v>23</v>
       </c>
       <c r="Q301" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Truly+Blessed+Jewels+-+Scottsdale/data=!4m7!3m6!1s0x872b0bbd075f72f5:0xe625e386ff4966fb!8m2!3d33.498152!4d-111.9292942!16s%2Fg%2F11hf00j2kh!19sChIJ9XJfB70LK4cR-2ZJ_4bjJeY</t>
+          <t>https://www.google.com/maps/place/Strings+for+Hope/data=!4m7!3m6!1s0x8864673b2485a245:0x7c5f1d365f1de575!8m2!3d36.1810664!4d-86.7859259!16s%2Fg%2F11p5x5j012!19sChIJRaKFJDtnZIgRdeUdXzYdX3w</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>2 of 3</t>
+          <t>2 of 3, custom-design, since-2010</t>
         </is>
       </c>
       <c r="S301" t="inlineStr">
@@ -34137,44 +34173,36 @@
       </c>
       <c r="T301" s="2" t="inlineStr">
         <is>
-          <t>https://trulyblessedjewels.com/pages/contact-us-1</t>
+          <t>https://stringsforhope.com/pages/about-us</t>
         </is>
       </c>
       <c r="U301" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=%22Lisa+Valenzuela%22+Scottsdale+linkedin&amp;hl=en&amp;num=10</t>
+          <t>https://www.google.com/search?q=%22Emily+Winters%22+Nashville+linkedin&amp;hl=en&amp;num=10</t>
         </is>
       </c>
       <c r="V301" t="inlineStr">
         <is>
-          <t>2026-10-14T01:05:54+05:30</t>
-        </is>
-      </c>
-      <c r="W301" t="inlineStr">
-        <is>
-          <t>Truly Blessed Jewels</t>
-        </is>
-      </c>
-      <c r="X301" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ</t>
-        </is>
-      </c>
+          <t>2026-10-14T01:01:21+05:30</t>
+        </is>
+      </c>
+      <c r="W301" t="inlineStr"/>
+      <c r="X301" t="inlineStr"/>
       <c r="Y301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z301" t="inlineStr"/>
       <c r="AA301" t="inlineStr"/>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>https://instagram.com/trulyblessedjewels, https://facebook.com/Truly Blessed Jewels</t>
+          <t>https://facebook.com/Stringsforhope, https://instagram.com/stringsforhope</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Exquisite Timepieces</t>
+          <t>Alltribes Indian Art</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -34184,45 +34212,53 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Jewelers, Watches</t>
+          <t>Jewelers, Native American Goods, Art Goods</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>(239) 227-2932</t>
+          <t>(800) 417-0024</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>team@exquisitetimepieces.com</t>
+          <t>admin@alltribes.com</t>
         </is>
       </c>
       <c r="F302" t="inlineStr"/>
-      <c r="G302" t="inlineStr"/>
-      <c r="H302" t="inlineStr"/>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Richard Candy</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>https://www.exquisitetimepieces.com</t>
+          <t>https://alltribes.com</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>4380 Gulf Shore Blvd N, Naples, FL 34103</t>
+          <t>75 W Baseline Rd Ste 6, Gilbert, AZ 85233</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>Naples</t>
+          <t>Gilbert</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Naples, FL</t>
+          <t>Scottsdale, AZ</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -34230,20 +34266,16 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O302" t="n">
-        <v>5</v>
-      </c>
-      <c r="P302" t="n">
-        <v>31</v>
-      </c>
+      <c r="O302" t="inlineStr"/>
+      <c r="P302" t="inlineStr"/>
       <c r="Q302" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/naples-fl/mip/exquisite-timepieces-14306847</t>
+          <t>https://www.yellowpages.com/gilbert-az/mip/alltribes-indian-art-15755647</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, ja, since-1998</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S302" t="inlineStr">
@@ -34253,13 +34285,13 @@
       </c>
       <c r="T302" s="2" t="inlineStr">
         <is>
-          <t>https://www.exquisitetimepieces.com/</t>
+          <t>https://alltribes.com/</t>
         </is>
       </c>
       <c r="U302" t="inlineStr"/>
       <c r="V302" t="inlineStr">
         <is>
-          <t>2026-10-14T01:47:28+05:30</t>
+          <t>2026-10-14T01:46:53+05:30</t>
         </is>
       </c>
       <c r="W302" t="inlineStr"/>
@@ -34267,42 +34299,42 @@
       <c r="Y302" t="n">
         <v>0</v>
       </c>
-      <c r="Z302" t="inlineStr"/>
+      <c r="Z302" t="inlineStr">
+        <is>
+          <t>toll-free</t>
+        </is>
+      </c>
       <c r="AA302" t="inlineStr">
         <is>
-          <t>(239) 262-4545</t>
+          <t>(480) 963-2284</t>
         </is>
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>https://facebook.com/pages/Exquisite-Timepieces/138888796144728, https://x.com/TimeExquisite, https://instagram.com/exquisitetimepieces, https://facebook.com/Exquisite-Timepieces-138888796144728, https://twitter.com/TimeExquisite</t>
+          <t>https://facebook.com/alltribes, https://instagram.com/alltribes_indian_art, https://facebook.com/pg/alltribes/videos/</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Gold Silver Naples</t>
+          <t>Diasparx</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Gold dealer</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>(239) 591-5999</t>
-        </is>
-      </c>
+          <t>Wholesale jeweler</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr">
         <is>
-          <t>goldsilvercoinsofnaples@gmail.com</t>
+          <t>daniel@diasparx.com</t>
         </is>
       </c>
       <c r="F303" t="inlineStr"/>
@@ -34310,19 +34342,27 @@
       <c r="H303" t="inlineStr"/>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldsilvernaples.com</t>
+          <t>https://www.diasparx.com</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>1575 Pine Ridge Rd Ste 20, Naples, FL 34109, United States</t>
-        </is>
-      </c>
-      <c r="K303" t="inlineStr"/>
-      <c r="L303" t="inlineStr"/>
+          <t>Camelback Tower, 6900 E Camelback Rd Suite 1050, Scottsdale, AZ 85251, United States</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Scottsdale</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Naples, FL</t>
+          <t>Scottsdale, AZ</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -34331,19 +34371,19 @@
         </is>
       </c>
       <c r="O303" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="P303" t="n">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="Q303" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Gold+Silver+Naples/data=!4m7!3m6!1s0x88db1d7e5a7b7a49:0x324bd0e63a60dfad!8m2!3d26.2126153!4d-81.7867476!16s%2Fg%2F11k9ml4kb0!19sChIJSXp7Wn4d24gRrd9gOubQSzI</t>
+          <t>https://www.google.com/maps/place/Diasparx/data=!4m7!3m6!1s0x872b0b6df95ae9b9:0x57de2ae948b26574!8m2!3d33.5025864!4d-111.9322129!16s%2Fg%2F11x19r328p!19sChIJuela-W0LK4cRdGWySOkq3lc</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, direct-line, gia, custom-design</t>
         </is>
       </c>
       <c r="S303" t="inlineStr">
@@ -34353,13 +34393,13 @@
       </c>
       <c r="T303" s="2" t="inlineStr">
         <is>
-          <t>https://goldsilvernaples.com/</t>
+          <t>https://www.diasparx.com/</t>
         </is>
       </c>
       <c r="U303" t="inlineStr"/>
       <c r="V303" t="inlineStr">
         <is>
-          <t>2026-10-14T01:13:03+05:30</t>
+          <t>2026-10-14T01:09:41+05:30</t>
         </is>
       </c>
       <c r="W303" t="inlineStr"/>
@@ -34370,63 +34410,67 @@
       <c r="Z303" t="inlineStr"/>
       <c r="AA303" t="inlineStr">
         <is>
-          <t>(239) 234-9588</t>
-        </is>
-      </c>
-      <c r="AB303" t="inlineStr"/>
+          <t>(212) 555-0134, (480) 640-0948</t>
+        </is>
+      </c>
+      <c r="AB303" t="inlineStr">
+        <is>
+          <t>https://instagram.com/diasparx, https://facebook.com/profile.php?id=100088561748204</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>International Diamond Center</t>
+          <t>Expert Shoe Luggage Watch &amp; Jewelry Repair</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Jewelry repair / goldsmith</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Shoe repair shop</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>(239) 342-2550</t>
+          <t>(480) 451-1214</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>u003emarketing@shopidc.com</t>
+          <t>info@expertshoerepair.com</t>
         </is>
       </c>
       <c r="F304" t="inlineStr"/>
-      <c r="G304" t="inlineStr">
-        <is>
-          <t>Keith Leclerc</t>
-        </is>
-      </c>
-      <c r="H304" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
+      <c r="G304" t="inlineStr"/>
+      <c r="H304" t="inlineStr"/>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>https://shopidc.com</t>
+          <t>https://expertslwjrepair.com</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>8840 Tamiami Trl N, Naples, FL 34108, United States</t>
-        </is>
-      </c>
-      <c r="K304" t="inlineStr"/>
-      <c r="L304" t="inlineStr"/>
+          <t>10105 E Vía Linda Ste A- 105, Scottsdale, AZ 85258, United States</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Scottsdale</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Naples, FL</t>
+          <t>Scottsdale, AZ</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -34438,16 +34482,16 @@
         <v>4.9</v>
       </c>
       <c r="P304" t="n">
-        <v>278</v>
+        <v>522</v>
       </c>
       <c r="Q304" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/International+Diamond+Center/data=!4m7!3m6!1s0x88db1f3b506da15f:0xd38690aae0aec00b!8m2!3d26.2479716!4d-81.800361!16s%2Fg%2F11t8h0cjn9!19sChIJX6FtUDsf24gRC8Cu4KqQhtM</t>
+          <t>https://www.google.com/maps/place/Expert+Shoe+Luggage+Watch+%26+Jewelry+Repair/data=!4m7!3m6!1s0x872b6d13c4a490a7:0x78beb810dbe170f!8m2!3d33.573104!4d-111.8634771!16s%2Fg%2F11hzvcxvl9!19sChIJp5CkxBNtK4cRDxe-DYHriwc</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design</t>
+          <t>2 of 3, role-email, direct-line, since-1960</t>
         </is>
       </c>
       <c r="S304" t="inlineStr">
@@ -34457,56 +34501,64 @@
       </c>
       <c r="T304" s="2" t="inlineStr">
         <is>
-          <t>https://shopidc.com/</t>
+          <t>https://www.expertshoerepair.com/</t>
         </is>
       </c>
       <c r="U304" t="inlineStr"/>
       <c r="V304" t="inlineStr">
         <is>
-          <t>2026-10-14T01:15:46+05:30</t>
-        </is>
-      </c>
-      <c r="W304" t="inlineStr"/>
+          <t>2026-10-14T01:10:03+05:30</t>
+        </is>
+      </c>
+      <c r="W304" t="inlineStr">
+        <is>
+          <t>Expert Shoe Repair</t>
+        </is>
+      </c>
       <c r="X304" t="inlineStr"/>
       <c r="Y304" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z304" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Z304" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA304" t="inlineStr">
         <is>
-          <t>(239) 364-1799, (352) 681-4550, (407) 770-5991, (407) 862-8990, (407) 903-9494, (727) 572-6323, (772) 408-4640, (813) 961-0097, (863) 226-4400, (912) 354-4344, (941) 278-3900</t>
+          <t>(480) 269-7591</t>
         </is>
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>https://facebook.com/internationaldiamondcenter, https://instagram.com/internationaldiamondcenter_, https://twitter.com/shopidc</t>
+          <t>https://facebook.com/expertshoerepair, https://instagram.com/expert_shoe_repair</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Mark Loren Design</t>
+          <t>Sunrise Jewelry &amp; Gallery</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Designers</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>(239) 596-5820</t>
+          <t>(480) 425-9944</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>contact@marklorendesigns.com</t>
+          <t>info@sunrisejewelryusa.com</t>
         </is>
       </c>
       <c r="F305" t="inlineStr"/>
@@ -34514,44 +34566,48 @@
       <c r="H305" t="inlineStr"/>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>https://www.marklorendesigns.com</t>
+          <t>https://www.sunrisejewelryusa.com</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>9118 Strada Pl Ste 8120, Naples, FL 34108</t>
+          <t>7254 E Main St Suite 101, Scottsdale, AZ 85251, United States</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>Naples</t>
+          <t>Scottsdale</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Naples, FL</t>
+          <t>Scottsdale, AZ</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O305" t="inlineStr"/>
-      <c r="P305" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O305" t="n">
+        <v>5</v>
+      </c>
+      <c r="P305" t="n">
+        <v>98</v>
+      </c>
       <c r="Q305" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/naples-fl/mip/mark-loren-design-475273503</t>
+          <t>https://www.google.com/maps/place/Sunrise+Jewelry+%26+Gallery/data=!4m7!3m6!1s0x872b0bd689ab1b37:0xfa243a0d0a63c6b6!8m2!3d33.4932392!4d-111.9247178!16s%2Fg%2F11q1rmxn64!19sChIJNxuridYLK4cRtsZjCg06JPo</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, bench, custom-design</t>
+          <t>2 of 3, role-email, direct-line, since-2006</t>
         </is>
       </c>
       <c r="S305" t="inlineStr">
@@ -34561,84 +34617,100 @@
       </c>
       <c r="T305" s="2" t="inlineStr">
         <is>
-          <t>https://marklorendesigns.com/</t>
+          <t>https://sunrisejewelryusa.com/</t>
         </is>
       </c>
       <c r="U305" t="inlineStr"/>
       <c r="V305" t="inlineStr">
         <is>
-          <t>2026-10-14T01:47:36+05:30</t>
-        </is>
-      </c>
-      <c r="W305" t="inlineStr"/>
+          <t>2026-10-14T01:05:57+05:30</t>
+        </is>
+      </c>
+      <c r="W305" t="inlineStr">
+        <is>
+          <t>Sunrise Trading Post</t>
+        </is>
+      </c>
       <c r="X305" t="inlineStr"/>
       <c r="Y305" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z305" t="inlineStr"/>
       <c r="AA305" t="inlineStr">
         <is>
-          <t>(239) 482-4664</t>
+          <t>(480) 994-0170</t>
         </is>
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>https://facebook.com/marklorendesigns, https://instagram.com/marklorendesign</t>
+          <t>https://instagram.com/sunrisejewelryandgallery, https://facebook.com/sunrisejewelryusa</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Black Rock Galleries</t>
+          <t>Truly Blessed Jewels - Scottsdale</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Estate liquidator</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>(203) 900-1110</t>
+          <t>(480) 306-4296</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>april@blackrockgalleries.com</t>
-        </is>
-      </c>
-      <c r="F306" t="inlineStr"/>
-      <c r="G306" t="inlineStr"/>
-      <c r="H306" t="inlineStr"/>
+          <t>becky@trulyblessedjewels.com</t>
+        </is>
+      </c>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lisa-valenzuela-801071264</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>Lisa Valenzuela</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>https://www.blackrockgalleries.com</t>
+          <t>https://trulyblessedjewels.com</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>179 Hamilton Ave, Greenwich, CT 06830, United States</t>
+          <t>7058 E 5th Ave, Scottsdale, AZ 85251, United States</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>Cary</t>
+          <t>Scottsdale</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Greenwich, CT</t>
+          <t>Scottsdale, AZ</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -34647,151 +34719,151 @@
         </is>
       </c>
       <c r="O306" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="P306" t="n">
-        <v>25</v>
+        <v>1244</v>
       </c>
       <c r="Q306" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Black+Rock+Galleries/data=!4m7!3m6!1s0x89c299cdad7d8901:0x806db5b713ec68d7!8m2!3d41.0179193!4d-73.6391571!16s%2Fg%2F11ckvlk1pv!19sChIJAYl9rc2ZwokR12jsE7e1bYA</t>
+          <t>https://www.google.com/maps/place/Truly+Blessed+Jewels+-+Scottsdale/data=!4m7!3m6!1s0x872b0bbd075f72f5:0xe625e386ff4966fb!8m2!3d33.498152!4d-111.9292942!16s%2Fg%2F11hf00j2kh!19sChIJ9XJfB70LK4cR-2ZJ_4bjJeY</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia</t>
+          <t>2 of 3</t>
         </is>
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T306" s="2" t="inlineStr">
         <is>
-          <t>https://www.blackrockgalleries.com/contact</t>
-        </is>
-      </c>
-      <c r="U306" t="inlineStr"/>
+          <t>https://trulyblessedjewels.com/pages/contact-us-1</t>
+        </is>
+      </c>
+      <c r="U306" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Lisa+Valenzuela%22+Scottsdale+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V306" t="inlineStr">
         <is>
-          <t>2026-10-14T01:19:56+05:30</t>
-        </is>
-      </c>
-      <c r="W306" t="inlineStr"/>
-      <c r="X306" t="inlineStr"/>
+          <t>2026-10-14T01:05:54+05:30</t>
+        </is>
+      </c>
+      <c r="W306" t="inlineStr">
+        <is>
+          <t>Truly Blessed Jewels</t>
+        </is>
+      </c>
+      <c r="X306" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ</t>
+        </is>
+      </c>
       <c r="Y306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z306" t="inlineStr"/>
-      <c r="AA306" t="inlineStr">
-        <is>
-          <t>(203) 335-0000, (203) 335-4444, (919) 702-7000</t>
-        </is>
-      </c>
+      <c r="AA306" t="inlineStr"/>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>https://facebook.com/blackrockgalleries, https://twitter.com/BRGalleries, https://instagram.com/blackrockgalleries</t>
+          <t>https://instagram.com/trulyblessedjewels, https://facebook.com/Truly Blessed Jewels</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Estate Treasures of Greenwich</t>
+          <t>Exquisite Timepieces</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Furniture store</t>
+          <t>Jewelers, Watches</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>(203) 637-4200</t>
+          <t>(239) 227-2932</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>hjantiques@aol.com</t>
-        </is>
-      </c>
-      <c r="F307" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/harriet-roughan-8982a220</t>
-        </is>
-      </c>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t>Harriet Roughan</t>
-        </is>
-      </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
+          <t>team@exquisitetimepieces.com</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr"/>
+      <c r="G307" t="inlineStr"/>
+      <c r="H307" t="inlineStr"/>
       <c r="I307" s="2" t="inlineStr">
         <is>
-          <t>https://www.estatetreasures.com</t>
+          <t>https://www.exquisitetimepieces.com</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>1381 E Putnam Ave, Old Greenwich, CT 06870, United States</t>
-        </is>
-      </c>
-      <c r="K307" t="inlineStr"/>
-      <c r="L307" t="inlineStr"/>
+          <t>4380 Gulf Shore Blvd N, Naples, FL 34103</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Naples</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Greenwich, CT</t>
+          <t>Naples, FL</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O307" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="P307" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="Q307" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Estate+Treasures+of+Greenwich/data=!4m7!3m6!1s0x89c298bd469b9045:0x4341ef96fb235d28!8m2!3d41.0447405!4d-73.5728257!16s%2Fg%2F1tg4xsb0!19sChIJRZCbRr2YwokRKF0j-5bvQUM</t>
+          <t>https://www.yellowpages.com/naples-fl/mip/exquisite-timepieces-14306847</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>2 of 3, custom-design</t>
+          <t>2 of 3, role-email, direct-line, ja, since-1998</t>
         </is>
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="T307" s="2" t="inlineStr">
         <is>
-          <t>https://estatetreasures.com/</t>
-        </is>
-      </c>
-      <c r="U307" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=%22Harriet+Roughan%22+Greenwich+linkedin&amp;hl=en&amp;num=10</t>
-        </is>
-      </c>
+          <t>https://www.exquisitetimepieces.com/</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr"/>
       <c r="V307" t="inlineStr">
         <is>
-          <t>2026-10-14T01:18:54+05:30</t>
+          <t>2026-10-14T01:47:28+05:30</t>
         </is>
       </c>
       <c r="W307" t="inlineStr"/>
@@ -34800,17 +34872,21 @@
         <v>0</v>
       </c>
       <c r="Z307" t="inlineStr"/>
-      <c r="AA307" t="inlineStr"/>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>(239) 262-4545</t>
+        </is>
+      </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>https://facebook.com/EstateTreasuresGreenwich, https://instagram.com/estatetreasuresgreenwich</t>
+          <t>https://facebook.com/pages/Exquisite-Timepieces/138888796144728, https://x.com/TimeExquisite, https://instagram.com/exquisitetimepieces, https://facebook.com/Exquisite-Timepieces-138888796144728, https://twitter.com/TimeExquisite</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Fine Elegant Jewelry</t>
+          <t>Gold Silver Naples</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -34820,17 +34896,17 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Gold dealer</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>(914) 937-2045</t>
+          <t>(239) 591-5999</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>elegantempirejewelers@gmail.com</t>
+          <t>goldsilvercoinsofnaples@gmail.com</t>
         </is>
       </c>
       <c r="F308" t="inlineStr"/>
@@ -34838,48 +34914,40 @@
       <c r="H308" t="inlineStr"/>
       <c r="I308" s="2" t="inlineStr">
         <is>
-          <t>https://eejewelers.com</t>
+          <t>https://www.goldsilvernaples.com</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>27 N Main St, Port Chester, NY 10573</t>
-        </is>
-      </c>
-      <c r="K308" t="inlineStr">
-        <is>
-          <t>Port Chester</t>
-        </is>
-      </c>
-      <c r="L308" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
+          <t>1575 Pine Ridge Rd Ste 20, Naples, FL 34109, United States</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr"/>
+      <c r="L308" t="inlineStr"/>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Greenwich, CT</t>
+          <t>Naples, FL</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O308" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="P308" t="n">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="Q308" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/port-chester-ny/mip/fine-elegant-jewelry-482445004</t>
+          <t>https://www.google.com/maps/place/Gold+Silver+Naples/data=!4m7!3m6!1s0x88db1d7e5a7b7a49:0x324bd0e63a60dfad!8m2!3d26.2126153!4d-81.7867476!16s%2Fg%2F11k9ml4kb0!19sChIJSXp7Wn4d24gRrd9gOubQSzI</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S308" t="inlineStr">
@@ -34889,49 +34957,37 @@
       </c>
       <c r="T308" s="2" t="inlineStr">
         <is>
-          <t>https://eejewelers.com/</t>
+          <t>https://goldsilvernaples.com/</t>
         </is>
       </c>
       <c r="U308" t="inlineStr"/>
       <c r="V308" t="inlineStr">
         <is>
-          <t>2026-10-14T01:48:10+05:30</t>
-        </is>
-      </c>
-      <c r="W308" t="inlineStr">
-        <is>
-          <t>Elegant Empire Jewelers</t>
-        </is>
-      </c>
+          <t>2026-10-14T01:13:03+05:30</t>
+        </is>
+      </c>
+      <c r="W308" t="inlineStr"/>
       <c r="X308" t="inlineStr"/>
       <c r="Y308" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z308" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z308" t="inlineStr"/>
       <c r="AA308" t="inlineStr">
         <is>
-          <t>(914) 305-3385</t>
-        </is>
-      </c>
-      <c r="AB308" t="inlineStr">
-        <is>
-          <t>https://instagram.com/eejewelers/, https://facebook.com/EEJewelers</t>
-        </is>
-      </c>
+          <t>(239) 234-9588</t>
+        </is>
+      </c>
+      <c r="AB308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Steven Fox Jewelry</t>
+          <t>International Diamond Center</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -34941,40 +34997,48 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>(203) 344-5409</t>
+          <t>(239) 342-2550</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>concierge@stevenfoxjewelry.com</t>
+          <t>u003emarketing@shopidc.com</t>
         </is>
       </c>
       <c r="F309" t="inlineStr"/>
-      <c r="G309" t="inlineStr"/>
-      <c r="H309" t="inlineStr"/>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>Keith Leclerc</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I309" s="2" t="inlineStr">
         <is>
-          <t>https://www.stevenfoxjewelry.com</t>
+          <t>https://shopidc.com</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>8 Lewis St, Greenwich, CT 06830, United States</t>
+          <t>8840 Tamiami Trl N, Naples, FL 34108, United States</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>Greenwich</t>
+          <t>Clearwater</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Greenwich, CT</t>
+          <t>Naples, FL</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -34983,19 +35047,19 @@
         </is>
       </c>
       <c r="O309" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P309" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q309" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Steven+Fox+Jewelry/data=!4m7!3m6!1s0x89c298489c931a41:0x67f0cb095f8447aa!8m2!3d41.0287029!4d-73.6255657!16s%2Fg%2F1thn6fp7!19sChIJQRqTnEiYwokRqkeEXwnL8Gc</t>
+          <t>https://www.google.com/maps/place/International+Diamond+Center/data=!4m7!3m6!1s0x88db1f3b506da15f:0xd38690aae0aec00b!8m2!3d26.2479716!4d-81.800361!16s%2Fg%2F11t8h0cjn9!19sChIJX6FtUDsf24gRC8Cu4KqQhtM</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, direct-line, custom-design, since-1983</t>
         </is>
       </c>
       <c r="S309" t="inlineStr">
@@ -35005,56 +35069,56 @@
       </c>
       <c r="T309" s="2" t="inlineStr">
         <is>
-          <t>https://www.stevenfoxjewelry.com/</t>
+          <t>https://shopidc.com/</t>
         </is>
       </c>
       <c r="U309" t="inlineStr"/>
       <c r="V309" t="inlineStr">
         <is>
-          <t>2026-10-14T01:17:44+05:30</t>
+          <t>2026-10-14T01:15:46+05:30</t>
         </is>
       </c>
       <c r="W309" t="inlineStr"/>
       <c r="X309" t="inlineStr"/>
       <c r="Y309" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z309" t="inlineStr"/>
       <c r="AA309" t="inlineStr">
         <is>
-          <t>(203) 629-3303</t>
+          <t>(239) 364-1799, (352) 681-4550, (407) 770-5991, (407) 862-8990, (407) 903-9494, (772) 408-4640, (813) 961-0097, (863) 226-4400, (912) 354-4344, (941) 278-3900</t>
         </is>
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>https://instagram.com/stevenfoxjewelry, https://facebook.com/stevenfoxjewelry</t>
+          <t>https://facebook.com/internationaldiamondcenter, https://instagram.com/internationaldiamondcenter_, https://twitter.com/shopidc</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Triple G Fine Jewelry Inc</t>
+          <t>Mark Loren Design</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>shop=jewelry</t>
+          <t>Jewelers, Jewelry Designers</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>(914) 937-2931</t>
+          <t>(239) 596-5820</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>rakhmin20@icloud.com</t>
+          <t>contact@marklorendesigns.com</t>
         </is>
       </c>
       <c r="F310" t="inlineStr"/>
@@ -35062,48 +35126,44 @@
       <c r="H310" t="inlineStr"/>
       <c r="I310" s="2" t="inlineStr">
         <is>
-          <t>https://triplegjewelry.rafaelsjewelrystore.com</t>
+          <t>https://www.marklorendesigns.com</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>38 South Main Street, Port Chester, NY 10573</t>
+          <t>9118 Strada Pl Ste 8120, Naples, FL 34108</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>Port Chester</t>
+          <t>Naples</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Greenwich, CT</t>
+          <t>Naples, FL</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t>OpenStreetMap</t>
-        </is>
-      </c>
-      <c r="O310" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P310" t="n">
-        <v>26</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr"/>
+      <c r="P310" t="inlineStr"/>
       <c r="Q310" s="2" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/10302134827</t>
+          <t>https://www.yellowpages.com/naples-fl/mip/mark-loren-design-475273503</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, role-email, direct-line, bench, custom-design</t>
         </is>
       </c>
       <c r="S310" t="inlineStr">
@@ -35113,40 +35173,36 @@
       </c>
       <c r="T310" s="2" t="inlineStr">
         <is>
-          <t>https://triplegjewelry.rafaelsjewelrystore.com/</t>
+          <t>https://marklorendesigns.com/</t>
         </is>
       </c>
       <c r="U310" t="inlineStr"/>
       <c r="V310" t="inlineStr">
         <is>
-          <t>2026-10-14T01:19:19+05:30</t>
-        </is>
-      </c>
-      <c r="W310" t="inlineStr">
-        <is>
-          <t>Triple J Fine Jewelry Inc, Triple J Jew Jewelry</t>
-        </is>
-      </c>
+          <t>2026-10-14T01:47:36+05:30</t>
+        </is>
+      </c>
+      <c r="W310" t="inlineStr"/>
       <c r="X310" t="inlineStr"/>
       <c r="Y310" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z310" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z310" t="inlineStr"/>
       <c r="AA310" t="inlineStr">
         <is>
-          <t>(917) 535-4155</t>
-        </is>
-      </c>
-      <c r="AB310" t="inlineStr"/>
+          <t>(239) 482-4664</t>
+        </is>
+      </c>
+      <c r="AB310" t="inlineStr">
+        <is>
+          <t>https://facebook.com/marklorendesigns, https://instagram.com/marklorendesign</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Arlex Jewelry Watches &amp; Clocks</t>
+          <t>Munchel's Fine Jewelry Inc.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -35156,35 +35212,43 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>(561) 641-8162</t>
+          <t>(863) 619-6269</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>info@arlexjewelry.com</t>
+          <t>contact@munchels.com</t>
         </is>
       </c>
       <c r="F311" t="inlineStr"/>
-      <c r="G311" t="inlineStr"/>
-      <c r="H311" t="inlineStr"/>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>William Munchel</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
       <c r="I311" s="2" t="inlineStr">
         <is>
-          <t>https://arlexjewelry.com</t>
+          <t>https://munchels.com</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>808 Lake Ave, Lake Worth Beach, FL 33460, United States</t>
+          <t>3227 S Florida Ave, Lakeland, FL 33803-4550</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>Lake Worth Beach</t>
+          <t>Lakeland</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
@@ -35194,28 +35258,24 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Palm Beach, FL</t>
+          <t>Naples, FL</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O311" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P311" t="n">
-        <v>105</v>
-      </c>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr"/>
+      <c r="P311" t="inlineStr"/>
       <c r="Q311" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Arlex+Jewelry+Watches+%26+Clocks/data=!4m7!3m6!1s0x88d8d834517d5a4d:0x1255d4758f02268f!8m2!3d26.6160147!4d-80.0567684!16s%2Fg%2F1tkc2xb0!19sChIJTVp9UTTY2IgRjyYCj3XUVRI</t>
+          <t>https://www.bbb.org/us/fl/lakeland/profile/jewelry-stores/munchels-fine-jewelry-inc-0733-124113100</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-1987</t>
+          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1991</t>
         </is>
       </c>
       <c r="S311" t="inlineStr">
@@ -35225,64 +35285,56 @@
       </c>
       <c r="T311" s="2" t="inlineStr">
         <is>
-          <t>https://arlexjewelry.com/contact/</t>
+          <t>https://munchels.com/</t>
         </is>
       </c>
       <c r="U311" t="inlineStr"/>
       <c r="V311" t="inlineStr">
         <is>
-          <t>2026-10-14T01:30:48+05:30</t>
-        </is>
-      </c>
-      <c r="W311" t="inlineStr">
-        <is>
-          <t>Arlex Jewelry Watches, Arlex Clocks, Arlex Jewelry &amp; Clocks</t>
-        </is>
-      </c>
+          <t>2026-10-14T06:55:32+05:30</t>
+        </is>
+      </c>
+      <c r="W311" t="inlineStr"/>
       <c r="X311" t="inlineStr"/>
       <c r="Y311" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z311" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z311" t="inlineStr"/>
       <c r="AA311" t="inlineStr">
         <is>
-          <t>(561) 876-7030</t>
+          <t>(863) 619-5206</t>
         </is>
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>https://facebook.com/Arlex-Jewelry-Watches-Clocks-811607869050062, https://twitter.com/arlexclocks, https://instagram.com/arlexjewelry11, https://facebook.com/ArlexJewelry, https://twitter.com/ArlexClocks</t>
+          <t>https://facebook.com/Munchels, https://twitter.com/munchelsjewelry</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Gemstone Gallery</t>
+          <t>Black Rock Galleries</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Designers</t>
+          <t>Estate liquidator</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>(561) 586-8868</t>
+          <t>(203) 900-1110</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>info@mygemstonegallery.com</t>
+          <t>april@blackrockgalleries.com</t>
         </is>
       </c>
       <c r="F312" t="inlineStr"/>
@@ -35290,32 +35342,48 @@
       <c r="H312" t="inlineStr"/>
       <c r="I312" s="2" t="inlineStr">
         <is>
-          <t>https://www.mygemstonegallery.com</t>
-        </is>
-      </c>
-      <c r="J312" t="inlineStr"/>
-      <c r="K312" t="inlineStr"/>
-      <c r="L312" t="inlineStr"/>
+          <t>https://www.blackrockgalleries.com</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>179 Hamilton Ave, Greenwich, CT 06830, United States</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Cary</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Palm Beach, FL</t>
+          <t>Greenwich, CT</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O312" t="inlineStr"/>
-      <c r="P312" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O312" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P312" t="n">
+        <v>25</v>
+      </c>
       <c r="Q312" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/nationwide/mip/gemstone-gallery-451204537</t>
+          <t>https://www.google.com/maps/place/Black+Rock+Galleries/data=!4m7!3m6!1s0x89c299cdad7d8901:0x806db5b713ec68d7!8m2!3d41.0179193!4d-73.6391571!16s%2Fg%2F11ckvlk1pv!19sChIJAYl9rc2ZwokR12jsE7e1bYA</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, direct-line, gia</t>
         </is>
       </c>
       <c r="S312" t="inlineStr">
@@ -35325,13 +35393,13 @@
       </c>
       <c r="T312" s="2" t="inlineStr">
         <is>
-          <t>https://www.mygemstonegallery.com/</t>
+          <t>https://www.blackrockgalleries.com/contact</t>
         </is>
       </c>
       <c r="U312" t="inlineStr"/>
       <c r="V312" t="inlineStr">
         <is>
-          <t>2026-10-14T01:50:22+05:30</t>
+          <t>2026-10-14T01:19:56+05:30</t>
         </is>
       </c>
       <c r="W312" t="inlineStr"/>
@@ -35339,74 +35407,74 @@
       <c r="Y312" t="n">
         <v>0</v>
       </c>
-      <c r="Z312" t="inlineStr">
-        <is>
-          <t>no-address</t>
-        </is>
-      </c>
+      <c r="Z312" t="inlineStr"/>
       <c r="AA312" t="inlineStr">
         <is>
-          <t>(917) 406-0779</t>
+          <t>(203) 335-0000, (203) 335-4444, (919) 702-7000</t>
         </is>
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>https://facebook.com/SuzanneHDeBow, https://twitter.com/GemstoneGallery, https://instagram.com/mygemstone_gallery</t>
+          <t>https://facebook.com/blackrockgalleries, https://twitter.com/BRGalleries, https://instagram.com/blackrockgalleries</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Hamilton Jewelers</t>
+          <t>Estate Treasures of Greenwich</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Jeweler</t>
+          <t>Furniture store</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>(561) 659-6788</t>
+          <t>(203) 637-4200</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>emartano@hamiltonjewelers.com</t>
-        </is>
-      </c>
-      <c r="F313" t="inlineStr"/>
-      <c r="G313" t="inlineStr"/>
-      <c r="H313" t="inlineStr"/>
+          <t>hjantiques@aol.com</t>
+        </is>
+      </c>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/harriet-roughan-8982a220</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>Harriet Roughan</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I313" s="2" t="inlineStr">
         <is>
-          <t>https://hamiltonjewelers.com</t>
+          <t>https://www.estatetreasures.com</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>215 Worth Ave, Palm Beach, FL 33480, United States</t>
-        </is>
-      </c>
-      <c r="K313" t="inlineStr">
-        <is>
-          <t>Palm Beach Gardens</t>
-        </is>
-      </c>
-      <c r="L313" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
+          <t>1381 E Putnam Ave, Old Greenwich, CT 06870, United States</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr"/>
+      <c r="L313" t="inlineStr"/>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Palm Beach, FL</t>
+          <t>Greenwich, CT</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -35415,63 +35483,63 @@
         </is>
       </c>
       <c r="O313" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="P313" t="n">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="Q313" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Hamilton+Jewelers/data=!4m7!3m6!1s0x88d8d6ec71416949:0x1f20ced2ff0489d1!8m2!3d26.7009363!4d-80.0371549!16s%2Fg%2F1tfz0xfv!19sChIJSWlBcezW2IgR0YkE_9LOIB8</t>
+          <t>https://www.google.com/maps/place/Estate+Treasures+of+Greenwich/data=!4m7!3m6!1s0x89c298bd469b9045:0x4341ef96fb235d28!8m2!3d41.0447405!4d-73.5728257!16s%2Fg%2F1tg4xsb0!19sChIJRZCbRr2YwokRKF0j-5bvQUM</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design, since-1912</t>
+          <t>2 of 3, custom-design</t>
         </is>
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T313" s="2" t="inlineStr">
         <is>
-          <t>https://hamiltonjewelers.com/</t>
-        </is>
-      </c>
-      <c r="U313" t="inlineStr"/>
+          <t>https://estatetreasures.com/</t>
+        </is>
+      </c>
+      <c r="U313" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Harriet+Roughan%22+Greenwich+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V313" t="inlineStr">
         <is>
-          <t>2026-10-14T01:25:01+05:30</t>
+          <t>2026-10-14T01:18:54+05:30</t>
         </is>
       </c>
       <c r="W313" t="inlineStr"/>
       <c r="X313" t="inlineStr"/>
       <c r="Y313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z313" t="inlineStr"/>
-      <c r="AA313" t="inlineStr">
-        <is>
-          <t>(609) 375-8003</t>
-        </is>
-      </c>
+      <c r="AA313" t="inlineStr"/>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>https://instagram.com/hamiltonjewelers, https://facebook.com/HamiltonJeweler</t>
+          <t>https://facebook.com/EstateTreasuresGreenwich, https://instagram.com/estatetreasuresgreenwich</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Raymond Lee Jewelers</t>
+          <t>Fine Elegant Jewelry</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -35481,12 +35549,12 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>(561) 622-7744</t>
+          <t>(914) 937-2045</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>info@raymondleejewelers.net</t>
+          <t>elegantempirejewelers@gmail.com</t>
         </is>
       </c>
       <c r="F314" t="inlineStr"/>
@@ -35494,27 +35562,27 @@
       <c r="H314" t="inlineStr"/>
       <c r="I314" s="2" t="inlineStr">
         <is>
-          <t>https://www.raymondleejewelers.net</t>
+          <t>https://eejewelers.com</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>500 Village Square Xing, Palm Beach Gardens, FL 33410</t>
+          <t>27 N Main St, Port Chester, NY 10573</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t>Palm Beach Gardens</t>
+          <t>Port Chester</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Palm Beach, FL</t>
+          <t>Greenwich, CT</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -35522,16 +35590,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O314" t="inlineStr"/>
-      <c r="P314" t="inlineStr"/>
+      <c r="O314" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P314" t="n">
+        <v>115</v>
+      </c>
       <c r="Q314" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/palm-beach-gardens-fl/mip/raymond-lee-jewelers-3693798</t>
+          <t>https://www.yellowpages.com/port-chester-ny/mip/fine-elegant-jewelry-482445004</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1983</t>
+          <t>2 of 3, direct-line, gia, custom-design</t>
         </is>
       </c>
       <c r="S314" t="inlineStr">
@@ -35541,19 +35613,23 @@
       </c>
       <c r="T314" s="2" t="inlineStr">
         <is>
-          <t>https://raymondleejewelers.net/pages/contact</t>
+          <t>https://eejewelers.com/</t>
         </is>
       </c>
       <c r="U314" t="inlineStr"/>
       <c r="V314" t="inlineStr">
         <is>
-          <t>2026-10-14T01:50:37+05:30</t>
-        </is>
-      </c>
-      <c r="W314" t="inlineStr"/>
+          <t>2026-10-14T01:48:10+05:30</t>
+        </is>
+      </c>
+      <c r="W314" t="inlineStr">
+        <is>
+          <t>Elegant Empire Jewelers</t>
+        </is>
+      </c>
       <c r="X314" t="inlineStr"/>
       <c r="Y314" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z314" t="inlineStr">
         <is>
@@ -35562,35 +35638,39 @@
       </c>
       <c r="AA314" t="inlineStr">
         <is>
-          <t>(561) 750-7808</t>
-        </is>
-      </c>
-      <c r="AB314" t="inlineStr"/>
+          <t>(914) 305-3385</t>
+        </is>
+      </c>
+      <c r="AB314" t="inlineStr">
+        <is>
+          <t>https://instagram.com/eejewelers/, https://facebook.com/EEJewelers</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Signature Diamonds</t>
+          <t>Steven Fox Jewelry</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Jewelers, Diamonds</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>(561) 686-5730</t>
+          <t>(203) 344-5409</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>signaturebuyers@yahoo.com</t>
+          <t>concierge@stevenfoxjewelry.com</t>
         </is>
       </c>
       <c r="F315" t="inlineStr"/>
@@ -35598,44 +35678,48 @@
       <c r="H315" t="inlineStr"/>
       <c r="I315" s="2" t="inlineStr">
         <is>
-          <t>https://sellyourdiamondsflorida.com</t>
+          <t>https://www.stevenfoxjewelry.com</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>2200 N Florida Mango Rd, West Palm Beach, FL 33409</t>
+          <t>8 Lewis St, Greenwich, CT 06830, United States</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>West Palm Beach</t>
+          <t>Greenwich</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Palm Beach, FL</t>
+          <t>Greenwich, CT</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O315" t="inlineStr"/>
-      <c r="P315" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O315" t="n">
+        <v>5</v>
+      </c>
+      <c r="P315" t="n">
+        <v>277</v>
+      </c>
       <c r="Q315" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/west-palm-beach-fl/mip/signature-diamonds-538406637</t>
+          <t>https://www.google.com/maps/place/Steven+Fox+Jewelry/data=!4m7!3m6!1s0x89c298489c931a41:0x67f0cb095f8447aa!8m2!3d41.0287029!4d-73.6255657!16s%2Fg%2F1thn6fp7!19sChIJQRqTnEiYwokRqkeEXwnL8Gc</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design, since-1945</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S315" t="inlineStr">
@@ -35645,36 +35729,36 @@
       </c>
       <c r="T315" s="2" t="inlineStr">
         <is>
-          <t>https://sellyourdiamondsflorida.com/</t>
+          <t>https://www.stevenfoxjewelry.com/</t>
         </is>
       </c>
       <c r="U315" t="inlineStr"/>
       <c r="V315" t="inlineStr">
         <is>
-          <t>2026-10-14T01:50:22+05:30</t>
+          <t>2026-10-14T01:17:44+05:30</t>
         </is>
       </c>
       <c r="W315" t="inlineStr"/>
       <c r="X315" t="inlineStr"/>
       <c r="Y315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z315" t="inlineStr"/>
       <c r="AA315" t="inlineStr">
         <is>
-          <t>(772) 562-6893</t>
+          <t>(203) 629-3303</t>
         </is>
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>https://facebook.com/pages/Signature-Estate-Diamond-Buyers/699915383378286, https://twitter.com/signaturebuyer</t>
+          <t>https://instagram.com/stevenfoxjewelry, https://facebook.com/stevenfoxjewelry</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>WPBWatchCo</t>
+          <t>Triple G Fine Jewelry Inc</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -35684,117 +35768,109 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Watch store</t>
+          <t>shop=jewelry</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>(561) 220-9107</t>
+          <t>(914) 937-2931</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>arinaldi@wpbwatchco.com</t>
-        </is>
-      </c>
-      <c r="F316" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/anthony-rinaldi-0293451b</t>
-        </is>
-      </c>
-      <c r="G316" t="inlineStr">
-        <is>
-          <t>Anthony Rinaldi</t>
-        </is>
-      </c>
-      <c r="H316" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
+          <t>rakhmin20@icloud.com</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr"/>
+      <c r="G316" t="inlineStr"/>
+      <c r="H316" t="inlineStr"/>
       <c r="I316" s="2" t="inlineStr">
         <is>
-          <t>https://www.wpbwatchco.com</t>
+          <t>https://triplegjewelry.rafaelsjewelrystore.com</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>1601 Forum Pl #1010, West Palm Beach, FL 33401, United States</t>
+          <t>38 South Main Street, Port Chester, NY 10573</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>West Palm Beach</t>
+          <t>Port Chester</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Palm Beach, FL</t>
+          <t>Greenwich, CT</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>OpenStreetMap</t>
         </is>
       </c>
       <c r="O316" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="P316" t="n">
-        <v>622</v>
+        <v>26</v>
       </c>
       <c r="Q316" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/WPBWatchCo/data=!4m7!3m6!1s0x88d91e304542d111:0xdd417b5f344332dc!8m2!3d26.7271055!4d-80.0794774!16s%2Fg%2F11dymb1krc!19sChIJEdFCRTAe2YgR3DJDNF97Qd0</t>
+          <t>https://www.openstreetmap.org/node/10302134827</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>2 of 3, since-2015</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="T316" s="2" t="inlineStr">
         <is>
-          <t>https://wpbwatchco.com/</t>
-        </is>
-      </c>
-      <c r="U316" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=%22Anthony+Rinaldi%22+Palm+Beach+linkedin&amp;hl=en&amp;num=10</t>
-        </is>
-      </c>
+          <t>https://triplegjewelry.rafaelsjewelrystore.com/</t>
+        </is>
+      </c>
+      <c r="U316" t="inlineStr"/>
       <c r="V316" t="inlineStr">
         <is>
-          <t>2026-10-14T01:27:35+05:30</t>
-        </is>
-      </c>
-      <c r="W316" t="inlineStr"/>
+          <t>2026-10-14T01:19:19+05:30</t>
+        </is>
+      </c>
+      <c r="W316" t="inlineStr">
+        <is>
+          <t>Triple J Fine Jewelry Inc, Triple J Jew Jewelry</t>
+        </is>
+      </c>
       <c r="X316" t="inlineStr"/>
       <c r="Y316" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z316" t="inlineStr"/>
-      <c r="AA316" t="inlineStr"/>
-      <c r="AB316" t="inlineStr">
-        <is>
-          <t>https://instagram.com/wpb_watch_co, https://facebook.com/anthony.rinaldi.7370</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="Z316" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>(917) 535-4155</t>
+        </is>
+      </c>
+      <c r="AB316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>YAFA Palm Beach</t>
+          <t>Arlex Jewelry Watches &amp; Clocks</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -35809,12 +35885,12 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>(561) 331-8611</t>
+          <t>(561) 641-8162</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>inquire@yafajewelry.com</t>
+          <t>info@arlexjewelry.com</t>
         </is>
       </c>
       <c r="F317" t="inlineStr"/>
@@ -35822,17 +35898,17 @@
       <c r="H317" t="inlineStr"/>
       <c r="I317" s="2" t="inlineStr">
         <is>
-          <t>https://yafasignedjewels.com</t>
+          <t>https://arlexjewelry.com</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>234 Worth Ave, Palm Beach, FL 33480, United States</t>
+          <t>808 Lake Ave, Lake Worth Beach, FL 33460, United States</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>Palm Beach</t>
+          <t>Lake Worth Beach</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
@@ -35851,19 +35927,19 @@
         </is>
       </c>
       <c r="O317" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="P317" t="n">
-        <v>9</v>
+        <v>105</v>
       </c>
       <c r="Q317" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/YAFA+Palm+Beach/data=!4m7!3m6!1s0x89c258fef868bda1:0x84b1b16f5ab524a9!8m2!3d26.7006755!4d-80.0378935!16s%2Fg%2F1td4l0sf!19sChIJob1o-P5YwokRqSS1Wm-xsYQ</t>
+          <t>https://www.google.com/maps/place/Arlex+Jewelry+Watches+%26+Clocks/data=!4m7!3m6!1s0x88d8d834517d5a4d:0x1255d4758f02268f!8m2!3d26.6160147!4d-80.0567684!16s%2Fg%2F1tkc2xb0!19sChIJTVp9UTTY2IgRjyYCj3XUVRI</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, since-1985</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-1987</t>
         </is>
       </c>
       <c r="S317" t="inlineStr">
@@ -35873,40 +35949,44 @@
       </c>
       <c r="T317" s="2" t="inlineStr">
         <is>
-          <t>https://yafasignedjewels.com/pages/contact</t>
+          <t>https://arlexjewelry.com/contact/</t>
         </is>
       </c>
       <c r="U317" t="inlineStr"/>
       <c r="V317" t="inlineStr">
         <is>
-          <t>2026-10-14T01:26:21+05:30</t>
+          <t>2026-10-14T01:30:48+05:30</t>
         </is>
       </c>
       <c r="W317" t="inlineStr">
         <is>
-          <t>Yafa Signed Jewels</t>
+          <t>Arlex Jewelry Watches, Arlex Clocks, Arlex Jewelry &amp; Clocks</t>
         </is>
       </c>
       <c r="X317" t="inlineStr"/>
       <c r="Y317" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z317" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="Z317" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA317" t="inlineStr">
         <is>
-          <t>(212) 719-9828, (516) 331-8611</t>
+          <t>(561) 876-7030</t>
         </is>
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>https://facebook.com/YafaSignedJewels, https://instagram.com/yafasignedjewels</t>
+          <t>https://facebook.com/Arlex-Jewelry-Watches-Clocks-811607869050062, https://twitter.com/arlexclocks, https://instagram.com/arlexjewelry11, https://facebook.com/ArlexJewelry, https://twitter.com/ArlexClocks</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Gold Gods</t>
+          <t>Gemstone Gallery</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -35916,17 +35996,17 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Jewelry Designers</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>(816) 721-9850</t>
+          <t>(561) 586-8868</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>support@thegoldgods.com</t>
+          <t>info@mygemstonegallery.com</t>
         </is>
       </c>
       <c r="F318" t="inlineStr"/>
@@ -35934,27 +36014,15 @@
       <c r="H318" t="inlineStr"/>
       <c r="I318" s="2" t="inlineStr">
         <is>
-          <t>https://thegoldgods.com</t>
-        </is>
-      </c>
-      <c r="J318" t="inlineStr">
-        <is>
-          <t>450 N Fairfax Ave, Los Angeles, CA 90036</t>
-        </is>
-      </c>
-      <c r="K318" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="L318" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
+          <t>https://www.mygemstonegallery.com</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr"/>
+      <c r="K318" t="inlineStr"/>
+      <c r="L318" t="inlineStr"/>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Beverly Hills, CA</t>
+          <t>Palm Beach, FL</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -35966,7 +36034,7 @@
       <c r="P318" t="inlineStr"/>
       <c r="Q318" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/los-angeles-ca/mip/gold-gods-548160699</t>
+          <t>https://www.yellowpages.com/nationwide/mip/gemstone-gallery-451204537</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
@@ -35981,13 +36049,13 @@
       </c>
       <c r="T318" s="2" t="inlineStr">
         <is>
-          <t>https://thegoldgods.com/pages/contact</t>
+          <t>https://www.mygemstonegallery.com/</t>
         </is>
       </c>
       <c r="U318" t="inlineStr"/>
       <c r="V318" t="inlineStr">
         <is>
-          <t>2026-10-14T01:52:07+05:30</t>
+          <t>2026-10-14T01:50:22+05:30</t>
         </is>
       </c>
       <c r="W318" t="inlineStr"/>
@@ -35995,18 +36063,26 @@
       <c r="Y318" t="n">
         <v>0</v>
       </c>
-      <c r="Z318" t="inlineStr"/>
+      <c r="Z318" t="inlineStr">
+        <is>
+          <t>no-address</t>
+        </is>
+      </c>
       <c r="AA318" t="inlineStr">
         <is>
-          <t>(816) 323-6447</t>
-        </is>
-      </c>
-      <c r="AB318" t="inlineStr"/>
+          <t>(917) 406-0779</t>
+        </is>
+      </c>
+      <c r="AB318" t="inlineStr">
+        <is>
+          <t>https://facebook.com/SuzanneHDeBow, https://twitter.com/GemstoneGallery, https://instagram.com/mygemstone_gallery</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Golden State</t>
+          <t>Hamilton Jewelers</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -36016,17 +36092,17 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers</t>
+          <t>Jeweler</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>(213) 629-2130</t>
+          <t>(561) 659-6788</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>sales@goldenstatejewelry.com</t>
+          <t>emartano@hamiltonjewelers.com</t>
         </is>
       </c>
       <c r="F319" t="inlineStr"/>
@@ -36034,48 +36110,48 @@
       <c r="H319" t="inlineStr"/>
       <c r="I319" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldenstatejewelry.com</t>
+          <t>https://hamiltonjewelers.com</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>550 S Hill St Ste 825, Los Angeles, CA 90013</t>
+          <t>215 Worth Ave, Palm Beach, FL 33480, United States</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Palm Beach Gardens</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Beverly Hills, CA</t>
+          <t>Palm Beach, FL</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O319" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P319" t="n">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="Q319" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/los-angeles-ca/mip/golden-state-467565356</t>
+          <t>https://www.google.com/maps/place/Hamilton+Jewelers/data=!4m7!3m6!1s0x88d8d6ec71416949:0x1f20ced2ff0489d1!8m2!3d26.7009363!4d-80.0371549!16s%2Fg%2F1tfz0xfv!19sChIJSWlBcezW2IgR0YkE_9LOIB8</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, bench, custom-design, since-1978</t>
+          <t>2 of 3, direct-line, gia, custom-design, since-1912</t>
         </is>
       </c>
       <c r="S319" t="inlineStr">
@@ -36085,49 +36161,41 @@
       </c>
       <c r="T319" s="2" t="inlineStr">
         <is>
-          <t>https://goldenstatejewelry.com/</t>
+          <t>https://hamiltonjewelers.com/</t>
         </is>
       </c>
       <c r="U319" t="inlineStr"/>
       <c r="V319" t="inlineStr">
         <is>
-          <t>2026-10-14T01:52:45+05:30</t>
-        </is>
-      </c>
-      <c r="W319" t="inlineStr">
-        <is>
-          <t>Golden Star Jewelry</t>
-        </is>
-      </c>
-      <c r="X319" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA</t>
-        </is>
-      </c>
+          <t>2026-10-14T01:25:01+05:30</t>
+        </is>
+      </c>
+      <c r="W319" t="inlineStr"/>
+      <c r="X319" t="inlineStr"/>
       <c r="Y319" t="n">
         <v>1</v>
       </c>
       <c r="Z319" t="inlineStr"/>
       <c r="AA319" t="inlineStr">
         <is>
-          <t>(213) 627-9677</t>
+          <t>(609) 375-8003</t>
         </is>
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>https://instagram.com/goldenstatejewelryla</t>
+          <t>https://instagram.com/hamiltonjewelers, https://facebook.com/HamiltonJeweler</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Hoorsenbuhs</t>
+          <t>Raymond Lee Jewelers</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -36137,12 +36205,12 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>(888) 692-2997</t>
+          <t>(561) 622-7744</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>info@hoorsenbuhs.com</t>
+          <t>info@raymondleejewelers.net</t>
         </is>
       </c>
       <c r="F320" t="inlineStr"/>
@@ -36150,27 +36218,27 @@
       <c r="H320" t="inlineStr"/>
       <c r="I320" s="2" t="inlineStr">
         <is>
-          <t>https://hoorsenbuhs.com</t>
+          <t>https://www.raymondleejewelers.net</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>2217 Main St, Santa Monica, CA 90405</t>
+          <t>500 Village Square Xing, Palm Beach Gardens, FL 33410</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Palm Beach Gardens</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Beverly Hills, CA</t>
+          <t>Palm Beach, FL</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -36182,12 +36250,12 @@
       <c r="P320" t="inlineStr"/>
       <c r="Q320" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/santa-monica-ca/mip/hoorsenbuhs-551622669</t>
+          <t>https://www.yellowpages.com/palm-beach-gardens-fl/mip/raymond-lee-jewelers-3693798</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line</t>
+          <t>2 of 3, role-email, direct-line, gia, custom-design, since-1983</t>
         </is>
       </c>
       <c r="S320" t="inlineStr">
@@ -36197,40 +36265,36 @@
       </c>
       <c r="T320" s="2" t="inlineStr">
         <is>
-          <t>https://hoorsenbuhs.com/</t>
+          <t>https://raymondleejewelers.net/pages/contact</t>
         </is>
       </c>
       <c r="U320" t="inlineStr"/>
       <c r="V320" t="inlineStr">
         <is>
-          <t>2026-10-14T01:53:36+05:30</t>
+          <t>2026-10-14T01:50:37+05:30</t>
         </is>
       </c>
       <c r="W320" t="inlineStr"/>
       <c r="X320" t="inlineStr"/>
       <c r="Y320" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z320" t="inlineStr">
         <is>
-          <t>toll-free</t>
+          <t>chain</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
         <is>
-          <t>(917) 206-9333</t>
-        </is>
-      </c>
-      <c r="AB320" t="inlineStr">
-        <is>
-          <t>https://instagram.com/hoorsenbuhs</t>
-        </is>
-      </c>
+          <t>(561) 750-7808</t>
+        </is>
+      </c>
+      <c r="AB320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Jennifer Fisher Jewelry</t>
+          <t>Signature Diamonds</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -36240,17 +36304,17 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers, Diamonds</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>(424) 374-5303</t>
+          <t>(561) 686-5730</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>la@jenniferfisher.com</t>
+          <t>signaturebuyers@yahoo.com</t>
         </is>
       </c>
       <c r="F321" t="inlineStr"/>
@@ -36258,40 +36322,44 @@
       <c r="H321" t="inlineStr"/>
       <c r="I321" s="2" t="inlineStr">
         <is>
-          <t>https://jenniferfisher.com</t>
+          <t>https://sellyourdiamondsflorida.com</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>363 N Beverly Dr, Beverly Hills, CA 90210, United States</t>
-        </is>
-      </c>
-      <c r="K321" t="inlineStr"/>
-      <c r="L321" t="inlineStr"/>
+          <t>2200 N Florida Mango Rd, West Palm Beach, FL 33409</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>West Palm Beach</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Beverly Hills, CA</t>
+          <t>Palm Beach, FL</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O321" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P321" t="n">
-        <v>44</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr"/>
+      <c r="P321" t="inlineStr"/>
       <c r="Q321" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Jennifer+Fisher+Jewelry/data=!4m7!3m6!1s0x80c2bdd6ed684985:0xb8fbea746e91ad05!8m2!3d34.0695438!4d-118.4019104!16s%2Fg%2F11n12hvwn5!19sChIJhUlo7da9woARBa2RbnTq-7g</t>
+          <t>https://www.yellowpages.com/west-palm-beach-fl/mip/signature-diamonds-538406637</t>
         </is>
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, direct-line, gia, custom-design, since-1945</t>
         </is>
       </c>
       <c r="S321" t="inlineStr">
@@ -36301,13 +36369,13 @@
       </c>
       <c r="T321" s="2" t="inlineStr">
         <is>
-          <t>https://jenniferfisher.com/pages/stockists</t>
+          <t>https://sellyourdiamondsflorida.com/</t>
         </is>
       </c>
       <c r="U321" t="inlineStr"/>
       <c r="V321" t="inlineStr">
         <is>
-          <t>2026-10-14T01:40:50+05:30</t>
+          <t>2026-10-14T01:50:22+05:30</t>
         </is>
       </c>
       <c r="W321" t="inlineStr"/>
@@ -36318,19 +36386,19 @@
       <c r="Z321" t="inlineStr"/>
       <c r="AA321" t="inlineStr">
         <is>
-          <t>(646) 366-9375</t>
+          <t>(772) 562-6893</t>
         </is>
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>https://instagram.com/jenniferfisherjewelry/, https://facebook.com/JenniferFisherJewelry, https://instagram.com/jenniferfisherjewelry</t>
+          <t>https://facebook.com/pages/Signature-Estate-Diamond-Buyers/699915383378286, https://twitter.com/signaturebuyer</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Jewelry &amp; Watch Buyers - Beverly Hills</t>
+          <t>WPBWatchCo</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -36340,37 +36408,57 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Jewelry buyer</t>
+          <t>Watch store</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>(310) 697-8177</t>
+          <t>(561) 220-9107</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>info@watchbuyers.us</t>
-        </is>
-      </c>
-      <c r="F322" t="inlineStr"/>
-      <c r="G322" t="inlineStr"/>
-      <c r="H322" t="inlineStr"/>
+          <t>arinaldi@wpbwatchco.com</t>
+        </is>
+      </c>
+      <c r="F322" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anthony-rinaldi-0293451b</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>Anthony Rinaldi</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="I322" s="2" t="inlineStr">
         <is>
-          <t>https://watchbuyers.us</t>
+          <t>https://www.wpbwatchco.com</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>468 N Camden Dr #205, Beverly Hills, CA 90210, United States</t>
-        </is>
-      </c>
-      <c r="K322" t="inlineStr"/>
-      <c r="L322" t="inlineStr"/>
+          <t>1601 Forum Pl #1010, West Palm Beach, FL 33401, United States</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>West Palm Beach</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Beverly Hills, CA</t>
+          <t>Palm Beach, FL</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -36379,59 +36467,63 @@
         </is>
       </c>
       <c r="O322" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P322" t="n">
-        <v>3</v>
+        <v>622</v>
       </c>
       <c r="Q322" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Jewelry+%26+Watch+Buyers+-+Beverly+Hills/data=!4m7!3m6!1s0x80c2bdbde9baacdb:0xbbce1c74141b63ce!8m2!3d34.0698858!4d-118.404944!16s%2Fg%2F11xt1px272!19sChIJ26y66b29woARzmMbFHQczrs</t>
+          <t>https://www.google.com/maps/place/WPBWatchCo/data=!4m7!3m6!1s0x88d91e304542d111:0xdd417b5f344332dc!8m2!3d26.7271055!4d-80.0794774!16s%2Fg%2F11dymb1krc!19sChIJEdFCRTAe2YgR3DJDNF97Qd0</t>
         </is>
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line</t>
+          <t>2 of 3, since-2015</t>
         </is>
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="T322" s="2" t="inlineStr">
         <is>
-          <t>https://watchbuyers.us/</t>
-        </is>
-      </c>
-      <c r="U322" t="inlineStr"/>
+          <t>https://wpbwatchco.com/</t>
+        </is>
+      </c>
+      <c r="U322" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%22Anthony+Rinaldi%22+Palm+Beach+linkedin&amp;hl=en&amp;num=10</t>
+        </is>
+      </c>
       <c r="V322" t="inlineStr">
         <is>
-          <t>2026-10-14T01:40:58+05:30</t>
+          <t>2026-10-14T01:27:35+05:30</t>
         </is>
       </c>
       <c r="W322" t="inlineStr"/>
       <c r="X322" t="inlineStr"/>
       <c r="Y322" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z322" t="inlineStr"/>
-      <c r="AA322" t="inlineStr">
-        <is>
-          <t>(305) 989-9099, (646) 413-7757</t>
-        </is>
-      </c>
-      <c r="AB322" t="inlineStr"/>
+      <c r="AA322" t="inlineStr"/>
+      <c r="AB322" t="inlineStr">
+        <is>
+          <t>https://instagram.com/wpb_watch_co, https://facebook.com/anthony.rinaldi.7370</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Jewels Aficionado Beverly Hills</t>
+          <t>YAFA Palm Beach</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -36439,10 +36531,14 @@
           <t>Jewelry store</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>(561) 331-8611</t>
+        </is>
+      </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>sales@jewelsaficionado.com</t>
+          <t>inquire@yafajewelry.com</t>
         </is>
       </c>
       <c r="F323" t="inlineStr"/>
@@ -36450,19 +36546,27 @@
       <c r="H323" t="inlineStr"/>
       <c r="I323" s="2" t="inlineStr">
         <is>
-          <t>https://jewelsaficionado.com</t>
+          <t>https://yafasignedjewels.com</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>9850 Wilshire Blvd, Beverly Hills, CA 90210, United States</t>
-        </is>
-      </c>
-      <c r="K323" t="inlineStr"/>
-      <c r="L323" t="inlineStr"/>
+          <t>234 Worth Ave, Palm Beach, FL 33480, United States</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Palm Beach</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Beverly Hills, CA</t>
+          <t>Palm Beach, FL</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -36470,16 +36574,20 @@
           <t>Google Maps</t>
         </is>
       </c>
-      <c r="O323" t="inlineStr"/>
-      <c r="P323" t="inlineStr"/>
+      <c r="O323" t="n">
+        <v>5</v>
+      </c>
+      <c r="P323" t="n">
+        <v>9</v>
+      </c>
       <c r="Q323" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Jewels+Aficionado+Beverly+Hills/data=!4m7!3m6!1s0x80c2bb445801322d:0x4ee3ff18cd9446bc!8m2!3d34.0666649!4d-118.4114543!16s%2Fg%2F11z2xf_27b!19sChIJLTIBWES7woARvEaUzRj_404</t>
+          <t>https://www.google.com/maps/place/YAFA+Palm+Beach/data=!4m7!3m6!1s0x89c258fef868bda1:0x84b1b16f5ab524a9!8m2!3d26.7006755!4d-80.0378935!16s%2Fg%2F1td4l0sf!19sChIJob1o-P5YwokRqSS1Wm-xsYQ</t>
         </is>
       </c>
       <c r="R323" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, direct-line, since-1985</t>
         </is>
       </c>
       <c r="S323" t="inlineStr">
@@ -36489,56 +36597,60 @@
       </c>
       <c r="T323" s="2" t="inlineStr">
         <is>
-          <t>https://jewelsaficionado.com/</t>
+          <t>https://yafasignedjewels.com/pages/contact</t>
         </is>
       </c>
       <c r="U323" t="inlineStr"/>
       <c r="V323" t="inlineStr">
         <is>
-          <t>2026-10-14T01:42:22+05:30</t>
-        </is>
-      </c>
-      <c r="W323" t="inlineStr"/>
+          <t>2026-10-14T01:26:21+05:30</t>
+        </is>
+      </c>
+      <c r="W323" t="inlineStr">
+        <is>
+          <t>Yafa Signed Jewels</t>
+        </is>
+      </c>
       <c r="X323" t="inlineStr"/>
       <c r="Y323" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z323" t="inlineStr"/>
       <c r="AA323" t="inlineStr">
         <is>
-          <t>(212) 422-2600</t>
+          <t>(212) 719-9828, (516) 331-8611</t>
         </is>
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>https://instagram.com/jewelsaficionado</t>
+          <t>https://facebook.com/YafaSignedJewels, https://instagram.com/yafasignedjewels</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Logan Hollowell Jewelry</t>
+          <t>Gold Gods</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>(323) 248-9685</t>
+          <t>(816) 721-9850</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>info@loganhollowell.com</t>
+          <t>support@thegoldgods.com</t>
         </is>
       </c>
       <c r="F324" t="inlineStr"/>
@@ -36546,16 +36658,24 @@
       <c r="H324" t="inlineStr"/>
       <c r="I324" s="2" t="inlineStr">
         <is>
-          <t>https://www.loganhollowell.com</t>
+          <t>https://thegoldgods.com</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>411 N Canon Dr, Beverly Hills, CA 90210, United States</t>
-        </is>
-      </c>
-      <c r="K324" t="inlineStr"/>
-      <c r="L324" t="inlineStr"/>
+          <t>450 N Fairfax Ave, Los Angeles, CA 90036</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
       <c r="M324" t="inlineStr">
         <is>
           <t>Beverly Hills, CA</t>
@@ -36563,23 +36683,19 @@
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O324" t="n">
-        <v>5</v>
-      </c>
-      <c r="P324" t="n">
-        <v>1</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr"/>
+      <c r="P324" t="inlineStr"/>
       <c r="Q324" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Logan+Hollowell+Jewelry/data=!4m7!3m6!1s0x80c2bd39cbc0865f:0x202c691c8504a898!8m2!3d34.07073!4d-118.4012945!16s%2Fg%2F11njp9zjzq!19sChIJX4bAyzm9woARmKgEhRxpLCA</t>
+          <t>https://www.yellowpages.com/los-angeles-ca/mip/gold-gods-548160699</t>
         </is>
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-2014</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S324" t="inlineStr">
@@ -36589,13 +36705,13 @@
       </c>
       <c r="T324" s="2" t="inlineStr">
         <is>
-          <t>https://loganhollowell.com/</t>
+          <t>https://thegoldgods.com/pages/contact</t>
         </is>
       </c>
       <c r="U324" t="inlineStr"/>
       <c r="V324" t="inlineStr">
         <is>
-          <t>2026-10-14T01:41:31+05:30</t>
+          <t>2026-10-14T01:52:07+05:30</t>
         </is>
       </c>
       <c r="W324" t="inlineStr"/>
@@ -36606,39 +36722,35 @@
       <c r="Z324" t="inlineStr"/>
       <c r="AA324" t="inlineStr">
         <is>
-          <t>(323) 853-7844</t>
-        </is>
-      </c>
-      <c r="AB324" t="inlineStr">
-        <is>
-          <t>https://instagram.com/loganhollowell, https://facebook.com/loganhollowelljewelry</t>
-        </is>
-      </c>
+          <t>(816) 323-6447</t>
+        </is>
+      </c>
+      <c r="AB324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Majestic Jewelry</t>
+          <t>Golden State</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>(323) 933-0288</t>
+          <t>(213) 629-2130</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>info@majesticjewelers.com</t>
+          <t>sales@goldenstatejewelry.com</t>
         </is>
       </c>
       <c r="F325" t="inlineStr"/>
@@ -36646,12 +36758,12 @@
       <c r="H325" t="inlineStr"/>
       <c r="I325" s="2" t="inlineStr">
         <is>
-          <t>https://majesticjewelers.com</t>
+          <t>https://www.goldenstatejewelry.com</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>6333 W 3rd St, Los Angeles, CA 90036</t>
+          <t>550 S Hill St Ste 825, Los Angeles, CA 90013</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
@@ -36675,19 +36787,19 @@
         </is>
       </c>
       <c r="O325" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P325" t="n">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="Q325" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/los-angeles-ca/mip/majestic-jewelry-458143900</t>
+          <t>https://www.yellowpages.com/los-angeles-ca/mip/golden-state-467565356</t>
         </is>
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-1986</t>
+          <t>2 of 3, role-email, direct-line, bench, custom-design, since-1978</t>
         </is>
       </c>
       <c r="S325" t="inlineStr">
@@ -36697,18 +36809,18 @@
       </c>
       <c r="T325" s="2" t="inlineStr">
         <is>
-          <t>https://www.majesticjewelers.com/about-us/</t>
+          <t>https://goldenstatejewelry.com/</t>
         </is>
       </c>
       <c r="U325" t="inlineStr"/>
       <c r="V325" t="inlineStr">
         <is>
-          <t>2026-10-14T01:52:20+05:30</t>
+          <t>2026-10-14T01:52:45+05:30</t>
         </is>
       </c>
       <c r="W325" t="inlineStr">
         <is>
-          <t>Majestic W.J.</t>
+          <t>Golden Star Jewelry</t>
         </is>
       </c>
       <c r="X325" t="inlineStr">
@@ -36722,19 +36834,19 @@
       <c r="Z325" t="inlineStr"/>
       <c r="AA325" t="inlineStr">
         <is>
-          <t>(407) 644-4824</t>
+          <t>(213) 627-9677</t>
         </is>
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>https://facebook.com/MajesticJewelersInc, https://instagram.com/majesticjewelerswp</t>
+          <t>https://instagram.com/goldenstatejewelryla</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Raven Fine Jewelers</t>
+          <t>Hoorsenbuhs</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -36749,12 +36861,12 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>(310) 432-5234</t>
+          <t>(888) 692-2997</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>info@ravenjewelers.com</t>
+          <t>info@hoorsenbuhs.com</t>
         </is>
       </c>
       <c r="F326" t="inlineStr"/>
@@ -36762,17 +36874,17 @@
       <c r="H326" t="inlineStr"/>
       <c r="I326" s="2" t="inlineStr">
         <is>
-          <t>https://ravenfinejewelers.localsearch.com</t>
+          <t>https://hoorsenbuhs.com</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>8350 Wilshire Blvd, Beverly Hills, CA 90211</t>
+          <t>2217 Main St, Santa Monica, CA 90405</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>Beverly Hills</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
@@ -36790,20 +36902,16 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O326" t="n">
-        <v>5</v>
-      </c>
-      <c r="P326" t="n">
-        <v>1</v>
-      </c>
+      <c r="O326" t="inlineStr"/>
+      <c r="P326" t="inlineStr"/>
       <c r="Q326" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/beverly-hills-ca/mip/raven-fine-jewelers-531865762</t>
+          <t>https://www.yellowpages.com/santa-monica-ca/mip/hoorsenbuhs-551622669</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, role-email, direct-line</t>
         </is>
       </c>
       <c r="S326" t="inlineStr">
@@ -36813,56 +36921,60 @@
       </c>
       <c r="T326" s="2" t="inlineStr">
         <is>
-          <t>https://ravendiamonds.com/</t>
+          <t>https://hoorsenbuhs.com/</t>
         </is>
       </c>
       <c r="U326" t="inlineStr"/>
       <c r="V326" t="inlineStr">
         <is>
-          <t>2026-10-14T01:51:20+05:30</t>
+          <t>2026-10-14T01:53:36+05:30</t>
         </is>
       </c>
       <c r="W326" t="inlineStr"/>
       <c r="X326" t="inlineStr"/>
       <c r="Y326" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z326" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Z326" t="inlineStr">
+        <is>
+          <t>toll-free</t>
+        </is>
+      </c>
       <c r="AA326" t="inlineStr">
         <is>
-          <t>(310) 887-1499</t>
+          <t>(917) 206-9333</t>
         </is>
       </c>
       <c r="AB326" t="inlineStr">
         <is>
-          <t>https://instagram.com/ravenfinejewelers, https://facebook.com/RavenFineJewelers</t>
+          <t>https://instagram.com/hoorsenbuhs</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Sunset Plaza</t>
+          <t>Jennifer Fisher Jewelry</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Jewelers, Watches, Real Estate Agents</t>
+          <t>Jewelry store</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>(310) 652-7137</t>
+          <t>(424) 374-5303</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>info@sunsetplaza.com</t>
+          <t>la@jenniferfisher.com</t>
         </is>
       </c>
       <c r="F327" t="inlineStr"/>
@@ -36870,24 +36982,16 @@
       <c r="H327" t="inlineStr"/>
       <c r="I327" s="2" t="inlineStr">
         <is>
-          <t>https://www.sunsetplaza.com</t>
+          <t>https://jenniferfisher.com</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>8623 W Sunset Blvd, West Hollywood, CA 90069</t>
-        </is>
-      </c>
-      <c r="K327" t="inlineStr">
-        <is>
-          <t>West Hollywood</t>
-        </is>
-      </c>
-      <c r="L327" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
+          <t>363 N Beverly Dr, Beverly Hills, CA 90210, United States</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr"/>
+      <c r="L327" t="inlineStr"/>
       <c r="M327" t="inlineStr">
         <is>
           <t>Beverly Hills, CA</t>
@@ -36895,19 +36999,23 @@
       </c>
       <c r="N327" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O327" t="inlineStr"/>
-      <c r="P327" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O327" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P327" t="n">
+        <v>44</v>
+      </c>
       <c r="Q327" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/west-hollywood-ca/mip/sunset-plaza-1562237</t>
+          <t>https://www.google.com/maps/place/Jennifer+Fisher+Jewelry/data=!4m7!3m6!1s0x80c2bdd6ed684985:0xb8fbea746e91ad05!8m2!3d34.0695438!4d-118.4019104!16s%2Fg%2F11n12hvwn5!19sChIJhUlo7da9woARBa2RbnTq-7g</t>
         </is>
       </c>
       <c r="R327" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, since-1924</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S327" t="inlineStr">
@@ -36917,13 +37025,13 @@
       </c>
       <c r="T327" s="2" t="inlineStr">
         <is>
-          <t>https://www.sunsetplaza.com/</t>
+          <t>https://jenniferfisher.com/pages/stockists</t>
         </is>
       </c>
       <c r="U327" t="inlineStr"/>
       <c r="V327" t="inlineStr">
         <is>
-          <t>2026-10-14T01:52:13+05:30</t>
+          <t>2026-10-14T01:40:50+05:30</t>
         </is>
       </c>
       <c r="W327" t="inlineStr"/>
@@ -36934,60 +37042,52 @@
       <c r="Z327" t="inlineStr"/>
       <c r="AA327" t="inlineStr">
         <is>
-          <t>(213) 500-3098, (213) 709-2282, (310) 210-0975, (310) 248-3750, (310) 274-1602, (310) 275-2222, (310) 289-1104, (310) 289-1105, (310) 360-6900, (310) 360-8889, (310) 424-3690, (310) 616-7888, (310) 652-2680, (310) 652-6844, (310) 652-7039, (310) 652-8886, (310) 657-2553, (310) 657-5070, (310) 657-5469, (310) 659-4411, (310) 659-9089, (310) 734-7296, (310) 786-7417, (310) 849-7185, (310) 854-0299, (310) 854-7700, (310) 855-8044, (323) 253-6747, (323) 345-4525, (323) 507-3943, (323) 650-0475, (323) 937-0355, (424) 407-4606, (424) 542-7730, (424) 667-0036, (424) 722-8502, (747) 724-3595</t>
+          <t>(646) 366-9375</t>
         </is>
       </c>
       <c r="AB327" t="inlineStr">
         <is>
-          <t>https://instagram.com/affluette_, https://instagram.com/alchemy43, https://facebook.com/alchemy43, https://instagram.com/andreas.fashions, https://facebook.com/andreasfashions, https://instagram.com/bbcmcafe, https://instagram.com/bootstarusa, https://facebook.com/Boot-Star-106137407505929, https://instagram.com/bossanovarestaurant, https://facebook.com/BossaNovaLA, https://instagram.com/charliechoukair/, https://instagram.com/cristallini_official, https://facebook.com/CRISTALLINIOfficial, https://instagram.com/architectureforsale/, https://instagram.com/cupidlipsofbeverlyhills, https://facebook.com/profile.php?id=100083257576786, https://instagram.com/dandeutschoo, https://instagram.com/davidorgell, https://instagram.com/drybarshopsus, https://facebook.com/thedrybar, https://instagram.com/elainekimcollection/, https://instagram.com/entouragebarbershop, https://instagram.com/fpjourneofficial, https://instagram.com/guyfloralstudio, https://instagram.com/hotpilates, https://facebook.com/Hot-Pilates-1806940676211478, https://instagram.com/kojitoyodasalon, https://instagram.com/metaclinic/, https://instagram.com/milamoursiskincare, https://instagram.com/olehenriksenspa/, https://instagram.com/oliverpeoples, https://instagram.com/osklo.la, https://instagram.com/philippressjeweler, https://instagram.com/puravidamiami, https://facebook.com/PuraVidaMiami, https://instagram.com/queenbnailsalon_sunsetplaza, https://instagram.com/andywarholrevolvergallery, https://instagram.com/rondorff, https://instagram.com/saltiegirlla, https://instagram.com/samira13jewelry, https://instagram.com/sargondental, https://facebook.com/sargonlazarofdds, https://instagram.com/serenityonsunset, https://instagram.com/sheilaonsunset, https://instagram.com/solatesbysamantha, https://instagram.com/sousla_official, https://instagram.com/sunsetkidsla, https://instagram.com/theoppenheimgroup, https://facebook.com/theoppenheimgroup, https://instagram.com/whitegloveestates, https://instagram.com/xrcyze_ny, https://facebook.com/xrcycle, https://instagram.com/sunsetplazaca, https://facebook.com/SunsetPlazaCA</t>
+          <t>https://instagram.com/jenniferfisherjewelry/, https://facebook.com/JenniferFisherJewelry, https://instagram.com/jenniferfisherjewelry</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Westime Beverly Hills</t>
+          <t>Jewelry &amp; Watch Buyers - Beverly Hills</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Watch store</t>
+          <t>Jewelry buyer</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>(310) 888-8880</t>
+          <t>(310) 697-8177</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>contact@westime.com</t>
+          <t>info@watchbuyers.us</t>
         </is>
       </c>
       <c r="F328" t="inlineStr"/>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>Greg Simonian</t>
-        </is>
-      </c>
-      <c r="H328" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
+      <c r="G328" t="inlineStr"/>
+      <c r="H328" t="inlineStr"/>
       <c r="I328" s="2" t="inlineStr">
         <is>
-          <t>https://westime.com</t>
+          <t>https://watchbuyers.us</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>206 N Rodeo Dr, Beverly Hills, CA 90210, United States</t>
+          <t>468 N Camden Dr #205, Beverly Hills, CA 90210, United States</t>
         </is>
       </c>
       <c r="K328" t="inlineStr"/>
@@ -37003,19 +37103,19 @@
         </is>
       </c>
       <c r="O328" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P328" t="n">
-        <v>274</v>
+        <v>3</v>
       </c>
       <c r="Q328" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Westime+Beverly+Hills/data=!4m7!3m6!1s0x80c2bc0ed6429065:0x2c357ea8ffa51b1f!8m2!3d34.067375!4d-118.4003799!16s%2Fg%2F11cfj2mg2!19sChIJZZBC1g68woARHxul_6h-NSw</t>
+          <t>https://www.google.com/maps/place/Jewelry+%26+Watch+Buyers+-+Beverly+Hills/data=!4m7!3m6!1s0x80c2bdbde9baacdb:0xbbce1c74141b63ce!8m2!3d34.0698858!4d-118.404944!16s%2Fg%2F11xt1px272!19sChIJ26y66b29woARzmMbFHQczrs</t>
         </is>
       </c>
       <c r="R328" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-1987</t>
+          <t>2 of 3, role-email, direct-line</t>
         </is>
       </c>
       <c r="S328" t="inlineStr">
@@ -37025,13 +37125,13 @@
       </c>
       <c r="T328" s="2" t="inlineStr">
         <is>
-          <t>https://westime.com/contact</t>
+          <t>https://watchbuyers.us/</t>
         </is>
       </c>
       <c r="U328" t="inlineStr"/>
       <c r="V328" t="inlineStr">
         <is>
-          <t>2026-10-14T01:39:33+05:30</t>
+          <t>2026-10-14T01:40:58+05:30</t>
         </is>
       </c>
       <c r="W328" t="inlineStr"/>
@@ -37042,39 +37142,31 @@
       <c r="Z328" t="inlineStr"/>
       <c r="AA328" t="inlineStr">
         <is>
-          <t>(786) 347-5353, (858) 459-2222</t>
-        </is>
-      </c>
-      <c r="AB328" t="inlineStr">
-        <is>
-          <t>https://instagram.com/westimewatches, https://facebook.com/Westime</t>
-        </is>
-      </c>
+          <t>(305) 989-9099, (646) 413-7757</t>
+        </is>
+      </c>
+      <c r="AB328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Wrist Aficionado Beverly Hills</t>
+          <t>Jewels Aficionado Beverly Hills</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Watch store</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>(310) 388-8201</t>
-        </is>
-      </c>
+          <t>Jewelry store</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr">
         <is>
-          <t>sales@wristaficionado.com</t>
+          <t>sales@jewelsaficionado.com</t>
         </is>
       </c>
       <c r="F329" t="inlineStr"/>
@@ -37082,7 +37174,7 @@
       <c r="H329" t="inlineStr"/>
       <c r="I329" s="2" t="inlineStr">
         <is>
-          <t>https://wristaficionado.com</t>
+          <t>https://jewelsaficionado.com</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
@@ -37090,16 +37182,8 @@
           <t>9850 Wilshire Blvd, Beverly Hills, CA 90210, United States</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr">
-        <is>
-          <t>Beverly Hills</t>
-        </is>
-      </c>
-      <c r="L329" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
+      <c r="K329" t="inlineStr"/>
+      <c r="L329" t="inlineStr"/>
       <c r="M329" t="inlineStr">
         <is>
           <t>Beverly Hills, CA</t>
@@ -37110,20 +37194,16 @@
           <t>Google Maps</t>
         </is>
       </c>
-      <c r="O329" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P329" t="n">
-        <v>101</v>
-      </c>
+      <c r="O329" t="inlineStr"/>
+      <c r="P329" t="inlineStr"/>
       <c r="Q329" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Wrist+Aficionado+Beverly+Hills/data=!4m7!3m6!1s0x80c2bb67e5181fcf:0xde9cbdbb118a155c!8m2!3d34.0667288!4d-118.4113018!16s%2Fg%2F11v12tg_x0!19sChIJzx8Y5We7woARXBWKEbu9nN4</t>
+          <t>https://www.google.com/maps/place/Jewels+Aficionado+Beverly+Hills/data=!4m7!3m6!1s0x80c2bb445801322d:0x4ee3ff18cd9446bc!8m2!3d34.0666649!4d-118.4114543!16s%2Fg%2F11z2xf_27b!19sChIJLTIBWES7woARvEaUzRj_404</t>
         </is>
       </c>
       <c r="R329" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-2017</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S329" t="inlineStr">
@@ -37133,13 +37213,13 @@
       </c>
       <c r="T329" s="2" t="inlineStr">
         <is>
-          <t>https://wristaficionado.com/</t>
+          <t>https://jewelsaficionado.com/</t>
         </is>
       </c>
       <c r="U329" t="inlineStr"/>
       <c r="V329" t="inlineStr">
         <is>
-          <t>2026-10-14T01:43:17+05:30</t>
+          <t>2026-10-14T01:42:22+05:30</t>
         </is>
       </c>
       <c r="W329" t="inlineStr"/>
@@ -37150,17 +37230,661 @@
       <c r="Z329" t="inlineStr"/>
       <c r="AA329" t="inlineStr">
         <is>
+          <t>(212) 422-2600</t>
+        </is>
+      </c>
+      <c r="AB329" t="inlineStr">
+        <is>
+          <t>https://instagram.com/jewelsaficionado</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Logan Hollowell Jewelry</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Jewelry store</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>(323) 248-9685</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>info@loganhollowell.com</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr"/>
+      <c r="G330" t="inlineStr"/>
+      <c r="H330" t="inlineStr"/>
+      <c r="I330" s="2" t="inlineStr">
+        <is>
+          <t>https://www.loganhollowell.com</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>411 N Canon Dr, Beverly Hills, CA 90210, United States</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr"/>
+      <c r="L330" t="inlineStr"/>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>Beverly Hills, CA</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O330" t="n">
+        <v>5</v>
+      </c>
+      <c r="P330" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q330" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Logan+Hollowell+Jewelry/data=!4m7!3m6!1s0x80c2bd39cbc0865f:0x202c691c8504a898!8m2!3d34.07073!4d-118.4012945!16s%2Fg%2F11njp9zjzq!19sChIJX4bAyzm9woARmKgEhRxpLCA</t>
+        </is>
+      </c>
+      <c r="R330" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, custom-design, since-2014</t>
+        </is>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T330" s="2" t="inlineStr">
+        <is>
+          <t>https://loganhollowell.com/</t>
+        </is>
+      </c>
+      <c r="U330" t="inlineStr"/>
+      <c r="V330" t="inlineStr">
+        <is>
+          <t>2026-10-14T01:41:31+05:30</t>
+        </is>
+      </c>
+      <c r="W330" t="inlineStr"/>
+      <c r="X330" t="inlineStr"/>
+      <c r="Y330" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z330" t="inlineStr"/>
+      <c r="AA330" t="inlineStr">
+        <is>
+          <t>(323) 853-7844</t>
+        </is>
+      </c>
+      <c r="AB330" t="inlineStr">
+        <is>
+          <t>https://instagram.com/loganhollowell, https://facebook.com/loganhollowelljewelry</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Majestic Jewelry</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Custom / bespoke jeweler</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Jewelers</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>(323) 933-0288</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>info@majesticjewelers.com</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr"/>
+      <c r="G331" t="inlineStr"/>
+      <c r="H331" t="inlineStr"/>
+      <c r="I331" s="2" t="inlineStr">
+        <is>
+          <t>https://majesticjewelers.com</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>6333 W 3rd St, Los Angeles, CA 90036</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>Beverly Hills, CA</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O331" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P331" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q331" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/los-angeles-ca/mip/majestic-jewelry-458143900</t>
+        </is>
+      </c>
+      <c r="R331" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, custom-design, since-1986</t>
+        </is>
+      </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T331" s="2" t="inlineStr">
+        <is>
+          <t>https://www.majesticjewelers.com/about-us/</t>
+        </is>
+      </c>
+      <c r="U331" t="inlineStr"/>
+      <c r="V331" t="inlineStr">
+        <is>
+          <t>2026-10-14T01:52:20+05:30</t>
+        </is>
+      </c>
+      <c r="W331" t="inlineStr">
+        <is>
+          <t>Majestic W.J.</t>
+        </is>
+      </c>
+      <c r="X331" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="Y331" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z331" t="inlineStr"/>
+      <c r="AA331" t="inlineStr">
+        <is>
+          <t>(407) 644-4824</t>
+        </is>
+      </c>
+      <c r="AB331" t="inlineStr">
+        <is>
+          <t>https://facebook.com/MajesticJewelersInc, https://instagram.com/majesticjewelerswp</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Raven Fine Jewelers</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Jewelers</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>(310) 432-5234</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>info@ravenjewelers.com</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr"/>
+      <c r="G332" t="inlineStr"/>
+      <c r="H332" t="inlineStr"/>
+      <c r="I332" s="2" t="inlineStr">
+        <is>
+          <t>https://ravenfinejewelers.localsearch.com</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>8350 Wilshire Blvd, Beverly Hills, CA 90211</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Beverly Hills</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>Beverly Hills, CA</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O332" t="n">
+        <v>5</v>
+      </c>
+      <c r="P332" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q332" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/beverly-hills-ca/mip/raven-fine-jewelers-531865762</t>
+        </is>
+      </c>
+      <c r="R332" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
+        </is>
+      </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T332" s="2" t="inlineStr">
+        <is>
+          <t>https://ravendiamonds.com/</t>
+        </is>
+      </c>
+      <c r="U332" t="inlineStr"/>
+      <c r="V332" t="inlineStr">
+        <is>
+          <t>2026-10-14T01:51:20+05:30</t>
+        </is>
+      </c>
+      <c r="W332" t="inlineStr"/>
+      <c r="X332" t="inlineStr"/>
+      <c r="Y332" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z332" t="inlineStr"/>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>(310) 887-1499</t>
+        </is>
+      </c>
+      <c r="AB332" t="inlineStr">
+        <is>
+          <t>https://instagram.com/ravenfinejewelers, https://facebook.com/RavenFineJewelers</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Sunset Plaza</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Estate &amp; antique jewelry</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Jewelers, Watches, Real Estate Agents</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>(310) 652-7137</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>info@sunsetplaza.com</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr"/>
+      <c r="G333" t="inlineStr"/>
+      <c r="H333" t="inlineStr"/>
+      <c r="I333" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sunsetplaza.com</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>8623 W Sunset Blvd, West Hollywood, CA 90069</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>West Hollywood</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>Beverly Hills, CA</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr"/>
+      <c r="P333" t="inlineStr"/>
+      <c r="Q333" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/west-hollywood-ca/mip/sunset-plaza-1562237</t>
+        </is>
+      </c>
+      <c r="R333" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, since-1924</t>
+        </is>
+      </c>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T333" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sunsetplaza.com/</t>
+        </is>
+      </c>
+      <c r="U333" t="inlineStr"/>
+      <c r="V333" t="inlineStr">
+        <is>
+          <t>2026-10-14T01:52:13+05:30</t>
+        </is>
+      </c>
+      <c r="W333" t="inlineStr"/>
+      <c r="X333" t="inlineStr"/>
+      <c r="Y333" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z333" t="inlineStr"/>
+      <c r="AA333" t="inlineStr">
+        <is>
+          <t>(213) 500-3098, (213) 709-2282, (310) 210-0975, (310) 248-3750, (310) 274-1602, (310) 275-2222, (310) 289-1104, (310) 289-1105, (310) 360-6900, (310) 360-8889, (310) 424-3690, (310) 616-7888, (310) 652-2680, (310) 652-6844, (310) 652-7039, (310) 652-8886, (310) 657-2553, (310) 657-5070, (310) 657-5469, (310) 659-4411, (310) 659-9089, (310) 734-7296, (310) 786-7417, (310) 849-7185, (310) 854-0299, (310) 854-7700, (310) 855-8044, (323) 253-6747, (323) 345-4525, (323) 507-3943, (323) 650-0475, (323) 937-0355, (424) 407-4606, (424) 542-7730, (424) 667-0036, (424) 722-8502, (747) 724-3595</t>
+        </is>
+      </c>
+      <c r="AB333" t="inlineStr">
+        <is>
+          <t>https://instagram.com/affluette_, https://instagram.com/alchemy43, https://facebook.com/alchemy43, https://instagram.com/andreas.fashions, https://facebook.com/andreasfashions, https://instagram.com/bbcmcafe, https://instagram.com/bootstarusa, https://facebook.com/Boot-Star-106137407505929, https://instagram.com/bossanovarestaurant, https://facebook.com/BossaNovaLA, https://instagram.com/charliechoukair/, https://instagram.com/cristallini_official, https://facebook.com/CRISTALLINIOfficial, https://instagram.com/architectureforsale/, https://instagram.com/cupidlipsofbeverlyhills, https://facebook.com/profile.php?id=100083257576786, https://instagram.com/dandeutschoo, https://instagram.com/davidorgell, https://instagram.com/drybarshopsus, https://facebook.com/thedrybar, https://instagram.com/elainekimcollection/, https://instagram.com/entouragebarbershop, https://instagram.com/fpjourneofficial, https://instagram.com/guyfloralstudio, https://instagram.com/hotpilates, https://facebook.com/Hot-Pilates-1806940676211478, https://instagram.com/kojitoyodasalon, https://instagram.com/metaclinic/, https://instagram.com/milamoursiskincare, https://instagram.com/olehenriksenspa/, https://instagram.com/oliverpeoples, https://instagram.com/osklo.la, https://instagram.com/philippressjeweler, https://instagram.com/puravidamiami, https://facebook.com/PuraVidaMiami, https://instagram.com/queenbnailsalon_sunsetplaza, https://instagram.com/andywarholrevolvergallery, https://instagram.com/rondorff, https://instagram.com/saltiegirlla, https://instagram.com/samira13jewelry, https://instagram.com/sargondental, https://facebook.com/sargonlazarofdds, https://instagram.com/serenityonsunset, https://instagram.com/sheilaonsunset, https://instagram.com/solatesbysamantha, https://instagram.com/sousla_official, https://instagram.com/sunsetkidsla, https://instagram.com/theoppenheimgroup, https://facebook.com/theoppenheimgroup, https://instagram.com/whitegloveestates, https://instagram.com/xrcyze_ny, https://facebook.com/xrcycle, https://instagram.com/sunsetplazaca, https://facebook.com/SunsetPlazaCA</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Westime Beverly Hills</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Custom / bespoke jeweler</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Watch store</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>(310) 888-8880</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>contact@westime.com</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr"/>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>Greg Simonian</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="I334" s="2" t="inlineStr">
+        <is>
+          <t>https://westime.com</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>206 N Rodeo Dr, Beverly Hills, CA 90210, United States</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr"/>
+      <c r="L334" t="inlineStr"/>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>Beverly Hills, CA</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O334" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P334" t="n">
+        <v>274</v>
+      </c>
+      <c r="Q334" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Westime+Beverly+Hills/data=!4m7!3m6!1s0x80c2bc0ed6429065:0x2c357ea8ffa51b1f!8m2!3d34.067375!4d-118.4003799!16s%2Fg%2F11cfj2mg2!19sChIJZZBC1g68woARHxul_6h-NSw</t>
+        </is>
+      </c>
+      <c r="R334" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, custom-design, since-1987</t>
+        </is>
+      </c>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T334" s="2" t="inlineStr">
+        <is>
+          <t>https://westime.com/contact</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr"/>
+      <c r="V334" t="inlineStr">
+        <is>
+          <t>2026-10-14T01:39:33+05:30</t>
+        </is>
+      </c>
+      <c r="W334" t="inlineStr"/>
+      <c r="X334" t="inlineStr"/>
+      <c r="Y334" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z334" t="inlineStr"/>
+      <c r="AA334" t="inlineStr">
+        <is>
+          <t>(786) 347-5353, (858) 459-2222</t>
+        </is>
+      </c>
+      <c r="AB334" t="inlineStr">
+        <is>
+          <t>https://instagram.com/westimewatches, https://facebook.com/Westime</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Wrist Aficionado Beverly Hills</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Watch store</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>(310) 388-8201</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>sales@wristaficionado.com</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr"/>
+      <c r="G335" t="inlineStr"/>
+      <c r="H335" t="inlineStr"/>
+      <c r="I335" s="2" t="inlineStr">
+        <is>
+          <t>https://wristaficionado.com</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>9850 Wilshire Blvd, Beverly Hills, CA 90210, United States</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Beverly Hills</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>Beverly Hills, CA</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O335" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P335" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q335" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Wrist+Aficionado+Beverly+Hills/data=!4m7!3m6!1s0x80c2bb67e5181fcf:0xde9cbdbb118a155c!8m2!3d34.0667288!4d-118.4113018!16s%2Fg%2F11v12tg_x0!19sChIJzx8Y5We7woARXBWKEbu9nN4</t>
+        </is>
+      </c>
+      <c r="R335" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, custom-design, since-2017</t>
+        </is>
+      </c>
+      <c r="S335" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T335" s="2" t="inlineStr">
+        <is>
+          <t>https://wristaficionado.com/</t>
+        </is>
+      </c>
+      <c r="U335" t="inlineStr"/>
+      <c r="V335" t="inlineStr">
+        <is>
+          <t>2026-10-14T01:43:17+05:30</t>
+        </is>
+      </c>
+      <c r="W335" t="inlineStr"/>
+      <c r="X335" t="inlineStr"/>
+      <c r="Y335" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z335" t="inlineStr"/>
+      <c r="AA335" t="inlineStr">
+        <is>
           <t>(305) 680-3735, (310) 861-3485, (646) 693-9384, (786) 889-6892</t>
         </is>
       </c>
-      <c r="AB329" t="inlineStr">
+      <c r="AB335" t="inlineStr">
         <is>
           <t>https://instagram.com/wristaficionado, https://instagram.com/wristaficionado/, https://facebook.com/shopwristaficionado, https://twitter.com/wristaficionado</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB329"/>
+  <autoFilter ref="A1:AB335"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId2"/>
@@ -38135,154 +38859,181 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q285" r:id="rId971"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T285" r:id="rId972"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U285" r:id="rId973"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I286" r:id="rId974"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q286" r:id="rId975"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T286" r:id="rId976"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F287" r:id="rId977"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I287" r:id="rId978"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q287" r:id="rId979"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T287" r:id="rId980"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U287" r:id="rId981"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I288" r:id="rId982"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q288" r:id="rId983"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T288" r:id="rId984"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F289" r:id="rId985"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I289" r:id="rId986"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q289" r:id="rId987"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T289" r:id="rId988"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U289" r:id="rId989"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I290" r:id="rId990"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q290" r:id="rId991"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T290" r:id="rId992"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F291" r:id="rId993"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I291" r:id="rId994"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q291" r:id="rId995"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T291" r:id="rId996"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U291" r:id="rId997"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I292" r:id="rId998"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q292" r:id="rId999"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T292" r:id="rId1000"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I293" r:id="rId1001"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q293" r:id="rId1002"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T293" r:id="rId1003"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I294" r:id="rId1004"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q294" r:id="rId1005"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T294" r:id="rId1006"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F295" r:id="rId1007"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I295" r:id="rId1008"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q295" r:id="rId1009"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T295" r:id="rId1010"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U295" r:id="rId1011"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F296" r:id="rId1012"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I296" r:id="rId1013"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q296" r:id="rId1014"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T296" r:id="rId1015"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U296" r:id="rId1016"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I297" r:id="rId1017"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q297" r:id="rId1018"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T297" r:id="rId1019"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I298" r:id="rId1020"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q298" r:id="rId1021"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T298" r:id="rId1022"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I299" r:id="rId1023"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q299" r:id="rId1024"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T299" r:id="rId1025"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I300" r:id="rId1026"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q300" r:id="rId1027"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T300" r:id="rId1028"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F301" r:id="rId1029"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I301" r:id="rId1030"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q301" r:id="rId1031"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T301" r:id="rId1032"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U301" r:id="rId1033"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I302" r:id="rId1034"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q302" r:id="rId1035"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T302" r:id="rId1036"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I303" r:id="rId1037"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q303" r:id="rId1038"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T303" r:id="rId1039"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I304" r:id="rId1040"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q304" r:id="rId1041"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T304" r:id="rId1042"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I305" r:id="rId1043"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q305" r:id="rId1044"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T305" r:id="rId1045"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I306" r:id="rId1046"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q306" r:id="rId1047"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T306" r:id="rId1048"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F307" r:id="rId1049"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I307" r:id="rId1050"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q307" r:id="rId1051"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T307" r:id="rId1052"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U307" r:id="rId1053"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I308" r:id="rId1054"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q308" r:id="rId1055"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T308" r:id="rId1056"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I309" r:id="rId1057"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q309" r:id="rId1058"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T309" r:id="rId1059"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I310" r:id="rId1060"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q310" r:id="rId1061"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T310" r:id="rId1062"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I311" r:id="rId1063"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q311" r:id="rId1064"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T311" r:id="rId1065"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I312" r:id="rId1066"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q312" r:id="rId1067"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T312" r:id="rId1068"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I313" r:id="rId1069"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q313" r:id="rId1070"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T313" r:id="rId1071"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I314" r:id="rId1072"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q314" r:id="rId1073"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T314" r:id="rId1074"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I315" r:id="rId1075"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q315" r:id="rId1076"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T315" r:id="rId1077"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F316" r:id="rId1078"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I316" r:id="rId1079"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q316" r:id="rId1080"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T316" r:id="rId1081"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U316" r:id="rId1082"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I317" r:id="rId1083"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q317" r:id="rId1084"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T317" r:id="rId1085"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I318" r:id="rId1086"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q318" r:id="rId1087"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T318" r:id="rId1088"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I319" r:id="rId1089"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q319" r:id="rId1090"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T319" r:id="rId1091"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I320" r:id="rId1092"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q320" r:id="rId1093"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T320" r:id="rId1094"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I321" r:id="rId1095"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q321" r:id="rId1096"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T321" r:id="rId1097"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I322" r:id="rId1098"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q322" r:id="rId1099"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T322" r:id="rId1100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I323" r:id="rId1101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q323" r:id="rId1102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T323" r:id="rId1103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I324" r:id="rId1104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q324" r:id="rId1105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T324" r:id="rId1106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I325" r:id="rId1107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q325" r:id="rId1108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T325" r:id="rId1109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I326" r:id="rId1110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q326" r:id="rId1111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T326" r:id="rId1112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I327" r:id="rId1113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q327" r:id="rId1114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T327" r:id="rId1115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I328" r:id="rId1116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q328" r:id="rId1117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T328" r:id="rId1118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I329" r:id="rId1119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q329" r:id="rId1120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T329" r:id="rId1121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F286" r:id="rId974"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I286" r:id="rId975"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q286" r:id="rId976"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T286" r:id="rId977"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U286" r:id="rId978"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I287" r:id="rId979"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q287" r:id="rId980"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T287" r:id="rId981"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F288" r:id="rId982"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I288" r:id="rId983"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q288" r:id="rId984"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T288" r:id="rId985"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U288" r:id="rId986"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I289" r:id="rId987"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q289" r:id="rId988"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T289" r:id="rId989"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F290" r:id="rId990"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I290" r:id="rId991"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q290" r:id="rId992"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T290" r:id="rId993"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U290" r:id="rId994"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F291" r:id="rId995"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I291" r:id="rId996"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q291" r:id="rId997"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T291" r:id="rId998"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U291" r:id="rId999"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I292" r:id="rId1000"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q292" r:id="rId1001"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T292" r:id="rId1002"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F293" r:id="rId1003"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I293" r:id="rId1004"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q293" r:id="rId1005"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T293" r:id="rId1006"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U293" r:id="rId1007"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I294" r:id="rId1008"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q294" r:id="rId1009"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T294" r:id="rId1010"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I295" r:id="rId1011"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q295" r:id="rId1012"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T295" r:id="rId1013"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F296" r:id="rId1014"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I296" r:id="rId1015"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q296" r:id="rId1016"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T296" r:id="rId1017"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U296" r:id="rId1018"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F297" r:id="rId1019"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I297" r:id="rId1020"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q297" r:id="rId1021"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U297" r:id="rId1022"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I298" r:id="rId1023"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q298" r:id="rId1024"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T298" r:id="rId1025"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F299" r:id="rId1026"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I299" r:id="rId1027"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q299" r:id="rId1028"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T299" r:id="rId1029"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U299" r:id="rId1030"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F300" r:id="rId1031"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I300" r:id="rId1032"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q300" r:id="rId1033"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T300" r:id="rId1034"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U300" r:id="rId1035"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F301" r:id="rId1036"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I301" r:id="rId1037"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q301" r:id="rId1038"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T301" r:id="rId1039"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U301" r:id="rId1040"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I302" r:id="rId1041"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q302" r:id="rId1042"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T302" r:id="rId1043"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I303" r:id="rId1044"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q303" r:id="rId1045"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T303" r:id="rId1046"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I304" r:id="rId1047"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q304" r:id="rId1048"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T304" r:id="rId1049"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I305" r:id="rId1050"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q305" r:id="rId1051"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T305" r:id="rId1052"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F306" r:id="rId1053"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I306" r:id="rId1054"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q306" r:id="rId1055"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T306" r:id="rId1056"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U306" r:id="rId1057"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I307" r:id="rId1058"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q307" r:id="rId1059"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T307" r:id="rId1060"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I308" r:id="rId1061"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q308" r:id="rId1062"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T308" r:id="rId1063"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I309" r:id="rId1064"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q309" r:id="rId1065"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T309" r:id="rId1066"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I310" r:id="rId1067"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q310" r:id="rId1068"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T310" r:id="rId1069"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I311" r:id="rId1070"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q311" r:id="rId1071"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T311" r:id="rId1072"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I312" r:id="rId1073"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q312" r:id="rId1074"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T312" r:id="rId1075"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F313" r:id="rId1076"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I313" r:id="rId1077"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q313" r:id="rId1078"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T313" r:id="rId1079"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U313" r:id="rId1080"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I314" r:id="rId1081"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q314" r:id="rId1082"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T314" r:id="rId1083"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I315" r:id="rId1084"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q315" r:id="rId1085"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T315" r:id="rId1086"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I316" r:id="rId1087"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q316" r:id="rId1088"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T316" r:id="rId1089"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I317" r:id="rId1090"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q317" r:id="rId1091"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T317" r:id="rId1092"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I318" r:id="rId1093"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q318" r:id="rId1094"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T318" r:id="rId1095"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I319" r:id="rId1096"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q319" r:id="rId1097"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T319" r:id="rId1098"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I320" r:id="rId1099"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q320" r:id="rId1100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T320" r:id="rId1101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I321" r:id="rId1102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q321" r:id="rId1103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T321" r:id="rId1104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F322" r:id="rId1105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I322" r:id="rId1106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q322" r:id="rId1107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T322" r:id="rId1108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U322" r:id="rId1109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I323" r:id="rId1110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q323" r:id="rId1111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T323" r:id="rId1112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I324" r:id="rId1113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q324" r:id="rId1114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T324" r:id="rId1115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I325" r:id="rId1116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q325" r:id="rId1117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T325" r:id="rId1118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I326" r:id="rId1119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q326" r:id="rId1120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T326" r:id="rId1121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I327" r:id="rId1122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q327" r:id="rId1123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T327" r:id="rId1124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I328" r:id="rId1125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q328" r:id="rId1126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T328" r:id="rId1127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I329" r:id="rId1128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q329" r:id="rId1129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T329" r:id="rId1130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I330" r:id="rId1131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q330" r:id="rId1132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T330" r:id="rId1133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I331" r:id="rId1134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q331" r:id="rId1135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T331" r:id="rId1136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I332" r:id="rId1137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q332" r:id="rId1138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T332" r:id="rId1139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I333" r:id="rId1140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q333" r:id="rId1141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T333" r:id="rId1142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I334" r:id="rId1143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q334" r:id="rId1144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T334" r:id="rId1145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I335" r:id="rId1146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q335" r:id="rId1147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T335" r:id="rId1148"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -38674,7 +39425,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
@@ -38688,7 +39439,7 @@
         <v>12</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -38785,21 +39536,21 @@
         <v>382</v>
       </c>
       <c r="C18" t="n">
+        <v>18</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4.7%</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
         <v>17</v>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>16</v>
-      </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -38812,21 +39563,21 @@
         <v>245</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F19" t="n">
+        <v>6</v>
+      </c>
+      <c r="G19" t="n">
         <v>5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -38839,21 +39590,21 @@
         <v>211</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -38866,21 +39617,21 @@
         <v>189</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -38890,14 +39641,14 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="C22" t="n">
         <v>5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -38917,21 +39668,21 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -39025,10 +39776,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10953</v>
+        <v>10990</v>
       </c>
       <c r="C27" t="n">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -39036,13 +39787,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="F27" t="n">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="G27" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -39082,7 +39833,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3">
@@ -39092,7 +39843,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4">
@@ -39102,7 +39853,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5">
@@ -39112,7 +39863,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -39154,7 +39905,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11">
@@ -39193,7 +39944,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T06:41:44+05:30</t>
+          <t>2026-10-14T07:15:56+05:30</t>
         </is>
       </c>
     </row>
@@ -39204,7 +39955,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>328</v>
+        <v>334</v>
       </c>
     </row>
     <row r="3">
@@ -39214,7 +39965,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>10953</v>
+        <v>10990</v>
       </c>
     </row>
     <row r="4">

--- a/leadrun_jewelry/jewelry_qualified.xlsx
+++ b/leadrun_jewelry/jewelry_qualified.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qualified Leads'!$A$1:$AB$340</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qualified Leads'!$A$1:$AB$341</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB340"/>
+  <dimension ref="A1:AB341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -38182,27 +38182,27 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Sunset Plaza</t>
+          <t>Sell My Rolex Watch</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Jewelers, Watches, Real Estate Agents</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>(310) 652-7137</t>
+          <t>(323) 407-7273</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>info@sunsetplaza.com</t>
+          <t>info@sellmyrolexwatches.com</t>
         </is>
       </c>
       <c r="F338" t="inlineStr"/>
@@ -38210,17 +38210,17 @@
       <c r="H338" t="inlineStr"/>
       <c r="I338" s="2" t="inlineStr">
         <is>
-          <t>https://www.sunsetplaza.com</t>
+          <t>https://sellmyrolexwatches.online</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>8623 W Sunset Blvd, West Hollywood, CA 90069</t>
+          <t>8308 Wilshire Boulevard, Beverly Hills, CA 90211</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>West Hollywood</t>
+          <t>Beverly Hills</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
@@ -38235,19 +38235,19 @@
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="O338" t="inlineStr"/>
       <c r="P338" t="inlineStr"/>
       <c r="Q338" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/west-hollywood-ca/mip/sunset-plaza-1562237</t>
+          <t>https://www.bbb.org/us/ca/beverly-hills/profile/jewelry-stores/sell-my-rolex-watch-1216-1000065823</t>
         </is>
       </c>
       <c r="R338" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, since-1924</t>
+          <t>2 of 3, role-email, direct-line, since-2019</t>
         </is>
       </c>
       <c r="S338" t="inlineStr">
@@ -38257,13 +38257,13 @@
       </c>
       <c r="T338" s="2" t="inlineStr">
         <is>
-          <t>https://www.sunsetplaza.com/</t>
+          <t>https://www.sellmyrolexwatches.online/</t>
         </is>
       </c>
       <c r="U338" t="inlineStr"/>
       <c r="V338" t="inlineStr">
         <is>
-          <t>2026-10-14T01:52:13+05:30</t>
+          <t>2026-10-14T07:31:37+05:30</t>
         </is>
       </c>
       <c r="W338" t="inlineStr"/>
@@ -38274,64 +38274,64 @@
       <c r="Z338" t="inlineStr"/>
       <c r="AA338" t="inlineStr">
         <is>
-          <t>(213) 500-3098, (213) 709-2282, (310) 210-0975, (310) 248-3750, (310) 274-1602, (310) 275-2222, (310) 289-1104, (310) 289-1105, (310) 360-6900, (310) 360-8889, (310) 424-3690, (310) 616-7888, (310) 652-2680, (310) 652-6844, (310) 652-7039, (310) 652-8886, (310) 657-2553, (310) 657-5070, (310) 657-5469, (310) 659-4411, (310) 659-9089, (310) 734-7296, (310) 786-7417, (310) 849-7185, (310) 854-0299, (310) 854-7700, (310) 855-8044, (323) 253-6747, (323) 345-4525, (323) 507-3943, (323) 650-0475, (323) 937-0355, (424) 407-4606, (424) 542-7730, (424) 667-0036, (424) 722-8502, (747) 724-3595</t>
+          <t>(786) 232-3333, (917) 277-8707</t>
         </is>
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>https://instagram.com/affluette_, https://instagram.com/alchemy43, https://facebook.com/alchemy43, https://instagram.com/andreas.fashions, https://facebook.com/andreasfashions, https://instagram.com/bbcmcafe, https://instagram.com/bootstarusa, https://facebook.com/Boot-Star-106137407505929, https://instagram.com/bossanovarestaurant, https://facebook.com/BossaNovaLA, https://instagram.com/charliechoukair/, https://instagram.com/cristallini_official, https://facebook.com/CRISTALLINIOfficial, https://instagram.com/architectureforsale/, https://instagram.com/cupidlipsofbeverlyhills, https://facebook.com/profile.php?id=100083257576786, https://instagram.com/dandeutschoo, https://instagram.com/davidorgell, https://instagram.com/drybarshopsus, https://facebook.com/thedrybar, https://instagram.com/elainekimcollection/, https://instagram.com/entouragebarbershop, https://instagram.com/fpjourneofficial, https://instagram.com/guyfloralstudio, https://instagram.com/hotpilates, https://facebook.com/Hot-Pilates-1806940676211478, https://instagram.com/kojitoyodasalon, https://instagram.com/metaclinic/, https://instagram.com/milamoursiskincare, https://instagram.com/olehenriksenspa/, https://instagram.com/oliverpeoples, https://instagram.com/osklo.la, https://instagram.com/philippressjeweler, https://instagram.com/puravidamiami, https://facebook.com/PuraVidaMiami, https://instagram.com/queenbnailsalon_sunsetplaza, https://instagram.com/andywarholrevolvergallery, https://instagram.com/rondorff, https://instagram.com/saltiegirlla, https://instagram.com/samira13jewelry, https://instagram.com/sargondental, https://facebook.com/sargonlazarofdds, https://instagram.com/serenityonsunset, https://instagram.com/sheilaonsunset, https://instagram.com/solatesbysamantha, https://instagram.com/sousla_official, https://instagram.com/sunsetkidsla, https://instagram.com/theoppenheimgroup, https://facebook.com/theoppenheimgroup, https://instagram.com/whitegloveestates, https://instagram.com/xrcyze_ny, https://facebook.com/xrcycle, https://instagram.com/sunsetplazaca, https://facebook.com/SunsetPlazaCA</t>
+          <t>https://instagram.com/sellmyrolexwatch, https://facebook.com/sellmyrolexwatches</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Westime Beverly Hills</t>
+          <t>Sunset Plaza</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Watch store</t>
+          <t>Jewelers, Watches, Real Estate Agents</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>(310) 888-8880</t>
+          <t>(310) 652-7137</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>contact@westime.com</t>
+          <t>info@sunsetplaza.com</t>
         </is>
       </c>
       <c r="F339" t="inlineStr"/>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t>Greg Simonian</t>
-        </is>
-      </c>
-      <c r="H339" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
+      <c r="G339" t="inlineStr"/>
+      <c r="H339" t="inlineStr"/>
       <c r="I339" s="2" t="inlineStr">
         <is>
-          <t>https://westime.com</t>
+          <t>https://www.sunsetplaza.com</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>206 N Rodeo Dr, Beverly Hills, CA 90210, United States</t>
-        </is>
-      </c>
-      <c r="K339" t="inlineStr"/>
-      <c r="L339" t="inlineStr"/>
+          <t>8623 W Sunset Blvd, West Hollywood, CA 90069</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>West Hollywood</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
       <c r="M339" t="inlineStr">
         <is>
           <t>Beverly Hills, CA</t>
@@ -38339,23 +38339,19 @@
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O339" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P339" t="n">
-        <v>274</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr"/>
+      <c r="P339" t="inlineStr"/>
       <c r="Q339" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Westime+Beverly+Hills/data=!4m7!3m6!1s0x80c2bc0ed6429065:0x2c357ea8ffa51b1f!8m2!3d34.067375!4d-118.4003799!16s%2Fg%2F11cfj2mg2!19sChIJZZBC1g68woARHxul_6h-NSw</t>
+          <t>https://www.yellowpages.com/west-hollywood-ca/mip/sunset-plaza-1562237</t>
         </is>
       </c>
       <c r="R339" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-1987</t>
+          <t>2 of 3, role-email, direct-line, since-1924</t>
         </is>
       </c>
       <c r="S339" t="inlineStr">
@@ -38365,13 +38361,13 @@
       </c>
       <c r="T339" s="2" t="inlineStr">
         <is>
-          <t>https://westime.com/contact</t>
+          <t>https://www.sunsetplaza.com/</t>
         </is>
       </c>
       <c r="U339" t="inlineStr"/>
       <c r="V339" t="inlineStr">
         <is>
-          <t>2026-10-14T01:39:33+05:30</t>
+          <t>2026-10-14T01:52:13+05:30</t>
         </is>
       </c>
       <c r="W339" t="inlineStr"/>
@@ -38382,24 +38378,24 @@
       <c r="Z339" t="inlineStr"/>
       <c r="AA339" t="inlineStr">
         <is>
-          <t>(786) 347-5353, (858) 459-2222</t>
+          <t>(213) 500-3098, (213) 709-2282, (310) 210-0975, (310) 248-3750, (310) 274-1602, (310) 275-2222, (310) 289-1104, (310) 289-1105, (310) 360-6900, (310) 360-8889, (310) 424-3690, (310) 616-7888, (310) 652-2680, (310) 652-6844, (310) 652-7039, (310) 652-8886, (310) 657-2553, (310) 657-5070, (310) 657-5469, (310) 659-4411, (310) 659-9089, (310) 734-7296, (310) 786-7417, (310) 849-7185, (310) 854-0299, (310) 854-7700, (310) 855-8044, (323) 253-6747, (323) 345-4525, (323) 507-3943, (323) 650-0475, (323) 937-0355, (424) 407-4606, (424) 542-7730, (424) 667-0036, (424) 722-8502, (747) 724-3595</t>
         </is>
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>https://instagram.com/westimewatches, https://facebook.com/Westime</t>
+          <t>https://instagram.com/affluette_, https://instagram.com/alchemy43, https://facebook.com/alchemy43, https://instagram.com/andreas.fashions, https://facebook.com/andreasfashions, https://instagram.com/bbcmcafe, https://instagram.com/bootstarusa, https://facebook.com/Boot-Star-106137407505929, https://instagram.com/bossanovarestaurant, https://facebook.com/BossaNovaLA, https://instagram.com/charliechoukair/, https://instagram.com/cristallini_official, https://facebook.com/CRISTALLINIOfficial, https://instagram.com/architectureforsale/, https://instagram.com/cupidlipsofbeverlyhills, https://facebook.com/profile.php?id=100083257576786, https://instagram.com/dandeutschoo, https://instagram.com/davidorgell, https://instagram.com/drybarshopsus, https://facebook.com/thedrybar, https://instagram.com/elainekimcollection/, https://instagram.com/entouragebarbershop, https://instagram.com/fpjourneofficial, https://instagram.com/guyfloralstudio, https://instagram.com/hotpilates, https://facebook.com/Hot-Pilates-1806940676211478, https://instagram.com/kojitoyodasalon, https://instagram.com/metaclinic/, https://instagram.com/milamoursiskincare, https://instagram.com/olehenriksenspa/, https://instagram.com/oliverpeoples, https://instagram.com/osklo.la, https://instagram.com/philippressjeweler, https://instagram.com/puravidamiami, https://facebook.com/PuraVidaMiami, https://instagram.com/queenbnailsalon_sunsetplaza, https://instagram.com/andywarholrevolvergallery, https://instagram.com/rondorff, https://instagram.com/saltiegirlla, https://instagram.com/samira13jewelry, https://instagram.com/sargondental, https://facebook.com/sargonlazarofdds, https://instagram.com/serenityonsunset, https://instagram.com/sheilaonsunset, https://instagram.com/solatesbysamantha, https://instagram.com/sousla_official, https://instagram.com/sunsetkidsla, https://instagram.com/theoppenheimgroup, https://facebook.com/theoppenheimgroup, https://instagram.com/whitegloveestates, https://instagram.com/xrcyze_ny, https://facebook.com/xrcycle, https://instagram.com/sunsetplazaca, https://facebook.com/SunsetPlazaCA</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Wrist Aficionado Beverly Hills</t>
+          <t>Westime Beverly Hills</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -38409,37 +38405,37 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>(310) 388-8201</t>
+          <t>(310) 888-8880</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>sales@wristaficionado.com</t>
+          <t>contact@westime.com</t>
         </is>
       </c>
       <c r="F340" t="inlineStr"/>
-      <c r="G340" t="inlineStr"/>
-      <c r="H340" t="inlineStr"/>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>Greg Simonian</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
       <c r="I340" s="2" t="inlineStr">
         <is>
-          <t>https://wristaficionado.com</t>
+          <t>https://westime.com</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>9850 Wilshire Blvd, Beverly Hills, CA 90210, United States</t>
-        </is>
-      </c>
-      <c r="K340" t="inlineStr">
-        <is>
-          <t>Beverly Hills</t>
-        </is>
-      </c>
-      <c r="L340" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
+          <t>206 N Rodeo Dr, Beverly Hills, CA 90210, United States</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr"/>
+      <c r="L340" t="inlineStr"/>
       <c r="M340" t="inlineStr">
         <is>
           <t>Beverly Hills, CA</t>
@@ -38451,19 +38447,19 @@
         </is>
       </c>
       <c r="O340" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="P340" t="n">
-        <v>101</v>
+        <v>274</v>
       </c>
       <c r="Q340" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Wrist+Aficionado+Beverly+Hills/data=!4m7!3m6!1s0x80c2bb67e5181fcf:0xde9cbdbb118a155c!8m2!3d34.0667288!4d-118.4113018!16s%2Fg%2F11v12tg_x0!19sChIJzx8Y5We7woARXBWKEbu9nN4</t>
+          <t>https://www.google.com/maps/place/Westime+Beverly+Hills/data=!4m7!3m6!1s0x80c2bc0ed6429065:0x2c357ea8ffa51b1f!8m2!3d34.067375!4d-118.4003799!16s%2Fg%2F11cfj2mg2!19sChIJZZBC1g68woARHxul_6h-NSw</t>
         </is>
       </c>
       <c r="R340" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-2017</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-1987</t>
         </is>
       </c>
       <c r="S340" t="inlineStr">
@@ -38473,13 +38469,13 @@
       </c>
       <c r="T340" s="2" t="inlineStr">
         <is>
-          <t>https://wristaficionado.com/</t>
+          <t>https://westime.com/contact</t>
         </is>
       </c>
       <c r="U340" t="inlineStr"/>
       <c r="V340" t="inlineStr">
         <is>
-          <t>2026-10-14T01:43:17+05:30</t>
+          <t>2026-10-14T01:39:33+05:30</t>
         </is>
       </c>
       <c r="W340" t="inlineStr"/>
@@ -38490,17 +38486,125 @@
       <c r="Z340" t="inlineStr"/>
       <c r="AA340" t="inlineStr">
         <is>
+          <t>(786) 347-5353, (858) 459-2222</t>
+        </is>
+      </c>
+      <c r="AB340" t="inlineStr">
+        <is>
+          <t>https://instagram.com/westimewatches, https://facebook.com/Westime</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Wrist Aficionado Beverly Hills</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Watch store</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>(310) 388-8201</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>sales@wristaficionado.com</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr"/>
+      <c r="G341" t="inlineStr"/>
+      <c r="H341" t="inlineStr"/>
+      <c r="I341" s="2" t="inlineStr">
+        <is>
+          <t>https://wristaficionado.com</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>9850 Wilshire Blvd, Beverly Hills, CA 90210, United States</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Beverly Hills</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>Beverly Hills, CA</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O341" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P341" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Wrist+Aficionado+Beverly+Hills/data=!4m7!3m6!1s0x80c2bb67e5181fcf:0xde9cbdbb118a155c!8m2!3d34.0667288!4d-118.4113018!16s%2Fg%2F11v12tg_x0!19sChIJzx8Y5We7woARXBWKEbu9nN4</t>
+        </is>
+      </c>
+      <c r="R341" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, custom-design, since-2017</t>
+        </is>
+      </c>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T341" s="2" t="inlineStr">
+        <is>
+          <t>https://wristaficionado.com/</t>
+        </is>
+      </c>
+      <c r="U341" t="inlineStr"/>
+      <c r="V341" t="inlineStr">
+        <is>
+          <t>2026-10-14T01:43:17+05:30</t>
+        </is>
+      </c>
+      <c r="W341" t="inlineStr"/>
+      <c r="X341" t="inlineStr"/>
+      <c r="Y341" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z341" t="inlineStr"/>
+      <c r="AA341" t="inlineStr">
+        <is>
           <t>(305) 680-3735, (310) 861-3485, (646) 693-9384, (786) 889-6892</t>
         </is>
       </c>
-      <c r="AB340" t="inlineStr">
+      <c r="AB341" t="inlineStr">
         <is>
           <t>https://instagram.com/wristaficionado, https://instagram.com/wristaficionado/, https://facebook.com/shopwristaficionado, https://twitter.com/wristaficionado</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB340"/>
+  <autoFilter ref="A1:AB341"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId2"/>
@@ -39675,6 +39779,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I340" r:id="rId1171"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q340" r:id="rId1172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T340" r:id="rId1173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I341" r:id="rId1174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q341" r:id="rId1175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T341" r:id="rId1176"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -40393,15 +40500,15 @@
         <v>458</v>
       </c>
       <c r="C26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
@@ -40420,7 +40527,7 @@
         <v>11025</v>
       </c>
       <c r="C27" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -40428,7 +40535,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F27" t="n">
         <v>181</v>
@@ -40474,7 +40581,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3">
@@ -40546,7 +40653,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11">
@@ -40585,7 +40692,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T07:36:10+05:30</t>
+          <t>2026-10-14T07:56:26+05:30</t>
         </is>
       </c>
     </row>
@@ -40596,7 +40703,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3">

--- a/leadrun_jewelry/jewelry_qualified.xlsx
+++ b/leadrun_jewelry/jewelry_qualified.xlsx
@@ -40692,7 +40692,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T07:56:26+05:30</t>
+          <t>2026-10-14T08:16:40+05:30</t>
         </is>
       </c>
     </row>

--- a/leadrun_jewelry/jewelry_qualified.xlsx
+++ b/leadrun_jewelry/jewelry_qualified.xlsx
@@ -42300,7 +42300,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T09:31:15+05:30</t>
+          <t>2026-10-14T09:51:31+05:30</t>
         </is>
       </c>
     </row>

--- a/leadrun_jewelry/jewelry_qualified.xlsx
+++ b/leadrun_jewelry/jewelry_qualified.xlsx
@@ -42300,7 +42300,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T09:51:31+05:30</t>
+          <t>2026-10-14T10:11:46+05:30</t>
         </is>
       </c>
     </row>

--- a/leadrun_jewelry/jewelry_qualified.xlsx
+++ b/leadrun_jewelry/jewelry_qualified.xlsx
@@ -42300,7 +42300,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T10:11:46+05:30</t>
+          <t>2026-10-14T11:48:19+05:30</t>
         </is>
       </c>
     </row>

--- a/leadrun_jewelry/jewelry_qualified.xlsx
+++ b/leadrun_jewelry/jewelry_qualified.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qualified Leads'!$A$1:$AB$366</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qualified Leads'!$A$1:$AB$373</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB366"/>
+  <dimension ref="A1:AB373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -15085,9 +15085,13 @@
         </is>
       </c>
       <c r="Y130" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z130" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr"/>
       <c r="AB130" t="inlineStr">
         <is>
@@ -16154,12 +16158,24 @@
           <t>2026-10-13T16:46:50+05:30</t>
         </is>
       </c>
-      <c r="W140" t="inlineStr"/>
-      <c r="X140" t="inlineStr"/>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Paradise Jewelry, Paradise Jewelry and Watches</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL</t>
+        </is>
+      </c>
       <c r="Y140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z140" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>(305) 429-6189</t>
@@ -26617,11 +26633,11 @@
       </c>
       <c r="X233" t="inlineStr">
         <is>
-          <t>Dallas, TX, Denver, CO, Portland, OR, San Diego, CA, San Francisco, CA, San Jose, CA, Seattle, WA</t>
+          <t>Dallas, TX, Denver, CO, Orlando, FL, Portland, OR, San Diego, CA, San Francisco, CA, San Jose, CA, Seattle, WA</t>
         </is>
       </c>
       <c r="Y233" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Z233" t="inlineStr">
         <is>
@@ -26630,7 +26646,7 @@
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>(407) 704-0564, (415) 421-0920, (619) 226-3677, (808) 293-2980, (808) 327-1749, (808) 661-8042, (808) 886-5019, (831) 612-7320</t>
+          <t>(415) 421-0920, (619) 226-3677, (808) 293-2980, (808) 327-1749, (808) 661-8042, (808) 886-5019, (831) 612-7320</t>
         </is>
       </c>
       <c r="AB233" t="inlineStr">
@@ -36486,14 +36502,18 @@
           <t>2026-10-14T01:15:46+05:30</t>
         </is>
       </c>
-      <c r="W320" t="inlineStr"/>
+      <c r="W320" t="inlineStr">
+        <is>
+          <t>Kma Sunbelt Trading Corp</t>
+        </is>
+      </c>
       <c r="X320" t="inlineStr">
         <is>
-          <t>Tampa, FL</t>
+          <t>Orlando, FL, Tampa, FL</t>
         </is>
       </c>
       <c r="Y320" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Z320" t="inlineStr">
         <is>
@@ -36502,7 +36522,7 @@
       </c>
       <c r="AA320" t="inlineStr">
         <is>
-          <t>(239) 364-1799, (352) 681-4550, (407) 770-5991, (407) 862-8990, (407) 903-9494, (772) 408-4640, (863) 226-4400, (912) 354-4344, (941) 278-3900</t>
+          <t>(239) 364-1799, (352) 681-4550, (407) 770-5991, (407) 862-8990, (772) 408-4640, (863) 226-4400, (912) 354-4344, (941) 278-3900</t>
         </is>
       </c>
       <c r="AB320" t="inlineStr">
@@ -39998,27 +40018,27 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Michele's Estate Jewelry and Silver</t>
+          <t>Dean Fredrick</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Estate &amp; antique jewelry</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Gold dealer</t>
+          <t>Jewelers, Watches</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>(512) 263-3235</t>
+          <t>(512) 493-0943</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>haileymicheles925@gmail.com</t>
+          <t>info@deanfredrick.com</t>
         </is>
       </c>
       <c r="F353" t="inlineStr"/>
@@ -40026,12 +40046,12 @@
       <c r="H353" t="inlineStr"/>
       <c r="I353" s="2" t="inlineStr">
         <is>
-          <t>https://www.michelessilver.com</t>
+          <t>https://deanfredrick.com</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>2808 Bee Caves Rd Ste B, Rollingwood, TX 78746, United States</t>
+          <t>1623 S Lamar Blvd, Austin, TX 78704</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
@@ -40051,23 +40071,19 @@
       </c>
       <c r="N353" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O353" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="P353" t="n">
-        <v>59</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr"/>
+      <c r="P353" t="inlineStr"/>
       <c r="Q353" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Michele%27s+Estate+Jewelry+and+Silver/data=!4m7!3m6!1s0x865b4aca3ee44ebd:0xefa578b7d2f7b05d!8m2!3d30.2714292!4d-97.7894928!16s%2Fg%2F1tfv5k0z!19sChIJvU7kPspKW4YRXbD30rd4pe8</t>
+          <t>https://www.yellowpages.com/austin-tx/mip/dean-fredrick-531224451</t>
         </is>
       </c>
       <c r="R353" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, since-1975</t>
+          <t>2 of 3, role-email, direct-line, gia, custom-design</t>
         </is>
       </c>
       <c r="S353" t="inlineStr">
@@ -40077,60 +40093,56 @@
       </c>
       <c r="T353" s="2" t="inlineStr">
         <is>
-          <t>https://www.michelessilver.com/</t>
+          <t>https://deanfredrick.com/</t>
         </is>
       </c>
       <c r="U353" t="inlineStr"/>
       <c r="V353" t="inlineStr">
         <is>
-          <t>2026-10-14T12:01:57+05:30</t>
-        </is>
-      </c>
-      <c r="W353" t="inlineStr">
-        <is>
-          <t>Michele's</t>
-        </is>
-      </c>
+          <t>2026-10-14T12:10:05+05:30</t>
+        </is>
+      </c>
+      <c r="W353" t="inlineStr"/>
       <c r="X353" t="inlineStr"/>
       <c r="Y353" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z353" t="inlineStr"/>
       <c r="AA353" t="inlineStr">
         <is>
-          <t>(970) 949-7717</t>
+          <t>(830) 522-2425</t>
         </is>
       </c>
       <c r="AB353" t="inlineStr">
         <is>
-          <t>https://facebook.com/Micheles-Estate-Jewelry-and-Silver-116505548409569, https://instagram.com/michelesjewelryandsilver</t>
+          <t>https://twitter.com/deanfredrick, https://facebook.com/deanfredrickjewelry%20, https://instagram.com/deanfredrickcustom, https://facebook.com/deanfredrickjewelry</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Alexander Design</t>
+          <t>Marc Robinson Jewelers</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers, Jewelry Designers</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>(408) 998-4539</t>
+          <t>(512) 922-6351</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>sales@alexander-dm.com</t>
+          <t>marketing@marcrobinsonjewelers.com</t>
         </is>
       </c>
       <c r="F354" t="inlineStr"/>
@@ -40138,44 +40150,48 @@
       <c r="H354" t="inlineStr"/>
       <c r="I354" s="2" t="inlineStr">
         <is>
-          <t>https://alexander-dm.com</t>
+          <t>https://marcrobinsonjewelers.com</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>1111 Story Rd Ste 1063, San Jose, CA 95122</t>
+          <t>2901 S Capital of Texas Highway, Suite J10A, Austin, TX 78746</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t>San Jose</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O354" t="inlineStr"/>
-      <c r="P354" t="inlineStr"/>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="O354" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P354" t="n">
+        <v>61</v>
+      </c>
       <c r="Q354" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/san-jose-ca/mip/alexander-design-692537</t>
+          <t>https://www.bbb.org/us/tx/austin/profile/jewelry-stores/marc-robinson-jewelers-0825-1000220199</t>
         </is>
       </c>
       <c r="R354" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-2001</t>
+          <t>2 of 3, role-email, direct-line, bench, custom-design</t>
         </is>
       </c>
       <c r="S354" t="inlineStr">
@@ -40185,52 +40201,60 @@
       </c>
       <c r="T354" s="2" t="inlineStr">
         <is>
-          <t>https://www.alexander-dm.com/</t>
+          <t>https://www.marcrobinsonjewelers.com/</t>
         </is>
       </c>
       <c r="U354" t="inlineStr"/>
       <c r="V354" t="inlineStr">
         <is>
-          <t>2026-10-14T12:05:25+05:30</t>
-        </is>
-      </c>
-      <c r="W354" t="inlineStr"/>
+          <t>2026-10-14T12:08:33+05:30</t>
+        </is>
+      </c>
+      <c r="W354" t="inlineStr">
+        <is>
+          <t>Marc Robinson Jewelers Barton Creek Mall</t>
+        </is>
+      </c>
       <c r="X354" t="inlineStr"/>
       <c r="Y354" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z354" t="inlineStr"/>
       <c r="AA354" t="inlineStr">
         <is>
-          <t>(213) 649-1924</t>
-        </is>
-      </c>
-      <c r="AB354" t="inlineStr"/>
+          <t>(512) 627-5133, (512) 868-0300, (903) 201-0249</t>
+        </is>
+      </c>
+      <c r="AB354" t="inlineStr">
+        <is>
+          <t>https://facebook.com/MarcRobinsonJewelers, https://instagram.com/marcrobinsonjeweler, https://instagram.com/marcrobinsonbartoncreekmall</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Ari Diamonds</t>
+          <t>Michele's Estate Jewelry and Silver</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Jewelers, Diamonds-Wholesale, Jewelers-Wholesale &amp; Manufacturers</t>
+          <t>Gold dealer</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>(801) 255-8992</t>
+          <t>(512) 263-3235</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>panna.aridiamonds@gmail.com</t>
+          <t>haileymicheles925@gmail.com</t>
         </is>
       </c>
       <c r="F355" t="inlineStr"/>
@@ -40238,48 +40262,48 @@
       <c r="H355" t="inlineStr"/>
       <c r="I355" s="2" t="inlineStr">
         <is>
-          <t>https://www.aridiamonds.com</t>
+          <t>https://www.michelessilver.com</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>807 E Fort Union Blvd, Midvale, UT 84047</t>
+          <t>2808 Bee Caves Rd Ste B, Rollingwood, TX 78746, United States</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t>Midvale</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>UT</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>Google Maps</t>
         </is>
       </c>
       <c r="O355" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="P355" t="n">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="Q355" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/midvale-ut/mip/ari-diamonds-23948160</t>
+          <t>https://www.google.com/maps/place/Michele%27s+Estate+Jewelry+and+Silver/data=!4m7!3m6!1s0x865b4aca3ee44ebd:0xefa578b7d2f7b05d!8m2!3d30.2714292!4d-97.7894928!16s%2Fg%2F1tfv5k0z!19sChIJvU7kPspKW4YRXbD30rd4pe8</t>
         </is>
       </c>
       <c r="R355" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design, since-1994</t>
+          <t>2 of 3, direct-line, since-1975</t>
         </is>
       </c>
       <c r="S355" t="inlineStr">
@@ -40289,56 +40313,60 @@
       </c>
       <c r="T355" s="2" t="inlineStr">
         <is>
-          <t>https://www.aridiamonds.com/</t>
+          <t>https://www.michelessilver.com/</t>
         </is>
       </c>
       <c r="U355" t="inlineStr"/>
       <c r="V355" t="inlineStr">
         <is>
-          <t>2026-10-14T12:03:18+05:30</t>
-        </is>
-      </c>
-      <c r="W355" t="inlineStr"/>
+          <t>2026-10-14T12:01:57+05:30</t>
+        </is>
+      </c>
+      <c r="W355" t="inlineStr">
+        <is>
+          <t>Michele's</t>
+        </is>
+      </c>
       <c r="X355" t="inlineStr"/>
       <c r="Y355" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z355" t="inlineStr"/>
       <c r="AA355" t="inlineStr">
         <is>
-          <t>(801) 776-8830</t>
+          <t>(970) 949-7717</t>
         </is>
       </c>
       <c r="AB355" t="inlineStr">
         <is>
-          <t>https://instagram.com/aridiamondsutah, https://facebook.com/aridiamonds</t>
+          <t>https://facebook.com/Micheles-Estate-Jewelry-and-Silver-116505548409569, https://instagram.com/michelesjewelryandsilver</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Jewelry By Tommy</t>
+          <t>The Jewel of Art Dance Studio</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers, Diamonds</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>(216) 464-6356</t>
+          <t>(210) 878-4089</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>greg@jewelrybytommy.com</t>
+          <t>info@jewelofartdance.com</t>
         </is>
       </c>
       <c r="F356" t="inlineStr"/>
@@ -40346,27 +40374,27 @@
       <c r="H356" t="inlineStr"/>
       <c r="I356" s="2" t="inlineStr">
         <is>
-          <t>https://www.jewelrybytommy.com</t>
+          <t>https://jewelofartdance.com</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>27600 Chagrin Blvd Ste 110, Woodmere, OH 44122</t>
+          <t>1909 Fredericksburg Rd, San Antonio, TX 78201</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t>Woodmere</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Cleveland, OH</t>
+          <t>San Antonio, TX</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -40378,12 +40406,12 @@
       <c r="P356" t="inlineStr"/>
       <c r="Q356" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/woodmere-oh/mip/jewelry-by-tommy-479852454</t>
+          <t>https://www.yellowpages.com/san-antonio-tx/mip/the-jewel-of-art-dance-studio-547319903</t>
         </is>
       </c>
       <c r="R356" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design</t>
+          <t>2 of 3, role-email, direct-line</t>
         </is>
       </c>
       <c r="S356" t="inlineStr">
@@ -40393,13 +40421,13 @@
       </c>
       <c r="T356" s="2" t="inlineStr">
         <is>
-          <t>https://jewelrybytommy.com/</t>
+          <t>https://jewelofartdance.com/</t>
         </is>
       </c>
       <c r="U356" t="inlineStr"/>
       <c r="V356" t="inlineStr">
         <is>
-          <t>2026-10-14T12:01:03+05:30</t>
+          <t>2026-10-14T12:12:32+05:30</t>
         </is>
       </c>
       <c r="W356" t="inlineStr"/>
@@ -40410,39 +40438,39 @@
       <c r="Z356" t="inlineStr"/>
       <c r="AA356" t="inlineStr">
         <is>
-          <t>(440) 413-5888</t>
+          <t>(210) 639-3756</t>
         </is>
       </c>
       <c r="AB356" t="inlineStr">
         <is>
-          <t>https://facebook.com/JewelrybyTommy</t>
+          <t>https://facebook.com/jewelofartdance, https://twitter.com/jewelofartdance, https://instagram.com/jewelofartdance</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Pearls Hope, Inc</t>
+          <t>Alexander Design</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers, Jewelry Designers</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>(440) 249-7000</t>
+          <t>(408) 998-4539</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>intake@pearlshope.com</t>
+          <t>sales@alexander-dm.com</t>
         </is>
       </c>
       <c r="F357" t="inlineStr"/>
@@ -40450,27 +40478,27 @@
       <c r="H357" t="inlineStr"/>
       <c r="I357" s="2" t="inlineStr">
         <is>
-          <t>https://pearlshope.com</t>
+          <t>https://alexander-dm.com</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>3659 Green Rd, Beachwood, OH 44122</t>
+          <t>1111 Story Rd Ste 1063, San Jose, CA 95122</t>
         </is>
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t>Beachwood</t>
+          <t>San Jose</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Cleveland, OH</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -40482,12 +40510,12 @@
       <c r="P357" t="inlineStr"/>
       <c r="Q357" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/beachwood-oh/mip/pearls-hope-inc-580059164</t>
+          <t>https://www.yellowpages.com/san-jose-ca/mip/alexander-design-692537</t>
         </is>
       </c>
       <c r="R357" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-2001</t>
         </is>
       </c>
       <c r="S357" t="inlineStr">
@@ -40497,13 +40525,13 @@
       </c>
       <c r="T357" s="2" t="inlineStr">
         <is>
-          <t>https://pearlshope.com/</t>
+          <t>https://www.alexander-dm.com/</t>
         </is>
       </c>
       <c r="U357" t="inlineStr"/>
       <c r="V357" t="inlineStr">
         <is>
-          <t>2026-10-14T12:00:59+05:30</t>
+          <t>2026-10-14T12:05:25+05:30</t>
         </is>
       </c>
       <c r="W357" t="inlineStr"/>
@@ -40514,7 +40542,7 @@
       <c r="Z357" t="inlineStr"/>
       <c r="AA357" t="inlineStr">
         <is>
-          <t>(216) 452-0082, (614) 781-0400, (937) 222-0002</t>
+          <t>(213) 649-1924</t>
         </is>
       </c>
       <c r="AB357" t="inlineStr"/>
@@ -40522,7 +40550,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Dakota Watch Co</t>
+          <t>Kumar Jewelers</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -40532,53 +40560,45 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Jewelers, Watch Repair, Watches</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>(317) 624-9115</t>
+          <t>(408) 246-0850</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>customerservice@dakotawatch.com</t>
+          <t>contact@kumarjewelers.com</t>
         </is>
       </c>
       <c r="F358" t="inlineStr"/>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>Albert Cooper</t>
-        </is>
-      </c>
-      <c r="H358" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
+      <c r="G358" t="inlineStr"/>
+      <c r="H358" t="inlineStr"/>
       <c r="I358" s="2" t="inlineStr">
         <is>
-          <t>https://dakotawatch.com</t>
+          <t>https://kumarjewelers.com</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>49 W Maryland St Ste 142, Indianapolis, IN 46204</t>
+          <t>3418 El Camino Real, Santa Clara, CA 95051</t>
         </is>
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Indianapolis, IN</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -40586,16 +40606,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O358" t="inlineStr"/>
-      <c r="P358" t="inlineStr"/>
+      <c r="O358" t="n">
+        <v>5</v>
+      </c>
+      <c r="P358" t="n">
+        <v>1</v>
+      </c>
       <c r="Q358" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/indianapolis-in/mip/dakota-watch-co-25573661</t>
+          <t>https://www.yellowpages.com/santa-clara-ca/mip/kumar-jewelers-7772087</t>
         </is>
       </c>
       <c r="R358" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S358" t="inlineStr">
@@ -40605,68 +40629,56 @@
       </c>
       <c r="T358" s="2" t="inlineStr">
         <is>
-          <t>https://dakotawatch.com/</t>
+          <t>https://www.kumarjewelers.com/</t>
         </is>
       </c>
       <c r="U358" t="inlineStr"/>
       <c r="V358" t="inlineStr">
         <is>
-          <t>2026-10-14T12:04:54+05:30</t>
-        </is>
-      </c>
-      <c r="W358" t="inlineStr">
-        <is>
-          <t>Dakota Watch Company, Cooper &amp; Co Inc</t>
-        </is>
-      </c>
-      <c r="X358" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, Pittsburgh, PA</t>
-        </is>
-      </c>
+          <t>2026-10-14T12:17:16+05:30</t>
+        </is>
+      </c>
+      <c r="W358" t="inlineStr"/>
+      <c r="X358" t="inlineStr"/>
       <c r="Y358" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z358" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z358" t="inlineStr"/>
       <c r="AA358" t="inlineStr">
         <is>
-          <t>(513) 879-3681</t>
+          <t>(510) 713-1040, (925) 248-2280</t>
         </is>
       </c>
       <c r="AB358" t="inlineStr">
         <is>
-          <t>https://facebook.com/profile.php?id=61550829076826, https://instagram.com/dakotawatch_co</t>
+          <t>https://facebook.com/kumarjewelers, https://instagram.com/kumarjewelers</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Indianapolis Crown Jewel Inc</t>
+          <t>Sacramento Watch &amp; Jewelry Service</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Jewelry repair / goldsmith</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Repairing, Watch Repair</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>(317) 602-3563</t>
+          <t>(916) 979-9106</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>crownjewel.cj@gmail.com</t>
+          <t>steve@sacramentowatchshop.com</t>
         </is>
       </c>
       <c r="F359" t="inlineStr"/>
@@ -40674,27 +40686,27 @@
       <c r="H359" t="inlineStr"/>
       <c r="I359" s="2" t="inlineStr">
         <is>
-          <t>https://www.indycrownjewel.com</t>
+          <t>https://sacramentowatchshop.com</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>3760 N Emerson Ave, Indianapolis, IN 46218</t>
+          <t>1620 Fulton Ave, Sacramento, CA 95825</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Indianapolis, IN</t>
+          <t>Sacramento, CA</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -40706,12 +40718,12 @@
       <c r="P359" t="inlineStr"/>
       <c r="Q359" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/indianapolis-in/mip/indianapolis-crown-jewel-inc-545777926</t>
+          <t>https://www.yellowpages.com/sacramento-ca/mip/sacramento-watch-jewelry-service-519958764</t>
         </is>
       </c>
       <c r="R359" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design</t>
+          <t>2 of 3, direct-line, since-1995</t>
         </is>
       </c>
       <c r="S359" t="inlineStr">
@@ -40721,40 +40733,36 @@
       </c>
       <c r="T359" s="2" t="inlineStr">
         <is>
-          <t>https://www.indycrownjewel.com/</t>
+          <t>https://sacramentowatchshop.com/</t>
         </is>
       </c>
       <c r="U359" t="inlineStr"/>
       <c r="V359" t="inlineStr">
         <is>
-          <t>2026-10-14T12:04:25+05:30</t>
-        </is>
-      </c>
-      <c r="W359" t="inlineStr">
-        <is>
-          <t>Indy Crown Jewel Inc.</t>
-        </is>
-      </c>
+          <t>2026-10-14T12:07:36+05:30</t>
+        </is>
+      </c>
+      <c r="W359" t="inlineStr"/>
       <c r="X359" t="inlineStr"/>
       <c r="Y359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z359" t="inlineStr"/>
       <c r="AA359" t="inlineStr">
         <is>
-          <t>(317) 228-7485</t>
+          <t>(916) 550-1863</t>
         </is>
       </c>
       <c r="AB359" t="inlineStr">
         <is>
-          <t>https://facebook.com/indycrownjewelcollection, https://instagram.com/indycrownjewel</t>
+          <t>https://facebook.com/sacramentowatchshop, https://facebook.com/The-Watch-Shop-727641780765411</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Jewelers Boutique Inc.</t>
+          <t>Ari Diamonds</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -40764,17 +40772,17 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Buyers, Jewelry Repairing, Jewelry Designers, Watches, Diamonds</t>
+          <t>Jewelers, Diamonds-Wholesale, Jewelers-Wholesale &amp; Manufacturers</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>(317) 983-6528</t>
+          <t>(801) 255-8992</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>jewelersboutique@att.net</t>
+          <t>panna.aridiamonds@gmail.com</t>
         </is>
       </c>
       <c r="F360" t="inlineStr"/>
@@ -40782,27 +40790,27 @@
       <c r="H360" t="inlineStr"/>
       <c r="I360" s="2" t="inlineStr">
         <is>
-          <t>https://jewelersboutique.us</t>
+          <t>https://www.aridiamonds.com</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>3320 Madison Ave, Indianapolis, IN 46227</t>
+          <t>807 E Fort Union Blvd, Midvale, UT 84047</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Midvale</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>UT</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Indianapolis, IN</t>
+          <t>Salt Lake City, UT</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -40814,16 +40822,16 @@
         <v>5</v>
       </c>
       <c r="P360" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q360" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/indianapolis-in/mip/jewelers-boutique-inc-8272936</t>
+          <t>https://www.yellowpages.com/midvale-ut/mip/ari-diamonds-23948160</t>
         </is>
       </c>
       <c r="R360" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design</t>
+          <t>2 of 3, direct-line, custom-design, since-1994</t>
         </is>
       </c>
       <c r="S360" t="inlineStr">
@@ -40833,13 +40841,13 @@
       </c>
       <c r="T360" s="2" t="inlineStr">
         <is>
-          <t>https://jewelersboutique.us/</t>
+          <t>https://www.aridiamonds.com/</t>
         </is>
       </c>
       <c r="U360" t="inlineStr"/>
       <c r="V360" t="inlineStr">
         <is>
-          <t>2026-10-14T12:04:18+05:30</t>
+          <t>2026-10-14T12:03:18+05:30</t>
         </is>
       </c>
       <c r="W360" t="inlineStr"/>
@@ -40850,19 +40858,19 @@
       <c r="Z360" t="inlineStr"/>
       <c r="AA360" t="inlineStr">
         <is>
-          <t>(317) 788-7679</t>
+          <t>(801) 776-8830</t>
         </is>
       </c>
       <c r="AB360" t="inlineStr">
         <is>
-          <t>https://facebook.com/JewelersBoutique</t>
+          <t>https://instagram.com/aridiamondsutah, https://facebook.com/aridiamonds</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Mason Jewelers Inc</t>
+          <t>Jewelry By Tommy</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -40872,17 +40880,17 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Jewelers, Appraisers</t>
+          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers, Diamonds</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>(317) 839-3202</t>
+          <t>(216) 464-6356</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>masonjewelers1957@gmail.com</t>
+          <t>greg@jewelrybytommy.com</t>
         </is>
       </c>
       <c r="F361" t="inlineStr"/>
@@ -40890,27 +40898,27 @@
       <c r="H361" t="inlineStr"/>
       <c r="I361" s="2" t="inlineStr">
         <is>
-          <t>https://www.masonjewelersco.com</t>
+          <t>https://www.jewelrybytommy.com</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>1822 E Main St, Plainfield, IN 46168</t>
+          <t>27600 Chagrin Blvd Ste 110, Woodmere, OH 44122</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>Plainfield</t>
+          <t>Woodmere</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Indianapolis, IN</t>
+          <t>Cleveland, OH</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -40922,12 +40930,12 @@
       <c r="P361" t="inlineStr"/>
       <c r="Q361" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/plainfield-in/mip/mason-jewelers-inc-705208</t>
+          <t>https://www.yellowpages.com/woodmere-oh/mip/jewelry-by-tommy-479852454</t>
         </is>
       </c>
       <c r="R361" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, since-1957</t>
+          <t>2 of 3, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S361" t="inlineStr">
@@ -40937,13 +40945,13 @@
       </c>
       <c r="T361" s="2" t="inlineStr">
         <is>
-          <t>https://www.masonjewelersco.com/</t>
+          <t>https://jewelrybytommy.com/</t>
         </is>
       </c>
       <c r="U361" t="inlineStr"/>
       <c r="V361" t="inlineStr">
         <is>
-          <t>2026-10-14T12:05:07+05:30</t>
+          <t>2026-10-14T12:01:03+05:30</t>
         </is>
       </c>
       <c r="W361" t="inlineStr"/>
@@ -40954,75 +40962,67 @@
       <c r="Z361" t="inlineStr"/>
       <c r="AA361" t="inlineStr">
         <is>
-          <t>(765) 653-5012</t>
+          <t>(440) 413-5888</t>
         </is>
       </c>
       <c r="AB361" t="inlineStr">
         <is>
-          <t>https://facebook.com/masonjewelers.net, https://facebook.com/Masonjewelersco</t>
+          <t>https://facebook.com/JewelrybyTommy</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Moyer Fine Jewelers</t>
+          <t>Pearls Hope, Inc</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Jewelers, Diamond Buyers, Watches</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>(317) 844-9003</t>
+          <t>(440) 249-7000</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>online@moyerfj.com</t>
+          <t>intake@pearlshope.com</t>
         </is>
       </c>
       <c r="F362" t="inlineStr"/>
-      <c r="G362" t="inlineStr">
-        <is>
-          <t>Dan Moyer</t>
-        </is>
-      </c>
-      <c r="H362" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
+      <c r="G362" t="inlineStr"/>
+      <c r="H362" t="inlineStr"/>
       <c r="I362" s="2" t="inlineStr">
         <is>
-          <t>https://moyerfinejewelers.com</t>
+          <t>https://pearlshope.com</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>14727 Thatcher Ln, Carmel, IN 46032</t>
+          <t>3659 Green Rd, Beachwood, OH 44122</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t>Carmel</t>
+          <t>Beachwood</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Indianapolis, IN</t>
+          <t>Cleveland, OH</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -41034,12 +41034,12 @@
       <c r="P362" t="inlineStr"/>
       <c r="Q362" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/carmel-in/mip/moyer-fine-jewelers-7900799</t>
+          <t>https://www.yellowpages.com/beachwood-oh/mip/pearls-hope-inc-580059164</t>
         </is>
       </c>
       <c r="R362" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, bench, custom-design</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S362" t="inlineStr">
@@ -41049,13 +41049,13 @@
       </c>
       <c r="T362" s="2" t="inlineStr">
         <is>
-          <t>https://www.moyerfinejewelers.com/pages/contact-us</t>
+          <t>https://pearlshope.com/</t>
         </is>
       </c>
       <c r="U362" t="inlineStr"/>
       <c r="V362" t="inlineStr">
         <is>
-          <t>2026-10-14T12:05:12+05:30</t>
+          <t>2026-10-14T12:00:59+05:30</t>
         </is>
       </c>
       <c r="W362" t="inlineStr"/>
@@ -41066,67 +41066,71 @@
       <c r="Z362" t="inlineStr"/>
       <c r="AA362" t="inlineStr">
         <is>
-          <t>(317) 785-1080, (317) 785-1138</t>
-        </is>
-      </c>
-      <c r="AB362" t="inlineStr">
-        <is>
-          <t>https://instagram.com/moyerfinejewelers, https://facebook.com/moyerfinejewelers, https://twitter.com/MoyerJewelers</t>
-        </is>
-      </c>
+          <t>(216) 452-0082, (614) 781-0400, (937) 222-0002</t>
+        </is>
+      </c>
+      <c r="AB362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Caesar's Designs</t>
+          <t>Dakota Watch Co</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Designers, Jewelry Repairing</t>
+          <t>Jewelers, Watch Repair, Watches</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>(412) 621-0345</t>
+          <t>(317) 624-9115</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>caesar@caesarsdesigns.com</t>
+          <t>customerservice@dakotawatch.com</t>
         </is>
       </c>
       <c r="F363" t="inlineStr"/>
-      <c r="G363" t="inlineStr"/>
-      <c r="H363" t="inlineStr"/>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>Albert Cooper</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="I363" s="2" t="inlineStr">
         <is>
-          <t>https://www.caesarsdesigns.com</t>
+          <t>https://dakotawatch.com</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>5413 Walnut St, Pittsburgh, PA 15232</t>
+          <t>49 W Maryland St Ste 142, Indianapolis, IN 46204</t>
         </is>
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Indianapolis, IN</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -41138,12 +41142,12 @@
       <c r="P363" t="inlineStr"/>
       <c r="Q363" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/pittsburgh-pa/mip/caesars-designs-9528656</t>
+          <t>https://www.yellowpages.com/indianapolis-in/mip/dakota-watch-co-25573661</t>
         </is>
       </c>
       <c r="R363" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design</t>
+          <t>2 of 3, role-email, direct-line</t>
         </is>
       </c>
       <c r="S363" t="inlineStr">
@@ -41153,56 +41157,68 @@
       </c>
       <c r="T363" s="2" t="inlineStr">
         <is>
-          <t>https://www.caesarsdesigns.com/</t>
+          <t>https://dakotawatch.com/</t>
         </is>
       </c>
       <c r="U363" t="inlineStr"/>
       <c r="V363" t="inlineStr">
         <is>
-          <t>2026-10-14T12:05:19+05:30</t>
-        </is>
-      </c>
-      <c r="W363" t="inlineStr"/>
-      <c r="X363" t="inlineStr"/>
+          <t>2026-10-14T12:04:54+05:30</t>
+        </is>
+      </c>
+      <c r="W363" t="inlineStr">
+        <is>
+          <t>Dakota Watch Company, Cooper &amp; Co Inc</t>
+        </is>
+      </c>
+      <c r="X363" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, Pittsburgh, PA</t>
+        </is>
+      </c>
       <c r="Y363" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z363" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Z363" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA363" t="inlineStr">
         <is>
-          <t>(412) 400-8582</t>
+          <t>(513) 879-3681</t>
         </is>
       </c>
       <c r="AB363" t="inlineStr">
         <is>
-          <t>https://facebook.com/CaesarsDesignsCreations, https://instagram.com/caesarsdesigns</t>
+          <t>https://facebook.com/profile.php?id=61550829076826, https://instagram.com/dakotawatch_co</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Custom Jewelry</t>
+          <t>Indianapolis Crown Jewel Inc</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Jewelry Repairing, Watch Repair</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>(813) 930-0380</t>
+          <t>(317) 602-3563</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>customhairtampabay@gmail.com</t>
+          <t>crownjewel.cj@gmail.com</t>
         </is>
       </c>
       <c r="F364" t="inlineStr"/>
@@ -41210,27 +41226,27 @@
       <c r="H364" t="inlineStr"/>
       <c r="I364" s="2" t="inlineStr">
         <is>
-          <t>https://customhairtampabay.com</t>
+          <t>https://www.indycrownjewel.com</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>11612 N Nebraska Ave, Tampa, FL 33612</t>
+          <t>3760 N Emerson Ave, Indianapolis, IN 46218</t>
         </is>
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t>Tampa</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Tampa, FL</t>
+          <t>Indianapolis, IN</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -41242,12 +41258,12 @@
       <c r="P364" t="inlineStr"/>
       <c r="Q364" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/tampa-fl/mip/custom-jewelry-481586478</t>
+          <t>https://www.yellowpages.com/indianapolis-in/mip/indianapolis-crown-jewel-inc-545777926</t>
         </is>
       </c>
       <c r="R364" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design, since-1969</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S364" t="inlineStr">
@@ -41257,56 +41273,60 @@
       </c>
       <c r="T364" s="2" t="inlineStr">
         <is>
-          <t>https://www.customhairtampabay.com/</t>
+          <t>https://www.indycrownjewel.com/</t>
         </is>
       </c>
       <c r="U364" t="inlineStr"/>
       <c r="V364" t="inlineStr">
         <is>
-          <t>2026-10-14T12:02:15+05:30</t>
-        </is>
-      </c>
-      <c r="W364" t="inlineStr">
-        <is>
-          <t>Janas Jewlery</t>
-        </is>
-      </c>
+          <t>2026-10-14T12:04:25+05:30</t>
+        </is>
+      </c>
+      <c r="W364" t="inlineStr"/>
       <c r="X364" t="inlineStr"/>
       <c r="Y364" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z364" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Z364" t="inlineStr">
+        <is>
+          <t>shared-switchboard</t>
+        </is>
+      </c>
       <c r="AA364" t="inlineStr">
         <is>
-          <t>(727) 725-1052, (813) 651-9484, (813) 932-5327</t>
-        </is>
-      </c>
-      <c r="AB364" t="inlineStr"/>
+          <t>(317) 228-7485</t>
+        </is>
+      </c>
+      <c r="AB364" t="inlineStr">
+        <is>
+          <t>https://facebook.com/indycrownjewelcollection, https://instagram.com/indycrownjewel</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>R Wolf Fine Jewelers</t>
+          <t>Mason Jewelers Inc</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Jewelers, Watches</t>
+          <t>Jewelers, Appraisers</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>(813) 816-2619</t>
+          <t>(317) 839-3202</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>rb.wolf@hotmail.com</t>
+          <t>masonjewelers1957@gmail.com</t>
         </is>
       </c>
       <c r="F365" t="inlineStr"/>
@@ -41314,27 +41334,27 @@
       <c r="H365" t="inlineStr"/>
       <c r="I365" s="2" t="inlineStr">
         <is>
-          <t>https://rwolfjewelry.com</t>
+          <t>https://www.masonjewelersco.com</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>100 S Ashley Dr, Tampa, FL 33602</t>
+          <t>1822 E Main St, Plainfield, IN 46168</t>
         </is>
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t>Tampa</t>
+          <t>Plainfield</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Tampa, FL</t>
+          <t>Indianapolis, IN</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -41342,16 +41362,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O365" t="inlineStr"/>
-      <c r="P365" t="inlineStr"/>
+      <c r="O365" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P365" t="n">
+        <v>355</v>
+      </c>
       <c r="Q365" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/tampa-fl/mip/r-wolf-fine-jewelers-543840292</t>
+          <t>https://www.yellowpages.com/plainfield-in/mip/mason-jewelers-inc-705208</t>
         </is>
       </c>
       <c r="R365" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, bench, custom-design</t>
+          <t>2 of 3, direct-line, since-1957</t>
         </is>
       </c>
       <c r="S365" t="inlineStr">
@@ -41361,36 +41385,40 @@
       </c>
       <c r="T365" s="2" t="inlineStr">
         <is>
-          <t>https://rwolfjewelry.com/</t>
+          <t>https://www.masonjewelersco.com/</t>
         </is>
       </c>
       <c r="U365" t="inlineStr"/>
       <c r="V365" t="inlineStr">
         <is>
-          <t>2026-10-14T12:02:02+05:30</t>
-        </is>
-      </c>
-      <c r="W365" t="inlineStr"/>
+          <t>2026-10-14T12:05:07+05:30</t>
+        </is>
+      </c>
+      <c r="W365" t="inlineStr">
+        <is>
+          <t>Mason Jewelers</t>
+        </is>
+      </c>
       <c r="X365" t="inlineStr"/>
       <c r="Y365" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z365" t="inlineStr"/>
       <c r="AA365" t="inlineStr">
         <is>
-          <t>(727) 275-0106</t>
+          <t>(765) 653-5012</t>
         </is>
       </c>
       <c r="AB365" t="inlineStr">
         <is>
-          <t>https://facebook.com/rwolf.jewelry, https://instagram.com/rwolfjewelry</t>
+          <t>https://facebook.com/masonjewelers.net, https://facebook.com/Masonjewelersco</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Grafted Growers</t>
+          <t>Moyer Fine Jewelers</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -41400,45 +41428,53 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Designers</t>
+          <t>Jewelers, Diamond Buyers, Watches</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>(984) 200-9545</t>
+          <t>(317) 844-9003</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>info@graftedgrowers.com</t>
+          <t>online@moyerfj.com</t>
         </is>
       </c>
       <c r="F366" t="inlineStr"/>
-      <c r="G366" t="inlineStr"/>
-      <c r="H366" t="inlineStr"/>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>Dan Moyer</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="I366" s="2" t="inlineStr">
         <is>
-          <t>https://graftedgrowers.com</t>
+          <t>https://moyerfinejewelers.com</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>4025 Atlantic Ave, Raleigh, NC 27604</t>
+          <t>14727 Thatcher Ln, Carmel, IN 46032</t>
         </is>
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>Raleigh</t>
+          <t>Carmel</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Raleigh, NC</t>
+          <t>Indianapolis, IN</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -41446,16 +41482,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O366" t="inlineStr"/>
-      <c r="P366" t="inlineStr"/>
+      <c r="O366" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P366" t="n">
+        <v>704</v>
+      </c>
       <c r="Q366" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/raleigh-nc/mip/grafted-growers-547754305</t>
+          <t>https://www.yellowpages.com/carmel-in/mip/moyer-fine-jewelers-7900799</t>
         </is>
       </c>
       <c r="R366" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line</t>
+          <t>2 of 3, direct-line, gia, bench, custom-design</t>
         </is>
       </c>
       <c r="S366" t="inlineStr">
@@ -41465,34 +41505,778 @@
       </c>
       <c r="T366" s="2" t="inlineStr">
         <is>
-          <t>https://graftedgrowers.com/</t>
+          <t>https://www.moyerfinejewelers.com/pages/contact-us</t>
         </is>
       </c>
       <c r="U366" t="inlineStr"/>
       <c r="V366" t="inlineStr">
         <is>
-          <t>2026-10-14T12:05:59+05:30</t>
+          <t>2026-10-14T12:05:12+05:30</t>
         </is>
       </c>
       <c r="W366" t="inlineStr"/>
       <c r="X366" t="inlineStr"/>
       <c r="Y366" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z366" t="inlineStr"/>
       <c r="AA366" t="inlineStr">
         <is>
+          <t>(317) 785-1080, (317) 785-1138</t>
+        </is>
+      </c>
+      <c r="AB366" t="inlineStr">
+        <is>
+          <t>https://instagram.com/moyerfinejewelers, https://facebook.com/moyerfinejewelers, https://twitter.com/MoyerJewelers</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Caesar's Designs</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Custom / bespoke jeweler</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Jewelers, Jewelry Designers, Jewelry Repairing</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>(412) 621-0345</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>caesar@caesarsdesigns.com</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr"/>
+      <c r="G367" t="inlineStr"/>
+      <c r="H367" t="inlineStr"/>
+      <c r="I367" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caesarsdesigns.com</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>5413 Walnut St, Pittsburgh, PA 15232</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Pittsburgh</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA</t>
+        </is>
+      </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O367" t="n">
+        <v>5</v>
+      </c>
+      <c r="P367" t="n">
+        <v>180</v>
+      </c>
+      <c r="Q367" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/pittsburgh-pa/mip/caesars-designs-9528656</t>
+        </is>
+      </c>
+      <c r="R367" t="inlineStr">
+        <is>
+          <t>2 of 3, direct-line, gia, custom-design</t>
+        </is>
+      </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T367" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caesarsdesigns.com/</t>
+        </is>
+      </c>
+      <c r="U367" t="inlineStr"/>
+      <c r="V367" t="inlineStr">
+        <is>
+          <t>2026-10-14T12:05:19+05:30</t>
+        </is>
+      </c>
+      <c r="W367" t="inlineStr"/>
+      <c r="X367" t="inlineStr"/>
+      <c r="Y367" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z367" t="inlineStr"/>
+      <c r="AA367" t="inlineStr">
+        <is>
+          <t>(412) 400-8582</t>
+        </is>
+      </c>
+      <c r="AB367" t="inlineStr">
+        <is>
+          <t>https://facebook.com/CaesarsDesignsCreations, https://instagram.com/caesarsdesigns</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Custom Jewelry</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Custom / bespoke jeweler</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Jewelers</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>(813) 930-0380</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>customhairtampabay@gmail.com</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr"/>
+      <c r="G368" t="inlineStr"/>
+      <c r="H368" t="inlineStr"/>
+      <c r="I368" s="2" t="inlineStr">
+        <is>
+          <t>https://customhairtampabay.com</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>11612 N Nebraska Ave, Tampa, FL 33612</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Tampa</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>Tampa, FL</t>
+        </is>
+      </c>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr"/>
+      <c r="P368" t="inlineStr"/>
+      <c r="Q368" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/tampa-fl/mip/custom-jewelry-481586478</t>
+        </is>
+      </c>
+      <c r="R368" t="inlineStr">
+        <is>
+          <t>2 of 3, direct-line, custom-design, since-1969</t>
+        </is>
+      </c>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T368" s="2" t="inlineStr">
+        <is>
+          <t>https://www.customhairtampabay.com/</t>
+        </is>
+      </c>
+      <c r="U368" t="inlineStr"/>
+      <c r="V368" t="inlineStr">
+        <is>
+          <t>2026-10-14T12:02:15+05:30</t>
+        </is>
+      </c>
+      <c r="W368" t="inlineStr">
+        <is>
+          <t>Janas Jewlery</t>
+        </is>
+      </c>
+      <c r="X368" t="inlineStr"/>
+      <c r="Y368" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z368" t="inlineStr"/>
+      <c r="AA368" t="inlineStr">
+        <is>
+          <t>(727) 725-1052, (813) 651-9484, (813) 932-5327</t>
+        </is>
+      </c>
+      <c r="AB368" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>R Wolf Fine Jewelers</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Custom / bespoke jeweler</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Jewelers, Watches</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>(813) 816-2619</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>rb.wolf@hotmail.com</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr"/>
+      <c r="G369" t="inlineStr"/>
+      <c r="H369" t="inlineStr"/>
+      <c r="I369" s="2" t="inlineStr">
+        <is>
+          <t>https://rwolfjewelry.com</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>100 S Ashley Dr, Tampa, FL 33602</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Tampa</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>Tampa, FL</t>
+        </is>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr"/>
+      <c r="P369" t="inlineStr"/>
+      <c r="Q369" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/tampa-fl/mip/r-wolf-fine-jewelers-543840292</t>
+        </is>
+      </c>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t>2 of 3, direct-line, bench, custom-design</t>
+        </is>
+      </c>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T369" s="2" t="inlineStr">
+        <is>
+          <t>https://rwolfjewelry.com/</t>
+        </is>
+      </c>
+      <c r="U369" t="inlineStr"/>
+      <c r="V369" t="inlineStr">
+        <is>
+          <t>2026-10-14T12:02:02+05:30</t>
+        </is>
+      </c>
+      <c r="W369" t="inlineStr"/>
+      <c r="X369" t="inlineStr"/>
+      <c r="Y369" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z369" t="inlineStr"/>
+      <c r="AA369" t="inlineStr">
+        <is>
+          <t>(727) 275-0106</t>
+        </is>
+      </c>
+      <c r="AB369" t="inlineStr">
+        <is>
+          <t>https://facebook.com/rwolf.jewelry, https://instagram.com/rwolfjewelry</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Grafted Growers</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Custom / bespoke jeweler</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Jewelers, Jewelry Designers</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>(984) 200-9545</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>info@graftedgrowers.com</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr"/>
+      <c r="G370" t="inlineStr"/>
+      <c r="H370" t="inlineStr"/>
+      <c r="I370" s="2" t="inlineStr">
+        <is>
+          <t>https://graftedgrowers.com</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>4025 Atlantic Ave, Raleigh, NC 27604</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Raleigh</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>Raleigh, NC</t>
+        </is>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr"/>
+      <c r="P370" t="inlineStr"/>
+      <c r="Q370" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/raleigh-nc/mip/grafted-growers-547754305</t>
+        </is>
+      </c>
+      <c r="R370" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line</t>
+        </is>
+      </c>
+      <c r="S370" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T370" s="2" t="inlineStr">
+        <is>
+          <t>https://graftedgrowers.com/</t>
+        </is>
+      </c>
+      <c r="U370" t="inlineStr"/>
+      <c r="V370" t="inlineStr">
+        <is>
+          <t>2026-10-14T12:05:59+05:30</t>
+        </is>
+      </c>
+      <c r="W370" t="inlineStr"/>
+      <c r="X370" t="inlineStr"/>
+      <c r="Y370" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z370" t="inlineStr"/>
+      <c r="AA370" t="inlineStr">
+        <is>
           <t>(919) 400-6022</t>
         </is>
       </c>
-      <c r="AB366" t="inlineStr">
+      <c r="AB370" t="inlineStr">
         <is>
           <t>https://facebook.com/graftedgrowers, https://instagram.com/graftedgrowers, https://twitter.com/GraftedGrowers</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Cajun Swamp</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Jewelers, Gift Shops</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>(504) 267-5075</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>info@cajunencounters.com</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr"/>
+      <c r="G371" t="inlineStr"/>
+      <c r="H371" t="inlineStr"/>
+      <c r="I371" s="2" t="inlineStr">
+        <is>
+          <t>https://cajunencounters.com</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>631 Bourbon St, New Orleans, LA 70130</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>New Orleans</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>New Orleans, LA</t>
+        </is>
+      </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr"/>
+      <c r="P371" t="inlineStr"/>
+      <c r="Q371" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/new-orleans-la/mip/cajun-swamp-7275033</t>
+        </is>
+      </c>
+      <c r="R371" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, since-1997</t>
+        </is>
+      </c>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T371" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cajunencounters.com/</t>
+        </is>
+      </c>
+      <c r="U371" t="inlineStr"/>
+      <c r="V371" t="inlineStr">
+        <is>
+          <t>2026-10-14T12:06:52+05:30</t>
+        </is>
+      </c>
+      <c r="W371" t="inlineStr"/>
+      <c r="X371" t="inlineStr"/>
+      <c r="Y371" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z371" t="inlineStr"/>
+      <c r="AA371" t="inlineStr">
+        <is>
+          <t>(504) 834-1770</t>
+        </is>
+      </c>
+      <c r="AB371" t="inlineStr">
+        <is>
+          <t>https://facebook.com/CajunEncounters, https://twitter.com/cajunencounters, https://instagram.com/cajunencounters</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>P &amp; R Jewelry Repair Inc</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Jewelry repair / goldsmith</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Jewelers, Watch Repair, Jewelry Repairing</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>(504) 366-1878</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>automatic8675@gmail.com</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr"/>
+      <c r="G372" t="inlineStr"/>
+      <c r="H372" t="inlineStr"/>
+      <c r="I372" s="2" t="inlineStr">
+        <is>
+          <t>https://quinterandsonsjewelers.jewelershowcase.com</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>197 Westbank Expy, Gretna, LA 70053</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Gretna</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>New Orleans, LA</t>
+        </is>
+      </c>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O372" t="n">
+        <v>5</v>
+      </c>
+      <c r="P372" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q372" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/gretna-la/mip/p-r-jewelry-repair-inc-477806444</t>
+        </is>
+      </c>
+      <c r="R372" t="inlineStr">
+        <is>
+          <t>2 of 3, direct-line, gia, bench, custom-design</t>
+        </is>
+      </c>
+      <c r="S372" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T372" s="2" t="inlineStr">
+        <is>
+          <t>https://quinterandsonsjewelers.jewelershowcase.com/contactthisjeweler</t>
+        </is>
+      </c>
+      <c r="U372" t="inlineStr"/>
+      <c r="V372" t="inlineStr">
+        <is>
+          <t>2026-10-14T12:07:32+05:30</t>
+        </is>
+      </c>
+      <c r="W372" t="inlineStr">
+        <is>
+          <t>Sol's Jewelers</t>
+        </is>
+      </c>
+      <c r="X372" t="inlineStr"/>
+      <c r="Y372" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z372" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="AA372" t="inlineStr">
+        <is>
+          <t>(985) 335-0908</t>
+        </is>
+      </c>
+      <c r="AB372" t="inlineStr">
+        <is>
+          <t>https://facebook.com/StullerInc, https://instagram.com/StullerInc, https://x.com/StullerInc</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Quarter Past Time</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Jewelers</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>(504) 410-0010</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>hello@quarterstitch.com</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr"/>
+      <c r="G373" t="inlineStr"/>
+      <c r="H373" t="inlineStr"/>
+      <c r="I373" s="2" t="inlineStr">
+        <is>
+          <t>https://quarterstitch.com</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>606 Chartres St, New Orleans, LA 70130</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>New Orleans</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>New Orleans, LA</t>
+        </is>
+      </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr"/>
+      <c r="P373" t="inlineStr"/>
+      <c r="Q373" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/new-orleans-la/mip/quarter-past-time-4483088</t>
+        </is>
+      </c>
+      <c r="R373" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, since-1969</t>
+        </is>
+      </c>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T373" s="2" t="inlineStr">
+        <is>
+          <t>https://www.quarterstitch.com/contact</t>
+        </is>
+      </c>
+      <c r="U373" t="inlineStr"/>
+      <c r="V373" t="inlineStr">
+        <is>
+          <t>2026-10-14T12:06:57+05:30</t>
+        </is>
+      </c>
+      <c r="W373" t="inlineStr"/>
+      <c r="X373" t="inlineStr"/>
+      <c r="Y373" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z373" t="inlineStr"/>
+      <c r="AA373" t="inlineStr">
+        <is>
+          <t>(504) 522-4451</t>
+        </is>
+      </c>
+      <c r="AB373" t="inlineStr">
+        <is>
+          <t>https://instagram.com/quarter_stitch, https://facebook.com/TheQuarterStitch</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB366"/>
+  <autoFilter ref="A1:AB373"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId2"/>
@@ -42769,6 +43553,27 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I366" r:id="rId1273"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q366" r:id="rId1274"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T366" r:id="rId1275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I367" r:id="rId1276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q367" r:id="rId1277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T367" r:id="rId1278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I368" r:id="rId1279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q368" r:id="rId1280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T368" r:id="rId1281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I369" r:id="rId1282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q369" r:id="rId1283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T369" r:id="rId1284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I370" r:id="rId1285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q370" r:id="rId1286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T370" r:id="rId1287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I371" r:id="rId1288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q371" r:id="rId1289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T371" r:id="rId1290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I372" r:id="rId1291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q372" r:id="rId1292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T372" r:id="rId1293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I373" r:id="rId1294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q373" r:id="rId1295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T373" r:id="rId1296"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -42780,7 +43585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -42836,7 +43641,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="C2" t="n">
         <v>36</v>
@@ -42890,7 +43695,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C4" t="n">
         <v>19</v>
@@ -42944,14 +43749,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C6" t="n">
         <v>8</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -42971,7 +43776,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C7" t="n">
         <v>34</v>
@@ -43295,7 +44100,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C19" t="n">
         <v>9</v>
@@ -43403,7 +44208,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C23" t="n">
         <v>6</v>
@@ -43457,7 +44262,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C25" t="n">
         <v>9</v>
@@ -43511,18 +44316,18 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -43538,18 +44343,18 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>232</v>
+        <v>297</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -43565,7 +44370,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>193</v>
+        <v>255</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -43592,18 +44397,18 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>166</v>
+        <v>235</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -43619,18 +44424,18 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -43700,7 +44505,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -43727,7 +44532,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -43754,7 +44559,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -43781,14 +44586,14 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="C37" t="n">
         <v>2</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -43808,7 +44613,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>108</v>
+        <v>205</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -43835,18 +44640,18 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>112</v>
+        <v>162</v>
       </c>
       <c r="C39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F39" t="n">
         <v>2</v>
@@ -43862,7 +44667,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
@@ -43889,7 +44694,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -43912,22 +44717,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Tampa, FL</t>
+          <t>Orlando, FL</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>134</v>
+        <v>223</v>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -43939,22 +44744,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL</t>
+          <t>Tampa, FL</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -43966,22 +44771,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Raleigh, NC</t>
+          <t>Fort Lauderdale, FL</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>111</v>
+        <v>315</v>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -43993,22 +44798,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>New Orleans, LA</t>
+          <t>Raleigh, NC</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -44020,27 +44825,54 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>New Orleans, LA</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>143</v>
+      </c>
+      <c r="C46" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>3</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B46" t="n">
-        <v>13811</v>
-      </c>
-      <c r="C46" t="n">
-        <v>365</v>
-      </c>
-      <c r="D46" t="inlineStr">
+      <c r="B47" t="n">
+        <v>14586</v>
+      </c>
+      <c r="C47" t="n">
+        <v>372</v>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>2.6%</t>
         </is>
       </c>
-      <c r="E46" t="n">
-        <v>357</v>
-      </c>
-      <c r="F46" t="n">
+      <c r="E47" t="n">
+        <v>364</v>
+      </c>
+      <c r="F47" t="n">
         <v>194</v>
       </c>
-      <c r="G46" t="n">
+      <c r="G47" t="n">
         <v>94</v>
       </c>
     </row>
@@ -44081,7 +44913,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3">
@@ -44091,7 +44923,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4">
@@ -44111,7 +44943,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -44133,7 +44965,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9">
@@ -44153,7 +44985,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11">
@@ -44192,7 +45024,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T12:20:46+05:30</t>
+          <t>2026-10-14T12:41:27+05:30</t>
         </is>
       </c>
     </row>
@@ -44203,7 +45035,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>365</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3">
@@ -44213,7 +45045,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>13811</v>
+        <v>14586</v>
       </c>
     </row>
     <row r="4">

--- a/leadrun_jewelry/jewelry_qualified.xlsx
+++ b/leadrun_jewelry/jewelry_qualified.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qualified Leads'!$A$1:$AB$373</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qualified Leads'!$A$1:$AB$383</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB373"/>
+  <dimension ref="A1:AB383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -40324,14 +40324,18 @@
       </c>
       <c r="W355" t="inlineStr">
         <is>
-          <t>Michele's</t>
+          <t>Michele's, Michele's Antiques</t>
         </is>
       </c>
       <c r="X355" t="inlineStr"/>
       <c r="Y355" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z355" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Z355" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA355" t="inlineStr">
         <is>
           <t>(970) 949-7717</t>
@@ -40346,12 +40350,12 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>The Jewel of Art Dance Studio</t>
+          <t>Texas Jewelers Association Inc</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Estate &amp; antique jewelry</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -40361,30 +40365,38 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>(210) 878-4089</t>
+          <t>(512) 472-7342</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>info@jewelofartdance.com</t>
+          <t>pastpresident@texasjewelers.org</t>
         </is>
       </c>
       <c r="F356" t="inlineStr"/>
-      <c r="G356" t="inlineStr"/>
-      <c r="H356" t="inlineStr"/>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>David Baker</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
       <c r="I356" s="2" t="inlineStr">
         <is>
-          <t>https://jewelofartdance.com</t>
+          <t>https://texasjewelers.org</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>1909 Fredericksburg Rd, San Antonio, TX 78201</t>
+          <t>611 Congress Ave, Austin, TX 78701</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
@@ -40394,7 +40406,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>San Antonio, TX</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -40406,12 +40418,12 @@
       <c r="P356" t="inlineStr"/>
       <c r="Q356" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/san-antonio-tx/mip/the-jewel-of-art-dance-studio-547319903</t>
+          <t>https://www.yellowpages.com/austin-tx/mip/texas-jewelers-association-inc-29795057</t>
         </is>
       </c>
       <c r="R356" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line</t>
+          <t>2 of 3, direct-line, ja, since-1906</t>
         </is>
       </c>
       <c r="S356" t="inlineStr">
@@ -40421,84 +40433,96 @@
       </c>
       <c r="T356" s="2" t="inlineStr">
         <is>
-          <t>https://jewelofartdance.com/</t>
+          <t>https://texasjewelers.org/about-us/</t>
         </is>
       </c>
       <c r="U356" t="inlineStr"/>
       <c r="V356" t="inlineStr">
         <is>
-          <t>2026-10-14T12:12:32+05:30</t>
-        </is>
-      </c>
-      <c r="W356" t="inlineStr"/>
+          <t>2026-10-14T12:10:05+05:30</t>
+        </is>
+      </c>
+      <c r="W356" t="inlineStr">
+        <is>
+          <t>Texas Jewelers Association</t>
+        </is>
+      </c>
       <c r="X356" t="inlineStr"/>
       <c r="Y356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z356" t="inlineStr"/>
       <c r="AA356" t="inlineStr">
         <is>
-          <t>(210) 639-3756</t>
+          <t>(252) 314-1611, (281) 300-5377, (281) 391-6333, (281) 482-4755, (325) 653-0112, (325) 655-3135, (915) 584-0022, (972) 910-0300</t>
         </is>
       </c>
       <c r="AB356" t="inlineStr">
         <is>
-          <t>https://facebook.com/jewelofartdance, https://twitter.com/jewelofartdance, https://instagram.com/jewelofartdance</t>
+          <t>https://facebook.com/TexasJewelersAssociation, https://facebook.com/oregonjewelersOJA</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Alexander Design</t>
+          <t>Charm N Jewelry</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers, Jewelry Designers</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>(408) 998-4539</t>
+          <t>(210) 483-8800</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>sales@alexander-dm.com</t>
+          <t>orders@charmnjewelry.com</t>
         </is>
       </c>
       <c r="F357" t="inlineStr"/>
-      <c r="G357" t="inlineStr"/>
-      <c r="H357" t="inlineStr"/>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>Larry McGill</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
       <c r="I357" s="2" t="inlineStr">
         <is>
-          <t>https://alexander-dm.com</t>
+          <t>https://www.charmnjewelry.com</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>1111 Story Rd Ste 1063, San Jose, CA 95122</t>
+          <t>27014 Spiral Cyn, San Antonio, TX 78261</t>
         </is>
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t>San Jose</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>San Antonio, TX</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -40510,12 +40534,12 @@
       <c r="P357" t="inlineStr"/>
       <c r="Q357" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/san-jose-ca/mip/alexander-design-692537</t>
+          <t>https://www.yellowpages.com/san-antonio-tx/mip/charm-n-jewelry-531435683</t>
         </is>
       </c>
       <c r="R357" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-2001</t>
+          <t>2 of 3, role-email, direct-line, since-1981</t>
         </is>
       </c>
       <c r="S357" t="inlineStr">
@@ -40525,37 +40549,49 @@
       </c>
       <c r="T357" s="2" t="inlineStr">
         <is>
-          <t>https://www.alexander-dm.com/</t>
+          <t>https://www.charmnjewelry.com/about-us</t>
         </is>
       </c>
       <c r="U357" t="inlineStr"/>
       <c r="V357" t="inlineStr">
         <is>
-          <t>2026-10-14T12:05:25+05:30</t>
-        </is>
-      </c>
-      <c r="W357" t="inlineStr"/>
+          <t>2026-10-14T12:12:22+05:30</t>
+        </is>
+      </c>
+      <c r="W357" t="inlineStr">
+        <is>
+          <t>Charm N Jewelry Inc, McGill Larry</t>
+        </is>
+      </c>
       <c r="X357" t="inlineStr"/>
       <c r="Y357" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z357" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Z357" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA357" t="inlineStr">
         <is>
-          <t>(213) 649-1924</t>
-        </is>
-      </c>
-      <c r="AB357" t="inlineStr"/>
+          <t>(830) 438-8960</t>
+        </is>
+      </c>
+      <c r="AB357" t="inlineStr">
+        <is>
+          <t>https://facebook.com/CharmnJewelry, https://twitter.com/charmnjewelry, https://facebook.com/CharmNJewelry</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Kumar Jewelers</t>
+          <t>The Jewel of Art Dance Studio</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -40565,12 +40601,12 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>(408) 246-0850</t>
+          <t>(210) 878-4089</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>contact@kumarjewelers.com</t>
+          <t>info@jewelofartdance.com</t>
         </is>
       </c>
       <c r="F358" t="inlineStr"/>
@@ -40578,27 +40614,27 @@
       <c r="H358" t="inlineStr"/>
       <c r="I358" s="2" t="inlineStr">
         <is>
-          <t>https://kumarjewelers.com</t>
+          <t>https://jewelofartdance.com</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>3418 El Camino Real, Santa Clara, CA 95051</t>
+          <t>1909 Fredericksburg Rd, San Antonio, TX 78201</t>
         </is>
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>San Antonio, TX</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -40606,20 +40642,16 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O358" t="n">
-        <v>5</v>
-      </c>
-      <c r="P358" t="n">
-        <v>1</v>
-      </c>
+      <c r="O358" t="inlineStr"/>
+      <c r="P358" t="inlineStr"/>
       <c r="Q358" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/santa-clara-ca/mip/kumar-jewelers-7772087</t>
+          <t>https://www.yellowpages.com/san-antonio-tx/mip/the-jewel-of-art-dance-studio-547319903</t>
         </is>
       </c>
       <c r="R358" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, role-email, direct-line</t>
         </is>
       </c>
       <c r="S358" t="inlineStr">
@@ -40629,13 +40661,13 @@
       </c>
       <c r="T358" s="2" t="inlineStr">
         <is>
-          <t>https://www.kumarjewelers.com/</t>
+          <t>https://jewelofartdance.com/</t>
         </is>
       </c>
       <c r="U358" t="inlineStr"/>
       <c r="V358" t="inlineStr">
         <is>
-          <t>2026-10-14T12:17:16+05:30</t>
+          <t>2026-10-14T12:12:32+05:30</t>
         </is>
       </c>
       <c r="W358" t="inlineStr"/>
@@ -40646,39 +40678,39 @@
       <c r="Z358" t="inlineStr"/>
       <c r="AA358" t="inlineStr">
         <is>
-          <t>(510) 713-1040, (925) 248-2280</t>
+          <t>(210) 639-3756</t>
         </is>
       </c>
       <c r="AB358" t="inlineStr">
         <is>
-          <t>https://facebook.com/kumarjewelers, https://instagram.com/kumarjewelers</t>
+          <t>https://facebook.com/jewelofartdance, https://twitter.com/jewelofartdance, https://instagram.com/jewelofartdance</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Sacramento Watch &amp; Jewelry Service</t>
+          <t>Tito Rosy Jewelry</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Jewelry repair / goldsmith</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelry manufacturer</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>(916) 979-9106</t>
+          <t>(210) 255-1265</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>steve@sacramentowatchshop.com</t>
+          <t>titorosyjewelry1@gmail.com</t>
         </is>
       </c>
       <c r="F359" t="inlineStr"/>
@@ -40686,44 +40718,40 @@
       <c r="H359" t="inlineStr"/>
       <c r="I359" s="2" t="inlineStr">
         <is>
-          <t>https://sacramentowatchshop.com</t>
+          <t>https://titorosyjewelry.com</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>1620 Fulton Ave, Sacramento, CA 95825</t>
-        </is>
-      </c>
-      <c r="K359" t="inlineStr">
-        <is>
-          <t>Sacramento</t>
-        </is>
-      </c>
-      <c r="L359" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
+          <t>5525 Blanco Rd #111, San Antonio, TX 78216, United States</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr"/>
+      <c r="L359" t="inlineStr"/>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Sacramento, CA</t>
+          <t>San Antonio, TX</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O359" t="inlineStr"/>
-      <c r="P359" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O359" t="n">
+        <v>5</v>
+      </c>
+      <c r="P359" t="n">
+        <v>42</v>
+      </c>
       <c r="Q359" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/sacramento-ca/mip/sacramento-watch-jewelry-service-519958764</t>
+          <t>https://www.google.com/maps/place/Tito+Rosy+Jewelry/data=!4m7!3m6!1s0x865c5f773ae58179:0xd412e0884c474983!8m2!3d29.5045048!4d-98.5074043!16s%2Fg%2F11xy_tyxvc!19sChIJeYHlOndfXIYRg0lHTIjgEtQ</t>
         </is>
       </c>
       <c r="R359" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, since-1995</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S359" t="inlineStr">
@@ -40733,13 +40761,13 @@
       </c>
       <c r="T359" s="2" t="inlineStr">
         <is>
-          <t>https://sacramentowatchshop.com/</t>
+          <t>https://titorosyjewelry.com/contactactanos/</t>
         </is>
       </c>
       <c r="U359" t="inlineStr"/>
       <c r="V359" t="inlineStr">
         <is>
-          <t>2026-10-14T12:07:36+05:30</t>
+          <t>2026-10-14T12:18:46+05:30</t>
         </is>
       </c>
       <c r="W359" t="inlineStr"/>
@@ -40750,19 +40778,19 @@
       <c r="Z359" t="inlineStr"/>
       <c r="AA359" t="inlineStr">
         <is>
-          <t>(916) 550-1863</t>
+          <t>(786) 492-3645</t>
         </is>
       </c>
       <c r="AB359" t="inlineStr">
         <is>
-          <t>https://facebook.com/sacramentowatchshop, https://facebook.com/The-Watch-Shop-727641780765411</t>
+          <t>https://instagram.com/titorosyjewelry1</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Ari Diamonds</t>
+          <t>Alexander Design</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -40772,17 +40800,17 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Jewelers, Diamonds-Wholesale, Jewelers-Wholesale &amp; Manufacturers</t>
+          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers, Jewelry Designers</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>(801) 255-8992</t>
+          <t>(408) 998-4539</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>panna.aridiamonds@gmail.com</t>
+          <t>sales@alexander-dm.com</t>
         </is>
       </c>
       <c r="F360" t="inlineStr"/>
@@ -40790,27 +40818,27 @@
       <c r="H360" t="inlineStr"/>
       <c r="I360" s="2" t="inlineStr">
         <is>
-          <t>https://www.aridiamonds.com</t>
+          <t>https://alexander-dm.com</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>807 E Fort Union Blvd, Midvale, UT 84047</t>
+          <t>1111 Story Rd Ste 1063, San Jose, CA 95122</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t>Midvale</t>
+          <t>San Jose</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>UT</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -40818,20 +40846,16 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O360" t="n">
-        <v>5</v>
-      </c>
-      <c r="P360" t="n">
-        <v>6</v>
-      </c>
+      <c r="O360" t="inlineStr"/>
+      <c r="P360" t="inlineStr"/>
       <c r="Q360" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/midvale-ut/mip/ari-diamonds-23948160</t>
+          <t>https://www.yellowpages.com/san-jose-ca/mip/alexander-design-692537</t>
         </is>
       </c>
       <c r="R360" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design, since-1994</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-2001</t>
         </is>
       </c>
       <c r="S360" t="inlineStr">
@@ -40841,13 +40865,13 @@
       </c>
       <c r="T360" s="2" t="inlineStr">
         <is>
-          <t>https://www.aridiamonds.com/</t>
+          <t>https://www.alexander-dm.com/</t>
         </is>
       </c>
       <c r="U360" t="inlineStr"/>
       <c r="V360" t="inlineStr">
         <is>
-          <t>2026-10-14T12:03:18+05:30</t>
+          <t>2026-10-14T12:05:25+05:30</t>
         </is>
       </c>
       <c r="W360" t="inlineStr"/>
@@ -40858,19 +40882,15 @@
       <c r="Z360" t="inlineStr"/>
       <c r="AA360" t="inlineStr">
         <is>
-          <t>(801) 776-8830</t>
-        </is>
-      </c>
-      <c r="AB360" t="inlineStr">
-        <is>
-          <t>https://instagram.com/aridiamondsutah, https://facebook.com/aridiamonds</t>
-        </is>
-      </c>
+          <t>(213) 649-1924</t>
+        </is>
+      </c>
+      <c r="AB360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Jewelry By Tommy</t>
+          <t>Kumar Jewelers</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -40880,17 +40900,17 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers, Diamonds</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>(216) 464-6356</t>
+          <t>(408) 246-0850</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>greg@jewelrybytommy.com</t>
+          <t>contact@kumarjewelers.com</t>
         </is>
       </c>
       <c r="F361" t="inlineStr"/>
@@ -40898,27 +40918,27 @@
       <c r="H361" t="inlineStr"/>
       <c r="I361" s="2" t="inlineStr">
         <is>
-          <t>https://www.jewelrybytommy.com</t>
+          <t>https://kumarjewelers.com</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>27600 Chagrin Blvd Ste 110, Woodmere, OH 44122</t>
+          <t>3418 El Camino Real, Santa Clara, CA 95051</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>Woodmere</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Cleveland, OH</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -40926,16 +40946,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O361" t="inlineStr"/>
-      <c r="P361" t="inlineStr"/>
+      <c r="O361" t="n">
+        <v>5</v>
+      </c>
+      <c r="P361" t="n">
+        <v>1</v>
+      </c>
       <c r="Q361" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/woodmere-oh/mip/jewelry-by-tommy-479852454</t>
+          <t>https://www.yellowpages.com/santa-clara-ca/mip/kumar-jewelers-7772087</t>
         </is>
       </c>
       <c r="R361" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S361" t="inlineStr">
@@ -40945,13 +40969,13 @@
       </c>
       <c r="T361" s="2" t="inlineStr">
         <is>
-          <t>https://jewelrybytommy.com/</t>
+          <t>https://www.kumarjewelers.com/</t>
         </is>
       </c>
       <c r="U361" t="inlineStr"/>
       <c r="V361" t="inlineStr">
         <is>
-          <t>2026-10-14T12:01:03+05:30</t>
+          <t>2026-10-14T12:17:16+05:30</t>
         </is>
       </c>
       <c r="W361" t="inlineStr"/>
@@ -40962,67 +40986,75 @@
       <c r="Z361" t="inlineStr"/>
       <c r="AA361" t="inlineStr">
         <is>
-          <t>(440) 413-5888</t>
+          <t>(510) 713-1040, (925) 248-2280</t>
         </is>
       </c>
       <c r="AB361" t="inlineStr">
         <is>
-          <t>https://facebook.com/JewelrybyTommy</t>
+          <t>https://facebook.com/kumarjewelers, https://instagram.com/kumarjewelers</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Pearls Hope, Inc</t>
+          <t>DeVons Jewelers</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Jewelry Designers, Diamonds</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>(440) 249-7000</t>
+          <t>(916) 929-3991</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>intake@pearlshope.com</t>
+          <t>info@devonsjewelers.com</t>
         </is>
       </c>
       <c r="F362" t="inlineStr"/>
-      <c r="G362" t="inlineStr"/>
-      <c r="H362" t="inlineStr"/>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>Adam Blankenship</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
       <c r="I362" s="2" t="inlineStr">
         <is>
-          <t>https://pearlshope.com</t>
+          <t>https://www.devonsjewelers.com</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>3659 Green Rd, Beachwood, OH 44122</t>
+          <t>1689 Arden Way, Sacramento, CA 95815</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t>Beachwood</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Cleveland, OH</t>
+          <t>Sacramento, CA</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -41030,16 +41062,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O362" t="inlineStr"/>
-      <c r="P362" t="inlineStr"/>
+      <c r="O362" t="n">
+        <v>5</v>
+      </c>
+      <c r="P362" t="n">
+        <v>7</v>
+      </c>
       <c r="Q362" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/beachwood-oh/mip/pearls-hope-inc-580059164</t>
+          <t>https://www.yellowpages.com/sacramento-ca/mip/devons-jewelers-495526219</t>
         </is>
       </c>
       <c r="R362" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, role-email, direct-line</t>
         </is>
       </c>
       <c r="S362" t="inlineStr">
@@ -41049,88 +41085,92 @@
       </c>
       <c r="T362" s="2" t="inlineStr">
         <is>
-          <t>https://pearlshope.com/</t>
+          <t>https://www.devonsjewelers.com/</t>
         </is>
       </c>
       <c r="U362" t="inlineStr"/>
       <c r="V362" t="inlineStr">
         <is>
-          <t>2026-10-14T12:00:59+05:30</t>
-        </is>
-      </c>
-      <c r="W362" t="inlineStr"/>
+          <t>2026-10-14T12:07:30+05:30</t>
+        </is>
+      </c>
+      <c r="W362" t="inlineStr">
+        <is>
+          <t>De Vons Jewelers</t>
+        </is>
+      </c>
       <c r="X362" t="inlineStr"/>
       <c r="Y362" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z362" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="Z362" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA362" t="inlineStr">
         <is>
-          <t>(216) 452-0082, (614) 781-0400, (937) 222-0002</t>
-        </is>
-      </c>
-      <c r="AB362" t="inlineStr"/>
+          <t>(209) 527-0196, (209) 726-8001, (209) 951-9610, (530) 223-2071, (530) 342-4493, (530) 674-2375, (559) 225-0496, (916) 788-4150</t>
+        </is>
+      </c>
+      <c r="AB362" t="inlineStr">
+        <is>
+          <t>https://facebook.com/devonsjewelers, https://instagram.com/devonsjewelers</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Dakota Watch Co</t>
+          <t>Kenny G &amp; Company Fine Jewelers</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Jewelers, Watch Repair, Watches</t>
+          <t>Jewelers, Jewelry Designers, Diamonds</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>(317) 624-9115</t>
+          <t>(916) 691-9600</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>customerservice@dakotawatch.com</t>
+          <t>citrusheights@kennygandco.com</t>
         </is>
       </c>
       <c r="F363" t="inlineStr"/>
-      <c r="G363" t="inlineStr">
-        <is>
-          <t>Albert Cooper</t>
-        </is>
-      </c>
-      <c r="H363" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
+      <c r="G363" t="inlineStr"/>
+      <c r="H363" t="inlineStr"/>
       <c r="I363" s="2" t="inlineStr">
         <is>
-          <t>https://dakotawatch.com</t>
+          <t>https://www.kennygandco.com</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>49 W Maryland St Ste 142, Indianapolis, IN 46204</t>
+          <t>7440 Laguna Blvd Ste 112, Elk Grove, CA 95758</t>
         </is>
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Elk Grove</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Indianapolis, IN</t>
+          <t>Sacramento, CA</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -41138,16 +41178,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O363" t="inlineStr"/>
-      <c r="P363" t="inlineStr"/>
+      <c r="O363" t="n">
+        <v>5</v>
+      </c>
+      <c r="P363" t="n">
+        <v>1</v>
+      </c>
       <c r="Q363" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/indianapolis-in/mip/dakota-watch-co-25573661</t>
+          <t>https://www.yellowpages.com/elk-grove-ca/mip/kenny-g-company-fine-jewelers-5526854</t>
         </is>
       </c>
       <c r="R363" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line</t>
+          <t>2 of 3, direct-line, gia, custom-design, since-1997</t>
         </is>
       </c>
       <c r="S363" t="inlineStr">
@@ -41157,68 +41201,56 @@
       </c>
       <c r="T363" s="2" t="inlineStr">
         <is>
-          <t>https://dakotawatch.com/</t>
+          <t>https://www.kennygandco.com/pages/contact</t>
         </is>
       </c>
       <c r="U363" t="inlineStr"/>
       <c r="V363" t="inlineStr">
         <is>
-          <t>2026-10-14T12:04:54+05:30</t>
-        </is>
-      </c>
-      <c r="W363" t="inlineStr">
-        <is>
-          <t>Dakota Watch Company, Cooper &amp; Co Inc</t>
-        </is>
-      </c>
-      <c r="X363" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, Pittsburgh, PA</t>
-        </is>
-      </c>
+          <t>2026-10-14T12:08:14+05:30</t>
+        </is>
+      </c>
+      <c r="W363" t="inlineStr"/>
+      <c r="X363" t="inlineStr"/>
       <c r="Y363" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z363" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z363" t="inlineStr"/>
       <c r="AA363" t="inlineStr">
         <is>
-          <t>(513) 879-3681</t>
+          <t>(775) 852-7700, (916) 772-8400, (916) 965-6664</t>
         </is>
       </c>
       <c r="AB363" t="inlineStr">
         <is>
-          <t>https://facebook.com/profile.php?id=61550829076826, https://instagram.com/dakotawatch_co</t>
+          <t>https://instagram.com/kennygandco, https://facebook.com/KennyGCo, https://instagram.com/kennygandco/</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Indianapolis Crown Jewel Inc</t>
+          <t>Sacramento Watch &amp; Jewelry Service</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Jewelry repair / goldsmith</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Repairing, Watch Repair</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>(317) 602-3563</t>
+          <t>(916) 979-9106</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>crownjewel.cj@gmail.com</t>
+          <t>steve@sacramentowatchshop.com</t>
         </is>
       </c>
       <c r="F364" t="inlineStr"/>
@@ -41226,27 +41258,27 @@
       <c r="H364" t="inlineStr"/>
       <c r="I364" s="2" t="inlineStr">
         <is>
-          <t>https://www.indycrownjewel.com</t>
+          <t>https://sacramentowatchshop.com</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>3760 N Emerson Ave, Indianapolis, IN 46218</t>
+          <t>1620 Fulton Ave, Sacramento, CA 95825</t>
         </is>
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Indianapolis, IN</t>
+          <t>Sacramento, CA</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -41258,12 +41290,12 @@
       <c r="P364" t="inlineStr"/>
       <c r="Q364" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/indianapolis-in/mip/indianapolis-crown-jewel-inc-545777926</t>
+          <t>https://www.yellowpages.com/sacramento-ca/mip/sacramento-watch-jewelry-service-519958764</t>
         </is>
       </c>
       <c r="R364" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, direct-line, since-1995</t>
         </is>
       </c>
       <c r="S364" t="inlineStr">
@@ -41273,13 +41305,13 @@
       </c>
       <c r="T364" s="2" t="inlineStr">
         <is>
-          <t>https://www.indycrownjewel.com/</t>
+          <t>https://sacramentowatchshop.com/</t>
         </is>
       </c>
       <c r="U364" t="inlineStr"/>
       <c r="V364" t="inlineStr">
         <is>
-          <t>2026-10-14T12:04:25+05:30</t>
+          <t>2026-10-14T12:07:36+05:30</t>
         </is>
       </c>
       <c r="W364" t="inlineStr"/>
@@ -41287,46 +41319,42 @@
       <c r="Y364" t="n">
         <v>0</v>
       </c>
-      <c r="Z364" t="inlineStr">
-        <is>
-          <t>shared-switchboard</t>
-        </is>
-      </c>
+      <c r="Z364" t="inlineStr"/>
       <c r="AA364" t="inlineStr">
         <is>
-          <t>(317) 228-7485</t>
+          <t>(916) 550-1863</t>
         </is>
       </c>
       <c r="AB364" t="inlineStr">
         <is>
-          <t>https://facebook.com/indycrownjewelcollection, https://instagram.com/indycrownjewel</t>
+          <t>https://facebook.com/sacramentowatchshop, https://facebook.com/The-Watch-Shop-727641780765411</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Mason Jewelers Inc</t>
+          <t>Ari Diamonds</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Jewelers, Appraisers</t>
+          <t>Jewelers, Diamonds-Wholesale, Jewelers-Wholesale &amp; Manufacturers</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>(317) 839-3202</t>
+          <t>(801) 255-8992</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>masonjewelers1957@gmail.com</t>
+          <t>panna.aridiamonds@gmail.com</t>
         </is>
       </c>
       <c r="F365" t="inlineStr"/>
@@ -41334,27 +41362,27 @@
       <c r="H365" t="inlineStr"/>
       <c r="I365" s="2" t="inlineStr">
         <is>
-          <t>https://www.masonjewelersco.com</t>
+          <t>https://www.aridiamonds.com</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>1822 E Main St, Plainfield, IN 46168</t>
+          <t>807 E Fort Union Blvd, Midvale, UT 84047</t>
         </is>
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t>Plainfield</t>
+          <t>Midvale</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>UT</t>
         </is>
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Indianapolis, IN</t>
+          <t>Salt Lake City, UT</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -41363,19 +41391,19 @@
         </is>
       </c>
       <c r="O365" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P365" t="n">
-        <v>355</v>
+        <v>6</v>
       </c>
       <c r="Q365" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/plainfield-in/mip/mason-jewelers-inc-705208</t>
+          <t>https://www.yellowpages.com/midvale-ut/mip/ari-diamonds-23948160</t>
         </is>
       </c>
       <c r="R365" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, since-1957</t>
+          <t>2 of 3, direct-line, custom-design, since-1994</t>
         </is>
       </c>
       <c r="S365" t="inlineStr">
@@ -41385,96 +41413,84 @@
       </c>
       <c r="T365" s="2" t="inlineStr">
         <is>
-          <t>https://www.masonjewelersco.com/</t>
+          <t>https://www.aridiamonds.com/</t>
         </is>
       </c>
       <c r="U365" t="inlineStr"/>
       <c r="V365" t="inlineStr">
         <is>
-          <t>2026-10-14T12:05:07+05:30</t>
-        </is>
-      </c>
-      <c r="W365" t="inlineStr">
-        <is>
-          <t>Mason Jewelers</t>
-        </is>
-      </c>
+          <t>2026-10-14T12:03:18+05:30</t>
+        </is>
+      </c>
+      <c r="W365" t="inlineStr"/>
       <c r="X365" t="inlineStr"/>
       <c r="Y365" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z365" t="inlineStr"/>
       <c r="AA365" t="inlineStr">
         <is>
-          <t>(765) 653-5012</t>
+          <t>(801) 776-8830</t>
         </is>
       </c>
       <c r="AB365" t="inlineStr">
         <is>
-          <t>https://facebook.com/masonjewelers.net, https://facebook.com/Masonjewelersco</t>
+          <t>https://instagram.com/aridiamondsutah, https://facebook.com/aridiamonds</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Moyer Fine Jewelers</t>
+          <t>Jewelry By Tommy</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Jewelers, Diamond Buyers, Watches</t>
+          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers, Diamonds</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>(317) 844-9003</t>
+          <t>(216) 464-6356</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>online@moyerfj.com</t>
+          <t>greg@jewelrybytommy.com</t>
         </is>
       </c>
       <c r="F366" t="inlineStr"/>
-      <c r="G366" t="inlineStr">
-        <is>
-          <t>Dan Moyer</t>
-        </is>
-      </c>
-      <c r="H366" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
+      <c r="G366" t="inlineStr"/>
+      <c r="H366" t="inlineStr"/>
       <c r="I366" s="2" t="inlineStr">
         <is>
-          <t>https://moyerfinejewelers.com</t>
+          <t>https://www.jewelrybytommy.com</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>14727 Thatcher Ln, Carmel, IN 46032</t>
+          <t>27600 Chagrin Blvd Ste 110, Woodmere, OH 44122</t>
         </is>
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>Carmel</t>
+          <t>Woodmere</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Indianapolis, IN</t>
+          <t>Cleveland, OH</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -41482,20 +41498,16 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O366" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P366" t="n">
-        <v>704</v>
-      </c>
+      <c r="O366" t="inlineStr"/>
+      <c r="P366" t="inlineStr"/>
       <c r="Q366" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/carmel-in/mip/moyer-fine-jewelers-7900799</t>
+          <t>https://www.yellowpages.com/woodmere-oh/mip/jewelry-by-tommy-479852454</t>
         </is>
       </c>
       <c r="R366" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, bench, custom-design</t>
+          <t>2 of 3, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S366" t="inlineStr">
@@ -41505,56 +41517,56 @@
       </c>
       <c r="T366" s="2" t="inlineStr">
         <is>
-          <t>https://www.moyerfinejewelers.com/pages/contact-us</t>
+          <t>https://jewelrybytommy.com/</t>
         </is>
       </c>
       <c r="U366" t="inlineStr"/>
       <c r="V366" t="inlineStr">
         <is>
-          <t>2026-10-14T12:05:12+05:30</t>
+          <t>2026-10-14T12:01:03+05:30</t>
         </is>
       </c>
       <c r="W366" t="inlineStr"/>
       <c r="X366" t="inlineStr"/>
       <c r="Y366" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z366" t="inlineStr"/>
       <c r="AA366" t="inlineStr">
         <is>
-          <t>(317) 785-1080, (317) 785-1138</t>
+          <t>(440) 413-5888</t>
         </is>
       </c>
       <c r="AB366" t="inlineStr">
         <is>
-          <t>https://instagram.com/moyerfinejewelers, https://facebook.com/moyerfinejewelers, https://twitter.com/MoyerJewelers</t>
+          <t>https://facebook.com/JewelrybyTommy</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Caesar's Designs</t>
+          <t>Pearls Hope, Inc</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Designers, Jewelry Repairing</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>(412) 621-0345</t>
+          <t>(440) 249-7000</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>caesar@caesarsdesigns.com</t>
+          <t>intake@pearlshope.com</t>
         </is>
       </c>
       <c r="F367" t="inlineStr"/>
@@ -41562,27 +41574,27 @@
       <c r="H367" t="inlineStr"/>
       <c r="I367" s="2" t="inlineStr">
         <is>
-          <t>https://www.caesarsdesigns.com</t>
+          <t>https://pearlshope.com</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>5413 Walnut St, Pittsburgh, PA 15232</t>
+          <t>3659 Green Rd, Beachwood, OH 44122</t>
         </is>
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Beachwood</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Cleveland, OH</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -41590,20 +41602,16 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O367" t="n">
-        <v>5</v>
-      </c>
-      <c r="P367" t="n">
-        <v>180</v>
-      </c>
+      <c r="O367" t="inlineStr"/>
+      <c r="P367" t="inlineStr"/>
       <c r="Q367" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/pittsburgh-pa/mip/caesars-designs-9528656</t>
+          <t>https://www.yellowpages.com/beachwood-oh/mip/pearls-hope-inc-580059164</t>
         </is>
       </c>
       <c r="R367" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S367" t="inlineStr">
@@ -41613,84 +41621,88 @@
       </c>
       <c r="T367" s="2" t="inlineStr">
         <is>
-          <t>https://www.caesarsdesigns.com/</t>
+          <t>https://pearlshope.com/</t>
         </is>
       </c>
       <c r="U367" t="inlineStr"/>
       <c r="V367" t="inlineStr">
         <is>
-          <t>2026-10-14T12:05:19+05:30</t>
+          <t>2026-10-14T12:00:59+05:30</t>
         </is>
       </c>
       <c r="W367" t="inlineStr"/>
       <c r="X367" t="inlineStr"/>
       <c r="Y367" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z367" t="inlineStr"/>
       <c r="AA367" t="inlineStr">
         <is>
-          <t>(412) 400-8582</t>
-        </is>
-      </c>
-      <c r="AB367" t="inlineStr">
-        <is>
-          <t>https://facebook.com/CaesarsDesignsCreations, https://instagram.com/caesarsdesigns</t>
-        </is>
-      </c>
+          <t>(216) 452-0082, (614) 781-0400, (937) 222-0002</t>
+        </is>
+      </c>
+      <c r="AB367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Custom Jewelry</t>
+          <t>Dakota Watch Co</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Watch Repair, Watches</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>(813) 930-0380</t>
+          <t>(317) 624-9115</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>customhairtampabay@gmail.com</t>
+          <t>customerservice@dakotawatch.com</t>
         </is>
       </c>
       <c r="F368" t="inlineStr"/>
-      <c r="G368" t="inlineStr"/>
-      <c r="H368" t="inlineStr"/>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>Albert Cooper</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="I368" s="2" t="inlineStr">
         <is>
-          <t>https://customhairtampabay.com</t>
+          <t>https://dakotawatch.com</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>11612 N Nebraska Ave, Tampa, FL 33612</t>
+          <t>49 W Maryland St Ste 142, Indianapolis, IN 46204</t>
         </is>
       </c>
       <c r="K368" t="inlineStr">
         <is>
-          <t>Tampa</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Tampa, FL</t>
+          <t>Indianapolis, IN</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -41702,12 +41714,12 @@
       <c r="P368" t="inlineStr"/>
       <c r="Q368" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/tampa-fl/mip/custom-jewelry-481586478</t>
+          <t>https://www.yellowpages.com/indianapolis-in/mip/dakota-watch-co-25573661</t>
         </is>
       </c>
       <c r="R368" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design, since-1969</t>
+          <t>2 of 3, role-email, direct-line</t>
         </is>
       </c>
       <c r="S368" t="inlineStr">
@@ -41717,56 +41729,68 @@
       </c>
       <c r="T368" s="2" t="inlineStr">
         <is>
-          <t>https://www.customhairtampabay.com/</t>
+          <t>https://dakotawatch.com/</t>
         </is>
       </c>
       <c r="U368" t="inlineStr"/>
       <c r="V368" t="inlineStr">
         <is>
-          <t>2026-10-14T12:02:15+05:30</t>
+          <t>2026-10-14T12:04:54+05:30</t>
         </is>
       </c>
       <c r="W368" t="inlineStr">
         <is>
-          <t>Janas Jewlery</t>
-        </is>
-      </c>
-      <c r="X368" t="inlineStr"/>
+          <t>Dakota Watch Company, Cooper &amp; Co Inc</t>
+        </is>
+      </c>
+      <c r="X368" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, Pittsburgh, PA</t>
+        </is>
+      </c>
       <c r="Y368" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z368" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Z368" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA368" t="inlineStr">
         <is>
-          <t>(727) 725-1052, (813) 651-9484, (813) 932-5327</t>
-        </is>
-      </c>
-      <c r="AB368" t="inlineStr"/>
+          <t>(513) 879-3681</t>
+        </is>
+      </c>
+      <c r="AB368" t="inlineStr">
+        <is>
+          <t>https://facebook.com/profile.php?id=61550829076826, https://instagram.com/dakotawatch_co</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>R Wolf Fine Jewelers</t>
+          <t>Indianapolis Crown Jewel Inc</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Jewelers, Watches</t>
+          <t>Jewelers, Jewelry Repairing, Watch Repair</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>(813) 816-2619</t>
+          <t>(317) 602-3563</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>rb.wolf@hotmail.com</t>
+          <t>crownjewel.cj@gmail.com</t>
         </is>
       </c>
       <c r="F369" t="inlineStr"/>
@@ -41774,27 +41798,27 @@
       <c r="H369" t="inlineStr"/>
       <c r="I369" s="2" t="inlineStr">
         <is>
-          <t>https://rwolfjewelry.com</t>
+          <t>https://www.indycrownjewel.com</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>100 S Ashley Dr, Tampa, FL 33602</t>
+          <t>3760 N Emerson Ave, Indianapolis, IN 46218</t>
         </is>
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t>Tampa</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Tampa, FL</t>
+          <t>Indianapolis, IN</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -41806,12 +41830,12 @@
       <c r="P369" t="inlineStr"/>
       <c r="Q369" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/tampa-fl/mip/r-wolf-fine-jewelers-543840292</t>
+          <t>https://www.yellowpages.com/indianapolis-in/mip/indianapolis-crown-jewel-inc-545777926</t>
         </is>
       </c>
       <c r="R369" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, bench, custom-design</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S369" t="inlineStr">
@@ -41821,13 +41845,13 @@
       </c>
       <c r="T369" s="2" t="inlineStr">
         <is>
-          <t>https://rwolfjewelry.com/</t>
+          <t>https://www.indycrownjewel.com/</t>
         </is>
       </c>
       <c r="U369" t="inlineStr"/>
       <c r="V369" t="inlineStr">
         <is>
-          <t>2026-10-14T12:02:02+05:30</t>
+          <t>2026-10-14T12:04:25+05:30</t>
         </is>
       </c>
       <c r="W369" t="inlineStr"/>
@@ -41835,42 +41859,46 @@
       <c r="Y369" t="n">
         <v>0</v>
       </c>
-      <c r="Z369" t="inlineStr"/>
+      <c r="Z369" t="inlineStr">
+        <is>
+          <t>shared-switchboard</t>
+        </is>
+      </c>
       <c r="AA369" t="inlineStr">
         <is>
-          <t>(727) 275-0106</t>
+          <t>(317) 228-7485</t>
         </is>
       </c>
       <c r="AB369" t="inlineStr">
         <is>
-          <t>https://facebook.com/rwolf.jewelry, https://instagram.com/rwolfjewelry</t>
+          <t>https://facebook.com/indycrownjewelcollection, https://instagram.com/indycrownjewel</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Grafted Growers</t>
+          <t>Mason Jewelers Inc</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Designers</t>
+          <t>Jewelers, Appraisers</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>(984) 200-9545</t>
+          <t>(317) 839-3202</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>info@graftedgrowers.com</t>
+          <t>masonjewelers1957@gmail.com</t>
         </is>
       </c>
       <c r="F370" t="inlineStr"/>
@@ -41878,27 +41906,27 @@
       <c r="H370" t="inlineStr"/>
       <c r="I370" s="2" t="inlineStr">
         <is>
-          <t>https://graftedgrowers.com</t>
+          <t>https://www.masonjewelersco.com</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>4025 Atlantic Ave, Raleigh, NC 27604</t>
+          <t>1822 E Main St, Plainfield, IN 46168</t>
         </is>
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t>Raleigh</t>
+          <t>Plainfield</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Raleigh, NC</t>
+          <t>Indianapolis, IN</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -41906,16 +41934,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O370" t="inlineStr"/>
-      <c r="P370" t="inlineStr"/>
+      <c r="O370" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P370" t="n">
+        <v>355</v>
+      </c>
       <c r="Q370" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/raleigh-nc/mip/grafted-growers-547754305</t>
+          <t>https://www.yellowpages.com/plainfield-in/mip/mason-jewelers-inc-705208</t>
         </is>
       </c>
       <c r="R370" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line</t>
+          <t>2 of 3, direct-line, since-1957</t>
         </is>
       </c>
       <c r="S370" t="inlineStr">
@@ -41925,84 +41957,96 @@
       </c>
       <c r="T370" s="2" t="inlineStr">
         <is>
-          <t>https://graftedgrowers.com/</t>
+          <t>https://www.masonjewelersco.com/</t>
         </is>
       </c>
       <c r="U370" t="inlineStr"/>
       <c r="V370" t="inlineStr">
         <is>
-          <t>2026-10-14T12:05:59+05:30</t>
-        </is>
-      </c>
-      <c r="W370" t="inlineStr"/>
+          <t>2026-10-14T12:05:07+05:30</t>
+        </is>
+      </c>
+      <c r="W370" t="inlineStr">
+        <is>
+          <t>Mason Jewelers</t>
+        </is>
+      </c>
       <c r="X370" t="inlineStr"/>
       <c r="Y370" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z370" t="inlineStr"/>
       <c r="AA370" t="inlineStr">
         <is>
-          <t>(919) 400-6022</t>
+          <t>(765) 653-5012</t>
         </is>
       </c>
       <c r="AB370" t="inlineStr">
         <is>
-          <t>https://facebook.com/graftedgrowers, https://instagram.com/graftedgrowers, https://twitter.com/GraftedGrowers</t>
+          <t>https://facebook.com/masonjewelers.net, https://facebook.com/Masonjewelersco</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Cajun Swamp</t>
+          <t>Moyer Fine Jewelers</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Jewelers, Gift Shops</t>
+          <t>Jewelers, Diamond Buyers, Watches</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>(504) 267-5075</t>
+          <t>(317) 844-9003</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>info@cajunencounters.com</t>
+          <t>online@moyerfj.com</t>
         </is>
       </c>
       <c r="F371" t="inlineStr"/>
-      <c r="G371" t="inlineStr"/>
-      <c r="H371" t="inlineStr"/>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>Dan Moyer</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="I371" s="2" t="inlineStr">
         <is>
-          <t>https://cajunencounters.com</t>
+          <t>https://moyerfinejewelers.com</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>631 Bourbon St, New Orleans, LA 70130</t>
+          <t>14727 Thatcher Ln, Carmel, IN 46032</t>
         </is>
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Carmel</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>New Orleans, LA</t>
+          <t>Indianapolis, IN</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -42010,16 +42054,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O371" t="inlineStr"/>
-      <c r="P371" t="inlineStr"/>
+      <c r="O371" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P371" t="n">
+        <v>704</v>
+      </c>
       <c r="Q371" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/new-orleans-la/mip/cajun-swamp-7275033</t>
+          <t>https://www.yellowpages.com/carmel-in/mip/moyer-fine-jewelers-7900799</t>
         </is>
       </c>
       <c r="R371" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, since-1997</t>
+          <t>2 of 3, direct-line, gia, bench, custom-design</t>
         </is>
       </c>
       <c r="S371" t="inlineStr">
@@ -42029,84 +42077,92 @@
       </c>
       <c r="T371" s="2" t="inlineStr">
         <is>
-          <t>https://www.cajunencounters.com/</t>
+          <t>https://www.moyerfinejewelers.com/pages/contact-us</t>
         </is>
       </c>
       <c r="U371" t="inlineStr"/>
       <c r="V371" t="inlineStr">
         <is>
-          <t>2026-10-14T12:06:52+05:30</t>
+          <t>2026-10-14T12:05:12+05:30</t>
         </is>
       </c>
       <c r="W371" t="inlineStr"/>
       <c r="X371" t="inlineStr"/>
       <c r="Y371" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z371" t="inlineStr"/>
       <c r="AA371" t="inlineStr">
         <is>
-          <t>(504) 834-1770</t>
+          <t>(317) 785-1080, (317) 785-1138</t>
         </is>
       </c>
       <c r="AB371" t="inlineStr">
         <is>
-          <t>https://facebook.com/CajunEncounters, https://twitter.com/cajunencounters, https://instagram.com/cajunencounters</t>
+          <t>https://instagram.com/moyerfinejewelers, https://facebook.com/moyerfinejewelers, https://twitter.com/MoyerJewelers</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>P &amp; R Jewelry Repair Inc</t>
+          <t>Bucci Jewelry Company</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Jewelry repair / goldsmith</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Jewelers, Watch Repair, Jewelry Repairing</t>
+          <t>Jewelers, Jewelry Designers, Jewelers-Wholesale &amp; Manufacturers</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>(504) 366-1878</t>
+          <t>(412) 391-1729</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>automatic8675@gmail.com</t>
+          <t>hello@buccijewelers.com</t>
         </is>
       </c>
       <c r="F372" t="inlineStr"/>
-      <c r="G372" t="inlineStr"/>
-      <c r="H372" t="inlineStr"/>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>Joe Bucci</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I372" s="2" t="inlineStr">
         <is>
-          <t>https://quinterandsonsjewelers.jewelershowcase.com</t>
+          <t>https://www.buccijewelers.com</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>197 Westbank Expy, Gretna, LA 70053</t>
+          <t>717 Liberty Ave, Suite 209, Pittsburgh, PA 15222</t>
         </is>
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t>Gretna</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>New Orleans, LA</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -42114,20 +42170,16 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O372" t="n">
-        <v>5</v>
-      </c>
-      <c r="P372" t="n">
-        <v>3</v>
-      </c>
+      <c r="O372" t="inlineStr"/>
+      <c r="P372" t="inlineStr"/>
       <c r="Q372" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/gretna-la/mip/p-r-jewelry-repair-inc-477806444</t>
+          <t>https://www.yellowpages.com/pittsburgh-pa/mip/bucci-jewelry-company-4896251</t>
         </is>
       </c>
       <c r="R372" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, bench, custom-design</t>
+          <t>2 of 3, role-email, direct-line, gia, bench, custom-design, since-1987</t>
         </is>
       </c>
       <c r="S372" t="inlineStr">
@@ -42137,64 +42189,56 @@
       </c>
       <c r="T372" s="2" t="inlineStr">
         <is>
-          <t>https://quinterandsonsjewelers.jewelershowcase.com/contactthisjeweler</t>
+          <t>https://www.buccijewelers.com/</t>
         </is>
       </c>
       <c r="U372" t="inlineStr"/>
       <c r="V372" t="inlineStr">
         <is>
-          <t>2026-10-14T12:07:32+05:30</t>
-        </is>
-      </c>
-      <c r="W372" t="inlineStr">
-        <is>
-          <t>Sol's Jewelers</t>
-        </is>
-      </c>
+          <t>2026-10-14T12:06:18+05:30</t>
+        </is>
+      </c>
+      <c r="W372" t="inlineStr"/>
       <c r="X372" t="inlineStr"/>
       <c r="Y372" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z372" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z372" t="inlineStr"/>
       <c r="AA372" t="inlineStr">
         <is>
-          <t>(985) 335-0908</t>
+          <t>(610) 828-1637</t>
         </is>
       </c>
       <c r="AB372" t="inlineStr">
         <is>
-          <t>https://facebook.com/StullerInc, https://instagram.com/StullerInc, https://x.com/StullerInc</t>
+          <t>https://instagram.com/ilovejoebucci, https://facebook.com/bucci.jewelers, https://instagram.com/buccijewelers</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Quarter Past Time</t>
+          <t>Caesar's Designs</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Jewelry Designers, Jewelry Repairing</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>(504) 410-0010</t>
+          <t>(412) 621-0345</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>hello@quarterstitch.com</t>
+          <t>caesar@caesarsdesigns.com</t>
         </is>
       </c>
       <c r="F373" t="inlineStr"/>
@@ -42202,27 +42246,27 @@
       <c r="H373" t="inlineStr"/>
       <c r="I373" s="2" t="inlineStr">
         <is>
-          <t>https://quarterstitch.com</t>
+          <t>https://www.caesarsdesigns.com</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>606 Chartres St, New Orleans, LA 70130</t>
+          <t>5413 Walnut St, Pittsburgh, PA 15232</t>
         </is>
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>New Orleans, LA</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -42230,16 +42274,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O373" t="inlineStr"/>
-      <c r="P373" t="inlineStr"/>
+      <c r="O373" t="n">
+        <v>5</v>
+      </c>
+      <c r="P373" t="n">
+        <v>180</v>
+      </c>
       <c r="Q373" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/new-orleans-la/mip/quarter-past-time-4483088</t>
+          <t>https://www.yellowpages.com/pittsburgh-pa/mip/caesars-designs-9528656</t>
         </is>
       </c>
       <c r="R373" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, since-1969</t>
+          <t>2 of 3, direct-line, gia, custom-design</t>
         </is>
       </c>
       <c r="S373" t="inlineStr">
@@ -42249,34 +42297,1098 @@
       </c>
       <c r="T373" s="2" t="inlineStr">
         <is>
-          <t>https://www.quarterstitch.com/contact</t>
+          <t>https://www.caesarsdesigns.com/</t>
         </is>
       </c>
       <c r="U373" t="inlineStr"/>
       <c r="V373" t="inlineStr">
         <is>
-          <t>2026-10-14T12:06:57+05:30</t>
+          <t>2026-10-14T12:05:19+05:30</t>
         </is>
       </c>
       <c r="W373" t="inlineStr"/>
       <c r="X373" t="inlineStr"/>
       <c r="Y373" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z373" t="inlineStr"/>
       <c r="AA373" t="inlineStr">
         <is>
+          <t>(412) 400-8582</t>
+        </is>
+      </c>
+      <c r="AB373" t="inlineStr">
+        <is>
+          <t>https://facebook.com/CaesarsDesignsCreations, https://instagram.com/caesarsdesigns</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Infinity Jewelers</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Jewelers</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>(443) 985-2476</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>customers@infinityjeweler.net</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr"/>
+      <c r="G374" t="inlineStr"/>
+      <c r="H374" t="inlineStr"/>
+      <c r="I374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infinity-jewelers.com</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>6901 Security Blvd, Baltimore, MD 21244</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Baltimore</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>Baltimore, MD</t>
+        </is>
+      </c>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr"/>
+      <c r="P374" t="inlineStr"/>
+      <c r="Q374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/baltimore-md/mip/infinity-jewelers-540149418</t>
+        </is>
+      </c>
+      <c r="R374" t="inlineStr">
+        <is>
+          <t>2 of 3, direct-line, since-2014</t>
+        </is>
+      </c>
+      <c r="S374" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infinity-jewelers.com/</t>
+        </is>
+      </c>
+      <c r="U374" t="inlineStr"/>
+      <c r="V374" t="inlineStr">
+        <is>
+          <t>2026-10-14T12:07:31+05:30</t>
+        </is>
+      </c>
+      <c r="W374" t="inlineStr"/>
+      <c r="X374" t="inlineStr"/>
+      <c r="Y374" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z374" t="inlineStr"/>
+      <c r="AA374" t="inlineStr">
+        <is>
+          <t>(443) 985-2376</t>
+        </is>
+      </c>
+      <c r="AB374" t="inlineStr">
+        <is>
+          <t>https://INSTAGRAM.COM/INFINITY.JEWELERS, https://instagram.com/infinity.jewelers, https://facebook.com/infinityjewelers1</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Kaylah Diamonds &amp; Jewelry</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>(410) 580-1149</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>sales@kaylahdiamonds.com</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr"/>
+      <c r="G375" t="inlineStr"/>
+      <c r="H375" t="inlineStr"/>
+      <c r="I375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kaylahdiamonds.com</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>1312 Reisterstown Rd, Pikesville, MD 21208</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Pikesville</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>Baltimore, MD</t>
+        </is>
+      </c>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr"/>
+      <c r="P375" t="inlineStr"/>
+      <c r="Q375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/pikesville-md/mip/kaylah-diamonds-jewelry-547970048</t>
+        </is>
+      </c>
+      <c r="R375" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
+        </is>
+      </c>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T375" s="2" t="inlineStr">
+        <is>
+          <t>https://kaylahdiamonds.com/</t>
+        </is>
+      </c>
+      <c r="U375" t="inlineStr"/>
+      <c r="V375" t="inlineStr">
+        <is>
+          <t>2026-10-14T12:07:46+05:30</t>
+        </is>
+      </c>
+      <c r="W375" t="inlineStr"/>
+      <c r="X375" t="inlineStr"/>
+      <c r="Y375" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z375" t="inlineStr"/>
+      <c r="AA375" t="inlineStr">
+        <is>
+          <t>(732) 367-4653</t>
+        </is>
+      </c>
+      <c r="AB375" t="inlineStr">
+        <is>
+          <t>https://facebook.com/KaylahDesigns, https://instagram.com/kaylah_diamonds, https://twitter.com/kaylahdiamonds</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Custom Jewelry</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Custom / bespoke jeweler</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Jewelers</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>(813) 930-0380</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>customhairtampabay@gmail.com</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr"/>
+      <c r="G376" t="inlineStr"/>
+      <c r="H376" t="inlineStr"/>
+      <c r="I376" s="2" t="inlineStr">
+        <is>
+          <t>https://customhairtampabay.com</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>11612 N Nebraska Ave, Tampa, FL 33612</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Tampa</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>Tampa, FL</t>
+        </is>
+      </c>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr"/>
+      <c r="P376" t="inlineStr"/>
+      <c r="Q376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/tampa-fl/mip/custom-jewelry-481586478</t>
+        </is>
+      </c>
+      <c r="R376" t="inlineStr">
+        <is>
+          <t>2 of 3, direct-line, custom-design, since-1969</t>
+        </is>
+      </c>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.customhairtampabay.com/</t>
+        </is>
+      </c>
+      <c r="U376" t="inlineStr"/>
+      <c r="V376" t="inlineStr">
+        <is>
+          <t>2026-10-14T12:02:15+05:30</t>
+        </is>
+      </c>
+      <c r="W376" t="inlineStr">
+        <is>
+          <t>Janas Jewlery</t>
+        </is>
+      </c>
+      <c r="X376" t="inlineStr"/>
+      <c r="Y376" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z376" t="inlineStr"/>
+      <c r="AA376" t="inlineStr">
+        <is>
+          <t>(727) 725-1052, (813) 651-9484, (813) 932-5327</t>
+        </is>
+      </c>
+      <c r="AB376" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>R Wolf Fine Jewelers</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Custom / bespoke jeweler</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Jewelers, Watches</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>(813) 816-2619</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>rb.wolf@hotmail.com</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr"/>
+      <c r="G377" t="inlineStr"/>
+      <c r="H377" t="inlineStr"/>
+      <c r="I377" s="2" t="inlineStr">
+        <is>
+          <t>https://rwolfjewelry.com</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>100 S Ashley Dr, Tampa, FL 33602</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Tampa</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>Tampa, FL</t>
+        </is>
+      </c>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr"/>
+      <c r="P377" t="inlineStr"/>
+      <c r="Q377" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/tampa-fl/mip/r-wolf-fine-jewelers-543840292</t>
+        </is>
+      </c>
+      <c r="R377" t="inlineStr">
+        <is>
+          <t>2 of 3, direct-line, bench, custom-design</t>
+        </is>
+      </c>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T377" s="2" t="inlineStr">
+        <is>
+          <t>https://rwolfjewelry.com/</t>
+        </is>
+      </c>
+      <c r="U377" t="inlineStr"/>
+      <c r="V377" t="inlineStr">
+        <is>
+          <t>2026-10-14T12:02:02+05:30</t>
+        </is>
+      </c>
+      <c r="W377" t="inlineStr"/>
+      <c r="X377" t="inlineStr"/>
+      <c r="Y377" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z377" t="inlineStr"/>
+      <c r="AA377" t="inlineStr">
+        <is>
+          <t>(727) 275-0106</t>
+        </is>
+      </c>
+      <c r="AB377" t="inlineStr">
+        <is>
+          <t>https://facebook.com/rwolf.jewelry, https://instagram.com/rwolfjewelry</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Grafted Growers</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Custom / bespoke jeweler</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Jewelers, Jewelry Designers</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>(984) 200-9545</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>info@graftedgrowers.com</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr"/>
+      <c r="G378" t="inlineStr"/>
+      <c r="H378" t="inlineStr"/>
+      <c r="I378" s="2" t="inlineStr">
+        <is>
+          <t>https://graftedgrowers.com</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>4025 Atlantic Ave, Raleigh, NC 27604</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Raleigh</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>Raleigh, NC</t>
+        </is>
+      </c>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr"/>
+      <c r="P378" t="inlineStr"/>
+      <c r="Q378" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/raleigh-nc/mip/grafted-growers-547754305</t>
+        </is>
+      </c>
+      <c r="R378" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line</t>
+        </is>
+      </c>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T378" s="2" t="inlineStr">
+        <is>
+          <t>https://graftedgrowers.com/</t>
+        </is>
+      </c>
+      <c r="U378" t="inlineStr"/>
+      <c r="V378" t="inlineStr">
+        <is>
+          <t>2026-10-14T12:05:59+05:30</t>
+        </is>
+      </c>
+      <c r="W378" t="inlineStr"/>
+      <c r="X378" t="inlineStr"/>
+      <c r="Y378" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z378" t="inlineStr"/>
+      <c r="AA378" t="inlineStr">
+        <is>
+          <t>(919) 400-6022</t>
+        </is>
+      </c>
+      <c r="AB378" t="inlineStr">
+        <is>
+          <t>https://facebook.com/graftedgrowers, https://instagram.com/graftedgrowers, https://twitter.com/GraftedGrowers</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Amir &amp; Associates Inc</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Jewelers, Diamonds-Wholesale</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>(504) 888-0229</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> amir@amircpas.com</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr"/>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>Amir Mujahid</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="I379" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amircpas.com</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>3655 Veterans Memorial Blvd, Metairie, LA 70002</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metairie</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>New Orleans, LA</t>
+        </is>
+      </c>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr"/>
+      <c r="P379" t="inlineStr"/>
+      <c r="Q379" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/metairie-la/mip/amir-associates-inc-541918551</t>
+        </is>
+      </c>
+      <c r="R379" t="inlineStr">
+        <is>
+          <t>2 of 3, direct-line, since-2008</t>
+        </is>
+      </c>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T379" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amircpas.com/contact</t>
+        </is>
+      </c>
+      <c r="U379" t="inlineStr"/>
+      <c r="V379" t="inlineStr">
+        <is>
+          <t>2026-10-14T12:07:40+05:30</t>
+        </is>
+      </c>
+      <c r="W379" t="inlineStr"/>
+      <c r="X379" t="inlineStr"/>
+      <c r="Y379" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z379" t="inlineStr"/>
+      <c r="AA379" t="inlineStr">
+        <is>
+          <t>(310) 214-6699</t>
+        </is>
+      </c>
+      <c r="AB379" t="inlineStr">
+        <is>
+          <t>https://facebook.com/AmirAndAssociatesCPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Brilliance In Diamonds - The Engagement Specialists</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Custom / bespoke jeweler</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers, Diamonds</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>(504) 383-8669</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>info@brillianceindiamonds.com</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr"/>
+      <c r="G380" t="inlineStr"/>
+      <c r="H380" t="inlineStr"/>
+      <c r="I380" s="2" t="inlineStr">
+        <is>
+          <t>https://www.brillianceindiamonds.com</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>3000 Kingman St Ste 215, Metairie, LA 70006</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metairie</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>New Orleans, LA</t>
+        </is>
+      </c>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O380" t="n">
+        <v>5</v>
+      </c>
+      <c r="P380" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q380" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/metairie-la/mip/brilliance-in-diamonds-the-engagement-specialists-479872499</t>
+        </is>
+      </c>
+      <c r="R380" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line</t>
+        </is>
+      </c>
+      <c r="S380" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T380" s="2" t="inlineStr">
+        <is>
+          <t>https://brillianceindiamonds.com/</t>
+        </is>
+      </c>
+      <c r="U380" t="inlineStr"/>
+      <c r="V380" t="inlineStr">
+        <is>
+          <t>2026-10-14T12:07:46+05:30</t>
+        </is>
+      </c>
+      <c r="W380" t="inlineStr"/>
+      <c r="X380" t="inlineStr"/>
+      <c r="Y380" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z380" t="inlineStr"/>
+      <c r="AA380" t="inlineStr">
+        <is>
+          <t>(504) 532-7474, (504) 655-9224</t>
+        </is>
+      </c>
+      <c r="AB380" t="inlineStr">
+        <is>
+          <t>https://facebook.com/BrillianceInDiamonds, https://instagram.com/brillianceindiamonds</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Cajun Swamp</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Jewelers, Gift Shops</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>(504) 267-5075</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>info@cajunencounters.com</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr"/>
+      <c r="G381" t="inlineStr"/>
+      <c r="H381" t="inlineStr"/>
+      <c r="I381" s="2" t="inlineStr">
+        <is>
+          <t>https://cajunencounters.com</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>631 Bourbon St, New Orleans, LA 70130</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>New Orleans</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>New Orleans, LA</t>
+        </is>
+      </c>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr"/>
+      <c r="P381" t="inlineStr"/>
+      <c r="Q381" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/new-orleans-la/mip/cajun-swamp-7275033</t>
+        </is>
+      </c>
+      <c r="R381" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, since-1997</t>
+        </is>
+      </c>
+      <c r="S381" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T381" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cajunencounters.com/</t>
+        </is>
+      </c>
+      <c r="U381" t="inlineStr"/>
+      <c r="V381" t="inlineStr">
+        <is>
+          <t>2026-10-14T12:06:52+05:30</t>
+        </is>
+      </c>
+      <c r="W381" t="inlineStr"/>
+      <c r="X381" t="inlineStr"/>
+      <c r="Y381" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z381" t="inlineStr"/>
+      <c r="AA381" t="inlineStr">
+        <is>
+          <t>(504) 834-1770</t>
+        </is>
+      </c>
+      <c r="AB381" t="inlineStr">
+        <is>
+          <t>https://facebook.com/CajunEncounters, https://twitter.com/cajunencounters, https://instagram.com/cajunencounters</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>P &amp; R Jewelry Repair Inc</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Jewelry repair / goldsmith</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Jewelers, Watch Repair, Jewelry Repairing</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>(504) 366-1878</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>automatic8675@gmail.com</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr"/>
+      <c r="G382" t="inlineStr"/>
+      <c r="H382" t="inlineStr"/>
+      <c r="I382" s="2" t="inlineStr">
+        <is>
+          <t>https://quinterandsonsjewelers.jewelershowcase.com</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>197 Westbank Expy, Gretna, LA 70053</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Gretna</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>New Orleans, LA</t>
+        </is>
+      </c>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O382" t="n">
+        <v>5</v>
+      </c>
+      <c r="P382" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/gretna-la/mip/p-r-jewelry-repair-inc-477806444</t>
+        </is>
+      </c>
+      <c r="R382" t="inlineStr">
+        <is>
+          <t>2 of 3, direct-line, gia, bench, custom-design</t>
+        </is>
+      </c>
+      <c r="S382" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T382" s="2" t="inlineStr">
+        <is>
+          <t>https://quinterandsonsjewelers.jewelershowcase.com/contactthisjeweler</t>
+        </is>
+      </c>
+      <c r="U382" t="inlineStr"/>
+      <c r="V382" t="inlineStr">
+        <is>
+          <t>2026-10-14T12:07:32+05:30</t>
+        </is>
+      </c>
+      <c r="W382" t="inlineStr">
+        <is>
+          <t>Sol's Jewelers</t>
+        </is>
+      </c>
+      <c r="X382" t="inlineStr"/>
+      <c r="Y382" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z382" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="AA382" t="inlineStr">
+        <is>
+          <t>(985) 335-0908</t>
+        </is>
+      </c>
+      <c r="AB382" t="inlineStr">
+        <is>
+          <t>https://facebook.com/StullerInc, https://instagram.com/StullerInc, https://x.com/StullerInc</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Quarter Past Time</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Jewelers</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>(504) 410-0010</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>hello@quarterstitch.com</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr"/>
+      <c r="G383" t="inlineStr"/>
+      <c r="H383" t="inlineStr"/>
+      <c r="I383" s="2" t="inlineStr">
+        <is>
+          <t>https://quarterstitch.com</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>606 Chartres St, New Orleans, LA 70130</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>New Orleans</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>New Orleans, LA</t>
+        </is>
+      </c>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr"/>
+      <c r="P383" t="inlineStr"/>
+      <c r="Q383" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/new-orleans-la/mip/quarter-past-time-4483088</t>
+        </is>
+      </c>
+      <c r="R383" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, since-1969</t>
+        </is>
+      </c>
+      <c r="S383" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T383" s="2" t="inlineStr">
+        <is>
+          <t>https://www.quarterstitch.com/contact</t>
+        </is>
+      </c>
+      <c r="U383" t="inlineStr"/>
+      <c r="V383" t="inlineStr">
+        <is>
+          <t>2026-10-14T12:06:57+05:30</t>
+        </is>
+      </c>
+      <c r="W383" t="inlineStr"/>
+      <c r="X383" t="inlineStr"/>
+      <c r="Y383" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z383" t="inlineStr"/>
+      <c r="AA383" t="inlineStr">
+        <is>
           <t>(504) 522-4451</t>
         </is>
       </c>
-      <c r="AB373" t="inlineStr">
+      <c r="AB383" t="inlineStr">
         <is>
           <t>https://instagram.com/quarter_stitch, https://facebook.com/TheQuarterStitch</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB373"/>
+  <autoFilter ref="A1:AB383"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId2"/>
@@ -43574,6 +44686,36 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I373" r:id="rId1294"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q373" r:id="rId1295"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T373" r:id="rId1296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I374" r:id="rId1297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q374" r:id="rId1298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T374" r:id="rId1299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I375" r:id="rId1300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q375" r:id="rId1301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T375" r:id="rId1302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I376" r:id="rId1303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q376" r:id="rId1304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T376" r:id="rId1305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I377" r:id="rId1306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q377" r:id="rId1307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T377" r:id="rId1308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I378" r:id="rId1309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q378" r:id="rId1310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T378" r:id="rId1311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I379" r:id="rId1312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q379" r:id="rId1313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T379" r:id="rId1314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I380" r:id="rId1315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q380" r:id="rId1316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T380" r:id="rId1317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I381" r:id="rId1318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q381" r:id="rId1319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T381" r:id="rId1320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I382" r:id="rId1321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q382" r:id="rId1322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T382" r:id="rId1323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I383" r:id="rId1324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q383" r:id="rId1325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T383" r:id="rId1326"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -43749,7 +44891,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C6" t="n">
         <v>8</v>
@@ -43857,7 +44999,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C10" t="n">
         <v>11</v>
@@ -44046,7 +45188,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C17" t="n">
         <v>6</v>
@@ -44127,7 +45269,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C20" t="n">
         <v>5</v>
@@ -44316,21 +45458,21 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>208</v>
+        <v>245</v>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -44343,21 +45485,21 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1.0%</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" t="n">
         <v>1</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -44370,7 +45512,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -44397,14 +45539,14 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="C30" t="n">
         <v>2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -44424,21 +45566,21 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>101</v>
+        <v>165</v>
       </c>
       <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" t="n">
         <v>1</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>1.0%</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -44451,7 +45593,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -44505,7 +45647,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -44532,7 +45674,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -44559,7 +45701,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -44586,7 +45728,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C37" t="n">
         <v>2</v>
@@ -44613,7 +45755,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -44667,21 +45809,21 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="n">
         <v>1</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -44694,18 +45836,18 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>158</v>
+        <v>218</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -44721,7 +45863,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -44802,7 +45944,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
@@ -44829,21 +45971,21 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -44856,10 +45998,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>14586</v>
+        <v>14836</v>
       </c>
       <c r="C47" t="n">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -44867,10 +46009,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="F47" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="G47" t="n">
         <v>94</v>
@@ -44913,7 +46055,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3">
@@ -44923,7 +46065,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4">
@@ -44933,7 +46075,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
@@ -44965,7 +46107,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>140</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9">
@@ -44975,7 +46117,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10">
@@ -45024,7 +46166,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T12:41:27+05:30</t>
+          <t>2026-10-14T13:02:00+05:30</t>
         </is>
       </c>
     </row>
@@ -45035,7 +46177,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>372</v>
+        <v>382</v>
       </c>
     </row>
     <row r="3">
@@ -45045,7 +46187,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>14586</v>
+        <v>14836</v>
       </c>
     </row>
     <row r="4">

--- a/leadrun_jewelry/jewelry_qualified.xlsx
+++ b/leadrun_jewelry/jewelry_qualified.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qualified Leads'!$A$1:$AB$383</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qualified Leads'!$A$1:$AB$391</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB383"/>
+  <dimension ref="A1:AB391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -26500,7 +26500,7 @@
       </c>
       <c r="W232" t="inlineStr">
         <is>
-          <t>Morgan Jewelers - Meadows Mall, Morgan Jewelers, Morgan Jewelers-Boulevard Mall, Morgan Jewelers - Boulevard Mall</t>
+          <t>Morgan Jewelers - Meadows Mall, Morgan Jewelers - City Creek, Morgan Jewelers - Valley Fair Mall, Morgan Jewelers - Center of Brilliance, Morgan Jewelers, Morgan Jewelers-Boulevard Mall, Morgan Jewelers - Boulevard Mall, Morgan Jewellers</t>
         </is>
       </c>
       <c r="X232" t="inlineStr">
@@ -26509,7 +26509,7 @@
         </is>
       </c>
       <c r="Y232" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Z232" t="inlineStr">
         <is>
@@ -40586,45 +40586,53 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>The Jewel of Art Dance Studio</t>
+          <t>Hyo Silver Buckles &amp; Jewelry</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>(210) 878-4089</t>
+          <t>(830) 796-7961</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>info@jewelofartdance.com</t>
+          <t>customerservice@hyosilver.com</t>
         </is>
       </c>
       <c r="F358" t="inlineStr"/>
-      <c r="G358" t="inlineStr"/>
-      <c r="H358" t="inlineStr"/>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>Joanne D. Symons</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
       <c r="I358" s="2" t="inlineStr">
         <is>
-          <t>https://jewelofartdance.com</t>
+          <t>https://hyosilver.com</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>1909 Fredericksburg Rd, San Antonio, TX 78201</t>
+          <t>1107 12th St, Bandera, TX 78003-3454</t>
         </is>
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Bandera</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
@@ -40639,19 +40647,19 @@
       </c>
       <c r="N358" t="inlineStr">
         <is>
-          <t>YellowPages</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="O358" t="inlineStr"/>
       <c r="P358" t="inlineStr"/>
       <c r="Q358" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/san-antonio-tx/mip/the-jewel-of-art-dance-studio-547319903</t>
+          <t>https://www.bbb.org/us/tx/bandera/profile/jewelry-stores/hyo-silver-buckles-jewelry-0825-90105642</t>
         </is>
       </c>
       <c r="R358" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-2003</t>
         </is>
       </c>
       <c r="S358" t="inlineStr">
@@ -40661,13 +40669,13 @@
       </c>
       <c r="T358" s="2" t="inlineStr">
         <is>
-          <t>https://jewelofartdance.com/</t>
+          <t>https://hyosilver.com/</t>
         </is>
       </c>
       <c r="U358" t="inlineStr"/>
       <c r="V358" t="inlineStr">
         <is>
-          <t>2026-10-14T12:12:32+05:30</t>
+          <t>2026-10-14T12:27:35+05:30</t>
         </is>
       </c>
       <c r="W358" t="inlineStr"/>
@@ -40678,39 +40686,39 @@
       <c r="Z358" t="inlineStr"/>
       <c r="AA358" t="inlineStr">
         <is>
-          <t>(210) 639-3756</t>
+          <t>(830) 850-0500</t>
         </is>
       </c>
       <c r="AB358" t="inlineStr">
         <is>
-          <t>https://facebook.com/jewelofartdance, https://twitter.com/jewelofartdance, https://instagram.com/jewelofartdance</t>
+          <t>https://instagram.com/hyo_silver, https://facebook.com/HyOSilverJewelry, https://twitter.com/hyosilverdotcom, https://x.com/hyosilverdotcom</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Tito Rosy Jewelry</t>
+          <t>The Jewel of Art Dance Studio</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Jewelry manufacturer</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>(210) 255-1265</t>
+          <t>(210) 878-4089</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>titorosyjewelry1@gmail.com</t>
+          <t>info@jewelofartdance.com</t>
         </is>
       </c>
       <c r="F359" t="inlineStr"/>
@@ -40718,16 +40726,24 @@
       <c r="H359" t="inlineStr"/>
       <c r="I359" s="2" t="inlineStr">
         <is>
-          <t>https://titorosyjewelry.com</t>
+          <t>https://jewelofartdance.com</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>5525 Blanco Rd #111, San Antonio, TX 78216, United States</t>
-        </is>
-      </c>
-      <c r="K359" t="inlineStr"/>
-      <c r="L359" t="inlineStr"/>
+          <t>1909 Fredericksburg Rd, San Antonio, TX 78201</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
       <c r="M359" t="inlineStr">
         <is>
           <t>San Antonio, TX</t>
@@ -40735,23 +40751,19 @@
       </c>
       <c r="N359" t="inlineStr">
         <is>
-          <t>Google Maps</t>
-        </is>
-      </c>
-      <c r="O359" t="n">
-        <v>5</v>
-      </c>
-      <c r="P359" t="n">
-        <v>42</v>
-      </c>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr"/>
+      <c r="P359" t="inlineStr"/>
       <c r="Q359" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Tito+Rosy+Jewelry/data=!4m7!3m6!1s0x865c5f773ae58179:0xd412e0884c474983!8m2!3d29.5045048!4d-98.5074043!16s%2Fg%2F11xy_tyxvc!19sChIJeYHlOndfXIYRg0lHTIjgEtQ</t>
+          <t>https://www.yellowpages.com/san-antonio-tx/mip/the-jewel-of-art-dance-studio-547319903</t>
         </is>
       </c>
       <c r="R359" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, role-email, direct-line</t>
         </is>
       </c>
       <c r="S359" t="inlineStr">
@@ -40761,13 +40773,13 @@
       </c>
       <c r="T359" s="2" t="inlineStr">
         <is>
-          <t>https://titorosyjewelry.com/contactactanos/</t>
+          <t>https://jewelofartdance.com/</t>
         </is>
       </c>
       <c r="U359" t="inlineStr"/>
       <c r="V359" t="inlineStr">
         <is>
-          <t>2026-10-14T12:18:46+05:30</t>
+          <t>2026-10-14T12:12:32+05:30</t>
         </is>
       </c>
       <c r="W359" t="inlineStr"/>
@@ -40778,39 +40790,39 @@
       <c r="Z359" t="inlineStr"/>
       <c r="AA359" t="inlineStr">
         <is>
-          <t>(786) 492-3645</t>
+          <t>(210) 639-3756</t>
         </is>
       </c>
       <c r="AB359" t="inlineStr">
         <is>
-          <t>https://instagram.com/titorosyjewelry1</t>
+          <t>https://facebook.com/jewelofartdance, https://twitter.com/jewelofartdance, https://instagram.com/jewelofartdance</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Alexander Design</t>
+          <t>Tito Rosy Jewelry</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers, Jewelry Designers</t>
+          <t>Jewelry manufacturer</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>(408) 998-4539</t>
+          <t>(210) 255-1265</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>sales@alexander-dm.com</t>
+          <t>titorosyjewelry1@gmail.com</t>
         </is>
       </c>
       <c r="F360" t="inlineStr"/>
@@ -40818,44 +40830,40 @@
       <c r="H360" t="inlineStr"/>
       <c r="I360" s="2" t="inlineStr">
         <is>
-          <t>https://alexander-dm.com</t>
+          <t>https://titorosyjewelry.com</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>1111 Story Rd Ste 1063, San Jose, CA 95122</t>
-        </is>
-      </c>
-      <c r="K360" t="inlineStr">
-        <is>
-          <t>San Jose</t>
-        </is>
-      </c>
-      <c r="L360" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
+          <t>5525 Blanco Rd #111, San Antonio, TX 78216, United States</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr"/>
+      <c r="L360" t="inlineStr"/>
       <c r="M360" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>San Antonio, TX</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O360" t="inlineStr"/>
-      <c r="P360" t="inlineStr"/>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="O360" t="n">
+        <v>5</v>
+      </c>
+      <c r="P360" t="n">
+        <v>42</v>
+      </c>
       <c r="Q360" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/san-jose-ca/mip/alexander-design-692537</t>
+          <t>https://www.google.com/maps/place/Tito+Rosy+Jewelry/data=!4m7!3m6!1s0x865c5f773ae58179:0xd412e0884c474983!8m2!3d29.5045048!4d-98.5074043!16s%2Fg%2F11xy_tyxvc!19sChIJeYHlOndfXIYRg0lHTIjgEtQ</t>
         </is>
       </c>
       <c r="R360" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design, since-2001</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S360" t="inlineStr">
@@ -40865,13 +40873,13 @@
       </c>
       <c r="T360" s="2" t="inlineStr">
         <is>
-          <t>https://www.alexander-dm.com/</t>
+          <t>https://titorosyjewelry.com/contactactanos/</t>
         </is>
       </c>
       <c r="U360" t="inlineStr"/>
       <c r="V360" t="inlineStr">
         <is>
-          <t>2026-10-14T12:05:25+05:30</t>
+          <t>2026-10-14T12:18:46+05:30</t>
         </is>
       </c>
       <c r="W360" t="inlineStr"/>
@@ -40882,35 +40890,39 @@
       <c r="Z360" t="inlineStr"/>
       <c r="AA360" t="inlineStr">
         <is>
-          <t>(213) 649-1924</t>
-        </is>
-      </c>
-      <c r="AB360" t="inlineStr"/>
+          <t>(786) 492-3645</t>
+        </is>
+      </c>
+      <c r="AB360" t="inlineStr">
+        <is>
+          <t>https://instagram.com/titorosyjewelry1</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Kumar Jewelers</t>
+          <t>Alexander Design</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers, Jewelry Designers</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>(408) 246-0850</t>
+          <t>(408) 998-4539</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>contact@kumarjewelers.com</t>
+          <t>sales@alexander-dm.com</t>
         </is>
       </c>
       <c r="F361" t="inlineStr"/>
@@ -40918,17 +40930,17 @@
       <c r="H361" t="inlineStr"/>
       <c r="I361" s="2" t="inlineStr">
         <is>
-          <t>https://kumarjewelers.com</t>
+          <t>https://alexander-dm.com</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>3418 El Camino Real, Santa Clara, CA 95051</t>
+          <t>1111 Story Rd Ste 1063, San Jose, CA 95122</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>San Jose</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
@@ -40946,20 +40958,16 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O361" t="n">
-        <v>5</v>
-      </c>
-      <c r="P361" t="n">
-        <v>1</v>
-      </c>
+      <c r="O361" t="inlineStr"/>
+      <c r="P361" t="inlineStr"/>
       <c r="Q361" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/santa-clara-ca/mip/kumar-jewelers-7772087</t>
+          <t>https://www.yellowpages.com/san-jose-ca/mip/alexander-design-692537</t>
         </is>
       </c>
       <c r="R361" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-2001</t>
         </is>
       </c>
       <c r="S361" t="inlineStr">
@@ -40969,13 +40977,13 @@
       </c>
       <c r="T361" s="2" t="inlineStr">
         <is>
-          <t>https://www.kumarjewelers.com/</t>
+          <t>https://www.alexander-dm.com/</t>
         </is>
       </c>
       <c r="U361" t="inlineStr"/>
       <c r="V361" t="inlineStr">
         <is>
-          <t>2026-10-14T12:17:16+05:30</t>
+          <t>2026-10-14T12:05:25+05:30</t>
         </is>
       </c>
       <c r="W361" t="inlineStr"/>
@@ -40986,65 +40994,53 @@
       <c r="Z361" t="inlineStr"/>
       <c r="AA361" t="inlineStr">
         <is>
-          <t>(510) 713-1040, (925) 248-2280</t>
-        </is>
-      </c>
-      <c r="AB361" t="inlineStr">
-        <is>
-          <t>https://facebook.com/kumarjewelers, https://instagram.com/kumarjewelers</t>
-        </is>
-      </c>
+          <t>(213) 649-1924</t>
+        </is>
+      </c>
+      <c r="AB361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>DeVons Jewelers</t>
+          <t>Kumar Jewelers</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Designers, Diamonds</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>(916) 929-3991</t>
+          <t>(408) 246-0850</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>info@devonsjewelers.com</t>
+          <t>contact@kumarjewelers.com</t>
         </is>
       </c>
       <c r="F362" t="inlineStr"/>
-      <c r="G362" t="inlineStr">
-        <is>
-          <t>Adam Blankenship</t>
-        </is>
-      </c>
-      <c r="H362" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
+      <c r="G362" t="inlineStr"/>
+      <c r="H362" t="inlineStr"/>
       <c r="I362" s="2" t="inlineStr">
         <is>
-          <t>https://www.devonsjewelers.com</t>
+          <t>https://kumarjewelers.com</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>1689 Arden Way, Sacramento, CA 95815</t>
+          <t>3418 El Camino Real, Santa Clara, CA 95051</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
@@ -41054,7 +41050,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Sacramento, CA</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -41066,16 +41062,16 @@
         <v>5</v>
       </c>
       <c r="P362" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Q362" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/sacramento-ca/mip/devons-jewelers-495526219</t>
+          <t>https://www.yellowpages.com/santa-clara-ca/mip/kumar-jewelers-7772087</t>
         </is>
       </c>
       <c r="R362" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S362" t="inlineStr">
@@ -41085,44 +41081,36 @@
       </c>
       <c r="T362" s="2" t="inlineStr">
         <is>
-          <t>https://www.devonsjewelers.com/</t>
+          <t>https://www.kumarjewelers.com/</t>
         </is>
       </c>
       <c r="U362" t="inlineStr"/>
       <c r="V362" t="inlineStr">
         <is>
-          <t>2026-10-14T12:07:30+05:30</t>
-        </is>
-      </c>
-      <c r="W362" t="inlineStr">
-        <is>
-          <t>De Vons Jewelers</t>
-        </is>
-      </c>
+          <t>2026-10-14T12:17:16+05:30</t>
+        </is>
+      </c>
+      <c r="W362" t="inlineStr"/>
       <c r="X362" t="inlineStr"/>
       <c r="Y362" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z362" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z362" t="inlineStr"/>
       <c r="AA362" t="inlineStr">
         <is>
-          <t>(209) 527-0196, (209) 726-8001, (209) 951-9610, (530) 223-2071, (530) 342-4493, (530) 674-2375, (559) 225-0496, (916) 788-4150</t>
+          <t>(510) 713-1040, (925) 248-2280</t>
         </is>
       </c>
       <c r="AB362" t="inlineStr">
         <is>
-          <t>https://facebook.com/devonsjewelers, https://instagram.com/devonsjewelers</t>
+          <t>https://facebook.com/kumarjewelers, https://instagram.com/kumarjewelers</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Kenny G &amp; Company Fine Jewelers</t>
+          <t>DeVons Jewelers</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -41137,30 +41125,38 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>(916) 691-9600</t>
+          <t>(916) 929-3991</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>citrusheights@kennygandco.com</t>
+          <t>info@devonsjewelers.com</t>
         </is>
       </c>
       <c r="F363" t="inlineStr"/>
-      <c r="G363" t="inlineStr"/>
-      <c r="H363" t="inlineStr"/>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>Adam Blankenship</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
       <c r="I363" s="2" t="inlineStr">
         <is>
-          <t>https://www.kennygandco.com</t>
+          <t>https://www.devonsjewelers.com</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>7440 Laguna Blvd Ste 112, Elk Grove, CA 95758</t>
+          <t>1689 Arden Way, Sacramento, CA 95815</t>
         </is>
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t>Elk Grove</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
@@ -41182,16 +41178,16 @@
         <v>5</v>
       </c>
       <c r="P363" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q363" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/elk-grove-ca/mip/kenny-g-company-fine-jewelers-5526854</t>
+          <t>https://www.yellowpages.com/sacramento-ca/mip/devons-jewelers-495526219</t>
         </is>
       </c>
       <c r="R363" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design, since-1997</t>
+          <t>2 of 3, role-email, direct-line</t>
         </is>
       </c>
       <c r="S363" t="inlineStr">
@@ -41201,56 +41197,64 @@
       </c>
       <c r="T363" s="2" t="inlineStr">
         <is>
-          <t>https://www.kennygandco.com/pages/contact</t>
+          <t>https://www.devonsjewelers.com/</t>
         </is>
       </c>
       <c r="U363" t="inlineStr"/>
       <c r="V363" t="inlineStr">
         <is>
-          <t>2026-10-14T12:08:14+05:30</t>
-        </is>
-      </c>
-      <c r="W363" t="inlineStr"/>
+          <t>2026-10-14T12:07:30+05:30</t>
+        </is>
+      </c>
+      <c r="W363" t="inlineStr">
+        <is>
+          <t>De Vons Jewelers</t>
+        </is>
+      </c>
       <c r="X363" t="inlineStr"/>
       <c r="Y363" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z363" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="Z363" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA363" t="inlineStr">
         <is>
-          <t>(775) 852-7700, (916) 772-8400, (916) 965-6664</t>
+          <t>(209) 527-0196, (209) 726-8001, (209) 951-9610, (530) 223-2071, (530) 342-4493, (530) 674-2375, (559) 225-0496, (916) 788-4150</t>
         </is>
       </c>
       <c r="AB363" t="inlineStr">
         <is>
-          <t>https://instagram.com/kennygandco, https://facebook.com/KennyGCo, https://instagram.com/kennygandco/</t>
+          <t>https://facebook.com/devonsjewelers, https://instagram.com/devonsjewelers</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Sacramento Watch &amp; Jewelry Service</t>
+          <t>Kenny G &amp; Company Fine Jewelers</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Jewelry repair / goldsmith</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Jewelry Designers, Diamonds</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>(916) 979-9106</t>
+          <t>(916) 691-9600</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>steve@sacramentowatchshop.com</t>
+          <t>citrusheights@kennygandco.com</t>
         </is>
       </c>
       <c r="F364" t="inlineStr"/>
@@ -41258,17 +41262,17 @@
       <c r="H364" t="inlineStr"/>
       <c r="I364" s="2" t="inlineStr">
         <is>
-          <t>https://sacramentowatchshop.com</t>
+          <t>https://www.kennygandco.com</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>1620 Fulton Ave, Sacramento, CA 95825</t>
+          <t>7440 Laguna Blvd Ste 112, Elk Grove, CA 95758</t>
         </is>
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Elk Grove</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
@@ -41286,16 +41290,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O364" t="inlineStr"/>
-      <c r="P364" t="inlineStr"/>
+      <c r="O364" t="n">
+        <v>5</v>
+      </c>
+      <c r="P364" t="n">
+        <v>1</v>
+      </c>
       <c r="Q364" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/sacramento-ca/mip/sacramento-watch-jewelry-service-519958764</t>
+          <t>https://www.yellowpages.com/elk-grove-ca/mip/kenny-g-company-fine-jewelers-5526854</t>
         </is>
       </c>
       <c r="R364" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, since-1995</t>
+          <t>2 of 3, direct-line, gia, custom-design, since-1997</t>
         </is>
       </c>
       <c r="S364" t="inlineStr">
@@ -41305,13 +41313,13 @@
       </c>
       <c r="T364" s="2" t="inlineStr">
         <is>
-          <t>https://sacramentowatchshop.com/</t>
+          <t>https://www.kennygandco.com/pages/contact</t>
         </is>
       </c>
       <c r="U364" t="inlineStr"/>
       <c r="V364" t="inlineStr">
         <is>
-          <t>2026-10-14T12:07:36+05:30</t>
+          <t>2026-10-14T12:08:14+05:30</t>
         </is>
       </c>
       <c r="W364" t="inlineStr"/>
@@ -41322,39 +41330,39 @@
       <c r="Z364" t="inlineStr"/>
       <c r="AA364" t="inlineStr">
         <is>
-          <t>(916) 550-1863</t>
+          <t>(775) 852-7700, (916) 772-8400, (916) 965-6664</t>
         </is>
       </c>
       <c r="AB364" t="inlineStr">
         <is>
-          <t>https://facebook.com/sacramentowatchshop, https://facebook.com/The-Watch-Shop-727641780765411</t>
+          <t>https://instagram.com/kennygandco, https://facebook.com/KennyGCo, https://instagram.com/kennygandco/</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Ari Diamonds</t>
+          <t>Prestigio Jewelers</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Jewelers, Diamonds-Wholesale, Jewelers-Wholesale &amp; Manufacturers</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>(801) 255-8992</t>
+          <t>(916) 455-5558</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>panna.aridiamonds@gmail.com</t>
+          <t>prestigiojewelers@hotmail.com</t>
         </is>
       </c>
       <c r="F365" t="inlineStr"/>
@@ -41362,27 +41370,27 @@
       <c r="H365" t="inlineStr"/>
       <c r="I365" s="2" t="inlineStr">
         <is>
-          <t>https://www.aridiamonds.com</t>
+          <t>https://prestigiojewelers.localsearch.com</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>807 E Fort Union Blvd, Midvale, UT 84047</t>
+          <t>4940 Stockton Blvd, Sacramento, CA 95820</t>
         </is>
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t>Midvale</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>UT</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT</t>
+          <t>Sacramento, CA</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -41391,19 +41399,19 @@
         </is>
       </c>
       <c r="O365" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P365" t="n">
-        <v>6</v>
+        <v>356</v>
       </c>
       <c r="Q365" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/midvale-ut/mip/ari-diamonds-23948160</t>
+          <t>https://www.yellowpages.com/sacramento-ca/mip/prestigio-jewelers-10705590</t>
         </is>
       </c>
       <c r="R365" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design, since-1994</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S365" t="inlineStr">
@@ -41413,56 +41421,56 @@
       </c>
       <c r="T365" s="2" t="inlineStr">
         <is>
-          <t>https://www.aridiamonds.com/</t>
+          <t>https://prestigiojewelers.localsearch.com/</t>
         </is>
       </c>
       <c r="U365" t="inlineStr"/>
       <c r="V365" t="inlineStr">
         <is>
-          <t>2026-10-14T12:03:18+05:30</t>
+          <t>2026-10-14T12:07:40+05:30</t>
         </is>
       </c>
       <c r="W365" t="inlineStr"/>
       <c r="X365" t="inlineStr"/>
       <c r="Y365" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z365" t="inlineStr"/>
       <c r="AA365" t="inlineStr">
         <is>
-          <t>(801) 776-8830</t>
+          <t>(209) 400-8864</t>
         </is>
       </c>
       <c r="AB365" t="inlineStr">
         <is>
-          <t>https://instagram.com/aridiamondsutah, https://facebook.com/aridiamonds</t>
+          <t>https://instagram.com/prestigiojewelers, https://facebook.com/prestigiojewelers</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Jewelry By Tommy</t>
+          <t>Sacramento Watch &amp; Jewelry Service</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Jewelry repair / goldsmith</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers, Diamonds</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>(216) 464-6356</t>
+          <t>(916) 979-9106</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>greg@jewelrybytommy.com</t>
+          <t>steve@sacramentowatchshop.com</t>
         </is>
       </c>
       <c r="F366" t="inlineStr"/>
@@ -41470,27 +41478,27 @@
       <c r="H366" t="inlineStr"/>
       <c r="I366" s="2" t="inlineStr">
         <is>
-          <t>https://www.jewelrybytommy.com</t>
+          <t>https://sacramentowatchshop.com</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>27600 Chagrin Blvd Ste 110, Woodmere, OH 44122</t>
+          <t>1620 Fulton Ave, Sacramento, CA 95825</t>
         </is>
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>Woodmere</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Cleveland, OH</t>
+          <t>Sacramento, CA</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -41502,12 +41510,12 @@
       <c r="P366" t="inlineStr"/>
       <c r="Q366" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/woodmere-oh/mip/jewelry-by-tommy-479852454</t>
+          <t>https://www.yellowpages.com/sacramento-ca/mip/sacramento-watch-jewelry-service-519958764</t>
         </is>
       </c>
       <c r="R366" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design</t>
+          <t>2 of 3, direct-line, since-1995</t>
         </is>
       </c>
       <c r="S366" t="inlineStr">
@@ -41517,13 +41525,13 @@
       </c>
       <c r="T366" s="2" t="inlineStr">
         <is>
-          <t>https://jewelrybytommy.com/</t>
+          <t>https://sacramentowatchshop.com/</t>
         </is>
       </c>
       <c r="U366" t="inlineStr"/>
       <c r="V366" t="inlineStr">
         <is>
-          <t>2026-10-14T12:01:03+05:30</t>
+          <t>2026-10-14T12:07:36+05:30</t>
         </is>
       </c>
       <c r="W366" t="inlineStr"/>
@@ -41534,39 +41542,39 @@
       <c r="Z366" t="inlineStr"/>
       <c r="AA366" t="inlineStr">
         <is>
-          <t>(440) 413-5888</t>
+          <t>(916) 550-1863</t>
         </is>
       </c>
       <c r="AB366" t="inlineStr">
         <is>
-          <t>https://facebook.com/JewelrybyTommy</t>
+          <t>https://facebook.com/sacramentowatchshop, https://facebook.com/The-Watch-Shop-727641780765411</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Pearls Hope, Inc</t>
+          <t>Ari Diamonds</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Diamonds-Wholesale, Jewelers-Wholesale &amp; Manufacturers</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>(440) 249-7000</t>
+          <t>(801) 255-8992</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>intake@pearlshope.com</t>
+          <t>panna.aridiamonds@gmail.com</t>
         </is>
       </c>
       <c r="F367" t="inlineStr"/>
@@ -41574,27 +41582,27 @@
       <c r="H367" t="inlineStr"/>
       <c r="I367" s="2" t="inlineStr">
         <is>
-          <t>https://pearlshope.com</t>
+          <t>https://www.aridiamonds.com</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>3659 Green Rd, Beachwood, OH 44122</t>
+          <t>807 E Fort Union Blvd, Midvale, UT 84047</t>
         </is>
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t>Beachwood</t>
+          <t>Midvale</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>UT</t>
         </is>
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Cleveland, OH</t>
+          <t>Salt Lake City, UT</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -41602,16 +41610,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O367" t="inlineStr"/>
-      <c r="P367" t="inlineStr"/>
+      <c r="O367" t="n">
+        <v>5</v>
+      </c>
+      <c r="P367" t="n">
+        <v>6</v>
+      </c>
       <c r="Q367" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/beachwood-oh/mip/pearls-hope-inc-580059164</t>
+          <t>https://www.yellowpages.com/midvale-ut/mip/ari-diamonds-23948160</t>
         </is>
       </c>
       <c r="R367" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, direct-line, custom-design, since-1994</t>
         </is>
       </c>
       <c r="S367" t="inlineStr">
@@ -41621,32 +41633,36 @@
       </c>
       <c r="T367" s="2" t="inlineStr">
         <is>
-          <t>https://pearlshope.com/</t>
+          <t>https://www.aridiamonds.com/</t>
         </is>
       </c>
       <c r="U367" t="inlineStr"/>
       <c r="V367" t="inlineStr">
         <is>
-          <t>2026-10-14T12:00:59+05:30</t>
+          <t>2026-10-14T12:03:18+05:30</t>
         </is>
       </c>
       <c r="W367" t="inlineStr"/>
       <c r="X367" t="inlineStr"/>
       <c r="Y367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z367" t="inlineStr"/>
       <c r="AA367" t="inlineStr">
         <is>
-          <t>(216) 452-0082, (614) 781-0400, (937) 222-0002</t>
-        </is>
-      </c>
-      <c r="AB367" t="inlineStr"/>
+          <t>(801) 776-8830</t>
+        </is>
+      </c>
+      <c r="AB367" t="inlineStr">
+        <is>
+          <t>https://instagram.com/aridiamondsutah, https://facebook.com/aridiamonds</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Dakota Watch Co</t>
+          <t>Shop Beautiful</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -41656,53 +41672,45 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Jewelers, Watch Repair, Watches</t>
+          <t>Jewelers, Gift Shops</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>(317) 624-9115</t>
+          <t>(913) 345-8887</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>customerservice@dakotawatch.com</t>
+          <t>info@shopbeautiful.com</t>
         </is>
       </c>
       <c r="F368" t="inlineStr"/>
-      <c r="G368" t="inlineStr">
-        <is>
-          <t>Albert Cooper</t>
-        </is>
-      </c>
-      <c r="H368" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
+      <c r="G368" t="inlineStr"/>
+      <c r="H368" t="inlineStr"/>
       <c r="I368" s="2" t="inlineStr">
         <is>
-          <t>https://dakotawatch.com</t>
+          <t>https://www.shopbeautiful.com</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>49 W Maryland St Ste 142, Indianapolis, IN 46204</t>
+          <t>5001 W 119th St, Leawood, KS 66209</t>
         </is>
       </c>
       <c r="K368" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Leawood</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>KS</t>
         </is>
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Indianapolis, IN</t>
+          <t>Kansas City, MO</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -41714,7 +41722,7 @@
       <c r="P368" t="inlineStr"/>
       <c r="Q368" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/indianapolis-in/mip/dakota-watch-co-25573661</t>
+          <t>https://www.yellowpages.com/leawood-ks/mip/shop-beautiful-11741963</t>
         </is>
       </c>
       <c r="R368" t="inlineStr">
@@ -41729,68 +41737,56 @@
       </c>
       <c r="T368" s="2" t="inlineStr">
         <is>
-          <t>https://dakotawatch.com/</t>
+          <t>https://shopbeautiful.com/</t>
         </is>
       </c>
       <c r="U368" t="inlineStr"/>
       <c r="V368" t="inlineStr">
         <is>
-          <t>2026-10-14T12:04:54+05:30</t>
-        </is>
-      </c>
-      <c r="W368" t="inlineStr">
-        <is>
-          <t>Dakota Watch Company, Cooper &amp; Co Inc</t>
-        </is>
-      </c>
-      <c r="X368" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, Pittsburgh, PA</t>
-        </is>
-      </c>
+          <t>2026-10-14T12:19:03+05:30</t>
+        </is>
+      </c>
+      <c r="W368" t="inlineStr"/>
+      <c r="X368" t="inlineStr"/>
       <c r="Y368" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z368" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z368" t="inlineStr"/>
       <c r="AA368" t="inlineStr">
         <is>
-          <t>(513) 879-3681</t>
+          <t>(913) 677-2881</t>
         </is>
       </c>
       <c r="AB368" t="inlineStr">
         <is>
-          <t>https://facebook.com/profile.php?id=61550829076826, https://instagram.com/dakotawatch_co</t>
+          <t>https://facebook.com/ShopBeautiful, https://instagram.com/shopbeautiful_kconline</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Indianapolis Crown Jewel Inc</t>
+          <t>Waldo Jewelers</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Repairing, Watch Repair</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>(317) 602-3563</t>
+          <t>(816) 333-4653</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>crownjewel.cj@gmail.com</t>
+          <t>design@waldojewelers.com</t>
         </is>
       </c>
       <c r="F369" t="inlineStr"/>
@@ -41798,27 +41794,27 @@
       <c r="H369" t="inlineStr"/>
       <c r="I369" s="2" t="inlineStr">
         <is>
-          <t>https://www.indycrownjewel.com</t>
+          <t>https://www.waldojewelers.com</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>3760 N Emerson Ave, Indianapolis, IN 46218</t>
+          <t>7437 N Broadway St, Kansas City, MO 64118</t>
         </is>
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Indianapolis, IN</t>
+          <t>Kansas City, MO</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -41826,16 +41822,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O369" t="inlineStr"/>
-      <c r="P369" t="inlineStr"/>
+      <c r="O369" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P369" t="n">
+        <v>361</v>
+      </c>
       <c r="Q369" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/indianapolis-in/mip/indianapolis-crown-jewel-inc-545777926</t>
+          <t>https://www.yellowpages.com/kansas-city-mo/mip/waldo-jewelers-482143540</t>
         </is>
       </c>
       <c r="R369" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-2009</t>
         </is>
       </c>
       <c r="S369" t="inlineStr">
@@ -41845,40 +41845,40 @@
       </c>
       <c r="T369" s="2" t="inlineStr">
         <is>
-          <t>https://www.indycrownjewel.com/</t>
+          <t>https://waldojewelers.com/</t>
         </is>
       </c>
       <c r="U369" t="inlineStr"/>
       <c r="V369" t="inlineStr">
         <is>
-          <t>2026-10-14T12:04:25+05:30</t>
+          <t>2026-10-14T12:03:46+05:30</t>
         </is>
       </c>
       <c r="W369" t="inlineStr"/>
       <c r="X369" t="inlineStr"/>
       <c r="Y369" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z369" t="inlineStr">
         <is>
-          <t>shared-switchboard</t>
+          <t>chain</t>
         </is>
       </c>
       <c r="AA369" t="inlineStr">
         <is>
-          <t>(317) 228-7485</t>
+          <t>(816) 398-2234</t>
         </is>
       </c>
       <c r="AB369" t="inlineStr">
         <is>
-          <t>https://facebook.com/indycrownjewelcollection, https://instagram.com/indycrownjewel</t>
+          <t>https://facebook.com/Waldojewelers, https://instagram.com/waldojewelerskc</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Mason Jewelers Inc</t>
+          <t>Jewelry By Tommy</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -41888,17 +41888,17 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Jewelers, Appraisers</t>
+          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers, Diamonds</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>(317) 839-3202</t>
+          <t>(216) 464-6356</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>masonjewelers1957@gmail.com</t>
+          <t>greg@jewelrybytommy.com</t>
         </is>
       </c>
       <c r="F370" t="inlineStr"/>
@@ -41906,27 +41906,27 @@
       <c r="H370" t="inlineStr"/>
       <c r="I370" s="2" t="inlineStr">
         <is>
-          <t>https://www.masonjewelersco.com</t>
+          <t>https://www.jewelrybytommy.com</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>1822 E Main St, Plainfield, IN 46168</t>
+          <t>27600 Chagrin Blvd Ste 110, Woodmere, OH 44122</t>
         </is>
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t>Plainfield</t>
+          <t>Woodmere</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Indianapolis, IN</t>
+          <t>Cleveland, OH</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -41934,20 +41934,16 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O370" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P370" t="n">
-        <v>355</v>
-      </c>
+      <c r="O370" t="inlineStr"/>
+      <c r="P370" t="inlineStr"/>
       <c r="Q370" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/plainfield-in/mip/mason-jewelers-inc-705208</t>
+          <t>https://www.yellowpages.com/woodmere-oh/mip/jewelry-by-tommy-479852454</t>
         </is>
       </c>
       <c r="R370" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, since-1957</t>
+          <t>2 of 3, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S370" t="inlineStr">
@@ -41957,96 +41953,84 @@
       </c>
       <c r="T370" s="2" t="inlineStr">
         <is>
-          <t>https://www.masonjewelersco.com/</t>
+          <t>https://jewelrybytommy.com/</t>
         </is>
       </c>
       <c r="U370" t="inlineStr"/>
       <c r="V370" t="inlineStr">
         <is>
-          <t>2026-10-14T12:05:07+05:30</t>
-        </is>
-      </c>
-      <c r="W370" t="inlineStr">
-        <is>
-          <t>Mason Jewelers</t>
-        </is>
-      </c>
+          <t>2026-10-14T12:01:03+05:30</t>
+        </is>
+      </c>
+      <c r="W370" t="inlineStr"/>
       <c r="X370" t="inlineStr"/>
       <c r="Y370" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z370" t="inlineStr"/>
       <c r="AA370" t="inlineStr">
         <is>
-          <t>(765) 653-5012</t>
+          <t>(440) 413-5888</t>
         </is>
       </c>
       <c r="AB370" t="inlineStr">
         <is>
-          <t>https://facebook.com/masonjewelers.net, https://facebook.com/Masonjewelersco</t>
+          <t>https://facebook.com/JewelrybyTommy</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Moyer Fine Jewelers</t>
+          <t>Pearls Hope, Inc</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Jewelers, Diamond Buyers, Watches</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>(317) 844-9003</t>
+          <t>(440) 249-7000</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>online@moyerfj.com</t>
+          <t>intake@pearlshope.com</t>
         </is>
       </c>
       <c r="F371" t="inlineStr"/>
-      <c r="G371" t="inlineStr">
-        <is>
-          <t>Dan Moyer</t>
-        </is>
-      </c>
-      <c r="H371" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
+      <c r="G371" t="inlineStr"/>
+      <c r="H371" t="inlineStr"/>
       <c r="I371" s="2" t="inlineStr">
         <is>
-          <t>https://moyerfinejewelers.com</t>
+          <t>https://pearlshope.com</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>14727 Thatcher Ln, Carmel, IN 46032</t>
+          <t>3659 Green Rd, Beachwood, OH 44122</t>
         </is>
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t>Carmel</t>
+          <t>Beachwood</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Indianapolis, IN</t>
+          <t>Cleveland, OH</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -42054,20 +42038,16 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O371" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P371" t="n">
-        <v>704</v>
-      </c>
+      <c r="O371" t="inlineStr"/>
+      <c r="P371" t="inlineStr"/>
       <c r="Q371" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/carmel-in/mip/moyer-fine-jewelers-7900799</t>
+          <t>https://www.yellowpages.com/beachwood-oh/mip/pearls-hope-inc-580059164</t>
         </is>
       </c>
       <c r="R371" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, bench, custom-design</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S371" t="inlineStr">
@@ -42077,92 +42057,88 @@
       </c>
       <c r="T371" s="2" t="inlineStr">
         <is>
-          <t>https://www.moyerfinejewelers.com/pages/contact-us</t>
+          <t>https://pearlshope.com/</t>
         </is>
       </c>
       <c r="U371" t="inlineStr"/>
       <c r="V371" t="inlineStr">
         <is>
-          <t>2026-10-14T12:05:12+05:30</t>
+          <t>2026-10-14T12:00:59+05:30</t>
         </is>
       </c>
       <c r="W371" t="inlineStr"/>
       <c r="X371" t="inlineStr"/>
       <c r="Y371" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z371" t="inlineStr"/>
       <c r="AA371" t="inlineStr">
         <is>
-          <t>(317) 785-1080, (317) 785-1138</t>
-        </is>
-      </c>
-      <c r="AB371" t="inlineStr">
-        <is>
-          <t>https://instagram.com/moyerfinejewelers, https://facebook.com/moyerfinejewelers, https://twitter.com/MoyerJewelers</t>
-        </is>
-      </c>
+          <t>(216) 452-0082, (614) 781-0400, (937) 222-0002</t>
+        </is>
+      </c>
+      <c r="AB371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Bucci Jewelry Company</t>
+          <t>Dakota Watch Co</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Designers, Jewelers-Wholesale &amp; Manufacturers</t>
+          <t>Jewelers, Watch Repair, Watches</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>(412) 391-1729</t>
+          <t>(317) 624-9115</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>hello@buccijewelers.com</t>
+          <t>customerservice@dakotawatch.com</t>
         </is>
       </c>
       <c r="F372" t="inlineStr"/>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Joe Bucci</t>
+          <t>Albert Cooper</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="I372" s="2" t="inlineStr">
         <is>
-          <t>https://www.buccijewelers.com</t>
+          <t>https://dakotawatch.com</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>717 Liberty Ave, Suite 209, Pittsburgh, PA 15222</t>
+          <t>49 W Maryland St Ste 142, Indianapolis, IN 46204</t>
         </is>
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Indianapolis, IN</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -42174,12 +42150,12 @@
       <c r="P372" t="inlineStr"/>
       <c r="Q372" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/pittsburgh-pa/mip/bucci-jewelry-company-4896251</t>
+          <t>https://www.yellowpages.com/indianapolis-in/mip/dakota-watch-co-25573661</t>
         </is>
       </c>
       <c r="R372" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, gia, bench, custom-design, since-1987</t>
+          <t>2 of 3, role-email, direct-line</t>
         </is>
       </c>
       <c r="S372" t="inlineStr">
@@ -42189,56 +42165,68 @@
       </c>
       <c r="T372" s="2" t="inlineStr">
         <is>
-          <t>https://www.buccijewelers.com/</t>
+          <t>https://dakotawatch.com/</t>
         </is>
       </c>
       <c r="U372" t="inlineStr"/>
       <c r="V372" t="inlineStr">
         <is>
-          <t>2026-10-14T12:06:18+05:30</t>
-        </is>
-      </c>
-      <c r="W372" t="inlineStr"/>
-      <c r="X372" t="inlineStr"/>
+          <t>2026-10-14T12:04:54+05:30</t>
+        </is>
+      </c>
+      <c r="W372" t="inlineStr">
+        <is>
+          <t>Dakota Watch Company, Cooper &amp; Co Inc</t>
+        </is>
+      </c>
+      <c r="X372" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, Pittsburgh, PA</t>
+        </is>
+      </c>
       <c r="Y372" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z372" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Z372" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
       <c r="AA372" t="inlineStr">
         <is>
-          <t>(610) 828-1637</t>
+          <t>(513) 879-3681</t>
         </is>
       </c>
       <c r="AB372" t="inlineStr">
         <is>
-          <t>https://instagram.com/ilovejoebucci, https://facebook.com/bucci.jewelers, https://instagram.com/buccijewelers</t>
+          <t>https://facebook.com/profile.php?id=61550829076826, https://instagram.com/dakotawatch_co</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Caesar's Designs</t>
+          <t>Indianapolis Crown Jewel Inc</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Designers, Jewelry Repairing</t>
+          <t>Jewelers, Jewelry Repairing, Watch Repair</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>(412) 621-0345</t>
+          <t>(317) 602-3563</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>caesar@caesarsdesigns.com</t>
+          <t>crownjewel.cj@gmail.com</t>
         </is>
       </c>
       <c r="F373" t="inlineStr"/>
@@ -42246,27 +42234,27 @@
       <c r="H373" t="inlineStr"/>
       <c r="I373" s="2" t="inlineStr">
         <is>
-          <t>https://www.caesarsdesigns.com</t>
+          <t>https://www.indycrownjewel.com</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>5413 Walnut St, Pittsburgh, PA 15232</t>
+          <t>3760 N Emerson Ave, Indianapolis, IN 46218</t>
         </is>
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Indianapolis, IN</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -42274,20 +42262,16 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O373" t="n">
-        <v>5</v>
-      </c>
-      <c r="P373" t="n">
-        <v>180</v>
-      </c>
+      <c r="O373" t="inlineStr"/>
+      <c r="P373" t="inlineStr"/>
       <c r="Q373" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/pittsburgh-pa/mip/caesars-designs-9528656</t>
+          <t>https://www.yellowpages.com/indianapolis-in/mip/indianapolis-crown-jewel-inc-545777926</t>
         </is>
       </c>
       <c r="R373" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, custom-design</t>
+          <t>2 of 3, direct-line</t>
         </is>
       </c>
       <c r="S373" t="inlineStr">
@@ -42297,36 +42281,40 @@
       </c>
       <c r="T373" s="2" t="inlineStr">
         <is>
-          <t>https://www.caesarsdesigns.com/</t>
+          <t>https://www.indycrownjewel.com/</t>
         </is>
       </c>
       <c r="U373" t="inlineStr"/>
       <c r="V373" t="inlineStr">
         <is>
-          <t>2026-10-14T12:05:19+05:30</t>
+          <t>2026-10-14T12:04:25+05:30</t>
         </is>
       </c>
       <c r="W373" t="inlineStr"/>
       <c r="X373" t="inlineStr"/>
       <c r="Y373" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z373" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Z373" t="inlineStr">
+        <is>
+          <t>shared-switchboard</t>
+        </is>
+      </c>
       <c r="AA373" t="inlineStr">
         <is>
-          <t>(412) 400-8582</t>
+          <t>(317) 228-7485</t>
         </is>
       </c>
       <c r="AB373" t="inlineStr">
         <is>
-          <t>https://facebook.com/CaesarsDesignsCreations, https://instagram.com/caesarsdesigns</t>
+          <t>https://facebook.com/indycrownjewelcollection, https://instagram.com/indycrownjewel</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Infinity Jewelers</t>
+          <t>Mason Jewelers Inc</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -42336,17 +42324,17 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Appraisers</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>(443) 985-2476</t>
+          <t>(317) 839-3202</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>customers@infinityjeweler.net</t>
+          <t>masonjewelers1957@gmail.com</t>
         </is>
       </c>
       <c r="F374" t="inlineStr"/>
@@ -42354,27 +42342,27 @@
       <c r="H374" t="inlineStr"/>
       <c r="I374" s="2" t="inlineStr">
         <is>
-          <t>https://www.infinity-jewelers.com</t>
+          <t>https://www.masonjewelersco.com</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>6901 Security Blvd, Baltimore, MD 21244</t>
+          <t>1822 E Main St, Plainfield, IN 46168</t>
         </is>
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t>Baltimore</t>
+          <t>Plainfield</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Baltimore, MD</t>
+          <t>Indianapolis, IN</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -42382,16 +42370,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O374" t="inlineStr"/>
-      <c r="P374" t="inlineStr"/>
+      <c r="O374" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P374" t="n">
+        <v>355</v>
+      </c>
       <c r="Q374" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/baltimore-md/mip/infinity-jewelers-540149418</t>
+          <t>https://www.yellowpages.com/plainfield-in/mip/mason-jewelers-inc-705208</t>
         </is>
       </c>
       <c r="R374" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, since-2014</t>
+          <t>2 of 3, direct-line, since-1957</t>
         </is>
       </c>
       <c r="S374" t="inlineStr">
@@ -42401,84 +42393,96 @@
       </c>
       <c r="T374" s="2" t="inlineStr">
         <is>
-          <t>https://www.infinity-jewelers.com/</t>
+          <t>https://www.masonjewelersco.com/</t>
         </is>
       </c>
       <c r="U374" t="inlineStr"/>
       <c r="V374" t="inlineStr">
         <is>
-          <t>2026-10-14T12:07:31+05:30</t>
-        </is>
-      </c>
-      <c r="W374" t="inlineStr"/>
+          <t>2026-10-14T12:05:07+05:30</t>
+        </is>
+      </c>
+      <c r="W374" t="inlineStr">
+        <is>
+          <t>Mason Jewelers</t>
+        </is>
+      </c>
       <c r="X374" t="inlineStr"/>
       <c r="Y374" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z374" t="inlineStr"/>
       <c r="AA374" t="inlineStr">
         <is>
-          <t>(443) 985-2376</t>
+          <t>(765) 653-5012</t>
         </is>
       </c>
       <c r="AB374" t="inlineStr">
         <is>
-          <t>https://INSTAGRAM.COM/INFINITY.JEWELERS, https://instagram.com/infinity.jewelers, https://facebook.com/infinityjewelers1</t>
+          <t>https://facebook.com/masonjewelers.net, https://facebook.com/Masonjewelersco</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Kaylah Diamonds &amp; Jewelry</t>
+          <t>Moyer Fine Jewelers</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers</t>
+          <t>Jewelers, Diamond Buyers, Watches</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>(410) 580-1149</t>
+          <t>(317) 844-9003</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>sales@kaylahdiamonds.com</t>
+          <t>online@moyerfj.com</t>
         </is>
       </c>
       <c r="F375" t="inlineStr"/>
-      <c r="G375" t="inlineStr"/>
-      <c r="H375" t="inlineStr"/>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>Dan Moyer</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="I375" s="2" t="inlineStr">
         <is>
-          <t>https://www.kaylahdiamonds.com</t>
+          <t>https://moyerfinejewelers.com</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>1312 Reisterstown Rd, Pikesville, MD 21208</t>
+          <t>14727 Thatcher Ln, Carmel, IN 46032</t>
         </is>
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t>Pikesville</t>
+          <t>Carmel</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Baltimore, MD</t>
+          <t>Indianapolis, IN</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -42486,16 +42490,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O375" t="inlineStr"/>
-      <c r="P375" t="inlineStr"/>
+      <c r="O375" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P375" t="n">
+        <v>704</v>
+      </c>
       <c r="Q375" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/pikesville-md/mip/kaylah-diamonds-jewelry-547970048</t>
+          <t>https://www.yellowpages.com/carmel-in/mip/moyer-fine-jewelers-7900799</t>
         </is>
       </c>
       <c r="R375" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, custom-design</t>
+          <t>2 of 3, direct-line, gia, bench, custom-design</t>
         </is>
       </c>
       <c r="S375" t="inlineStr">
@@ -42505,36 +42513,36 @@
       </c>
       <c r="T375" s="2" t="inlineStr">
         <is>
-          <t>https://kaylahdiamonds.com/</t>
+          <t>https://www.moyerfinejewelers.com/pages/contact-us</t>
         </is>
       </c>
       <c r="U375" t="inlineStr"/>
       <c r="V375" t="inlineStr">
         <is>
-          <t>2026-10-14T12:07:46+05:30</t>
+          <t>2026-10-14T12:05:12+05:30</t>
         </is>
       </c>
       <c r="W375" t="inlineStr"/>
       <c r="X375" t="inlineStr"/>
       <c r="Y375" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z375" t="inlineStr"/>
       <c r="AA375" t="inlineStr">
         <is>
-          <t>(732) 367-4653</t>
+          <t>(317) 785-1080, (317) 785-1138</t>
         </is>
       </c>
       <c r="AB375" t="inlineStr">
         <is>
-          <t>https://facebook.com/KaylahDesigns, https://instagram.com/kaylah_diamonds, https://twitter.com/kaylahdiamonds</t>
+          <t>https://instagram.com/moyerfinejewelers, https://facebook.com/moyerfinejewelers, https://twitter.com/MoyerJewelers</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Custom Jewelry</t>
+          <t>Princess Jewelry</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -42549,40 +42557,48 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>(813) 930-0380</t>
+          <t>(317) 329-8139</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>customhairtampabay@gmail.com</t>
+          <t>sales@princessjewelry.com</t>
         </is>
       </c>
       <c r="F376" t="inlineStr"/>
-      <c r="G376" t="inlineStr"/>
-      <c r="H376" t="inlineStr"/>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>Simon G. House</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>Featured On About Page</t>
+        </is>
+      </c>
       <c r="I376" s="2" t="inlineStr">
         <is>
-          <t>https://customhairtampabay.com</t>
+          <t>https://www.princessjewelry.com</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>11612 N Nebraska Ave, Tampa, FL 33612</t>
+          <t>3919 Lafayette Rd, Indianapolis, IN 46254</t>
         </is>
       </c>
       <c r="K376" t="inlineStr">
         <is>
-          <t>Tampa</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Tampa, FL</t>
+          <t>Indianapolis, IN</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -42594,12 +42610,12 @@
       <c r="P376" t="inlineStr"/>
       <c r="Q376" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/tampa-fl/mip/custom-jewelry-481586478</t>
+          <t>https://www.yellowpages.com/indianapolis-in/mip/princess-jewelry-7581229</t>
         </is>
       </c>
       <c r="R376" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design, since-1969</t>
+          <t>2 of 3, role-email, direct-line, custom-design, since-1985</t>
         </is>
       </c>
       <c r="S376" t="inlineStr">
@@ -42609,36 +42625,36 @@
       </c>
       <c r="T376" s="2" t="inlineStr">
         <is>
-          <t>https://www.customhairtampabay.com/</t>
+          <t>https://princessjewelry.com/</t>
         </is>
       </c>
       <c r="U376" t="inlineStr"/>
       <c r="V376" t="inlineStr">
         <is>
-          <t>2026-10-14T12:02:15+05:30</t>
-        </is>
-      </c>
-      <c r="W376" t="inlineStr">
-        <is>
-          <t>Janas Jewlery</t>
-        </is>
-      </c>
+          <t>2026-10-14T12:04:42+05:30</t>
+        </is>
+      </c>
+      <c r="W376" t="inlineStr"/>
       <c r="X376" t="inlineStr"/>
       <c r="Y376" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z376" t="inlineStr"/>
       <c r="AA376" t="inlineStr">
         <is>
-          <t>(727) 725-1052, (813) 651-9484, (813) 932-5327</t>
-        </is>
-      </c>
-      <c r="AB376" t="inlineStr"/>
+          <t>(952) 898-3322</t>
+        </is>
+      </c>
+      <c r="AB376" t="inlineStr">
+        <is>
+          <t>https://instagram.com/princessjewelrymn, https://facebook.com/PrincessJewelryMN, https://x.com/princessjewelry, https://facebook.com/princessjewelrymn</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>R Wolf Fine Jewelers</t>
+          <t>Bucci Jewelry Company</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -42648,45 +42664,53 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Jewelers, Watches</t>
+          <t>Jewelers, Jewelry Designers, Jewelers-Wholesale &amp; Manufacturers</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>(813) 816-2619</t>
+          <t>(412) 391-1729</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>rb.wolf@hotmail.com</t>
+          <t>hello@buccijewelers.com</t>
         </is>
       </c>
       <c r="F377" t="inlineStr"/>
-      <c r="G377" t="inlineStr"/>
-      <c r="H377" t="inlineStr"/>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>Joe Bucci</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I377" s="2" t="inlineStr">
         <is>
-          <t>https://rwolfjewelry.com</t>
+          <t>https://www.buccijewelers.com</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>100 S Ashley Dr, Tampa, FL 33602</t>
+          <t>717 Liberty Ave, Suite 209, Pittsburgh, PA 15222</t>
         </is>
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t>Tampa</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Tampa, FL</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -42698,12 +42722,12 @@
       <c r="P377" t="inlineStr"/>
       <c r="Q377" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/tampa-fl/mip/r-wolf-fine-jewelers-543840292</t>
+          <t>https://www.yellowpages.com/pittsburgh-pa/mip/bucci-jewelry-company-4896251</t>
         </is>
       </c>
       <c r="R377" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, bench, custom-design</t>
+          <t>2 of 3, role-email, direct-line, gia, bench, custom-design, since-1987</t>
         </is>
       </c>
       <c r="S377" t="inlineStr">
@@ -42713,13 +42737,13 @@
       </c>
       <c r="T377" s="2" t="inlineStr">
         <is>
-          <t>https://rwolfjewelry.com/</t>
+          <t>https://www.buccijewelers.com/</t>
         </is>
       </c>
       <c r="U377" t="inlineStr"/>
       <c r="V377" t="inlineStr">
         <is>
-          <t>2026-10-14T12:02:02+05:30</t>
+          <t>2026-10-14T12:06:18+05:30</t>
         </is>
       </c>
       <c r="W377" t="inlineStr"/>
@@ -42730,19 +42754,19 @@
       <c r="Z377" t="inlineStr"/>
       <c r="AA377" t="inlineStr">
         <is>
-          <t>(727) 275-0106</t>
+          <t>(610) 828-1637</t>
         </is>
       </c>
       <c r="AB377" t="inlineStr">
         <is>
-          <t>https://facebook.com/rwolf.jewelry, https://instagram.com/rwolfjewelry</t>
+          <t>https://instagram.com/ilovejoebucci, https://facebook.com/bucci.jewelers, https://instagram.com/buccijewelers</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Grafted Growers</t>
+          <t>Caesar's Designs</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -42752,17 +42776,17 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelry Designers</t>
+          <t>Jewelers, Jewelry Designers, Jewelry Repairing</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>(984) 200-9545</t>
+          <t>(412) 621-0345</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>info@graftedgrowers.com</t>
+          <t>caesar@caesarsdesigns.com</t>
         </is>
       </c>
       <c r="F378" t="inlineStr"/>
@@ -42770,27 +42794,27 @@
       <c r="H378" t="inlineStr"/>
       <c r="I378" s="2" t="inlineStr">
         <is>
-          <t>https://graftedgrowers.com</t>
+          <t>https://www.caesarsdesigns.com</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>4025 Atlantic Ave, Raleigh, NC 27604</t>
+          <t>5413 Walnut St, Pittsburgh, PA 15232</t>
         </is>
       </c>
       <c r="K378" t="inlineStr">
         <is>
-          <t>Raleigh</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Raleigh, NC</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -42798,16 +42822,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O378" t="inlineStr"/>
-      <c r="P378" t="inlineStr"/>
+      <c r="O378" t="n">
+        <v>5</v>
+      </c>
+      <c r="P378" t="n">
+        <v>180</v>
+      </c>
       <c r="Q378" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/raleigh-nc/mip/grafted-growers-547754305</t>
+          <t>https://www.yellowpages.com/pittsburgh-pa/mip/caesars-designs-9528656</t>
         </is>
       </c>
       <c r="R378" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line</t>
+          <t>2 of 3, direct-line, gia, custom-design</t>
         </is>
       </c>
       <c r="S378" t="inlineStr">
@@ -42817,36 +42845,36 @@
       </c>
       <c r="T378" s="2" t="inlineStr">
         <is>
-          <t>https://graftedgrowers.com/</t>
+          <t>https://www.caesarsdesigns.com/</t>
         </is>
       </c>
       <c r="U378" t="inlineStr"/>
       <c r="V378" t="inlineStr">
         <is>
-          <t>2026-10-14T12:05:59+05:30</t>
+          <t>2026-10-14T12:05:19+05:30</t>
         </is>
       </c>
       <c r="W378" t="inlineStr"/>
       <c r="X378" t="inlineStr"/>
       <c r="Y378" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z378" t="inlineStr"/>
       <c r="AA378" t="inlineStr">
         <is>
-          <t>(919) 400-6022</t>
+          <t>(412) 400-8582</t>
         </is>
       </c>
       <c r="AB378" t="inlineStr">
         <is>
-          <t>https://facebook.com/graftedgrowers, https://instagram.com/graftedgrowers, https://twitter.com/GraftedGrowers</t>
+          <t>https://facebook.com/CaesarsDesignsCreations, https://instagram.com/caesarsdesigns</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Amir &amp; Associates Inc</t>
+          <t>Yuriy's Jewelry</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -42856,53 +42884,45 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Jewelers, Diamonds-Wholesale</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>(504) 888-0229</t>
+          <t>(412) 788-8833</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t xml:space="preserve"> amir@amircpas.com</t>
+          <t>mishathejeweler@gmail.com</t>
         </is>
       </c>
       <c r="F379" t="inlineStr"/>
-      <c r="G379" t="inlineStr">
-        <is>
-          <t>Amir Mujahid</t>
-        </is>
-      </c>
-      <c r="H379" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
+      <c r="G379" t="inlineStr"/>
+      <c r="H379" t="inlineStr"/>
       <c r="I379" s="2" t="inlineStr">
         <is>
-          <t>https://www.amircpas.com</t>
+          <t>https://www.yuriysjewelry.com</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>3655 Veterans Memorial Blvd, Metairie, LA 70002</t>
+          <t>301 S Hills Vlg, Pittsburgh, PA 15241</t>
         </is>
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t>Metairie</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>New Orleans, LA</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -42910,16 +42930,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O379" t="inlineStr"/>
-      <c r="P379" t="inlineStr"/>
+      <c r="O379" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P379" t="n">
+        <v>272</v>
+      </c>
       <c r="Q379" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/metairie-la/mip/amir-associates-inc-541918551</t>
+          <t>https://www.yellowpages.com/pittsburgh-pa/mip/yuriys-jewelry-547790709</t>
         </is>
       </c>
       <c r="R379" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, since-2008</t>
+          <t>2 of 3, direct-line, bench, custom-design</t>
         </is>
       </c>
       <c r="S379" t="inlineStr">
@@ -42929,56 +42953,56 @@
       </c>
       <c r="T379" s="2" t="inlineStr">
         <is>
-          <t>https://www.amircpas.com/contact</t>
+          <t>https://www.yuriysjewelry.com/contact</t>
         </is>
       </c>
       <c r="U379" t="inlineStr"/>
       <c r="V379" t="inlineStr">
         <is>
-          <t>2026-10-14T12:07:40+05:30</t>
+          <t>2026-10-14T12:05:52+05:30</t>
         </is>
       </c>
       <c r="W379" t="inlineStr"/>
       <c r="X379" t="inlineStr"/>
       <c r="Y379" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z379" t="inlineStr"/>
       <c r="AA379" t="inlineStr">
         <is>
-          <t>(310) 214-6699</t>
+          <t>(412) 805-9968</t>
         </is>
       </c>
       <c r="AB379" t="inlineStr">
         <is>
-          <t>https://facebook.com/AmirAndAssociatesCPA</t>
+          <t>https://facebook.com/YuriysJewelry, https://instagram.com/misha_the_jeweler, https://twitter.com/MishaBekman</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Brilliance In Diamonds - The Engagement Specialists</t>
+          <t>Infinity Jewelers</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers, Diamonds</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>(504) 383-8669</t>
+          <t>(443) 985-2476</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>info@brillianceindiamonds.com</t>
+          <t>customers@infinityjeweler.net</t>
         </is>
       </c>
       <c r="F380" t="inlineStr"/>
@@ -42986,27 +43010,27 @@
       <c r="H380" t="inlineStr"/>
       <c r="I380" s="2" t="inlineStr">
         <is>
-          <t>https://www.brillianceindiamonds.com</t>
+          <t>https://www.infinity-jewelers.com</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>3000 Kingman St Ste 215, Metairie, LA 70006</t>
+          <t>6901 Security Blvd, Baltimore, MD 21244</t>
         </is>
       </c>
       <c r="K380" t="inlineStr">
         <is>
-          <t>Metairie</t>
+          <t>Baltimore</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>New Orleans, LA</t>
+          <t>Baltimore, MD</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -43014,20 +43038,16 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O380" t="n">
-        <v>5</v>
-      </c>
-      <c r="P380" t="n">
-        <v>1</v>
-      </c>
+      <c r="O380" t="inlineStr"/>
+      <c r="P380" t="inlineStr"/>
       <c r="Q380" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/metairie-la/mip/brilliance-in-diamonds-the-engagement-specialists-479872499</t>
+          <t>https://www.yellowpages.com/baltimore-md/mip/infinity-jewelers-540149418</t>
         </is>
       </c>
       <c r="R380" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line</t>
+          <t>2 of 3, direct-line, since-2014</t>
         </is>
       </c>
       <c r="S380" t="inlineStr">
@@ -43037,13 +43057,13 @@
       </c>
       <c r="T380" s="2" t="inlineStr">
         <is>
-          <t>https://brillianceindiamonds.com/</t>
+          <t>https://www.infinity-jewelers.com/</t>
         </is>
       </c>
       <c r="U380" t="inlineStr"/>
       <c r="V380" t="inlineStr">
         <is>
-          <t>2026-10-14T12:07:46+05:30</t>
+          <t>2026-10-14T12:07:31+05:30</t>
         </is>
       </c>
       <c r="W380" t="inlineStr"/>
@@ -43054,19 +43074,19 @@
       <c r="Z380" t="inlineStr"/>
       <c r="AA380" t="inlineStr">
         <is>
-          <t>(504) 532-7474, (504) 655-9224</t>
+          <t>(443) 985-2376</t>
         </is>
       </c>
       <c r="AB380" t="inlineStr">
         <is>
-          <t>https://facebook.com/BrillianceInDiamonds, https://instagram.com/brillianceindiamonds</t>
+          <t>https://INSTAGRAM.COM/INFINITY.JEWELERS, https://instagram.com/infinity.jewelers, https://facebook.com/infinityjewelers1</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Cajun Swamp</t>
+          <t>Kaylah Diamonds &amp; Jewelry</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -43076,17 +43096,17 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Jewelers, Gift Shops</t>
+          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>(504) 267-5075</t>
+          <t>(410) 580-1149</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>info@cajunencounters.com</t>
+          <t>sales@kaylahdiamonds.com</t>
         </is>
       </c>
       <c r="F381" t="inlineStr"/>
@@ -43094,27 +43114,27 @@
       <c r="H381" t="inlineStr"/>
       <c r="I381" s="2" t="inlineStr">
         <is>
-          <t>https://cajunencounters.com</t>
+          <t>https://www.kaylahdiamonds.com</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>631 Bourbon St, New Orleans, LA 70130</t>
+          <t>1312 Reisterstown Rd, Pikesville, MD 21208</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Pikesville</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>New Orleans, LA</t>
+          <t>Baltimore, MD</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -43126,12 +43146,12 @@
       <c r="P381" t="inlineStr"/>
       <c r="Q381" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/new-orleans-la/mip/cajun-swamp-7275033</t>
+          <t>https://www.yellowpages.com/pikesville-md/mip/kaylah-diamonds-jewelry-547970048</t>
         </is>
       </c>
       <c r="R381" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, since-1997</t>
+          <t>2 of 3, role-email, direct-line, custom-design</t>
         </is>
       </c>
       <c r="S381" t="inlineStr">
@@ -43141,13 +43161,13 @@
       </c>
       <c r="T381" s="2" t="inlineStr">
         <is>
-          <t>https://www.cajunencounters.com/</t>
+          <t>https://kaylahdiamonds.com/</t>
         </is>
       </c>
       <c r="U381" t="inlineStr"/>
       <c r="V381" t="inlineStr">
         <is>
-          <t>2026-10-14T12:06:52+05:30</t>
+          <t>2026-10-14T12:07:46+05:30</t>
         </is>
       </c>
       <c r="W381" t="inlineStr"/>
@@ -43158,39 +43178,39 @@
       <c r="Z381" t="inlineStr"/>
       <c r="AA381" t="inlineStr">
         <is>
-          <t>(504) 834-1770</t>
+          <t>(732) 367-4653</t>
         </is>
       </c>
       <c r="AB381" t="inlineStr">
         <is>
-          <t>https://facebook.com/CajunEncounters, https://twitter.com/cajunencounters, https://instagram.com/cajunencounters</t>
+          <t>https://facebook.com/KaylahDesigns, https://instagram.com/kaylah_diamonds, https://twitter.com/kaylahdiamonds</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>P &amp; R Jewelry Repair Inc</t>
+          <t>Custom Jewelry</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Jewelry repair / goldsmith</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Jewelers, Watch Repair, Jewelry Repairing</t>
+          <t>Jewelers</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>(504) 366-1878</t>
+          <t>(813) 930-0380</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>automatic8675@gmail.com</t>
+          <t>customhairtampabay@gmail.com</t>
         </is>
       </c>
       <c r="F382" t="inlineStr"/>
@@ -43198,27 +43218,27 @@
       <c r="H382" t="inlineStr"/>
       <c r="I382" s="2" t="inlineStr">
         <is>
-          <t>https://quinterandsonsjewelers.jewelershowcase.com</t>
+          <t>https://customhairtampabay.com</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>197 Westbank Expy, Gretna, LA 70053</t>
+          <t>11612 N Nebraska Ave, Tampa, FL 33612</t>
         </is>
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t>Gretna</t>
+          <t>Tampa</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>New Orleans, LA</t>
+          <t>Tampa, FL</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -43226,20 +43246,16 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O382" t="n">
-        <v>5</v>
-      </c>
-      <c r="P382" t="n">
-        <v>3</v>
-      </c>
+      <c r="O382" t="inlineStr"/>
+      <c r="P382" t="inlineStr"/>
       <c r="Q382" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/gretna-la/mip/p-r-jewelry-repair-inc-477806444</t>
+          <t>https://www.yellowpages.com/tampa-fl/mip/custom-jewelry-481586478</t>
         </is>
       </c>
       <c r="R382" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, gia, bench, custom-design</t>
+          <t>2 of 3, direct-line, custom-design, since-1969</t>
         </is>
       </c>
       <c r="S382" t="inlineStr">
@@ -43249,64 +43265,56 @@
       </c>
       <c r="T382" s="2" t="inlineStr">
         <is>
-          <t>https://quinterandsonsjewelers.jewelershowcase.com/contactthisjeweler</t>
+          <t>https://www.customhairtampabay.com/</t>
         </is>
       </c>
       <c r="U382" t="inlineStr"/>
       <c r="V382" t="inlineStr">
         <is>
-          <t>2026-10-14T12:07:32+05:30</t>
+          <t>2026-10-14T12:02:15+05:30</t>
         </is>
       </c>
       <c r="W382" t="inlineStr">
         <is>
-          <t>Sol's Jewelers</t>
+          <t>Janas Jewlery</t>
         </is>
       </c>
       <c r="X382" t="inlineStr"/>
       <c r="Y382" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z382" t="inlineStr">
-        <is>
-          <t>chain</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Z382" t="inlineStr"/>
       <c r="AA382" t="inlineStr">
         <is>
-          <t>(985) 335-0908</t>
-        </is>
-      </c>
-      <c r="AB382" t="inlineStr">
-        <is>
-          <t>https://facebook.com/StullerInc, https://instagram.com/StullerInc, https://x.com/StullerInc</t>
-        </is>
-      </c>
+          <t>(727) 725-1052, (813) 651-9484, (813) 932-5327</t>
+        </is>
+      </c>
+      <c r="AB382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Quarter Past Time</t>
+          <t>Eddy Jewelers</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Jewelers</t>
+          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers, Watches</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>(504) 410-0010</t>
+          <t>(813) 876-0929</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>hello@quarterstitch.com</t>
+          <t>eddysjewelers@gmail.com</t>
         </is>
       </c>
       <c r="F383" t="inlineStr"/>
@@ -43314,27 +43322,27 @@
       <c r="H383" t="inlineStr"/>
       <c r="I383" s="2" t="inlineStr">
         <is>
-          <t>https://quarterstitch.com</t>
+          <t>https://eddysjewelers.com</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>606 Chartres St, New Orleans, LA 70130</t>
+          <t>3306 W Columbus Dr, Tampa, FL 33607</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Tampa</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>New Orleans, LA</t>
+          <t>Tampa, FL</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -43342,16 +43350,20 @@
           <t>YellowPages</t>
         </is>
       </c>
-      <c r="O383" t="inlineStr"/>
-      <c r="P383" t="inlineStr"/>
+      <c r="O383" t="n">
+        <v>1</v>
+      </c>
+      <c r="P383" t="n">
+        <v>1</v>
+      </c>
       <c r="Q383" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/new-orleans-la/mip/quarter-past-time-4483088</t>
+          <t>https://www.yellowpages.com/tampa-fl/mip/eddy-jewelers-23154095</t>
         </is>
       </c>
       <c r="R383" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, since-1969</t>
+          <t>2 of 3, direct-line, custom-design, since-1993</t>
         </is>
       </c>
       <c r="S383" t="inlineStr">
@@ -43361,34 +43373,894 @@
       </c>
       <c r="T383" s="2" t="inlineStr">
         <is>
-          <t>https://www.quarterstitch.com/contact</t>
+          <t>https://eddysjewelers.company.site/</t>
         </is>
       </c>
       <c r="U383" t="inlineStr"/>
       <c r="V383" t="inlineStr">
         <is>
-          <t>2026-10-14T12:06:57+05:30</t>
-        </is>
-      </c>
-      <c r="W383" t="inlineStr"/>
+          <t>2026-10-14T12:02:29+05:30</t>
+        </is>
+      </c>
+      <c r="W383" t="inlineStr">
+        <is>
+          <t>Eddy's Jewelers</t>
+        </is>
+      </c>
       <c r="X383" t="inlineStr"/>
       <c r="Y383" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z383" t="inlineStr"/>
       <c r="AA383" t="inlineStr">
         <is>
+          <t>(813) 876-3119</t>
+        </is>
+      </c>
+      <c r="AB383" t="inlineStr">
+        <is>
+          <t>https://instagram.com/eddysjewelers</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>R Wolf Fine Jewelers</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Custom / bespoke jeweler</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Jewelers, Watches</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>(813) 816-2619</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>rb.wolf@hotmail.com</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr"/>
+      <c r="G384" t="inlineStr"/>
+      <c r="H384" t="inlineStr"/>
+      <c r="I384" s="2" t="inlineStr">
+        <is>
+          <t>https://rwolfjewelry.com</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>100 S Ashley Dr, Tampa, FL 33602</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Tampa</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>Tampa, FL</t>
+        </is>
+      </c>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr"/>
+      <c r="P384" t="inlineStr"/>
+      <c r="Q384" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/tampa-fl/mip/r-wolf-fine-jewelers-543840292</t>
+        </is>
+      </c>
+      <c r="R384" t="inlineStr">
+        <is>
+          <t>2 of 3, direct-line, bench, custom-design</t>
+        </is>
+      </c>
+      <c r="S384" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T384" s="2" t="inlineStr">
+        <is>
+          <t>https://rwolfjewelry.com/</t>
+        </is>
+      </c>
+      <c r="U384" t="inlineStr"/>
+      <c r="V384" t="inlineStr">
+        <is>
+          <t>2026-10-14T12:02:02+05:30</t>
+        </is>
+      </c>
+      <c r="W384" t="inlineStr"/>
+      <c r="X384" t="inlineStr"/>
+      <c r="Y384" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z384" t="inlineStr"/>
+      <c r="AA384" t="inlineStr">
+        <is>
+          <t>(727) 275-0106</t>
+        </is>
+      </c>
+      <c r="AB384" t="inlineStr">
+        <is>
+          <t>https://facebook.com/rwolf.jewelry, https://instagram.com/rwolfjewelry</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Deluxe Jewelry Inc</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Jewelers, Jewelry Repairing</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>(954) 977-9979</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>dvintagejewelry@gmail.com</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr"/>
+      <c r="G385" t="inlineStr"/>
+      <c r="H385" t="inlineStr"/>
+      <c r="I385" s="2" t="inlineStr">
+        <is>
+          <t>https://deluxejewelers.com</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>2900 W Sample Rd, Pompano Beach, FL 33073</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Pompano Beach</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL</t>
+        </is>
+      </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr"/>
+      <c r="P385" t="inlineStr"/>
+      <c r="Q385" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/pompano-beach-fl/mip/deluxe-jewelry-inc-456167645</t>
+        </is>
+      </c>
+      <c r="R385" t="inlineStr">
+        <is>
+          <t>2 of 3, direct-line, since-1995</t>
+        </is>
+      </c>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T385" s="2" t="inlineStr">
+        <is>
+          <t>https://deluxejewelers.com/</t>
+        </is>
+      </c>
+      <c r="U385" t="inlineStr"/>
+      <c r="V385" t="inlineStr">
+        <is>
+          <t>2026-10-14T12:25:30+05:30</t>
+        </is>
+      </c>
+      <c r="W385" t="inlineStr"/>
+      <c r="X385" t="inlineStr"/>
+      <c r="Y385" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z385" t="inlineStr"/>
+      <c r="AA385" t="inlineStr">
+        <is>
+          <t>(954) 247-5463, (954) 531-0135</t>
+        </is>
+      </c>
+      <c r="AB385" t="inlineStr">
+        <is>
+          <t>https://instagram.com/deluxejewelers</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Grafted Growers</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Custom / bespoke jeweler</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Jewelers, Jewelry Designers</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>(984) 200-9545</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>info@graftedgrowers.com</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr"/>
+      <c r="G386" t="inlineStr"/>
+      <c r="H386" t="inlineStr"/>
+      <c r="I386" s="2" t="inlineStr">
+        <is>
+          <t>https://graftedgrowers.com</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>4025 Atlantic Ave, Raleigh, NC 27604</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Raleigh</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>Raleigh, NC</t>
+        </is>
+      </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr"/>
+      <c r="P386" t="inlineStr"/>
+      <c r="Q386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/raleigh-nc/mip/grafted-growers-547754305</t>
+        </is>
+      </c>
+      <c r="R386" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line</t>
+        </is>
+      </c>
+      <c r="S386" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T386" s="2" t="inlineStr">
+        <is>
+          <t>https://graftedgrowers.com/</t>
+        </is>
+      </c>
+      <c r="U386" t="inlineStr"/>
+      <c r="V386" t="inlineStr">
+        <is>
+          <t>2026-10-14T12:05:59+05:30</t>
+        </is>
+      </c>
+      <c r="W386" t="inlineStr"/>
+      <c r="X386" t="inlineStr"/>
+      <c r="Y386" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z386" t="inlineStr"/>
+      <c r="AA386" t="inlineStr">
+        <is>
+          <t>(919) 400-6022</t>
+        </is>
+      </c>
+      <c r="AB386" t="inlineStr">
+        <is>
+          <t>https://facebook.com/graftedgrowers, https://instagram.com/graftedgrowers, https://twitter.com/GraftedGrowers</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Amir &amp; Associates Inc</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Jewelers, Diamonds-Wholesale</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>(504) 888-0229</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> amir@amircpas.com</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr"/>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>Amir Mujahid</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="I387" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amircpas.com</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>3655 Veterans Memorial Blvd, Metairie, LA 70002</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metairie</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>New Orleans, LA</t>
+        </is>
+      </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr"/>
+      <c r="P387" t="inlineStr"/>
+      <c r="Q387" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/metairie-la/mip/amir-associates-inc-541918551</t>
+        </is>
+      </c>
+      <c r="R387" t="inlineStr">
+        <is>
+          <t>2 of 3, direct-line, since-2008</t>
+        </is>
+      </c>
+      <c r="S387" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T387" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amircpas.com/contact</t>
+        </is>
+      </c>
+      <c r="U387" t="inlineStr"/>
+      <c r="V387" t="inlineStr">
+        <is>
+          <t>2026-10-14T12:07:40+05:30</t>
+        </is>
+      </c>
+      <c r="W387" t="inlineStr"/>
+      <c r="X387" t="inlineStr"/>
+      <c r="Y387" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z387" t="inlineStr"/>
+      <c r="AA387" t="inlineStr">
+        <is>
+          <t>(310) 214-6699</t>
+        </is>
+      </c>
+      <c r="AB387" t="inlineStr">
+        <is>
+          <t>https://facebook.com/AmirAndAssociatesCPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Brilliance In Diamonds - The Engagement Specialists</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Custom / bespoke jeweler</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Jewelers, Jewelers-Wholesale &amp; Manufacturers, Diamonds</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>(504) 383-8669</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>info@brillianceindiamonds.com</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr"/>
+      <c r="G388" t="inlineStr"/>
+      <c r="H388" t="inlineStr"/>
+      <c r="I388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.brillianceindiamonds.com</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>3000 Kingman St Ste 215, Metairie, LA 70006</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metairie</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>New Orleans, LA</t>
+        </is>
+      </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O388" t="n">
+        <v>5</v>
+      </c>
+      <c r="P388" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/metairie-la/mip/brilliance-in-diamonds-the-engagement-specialists-479872499</t>
+        </is>
+      </c>
+      <c r="R388" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line</t>
+        </is>
+      </c>
+      <c r="S388" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T388" s="2" t="inlineStr">
+        <is>
+          <t>https://brillianceindiamonds.com/</t>
+        </is>
+      </c>
+      <c r="U388" t="inlineStr"/>
+      <c r="V388" t="inlineStr">
+        <is>
+          <t>2026-10-14T12:07:46+05:30</t>
+        </is>
+      </c>
+      <c r="W388" t="inlineStr"/>
+      <c r="X388" t="inlineStr"/>
+      <c r="Y388" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z388" t="inlineStr"/>
+      <c r="AA388" t="inlineStr">
+        <is>
+          <t>(504) 532-7474, (504) 655-9224</t>
+        </is>
+      </c>
+      <c r="AB388" t="inlineStr">
+        <is>
+          <t>https://facebook.com/BrillianceInDiamonds, https://instagram.com/brillianceindiamonds</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Cajun Swamp</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Jewelers, Gift Shops</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>(504) 267-5075</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>info@cajunencounters.com</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr"/>
+      <c r="G389" t="inlineStr"/>
+      <c r="H389" t="inlineStr"/>
+      <c r="I389" s="2" t="inlineStr">
+        <is>
+          <t>https://cajunencounters.com</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>631 Bourbon St, New Orleans, LA 70130</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>New Orleans</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>New Orleans, LA</t>
+        </is>
+      </c>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr"/>
+      <c r="P389" t="inlineStr"/>
+      <c r="Q389" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/new-orleans-la/mip/cajun-swamp-7275033</t>
+        </is>
+      </c>
+      <c r="R389" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, since-1997</t>
+        </is>
+      </c>
+      <c r="S389" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T389" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cajunencounters.com/</t>
+        </is>
+      </c>
+      <c r="U389" t="inlineStr"/>
+      <c r="V389" t="inlineStr">
+        <is>
+          <t>2026-10-14T12:06:52+05:30</t>
+        </is>
+      </c>
+      <c r="W389" t="inlineStr"/>
+      <c r="X389" t="inlineStr"/>
+      <c r="Y389" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z389" t="inlineStr"/>
+      <c r="AA389" t="inlineStr">
+        <is>
+          <t>(504) 834-1770</t>
+        </is>
+      </c>
+      <c r="AB389" t="inlineStr">
+        <is>
+          <t>https://facebook.com/CajunEncounters, https://twitter.com/cajunencounters, https://instagram.com/cajunencounters</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>P &amp; R Jewelry Repair Inc</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Jewelry repair / goldsmith</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Jewelers, Watch Repair, Jewelry Repairing</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>(504) 366-1878</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>automatic8675@gmail.com</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr"/>
+      <c r="G390" t="inlineStr"/>
+      <c r="H390" t="inlineStr"/>
+      <c r="I390" s="2" t="inlineStr">
+        <is>
+          <t>https://quinterandsonsjewelers.jewelershowcase.com</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>197 Westbank Expy, Gretna, LA 70053</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Gretna</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>New Orleans, LA</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O390" t="n">
+        <v>5</v>
+      </c>
+      <c r="P390" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q390" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/gretna-la/mip/p-r-jewelry-repair-inc-477806444</t>
+        </is>
+      </c>
+      <c r="R390" t="inlineStr">
+        <is>
+          <t>2 of 3, direct-line, gia, bench, custom-design</t>
+        </is>
+      </c>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T390" s="2" t="inlineStr">
+        <is>
+          <t>https://quinterandsonsjewelers.jewelershowcase.com/contactthisjeweler</t>
+        </is>
+      </c>
+      <c r="U390" t="inlineStr"/>
+      <c r="V390" t="inlineStr">
+        <is>
+          <t>2026-10-14T12:07:32+05:30</t>
+        </is>
+      </c>
+      <c r="W390" t="inlineStr">
+        <is>
+          <t>Sol's Jewelers</t>
+        </is>
+      </c>
+      <c r="X390" t="inlineStr"/>
+      <c r="Y390" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z390" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="AA390" t="inlineStr">
+        <is>
+          <t>(985) 335-0908</t>
+        </is>
+      </c>
+      <c r="AB390" t="inlineStr">
+        <is>
+          <t>https://facebook.com/StullerInc, https://instagram.com/StullerInc, https://x.com/StullerInc</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Quarter Past Time</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Jewelry retailer</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Jewelers</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>(504) 410-0010</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>hello@quarterstitch.com</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr"/>
+      <c r="G391" t="inlineStr"/>
+      <c r="H391" t="inlineStr"/>
+      <c r="I391" s="2" t="inlineStr">
+        <is>
+          <t>https://quarterstitch.com</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>606 Chartres St, New Orleans, LA 70130</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>New Orleans</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>New Orleans, LA</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>YellowPages</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr"/>
+      <c r="P391" t="inlineStr"/>
+      <c r="Q391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.com/new-orleans-la/mip/quarter-past-time-4483088</t>
+        </is>
+      </c>
+      <c r="R391" t="inlineStr">
+        <is>
+          <t>2 of 3, role-email, direct-line, since-1969</t>
+        </is>
+      </c>
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="T391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.quarterstitch.com/contact</t>
+        </is>
+      </c>
+      <c r="U391" t="inlineStr"/>
+      <c r="V391" t="inlineStr">
+        <is>
+          <t>2026-10-14T12:06:57+05:30</t>
+        </is>
+      </c>
+      <c r="W391" t="inlineStr"/>
+      <c r="X391" t="inlineStr"/>
+      <c r="Y391" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z391" t="inlineStr"/>
+      <c r="AA391" t="inlineStr">
+        <is>
           <t>(504) 522-4451</t>
         </is>
       </c>
-      <c r="AB383" t="inlineStr">
+      <c r="AB391" t="inlineStr">
         <is>
           <t>https://instagram.com/quarter_stitch, https://facebook.com/TheQuarterStitch</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB383"/>
+  <autoFilter ref="A1:AB391"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId2"/>
@@ -44716,6 +45588,30 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I383" r:id="rId1324"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q383" r:id="rId1325"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T383" r:id="rId1326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I384" r:id="rId1327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q384" r:id="rId1328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T384" r:id="rId1329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I385" r:id="rId1330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q385" r:id="rId1331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T385" r:id="rId1332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I386" r:id="rId1333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q386" r:id="rId1334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T386" r:id="rId1335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I387" r:id="rId1336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q387" r:id="rId1337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T387" r:id="rId1338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I388" r:id="rId1339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q388" r:id="rId1340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T388" r:id="rId1341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I389" r:id="rId1342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q389" r:id="rId1343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T389" r:id="rId1344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I390" r:id="rId1345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q390" r:id="rId1346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T390" r:id="rId1347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I391" r:id="rId1348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q391" r:id="rId1349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T391" r:id="rId1350"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -44783,7 +45679,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="C2" t="n">
         <v>36</v>
@@ -44999,7 +45895,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C10" t="n">
         <v>11</v>
@@ -45269,7 +46165,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C20" t="n">
         <v>5</v>
@@ -45296,14 +46192,14 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C21" t="n">
         <v>4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -45350,14 +46246,14 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C23" t="n">
         <v>6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -45458,14 +46354,14 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="C27" t="n">
         <v>5</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -45485,21 +46381,21 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -45512,7 +46408,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -45539,7 +46435,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C30" t="n">
         <v>2</v>
@@ -45566,18 +46462,18 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F31" t="n">
         <v>1</v>
@@ -45593,7 +46489,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>198</v>
+        <v>238</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -45620,14 +46516,14 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>110</v>
+        <v>167</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -45647,18 +46543,18 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -45674,7 +46570,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -45701,7 +46597,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -45728,7 +46624,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C37" t="n">
         <v>2</v>
@@ -45755,7 +46651,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -45782,21 +46678,21 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -45809,18 +46705,18 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40" t="n">
         <v>1</v>
@@ -45836,7 +46732,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C41" t="n">
         <v>2</v>
@@ -45863,7 +46759,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -45890,18 +46786,18 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -45917,18 +46813,18 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -45944,7 +46840,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
@@ -45971,14 +46867,14 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C46" t="n">
         <v>5</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -45998,21 +46894,21 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>14836</v>
+        <v>14993</v>
       </c>
       <c r="C47" t="n">
+        <v>390</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
         <v>382</v>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>374</v>
-      </c>
       <c r="F47" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G47" t="n">
         <v>94</v>
@@ -46055,7 +46951,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3">
@@ -46065,7 +46961,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4">
@@ -46107,7 +47003,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9">
@@ -46127,7 +47023,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11">
@@ -46166,7 +47062,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T13:02:00+05:30</t>
+          <t>2026-10-14T13:22:36+05:30</t>
         </is>
       </c>
     </row>
@@ -46177,7 +47073,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>382</v>
+        <v>390</v>
       </c>
     </row>
     <row r="3">
@@ -46187,7 +47083,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>14836</v>
+        <v>14993</v>
       </c>
     </row>
     <row r="4">

--- a/leadrun_jewelry/jewelry_qualified.xlsx
+++ b/leadrun_jewelry/jewelry_qualified.xlsx
@@ -50098,7 +50098,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C37" t="n">
         <v>2</v>
@@ -50368,7 +50368,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>15332</v>
+        <v>15339</v>
       </c>
       <c r="C47" t="n">
         <v>421</v>
@@ -50536,7 +50536,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T14:09:05+05:30</t>
+          <t>2026-10-14T14:15:45+05:30</t>
         </is>
       </c>
     </row>
@@ -50557,7 +50557,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>15332</v>
+        <v>15339</v>
       </c>
     </row>
     <row r="4">

--- a/leadrun_jewelry/jewelry_qualified.xlsx
+++ b/leadrun_jewelry/jewelry_qualified.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qualified Leads'!$A$1:$AB$422</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qualified Leads'!$A$1:$AB$423</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB422"/>
+  <dimension ref="A1:AB423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -26281,7 +26281,7 @@
         </is>
       </c>
       <c r="Y230" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Z230" t="inlineStr">
         <is>
@@ -42122,76 +42122,80 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Ari Diamonds</t>
+          <t>Trade Shop</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Jewelers, Diamonds-Wholesale, Jewelers-Wholesale &amp; Manufacturers</t>
+          <t>Jewelry Stores</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>(801) 255-8992</t>
+          <t>(503) 251-5988</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>panna.aridiamonds@gmail.com</t>
+          <t>info@tradeshop.com</t>
         </is>
       </c>
       <c r="F372" t="inlineStr"/>
-      <c r="G372" t="inlineStr"/>
-      <c r="H372" t="inlineStr"/>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>Beth Scott</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
       <c r="I372" s="2" t="inlineStr">
         <is>
-          <t>https://www.aridiamonds.com</t>
+          <t>https://www.tradeshop.com</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>807 E Fort Union Blvd, Midvale, UT 84047</t>
+          <t>534 SW 3rd Ave Ste 320, Portland, OR 97204-2517</t>
         </is>
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t>Midvale</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>UT</t>
+          <t>OR</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT</t>
+          <t>Portland, OR</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
         <is>
-          <t>YellowPages</t>
-        </is>
-      </c>
-      <c r="O372" t="n">
-        <v>5</v>
-      </c>
-      <c r="P372" t="n">
-        <v>6</v>
-      </c>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr"/>
+      <c r="P372" t="inlineStr"/>
       <c r="Q372" s="2" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.com/midvale-ut/mip/ari-diamonds-23948160</t>
+          <t>https://www.bbb.org/us/or/portland/profile/jewelry-stores/trade-shop-1296-74002609</t>
         </is>
       </c>
       <c r="R372" t="inlineStr">
         <is>
-          <t>2 of 3, direct-line, custom-design, since-1994</t>
+          <t>2 of 3, role-email, direct-line, ags, since-1997</t>
         </is>
       </c>
       <c r="S372" t="inlineStr">
@@ -42201,82 +42205,78 @@
       </c>
       <c r="T372" s="2" t="inlineStr">
         <is>
-          <t>https://www.aridiamonds.com/</t>
+          <t>https://www.tradeshop.com/</t>
         </is>
       </c>
       <c r="U372" t="inlineStr"/>
       <c r="V372" t="inlineStr">
         <is>
-          <t>2026-10-14T12:03:18+05:30</t>
+          <t>2026-10-14T14:20:45+05:30</t>
         </is>
       </c>
       <c r="W372" t="inlineStr"/>
       <c r="X372" t="inlineStr"/>
       <c r="Y372" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z372" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Z372" t="inlineStr">
+        <is>
+          <t>shared-switchboard</t>
+        </is>
+      </c>
       <c r="AA372" t="inlineStr">
         <is>
-          <t>(801) 776-8830</t>
+          <t>(940) 400-1976</t>
         </is>
       </c>
       <c r="AB372" t="inlineStr">
         <is>
-          <t>https://instagram.com/aridiamondsutah, https://facebook.com/aridiamonds</t>
+          <t>https://facebook.com/profile.php?id=61552692278402, https://x.com/tradeshopcc, https://instagram.com/tradeshopcc</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>O.C. Tanner Jewelers</t>
+          <t>Ari Diamonds</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Jewelry retailer</t>
+          <t>Custom / bespoke jeweler</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Jewelry store</t>
+          <t>Jewelers, Diamonds-Wholesale, Jewelers-Wholesale &amp; Manufacturers</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>(801) 532-3222</t>
+          <t>(801) 255-8992</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>concierge@octanner.com</t>
+          <t>panna.aridiamonds@gmail.com</t>
         </is>
       </c>
       <c r="F373" t="inlineStr"/>
-      <c r="G373" t="inlineStr">
-        <is>
-          <t>Alex Hughes</t>
-        </is>
-      </c>
-      <c r="H373" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
+      <c r="G373" t="inlineStr"/>
+      <c r="H373" t="inlineStr"/>
       <c r="I373" s="2" t="inlineStr">
         <is>
-          <t>https://www.octannerjewelers.com</t>
+          <t>https://www.aridiamonds.com</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>15 S State St, Salt Lake City, UT 84111, United States</t>
+          <t>807 E Fort Union Blvd, Midvale, UT 84047</t>
         </is>
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t>Park City</t>
+          <t>Midvale</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
@@ -42291,23 +42291,23 @@
       </c>
       <c r="N373" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>YellowPages</t>
         </is>
       </c>
       <c r="O373" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="P373" t="n">
-        <v>189</v>
+        <v>6</v>
       </c>
       <c r="Q373" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/O.C.+Tanner+Jewelers/data=!4m7!3m6!1s0x8752f5094f69860b:0xbb7505c9581ba1b7!8m2!3d40.7688102!4d-111.8877533!16s%2Fg%2F1wk6_7j7!19sChIJC4ZpTwn1UocRt6EbWMkFdbs</t>
+          <t>https://www.yellowpages.com/midvale-ut/mip/ari-diamonds-23948160</t>
         </is>
       </c>
       <c r="R373" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, bench, since-1927</t>
+          <t>2 of 3, direct-line, custom-design, since-1994</t>
         </is>
       </c>
       <c r="S373" t="inlineStr">
@@ -42317,13 +42317,13 @@
       </c>
       <c r="T373" s="2" t="inlineStr">
         <is>
-          <t>https://octannerjewelers.localsearch.com/</t>
+          <t>https://www.aridiamonds.com/</t>
         </is>
       </c>
       <c r="U373" t="inlineStr"/>
       <c r="V373" t="inlineStr">
         <is>
-          <t>2026-10-14T13:10:29+05:30</t>
+          <t>2026-10-14T12:03:18+05:30</t>
         </is>
       </c>
       <c r="W373" t="inlineStr"/>
@@ -42334,24 +42334,24 @@
       <c r="Z373" t="inlineStr"/>
       <c r="AA373" t="inlineStr">
         <is>
-          <t>(435) 940-9470</t>
+          <t>(801) 776-8830</t>
         </is>
       </c>
       <c r="AB373" t="inlineStr">
         <is>
-          <t>https://facebook.com/octannerjewelers, https://instagram.com/octannerjewelers, https://twitter.com/examplejewelers</t>
+          <t>https://instagram.com/aridiamondsutah, https://facebook.com/aridiamonds</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Noble House Jewelry</t>
+          <t>O.C. Tanner Jewelers</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Custom / bespoke jeweler</t>
+          <t>Jewelry retailer</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -42361,32 +42361,48 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>(913) 491-4861</t>
+          <t>(801) 532-3222</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>info@noblehousejewelry.com</t>
+          <t>concierge@octanner.com</t>
         </is>
       </c>
       <c r="F374" t="inlineStr"/>
-      <c r="G374" t="inlineStr"/>
-      <c r="H374" t="inlineStr"/>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>Alex Hughes</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="I374" s="2" t="inlineStr">
         <is>
-          <t>https://www.noblehousejewelry.com</t>
+          <t>https://www.octannerjewelers.com</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>11620 Metcalf Ave, Overland Park, KS 66210, United States</t>
-        </is>
-      </c>
-      <c r="K374" t="inlineStr"/>
-      <c r="L374" t="inlineStr"/>
+          <t>15 S State St, Salt Lake City, UT 84111, United States</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Park City</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Kansas City, MO</t>
+          <t>Salt Lake City, UT</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -42395,19 +42411,19 @@
         </is>
       </c>
       <c r="O374" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="P374" t="n">
-        <v>318</v>
+        <v>189</v>
       </c>
       <c r="Q374" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Noble+House+Jewelry/data=!4m7!3m6!1s0x87c0ea6a64e64a13:0x405006847d2a827f!8m2!3d38.916106!4d-94.669196!16s%2Fg%2F1tmcmrv2!19sChIJE0rmZGrqwIcRf4IqfYQGUEA</t>
+          <t>https://www.google.com/maps/place/O.C.+Tanner+Jewelers/data=!4m7!3m6!1s0x8752f5094f69860b:0xbb7505c9581ba1b7!8m2!3d40.7688102!4d-111.8877533!16s%2Fg%2F1wk6_7j7!19sChIJC4ZpTwn1UocRt6EbWMkFdbs</t>
         </is>
       </c>
       <c r="R374" t="inlineStr">
         <is>
-          <t>2 of 3, role-email, direct-line, gia, bench, custom-design</t>
+          <t>2 of 3, role-email, direct-line, bench, since-1927</t>
         </is>
       </c>
       <c r="S374" t="inlineStr">
@@ -42417,36 +42433,36 @@
       </c>
       <c r="T374" s="2" t="inlineStr">
         <is>
-          <t>https://www.noblehousejewelry.com/</t>
+          <t>https://octannerjewelers.localsearch.com/</t>
         </is>
       <